--- a/audits/FORTLESS_MASTER_SECURITY_UI_BUG_TRACKER.xlsx
+++ b/audits/FORTLESS_MASTER_SECURITY_UI_BUG_TRACKER.xlsx
@@ -2,13 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Findings" sheetId="1" r:id="Ra3a5dbe249104833"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="2" r:id="R90d3d1708bb74a7a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audit Coverage" sheetId="3" r:id="Rdfc7644eca3241cf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Push History" sheetId="4" r:id="Rc3759e6a874b4c5a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Status History" sheetId="5" r:id="R1d4e5e9505da4b79"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ideas Separate" sheetId="6" r:id="R489c39e9a29c434c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="How To Update" sheetId="7" r:id="Rd50d91fb8c79463d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Findings" sheetId="1" r:id="R1d6ec6185841420d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="2" r:id="Rc951f5f95f5f4319"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audit Coverage" sheetId="3" r:id="R47ae13c680fa4d4c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Push History" sheetId="4" r:id="R1f137a69bd2f4a61"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Status History" sheetId="5" r:id="R151a16a584ca4237"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ideas Separate" sheetId="6" r:id="R6c7e1f089c3045b1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="How To Update" sheetId="7" r:id="R7acc59c623d84553"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MFA Policy" sheetId="8" r:id="R66035a945ea541ab"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Release Gates" sheetId="9" r:id="R20d1a623fa8a4960"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -19,7 +21,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="15">
+  <x:fonts count="16">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -104,8 +106,14 @@
       <x:color rgb="FFFFFFFF"/>
       <x:name val="Carlito"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="14"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="11">
+  <x:fills count="13">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -157,6 +165,16 @@
         <x:fgColor rgb="FFF8FAFD"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF142235"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF1D4254"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="2">
     <x:border/>
@@ -165,7 +183,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="73">
+  <x:cellXfs count="77">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -287,6 +305,10 @@
     <x:xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="15" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="8" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -350,35 +372,35 @@
     </x:dxf>
     <x:dxf>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFEE2E2"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
     <x:dxf>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF1D6"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
     <x:dxf>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFF3E8FF"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
     <x:dxf>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDBEAFE"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
     <x:dxf>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFE0F7E9"/>
         </x:patternFill>
       </x:fill>
@@ -668,7 +690,7 @@
     </x:row>
     <x:row r="2" ht="28" customHeight="1">
       <x:c r="A2" s="7" t="str">
-        <x:v>MASTER TRACKER  •  6203687 HEAD rechecked 19 Oct 2026  •  11 added findings  •  fixes still require independent tests</x:v>
+        <x:v>MASTER TRACKER  •  b929281 rechecked 19 Oct 2026  •  9 new defects; production validation still pending</x:v>
       </x:c>
       <x:c r="B2" s="7"/>
       <x:c r="C2" s="7"/>
@@ -934,7 +956,7 @@
         <x:v>Pending MFA challenges have an overly long lifetime and per-session attempt accounting</x:v>
       </x:c>
       <x:c r="F7" s="18" t="str">
-        <x:v>PARTIAL</x:v>
+        <x:v>FIXED_IN_CODE</x:v>
       </x:c>
       <x:c r="G7" s="18" t="str">
         <x:v>2026-10-19</x:v>
@@ -943,10 +965,10 @@
         <x:v>2026-10-19</x:v>
       </x:c>
       <x:c r="I7" s="18" t="str">
-        <x:v>9dacfcb</x:v>
+        <x:v>b929281</x:v>
       </x:c>
       <x:c r="J7" s="18" t="str">
-        <x:v>6203687</x:v>
+        <x:v>b929281</x:v>
       </x:c>
       <x:c r="K7" s="18" t="str"/>
       <x:c r="L7" s="18" t="str">
@@ -969,7 +991,7 @@
         <x:v>Coding AI</x:v>
       </x:c>
       <x:c r="S7" s="18" t="str">
-        <x:v>Pending MFA 15-min limit added; per-user attempt reset issue remains FTL-SEC-202</x:v>
+        <x:v>Pending MFA 15-min limit added; per-user attempt reset issue remains FTL-SEC-202 | b929281: Pending-MFA 15-min TTL and account-wide failures in auth.ts; requires runtime test.</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="66" customHeight="1">
@@ -1668,7 +1690,7 @@
         <x:v>Existing TOTP can be silently replaced with an unconfirmed factor</x:v>
       </x:c>
       <x:c r="F21" s="18" t="str">
-        <x:v>OPEN</x:v>
+        <x:v>FIXED_IN_CODE</x:v>
       </x:c>
       <x:c r="G21" s="18" t="str">
         <x:v>2026-10-19</x:v>
@@ -1677,10 +1699,10 @@
         <x:v>2026-10-19</x:v>
       </x:c>
       <x:c r="I21" s="18" t="str">
-        <x:v>6203687</x:v>
+        <x:v>b929281</x:v>
       </x:c>
       <x:c r="J21" s="18" t="str">
-        <x:v>6203687</x:v>
+        <x:v>b929281</x:v>
       </x:c>
       <x:c r="K21" s="18" t="str">
         <x:v>src/modules/identity/auth.ts, src/server.ts</x:v>
@@ -1706,7 +1728,9 @@
       <x:c r="R21" s="18" t="str">
         <x:v>Coding AI</x:v>
       </x:c>
-      <x:c r="S21" s="18" t="str"/>
+      <x:c r="S21" s="18" t="str">
+        <x:v>| b929281: Confirmed factor remains active; pending_secret_encrypted used for replacement.</x:v>
+      </x:c>
     </x:row>
     <x:row r="22" ht="66" customHeight="1">
       <x:c r="A22" s="18" t="str">
@@ -1725,7 +1749,7 @@
         <x:v>Global MFA attempt limit resets on same-device relogin</x:v>
       </x:c>
       <x:c r="F22" s="18" t="str">
-        <x:v>OPEN</x:v>
+        <x:v>FIXED_IN_CODE</x:v>
       </x:c>
       <x:c r="G22" s="18" t="str">
         <x:v>2026-10-19</x:v>
@@ -1734,10 +1758,10 @@
         <x:v>2026-10-19</x:v>
       </x:c>
       <x:c r="I22" s="18" t="str">
-        <x:v>6203687</x:v>
+        <x:v>b929281</x:v>
       </x:c>
       <x:c r="J22" s="18" t="str">
-        <x:v>6203687</x:v>
+        <x:v>b929281</x:v>
       </x:c>
       <x:c r="K22" s="18" t="str">
         <x:v>src/modules/identity/auth.ts</x:v>
@@ -1763,7 +1787,9 @@
       <x:c r="R22" s="18" t="str">
         <x:v>Coding AI</x:v>
       </x:c>
-      <x:c r="S22" s="18" t="str"/>
+      <x:c r="S22" s="18" t="str">
+        <x:v>| b929281: MFA failures now queried by user_id across all pending sessions.</x:v>
+      </x:c>
     </x:row>
     <x:row r="23" ht="66" customHeight="1">
       <x:c r="A23" s="18" t="str">
@@ -1782,7 +1808,7 @@
         <x:v>Recovery-code regeneration lacks sensitive-action reauthentication</x:v>
       </x:c>
       <x:c r="F23" s="18" t="str">
-        <x:v>OPEN</x:v>
+        <x:v>FIXED_IN_CODE</x:v>
       </x:c>
       <x:c r="G23" s="18" t="str">
         <x:v>2026-10-19</x:v>
@@ -1791,10 +1817,10 @@
         <x:v>2026-10-19</x:v>
       </x:c>
       <x:c r="I23" s="18" t="str">
-        <x:v>6203687</x:v>
+        <x:v>b929281</x:v>
       </x:c>
       <x:c r="J23" s="18" t="str">
-        <x:v>6203687</x:v>
+        <x:v>b929281</x:v>
       </x:c>
       <x:c r="K23" s="18" t="str">
         <x:v>src/server.ts, src/modules/identity/auth.ts</x:v>
@@ -1820,7 +1846,9 @@
       <x:c r="R23" s="18" t="str">
         <x:v>Coding AI</x:v>
       </x:c>
-      <x:c r="S23" s="18" t="str"/>
+      <x:c r="S23" s="18" t="str">
+        <x:v>| b929281: Recovery-code regeneration protected by requireRecentStepUp.</x:v>
+      </x:c>
     </x:row>
     <x:row r="24" ht="66" customHeight="1">
       <x:c r="A24" s="18" t="str">
@@ -1839,7 +1867,7 @@
         <x:v>Monthly Stripe plan for nonmonthly quote intervals</x:v>
       </x:c>
       <x:c r="F24" s="18" t="str">
-        <x:v>OPEN</x:v>
+        <x:v>PARTIAL</x:v>
       </x:c>
       <x:c r="G24" s="18" t="str">
         <x:v>2026-10-19</x:v>
@@ -1848,10 +1876,10 @@
         <x:v>2026-10-19</x:v>
       </x:c>
       <x:c r="I24" s="18" t="str">
-        <x:v>6203687</x:v>
+        <x:v>b929281</x:v>
       </x:c>
       <x:c r="J24" s="18" t="str">
-        <x:v>6203687</x:v>
+        <x:v>b929281</x:v>
       </x:c>
       <x:c r="K24" s="18" t="str">
         <x:v>src/modules/pricing/quote.ts, src/modules/checkout/checkout.ts</x:v>
@@ -1877,7 +1905,9 @@
       <x:c r="R24" s="18" t="str">
         <x:v>Coding AI</x:v>
       </x:c>
-      <x:c r="S24" s="18" t="str"/>
+      <x:c r="S24" s="18" t="str">
+        <x:v>| b929281: Stripe recurring interval mapped correctly; webhook still persists local subscriptions as MONTHLY.</x:v>
+      </x:c>
     </x:row>
     <x:row r="25" ht="66" customHeight="1">
       <x:c r="A25" s="18" t="str">
@@ -1896,7 +1926,7 @@
         <x:v>Refund/chargeback changes local service state without provider action</x:v>
       </x:c>
       <x:c r="F25" s="18" t="str">
-        <x:v>OPEN</x:v>
+        <x:v>PARTIAL</x:v>
       </x:c>
       <x:c r="G25" s="18" t="str">
         <x:v>2026-10-19</x:v>
@@ -1905,10 +1935,10 @@
         <x:v>2026-10-19</x:v>
       </x:c>
       <x:c r="I25" s="18" t="str">
-        <x:v>6203687</x:v>
+        <x:v>b929281</x:v>
       </x:c>
       <x:c r="J25" s="18" t="str">
-        <x:v>6203687</x:v>
+        <x:v>b929281</x:v>
       </x:c>
       <x:c r="K25" s="18" t="str">
         <x:v>src/modules/payments/webhooks.ts</x:v>
@@ -1934,7 +1964,9 @@
       <x:c r="R25" s="18" t="str">
         <x:v>Coding AI</x:v>
       </x:c>
-      <x:c r="S25" s="18" t="str"/>
+      <x:c r="S25" s="18" t="str">
+        <x:v>| b929281: Refund/dispute webhook enqueues suspend/terminate actions; staff refund path still bypasses PSP/provider.</x:v>
+      </x:c>
     </x:row>
     <x:row r="26" ht="66" customHeight="1">
       <x:c r="A26" s="18" t="str">
@@ -1953,7 +1985,7 @@
         <x:v>Distinct Stripe events for same payment can re-run fulfillment</x:v>
       </x:c>
       <x:c r="F26" s="18" t="str">
-        <x:v>OPEN</x:v>
+        <x:v>FIXED_IN_CODE</x:v>
       </x:c>
       <x:c r="G26" s="18" t="str">
         <x:v>2026-10-19</x:v>
@@ -1962,10 +1994,10 @@
         <x:v>2026-10-19</x:v>
       </x:c>
       <x:c r="I26" s="18" t="str">
-        <x:v>6203687</x:v>
+        <x:v>b929281</x:v>
       </x:c>
       <x:c r="J26" s="18" t="str">
-        <x:v>6203687</x:v>
+        <x:v>b929281</x:v>
       </x:c>
       <x:c r="K26" s="18" t="str">
         <x:v>src/modules/payments/webhooks.ts, src/database/schema.ts</x:v>
@@ -1991,7 +2023,9 @@
       <x:c r="R26" s="18" t="str">
         <x:v>Coding AI</x:v>
       </x:c>
-      <x:c r="S26" s="18" t="str"/>
+      <x:c r="S26" s="18" t="str">
+        <x:v>| b929281: Webhook checks payment_attempts.status/order.status before repeated fulfillment.</x:v>
+      </x:c>
     </x:row>
     <x:row r="27" ht="66" customHeight="1">
       <x:c r="A27" s="18" t="str">
@@ -2010,7 +2044,7 @@
         <x:v>Stripe PaymentIntent/refund/dispute correlation does not use actual Stripe IDs</x:v>
       </x:c>
       <x:c r="F27" s="18" t="str">
-        <x:v>OPEN</x:v>
+        <x:v>PARTIAL</x:v>
       </x:c>
       <x:c r="G27" s="18" t="str">
         <x:v>2026-10-19</x:v>
@@ -2019,10 +2053,10 @@
         <x:v>2026-10-19</x:v>
       </x:c>
       <x:c r="I27" s="18" t="str">
-        <x:v>6203687</x:v>
+        <x:v>b929281</x:v>
       </x:c>
       <x:c r="J27" s="18" t="str">
-        <x:v>6203687</x:v>
+        <x:v>b929281</x:v>
       </x:c>
       <x:c r="K27" s="18" t="str">
         <x:v>src/modules/checkout/checkout.ts, src/modules/payments/webhooks.ts, src/database/schema.ts</x:v>
@@ -2048,7 +2082,9 @@
       <x:c r="R27" s="18" t="str">
         <x:v>Coding AI</x:v>
       </x:c>
-      <x:c r="S27" s="18" t="str"/>
+      <x:c r="S27" s="18" t="str">
+        <x:v>| b929281: Real payment_intent IDs stored; invoice.paid settlement scopes invoices by account, not Stripe invoice.</x:v>
+      </x:c>
     </x:row>
     <x:row r="28" ht="66" customHeight="1">
       <x:c r="A28" s="18" t="str">
@@ -2067,7 +2103,7 @@
         <x:v>Subscription renewal flow not aligned with Stripe's auto-renewal</x:v>
       </x:c>
       <x:c r="F28" s="18" t="str">
-        <x:v>OPEN</x:v>
+        <x:v>PARTIAL</x:v>
       </x:c>
       <x:c r="G28" s="18" t="str">
         <x:v>2026-10-19</x:v>
@@ -2076,10 +2112,10 @@
         <x:v>2026-10-19</x:v>
       </x:c>
       <x:c r="I28" s="18" t="str">
-        <x:v>6203687</x:v>
+        <x:v>b929281</x:v>
       </x:c>
       <x:c r="J28" s="18" t="str">
-        <x:v>6203687</x:v>
+        <x:v>b929281</x:v>
       </x:c>
       <x:c r="K28" s="18" t="str">
         <x:v>src/modules/billing/renewal-dunning.ts, src/modules/payments/webhooks.ts</x:v>
@@ -2105,7 +2141,9 @@
       <x:c r="R28" s="18" t="str">
         <x:v>Coding AI</x:v>
       </x:c>
-      <x:c r="S28" s="18" t="str"/>
+      <x:c r="S28" s="18" t="str">
+        <x:v>| b929281: Stripe subscriptions exempted from local dunning; invoice.paid wrongly settles all account invoices.</x:v>
+      </x:c>
     </x:row>
     <x:row r="29" ht="66" customHeight="1">
       <x:c r="A29" s="18" t="str">
@@ -2181,7 +2219,7 @@
         <x:v>Worker uses one global provider for all service types</x:v>
       </x:c>
       <x:c r="F30" s="18" t="str">
-        <x:v>OPEN</x:v>
+        <x:v>PARTIAL</x:v>
       </x:c>
       <x:c r="G30" s="18" t="str">
         <x:v>2026-10-19</x:v>
@@ -2190,10 +2228,10 @@
         <x:v>2026-10-19</x:v>
       </x:c>
       <x:c r="I30" s="18" t="str">
-        <x:v>6203687</x:v>
+        <x:v>b929281</x:v>
       </x:c>
       <x:c r="J30" s="18" t="str">
-        <x:v>6203687</x:v>
+        <x:v>b929281</x:v>
       </x:c>
       <x:c r="K30" s="18" t="str">
         <x:v>src/modules/outbox/worker.ts, src/modules/checkout/checkout.ts, src/modules/payments/webhooks.ts</x:v>
@@ -2219,7 +2257,9 @@
       <x:c r="R30" s="18" t="str">
         <x:v>Coding AI</x:v>
       </x:c>
-      <x:c r="S30" s="18" t="str"/>
+      <x:c r="S30" s="18" t="str">
+        <x:v>| b929281: Dispatch by provider_type added, but CPANEL/VPS dispatch still constructs mock adapters in worker.</x:v>
+      </x:c>
     </x:row>
     <x:row r="31" ht="66" customHeight="1">
       <x:c r="A31" s="18" t="str">
@@ -2238,7 +2278,7 @@
         <x:v>Hardcoded node fallback and no capacity-aware assignment on paid/free checkout</x:v>
       </x:c>
       <x:c r="F31" s="18" t="str">
-        <x:v>OPEN</x:v>
+        <x:v>PARTIAL</x:v>
       </x:c>
       <x:c r="G31" s="18" t="str">
         <x:v>2026-10-19</x:v>
@@ -2247,10 +2287,10 @@
         <x:v>2026-10-19</x:v>
       </x:c>
       <x:c r="I31" s="18" t="str">
-        <x:v>6203687</x:v>
+        <x:v>b929281</x:v>
       </x:c>
       <x:c r="J31" s="18" t="str">
-        <x:v>6203687</x:v>
+        <x:v>b929281</x:v>
       </x:c>
       <x:c r="K31" s="18" t="str">
         <x:v>src/modules/checkout/checkout.ts, src/modules/payments/webhooks.ts</x:v>
@@ -2276,7 +2316,9 @@
       <x:c r="R31" s="18" t="str">
         <x:v>Coding AI</x:v>
       </x:c>
-      <x:c r="S31" s="18" t="str"/>
+      <x:c r="S31" s="18" t="str">
+        <x:v>| b929281: Hardcoded node_fra_01 removed; fallback still chooses wrong region/no-capacity nodes.</x:v>
+      </x:c>
     </x:row>
     <x:row r="32" ht="66" customHeight="1">
       <x:c r="A32" s="18" t="str">
@@ -2295,7 +2337,7 @@
         <x:v>Capacity concurrency check is not atomic with reservation/update</x:v>
       </x:c>
       <x:c r="F32" s="18" t="str">
-        <x:v>OPEN</x:v>
+        <x:v>FIXED_IN_CODE</x:v>
       </x:c>
       <x:c r="G32" s="18" t="str">
         <x:v>2026-10-19</x:v>
@@ -2304,10 +2346,10 @@
         <x:v>2026-10-19</x:v>
       </x:c>
       <x:c r="I32" s="18" t="str">
-        <x:v>6203687</x:v>
+        <x:v>b929281</x:v>
       </x:c>
       <x:c r="J32" s="18" t="str">
-        <x:v>6203687</x:v>
+        <x:v>b929281</x:v>
       </x:c>
       <x:c r="K32" s="18" t="str">
         <x:v>src/modules/outbox/worker.ts</x:v>
@@ -2333,7 +2375,9 @@
       <x:c r="R32" s="18" t="str">
         <x:v>Coding AI</x:v>
       </x:c>
-      <x:c r="S32" s="18" t="str"/>
+      <x:c r="S32" s="18" t="str">
+        <x:v>| b929281: Worker now atomically reserves capacity with conditional UPDATE.</x:v>
+      </x:c>
     </x:row>
     <x:row r="33" ht="66" customHeight="1">
       <x:c r="A33" s="18" t="str">
@@ -2409,7 +2453,7 @@
         <x:v>Domain search is not external registrar availability</x:v>
       </x:c>
       <x:c r="F34" s="18" t="str">
-        <x:v>OPEN</x:v>
+        <x:v>PARTIAL</x:v>
       </x:c>
       <x:c r="G34" s="18" t="str">
         <x:v>2026-10-19</x:v>
@@ -2418,10 +2462,10 @@
         <x:v>2026-10-19</x:v>
       </x:c>
       <x:c r="I34" s="18" t="str">
-        <x:v>6203687</x:v>
+        <x:v>b929281</x:v>
       </x:c>
       <x:c r="J34" s="18" t="str">
-        <x:v>6203687</x:v>
+        <x:v>b929281</x:v>
       </x:c>
       <x:c r="K34" s="18" t="str">
         <x:v>src/modules/domains/dns.ts</x:v>
@@ -2445,7 +2489,9 @@
       <x:c r="R34" s="18" t="str">
         <x:v>Coding AI</x:v>
       </x:c>
-      <x:c r="S34" s="18" t="str"/>
+      <x:c r="S34" s="18" t="str">
+        <x:v>| b929281: Search discloses LOCAL_ZONE_AVAILABLE, but still returns available:true without registrar check.</x:v>
+      </x:c>
     </x:row>
     <x:row r="35" ht="66" customHeight="1">
       <x:c r="A35" s="18" t="str">
@@ -2464,7 +2510,7 @@
         <x:v>Locally created zone advertised ACTIVE without DNS authority proof</x:v>
       </x:c>
       <x:c r="F35" s="18" t="str">
-        <x:v>OPEN</x:v>
+        <x:v>PARTIAL</x:v>
       </x:c>
       <x:c r="G35" s="18" t="str">
         <x:v>2026-10-19</x:v>
@@ -2473,10 +2519,10 @@
         <x:v>2026-10-19</x:v>
       </x:c>
       <x:c r="I35" s="18" t="str">
-        <x:v>6203687</x:v>
+        <x:v>b929281</x:v>
       </x:c>
       <x:c r="J35" s="18" t="str">
-        <x:v>6203687</x:v>
+        <x:v>b929281</x:v>
       </x:c>
       <x:c r="K35" s="18" t="str">
         <x:v>src/modules/domains/dns.ts</x:v>
@@ -2502,7 +2548,9 @@
       <x:c r="R35" s="18" t="str">
         <x:v>Coding AI</x:v>
       </x:c>
-      <x:c r="S35" s="18" t="str"/>
+      <x:c r="S35" s="18" t="str">
+        <x:v>| b929281: Zone has pending/delegation distinction; authoritative DNS/registrar integration not verified.</x:v>
+      </x:c>
     </x:row>
     <x:row r="36" ht="66" customHeight="1">
       <x:c r="A36" s="18" t="str">
@@ -2521,7 +2569,7 @@
         <x:v>Recovery-code entropy only ~32 bits, fast hash</x:v>
       </x:c>
       <x:c r="F36" s="18" t="str">
-        <x:v>OPEN</x:v>
+        <x:v>FIXED_IN_CODE</x:v>
       </x:c>
       <x:c r="G36" s="18" t="str">
         <x:v>2026-10-19</x:v>
@@ -2530,10 +2578,10 @@
         <x:v>2026-10-19</x:v>
       </x:c>
       <x:c r="I36" s="18" t="str">
-        <x:v>6203687</x:v>
+        <x:v>b929281</x:v>
       </x:c>
       <x:c r="J36" s="18" t="str">
-        <x:v>6203687</x:v>
+        <x:v>b929281</x:v>
       </x:c>
       <x:c r="K36" s="18" t="str">
         <x:v>src/modules/identity/auth.ts</x:v>
@@ -2559,7 +2607,9 @@
       <x:c r="R36" s="18" t="str">
         <x:v>Coding AI</x:v>
       </x:c>
-      <x:c r="S36" s="18" t="str"/>
+      <x:c r="S36" s="18" t="str">
+        <x:v>| b929281: Recovery codes now 128-bit generated from randomBytes(16).</x:v>
+      </x:c>
     </x:row>
     <x:row r="37" ht="66" customHeight="1">
       <x:c r="A37" s="18" t="str">
@@ -2578,7 +2628,7 @@
         <x:v>Account-and-IP login throttle has no account-wide distributed limit</x:v>
       </x:c>
       <x:c r="F37" s="18" t="str">
-        <x:v>OPEN</x:v>
+        <x:v>FIXED_IN_CODE</x:v>
       </x:c>
       <x:c r="G37" s="18" t="str">
         <x:v>2026-10-19</x:v>
@@ -2587,10 +2637,10 @@
         <x:v>2026-10-19</x:v>
       </x:c>
       <x:c r="I37" s="18" t="str">
-        <x:v>6203687</x:v>
+        <x:v>b929281</x:v>
       </x:c>
       <x:c r="J37" s="18" t="str">
-        <x:v>6203687</x:v>
+        <x:v>b929281</x:v>
       </x:c>
       <x:c r="K37" s="18" t="str">
         <x:v>src/modules/identity/auth.ts</x:v>
@@ -2614,7 +2664,9 @@
       <x:c r="R37" s="18" t="str">
         <x:v>Coding AI</x:v>
       </x:c>
-      <x:c r="S37" s="18" t="str"/>
+      <x:c r="S37" s="18" t="str">
+        <x:v>| b929281: isLoginThrottled now counts 10 failures account-wide independent of IP.</x:v>
+      </x:c>
     </x:row>
     <x:row r="38" ht="66" customHeight="1">
       <x:c r="A38" s="18" t="str">
@@ -2633,7 +2685,7 @@
         <x:v>Billing-only workspace user sees server power buttons</x:v>
       </x:c>
       <x:c r="F38" s="18" t="str">
-        <x:v>OPEN</x:v>
+        <x:v>FIXED_IN_CODE</x:v>
       </x:c>
       <x:c r="G38" s="18" t="str">
         <x:v>2026-10-19</x:v>
@@ -2642,10 +2694,10 @@
         <x:v>2026-10-19</x:v>
       </x:c>
       <x:c r="I38" s="18" t="str">
-        <x:v>6203687</x:v>
+        <x:v>b929281</x:v>
       </x:c>
       <x:c r="J38" s="18" t="str">
-        <x:v>6203687</x:v>
+        <x:v>b929281</x:v>
       </x:c>
       <x:c r="K38" s="18" t="str">
         <x:v>src/frontend/client/pages/dashboard/index.ts, src/modules/provisioning/service-access.ts</x:v>
@@ -2669,7 +2721,9 @@
       <x:c r="R38" s="18" t="str">
         <x:v>Coding AI</x:v>
       </x:c>
-      <x:c r="S38" s="18" t="str"/>
+      <x:c r="S38" s="18" t="str">
+        <x:v>| b929281: Service list checks user_can_control, detailed page checks explicit permissions; runtime E2E needed.</x:v>
+      </x:c>
     </x:row>
     <x:row r="39" ht="66" customHeight="1">
       <x:c r="A39" s="18" t="str">
@@ -2688,7 +2742,7 @@
         <x:v>Service detail renders Pterodactyl actions for incompatible provider types</x:v>
       </x:c>
       <x:c r="F39" s="18" t="str">
-        <x:v>OPEN</x:v>
+        <x:v>FIXED_IN_CODE</x:v>
       </x:c>
       <x:c r="G39" s="18" t="str">
         <x:v>2026-10-19</x:v>
@@ -2697,10 +2751,10 @@
         <x:v>2026-10-19</x:v>
       </x:c>
       <x:c r="I39" s="18" t="str">
-        <x:v>6203687</x:v>
+        <x:v>b929281</x:v>
       </x:c>
       <x:c r="J39" s="18" t="str">
-        <x:v>6203687</x:v>
+        <x:v>b929281</x:v>
       </x:c>
       <x:c r="K39" s="18" t="str">
         <x:v>src/frontend/client/pages/services/index.ts</x:v>
@@ -2724,7 +2778,9 @@
       <x:c r="R39" s="18" t="str">
         <x:v>Coding AI</x:v>
       </x:c>
-      <x:c r="S39" s="18" t="str"/>
+      <x:c r="S39" s="18" t="str">
+        <x:v>| b929281: Service details filter provider tabs by capabilities and permissions.</x:v>
+      </x:c>
     </x:row>
     <x:row r="40" ht="66" customHeight="1">
       <x:c r="A40" s="18" t="str">
@@ -2743,7 +2799,7 @@
         <x:v>Route navigation is not race-safe for async page loaders</x:v>
       </x:c>
       <x:c r="F40" s="18" t="str">
-        <x:v>OPEN</x:v>
+        <x:v>PARTIAL</x:v>
       </x:c>
       <x:c r="G40" s="18" t="str">
         <x:v>2026-10-19</x:v>
@@ -2752,10 +2808,10 @@
         <x:v>2026-10-19</x:v>
       </x:c>
       <x:c r="I40" s="18" t="str">
-        <x:v>6203687</x:v>
+        <x:v>b929281</x:v>
       </x:c>
       <x:c r="J40" s="18" t="str">
-        <x:v>6203687</x:v>
+        <x:v>b929281</x:v>
       </x:c>
       <x:c r="K40" s="18" t="str">
         <x:v>src/frontend/core/router/router.ts</x:v>
@@ -2781,7 +2837,9 @@
       <x:c r="R40" s="18" t="str">
         <x:v>Coding AI</x:v>
       </x:c>
-      <x:c r="S40" s="18" t="str"/>
+      <x:c r="S40" s="18" t="str">
+        <x:v>| b929281: Router has sequence and AbortController; async page fetches do not consistently use signal guard.</x:v>
+      </x:c>
     </x:row>
     <x:row r="41" ht="66" customHeight="1">
       <x:c r="A41" s="18" t="str">
@@ -2800,7 +2858,7 @@
         <x:v>Canonical visual QA checks 22 routes, omits 2 required views</x:v>
       </x:c>
       <x:c r="F41" s="18" t="str">
-        <x:v>OPEN</x:v>
+        <x:v>PARTIAL</x:v>
       </x:c>
       <x:c r="G41" s="18" t="str">
         <x:v>2026-10-19</x:v>
@@ -2809,10 +2867,10 @@
         <x:v>2026-10-19</x:v>
       </x:c>
       <x:c r="I41" s="18" t="str">
-        <x:v>6203687</x:v>
+        <x:v>b929281</x:v>
       </x:c>
       <x:c r="J41" s="18" t="str">
-        <x:v>6203687</x:v>
+        <x:v>b929281</x:v>
       </x:c>
       <x:c r="K41" s="18" t="str">
         <x:v>scripts/verify-views.py</x:v>
@@ -2837,7 +2895,7 @@
         <x:v>Coding AI</x:v>
       </x:c>
       <x:c r="S41" s="18" t="str">
-        <x:v>22/24 routes covered by screenshot script, incomplete visual parity checks</x:v>
+        <x:v>22/24 routes covered by screenshot script, incomplete visual parity checks | b929281: 24 route definitions present in verify-views.py, but no authenticated fixture/pixel reference comparison.</x:v>
       </x:c>
     </x:row>
     <x:row r="42" ht="66" customHeight="1">
@@ -2866,10 +2924,10 @@
         <x:v>2026-10-19</x:v>
       </x:c>
       <x:c r="I42" s="18" t="str">
-        <x:v>6203687</x:v>
+        <x:v>b929281</x:v>
       </x:c>
       <x:c r="J42" s="18" t="str">
-        <x:v>6203687</x:v>
+        <x:v>b929281</x:v>
       </x:c>
       <x:c r="K42" s="18" t="str">
         <x:v>src/frontend/client/pages/dashboard/index.ts</x:v>
@@ -2893,7 +2951,9 @@
       <x:c r="R42" s="18" t="str">
         <x:v>Coding AI</x:v>
       </x:c>
-      <x:c r="S42" s="18" t="str"/>
+      <x:c r="S42" s="18" t="str">
+        <x:v>| b929281: Refresh renderServices catches API error internally, then caller still fires refreshed toast.</x:v>
+      </x:c>
     </x:row>
     <x:row r="43" ht="66" customHeight="1">
       <x:c r="A43" s="18" t="str">
@@ -2912,7 +2972,7 @@
         <x:v>Client power controls do not use runtime-action eligibility or live provider-specific state comprehensively</x:v>
       </x:c>
       <x:c r="F43" s="18" t="str">
-        <x:v>OPEN</x:v>
+        <x:v>PARTIAL</x:v>
       </x:c>
       <x:c r="G43" s="18" t="str">
         <x:v>2026-10-19</x:v>
@@ -2921,10 +2981,10 @@
         <x:v>2026-10-19</x:v>
       </x:c>
       <x:c r="I43" s="18" t="str">
-        <x:v>6203687</x:v>
+        <x:v>b929281</x:v>
       </x:c>
       <x:c r="J43" s="18" t="str">
-        <x:v>6203687</x:v>
+        <x:v>b929281</x:v>
       </x:c>
       <x:c r="K43" s="18" t="str">
         <x:v>src/frontend/client/pages/services/status.ts, src/frontend/client/pages/dashboard/index.ts, src/frontend/client/pages/services/index.ts</x:v>
@@ -2948,7 +3008,9 @@
       <x:c r="R43" s="18" t="str">
         <x:v>Coding AI</x:v>
       </x:c>
-      <x:c r="S43" s="18" t="str"/>
+      <x:c r="S43" s="18" t="str">
+        <x:v>| b929281: Buttons account for contract/runtime status but per-button action permission and provider feedback remain incomplete.</x:v>
+      </x:c>
     </x:row>
     <x:row r="44" ht="66" customHeight="1">
       <x:c r="A44" s="18" t="str">
@@ -4934,6 +4996,537 @@
       </x:c>
       <x:c r="S77" s="18" t="str">
         <x:v>UX inconsistency, not authorization bypass; protected route correctly denies navigation.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="78" ht="50" customHeight="1">
+      <x:c r="A78" s="66" t="str">
+        <x:v>NEW-330</x:v>
+      </x:c>
+      <x:c r="B78" s="66" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="C78" s="66" t="str">
+        <x:v>CRITICAL</x:v>
+      </x:c>
+      <x:c r="D78" s="66" t="str">
+        <x:v>Billing</x:v>
+      </x:c>
+      <x:c r="E78" s="66" t="str">
+        <x:v>Stripe invoice.paid can mark unrelated issued invoices paid</x:v>
+      </x:c>
+      <x:c r="F78" s="66" t="str">
+        <x:v>OPEN</x:v>
+      </x:c>
+      <x:c r="G78" s="66" t="str">
+        <x:v>2026-10-19</x:v>
+      </x:c>
+      <x:c r="H78" s="66" t="str">
+        <x:v>2026-10-19</x:v>
+      </x:c>
+      <x:c r="I78" s="66" t="str">
+        <x:v>b929281</x:v>
+      </x:c>
+      <x:c r="J78" s="66" t="str">
+        <x:v>b929281</x:v>
+      </x:c>
+      <x:c r="K78" s="66" t="str">
+        <x:v>src/modules/payments/webhooks.ts:218-245</x:v>
+      </x:c>
+      <x:c r="L78" s="66" t="str">
+        <x:v>invoice.paid resolves a subscription, then UPDATE invoices SET status='PAID' WHERE account_id=? AND status='ISSUED'; no Stripe invoice ID or amount is joined.</x:v>
+      </x:c>
+      <x:c r="M78" s="66" t="str">
+        <x:v>One successful renewal may falsely settle every other open issued invoice for that account.</x:v>
+      </x:c>
+      <x:c r="N78" s="66" t="str">
+        <x:v>Persist and uniquely map Stripe invoice ID and payment to ONE Fortless invoice/subscription; validate money/currency and idempotence, never bulk-settle by account.</x:v>
+      </x:c>
+      <x:c r="O78" s="66" t="str">
+        <x:v>Create 2 active subscriptions plus 3 issued invoices for same account; paying only one must update exactly its matching invoice.</x:v>
+      </x:c>
+      <x:c r="P78" s="66" t="str">
+        <x:v>FORTLESS_AUDIT_BOUNTY_b929281.md</x:v>
+      </x:c>
+      <x:c r="Q78" s="66" t="str">
+        <x:v>https://github.com/trencito42/fortless/blob/b9292811a22159a28a7159deee2c7ff27f41a873/src/modules/payments/webhooks.ts</x:v>
+      </x:c>
+      <x:c r="R78" s="66" t="str">
+        <x:v>Coding AI</x:v>
+      </x:c>
+      <x:c r="S78" s="66" t="str">
+        <x:v>New code finding; verified statically, no authorized runtime exploit or E2E validation.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="79" ht="50" customHeight="1">
+      <x:c r="A79" s="66" t="str">
+        <x:v>NEW-331</x:v>
+      </x:c>
+      <x:c r="B79" s="66" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="C79" s="66" t="str">
+        <x:v>HIGH</x:v>
+      </x:c>
+      <x:c r="D79" s="66" t="str">
+        <x:v>Authorization</x:v>
+      </x:c>
+      <x:c r="E79" s="66" t="str">
+        <x:v>TECH_ADMIN can invite a new workspace OWNER</x:v>
+      </x:c>
+      <x:c r="F79" s="66" t="str">
+        <x:v>OPEN</x:v>
+      </x:c>
+      <x:c r="G79" s="66" t="str">
+        <x:v>2026-10-19</x:v>
+      </x:c>
+      <x:c r="H79" s="66" t="str">
+        <x:v>2026-10-19</x:v>
+      </x:c>
+      <x:c r="I79" s="66" t="str">
+        <x:v>b929281</x:v>
+      </x:c>
+      <x:c r="J79" s="66" t="str">
+        <x:v>b929281</x:v>
+      </x:c>
+      <x:c r="K79" s="66" t="str">
+        <x:v>src/modules/identity/teams.ts:69-123; src/server.ts:1020-1043</x:v>
+      </x:c>
+      <x:c r="L79" s="66" t="str">
+        <x:v>inviteAccountMember permits OWNER or TECH_ADMIN as inviter; accepts unrestricted requested role including OWNER; API exposes OWNER to TECH_ADMIN.</x:v>
+      </x:c>
+      <x:c r="M79" s="66" t="str">
+        <x:v>A technical admin can grant highest workspace privileges via email invitation.</x:v>
+      </x:c>
+      <x:c r="N79" s="66" t="str">
+        <x:v>Only existing OWNER may invite/assign OWNER; enforce role-grant ceiling inside service function, not only frontend; require recent step-up for ownership changes.</x:v>
+      </x:c>
+      <x:c r="O79" s="66" t="str">
+        <x:v>As TECH_ADMIN POST invite role OWNER returns 403; invites lower authorized roles still work; OWNER with step-up may invite OWNER.</x:v>
+      </x:c>
+      <x:c r="P79" s="66" t="str">
+        <x:v>FORTLESS_AUDIT_BOUNTY_b929281.md</x:v>
+      </x:c>
+      <x:c r="Q79" s="66" t="str">
+        <x:v>https://github.com/trencito42/fortless/blob/b9292811a22159a28a7159deee2c7ff27f41a873/src/modules/identity/teams.ts</x:v>
+      </x:c>
+      <x:c r="R79" s="66" t="str">
+        <x:v>Coding AI</x:v>
+      </x:c>
+      <x:c r="S79" s="66" t="str">
+        <x:v>New code finding; verified statically, no authorized runtime exploit or E2E validation.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="80" ht="50" customHeight="1">
+      <x:c r="A80" s="66" t="str">
+        <x:v>NEW-332</x:v>
+      </x:c>
+      <x:c r="B80" s="66" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="C80" s="66" t="str">
+        <x:v>HIGH</x:v>
+      </x:c>
+      <x:c r="D80" s="66" t="str">
+        <x:v>Provisioning</x:v>
+      </x:c>
+      <x:c r="E80" s="66" t="str">
+        <x:v>Live cPanel/VPS routes fall back to in-memory mock adapters</x:v>
+      </x:c>
+      <x:c r="F80" s="66" t="str">
+        <x:v>OPEN</x:v>
+      </x:c>
+      <x:c r="G80" s="66" t="str">
+        <x:v>2026-10-19</x:v>
+      </x:c>
+      <x:c r="H80" s="66" t="str">
+        <x:v>2026-10-19</x:v>
+      </x:c>
+      <x:c r="I80" s="66" t="str">
+        <x:v>b929281</x:v>
+      </x:c>
+      <x:c r="J80" s="66" t="str">
+        <x:v>b929281</x:v>
+      </x:c>
+      <x:c r="K80" s="66" t="str">
+        <x:v>src/modules/outbox/worker.ts:19-34; src/index.ts:44-93</x:v>
+      </x:c>
+      <x:c r="L80" s="66" t="str">
+        <x:v>getAdapterForService returns new MockCpanelAdapter/MockProxmoxAdapter for CPANEL/VPS. bootstrap configures only PterodactylHttpAdapter.</x:v>
+      </x:c>
+      <x:c r="M80" s="66" t="str">
+        <x:v>Order might be fulfilled with a fake remote resource; state shown in Fortless would not exist at provider.</x:v>
+      </x:c>
+      <x:c r="N80" s="66" t="str">
+        <x:v>Inject a provider registry with real configured CpanelHttpAdapter and ProxmoxHttpAdapter; fail closed when unavailable; isolate mocks strictly to test mode.</x:v>
+      </x:c>
+      <x:c r="O80" s="66" t="str">
+        <x:v>In production mode, no CPANEL/VPS event may instantiate Mock*Adapter; integration test checks real provider account/VM and reconciliation.</x:v>
+      </x:c>
+      <x:c r="P80" s="66" t="str">
+        <x:v>FORTLESS_AUDIT_BOUNTY_b929281.md</x:v>
+      </x:c>
+      <x:c r="Q80" s="66" t="str">
+        <x:v>https://github.com/trencito42/fortless/blob/b9292811a22159a28a7159deee2c7ff27f41a873/src/modules/outbox/worker.ts</x:v>
+      </x:c>
+      <x:c r="R80" s="66" t="str">
+        <x:v>Coding AI</x:v>
+      </x:c>
+      <x:c r="S80" s="66" t="str">
+        <x:v>New code finding; verified statically, no authorized runtime exploit or E2E validation.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="81" ht="50" customHeight="1">
+      <x:c r="A81" s="66" t="str">
+        <x:v>NEW-333</x:v>
+      </x:c>
+      <x:c r="B81" s="66" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="C81" s="66" t="str">
+        <x:v>HIGH</x:v>
+      </x:c>
+      <x:c r="D81" s="66" t="str">
+        <x:v>Billing</x:v>
+      </x:c>
+      <x:c r="E81" s="66" t="str">
+        <x:v>Fortless cancellation does not cancel Stripe subscription</x:v>
+      </x:c>
+      <x:c r="F81" s="66" t="str">
+        <x:v>OPEN</x:v>
+      </x:c>
+      <x:c r="G81" s="66" t="str">
+        <x:v>2026-10-19</x:v>
+      </x:c>
+      <x:c r="H81" s="66" t="str">
+        <x:v>2026-10-19</x:v>
+      </x:c>
+      <x:c r="I81" s="66" t="str">
+        <x:v>b929281</x:v>
+      </x:c>
+      <x:c r="J81" s="66" t="str">
+        <x:v>b929281</x:v>
+      </x:c>
+      <x:c r="K81" s="66" t="str">
+        <x:v>src/modules/billing/subscriptions.ts:56-132; src/server.ts:1810-1834</x:v>
+      </x:c>
+      <x:c r="L81" s="66" t="str">
+        <x:v>cancelSubscription sets CANCELED or CANCEL_SCHEDULED and auto_renew=0 in SQLite without calling Stripe cancellation/update.</x:v>
+      </x:c>
+      <x:c r="M81" s="66" t="str">
+        <x:v>Customer may see canceled hosting while Stripe keeps charging future invoices.</x:v>
+      </x:c>
+      <x:c r="N81" s="66" t="str">
+        <x:v>Use Stripe API idempotent cancellation at period end or immediate; record PSP state and reconcile asynchronously before final local state.</x:v>
+      </x:c>
+      <x:c r="O81" s="66" t="str">
+        <x:v>Cancel subscription at-period-end and immediate in Stripe test mode; verify Stripe state and Fortless state converge; handle PSP errors/retries.</x:v>
+      </x:c>
+      <x:c r="P81" s="66" t="str">
+        <x:v>FORTLESS_AUDIT_BOUNTY_b929281.md</x:v>
+      </x:c>
+      <x:c r="Q81" s="66" t="str">
+        <x:v>https://github.com/trencito42/fortless/blob/b9292811a22159a28a7159deee2c7ff27f41a873/src/modules/billing/subscriptions.ts</x:v>
+      </x:c>
+      <x:c r="R81" s="66" t="str">
+        <x:v>Coding AI</x:v>
+      </x:c>
+      <x:c r="S81" s="66" t="str">
+        <x:v>New code finding; verified statically, no authorized runtime exploit or E2E validation.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="82" ht="50" customHeight="1">
+      <x:c r="A82" s="66" t="str">
+        <x:v>NEW-334</x:v>
+      </x:c>
+      <x:c r="B82" s="66" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="C82" s="66" t="str">
+        <x:v>HIGH</x:v>
+      </x:c>
+      <x:c r="D82" s="66" t="str">
+        <x:v>Billing</x:v>
+      </x:c>
+      <x:c r="E82" s="66" t="str">
+        <x:v>Staff refund modifies local ledger but no PSP refund is made</x:v>
+      </x:c>
+      <x:c r="F82" s="66" t="str">
+        <x:v>OPEN</x:v>
+      </x:c>
+      <x:c r="G82" s="66" t="str">
+        <x:v>2026-10-19</x:v>
+      </x:c>
+      <x:c r="H82" s="66" t="str">
+        <x:v>2026-10-19</x:v>
+      </x:c>
+      <x:c r="I82" s="66" t="str">
+        <x:v>b929281</x:v>
+      </x:c>
+      <x:c r="J82" s="66" t="str">
+        <x:v>b929281</x:v>
+      </x:c>
+      <x:c r="K82" s="66" t="str">
+        <x:v>src/modules/payments/webhooks.ts:521-577; src/server.ts:1920-1950</x:v>
+      </x:c>
+      <x:c r="L82" s="66" t="str">
+        <x:v>processStaffRefund changes invoices and orders locally, calls no Stripe refund API and enqueues no provider teardown for full refunds.</x:v>
+      </x:c>
+      <x:c r="M82" s="66" t="str">
+        <x:v>Customer may be told funds were refunded without receiving money; servers may also remain running.</x:v>
+      </x:c>
+      <x:c r="N82" s="66" t="str">
+        <x:v>Create actual idempotent Stripe refund with PSP refund ID; settle credit note only after accepted/completed provider result and use lifecycle outbox for full refund.</x:v>
+      </x:c>
+      <x:c r="O82" s="66" t="str">
+        <x:v>Staff performs refund of €5: validate Stripe refund exists and amount, exact invoice ledger state, no double refund and service lifecycle matching policy.</x:v>
+      </x:c>
+      <x:c r="P82" s="66" t="str">
+        <x:v>FORTLESS_AUDIT_BOUNTY_b929281.md</x:v>
+      </x:c>
+      <x:c r="Q82" s="66" t="str">
+        <x:v>https://github.com/trencito42/fortless/blob/b9292811a22159a28a7159deee2c7ff27f41a873/src/modules/payments/webhooks.ts</x:v>
+      </x:c>
+      <x:c r="R82" s="66" t="str">
+        <x:v>Coding AI</x:v>
+      </x:c>
+      <x:c r="S82" s="66" t="str">
+        <x:v>New code finding; verified statically, no authorized runtime exploit or E2E validation.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="83" ht="50" customHeight="1">
+      <x:c r="A83" s="66" t="str">
+        <x:v>NEW-335</x:v>
+      </x:c>
+      <x:c r="B83" s="66" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="C83" s="66" t="str">
+        <x:v>HIGH</x:v>
+      </x:c>
+      <x:c r="D83" s="66" t="str">
+        <x:v>Billing</x:v>
+      </x:c>
+      <x:c r="E83" s="66" t="str">
+        <x:v>Multiple partial refunds subtract Stripe cumulative refunded amount repeatedly</x:v>
+      </x:c>
+      <x:c r="F83" s="66" t="str">
+        <x:v>OPEN</x:v>
+      </x:c>
+      <x:c r="G83" s="66" t="str">
+        <x:v>2026-10-19</x:v>
+      </x:c>
+      <x:c r="H83" s="66" t="str">
+        <x:v>2026-10-19</x:v>
+      </x:c>
+      <x:c r="I83" s="66" t="str">
+        <x:v>b929281</x:v>
+      </x:c>
+      <x:c r="J83" s="66" t="str">
+        <x:v>b929281</x:v>
+      </x:c>
+      <x:c r="K83" s="66" t="str">
+        <x:v>src/modules/payments/webhooks.ts:105-145</x:v>
+      </x:c>
+      <x:c r="L83" s="66" t="str">
+        <x:v>charge.refunded uses rawObj.amount_refunded (cumulative on charge) and subtracts it every distinct webhook event; no per-refund delta ledger.</x:v>
+      </x:c>
+      <x:c r="M83" s="66" t="str">
+        <x:v>Two separate partial refunds can overstate total refunded and understate amount paid.</x:v>
+      </x:c>
+      <x:c r="N83" s="66" t="str">
+        <x:v>Reconcile refundable amount via unique refund IDs and delta, or store previous cumulative refunded amount and apply positive difference only.</x:v>
+      </x:c>
+      <x:c r="O83" s="66" t="str">
+        <x:v>Sequential €2 then €3 refunds on €10 charge result in €5 total credited, not €7; replay/out-of-order events have no extra effect.</x:v>
+      </x:c>
+      <x:c r="P83" s="66" t="str">
+        <x:v>FORTLESS_AUDIT_BOUNTY_b929281.md</x:v>
+      </x:c>
+      <x:c r="Q83" s="66" t="str">
+        <x:v>https://github.com/trencito42/fortless/blob/b9292811a22159a28a7159deee2c7ff27f41a873/src/modules/payments/webhooks.ts</x:v>
+      </x:c>
+      <x:c r="R83" s="66" t="str">
+        <x:v>Coding AI</x:v>
+      </x:c>
+      <x:c r="S83" s="66" t="str">
+        <x:v>New code finding; verified statically, no authorized runtime exploit or E2E validation.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="84" ht="50" customHeight="1">
+      <x:c r="A84" s="66" t="str">
+        <x:v>NEW-336</x:v>
+      </x:c>
+      <x:c r="B84" s="66" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="C84" s="66" t="str">
+        <x:v>HIGH</x:v>
+      </x:c>
+      <x:c r="D84" s="66" t="str">
+        <x:v>Billing</x:v>
+      </x:c>
+      <x:c r="E84" s="66" t="str">
+        <x:v>Successful Stripe renewal does not unsuspend an overdue hosting service</x:v>
+      </x:c>
+      <x:c r="F84" s="66" t="str">
+        <x:v>OPEN</x:v>
+      </x:c>
+      <x:c r="G84" s="66" t="str">
+        <x:v>2026-10-19</x:v>
+      </x:c>
+      <x:c r="H84" s="66" t="str">
+        <x:v>2026-10-19</x:v>
+      </x:c>
+      <x:c r="I84" s="66" t="str">
+        <x:v>b929281</x:v>
+      </x:c>
+      <x:c r="J84" s="66" t="str">
+        <x:v>b929281</x:v>
+      </x:c>
+      <x:c r="K84" s="66" t="str">
+        <x:v>src/modules/payments/webhooks.ts:218-246; src/modules/billing/renewal-dunning.ts:235-273</x:v>
+      </x:c>
+      <x:c r="L84" s="66" t="str">
+        <x:v>invoice.paid flips subscription ACTIVE but does not invoke unsuspendService or enqueue reactivation after dunning suspension.</x:v>
+      </x:c>
+      <x:c r="M84" s="66" t="str">
+        <x:v>Customer remains unable to access paid service even after successful retry.</x:v>
+      </x:c>
+      <x:c r="N84" s="66" t="str">
+        <x:v>On matched successful renewal enqueue idempotent unsuspend/reconcile job only when service had been suspended for billing; verify provider state.</x:v>
+      </x:c>
+      <x:c r="O84" s="66" t="str">
+        <x:v>Simulate failed renewal -&gt; grace expiry -&gt; provider suspension -&gt; successful retry; service and provider become active exactly once.</x:v>
+      </x:c>
+      <x:c r="P84" s="66" t="str">
+        <x:v>FORTLESS_AUDIT_BOUNTY_b929281.md</x:v>
+      </x:c>
+      <x:c r="Q84" s="66" t="str">
+        <x:v>https://github.com/trencito42/fortless/blob/b9292811a22159a28a7159deee2c7ff27f41a873/src/modules/payments/webhooks.ts</x:v>
+      </x:c>
+      <x:c r="R84" s="66" t="str">
+        <x:v>Coding AI</x:v>
+      </x:c>
+      <x:c r="S84" s="66" t="str">
+        <x:v>New code finding; verified statically, no authorized runtime exploit or E2E validation.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="85" ht="50" customHeight="1">
+      <x:c r="A85" s="66" t="str">
+        <x:v>NEW-337</x:v>
+      </x:c>
+      <x:c r="B85" s="66" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="C85" s="66" t="str">
+        <x:v>MEDIUM</x:v>
+      </x:c>
+      <x:c r="D85" s="66" t="str">
+        <x:v>Provisioning</x:v>
+      </x:c>
+      <x:c r="E85" s="66" t="str">
+        <x:v>Dead-letter for termination incorrectly reclassifies service as SUSPENDED</x:v>
+      </x:c>
+      <x:c r="F85" s="66" t="str">
+        <x:v>OPEN</x:v>
+      </x:c>
+      <x:c r="G85" s="66" t="str">
+        <x:v>2026-10-19</x:v>
+      </x:c>
+      <x:c r="H85" s="66" t="str">
+        <x:v>2026-10-19</x:v>
+      </x:c>
+      <x:c r="I85" s="66" t="str">
+        <x:v>b929281</x:v>
+      </x:c>
+      <x:c r="J85" s="66" t="str">
+        <x:v>b929281</x:v>
+      </x:c>
+      <x:c r="K85" s="66" t="str">
+        <x:v>src/modules/outbox/worker.ts:145-183</x:v>
+      </x:c>
+      <x:c r="L85" s="66" t="str">
+        <x:v>Worker dead-letter handler unconditionally UPDATE services SET contract_status='SUSPENDED' and logs service.provision_failed for any event type, including service.terminate.v1.</x:v>
+      </x:c>
+      <x:c r="M85" s="66" t="str">
+        <x:v>Failed deletion can restore a terminated service to suspended, obscuring lifecycle and retry obligations.</x:v>
+      </x:c>
+      <x:c r="N85" s="66" t="str">
+        <x:v>Use event-type-specific failure states/audit; deletion failure must stay PENDING_TERMINATION/manual-review, never change to unrelated contract state.</x:v>
+      </x:c>
+      <x:c r="O85" s="66" t="str">
+        <x:v>Force termination provider failure 5 times: service not resurrected as SUSPENDED; actionable failed-delete state/alert remains.</x:v>
+      </x:c>
+      <x:c r="P85" s="66" t="str">
+        <x:v>FORTLESS_AUDIT_BOUNTY_b929281.md</x:v>
+      </x:c>
+      <x:c r="Q85" s="66" t="str">
+        <x:v>https://github.com/trencito42/fortless/blob/b9292811a22159a28a7159deee2c7ff27f41a873/src/modules/outbox/worker.ts</x:v>
+      </x:c>
+      <x:c r="R85" s="66" t="str">
+        <x:v>Coding AI</x:v>
+      </x:c>
+      <x:c r="S85" s="66" t="str">
+        <x:v>New code finding; verified statically, no authorized runtime exploit or E2E validation.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="86" ht="50" customHeight="1">
+      <x:c r="A86" s="66" t="str">
+        <x:v>NEW-338</x:v>
+      </x:c>
+      <x:c r="B86" s="66" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="C86" s="66" t="str">
+        <x:v>HIGH</x:v>
+      </x:c>
+      <x:c r="D86" s="66" t="str">
+        <x:v>Billing</x:v>
+      </x:c>
+      <x:c r="E86" s="66" t="str">
+        <x:v>Order-level Stripe subscription is duplicated across per-service records and amount</x:v>
+      </x:c>
+      <x:c r="F86" s="66" t="str">
+        <x:v>OPEN</x:v>
+      </x:c>
+      <x:c r="G86" s="66" t="str">
+        <x:v>2026-10-19</x:v>
+      </x:c>
+      <x:c r="H86" s="66" t="str">
+        <x:v>2026-10-19</x:v>
+      </x:c>
+      <x:c r="I86" s="66" t="str">
+        <x:v>b929281</x:v>
+      </x:c>
+      <x:c r="J86" s="66" t="str">
+        <x:v>b929281</x:v>
+      </x:c>
+      <x:c r="K86" s="66" t="str">
+        <x:v>src/modules/payments/webhooks.ts:375-462; src/modules/checkout/checkout.ts:198-229</x:v>
+      </x:c>
+      <x:c r="L86" s="66" t="str">
+        <x:v>Checkout creates one Stripe subscription for entire order; webhook inserts one local subscriptions record per service using identical Stripe subscription ID and full order amount as each service renewal_price.</x:v>
+      </x:c>
+      <x:c r="M86" s="66" t="str">
+        <x:v>Renewal totals, cancellations and support actions become ambiguous for multi-service order and may show exaggerated per-service prices.</x:v>
+      </x:c>
+      <x:c r="N86" s="66" t="str">
+        <x:v>Model one PSP subscription per order/invoice with service links and allocations OR one Stripe subscription item per service; persist correct interval and line-item price.</x:v>
+      </x:c>
+      <x:c r="O86" s="66" t="str">
+        <x:v>Buy 2 services in one checkout; one Stripe sub billed correct amount, individual service renewal prices sum to order, cancellation semantics unambiguous.</x:v>
+      </x:c>
+      <x:c r="P86" s="66" t="str">
+        <x:v>FORTLESS_AUDIT_BOUNTY_b929281.md</x:v>
+      </x:c>
+      <x:c r="Q86" s="66" t="str">
+        <x:v>https://github.com/trencito42/fortless/blob/b9292811a22159a28a7159deee2c7ff27f41a873/src/modules/payments/webhooks.ts</x:v>
+      </x:c>
+      <x:c r="R86" s="66" t="str">
+        <x:v>Coding AI</x:v>
+      </x:c>
+      <x:c r="S86" s="66" t="str">
+        <x:v>New code finding; verified statically, no authorized runtime exploit or E2E validation.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -5000,7 +5593,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra06e05c174ae46bb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0abc569929324744"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5033,7 +5626,7 @@
     </x:row>
     <x:row r="2" ht="29" customHeight="1">
       <x:c r="A2" s="7" t="str">
-        <x:v>Engineering control center · baseline 9dacfcb → 6203687 · additional review (same SHA) · 19 October 2026</x:v>
+        <x:v>Engineering control center · baseline 9dacfcb → b929281 · post-fix source review · 19 October 2026</x:v>
       </x:c>
       <x:c r="B2" s="7"/>
       <x:c r="C2" s="7"/>
@@ -5063,22 +5656,22 @@
     </x:row>
     <x:row r="5" ht="31" customHeight="1">
       <x:c r="A5" s="33" t="n">
-        <x:f>COUNTA(Findings!A4:A77)</x:f>
-        <x:v>74</x:v>
+        <x:f>COUNTA(Findings!A4:A86)</x:f>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B5" s="33"/>
       <x:c r="C5" s="33" t="n">
-        <x:f>COUNTIF(Findings!F4:F77,"OPEN")+COUNTIF(Findings!F4:F77,"REGRESSION")</x:f>
-        <x:v>51</x:v>
+        <x:f>COUNTIF(Findings!F4:F86,"OPEN")+COUNTIF(Findings!F4:F86,"REGRESSION")</x:f>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D5" s="33"/>
       <x:c r="E5" s="33" t="n">
-        <x:f>COUNTIF(Findings!F4:F77,"FIXED_IN_CODE")</x:f>
-        <x:v>7</x:v>
+        <x:f>COUNTIF(Findings!F4:F86,"FIXED_IN_CODE")</x:f>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F5" s="33"/>
       <x:c r="G5" s="33" t="n">
-        <x:f>COUNTIF(Findings!F4:F77,"CLOSED")+COUNTIF(Findings!F4:F77,"TESTED")</x:f>
+        <x:f>COUNTIF(Findings!F4:F86,"CLOSED")+COUNTIF(Findings!F4:F86,"TESTED")</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="H5" s="33"/>
@@ -5111,8 +5704,8 @@
         <x:v>OPEN</x:v>
       </x:c>
       <x:c r="B10" t="n">
-        <x:f>COUNTIF(Findings!F4:F77,A10)</x:f>
-        <x:v>51</x:v>
+        <x:f>COUNTIF(Findings!F4:F86,A10)</x:f>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C10" t="str">
         <x:v>Priority</x:v>
@@ -5121,9 +5714,9 @@
         <x:v>Count</x:v>
       </x:c>
       <x:c r="F10" s="43" t="str">
-        <x:v>NOT CLEARED FOR PUBLIC PAID LAUNCH
-Static code findings remain, provider E2E and Stripe billing lifecycles not independently tested.
-Do not close a ticket based only on an AI statement or commit title.</x:v>
+        <x:v>NOT CLEARED FOR REAL PAYMENTS
+High-impact billing and provider consistency defects remain.
+Static review only. Require real PSP/provider E2E and verified backups before launch.</x:v>
       </x:c>
       <x:c r="G10" s="43"/>
       <x:c r="H10" s="43"/>
@@ -5133,15 +5726,15 @@
         <x:v>PARTIAL</x:v>
       </x:c>
       <x:c r="B11" t="n">
-        <x:f>COUNTIF(Findings!F4:F77,A11)</x:f>
-        <x:v>3</x:v>
+        <x:f>COUNTIF(Findings!F4:F86,A11)</x:f>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C11" t="str">
         <x:v>P0</x:v>
       </x:c>
       <x:c r="D11" t="n">
-        <x:f>COUNTIF(Findings!B4:B77,C11)</x:f>
-        <x:v>26</x:v>
+        <x:f>COUNTIF(Findings!B4:B86,C11)</x:f>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="F11" s="43"/>
       <x:c r="G11" s="43"/>
@@ -5152,15 +5745,15 @@
         <x:v>NEEDS_VERIFICATION</x:v>
       </x:c>
       <x:c r="B12" t="n">
-        <x:f>COUNTIF(Findings!F4:F77,A12)</x:f>
+        <x:f>COUNTIF(Findings!F4:F86,A12)</x:f>
         <x:v>11</x:v>
       </x:c>
       <x:c r="C12" t="str">
         <x:v>P1</x:v>
       </x:c>
       <x:c r="D12" t="n">
-        <x:f>COUNTIF(Findings!B4:B77,C12)</x:f>
-        <x:v>46</x:v>
+        <x:f>COUNTIF(Findings!B4:B86,C12)</x:f>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="F12" s="43"/>
       <x:c r="G12" s="43"/>
@@ -5171,14 +5764,14 @@
         <x:v>POLICY_DECISION</x:v>
       </x:c>
       <x:c r="B13" t="n">
-        <x:f>COUNTIF(Findings!F4:F77,A13)</x:f>
+        <x:f>COUNTIF(Findings!F4:F86,A13)</x:f>
         <x:v>2</x:v>
       </x:c>
       <x:c r="C13" t="str">
         <x:v>P2</x:v>
       </x:c>
       <x:c r="D13" t="n">
-        <x:f>COUNTIF(Findings!B4:B77,C13)</x:f>
+        <x:f>COUNTIF(Findings!B4:B86,C13)</x:f>
         <x:v>2</x:v>
       </x:c>
       <x:c r="F13" s="43"/>
@@ -5190,8 +5783,8 @@
         <x:v>FIXED_IN_CODE</x:v>
       </x:c>
       <x:c r="B14" t="n">
-        <x:f>COUNTIF(Findings!F4:F77,A14)</x:f>
-        <x:v>7</x:v>
+        <x:f>COUNTIF(Findings!F4:F86,A14)</x:f>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F14" s="43"/>
       <x:c r="G14" s="43"/>
@@ -5202,7 +5795,7 @@
         <x:v>TESTED</x:v>
       </x:c>
       <x:c r="B15" t="n">
-        <x:f>COUNTIF(Findings!F4:F77,A15)</x:f>
+        <x:f>COUNTIF(Findings!F4:F86,A15)</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -5211,7 +5804,7 @@
         <x:v>CLOSED</x:v>
       </x:c>
       <x:c r="B16" t="n">
-        <x:f>COUNTIF(Findings!F4:F77,A16)</x:f>
+        <x:f>COUNTIF(Findings!F4:F86,A16)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="F16" t="str">
@@ -5223,11 +5816,11 @@
         <x:v>REGRESSION</x:v>
       </x:c>
       <x:c r="B17" t="n">
-        <x:f>COUNTIF(Findings!F4:F77,A17)</x:f>
+        <x:f>COUNTIF(Findings!F4:F86,A17)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="F17" s="51" t="str">
-        <x:v>620368742f1d</x:v>
+        <x:v>b9292811a221</x:v>
       </x:c>
       <x:c r="G17" s="51"/>
       <x:c r="H17" s="51"/>
@@ -5968,7 +6561,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R713fc674367a4f18"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R690f713a26384c84"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6163,6 +6756,26 @@
       </x:c>
       <x:c r="F10" s="18" t="str">
         <x:v>Same HEAD 6203687; not a new push</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" t="str">
+        <x:v>2026-10-19 04:02</x:v>
+      </x:c>
+      <x:c r="B11" t="str">
+        <x:v>b929281</x:v>
+      </x:c>
+      <x:c r="C11" t="str">
+        <x:v>Agent's audit delta security/billing/UI corrections</x:v>
+      </x:c>
+      <x:c r="D11" t="str">
+        <x:v>Independent static recheck: 21 status transitions; 9 new findings NEW-330…338</x:v>
+      </x:c>
+      <x:c r="E11" t="str">
+        <x:v>STATIC_SOURCE_ONLY</x:v>
+      </x:c>
+      <x:c r="F11" t="str">
+        <x:v>b9292811a22159a28a7159deee2c7ff27f41a873</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -6462,6 +7075,489 @@
         <x:v>Terminated service no longer displays Manage</x:v>
       </x:c>
     </x:row>
+    <x:row r="14" ht="27" customHeight="1">
+      <x:c r="A14" t="str">
+        <x:v>2026-10-19</x:v>
+      </x:c>
+      <x:c r="B14" t="str">
+        <x:v>b929281</x:v>
+      </x:c>
+      <x:c r="C14" t="str">
+        <x:v>SEC-04</x:v>
+      </x:c>
+      <x:c r="D14" t="str">
+        <x:v>PARTIAL</x:v>
+      </x:c>
+      <x:c r="E14" t="str">
+        <x:v>FIXED_IN_CODE</x:v>
+      </x:c>
+      <x:c r="F14" t="str">
+        <x:v>Static source inspection</x:v>
+      </x:c>
+      <x:c r="G14" t="str">
+        <x:v>Pending-MFA 15-min TTL and account-wide failures in auth.ts; requires runtime test.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="27" customHeight="1">
+      <x:c r="A15" t="str">
+        <x:v>2026-10-19</x:v>
+      </x:c>
+      <x:c r="B15" t="str">
+        <x:v>b929281</x:v>
+      </x:c>
+      <x:c r="C15" t="str">
+        <x:v>FTL-SEC-201</x:v>
+      </x:c>
+      <x:c r="D15" t="str">
+        <x:v>OPEN</x:v>
+      </x:c>
+      <x:c r="E15" t="str">
+        <x:v>FIXED_IN_CODE</x:v>
+      </x:c>
+      <x:c r="F15" t="str">
+        <x:v>Static source inspection</x:v>
+      </x:c>
+      <x:c r="G15" t="str">
+        <x:v>Confirmed factor remains active; pending_secret_encrypted used for replacement.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="27" customHeight="1">
+      <x:c r="A16" t="str">
+        <x:v>2026-10-19</x:v>
+      </x:c>
+      <x:c r="B16" t="str">
+        <x:v>b929281</x:v>
+      </x:c>
+      <x:c r="C16" t="str">
+        <x:v>FTL-SEC-202</x:v>
+      </x:c>
+      <x:c r="D16" t="str">
+        <x:v>OPEN</x:v>
+      </x:c>
+      <x:c r="E16" t="str">
+        <x:v>FIXED_IN_CODE</x:v>
+      </x:c>
+      <x:c r="F16" t="str">
+        <x:v>Static source inspection</x:v>
+      </x:c>
+      <x:c r="G16" t="str">
+        <x:v>MFA failures now queried by user_id across all pending sessions.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="27" customHeight="1">
+      <x:c r="A17" t="str">
+        <x:v>2026-10-19</x:v>
+      </x:c>
+      <x:c r="B17" t="str">
+        <x:v>b929281</x:v>
+      </x:c>
+      <x:c r="C17" t="str">
+        <x:v>FTL-SEC-203</x:v>
+      </x:c>
+      <x:c r="D17" t="str">
+        <x:v>OPEN</x:v>
+      </x:c>
+      <x:c r="E17" t="str">
+        <x:v>FIXED_IN_CODE</x:v>
+      </x:c>
+      <x:c r="F17" t="str">
+        <x:v>Static source inspection</x:v>
+      </x:c>
+      <x:c r="G17" t="str">
+        <x:v>Recovery-code regeneration protected by requireRecentStepUp.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="27" customHeight="1">
+      <x:c r="A18" t="str">
+        <x:v>2026-10-19</x:v>
+      </x:c>
+      <x:c r="B18" t="str">
+        <x:v>b929281</x:v>
+      </x:c>
+      <x:c r="C18" t="str">
+        <x:v>FTL-SEC-204</x:v>
+      </x:c>
+      <x:c r="D18" t="str">
+        <x:v>OPEN</x:v>
+      </x:c>
+      <x:c r="E18" t="str">
+        <x:v>FIXED_IN_CODE</x:v>
+      </x:c>
+      <x:c r="F18" t="str">
+        <x:v>Static source inspection</x:v>
+      </x:c>
+      <x:c r="G18" t="str">
+        <x:v>Recovery codes now 128-bit generated from randomBytes(16).</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="27" customHeight="1">
+      <x:c r="A19" t="str">
+        <x:v>2026-10-19</x:v>
+      </x:c>
+      <x:c r="B19" t="str">
+        <x:v>b929281</x:v>
+      </x:c>
+      <x:c r="C19" t="str">
+        <x:v>FTL-SEC-205</x:v>
+      </x:c>
+      <x:c r="D19" t="str">
+        <x:v>OPEN</x:v>
+      </x:c>
+      <x:c r="E19" t="str">
+        <x:v>FIXED_IN_CODE</x:v>
+      </x:c>
+      <x:c r="F19" t="str">
+        <x:v>Static source inspection</x:v>
+      </x:c>
+      <x:c r="G19" t="str">
+        <x:v>isLoginThrottled now counts 10 failures account-wide independent of IP.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="27" customHeight="1">
+      <x:c r="A20" t="str">
+        <x:v>2026-10-19</x:v>
+      </x:c>
+      <x:c r="B20" t="str">
+        <x:v>b929281</x:v>
+      </x:c>
+      <x:c r="C20" t="str">
+        <x:v>FTL-BILL-201</x:v>
+      </x:c>
+      <x:c r="D20" t="str">
+        <x:v>OPEN</x:v>
+      </x:c>
+      <x:c r="E20" t="str">
+        <x:v>PARTIAL</x:v>
+      </x:c>
+      <x:c r="F20" t="str">
+        <x:v>Static source inspection</x:v>
+      </x:c>
+      <x:c r="G20" t="str">
+        <x:v>Stripe recurring interval mapped correctly; webhook still persists local subscriptions as MONTHLY.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="27" customHeight="1">
+      <x:c r="A21" t="str">
+        <x:v>2026-10-19</x:v>
+      </x:c>
+      <x:c r="B21" t="str">
+        <x:v>b929281</x:v>
+      </x:c>
+      <x:c r="C21" t="str">
+        <x:v>FTL-BILL-202</x:v>
+      </x:c>
+      <x:c r="D21" t="str">
+        <x:v>OPEN</x:v>
+      </x:c>
+      <x:c r="E21" t="str">
+        <x:v>PARTIAL</x:v>
+      </x:c>
+      <x:c r="F21" t="str">
+        <x:v>Static source inspection</x:v>
+      </x:c>
+      <x:c r="G21" t="str">
+        <x:v>Refund/dispute webhook enqueues suspend/terminate actions; staff refund path still bypasses PSP/provider.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="27" customHeight="1">
+      <x:c r="A22" t="str">
+        <x:v>2026-10-19</x:v>
+      </x:c>
+      <x:c r="B22" t="str">
+        <x:v>b929281</x:v>
+      </x:c>
+      <x:c r="C22" t="str">
+        <x:v>FTL-BILL-203</x:v>
+      </x:c>
+      <x:c r="D22" t="str">
+        <x:v>OPEN</x:v>
+      </x:c>
+      <x:c r="E22" t="str">
+        <x:v>FIXED_IN_CODE</x:v>
+      </x:c>
+      <x:c r="F22" t="str">
+        <x:v>Static source inspection</x:v>
+      </x:c>
+      <x:c r="G22" t="str">
+        <x:v>Webhook checks payment_attempts.status/order.status before repeated fulfillment.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" ht="27" customHeight="1">
+      <x:c r="A23" t="str">
+        <x:v>2026-10-19</x:v>
+      </x:c>
+      <x:c r="B23" t="str">
+        <x:v>b929281</x:v>
+      </x:c>
+      <x:c r="C23" t="str">
+        <x:v>FTL-BILL-204</x:v>
+      </x:c>
+      <x:c r="D23" t="str">
+        <x:v>OPEN</x:v>
+      </x:c>
+      <x:c r="E23" t="str">
+        <x:v>PARTIAL</x:v>
+      </x:c>
+      <x:c r="F23" t="str">
+        <x:v>Static source inspection</x:v>
+      </x:c>
+      <x:c r="G23" t="str">
+        <x:v>Real payment_intent IDs stored; invoice.paid settlement scopes invoices by account, not Stripe invoice.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" ht="27" customHeight="1">
+      <x:c r="A24" t="str">
+        <x:v>2026-10-19</x:v>
+      </x:c>
+      <x:c r="B24" t="str">
+        <x:v>b929281</x:v>
+      </x:c>
+      <x:c r="C24" t="str">
+        <x:v>FTL-BILL-205</x:v>
+      </x:c>
+      <x:c r="D24" t="str">
+        <x:v>OPEN</x:v>
+      </x:c>
+      <x:c r="E24" t="str">
+        <x:v>PARTIAL</x:v>
+      </x:c>
+      <x:c r="F24" t="str">
+        <x:v>Static source inspection</x:v>
+      </x:c>
+      <x:c r="G24" t="str">
+        <x:v>Stripe subscriptions exempted from local dunning; invoice.paid wrongly settles all account invoices.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" ht="27" customHeight="1">
+      <x:c r="A25" t="str">
+        <x:v>2026-10-19</x:v>
+      </x:c>
+      <x:c r="B25" t="str">
+        <x:v>b929281</x:v>
+      </x:c>
+      <x:c r="C25" t="str">
+        <x:v>FTL-PROV-201</x:v>
+      </x:c>
+      <x:c r="D25" t="str">
+        <x:v>OPEN</x:v>
+      </x:c>
+      <x:c r="E25" t="str">
+        <x:v>PARTIAL</x:v>
+      </x:c>
+      <x:c r="F25" t="str">
+        <x:v>Static source inspection</x:v>
+      </x:c>
+      <x:c r="G25" t="str">
+        <x:v>Dispatch by provider_type added, but CPANEL/VPS dispatch still constructs mock adapters in worker.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" ht="27" customHeight="1">
+      <x:c r="A26" t="str">
+        <x:v>2026-10-19</x:v>
+      </x:c>
+      <x:c r="B26" t="str">
+        <x:v>b929281</x:v>
+      </x:c>
+      <x:c r="C26" t="str">
+        <x:v>FTL-PROV-202</x:v>
+      </x:c>
+      <x:c r="D26" t="str">
+        <x:v>OPEN</x:v>
+      </x:c>
+      <x:c r="E26" t="str">
+        <x:v>PARTIAL</x:v>
+      </x:c>
+      <x:c r="F26" t="str">
+        <x:v>Static source inspection</x:v>
+      </x:c>
+      <x:c r="G26" t="str">
+        <x:v>Hardcoded node_fra_01 removed; fallback still chooses wrong region/no-capacity nodes.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" ht="27" customHeight="1">
+      <x:c r="A27" t="str">
+        <x:v>2026-10-19</x:v>
+      </x:c>
+      <x:c r="B27" t="str">
+        <x:v>b929281</x:v>
+      </x:c>
+      <x:c r="C27" t="str">
+        <x:v>FTL-PROV-203</x:v>
+      </x:c>
+      <x:c r="D27" t="str">
+        <x:v>OPEN</x:v>
+      </x:c>
+      <x:c r="E27" t="str">
+        <x:v>FIXED_IN_CODE</x:v>
+      </x:c>
+      <x:c r="F27" t="str">
+        <x:v>Static source inspection</x:v>
+      </x:c>
+      <x:c r="G27" t="str">
+        <x:v>Worker now atomically reserves capacity with conditional UPDATE.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" ht="27" customHeight="1">
+      <x:c r="A28" t="str">
+        <x:v>2026-10-19</x:v>
+      </x:c>
+      <x:c r="B28" t="str">
+        <x:v>b929281</x:v>
+      </x:c>
+      <x:c r="C28" t="str">
+        <x:v>FTL-DNS-201</x:v>
+      </x:c>
+      <x:c r="D28" t="str">
+        <x:v>OPEN</x:v>
+      </x:c>
+      <x:c r="E28" t="str">
+        <x:v>PARTIAL</x:v>
+      </x:c>
+      <x:c r="F28" t="str">
+        <x:v>Static source inspection</x:v>
+      </x:c>
+      <x:c r="G28" t="str">
+        <x:v>Search discloses LOCAL_ZONE_AVAILABLE, but still returns available:true without registrar check.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" ht="27" customHeight="1">
+      <x:c r="A29" t="str">
+        <x:v>2026-10-19</x:v>
+      </x:c>
+      <x:c r="B29" t="str">
+        <x:v>b929281</x:v>
+      </x:c>
+      <x:c r="C29" t="str">
+        <x:v>FTL-DNS-202</x:v>
+      </x:c>
+      <x:c r="D29" t="str">
+        <x:v>OPEN</x:v>
+      </x:c>
+      <x:c r="E29" t="str">
+        <x:v>PARTIAL</x:v>
+      </x:c>
+      <x:c r="F29" t="str">
+        <x:v>Static source inspection</x:v>
+      </x:c>
+      <x:c r="G29" t="str">
+        <x:v>Zone has pending/delegation distinction; authoritative DNS/registrar integration not verified.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" ht="27" customHeight="1">
+      <x:c r="A30" t="str">
+        <x:v>2026-10-19</x:v>
+      </x:c>
+      <x:c r="B30" t="str">
+        <x:v>b929281</x:v>
+      </x:c>
+      <x:c r="C30" t="str">
+        <x:v>FTL-UI-201</x:v>
+      </x:c>
+      <x:c r="D30" t="str">
+        <x:v>OPEN</x:v>
+      </x:c>
+      <x:c r="E30" t="str">
+        <x:v>FIXED_IN_CODE</x:v>
+      </x:c>
+      <x:c r="F30" t="str">
+        <x:v>Static source inspection</x:v>
+      </x:c>
+      <x:c r="G30" t="str">
+        <x:v>Service list checks user_can_control, detailed page checks explicit permissions; runtime E2E needed.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" ht="27" customHeight="1">
+      <x:c r="A31" t="str">
+        <x:v>2026-10-19</x:v>
+      </x:c>
+      <x:c r="B31" t="str">
+        <x:v>b929281</x:v>
+      </x:c>
+      <x:c r="C31" t="str">
+        <x:v>FTL-UI-202</x:v>
+      </x:c>
+      <x:c r="D31" t="str">
+        <x:v>OPEN</x:v>
+      </x:c>
+      <x:c r="E31" t="str">
+        <x:v>FIXED_IN_CODE</x:v>
+      </x:c>
+      <x:c r="F31" t="str">
+        <x:v>Static source inspection</x:v>
+      </x:c>
+      <x:c r="G31" t="str">
+        <x:v>Service details filter provider tabs by capabilities and permissions.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" ht="27" customHeight="1">
+      <x:c r="A32" t="str">
+        <x:v>2026-10-19</x:v>
+      </x:c>
+      <x:c r="B32" t="str">
+        <x:v>b929281</x:v>
+      </x:c>
+      <x:c r="C32" t="str">
+        <x:v>FTL-UI-203</x:v>
+      </x:c>
+      <x:c r="D32" t="str">
+        <x:v>OPEN</x:v>
+      </x:c>
+      <x:c r="E32" t="str">
+        <x:v>PARTIAL</x:v>
+      </x:c>
+      <x:c r="F32" t="str">
+        <x:v>Static source inspection</x:v>
+      </x:c>
+      <x:c r="G32" t="str">
+        <x:v>Router has sequence and AbortController; async page fetches do not consistently use signal guard.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" ht="27" customHeight="1">
+      <x:c r="A33" t="str">
+        <x:v>2026-10-19</x:v>
+      </x:c>
+      <x:c r="B33" t="str">
+        <x:v>b929281</x:v>
+      </x:c>
+      <x:c r="C33" t="str">
+        <x:v>FTL-UI-204</x:v>
+      </x:c>
+      <x:c r="D33" t="str">
+        <x:v>OPEN</x:v>
+      </x:c>
+      <x:c r="E33" t="str">
+        <x:v>PARTIAL</x:v>
+      </x:c>
+      <x:c r="F33" t="str">
+        <x:v>Static source inspection</x:v>
+      </x:c>
+      <x:c r="G33" t="str">
+        <x:v>24 route definitions present in verify-views.py, but no authenticated fixture/pixel reference comparison.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" ht="27" customHeight="1">
+      <x:c r="A34" t="str">
+        <x:v>2026-10-19</x:v>
+      </x:c>
+      <x:c r="B34" t="str">
+        <x:v>b929281</x:v>
+      </x:c>
+      <x:c r="C34" t="str">
+        <x:v>FTL-UI-206</x:v>
+      </x:c>
+      <x:c r="D34" t="str">
+        <x:v>OPEN</x:v>
+      </x:c>
+      <x:c r="E34" t="str">
+        <x:v>PARTIAL</x:v>
+      </x:c>
+      <x:c r="F34" t="str">
+        <x:v>Static source inspection</x:v>
+      </x:c>
+      <x:c r="G34" t="str">
+        <x:v>Buttons account for contract/runtime status but per-button action permission and provider feedback remain incomplete.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:G1"/>
@@ -6917,4 +8013,516 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="28" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="30" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="40" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="47" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="27" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="33" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="32" customHeight="1">
+      <x:c r="A1" s="74" t="str">
+        <x:v>FORTLESS  /  RISK-BASED MFA &amp; STEP-UP MATRIX</x:v>
+      </x:c>
+      <x:c r="B1" s="74"/>
+      <x:c r="C1" s="74"/>
+      <x:c r="D1" s="74"/>
+      <x:c r="E1" s="74"/>
+      <x:c r="F1" s="74"/>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" t="str">
+        <x:v>Recommend strong verification only for identity, ownership, finance, destructive changes. Keep routine server operations frictionless.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="30" customHeight="1">
+      <x:c r="A4" s="76" t="str">
+        <x:v>Action / endpoint</x:v>
+      </x:c>
+      <x:c r="B4" s="76" t="str">
+        <x:v>Policy</x:v>
+      </x:c>
+      <x:c r="C4" s="76" t="str">
+        <x:v>Existing observed control</x:v>
+      </x:c>
+      <x:c r="D4" s="76" t="str">
+        <x:v>Gap / change needed</x:v>
+      </x:c>
+      <x:c r="E4" s="76" t="str">
+        <x:v>Reason</x:v>
+      </x:c>
+      <x:c r="F4" s="76" t="str">
+        <x:v>Tracking / code</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="39" customHeight="1">
+      <x:c r="A5" s="66" t="str">
+        <x:v>Staff admin access</x:v>
+      </x:c>
+      <x:c r="B5" s="66" t="str">
+        <x:v>MFA mandatory</x:v>
+      </x:c>
+      <x:c r="C5" s="66" t="str">
+        <x:v>Staff guard requires verified MFA</x:v>
+      </x:c>
+      <x:c r="D5" s="66" t="str">
+        <x:v>Test direct API and SSO consistency</x:v>
+      </x:c>
+      <x:c r="E5" s="66" t="str">
+        <x:v>Privileged all-tenant surface</x:v>
+      </x:c>
+      <x:c r="F5" s="66" t="str">
+        <x:v>src/server.ts requireStaff</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="39" customHeight="1">
+      <x:c r="A6" s="66" t="str">
+        <x:v>Staff refund</x:v>
+      </x:c>
+      <x:c r="B6" s="66" t="str">
+        <x:v>Recent step-up mandatory</x:v>
+      </x:c>
+      <x:c r="C6" s="66" t="str">
+        <x:v>requireRecentStepUp in refund route</x:v>
+      </x:c>
+      <x:c r="D6" s="66" t="str">
+        <x:v>Keep, enforce PSP refund idempotence</x:v>
+      </x:c>
+      <x:c r="E6" s="66" t="str">
+        <x:v>Financial mutation</x:v>
+      </x:c>
+      <x:c r="F6" s="66" t="str">
+        <x:v>src/server.ts:1920; NEW-334</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="39" customHeight="1">
+      <x:c r="A7" s="66" t="str">
+        <x:v>Staff service terminate / relink</x:v>
+      </x:c>
+      <x:c r="B7" s="66" t="str">
+        <x:v>Recent step-up mandatory</x:v>
+      </x:c>
+      <x:c r="C7" s="66" t="str">
+        <x:v>Admin routes guarded</x:v>
+      </x:c>
+      <x:c r="D7" s="66" t="str">
+        <x:v>Keep; provider deletion must reconcile</x:v>
+      </x:c>
+      <x:c r="E7" s="66" t="str">
+        <x:v>Permanent destructive change</x:v>
+      </x:c>
+      <x:c r="F7" s="66" t="str">
+        <x:v>src/server.ts; NEW-337</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="39" customHeight="1">
+      <x:c r="A8" s="66" t="str">
+        <x:v>Invite/promote OWNER</x:v>
+      </x:c>
+      <x:c r="B8" s="66" t="str">
+        <x:v>Owner-only + fresh step-up</x:v>
+      </x:c>
+      <x:c r="C8" s="66" t="str">
+        <x:v>TECH_ADMIN may currently invite OWNER</x:v>
+      </x:c>
+      <x:c r="D8" s="66" t="str">
+        <x:v>Deny upward grant; step-up owner changes</x:v>
+      </x:c>
+      <x:c r="E8" s="66" t="str">
+        <x:v>Privilege escalation</x:v>
+      </x:c>
+      <x:c r="F8" s="66" t="str">
+        <x:v>NEW-331</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="39" customHeight="1">
+      <x:c r="A9" s="66" t="str">
+        <x:v>Register / delete passkeys</x:v>
+      </x:c>
+      <x:c r="B9" s="66" t="str">
+        <x:v>Recent step-up</x:v>
+      </x:c>
+      <x:c r="C9" s="66" t="str">
+        <x:v>Authentication only on passkey routes</x:v>
+      </x:c>
+      <x:c r="D9" s="66" t="str">
+        <x:v>Require recent auth or UV; alert user</x:v>
+      </x:c>
+      <x:c r="E9" s="66" t="str">
+        <x:v>Future account takeover</x:v>
+      </x:c>
+      <x:c r="F9" s="66" t="str">
+        <x:v>NEW-306</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="39" customHeight="1">
+      <x:c r="A10" s="66" t="str">
+        <x:v>Reset/replace MFA</x:v>
+      </x:c>
+      <x:c r="B10" s="66" t="str">
+        <x:v>Recent step-up + notify</x:v>
+      </x:c>
+      <x:c r="C10" s="66" t="str">
+        <x:v>TOTP replacement step-up; recovery regenerate step-up</x:v>
+      </x:c>
+      <x:c r="D10" s="66" t="str">
+        <x:v>Test session revocation and step-up replay</x:v>
+      </x:c>
+      <x:c r="E10" s="66" t="str">
+        <x:v>Security factor change</x:v>
+      </x:c>
+      <x:c r="F10" s="66" t="str">
+        <x:v>FTL-SEC-201/203</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="39" customHeight="1">
+      <x:c r="A11" s="66" t="str">
+        <x:v>Disable MFA</x:v>
+      </x:c>
+      <x:c r="B11" s="66" t="str">
+        <x:v>Password + current MFA; alerts</x:v>
+      </x:c>
+      <x:c r="C11" s="66" t="str">
+        <x:v>Password + TOTP checked</x:v>
+      </x:c>
+      <x:c r="D11" s="66" t="str">
+        <x:v>Review session revocation; staff policy</x:v>
+      </x:c>
+      <x:c r="E11" s="66" t="str">
+        <x:v>Weakens account protection</x:v>
+      </x:c>
+      <x:c r="F11" s="66" t="str">
+        <x:v>src/modules/identity/auth.ts</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="39" customHeight="1">
+      <x:c r="A12" s="66" t="str">
+        <x:v>Workspace invite TECH_ADMIN</x:v>
+      </x:c>
+      <x:c r="B12" s="66" t="str">
+        <x:v>Owner or allowed tech admin + step-up</x:v>
+      </x:c>
+      <x:c r="C12" s="66" t="str">
+        <x:v>Only role check</x:v>
+      </x:c>
+      <x:c r="D12" s="66" t="str">
+        <x:v>Add step-up for privileged invitations</x:v>
+      </x:c>
+      <x:c r="E12" s="66" t="str">
+        <x:v>Role management</x:v>
+      </x:c>
+      <x:c r="F12" s="66" t="str">
+        <x:v>src/modules/identity/teams.ts</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="39" customHeight="1">
+      <x:c r="A13" s="66" t="str">
+        <x:v>Change PSP/provider API keys</x:v>
+      </x:c>
+      <x:c r="B13" s="66" t="str">
+        <x:v>Fresh step-up + confirmation</x:v>
+      </x:c>
+      <x:c r="C13" s="66" t="str">
+        <x:v>Config mostly via server env</x:v>
+      </x:c>
+      <x:c r="D13" s="66" t="str">
+        <x:v>Gate any future admin UI and dual confirmation</x:v>
+      </x:c>
+      <x:c r="E13" s="66" t="str">
+        <x:v>Can control all infrastructure / money</x:v>
+      </x:c>
+      <x:c r="F13" s="66" t="str">
+        <x:v>Launch controls</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="39" customHeight="1">
+      <x:c r="A14" s="66" t="str">
+        <x:v>Backup restore / reinstall</x:v>
+      </x:c>
+      <x:c r="B14" s="66" t="str">
+        <x:v>Confirmation; optional recent step-up</x:v>
+      </x:c>
+      <x:c r="C14" s="66" t="str">
+        <x:v>Permission checks on API</x:v>
+      </x:c>
+      <x:c r="D14" s="66" t="str">
+        <x:v>Use step-up on destructive restore, not listing</x:v>
+      </x:c>
+      <x:c r="E14" s="66" t="str">
+        <x:v>Destructive service operation</x:v>
+      </x:c>
+      <x:c r="F14" s="66" t="str">
+        <x:v>src/modules/provisioning/server-panel.ts</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="39" customHeight="1">
+      <x:c r="A15" s="66" t="str">
+        <x:v>Routine start/stop/console</x:v>
+      </x:c>
+      <x:c r="B15" s="66" t="str">
+        <x:v>No additional MFA per click</x:v>
+      </x:c>
+      <x:c r="C15" s="66" t="str">
+        <x:v>Session + per-service permissions</x:v>
+      </x:c>
+      <x:c r="D15" s="66" t="str">
+        <x:v>Keep quick and responsive</x:v>
+      </x:c>
+      <x:c r="E15" s="66" t="str">
+        <x:v>UX without unnecessary friction</x:v>
+      </x:c>
+      <x:c r="F15" s="66" t="str">
+        <x:v>src/modules/provisioning/service-access.ts</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="39" customHeight="1">
+      <x:c r="A16" s="66" t="str">
+        <x:v>Normal checkout</x:v>
+      </x:c>
+      <x:c r="B16" s="66" t="str">
+        <x:v>SCA through Stripe, no duplicate TOTP</x:v>
+      </x:c>
+      <x:c r="C16" s="66" t="str">
+        <x:v>Stripe Checkout handles payment auth</x:v>
+      </x:c>
+      <x:c r="D16" s="66" t="str">
+        <x:v>Avoid double MFA unless suspicious session</x:v>
+      </x:c>
+      <x:c r="E16" s="66" t="str">
+        <x:v>Reduce checkout friction</x:v>
+      </x:c>
+      <x:c r="F16" s="66" t="str">
+        <x:v>src/modules/checkout/checkout.ts</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="39" customHeight="1">
+      <x:c r="A17" s="66" t="str">
+        <x:v>Staff passkey sign-in</x:v>
+      </x:c>
+      <x:c r="B17" s="66" t="str">
+        <x:v>Require authenticator user verification</x:v>
+      </x:c>
+      <x:c r="C17" s="66" t="str">
+        <x:v>Policy userVerification preferred</x:v>
+      </x:c>
+      <x:c r="D17" s="66" t="str">
+        <x:v>Upgrade privileged authentication policy to required</x:v>
+      </x:c>
+      <x:c r="E17" s="66" t="str">
+        <x:v>Phishing-resistant control</x:v>
+      </x:c>
+      <x:c r="F17" s="66" t="str">
+        <x:v>NEW-307</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:F1"/>
+    <x:mergeCell ref="A2:F2"/>
+  </x:mergeCells>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="10" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="30" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="58" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="49" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="32" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="22" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="32" customHeight="1">
+      <x:c r="A1" s="74" t="str">
+        <x:v>FORTLESS  /  SINGLE-OPERATOR HOSTING RELEASE GATES</x:v>
+      </x:c>
+      <x:c r="B1" s="74"/>
+      <x:c r="C1" s="74"/>
+      <x:c r="D1" s="74"/>
+      <x:c r="E1" s="74"/>
+      <x:c r="F1" s="74"/>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" t="str">
+        <x:v>Designed for a controlled commercial hosting launch, not hyperscale. Ship Pterodactyl first; disable unverified providers until live integration passes.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="32" customHeight="1">
+      <x:c r="A4" s="76" t="str">
+        <x:v>Phase</x:v>
+      </x:c>
+      <x:c r="B4" s="76" t="str">
+        <x:v>Release gate</x:v>
+      </x:c>
+      <x:c r="C4" s="76" t="str">
+        <x:v>Exit criterion (not just AI green text)</x:v>
+      </x:c>
+      <x:c r="D4" s="76" t="str">
+        <x:v>Evidence required</x:v>
+      </x:c>
+      <x:c r="E4" s="76" t="str">
+        <x:v>Scope</x:v>
+      </x:c>
+      <x:c r="F4" s="76" t="str">
+        <x:v>State</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="64" customHeight="1">
+      <x:c r="A5" s="66" t="str">
+        <x:v>01</x:v>
+      </x:c>
+      <x:c r="B5" s="66" t="str">
+        <x:v>Stop incorrect money flow</x:v>
+      </x:c>
+      <x:c r="C5" s="66" t="str">
+        <x:v>Stripe invoice/payment/subscription/refund/cancel exactly matched; no double settlement or charging after cancel</x:v>
+      </x:c>
+      <x:c r="D5" s="66" t="str">
+        <x:v>Integration tests + Stripe test mode webhook replay + sample invoices</x:v>
+      </x:c>
+      <x:c r="E5" s="66" t="str">
+        <x:v>Billing, credit notes, VAT, pricing</x:v>
+      </x:c>
+      <x:c r="F5" s="66" t="str">
+        <x:v>BLOCKED</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="64" customHeight="1">
+      <x:c r="A6" s="66" t="str">
+        <x:v>02</x:v>
+      </x:c>
+      <x:c r="B6" s="66" t="str">
+        <x:v>Fix privilege boundaries</x:v>
+      </x:c>
+      <x:c r="C6" s="66" t="str">
+        <x:v>OWNER roles ungrantable by TECH_ADMIN; all service operations pass two-account RBAC tests</x:v>
+      </x:c>
+      <x:c r="D6" s="66" t="str">
+        <x:v>Test matrix across OWNER/TECH_ADMIN/BILLING/VIEWER/shared presets</x:v>
+      </x:c>
+      <x:c r="E6" s="66" t="str">
+        <x:v>Auth, sessions, service permissions</x:v>
+      </x:c>
+      <x:c r="F6" s="66" t="str">
+        <x:v>BLOCKED</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="64" customHeight="1">
+      <x:c r="A7" s="66" t="str">
+        <x:v>03</x:v>
+      </x:c>
+      <x:c r="B7" s="66" t="str">
+        <x:v>Real provider operations only</x:v>
+      </x:c>
+      <x:c r="C7" s="66" t="str">
+        <x:v>No mock provisioning in live; one successful create, suspend, resume, delete, retry &amp; reconcile for each published provider</x:v>
+      </x:c>
+      <x:c r="D7" s="66" t="str">
+        <x:v>Provider sandbox/live test resources + logs</x:v>
+      </x:c>
+      <x:c r="E7" s="66" t="str">
+        <x:v>Pterodactyl core; cPanel/VPS gated</x:v>
+      </x:c>
+      <x:c r="F7" s="66" t="str">
+        <x:v>BLOCKED</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="64" customHeight="1">
+      <x:c r="A8" s="66" t="str">
+        <x:v>04</x:v>
+      </x:c>
+      <x:c r="B8" s="66" t="str">
+        <x:v>State machine &amp; reconciliation</x:v>
+      </x:c>
+      <x:c r="C8" s="66" t="str">
+        <x:v>Never show terminated/paid/running without remote/PSP confirmation; recovery from outage/crash</x:v>
+      </x:c>
+      <x:c r="D8" s="66" t="str">
+        <x:v>Forced-failure integration tests; dead-letter alert evidence</x:v>
+      </x:c>
+      <x:c r="E8" s="66" t="str">
+        <x:v>Provisioning, billing, UX</x:v>
+      </x:c>
+      <x:c r="F8" s="66" t="str">
+        <x:v>BLOCKED</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="64" customHeight="1">
+      <x:c r="A9" s="66" t="str">
+        <x:v>05</x:v>
+      </x:c>
+      <x:c r="B9" s="66" t="str">
+        <x:v>Operational readiness</x:v>
+      </x:c>
+      <x:c r="C9" s="66" t="str">
+        <x:v>Backup/restore test, secret rotation plan, mail deliverability, structured alerts, rate-limit, TLS headers</x:v>
+      </x:c>
+      <x:c r="D9" s="66" t="str">
+        <x:v>Documented restore drill + security test results</x:v>
+      </x:c>
+      <x:c r="E9" s="66" t="str">
+        <x:v>Operations</x:v>
+      </x:c>
+      <x:c r="F9" s="66" t="str">
+        <x:v>UNVERIFIED</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="64" customHeight="1">
+      <x:c r="A10" s="66" t="str">
+        <x:v>06</x:v>
+      </x:c>
+      <x:c r="B10" s="66" t="str">
+        <x:v>Smart Petal interaction QA</x:v>
+      </x:c>
+      <x:c r="C10" s="66" t="str">
+        <x:v>One canonical tab/navigation/status model, no dead Manage buttons, responsive, safe loading/error and action permissions</x:v>
+      </x:c>
+      <x:c r="D10" s="66" t="str">
+        <x:v>Screenshots against Fortless Views; role/provider/status matrix</x:v>
+      </x:c>
+      <x:c r="E10" s="66" t="str">
+        <x:v>UI/UX</x:v>
+      </x:c>
+      <x:c r="F10" s="66" t="str">
+        <x:v>UNVERIFIED</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="64" customHeight="1">
+      <x:c r="A11" s="66" t="str">
+        <x:v>07</x:v>
+      </x:c>
+      <x:c r="B11" s="66" t="str">
+        <x:v>Controlled launch</x:v>
+      </x:c>
+      <x:c r="C11" s="66" t="str">
+        <x:v>Start with internal test account then small invite-only paid pilot, manual support and rollback procedure</x:v>
+      </x:c>
+      <x:c r="D11" s="66" t="str">
+        <x:v>Signed go/no-go checklist + incident owner + pilot feedback</x:v>
+      </x:c>
+      <x:c r="E11" s="66" t="str">
+        <x:v>Business operations</x:v>
+      </x:c>
+      <x:c r="F11" s="66" t="str">
+        <x:v>NOT STARTED</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:F1"/>
+    <x:mergeCell ref="A2:F2"/>
+  </x:mergeCells>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
 </file>
--- a/audits/FORTLESS_MASTER_SECURITY_UI_BUG_TRACKER.xlsx
+++ b/audits/FORTLESS_MASTER_SECURITY_UI_BUG_TRACKER.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3376" uniqueCount="1393">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3486" uniqueCount="1429">
   <si>
     <t>FORTLESS   /   ENGINEERING FINDINGS REGISTER</t>
   </si>
@@ -2673,7 +2673,100 @@
     <t>Check: on the live host NODE_ENV is production, cookies carry Secure and backups require a key.</t>
   </si>
   <si>
-    <t>[CONFIG_DEPENDENT] Observed from the running process and .env value NODE_ENV only; no secrets recorded.</t>
+    <t>[CONFIG_DEPENDENT] Observed from the running process and .env value NODE_ENV only; no secrets recorded. | AUDIT 3cb35de: SESSION_SECRET is empty in .env, so the process falls back to a random secret stored in data/.development-session-secret (config/index.ts:77). Cookie signing, CSRF tokens, TOTP secrets and per-account panel keys derive from that file, which sits in the data directory next to the database and backups.</t>
+  </si>
+  <si>
+    <t>NEW-362</t>
+  </si>
+  <si>
+    <t>Account enumeration through registration errors and login timing</t>
+  </si>
+  <si>
+    <t>src/modules/identity/auth.ts:220,319; src/server.ts:649-651</t>
+  </si>
+  <si>
+    <t>registerUser throws "An account with this email address already exists." (auth.ts:220) and the route returns it as a 400 (server.ts:649-651). loginUser short-circuits when the email is unknown (auth.ts:319), skipping the Argon2 verification that runs for real accounts, so response time differs. Forgot-password and resend-verification already return generic messages.</t>
+  </si>
+  <si>
+    <t>Anyone can test which email addresses have Fortless accounts, which helps targeted phishing and the lockout in NEW-364.</t>
+  </si>
+  <si>
+    <t>Return a generic registration response (email the existing owner instead), and run a dummy password hash for unknown users.</t>
+  </si>
+  <si>
+    <t>Test: registering an existing email returns the same status and body as a new one; login timing for known and unknown emails is within noise.</t>
+  </si>
+  <si>
+    <t>[CONFIRMED_CODE] Source trace. Timing difference is TEST_NEEDED at runtime.</t>
+  </si>
+  <si>
+    <t>NEW-363</t>
+  </si>
+  <si>
+    <t>Email verification link signs in whoever clicks it, enabling pre-registration hijack</t>
+  </si>
+  <si>
+    <t>src/modules/identity/auth.ts:213-246,248-280; src/server.ts:695-708</t>
+  </si>
+  <si>
+    <t>registerUser accepts any email and password without proving mailbox control (auth.ts:213-246). verifyEmail then activates the account and issues a session with MFA marked verified (auth.ts:257-260, server.ts:705).</t>
+  </si>
+  <si>
+    <t>An attacker pre-registers a victim email with a password they know. When the victim clicks the verification email they are signed in to the attacker-controlled account and may add billing details or services; the attacker keeps the password.</t>
+  </si>
+  <si>
+    <t>Do not create a session from the verification link, or require setting a new password at verification; notify and invalidate the original password when verification happens from a different context.</t>
+  </si>
+  <si>
+    <t>Test: after verification the user must authenticate; the pre-registration password no longer works once the mailbox owner verifies.</t>
+  </si>
+  <si>
+    <t>[CONFIRMED_CODE] Source trace; exploit needs a victim who acts on the email.</t>
+  </si>
+  <si>
+    <t>NEW-364</t>
+  </si>
+  <si>
+    <t>Account-wide failure limit lets anyone lock a known account out</t>
+  </si>
+  <si>
+    <t>src/modules/identity/auth.ts:305-312</t>
+  </si>
+  <si>
+    <t>Ten failed attempts for an email from any addresses within 15 minutes throttle every login for that email (auth.ts:309-311). There is no allowance for trusted devices or a recovery path other than waiting.</t>
+  </si>
+  <si>
+    <t>An attacker can keep an OWNER or staff account locked out indefinitely with scripted bad passwords from a few addresses.</t>
+  </si>
+  <si>
+    <t>Policy decision: combine the account limit with device or IP reputation, allow signed-in devices, and alert the owner.</t>
+  </si>
+  <si>
+    <t>Policy: define behaviour for sustained failed attempts that does not block the legitimate owner.</t>
+  </si>
+  <si>
+    <t>[POLICY_DECISION] Trade-off between brute force defence (FTL-SEC-205) and availability.</t>
+  </si>
+  <si>
+    <t>NEW-365</t>
+  </si>
+  <si>
+    <t>No per-recipient cooldown on verification and reset emails</t>
+  </si>
+  <si>
+    <t>src/server.ts:624-652,711-723; src/modules/identity/auth.ts:282-299,348-364</t>
+  </si>
+  <si>
+    <t>Registration, resend-verification and forgot-password queue an email on every request. The only brake is the global 100 requests per minute per IP (server.ts:210-213). Resend creates a fresh token each time (auth.ts:288).</t>
+  </si>
+  <si>
+    <t>A third party can flood a victim mailbox or exhaust the SMTP provider quota and reputation using a few addresses.</t>
+  </si>
+  <si>
+    <t>Add a per-recipient cooldown and daily cap, and collapse repeated requests into one pending message.</t>
+  </si>
+  <si>
+    <t>Test: the second request for the same address within the cooldown queues no new email.</t>
   </si>
   <si>
     <t>FORTLESS   /   SECURITY &amp; PRODUCT QUALITY</t>
@@ -2694,387 +2787,393 @@
     <t>CLOSED &amp; TESTED</t>
   </si>
   <si>
-    <t>106</t>
+    <t>110</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>58</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>PRIORITY &amp; STATUS</t>
+  </si>
+  <si>
+    <t>RELEASE CONTROL</t>
+  </si>
+  <si>
+    <t>Count</t>
+  </si>
+  <si>
+    <t>NOT CLEARED FOR REAL PAYMENTS Critical billing defects reproduced in source (checkout amount mismatch, inbox event loss, SEMI_ANNUAL settlement, scheduled cancellation). Static review plus local reproductions only.</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>39</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>62</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>TESTED</t>
+  </si>
+  <si>
+    <t>CLOSED</t>
+  </si>
+  <si>
+    <t>LATEST VERIFIED COMMIT</t>
+  </si>
+  <si>
+    <t>REGRESSION</t>
+  </si>
+  <si>
+    <t>3cb35de (independent audit batch 1)</t>
+  </si>
+  <si>
+    <t>STATUS CONTRACT</t>
+  </si>
+  <si>
+    <t>Issue present in inspected source</t>
+  </si>
+  <si>
+    <t>Some code fixed; unresolved conditions remain</t>
+  </si>
+  <si>
+    <t>Fix observed in source; still needs regression/runtime validation</t>
+  </si>
+  <si>
+    <t>Question or risk not independently demonstrated</t>
+  </si>
+  <si>
+    <t>Requires an explicit product/security policy</t>
+  </si>
+  <si>
+    <t>Automated/authorized tests executed and evidence stored</t>
+  </si>
+  <si>
+    <t>Fix independently verified and accepted</t>
+  </si>
+  <si>
+    <t>Previously fixed behavior has returned</t>
+  </si>
+  <si>
+    <t>FORTLESS   /   30 SECURITY AUDIT DOMAINS</t>
+  </si>
+  <si>
+    <t>Static source review expanded at 6203687. Coverage is NOT an independent runtime, load, security or pixel-diff test.</t>
+  </si>
+  <si>
+    <t>#</t>
+  </si>
+  <si>
+    <t>Scope</t>
+  </si>
+  <si>
+    <t>Related finding IDs</t>
+  </si>
+  <si>
+    <t>Audit coverage</t>
+  </si>
+  <si>
+    <t>01</t>
+  </si>
+  <si>
+    <t>Authentication</t>
+  </si>
+  <si>
+    <t>Login/register/reset, brute force, enumeration</t>
+  </si>
+  <si>
+    <t>SEC-09, FTL-SEC-205, NEW-362, NEW-363, NEW-364, NEW-365</t>
+  </si>
+  <si>
+    <t>STATIC_PARTIAL</t>
+  </si>
+  <si>
+    <t>02</t>
+  </si>
+  <si>
+    <t>Sessions &amp; Devices</t>
+  </si>
+  <si>
+    <t>Token rotation, expiry, login/logout, revocation</t>
+  </si>
+  <si>
+    <t>SEC-03, SEC-04, FTL-SEC-202, NEW-363</t>
+  </si>
+  <si>
+    <t>03</t>
+  </si>
+  <si>
+    <t>MFA &amp; Passkeys</t>
+  </si>
+  <si>
+    <t>TOTP, WebAuthn, recovery, replay, UV</t>
+  </si>
+  <si>
+    <t>FTL-SEC-201, FTL-SEC-202, FTL-SEC-203, NEW-306, NEW-307, NEW-318, NEW-358, NEW-360</t>
+  </si>
+  <si>
+    <t>04</t>
+  </si>
+  <si>
+    <t>Authorization / RBAC</t>
+  </si>
+  <si>
+    <t>Every API permission and role</t>
+  </si>
+  <si>
+    <t>FTL-UI-201, SSO-01, NEW-322, NEW-328, NEW-359</t>
+  </si>
+  <si>
+    <t>05</t>
+  </si>
+  <si>
+    <t>IDOR / BOLA</t>
+  </si>
+  <si>
+    <t>Cross-account resource access</t>
+  </si>
+  <si>
+    <t>SEC-05, NEW-310, NEW-322</t>
+  </si>
+  <si>
+    <t>06</t>
+  </si>
+  <si>
+    <t>Multi-tenancy</t>
+  </si>
+  <si>
+    <t>Organization/service separation</t>
+  </si>
+  <si>
+    <t>SEC-05, SEC-06, NEW-310, NEW-322</t>
+  </si>
+  <si>
+    <t>07</t>
+  </si>
+  <si>
+    <t>API Security</t>
+  </si>
+  <si>
+    <t>Request validation/mass assignment/rate limiting</t>
+  </si>
+  <si>
+    <t>FTL-SEC-205, NEW-311, NEW-321, NEW-328</t>
+  </si>
+  <si>
+    <t>08</t>
+  </si>
+  <si>
+    <t>CSRF &amp; CORS</t>
+  </si>
+  <si>
+    <t>Origin, cookies, CSRF all writes</t>
+  </si>
+  <si>
+    <t>RUNTIME_REQUIRED</t>
+  </si>
+  <si>
+    <t>09</t>
+  </si>
+  <si>
+    <t>XSS &amp; HTML Injection</t>
+  </si>
+  <si>
+    <t>Ticket/email/console/DOM output</t>
+  </si>
+  <si>
+    <t>UI-06, MAIL-01</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>SQL / Command Injection</t>
+  </si>
+  <si>
+    <t>SQL/shell/path/template injection</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>SSRF</t>
+  </si>
+  <si>
+    <t>Private IP, DNS rebinding, redirects</t>
+  </si>
+  <si>
+    <t>SEC-08, NEW-314</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>Secrets &amp; Credentials</t>
+  </si>
+  <si>
+    <t>Provider keys, vault, rotation</t>
+  </si>
+  <si>
+    <t>NEW-313, SEC-02, NEW-323</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>Pterodactyl API</t>
+  </si>
+  <si>
+    <t>Provider scoping &amp; ownership</t>
+  </si>
+  <si>
+    <t>FTL-PROV-201, FTL-UI-202, NEW-322, NEW-323</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>OIDC callback, native reset, revoke</t>
+  </si>
+  <si>
+    <t>SSO-01, SSO-02, SSO-03</t>
+  </si>
+  <si>
+    <t>Wings &amp; WebSockets</t>
+  </si>
+  <si>
+    <t>Socket tokens, console, revocation</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>File Manager</t>
+  </si>
+  <si>
+    <t>Traversal, archives, symlinks, quota</t>
+  </si>
+  <si>
+    <t>NEW-314, NEW-321</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>Minecraft Installers</t>
+  </si>
+  <si>
+    <t>SHA512, compatibility, redirect, limits</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>Web App Isolation</t>
+  </si>
+  <si>
+    <t>Container isolation, network, privilege</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>Stripe &amp; Payments</t>
+  </si>
+  <si>
+    <t>Signatures, replay, idempotency, ordering</t>
+  </si>
+  <si>
+    <t>FTL-BILL-201, FTL-BILL-203, FTL-BILL-204, FTL-BILL-206, NEW-324, NEW-340, NEW-345, NEW-346, NEW-347, NEW-349, NEW-350</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>Billing &amp; Subscriptions</t>
+  </si>
+  <si>
+    <t>Renewal, refunds, tax, coupons, invoices</t>
+  </si>
+  <si>
+    <t>FTL-BILL-202, FTL-BILL-205, NEW-301, NEW-303, NEW-304, NEW-305, NEW-316, NEW-319, NEW-324, NEW-330, NEW-333, NEW-334, NEW-338, NEW-344, NEW-348, NEW-351, NEW-352, NEW-353, NEW-355, NEW-356</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>Node, cap, retry, lifecycle</t>
+  </si>
+  <si>
+    <t>FTL-PROV-201, FTL-PROV-202, FTL-PROV-203, FTL-PROV-204, NEW-302, NEW-322, NEW-327, NEW-352, NEW-357</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>cPanel / WHM</t>
+  </si>
+  <si>
+    <t>Permission, lifecycle, safe API</t>
+  </si>
+  <si>
+    <t>FTL-PROV-201, SEC-08</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>Proxmox / VPS</t>
+  </si>
+  <si>
+    <t>VM isolation, templates, snapshots</t>
+  </si>
+  <si>
+    <t>FTL-PROV-201, NEW-326, NEW-327</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>DNS &amp; Domains</t>
+  </si>
+  <si>
+    <t>Ownership, delegation, DNS records</t>
+  </si>
+  <si>
+    <t>FTL-DNS-201, FTL-DNS-202</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>Database Security</t>
+  </si>
+  <si>
+    <t>Transactions, migrations, corruption</t>
+  </si>
+  <si>
+    <t>NEW-308, NEW-309, NEW-321</t>
   </si>
   <si>
     <t>26</t>
   </si>
   <si>
-    <t>58</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>PRIORITY &amp; STATUS</t>
-  </si>
-  <si>
-    <t>RELEASE CONTROL</t>
-  </si>
-  <si>
-    <t>Count</t>
-  </si>
-  <si>
-    <t>NOT CLEARED FOR REAL PAYMENTS Critical billing defects reproduced in source (checkout amount mismatch, inbox event loss, SEMI_ANNUAL settlement, scheduled cancellation). Static review plus local reproductions only.</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>39</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>61</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>TESTED</t>
-  </si>
-  <si>
-    <t>CLOSED</t>
-  </si>
-  <si>
-    <t>LATEST VERIFIED COMMIT</t>
-  </si>
-  <si>
-    <t>REGRESSION</t>
-  </si>
-  <si>
-    <t>3cb35de (independent audit batch 1)</t>
-  </si>
-  <si>
-    <t>STATUS CONTRACT</t>
-  </si>
-  <si>
-    <t>Issue present in inspected source</t>
-  </si>
-  <si>
-    <t>Some code fixed; unresolved conditions remain</t>
-  </si>
-  <si>
-    <t>Fix observed in source; still needs regression/runtime validation</t>
-  </si>
-  <si>
-    <t>Question or risk not independently demonstrated</t>
-  </si>
-  <si>
-    <t>Requires an explicit product/security policy</t>
-  </si>
-  <si>
-    <t>Automated/authorized tests executed and evidence stored</t>
-  </si>
-  <si>
-    <t>Fix independently verified and accepted</t>
-  </si>
-  <si>
-    <t>Previously fixed behavior has returned</t>
-  </si>
-  <si>
-    <t>FORTLESS   /   30 SECURITY AUDIT DOMAINS</t>
-  </si>
-  <si>
-    <t>Static source review expanded at 6203687. Coverage is NOT an independent runtime, load, security or pixel-diff test.</t>
-  </si>
-  <si>
-    <t>#</t>
-  </si>
-  <si>
-    <t>Scope</t>
-  </si>
-  <si>
-    <t>Related finding IDs</t>
-  </si>
-  <si>
-    <t>Audit coverage</t>
-  </si>
-  <si>
-    <t>01</t>
-  </si>
-  <si>
-    <t>Authentication</t>
-  </si>
-  <si>
-    <t>Login/register/reset, brute force, enumeration</t>
-  </si>
-  <si>
-    <t>SEC-09, FTL-SEC-205</t>
-  </si>
-  <si>
-    <t>STATIC_PARTIAL</t>
-  </si>
-  <si>
-    <t>02</t>
-  </si>
-  <si>
-    <t>Sessions &amp; Devices</t>
-  </si>
-  <si>
-    <t>Token rotation, expiry, login/logout, revocation</t>
-  </si>
-  <si>
-    <t>SEC-03, SEC-04, FTL-SEC-202</t>
-  </si>
-  <si>
-    <t>03</t>
-  </si>
-  <si>
-    <t>MFA &amp; Passkeys</t>
-  </si>
-  <si>
-    <t>TOTP, WebAuthn, recovery, replay, UV</t>
-  </si>
-  <si>
-    <t>FTL-SEC-201, FTL-SEC-202, FTL-SEC-203, NEW-306, NEW-307, NEW-318, NEW-358, NEW-360</t>
-  </si>
-  <si>
-    <t>04</t>
-  </si>
-  <si>
-    <t>Authorization / RBAC</t>
-  </si>
-  <si>
-    <t>Every API permission and role</t>
-  </si>
-  <si>
-    <t>FTL-UI-201, SSO-01, NEW-322, NEW-328, NEW-359</t>
-  </si>
-  <si>
-    <t>05</t>
-  </si>
-  <si>
-    <t>IDOR / BOLA</t>
-  </si>
-  <si>
-    <t>Cross-account resource access</t>
-  </si>
-  <si>
-    <t>SEC-05, NEW-310, NEW-322</t>
-  </si>
-  <si>
-    <t>06</t>
-  </si>
-  <si>
-    <t>Multi-tenancy</t>
-  </si>
-  <si>
-    <t>Organization/service separation</t>
-  </si>
-  <si>
-    <t>SEC-05, SEC-06, NEW-310, NEW-322</t>
-  </si>
-  <si>
-    <t>07</t>
-  </si>
-  <si>
-    <t>API Security</t>
-  </si>
-  <si>
-    <t>Request validation/mass assignment/rate limiting</t>
-  </si>
-  <si>
-    <t>FTL-SEC-205, NEW-311, NEW-321, NEW-328</t>
-  </si>
-  <si>
-    <t>08</t>
-  </si>
-  <si>
-    <t>CSRF &amp; CORS</t>
-  </si>
-  <si>
-    <t>Origin, cookies, CSRF all writes</t>
-  </si>
-  <si>
-    <t>RUNTIME_REQUIRED</t>
-  </si>
-  <si>
-    <t>09</t>
-  </si>
-  <si>
-    <t>XSS &amp; HTML Injection</t>
-  </si>
-  <si>
-    <t>Ticket/email/console/DOM output</t>
-  </si>
-  <si>
-    <t>UI-06, MAIL-01</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>SQL / Command Injection</t>
-  </si>
-  <si>
-    <t>SQL/shell/path/template injection</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>SSRF</t>
-  </si>
-  <si>
-    <t>Private IP, DNS rebinding, redirects</t>
-  </si>
-  <si>
-    <t>SEC-08, NEW-314</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>Secrets &amp; Credentials</t>
-  </si>
-  <si>
-    <t>Provider keys, vault, rotation</t>
-  </si>
-  <si>
-    <t>NEW-313, SEC-02, NEW-323</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>Pterodactyl API</t>
-  </si>
-  <si>
-    <t>Provider scoping &amp; ownership</t>
-  </si>
-  <si>
-    <t>FTL-PROV-201, FTL-UI-202, NEW-322, NEW-323</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>OIDC callback, native reset, revoke</t>
-  </si>
-  <si>
-    <t>SSO-01, SSO-02, SSO-03</t>
-  </si>
-  <si>
-    <t>Wings &amp; WebSockets</t>
-  </si>
-  <si>
-    <t>Socket tokens, console, revocation</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>File Manager</t>
-  </si>
-  <si>
-    <t>Traversal, archives, symlinks, quota</t>
-  </si>
-  <si>
-    <t>NEW-314, NEW-321</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>Minecraft Installers</t>
-  </si>
-  <si>
-    <t>SHA512, compatibility, redirect, limits</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>Web App Isolation</t>
-  </si>
-  <si>
-    <t>Container isolation, network, privilege</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>Stripe &amp; Payments</t>
-  </si>
-  <si>
-    <t>Signatures, replay, idempotency, ordering</t>
-  </si>
-  <si>
-    <t>FTL-BILL-201, FTL-BILL-203, FTL-BILL-204, FTL-BILL-206, NEW-324, NEW-340, NEW-345, NEW-346, NEW-347, NEW-349, NEW-350</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>Billing &amp; Subscriptions</t>
-  </si>
-  <si>
-    <t>Renewal, refunds, tax, coupons, invoices</t>
-  </si>
-  <si>
-    <t>FTL-BILL-202, FTL-BILL-205, NEW-301, NEW-303, NEW-304, NEW-305, NEW-316, NEW-319, NEW-324, NEW-330, NEW-333, NEW-334, NEW-338, NEW-344, NEW-348, NEW-351, NEW-352, NEW-353, NEW-355, NEW-356</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>Node, cap, retry, lifecycle</t>
-  </si>
-  <si>
-    <t>FTL-PROV-201, FTL-PROV-202, FTL-PROV-203, FTL-PROV-204, NEW-302, NEW-322, NEW-327, NEW-352, NEW-357</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>cPanel / WHM</t>
-  </si>
-  <si>
-    <t>Permission, lifecycle, safe API</t>
-  </si>
-  <si>
-    <t>FTL-PROV-201, SEC-08</t>
-  </si>
-  <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>Proxmox / VPS</t>
-  </si>
-  <si>
-    <t>VM isolation, templates, snapshots</t>
-  </si>
-  <si>
-    <t>FTL-PROV-201, NEW-326, NEW-327</t>
-  </si>
-  <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>DNS &amp; Domains</t>
-  </si>
-  <si>
-    <t>Ownership, delegation, DNS records</t>
-  </si>
-  <si>
-    <t>FTL-DNS-201, FTL-DNS-202</t>
-  </si>
-  <si>
-    <t>25</t>
-  </si>
-  <si>
-    <t>Database Security</t>
-  </si>
-  <si>
-    <t>Transactions, migrations, corruption</t>
-  </si>
-  <si>
-    <t>NEW-308, NEW-309, NEW-321</t>
-  </si>
-  <si>
     <t>Job leases, ordering, retry, dead letters</t>
   </si>
   <si>
@@ -3105,9 +3204,6 @@
     <t>NOT_STARTED</t>
   </si>
   <si>
-    <t>29</t>
-  </si>
-  <si>
     <t>Backups &amp; Recovery</t>
   </si>
   <si>
@@ -3310,6 +3406,18 @@
   </si>
   <si>
     <t>STATIC_SOURCE_REVIEW + local reproductions; test suite 237/237 and tsc clean at audit time</t>
+  </si>
+  <si>
+    <t>2026-10-19 06:20</t>
+  </si>
+  <si>
+    <t>Independent audit batch 2: identity flows (NEW-362..NEW-365) and live runtime configuration note</t>
+  </si>
+  <si>
+    <t>Registration, verification, login throttling and reset flows read end to end; live deployment settings classified without recording secrets. No implementation code changed.</t>
+  </si>
+  <si>
+    <t>STATIC_SOURCE_REVIEW</t>
   </si>
   <si>
     <t>FORTLESS   /   IMMUTABLE STATUS HISTORY</t>
@@ -4574,7 +4682,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:S109"/>
+  <dimension ref="A1:S113"/>
   <sheetFormatPr defaultRowHeight="0" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" customHeight="1"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
@@ -10727,6 +10835,242 @@
       </c>
       <c r="S109" t="s">
         <v>884</v>
+      </c>
+    </row>
+    <row r="110" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>885</v>
+      </c>
+      <c r="B110" t="s">
+        <v>308</v>
+      </c>
+      <c r="C110" t="s">
+        <v>62</v>
+      </c>
+      <c r="D110" t="s">
+        <v>24</v>
+      </c>
+      <c r="E110" t="s">
+        <v>886</v>
+      </c>
+      <c r="F110" t="s">
+        <v>112</v>
+      </c>
+      <c r="G110" t="s">
+        <v>27</v>
+      </c>
+      <c r="H110" t="s">
+        <v>27</v>
+      </c>
+      <c r="I110" t="s">
+        <v>206</v>
+      </c>
+      <c r="J110" t="s">
+        <v>206</v>
+      </c>
+      <c r="K110" t="s">
+        <v>887</v>
+      </c>
+      <c r="L110" t="s">
+        <v>888</v>
+      </c>
+      <c r="M110" t="s">
+        <v>889</v>
+      </c>
+      <c r="N110" t="s">
+        <v>890</v>
+      </c>
+      <c r="O110" t="s">
+        <v>891</v>
+      </c>
+      <c r="P110" t="s">
+        <v>747</v>
+      </c>
+      <c r="Q110" t="s">
+        <v>748</v>
+      </c>
+      <c r="R110" t="s">
+        <v>36</v>
+      </c>
+      <c r="S110" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="111" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>893</v>
+      </c>
+      <c r="B111" t="s">
+        <v>61</v>
+      </c>
+      <c r="C111" t="s">
+        <v>62</v>
+      </c>
+      <c r="D111" t="s">
+        <v>24</v>
+      </c>
+      <c r="E111" t="s">
+        <v>894</v>
+      </c>
+      <c r="F111" t="s">
+        <v>112</v>
+      </c>
+      <c r="G111" t="s">
+        <v>27</v>
+      </c>
+      <c r="H111" t="s">
+        <v>27</v>
+      </c>
+      <c r="I111" t="s">
+        <v>206</v>
+      </c>
+      <c r="J111" t="s">
+        <v>206</v>
+      </c>
+      <c r="K111" t="s">
+        <v>895</v>
+      </c>
+      <c r="L111" t="s">
+        <v>896</v>
+      </c>
+      <c r="M111" t="s">
+        <v>897</v>
+      </c>
+      <c r="N111" t="s">
+        <v>898</v>
+      </c>
+      <c r="O111" t="s">
+        <v>899</v>
+      </c>
+      <c r="P111" t="s">
+        <v>747</v>
+      </c>
+      <c r="Q111" t="s">
+        <v>748</v>
+      </c>
+      <c r="R111" t="s">
+        <v>36</v>
+      </c>
+      <c r="S111" t="s">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="112" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>901</v>
+      </c>
+      <c r="B112" t="s">
+        <v>308</v>
+      </c>
+      <c r="C112" t="s">
+        <v>62</v>
+      </c>
+      <c r="D112" t="s">
+        <v>24</v>
+      </c>
+      <c r="E112" t="s">
+        <v>902</v>
+      </c>
+      <c r="F112" t="s">
+        <v>453</v>
+      </c>
+      <c r="G112" t="s">
+        <v>27</v>
+      </c>
+      <c r="H112" t="s">
+        <v>27</v>
+      </c>
+      <c r="I112" t="s">
+        <v>206</v>
+      </c>
+      <c r="J112" t="s">
+        <v>206</v>
+      </c>
+      <c r="K112" t="s">
+        <v>903</v>
+      </c>
+      <c r="L112" t="s">
+        <v>904</v>
+      </c>
+      <c r="M112" t="s">
+        <v>905</v>
+      </c>
+      <c r="N112" t="s">
+        <v>906</v>
+      </c>
+      <c r="O112" t="s">
+        <v>907</v>
+      </c>
+      <c r="P112" t="s">
+        <v>747</v>
+      </c>
+      <c r="Q112" t="s">
+        <v>748</v>
+      </c>
+      <c r="R112" t="s">
+        <v>36</v>
+      </c>
+      <c r="S112" t="s">
+        <v>908</v>
+      </c>
+    </row>
+    <row r="113" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>909</v>
+      </c>
+      <c r="B113" t="s">
+        <v>308</v>
+      </c>
+      <c r="C113" t="s">
+        <v>62</v>
+      </c>
+      <c r="D113" t="s">
+        <v>24</v>
+      </c>
+      <c r="E113" t="s">
+        <v>910</v>
+      </c>
+      <c r="F113" t="s">
+        <v>112</v>
+      </c>
+      <c r="G113" t="s">
+        <v>27</v>
+      </c>
+      <c r="H113" t="s">
+        <v>27</v>
+      </c>
+      <c r="I113" t="s">
+        <v>206</v>
+      </c>
+      <c r="J113" t="s">
+        <v>206</v>
+      </c>
+      <c r="K113" t="s">
+        <v>911</v>
+      </c>
+      <c r="L113" t="s">
+        <v>912</v>
+      </c>
+      <c r="M113" t="s">
+        <v>913</v>
+      </c>
+      <c r="N113" t="s">
+        <v>914</v>
+      </c>
+      <c r="O113" t="s">
+        <v>915</v>
+      </c>
+      <c r="P113" t="s">
+        <v>747</v>
+      </c>
+      <c r="Q113" t="s">
+        <v>748</v>
+      </c>
+      <c r="R113" t="s">
+        <v>36</v>
+      </c>
+      <c r="S113" t="s">
+        <v>765</v>
       </c>
     </row>
   </sheetData>
@@ -10740,48 +11084,48 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>885</v>
+        <v>916</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>886</v>
+        <v>917</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>887</v>
+        <v>918</v>
       </c>
       <c r="C4" t="s">
-        <v>888</v>
+        <v>919</v>
       </c>
       <c r="E4" t="s">
-        <v>889</v>
+        <v>920</v>
       </c>
       <c r="G4" t="s">
-        <v>890</v>
+        <v>921</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>891</v>
+        <v>922</v>
       </c>
       <c r="C5" t="s">
-        <v>892</v>
+        <v>923</v>
       </c>
       <c r="E5" t="s">
-        <v>893</v>
+        <v>924</v>
       </c>
       <c r="G5" t="s">
-        <v>894</v>
+        <v>925</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>895</v>
+        <v>926</v>
       </c>
       <c r="F9" t="s">
-        <v>896</v>
+        <v>927</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -10789,16 +11133,16 @@
         <v>112</v>
       </c>
       <c r="B10" t="s">
-        <v>892</v>
+        <v>923</v>
       </c>
       <c r="C10" t="s">
         <v>3</v>
       </c>
       <c r="D10" t="s">
-        <v>897</v>
+        <v>928</v>
       </c>
       <c r="F10" t="s">
-        <v>898</v>
+        <v>929</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -10806,13 +11150,13 @@
         <v>86</v>
       </c>
       <c r="B11" t="s">
-        <v>899</v>
+        <v>930</v>
       </c>
       <c r="C11" t="s">
         <v>22</v>
       </c>
       <c r="D11" t="s">
-        <v>900</v>
+        <v>931</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -10820,13 +11164,13 @@
         <v>95</v>
       </c>
       <c r="B12" t="s">
-        <v>901</v>
+        <v>932</v>
       </c>
       <c r="C12" t="s">
         <v>61</v>
       </c>
       <c r="D12" t="s">
-        <v>902</v>
+        <v>933</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -10834,13 +11178,13 @@
         <v>453</v>
       </c>
       <c r="B13" t="s">
-        <v>903</v>
+        <v>934</v>
       </c>
       <c r="C13" t="s">
         <v>308</v>
       </c>
       <c r="D13" t="s">
-        <v>901</v>
+        <v>935</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
@@ -10848,42 +11192,42 @@
         <v>26</v>
       </c>
       <c r="B14" t="s">
-        <v>893</v>
+        <v>924</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>904</v>
+        <v>936</v>
       </c>
       <c r="B15" t="s">
-        <v>894</v>
+        <v>925</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>905</v>
+        <v>937</v>
       </c>
       <c r="B16" t="s">
-        <v>894</v>
+        <v>925</v>
       </c>
       <c r="F16" t="s">
-        <v>906</v>
+        <v>938</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>907</v>
+        <v>939</v>
       </c>
       <c r="B17" t="s">
-        <v>894</v>
+        <v>925</v>
       </c>
       <c r="F17" t="s">
-        <v>908</v>
+        <v>940</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>909</v>
+        <v>941</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
@@ -10891,7 +11235,7 @@
         <v>112</v>
       </c>
       <c r="C22" t="s">
-        <v>910</v>
+        <v>942</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
@@ -10899,7 +11243,7 @@
         <v>86</v>
       </c>
       <c r="C23" t="s">
-        <v>911</v>
+        <v>943</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
@@ -10907,7 +11251,7 @@
         <v>26</v>
       </c>
       <c r="C24" t="s">
-        <v>912</v>
+        <v>944</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
@@ -10915,7 +11259,7 @@
         <v>95</v>
       </c>
       <c r="C25" t="s">
-        <v>913</v>
+        <v>945</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
@@ -10923,31 +11267,31 @@
         <v>453</v>
       </c>
       <c r="C26" t="s">
-        <v>914</v>
+        <v>946</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>904</v>
+        <v>936</v>
       </c>
       <c r="C27" t="s">
-        <v>915</v>
+        <v>947</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>905</v>
+        <v>937</v>
       </c>
       <c r="C28" t="s">
-        <v>916</v>
+        <v>948</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>907</v>
+        <v>939</v>
       </c>
       <c r="C29" t="s">
-        <v>917</v>
+        <v>949</v>
       </c>
     </row>
   </sheetData>
@@ -10961,7 +11305,7 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>918</v>
+        <v>950</v>
       </c>
       <c r="B1"/>
       <c r="C1"/>
@@ -10970,7 +11314,7 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>919</v>
+        <v>951</v>
       </c>
       <c r="B2"/>
       <c r="C2"/>
@@ -10979,529 +11323,529 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>920</v>
+        <v>952</v>
       </c>
       <c r="B3" t="s">
         <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>921</v>
+        <v>953</v>
       </c>
       <c r="D3" t="s">
-        <v>922</v>
+        <v>954</v>
       </c>
       <c r="E3" t="s">
-        <v>923</v>
+        <v>955</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>924</v>
+        <v>956</v>
       </c>
       <c r="B4" t="s">
-        <v>925</v>
+        <v>957</v>
       </c>
       <c r="C4" t="s">
-        <v>926</v>
+        <v>958</v>
       </c>
       <c r="D4" t="s">
-        <v>927</v>
+        <v>959</v>
       </c>
       <c r="E4" t="s">
-        <v>928</v>
+        <v>960</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>929</v>
+        <v>961</v>
       </c>
       <c r="B5" t="s">
-        <v>930</v>
+        <v>962</v>
       </c>
       <c r="C5" t="s">
-        <v>931</v>
+        <v>963</v>
       </c>
       <c r="D5" t="s">
-        <v>932</v>
+        <v>964</v>
       </c>
       <c r="E5" t="s">
-        <v>928</v>
+        <v>960</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>933</v>
+        <v>965</v>
       </c>
       <c r="B6" t="s">
-        <v>934</v>
+        <v>966</v>
       </c>
       <c r="C6" t="s">
-        <v>935</v>
+        <v>967</v>
       </c>
       <c r="D6" t="s">
-        <v>936</v>
+        <v>968</v>
       </c>
       <c r="E6" t="s">
-        <v>928</v>
+        <v>960</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>937</v>
+        <v>969</v>
       </c>
       <c r="B7" t="s">
-        <v>938</v>
+        <v>970</v>
       </c>
       <c r="C7" t="s">
-        <v>939</v>
+        <v>971</v>
       </c>
       <c r="D7" t="s">
-        <v>940</v>
+        <v>972</v>
       </c>
       <c r="E7" t="s">
-        <v>928</v>
+        <v>960</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>941</v>
+        <v>973</v>
       </c>
       <c r="B8" t="s">
-        <v>942</v>
+        <v>974</v>
       </c>
       <c r="C8" t="s">
-        <v>943</v>
+        <v>975</v>
       </c>
       <c r="D8" t="s">
-        <v>944</v>
+        <v>976</v>
       </c>
       <c r="E8" t="s">
-        <v>928</v>
+        <v>960</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>945</v>
+        <v>977</v>
       </c>
       <c r="B9" t="s">
-        <v>946</v>
+        <v>978</v>
       </c>
       <c r="C9" t="s">
-        <v>947</v>
+        <v>979</v>
       </c>
       <c r="D9" t="s">
-        <v>948</v>
+        <v>980</v>
       </c>
       <c r="E9" t="s">
-        <v>928</v>
+        <v>960</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>949</v>
+        <v>981</v>
       </c>
       <c r="B10" t="s">
-        <v>950</v>
+        <v>982</v>
       </c>
       <c r="C10" t="s">
-        <v>951</v>
+        <v>983</v>
       </c>
       <c r="D10" t="s">
-        <v>952</v>
+        <v>984</v>
       </c>
       <c r="E10" t="s">
-        <v>928</v>
+        <v>960</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>953</v>
+        <v>985</v>
       </c>
       <c r="B11" t="s">
-        <v>954</v>
+        <v>986</v>
       </c>
       <c r="C11" t="s">
-        <v>955</v>
+        <v>987</v>
       </c>
       <c r="D11" t="s">
         <v>93</v>
       </c>
       <c r="E11" t="s">
-        <v>956</v>
+        <v>988</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>957</v>
+        <v>989</v>
       </c>
       <c r="B12" t="s">
-        <v>958</v>
+        <v>990</v>
       </c>
       <c r="C12" t="s">
-        <v>959</v>
+        <v>991</v>
       </c>
       <c r="D12" t="s">
+        <v>992</v>
+      </c>
+      <c r="E12" t="s">
         <v>960</v>
-      </c>
-      <c r="E12" t="s">
-        <v>928</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>961</v>
+        <v>993</v>
       </c>
       <c r="B13" t="s">
-        <v>962</v>
+        <v>994</v>
       </c>
       <c r="C13" t="s">
-        <v>963</v>
+        <v>995</v>
       </c>
       <c r="D13" t="s">
         <v>403</v>
       </c>
       <c r="E13" t="s">
-        <v>956</v>
+        <v>988</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>964</v>
+        <v>996</v>
       </c>
       <c r="B14" t="s">
-        <v>965</v>
+        <v>997</v>
       </c>
       <c r="C14" t="s">
-        <v>966</v>
+        <v>998</v>
       </c>
       <c r="D14" t="s">
-        <v>967</v>
+        <v>999</v>
       </c>
       <c r="E14" t="s">
-        <v>928</v>
+        <v>960</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>968</v>
+        <v>1000</v>
       </c>
       <c r="B15" t="s">
-        <v>969</v>
+        <v>1001</v>
       </c>
       <c r="C15" t="s">
-        <v>970</v>
+        <v>1002</v>
       </c>
       <c r="D15" t="s">
-        <v>971</v>
+        <v>1003</v>
       </c>
       <c r="E15" t="s">
-        <v>928</v>
+        <v>960</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>972</v>
+        <v>1004</v>
       </c>
       <c r="B16" t="s">
-        <v>973</v>
+        <v>1005</v>
       </c>
       <c r="C16" t="s">
-        <v>974</v>
+        <v>1006</v>
       </c>
       <c r="D16" t="s">
-        <v>975</v>
+        <v>1007</v>
       </c>
       <c r="E16" t="s">
-        <v>928</v>
+        <v>960</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>976</v>
+        <v>1008</v>
       </c>
       <c r="B17" t="s">
         <v>435</v>
       </c>
       <c r="C17" t="s">
-        <v>977</v>
+        <v>1009</v>
       </c>
       <c r="D17" t="s">
-        <v>978</v>
+        <v>1010</v>
       </c>
       <c r="E17" t="s">
-        <v>956</v>
+        <v>988</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>899</v>
+        <v>930</v>
       </c>
       <c r="B18" t="s">
-        <v>979</v>
+        <v>1011</v>
       </c>
       <c r="C18" t="s">
-        <v>980</v>
+        <v>1012</v>
       </c>
       <c r="D18" t="s">
         <v>316</v>
       </c>
       <c r="E18" t="s">
-        <v>956</v>
+        <v>988</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>981</v>
+        <v>1013</v>
       </c>
       <c r="B19" t="s">
-        <v>982</v>
+        <v>1014</v>
       </c>
       <c r="C19" t="s">
-        <v>983</v>
+        <v>1015</v>
       </c>
       <c r="D19" t="s">
-        <v>984</v>
+        <v>1016</v>
       </c>
       <c r="E19" t="s">
-        <v>956</v>
+        <v>988</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>985</v>
+        <v>1017</v>
       </c>
       <c r="B20" t="s">
-        <v>986</v>
+        <v>1018</v>
       </c>
       <c r="C20" t="s">
-        <v>987</v>
+        <v>1019</v>
       </c>
       <c r="D20" t="s">
         <v>475</v>
       </c>
       <c r="E20" t="s">
-        <v>928</v>
+        <v>960</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>988</v>
+        <v>1020</v>
       </c>
       <c r="B21" t="s">
-        <v>989</v>
+        <v>1021</v>
       </c>
       <c r="C21" t="s">
-        <v>990</v>
+        <v>1022</v>
       </c>
       <c r="D21" t="s">
         <v>213</v>
       </c>
       <c r="E21" t="s">
-        <v>956</v>
+        <v>988</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>991</v>
+        <v>1023</v>
       </c>
       <c r="B22" t="s">
-        <v>992</v>
+        <v>1024</v>
       </c>
       <c r="C22" t="s">
-        <v>993</v>
+        <v>1025</v>
       </c>
       <c r="D22" t="s">
-        <v>994</v>
+        <v>1026</v>
       </c>
       <c r="E22" t="s">
-        <v>928</v>
+        <v>960</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>995</v>
+        <v>1027</v>
       </c>
       <c r="B23" t="s">
-        <v>996</v>
+        <v>1028</v>
       </c>
       <c r="C23" t="s">
-        <v>997</v>
+        <v>1029</v>
       </c>
       <c r="D23" t="s">
-        <v>998</v>
+        <v>1030</v>
       </c>
       <c r="E23" t="s">
-        <v>928</v>
+        <v>960</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>999</v>
+        <v>1031</v>
       </c>
       <c r="B24" t="s">
         <v>214</v>
       </c>
       <c r="C24" t="s">
-        <v>1000</v>
+        <v>1032</v>
       </c>
       <c r="D24" t="s">
-        <v>1001</v>
+        <v>1033</v>
       </c>
       <c r="E24" t="s">
-        <v>928</v>
+        <v>960</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>1002</v>
+        <v>1034</v>
       </c>
       <c r="B25" t="s">
-        <v>1003</v>
+        <v>1035</v>
       </c>
       <c r="C25" t="s">
-        <v>1004</v>
+        <v>1036</v>
       </c>
       <c r="D25" t="s">
-        <v>1005</v>
+        <v>1037</v>
       </c>
       <c r="E25" t="s">
-        <v>956</v>
+        <v>988</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>1006</v>
+        <v>1038</v>
       </c>
       <c r="B26" t="s">
-        <v>1007</v>
+        <v>1039</v>
       </c>
       <c r="C26" t="s">
-        <v>1008</v>
+        <v>1040</v>
       </c>
       <c r="D26" t="s">
-        <v>1009</v>
+        <v>1041</v>
       </c>
       <c r="E26" t="s">
-        <v>956</v>
+        <v>988</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>1010</v>
+        <v>1042</v>
       </c>
       <c r="B27" t="s">
-        <v>1011</v>
+        <v>1043</v>
       </c>
       <c r="C27" t="s">
-        <v>1012</v>
+        <v>1044</v>
       </c>
       <c r="D27" t="s">
-        <v>1013</v>
+        <v>1045</v>
       </c>
       <c r="E27" t="s">
-        <v>928</v>
+        <v>960</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>1014</v>
+        <v>1046</v>
       </c>
       <c r="B28" t="s">
-        <v>1015</v>
+        <v>1047</v>
       </c>
       <c r="C28" t="s">
-        <v>1016</v>
+        <v>1048</v>
       </c>
       <c r="D28" t="s">
-        <v>1017</v>
+        <v>1049</v>
       </c>
       <c r="E28" t="s">
-        <v>928</v>
+        <v>960</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>892</v>
+        <v>1050</v>
       </c>
       <c r="B29" t="s">
         <v>822</v>
       </c>
       <c r="C29" t="s">
-        <v>1018</v>
+        <v>1051</v>
       </c>
       <c r="D29" t="s">
-        <v>1019</v>
+        <v>1052</v>
       </c>
       <c r="E29" t="s">
-        <v>928</v>
+        <v>960</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>1020</v>
+        <v>1053</v>
       </c>
       <c r="B30" t="s">
-        <v>1021</v>
+        <v>1054</v>
       </c>
       <c r="C30" t="s">
-        <v>1022</v>
+        <v>1055</v>
       </c>
       <c r="D30" t="s">
-        <v>1023</v>
+        <v>1056</v>
       </c>
       <c r="E30" t="s">
-        <v>956</v>
+        <v>988</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>1024</v>
+        <v>1057</v>
       </c>
       <c r="B31" t="s">
-        <v>1025</v>
+        <v>1058</v>
       </c>
       <c r="C31" t="s">
-        <v>1026</v>
+        <v>1059</v>
       </c>
       <c r="D31" t="s">
         <v>93</v>
       </c>
       <c r="E31" t="s">
-        <v>1027</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>1028</v>
+        <v>923</v>
       </c>
       <c r="B32" t="s">
-        <v>1029</v>
+        <v>1061</v>
       </c>
       <c r="C32" t="s">
-        <v>1030</v>
+        <v>1062</v>
       </c>
       <c r="D32" t="s">
-        <v>1031</v>
+        <v>1063</v>
       </c>
       <c r="E32" t="s">
-        <v>928</v>
+        <v>960</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>1032</v>
+        <v>1064</v>
       </c>
       <c r="B33" t="s">
-        <v>1033</v>
+        <v>1065</v>
       </c>
       <c r="C33" t="s">
-        <v>1034</v>
+        <v>1066</v>
       </c>
       <c r="D33" t="s">
-        <v>1035</v>
+        <v>1067</v>
       </c>
       <c r="E33" t="s">
-        <v>956</v>
+        <v>988</v>
       </c>
     </row>
   </sheetData>
@@ -11515,157 +11859,157 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr defaultRowHeight="0" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" customHeight="1"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>1036</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1037</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>1038</v>
+        <v>1070</v>
       </c>
       <c r="B3" t="s">
-        <v>1039</v>
+        <v>1071</v>
       </c>
       <c r="C3" t="s">
-        <v>1040</v>
+        <v>1072</v>
       </c>
       <c r="D3" t="s">
-        <v>1041</v>
+        <v>1073</v>
       </c>
       <c r="E3" t="s">
-        <v>1042</v>
+        <v>1074</v>
       </c>
       <c r="F3" t="s">
-        <v>1043</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1044</v>
+        <v>1076</v>
       </c>
       <c r="B4" t="s">
         <v>28</v>
       </c>
       <c r="C4" t="s">
-        <v>1045</v>
+        <v>1077</v>
       </c>
       <c r="D4" t="s">
-        <v>1046</v>
+        <v>1078</v>
       </c>
       <c r="E4" t="s">
-        <v>1047</v>
+        <v>1079</v>
       </c>
       <c r="F4" t="s">
-        <v>1048</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1049</v>
+        <v>1081</v>
       </c>
       <c r="B5" t="s">
-        <v>1050</v>
+        <v>1082</v>
       </c>
       <c r="C5" t="s">
-        <v>1051</v>
+        <v>1083</v>
       </c>
       <c r="D5" t="s">
-        <v>1052</v>
+        <v>1084</v>
       </c>
       <c r="E5" t="s">
-        <v>1053</v>
+        <v>1085</v>
       </c>
       <c r="F5" t="s">
-        <v>1054</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>1055</v>
+        <v>1087</v>
       </c>
       <c r="B6" t="s">
-        <v>1056</v>
+        <v>1088</v>
       </c>
       <c r="C6" t="s">
-        <v>1057</v>
+        <v>1089</v>
       </c>
       <c r="D6" t="s">
-        <v>1058</v>
+        <v>1090</v>
       </c>
       <c r="E6" t="s">
-        <v>1059</v>
+        <v>1091</v>
       </c>
       <c r="F6" t="s">
-        <v>1060</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>1061</v>
+        <v>1093</v>
       </c>
       <c r="B7" t="s">
-        <v>1062</v>
+        <v>1094</v>
       </c>
       <c r="C7" t="s">
-        <v>1063</v>
+        <v>1095</v>
       </c>
       <c r="D7" t="s">
-        <v>1064</v>
+        <v>1096</v>
       </c>
       <c r="E7" t="s">
-        <v>1059</v>
+        <v>1091</v>
       </c>
       <c r="F7" t="s">
-        <v>1065</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>1066</v>
+        <v>1098</v>
       </c>
       <c r="B8" t="s">
-        <v>1067</v>
+        <v>1099</v>
       </c>
       <c r="C8" t="s">
-        <v>1068</v>
+        <v>1100</v>
       </c>
       <c r="D8" t="s">
-        <v>1069</v>
+        <v>1101</v>
       </c>
       <c r="E8" t="s">
-        <v>1059</v>
+        <v>1091</v>
       </c>
       <c r="F8" t="s">
-        <v>1065</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>1070</v>
+        <v>1102</v>
       </c>
       <c r="B9" t="s">
         <v>29</v>
       </c>
       <c r="C9" t="s">
-        <v>1071</v>
+        <v>1103</v>
       </c>
       <c r="D9" t="s">
-        <v>1072</v>
+        <v>1104</v>
       </c>
       <c r="E9" t="s">
-        <v>1047</v>
+        <v>1079</v>
       </c>
       <c r="F9" t="s">
-        <v>1073</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -11676,95 +12020,115 @@
         <v>29</v>
       </c>
       <c r="C10" t="s">
-        <v>1074</v>
+        <v>1106</v>
       </c>
       <c r="D10" t="s">
-        <v>1075</v>
+        <v>1107</v>
       </c>
       <c r="E10" t="s">
-        <v>1076</v>
+        <v>1108</v>
       </c>
       <c r="F10" t="s">
-        <v>1077</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>1078</v>
+        <v>1110</v>
       </c>
       <c r="B11" t="s">
         <v>55</v>
       </c>
       <c r="C11" t="s">
-        <v>1079</v>
+        <v>1111</v>
       </c>
       <c r="D11" t="s">
-        <v>1080</v>
+        <v>1112</v>
       </c>
       <c r="E11" t="s">
-        <v>1076</v>
+        <v>1108</v>
       </c>
       <c r="F11" t="s">
-        <v>1081</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>1082</v>
+        <v>1114</v>
       </c>
       <c r="B12" t="s">
         <v>161</v>
       </c>
       <c r="C12" t="s">
-        <v>1083</v>
+        <v>1115</v>
       </c>
       <c r="D12" t="s">
-        <v>1084</v>
+        <v>1116</v>
       </c>
       <c r="E12" t="s">
-        <v>1085</v>
+        <v>1117</v>
       </c>
       <c r="F12" t="s">
-        <v>1086</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>1087</v>
+        <v>1119</v>
       </c>
       <c r="B13" t="s">
-        <v>1088</v>
+        <v>1120</v>
       </c>
       <c r="C13" t="s">
-        <v>1089</v>
+        <v>1121</v>
       </c>
       <c r="D13" t="s">
-        <v>1090</v>
+        <v>1122</v>
       </c>
       <c r="E13" t="s">
-        <v>1091</v>
+        <v>1123</v>
       </c>
       <c r="F13" t="s">
-        <v>1092</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>1093</v>
+        <v>1125</v>
       </c>
       <c r="B14" t="s">
         <v>206</v>
       </c>
       <c r="C14" t="s">
-        <v>1094</v>
+        <v>1126</v>
       </c>
       <c r="D14" t="s">
-        <v>1095</v>
+        <v>1127</v>
       </c>
       <c r="E14" t="s">
-        <v>1096</v>
+        <v>1128</v>
       </c>
       <c r="F14" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>1129</v>
+      </c>
+      <c r="B15" t="s">
+        <v>206</v>
+      </c>
+      <c r="C15" t="s">
+        <v>1130</v>
+      </c>
+      <c r="D15" t="s">
+        <v>1131</v>
+      </c>
+      <c r="E15" t="s">
+        <v>1132</v>
+      </c>
+      <c r="F15" t="s">
         <v>748</v>
       </c>
     </row>
@@ -11774,40 +12138,40 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G125"/>
+  <dimension ref="A1:G129"/>
   <sheetFormatPr defaultRowHeight="0" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" customHeight="1"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>1097</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1098</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>1099</v>
+        <v>1135</v>
       </c>
       <c r="B3" t="s">
-        <v>1100</v>
+        <v>1136</v>
       </c>
       <c r="C3" t="s">
-        <v>1101</v>
+        <v>1137</v>
       </c>
       <c r="D3" t="s">
-        <v>1102</v>
+        <v>1138</v>
       </c>
       <c r="E3" t="s">
-        <v>1103</v>
+        <v>1139</v>
       </c>
       <c r="F3" t="s">
-        <v>1104</v>
+        <v>1140</v>
       </c>
       <c r="G3" t="s">
-        <v>1105</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -11827,10 +12191,10 @@
         <v>26</v>
       </c>
       <c r="F4" t="s">
-        <v>1106</v>
+        <v>1142</v>
       </c>
       <c r="G4" t="s">
-        <v>1107</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -11850,10 +12214,10 @@
         <v>26</v>
       </c>
       <c r="F5" t="s">
-        <v>1106</v>
+        <v>1142</v>
       </c>
       <c r="G5" t="s">
-        <v>1108</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -11873,10 +12237,10 @@
         <v>26</v>
       </c>
       <c r="F6" t="s">
-        <v>1106</v>
+        <v>1142</v>
       </c>
       <c r="G6" t="s">
-        <v>1109</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -11896,10 +12260,10 @@
         <v>86</v>
       </c>
       <c r="F7" t="s">
-        <v>1106</v>
+        <v>1142</v>
       </c>
       <c r="G7" t="s">
-        <v>1110</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -11919,10 +12283,10 @@
         <v>26</v>
       </c>
       <c r="F8" t="s">
-        <v>1106</v>
+        <v>1142</v>
       </c>
       <c r="G8" t="s">
-        <v>1111</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -11942,10 +12306,10 @@
         <v>26</v>
       </c>
       <c r="F9" t="s">
-        <v>1106</v>
+        <v>1142</v>
       </c>
       <c r="G9" t="s">
-        <v>1112</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -11965,10 +12329,10 @@
         <v>26</v>
       </c>
       <c r="F10" t="s">
-        <v>1106</v>
+        <v>1142</v>
       </c>
       <c r="G10" t="s">
-        <v>1113</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -11988,10 +12352,10 @@
         <v>86</v>
       </c>
       <c r="F11" t="s">
-        <v>1106</v>
+        <v>1142</v>
       </c>
       <c r="G11" t="s">
-        <v>1114</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -12011,10 +12375,10 @@
         <v>86</v>
       </c>
       <c r="F12" t="s">
-        <v>1106</v>
+        <v>1142</v>
       </c>
       <c r="G12" t="s">
-        <v>1115</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -12034,10 +12398,10 @@
         <v>26</v>
       </c>
       <c r="F13" t="s">
-        <v>1106</v>
+        <v>1142</v>
       </c>
       <c r="G13" t="s">
-        <v>1116</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -12057,10 +12421,10 @@
         <v>26</v>
       </c>
       <c r="F14" t="s">
-        <v>1117</v>
+        <v>1153</v>
       </c>
       <c r="G14" t="s">
-        <v>1118</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -12080,10 +12444,10 @@
         <v>26</v>
       </c>
       <c r="F15" t="s">
-        <v>1117</v>
+        <v>1153</v>
       </c>
       <c r="G15" t="s">
-        <v>1119</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -12103,10 +12467,10 @@
         <v>26</v>
       </c>
       <c r="F16" t="s">
-        <v>1117</v>
+        <v>1153</v>
       </c>
       <c r="G16" t="s">
-        <v>1120</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -12126,10 +12490,10 @@
         <v>26</v>
       </c>
       <c r="F17" t="s">
-        <v>1117</v>
+        <v>1153</v>
       </c>
       <c r="G17" t="s">
-        <v>1121</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -12149,10 +12513,10 @@
         <v>26</v>
       </c>
       <c r="F18" t="s">
-        <v>1117</v>
+        <v>1153</v>
       </c>
       <c r="G18" t="s">
-        <v>1122</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -12172,10 +12536,10 @@
         <v>26</v>
       </c>
       <c r="F19" t="s">
-        <v>1117</v>
+        <v>1153</v>
       </c>
       <c r="G19" t="s">
-        <v>1123</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -12195,10 +12559,10 @@
         <v>86</v>
       </c>
       <c r="F20" t="s">
-        <v>1117</v>
+        <v>1153</v>
       </c>
       <c r="G20" t="s">
-        <v>1124</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -12218,10 +12582,10 @@
         <v>86</v>
       </c>
       <c r="F21" t="s">
-        <v>1117</v>
+        <v>1153</v>
       </c>
       <c r="G21" t="s">
-        <v>1125</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
@@ -12241,10 +12605,10 @@
         <v>26</v>
       </c>
       <c r="F22" t="s">
-        <v>1117</v>
+        <v>1153</v>
       </c>
       <c r="G22" t="s">
-        <v>1126</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
@@ -12264,10 +12628,10 @@
         <v>86</v>
       </c>
       <c r="F23" t="s">
-        <v>1117</v>
+        <v>1153</v>
       </c>
       <c r="G23" t="s">
-        <v>1127</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -12287,10 +12651,10 @@
         <v>86</v>
       </c>
       <c r="F24" t="s">
-        <v>1117</v>
+        <v>1153</v>
       </c>
       <c r="G24" t="s">
-        <v>1128</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
@@ -12310,10 +12674,10 @@
         <v>86</v>
       </c>
       <c r="F25" t="s">
-        <v>1117</v>
+        <v>1153</v>
       </c>
       <c r="G25" t="s">
-        <v>1129</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
@@ -12333,10 +12697,10 @@
         <v>86</v>
       </c>
       <c r="F26" t="s">
-        <v>1117</v>
+        <v>1153</v>
       </c>
       <c r="G26" t="s">
-        <v>1130</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
@@ -12356,10 +12720,10 @@
         <v>26</v>
       </c>
       <c r="F27" t="s">
-        <v>1117</v>
+        <v>1153</v>
       </c>
       <c r="G27" t="s">
-        <v>1131</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
@@ -12379,10 +12743,10 @@
         <v>86</v>
       </c>
       <c r="F28" t="s">
-        <v>1117</v>
+        <v>1153</v>
       </c>
       <c r="G28" t="s">
-        <v>1132</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
@@ -12402,10 +12766,10 @@
         <v>86</v>
       </c>
       <c r="F29" t="s">
-        <v>1117</v>
+        <v>1153</v>
       </c>
       <c r="G29" t="s">
-        <v>1133</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
@@ -12425,10 +12789,10 @@
         <v>26</v>
       </c>
       <c r="F30" t="s">
-        <v>1117</v>
+        <v>1153</v>
       </c>
       <c r="G30" t="s">
-        <v>1134</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
@@ -12448,10 +12812,10 @@
         <v>26</v>
       </c>
       <c r="F31" t="s">
-        <v>1117</v>
+        <v>1153</v>
       </c>
       <c r="G31" t="s">
-        <v>1135</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
@@ -12471,10 +12835,10 @@
         <v>86</v>
       </c>
       <c r="F32" t="s">
-        <v>1117</v>
+        <v>1153</v>
       </c>
       <c r="G32" t="s">
-        <v>1136</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
@@ -12494,10 +12858,10 @@
         <v>86</v>
       </c>
       <c r="F33" t="s">
-        <v>1117</v>
+        <v>1153</v>
       </c>
       <c r="G33" t="s">
-        <v>1137</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
@@ -12517,10 +12881,10 @@
         <v>86</v>
       </c>
       <c r="F34" t="s">
-        <v>1117</v>
+        <v>1153</v>
       </c>
       <c r="G34" t="s">
-        <v>1138</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
@@ -12540,7 +12904,7 @@
         <v>26</v>
       </c>
       <c r="F35" t="s">
-        <v>1139</v>
+        <v>1175</v>
       </c>
       <c r="G35" t="s">
         <v>168</v>
@@ -12563,7 +12927,7 @@
         <v>26</v>
       </c>
       <c r="F36" t="s">
-        <v>1139</v>
+        <v>1175</v>
       </c>
       <c r="G36" t="s">
         <v>177</v>
@@ -12586,7 +12950,7 @@
         <v>26</v>
       </c>
       <c r="F37" t="s">
-        <v>1139</v>
+        <v>1175</v>
       </c>
       <c r="G37" t="s">
         <v>194</v>
@@ -12609,7 +12973,7 @@
         <v>26</v>
       </c>
       <c r="F38" t="s">
-        <v>1139</v>
+        <v>1175</v>
       </c>
       <c r="G38" t="s">
         <v>203</v>
@@ -12632,7 +12996,7 @@
         <v>26</v>
       </c>
       <c r="F39" t="s">
-        <v>1139</v>
+        <v>1175</v>
       </c>
       <c r="G39" t="s">
         <v>222</v>
@@ -12655,7 +13019,7 @@
         <v>26</v>
       </c>
       <c r="F40" t="s">
-        <v>1139</v>
+        <v>1175</v>
       </c>
       <c r="G40" t="s">
         <v>245</v>
@@ -12678,10 +13042,10 @@
         <v>26</v>
       </c>
       <c r="F41" t="s">
-        <v>1139</v>
+        <v>1175</v>
       </c>
       <c r="G41" t="s">
-        <v>1140</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
@@ -12701,10 +13065,10 @@
         <v>26</v>
       </c>
       <c r="F42" t="s">
-        <v>1139</v>
+        <v>1175</v>
       </c>
       <c r="G42" t="s">
-        <v>1141</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
@@ -12724,10 +13088,10 @@
         <v>26</v>
       </c>
       <c r="F43" t="s">
-        <v>1139</v>
+        <v>1175</v>
       </c>
       <c r="G43" t="s">
-        <v>1142</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
@@ -12747,7 +13111,7 @@
         <v>26</v>
       </c>
       <c r="F44" t="s">
-        <v>1139</v>
+        <v>1175</v>
       </c>
       <c r="G44" t="s">
         <v>360</v>
@@ -12770,7 +13134,7 @@
         <v>26</v>
       </c>
       <c r="F45" t="s">
-        <v>1139</v>
+        <v>1175</v>
       </c>
       <c r="G45" t="s">
         <v>368</v>
@@ -12793,10 +13157,10 @@
         <v>26</v>
       </c>
       <c r="F46" t="s">
-        <v>1139</v>
+        <v>1175</v>
       </c>
       <c r="G46" t="s">
-        <v>1143</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
@@ -12816,7 +13180,7 @@
         <v>26</v>
       </c>
       <c r="F47" t="s">
-        <v>1139</v>
+        <v>1175</v>
       </c>
       <c r="G47" t="s">
         <v>386</v>
@@ -12839,10 +13203,10 @@
         <v>26</v>
       </c>
       <c r="F48" t="s">
-        <v>1139</v>
+        <v>1175</v>
       </c>
       <c r="G48" t="s">
-        <v>1144</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
@@ -12862,7 +13226,7 @@
         <v>26</v>
       </c>
       <c r="F49" t="s">
-        <v>1139</v>
+        <v>1175</v>
       </c>
       <c r="G49" t="s">
         <v>402</v>
@@ -12885,7 +13249,7 @@
         <v>26</v>
       </c>
       <c r="F50" t="s">
-        <v>1139</v>
+        <v>1175</v>
       </c>
       <c r="G50" t="s">
         <v>411</v>
@@ -12908,7 +13272,7 @@
         <v>26</v>
       </c>
       <c r="F51" t="s">
-        <v>1139</v>
+        <v>1175</v>
       </c>
       <c r="G51" t="s">
         <v>419</v>
@@ -12931,7 +13295,7 @@
         <v>26</v>
       </c>
       <c r="F52" t="s">
-        <v>1139</v>
+        <v>1175</v>
       </c>
       <c r="G52" t="s">
         <v>426</v>
@@ -12954,7 +13318,7 @@
         <v>26</v>
       </c>
       <c r="F53" t="s">
-        <v>1139</v>
+        <v>1175</v>
       </c>
       <c r="G53" t="s">
         <v>433</v>
@@ -12977,7 +13341,7 @@
         <v>26</v>
       </c>
       <c r="F54" t="s">
-        <v>1139</v>
+        <v>1175</v>
       </c>
       <c r="G54" t="s">
         <v>467</v>
@@ -13000,7 +13364,7 @@
         <v>26</v>
       </c>
       <c r="F55" t="s">
-        <v>1139</v>
+        <v>1175</v>
       </c>
       <c r="G55" t="s">
         <v>485</v>
@@ -13023,7 +13387,7 @@
         <v>26</v>
       </c>
       <c r="F56" t="s">
-        <v>1139</v>
+        <v>1175</v>
       </c>
       <c r="G56" t="s">
         <v>494</v>
@@ -13046,7 +13410,7 @@
         <v>26</v>
       </c>
       <c r="F57" t="s">
-        <v>1139</v>
+        <v>1175</v>
       </c>
       <c r="G57" t="s">
         <v>502</v>
@@ -13069,7 +13433,7 @@
         <v>26</v>
       </c>
       <c r="F58" t="s">
-        <v>1139</v>
+        <v>1175</v>
       </c>
       <c r="G58" t="s">
         <v>511</v>
@@ -13092,7 +13456,7 @@
         <v>26</v>
       </c>
       <c r="F59" t="s">
-        <v>1139</v>
+        <v>1175</v>
       </c>
       <c r="G59" t="s">
         <v>520</v>
@@ -13115,7 +13479,7 @@
         <v>26</v>
       </c>
       <c r="F60" t="s">
-        <v>1139</v>
+        <v>1175</v>
       </c>
       <c r="G60" t="s">
         <v>530</v>
@@ -13138,7 +13502,7 @@
         <v>26</v>
       </c>
       <c r="F61" t="s">
-        <v>1139</v>
+        <v>1175</v>
       </c>
       <c r="G61" t="s">
         <v>539</v>
@@ -13161,7 +13525,7 @@
         <v>26</v>
       </c>
       <c r="F62" t="s">
-        <v>1139</v>
+        <v>1175</v>
       </c>
       <c r="G62" t="s">
         <v>547</v>
@@ -13184,7 +13548,7 @@
         <v>26</v>
       </c>
       <c r="F63" t="s">
-        <v>1139</v>
+        <v>1175</v>
       </c>
       <c r="G63" t="s">
         <v>557</v>
@@ -13207,7 +13571,7 @@
         <v>26</v>
       </c>
       <c r="F64" t="s">
-        <v>1139</v>
+        <v>1175</v>
       </c>
       <c r="G64" t="s">
         <v>567</v>
@@ -13230,7 +13594,7 @@
         <v>26</v>
       </c>
       <c r="F65" t="s">
-        <v>1139</v>
+        <v>1175</v>
       </c>
       <c r="G65" t="s">
         <v>576</v>
@@ -13253,7 +13617,7 @@
         <v>26</v>
       </c>
       <c r="F66" t="s">
-        <v>1139</v>
+        <v>1175</v>
       </c>
       <c r="G66" t="s">
         <v>584</v>
@@ -13276,7 +13640,7 @@
         <v>26</v>
       </c>
       <c r="F67" t="s">
-        <v>1139</v>
+        <v>1175</v>
       </c>
       <c r="G67" t="s">
         <v>594</v>
@@ -13299,7 +13663,7 @@
         <v>26</v>
       </c>
       <c r="F68" t="s">
-        <v>1139</v>
+        <v>1175</v>
       </c>
       <c r="G68" t="s">
         <v>602</v>
@@ -13322,7 +13686,7 @@
         <v>26</v>
       </c>
       <c r="F69" t="s">
-        <v>1139</v>
+        <v>1175</v>
       </c>
       <c r="G69" t="s">
         <v>611</v>
@@ -13345,7 +13709,7 @@
         <v>26</v>
       </c>
       <c r="F70" t="s">
-        <v>1139</v>
+        <v>1175</v>
       </c>
       <c r="G70" t="s">
         <v>618</v>
@@ -13368,10 +13732,10 @@
         <v>26</v>
       </c>
       <c r="F71" t="s">
-        <v>1139</v>
+        <v>1175</v>
       </c>
       <c r="G71" t="s">
-        <v>1145</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
@@ -13391,10 +13755,10 @@
         <v>26</v>
       </c>
       <c r="F72" t="s">
-        <v>1139</v>
+        <v>1175</v>
       </c>
       <c r="G72" t="s">
-        <v>1146</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
@@ -13414,10 +13778,10 @@
         <v>26</v>
       </c>
       <c r="F73" t="s">
-        <v>1139</v>
+        <v>1175</v>
       </c>
       <c r="G73" t="s">
-        <v>1147</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
@@ -13437,10 +13801,10 @@
         <v>26</v>
       </c>
       <c r="F74" t="s">
-        <v>1139</v>
+        <v>1175</v>
       </c>
       <c r="G74" t="s">
-        <v>1148</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
@@ -13460,10 +13824,10 @@
         <v>26</v>
       </c>
       <c r="F75" t="s">
-        <v>1139</v>
+        <v>1175</v>
       </c>
       <c r="G75" t="s">
-        <v>1149</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
@@ -13483,10 +13847,10 @@
         <v>26</v>
       </c>
       <c r="F76" t="s">
-        <v>1139</v>
+        <v>1175</v>
       </c>
       <c r="G76" t="s">
-        <v>1150</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
@@ -13506,10 +13870,10 @@
         <v>26</v>
       </c>
       <c r="F77" t="s">
-        <v>1139</v>
+        <v>1175</v>
       </c>
       <c r="G77" t="s">
-        <v>1151</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
@@ -13529,10 +13893,10 @@
         <v>26</v>
       </c>
       <c r="F78" t="s">
-        <v>1139</v>
+        <v>1175</v>
       </c>
       <c r="G78" t="s">
-        <v>1152</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
@@ -13552,10 +13916,10 @@
         <v>26</v>
       </c>
       <c r="F79" t="s">
-        <v>1139</v>
+        <v>1175</v>
       </c>
       <c r="G79" t="s">
-        <v>1153</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
@@ -13563,7 +13927,7 @@
         <v>27</v>
       </c>
       <c r="B80" t="s">
-        <v>1088</v>
+        <v>1120</v>
       </c>
       <c r="C80" t="s">
         <v>697</v>
@@ -13575,10 +13939,10 @@
         <v>26</v>
       </c>
       <c r="F80" t="s">
-        <v>1154</v>
+        <v>1190</v>
       </c>
       <c r="G80" t="s">
-        <v>1155</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
@@ -13586,7 +13950,7 @@
         <v>27</v>
       </c>
       <c r="B81" t="s">
-        <v>1088</v>
+        <v>1120</v>
       </c>
       <c r="C81" t="s">
         <v>708</v>
@@ -13598,10 +13962,10 @@
         <v>26</v>
       </c>
       <c r="F81" t="s">
-        <v>1154</v>
+        <v>1190</v>
       </c>
       <c r="G81" t="s">
-        <v>1156</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
@@ -13609,7 +13973,7 @@
         <v>27</v>
       </c>
       <c r="B82" t="s">
-        <v>1088</v>
+        <v>1120</v>
       </c>
       <c r="C82" t="s">
         <v>715</v>
@@ -13621,10 +13985,10 @@
         <v>26</v>
       </c>
       <c r="F82" t="s">
-        <v>1154</v>
+        <v>1190</v>
       </c>
       <c r="G82" t="s">
-        <v>1157</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
@@ -13632,7 +13996,7 @@
         <v>27</v>
       </c>
       <c r="B83" t="s">
-        <v>1088</v>
+        <v>1120</v>
       </c>
       <c r="C83" t="s">
         <v>723</v>
@@ -13644,10 +14008,10 @@
         <v>26</v>
       </c>
       <c r="F83" t="s">
-        <v>1154</v>
+        <v>1190</v>
       </c>
       <c r="G83" t="s">
-        <v>1158</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
@@ -13655,7 +14019,7 @@
         <v>27</v>
       </c>
       <c r="B84" t="s">
-        <v>1088</v>
+        <v>1120</v>
       </c>
       <c r="C84" t="s">
         <v>732</v>
@@ -13667,10 +14031,10 @@
         <v>26</v>
       </c>
       <c r="F84" t="s">
-        <v>1154</v>
+        <v>1190</v>
       </c>
       <c r="G84" t="s">
-        <v>1159</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
@@ -13678,7 +14042,7 @@
         <v>27</v>
       </c>
       <c r="B85" t="s">
-        <v>1160</v>
+        <v>1196</v>
       </c>
       <c r="C85" t="s">
         <v>324</v>
@@ -13690,10 +14054,10 @@
         <v>86</v>
       </c>
       <c r="F85" t="s">
-        <v>1161</v>
+        <v>1197</v>
       </c>
       <c r="G85" t="s">
-        <v>1162</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
@@ -13701,7 +14065,7 @@
         <v>27</v>
       </c>
       <c r="B86" t="s">
-        <v>1160</v>
+        <v>1196</v>
       </c>
       <c r="C86" t="s">
         <v>335</v>
@@ -13713,10 +14077,10 @@
         <v>86</v>
       </c>
       <c r="F86" t="s">
-        <v>1161</v>
+        <v>1197</v>
       </c>
       <c r="G86" t="s">
-        <v>1163</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
@@ -13724,7 +14088,7 @@
         <v>27</v>
       </c>
       <c r="B87" t="s">
-        <v>1160</v>
+        <v>1196</v>
       </c>
       <c r="C87" t="s">
         <v>344</v>
@@ -13736,10 +14100,10 @@
         <v>86</v>
       </c>
       <c r="F87" t="s">
-        <v>1161</v>
+        <v>1197</v>
       </c>
       <c r="G87" t="s">
-        <v>1164</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
@@ -13747,7 +14111,7 @@
         <v>27</v>
       </c>
       <c r="B88" t="s">
-        <v>1160</v>
+        <v>1196</v>
       </c>
       <c r="C88" t="s">
         <v>369</v>
@@ -13759,10 +14123,10 @@
         <v>112</v>
       </c>
       <c r="F88" t="s">
-        <v>1161</v>
+        <v>1197</v>
       </c>
       <c r="G88" t="s">
-        <v>1165</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
@@ -13782,10 +14146,10 @@
         <v>26</v>
       </c>
       <c r="F89" t="s">
-        <v>1166</v>
+        <v>1202</v>
       </c>
       <c r="G89" t="s">
-        <v>1167</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
@@ -13793,7 +14157,7 @@
         <v>27</v>
       </c>
       <c r="B90" t="s">
-        <v>1160</v>
+        <v>1196</v>
       </c>
       <c r="C90" t="s">
         <v>619</v>
@@ -13805,10 +14169,10 @@
         <v>112</v>
       </c>
       <c r="F90" t="s">
-        <v>1161</v>
+        <v>1197</v>
       </c>
       <c r="G90" t="s">
-        <v>1168</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
@@ -13816,7 +14180,7 @@
         <v>27</v>
       </c>
       <c r="B91" t="s">
-        <v>1160</v>
+        <v>1196</v>
       </c>
       <c r="C91" t="s">
         <v>639</v>
@@ -13828,10 +14192,10 @@
         <v>86</v>
       </c>
       <c r="F91" t="s">
-        <v>1161</v>
+        <v>1197</v>
       </c>
       <c r="G91" t="s">
-        <v>1169</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
@@ -13839,7 +14203,7 @@
         <v>27</v>
       </c>
       <c r="B92" t="s">
-        <v>1160</v>
+        <v>1196</v>
       </c>
       <c r="C92" t="s">
         <v>648</v>
@@ -13851,10 +14215,10 @@
         <v>112</v>
       </c>
       <c r="F92" t="s">
-        <v>1161</v>
+        <v>1197</v>
       </c>
       <c r="G92" t="s">
-        <v>1170</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
@@ -13874,10 +14238,10 @@
         <v>86</v>
       </c>
       <c r="F93" t="s">
-        <v>1166</v>
+        <v>1202</v>
       </c>
       <c r="G93" t="s">
-        <v>1171</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
@@ -13885,7 +14249,7 @@
         <v>27</v>
       </c>
       <c r="B94" t="s">
-        <v>1160</v>
+        <v>1196</v>
       </c>
       <c r="C94" t="s">
         <v>657</v>
@@ -13897,10 +14261,10 @@
         <v>112</v>
       </c>
       <c r="F94" t="s">
-        <v>1161</v>
+        <v>1197</v>
       </c>
       <c r="G94" t="s">
-        <v>1172</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
@@ -13908,7 +14272,7 @@
         <v>27</v>
       </c>
       <c r="B95" t="s">
-        <v>1160</v>
+        <v>1196</v>
       </c>
       <c r="C95" t="s">
         <v>673</v>
@@ -13920,10 +14284,10 @@
         <v>112</v>
       </c>
       <c r="F95" t="s">
-        <v>1161</v>
+        <v>1197</v>
       </c>
       <c r="G95" t="s">
-        <v>1173</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
@@ -13943,10 +14307,10 @@
         <v>26</v>
       </c>
       <c r="F96" t="s">
-        <v>1166</v>
+        <v>1202</v>
       </c>
       <c r="G96" t="s">
-        <v>1174</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
@@ -13954,7 +14318,7 @@
         <v>27</v>
       </c>
       <c r="B97" t="s">
-        <v>1160</v>
+        <v>1196</v>
       </c>
       <c r="C97" t="s">
         <v>689</v>
@@ -13966,10 +14330,10 @@
         <v>112</v>
       </c>
       <c r="F97" t="s">
-        <v>1161</v>
+        <v>1197</v>
       </c>
       <c r="G97" t="s">
-        <v>1175</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
@@ -13977,7 +14341,7 @@
         <v>27</v>
       </c>
       <c r="B98" t="s">
-        <v>1160</v>
+        <v>1196</v>
       </c>
       <c r="C98" t="s">
         <v>697</v>
@@ -13989,10 +14353,10 @@
         <v>112</v>
       </c>
       <c r="F98" t="s">
-        <v>1161</v>
+        <v>1197</v>
       </c>
       <c r="G98" t="s">
-        <v>1176</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
@@ -14012,10 +14376,10 @@
         <v>26</v>
       </c>
       <c r="F99" t="s">
-        <v>1166</v>
+        <v>1202</v>
       </c>
       <c r="G99" t="s">
-        <v>1177</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
@@ -14023,7 +14387,7 @@
         <v>27</v>
       </c>
       <c r="B100" t="s">
-        <v>1160</v>
+        <v>1196</v>
       </c>
       <c r="C100" t="s">
         <v>708</v>
@@ -14035,10 +14399,10 @@
         <v>112</v>
       </c>
       <c r="F100" t="s">
-        <v>1161</v>
+        <v>1197</v>
       </c>
       <c r="G100" t="s">
-        <v>1178</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
@@ -14058,10 +14422,10 @@
         <v>86</v>
       </c>
       <c r="F101" t="s">
-        <v>1166</v>
+        <v>1202</v>
       </c>
       <c r="G101" t="s">
-        <v>1179</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
@@ -14069,7 +14433,7 @@
         <v>27</v>
       </c>
       <c r="B102" t="s">
-        <v>1160</v>
+        <v>1196</v>
       </c>
       <c r="C102" t="s">
         <v>715</v>
@@ -14081,10 +14445,10 @@
         <v>112</v>
       </c>
       <c r="F102" t="s">
-        <v>1161</v>
+        <v>1197</v>
       </c>
       <c r="G102" t="s">
-        <v>1180</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
@@ -14104,10 +14468,10 @@
         <v>86</v>
       </c>
       <c r="F103" t="s">
-        <v>1166</v>
+        <v>1202</v>
       </c>
       <c r="G103" t="s">
-        <v>1181</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
@@ -14115,7 +14479,7 @@
         <v>27</v>
       </c>
       <c r="B104" t="s">
-        <v>1160</v>
+        <v>1196</v>
       </c>
       <c r="C104" t="s">
         <v>723</v>
@@ -14127,10 +14491,10 @@
         <v>112</v>
       </c>
       <c r="F104" t="s">
-        <v>1161</v>
+        <v>1197</v>
       </c>
       <c r="G104" t="s">
-        <v>1182</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
@@ -14150,10 +14514,10 @@
         <v>26</v>
       </c>
       <c r="F105" t="s">
-        <v>1166</v>
+        <v>1202</v>
       </c>
       <c r="G105" t="s">
-        <v>1183</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
@@ -14161,7 +14525,7 @@
         <v>27</v>
       </c>
       <c r="B106" t="s">
-        <v>1160</v>
+        <v>1196</v>
       </c>
       <c r="C106" t="s">
         <v>732</v>
@@ -14173,10 +14537,10 @@
         <v>112</v>
       </c>
       <c r="F106" t="s">
-        <v>1161</v>
+        <v>1197</v>
       </c>
       <c r="G106" t="s">
-        <v>1184</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
@@ -14196,10 +14560,10 @@
         <v>26</v>
       </c>
       <c r="F107" t="s">
-        <v>1166</v>
+        <v>1202</v>
       </c>
       <c r="G107" t="s">
-        <v>1185</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
@@ -14213,13 +14577,13 @@
         <v>740</v>
       </c>
       <c r="D108" t="s">
-        <v>1186</v>
+        <v>1222</v>
       </c>
       <c r="E108" t="s">
         <v>112</v>
       </c>
       <c r="F108" t="s">
-        <v>1166</v>
+        <v>1202</v>
       </c>
       <c r="G108" t="s">
         <v>741</v>
@@ -14236,13 +14600,13 @@
         <v>750</v>
       </c>
       <c r="D109" t="s">
-        <v>1186</v>
+        <v>1222</v>
       </c>
       <c r="E109" t="s">
         <v>112</v>
       </c>
       <c r="F109" t="s">
-        <v>1166</v>
+        <v>1202</v>
       </c>
       <c r="G109" t="s">
         <v>751</v>
@@ -14259,13 +14623,13 @@
         <v>758</v>
       </c>
       <c r="D110" t="s">
-        <v>1186</v>
+        <v>1222</v>
       </c>
       <c r="E110" t="s">
         <v>112</v>
       </c>
       <c r="F110" t="s">
-        <v>1166</v>
+        <v>1202</v>
       </c>
       <c r="G110" t="s">
         <v>759</v>
@@ -14282,13 +14646,13 @@
         <v>766</v>
       </c>
       <c r="D111" t="s">
-        <v>1186</v>
+        <v>1222</v>
       </c>
       <c r="E111" t="s">
         <v>112</v>
       </c>
       <c r="F111" t="s">
-        <v>1166</v>
+        <v>1202</v>
       </c>
       <c r="G111" t="s">
         <v>767</v>
@@ -14305,13 +14669,13 @@
         <v>774</v>
       </c>
       <c r="D112" t="s">
-        <v>1186</v>
+        <v>1222</v>
       </c>
       <c r="E112" t="s">
         <v>112</v>
       </c>
       <c r="F112" t="s">
-        <v>1166</v>
+        <v>1202</v>
       </c>
       <c r="G112" t="s">
         <v>775</v>
@@ -14328,13 +14692,13 @@
         <v>782</v>
       </c>
       <c r="D113" t="s">
-        <v>1186</v>
+        <v>1222</v>
       </c>
       <c r="E113" t="s">
         <v>112</v>
       </c>
       <c r="F113" t="s">
-        <v>1166</v>
+        <v>1202</v>
       </c>
       <c r="G113" t="s">
         <v>783</v>
@@ -14351,13 +14715,13 @@
         <v>790</v>
       </c>
       <c r="D114" t="s">
-        <v>1186</v>
+        <v>1222</v>
       </c>
       <c r="E114" t="s">
         <v>112</v>
       </c>
       <c r="F114" t="s">
-        <v>1166</v>
+        <v>1202</v>
       </c>
       <c r="G114" t="s">
         <v>791</v>
@@ -14374,13 +14738,13 @@
         <v>798</v>
       </c>
       <c r="D115" t="s">
-        <v>1186</v>
+        <v>1222</v>
       </c>
       <c r="E115" t="s">
         <v>112</v>
       </c>
       <c r="F115" t="s">
-        <v>1166</v>
+        <v>1202</v>
       </c>
       <c r="G115" t="s">
         <v>799</v>
@@ -14397,13 +14761,13 @@
         <v>806</v>
       </c>
       <c r="D116" t="s">
-        <v>1186</v>
+        <v>1222</v>
       </c>
       <c r="E116" t="s">
         <v>112</v>
       </c>
       <c r="F116" t="s">
-        <v>1166</v>
+        <v>1202</v>
       </c>
       <c r="G116" t="s">
         <v>807</v>
@@ -14420,13 +14784,13 @@
         <v>814</v>
       </c>
       <c r="D117" t="s">
-        <v>1186</v>
+        <v>1222</v>
       </c>
       <c r="E117" t="s">
         <v>112</v>
       </c>
       <c r="F117" t="s">
-        <v>1166</v>
+        <v>1202</v>
       </c>
       <c r="G117" t="s">
         <v>815</v>
@@ -14443,13 +14807,13 @@
         <v>821</v>
       </c>
       <c r="D118" t="s">
-        <v>1186</v>
+        <v>1222</v>
       </c>
       <c r="E118" t="s">
         <v>112</v>
       </c>
       <c r="F118" t="s">
-        <v>1166</v>
+        <v>1202</v>
       </c>
       <c r="G118" t="s">
         <v>823</v>
@@ -14466,13 +14830,13 @@
         <v>830</v>
       </c>
       <c r="D119" t="s">
-        <v>1186</v>
+        <v>1222</v>
       </c>
       <c r="E119" t="s">
         <v>112</v>
       </c>
       <c r="F119" t="s">
-        <v>1166</v>
+        <v>1202</v>
       </c>
       <c r="G119" t="s">
         <v>831</v>
@@ -14489,13 +14853,13 @@
         <v>837</v>
       </c>
       <c r="D120" t="s">
-        <v>1186</v>
+        <v>1222</v>
       </c>
       <c r="E120" t="s">
         <v>112</v>
       </c>
       <c r="F120" t="s">
-        <v>1166</v>
+        <v>1202</v>
       </c>
       <c r="G120" t="s">
         <v>838</v>
@@ -14512,13 +14876,13 @@
         <v>844</v>
       </c>
       <c r="D121" t="s">
-        <v>1186</v>
+        <v>1222</v>
       </c>
       <c r="E121" t="s">
         <v>112</v>
       </c>
       <c r="F121" t="s">
-        <v>1166</v>
+        <v>1202</v>
       </c>
       <c r="G121" t="s">
         <v>845</v>
@@ -14535,13 +14899,13 @@
         <v>852</v>
       </c>
       <c r="D122" t="s">
-        <v>1186</v>
+        <v>1222</v>
       </c>
       <c r="E122" t="s">
         <v>26</v>
       </c>
       <c r="F122" t="s">
-        <v>1166</v>
+        <v>1202</v>
       </c>
       <c r="G122" t="s">
         <v>853</v>
@@ -14558,13 +14922,13 @@
         <v>860</v>
       </c>
       <c r="D123" t="s">
-        <v>1186</v>
+        <v>1222</v>
       </c>
       <c r="E123" t="s">
         <v>112</v>
       </c>
       <c r="F123" t="s">
-        <v>1166</v>
+        <v>1202</v>
       </c>
       <c r="G123" t="s">
         <v>861</v>
@@ -14581,13 +14945,13 @@
         <v>868</v>
       </c>
       <c r="D124" t="s">
-        <v>1186</v>
+        <v>1222</v>
       </c>
       <c r="E124" t="s">
         <v>112</v>
       </c>
       <c r="F124" t="s">
-        <v>1166</v>
+        <v>1202</v>
       </c>
       <c r="G124" t="s">
         <v>869</v>
@@ -14604,16 +14968,108 @@
         <v>876</v>
       </c>
       <c r="D125" t="s">
-        <v>1186</v>
+        <v>1222</v>
       </c>
       <c r="E125" t="s">
         <v>112</v>
       </c>
       <c r="F125" t="s">
-        <v>1166</v>
+        <v>1202</v>
       </c>
       <c r="G125" t="s">
         <v>878</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>27</v>
+      </c>
+      <c r="B126" t="s">
+        <v>206</v>
+      </c>
+      <c r="C126" t="s">
+        <v>885</v>
+      </c>
+      <c r="D126" t="s">
+        <v>1222</v>
+      </c>
+      <c r="E126" t="s">
+        <v>112</v>
+      </c>
+      <c r="F126" t="s">
+        <v>1202</v>
+      </c>
+      <c r="G126" t="s">
+        <v>886</v>
+      </c>
+    </row>
+    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>27</v>
+      </c>
+      <c r="B127" t="s">
+        <v>206</v>
+      </c>
+      <c r="C127" t="s">
+        <v>893</v>
+      </c>
+      <c r="D127" t="s">
+        <v>1222</v>
+      </c>
+      <c r="E127" t="s">
+        <v>112</v>
+      </c>
+      <c r="F127" t="s">
+        <v>1202</v>
+      </c>
+      <c r="G127" t="s">
+        <v>894</v>
+      </c>
+    </row>
+    <row r="128" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>27</v>
+      </c>
+      <c r="B128" t="s">
+        <v>206</v>
+      </c>
+      <c r="C128" t="s">
+        <v>901</v>
+      </c>
+      <c r="D128" t="s">
+        <v>1222</v>
+      </c>
+      <c r="E128" t="s">
+        <v>453</v>
+      </c>
+      <c r="F128" t="s">
+        <v>1202</v>
+      </c>
+      <c r="G128" t="s">
+        <v>902</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>27</v>
+      </c>
+      <c r="B129" t="s">
+        <v>206</v>
+      </c>
+      <c r="C129" t="s">
+        <v>909</v>
+      </c>
+      <c r="D129" t="s">
+        <v>1222</v>
+      </c>
+      <c r="E129" t="s">
+        <v>112</v>
+      </c>
+      <c r="F129" t="s">
+        <v>1202</v>
+      </c>
+      <c r="G129" t="s">
+        <v>910</v>
       </c>
     </row>
   </sheetData>
@@ -14627,7 +15083,7 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>1187</v>
+        <v>1223</v>
       </c>
       <c r="B1"/>
       <c r="C1"/>
@@ -14635,7 +15091,7 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1188</v>
+        <v>1224</v>
       </c>
       <c r="B2"/>
       <c r="C2"/>
@@ -14646,181 +15102,181 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>1189</v>
+        <v>1225</v>
       </c>
       <c r="C3" t="s">
-        <v>1190</v>
+        <v>1226</v>
       </c>
       <c r="D3" t="s">
-        <v>1191</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1192</v>
+        <v>1228</v>
       </c>
       <c r="B4" t="s">
-        <v>1193</v>
+        <v>1229</v>
       </c>
       <c r="C4" t="s">
-        <v>1194</v>
+        <v>1230</v>
       </c>
       <c r="D4" t="s">
-        <v>1195</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1196</v>
+        <v>1232</v>
       </c>
       <c r="B5" t="s">
-        <v>1193</v>
+        <v>1229</v>
       </c>
       <c r="C5" t="s">
-        <v>1197</v>
+        <v>1233</v>
       </c>
       <c r="D5" t="s">
-        <v>1198</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>1199</v>
+        <v>1235</v>
       </c>
       <c r="B6" t="s">
-        <v>1193</v>
+        <v>1229</v>
       </c>
       <c r="C6" t="s">
-        <v>1200</v>
+        <v>1236</v>
       </c>
       <c r="D6" t="s">
-        <v>1201</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>1202</v>
+        <v>1238</v>
       </c>
       <c r="B7" t="s">
-        <v>1193</v>
+        <v>1229</v>
       </c>
       <c r="C7" t="s">
-        <v>1203</v>
+        <v>1239</v>
       </c>
       <c r="D7" t="s">
-        <v>1204</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>1205</v>
+        <v>1241</v>
       </c>
       <c r="B8" t="s">
-        <v>1193</v>
+        <v>1229</v>
       </c>
       <c r="C8" t="s">
-        <v>1206</v>
+        <v>1242</v>
       </c>
       <c r="D8" t="s">
-        <v>1207</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>1208</v>
+        <v>1244</v>
       </c>
       <c r="B9" t="s">
-        <v>1209</v>
+        <v>1245</v>
       </c>
       <c r="C9" t="s">
-        <v>1210</v>
+        <v>1246</v>
       </c>
       <c r="D9" t="s">
-        <v>1211</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>1212</v>
+        <v>1248</v>
       </c>
       <c r="B10" t="s">
-        <v>1209</v>
+        <v>1245</v>
       </c>
       <c r="C10" t="s">
-        <v>1213</v>
+        <v>1249</v>
       </c>
       <c r="D10" t="s">
-        <v>1214</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>1215</v>
+        <v>1251</v>
       </c>
       <c r="B11" t="s">
-        <v>1209</v>
+        <v>1245</v>
       </c>
       <c r="C11" t="s">
-        <v>1216</v>
+        <v>1252</v>
       </c>
       <c r="D11" t="s">
-        <v>1217</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>1218</v>
+        <v>1254</v>
       </c>
       <c r="B12" t="s">
-        <v>1219</v>
+        <v>1255</v>
       </c>
       <c r="C12" t="s">
-        <v>1220</v>
+        <v>1256</v>
       </c>
       <c r="D12" t="s">
-        <v>1221</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>1222</v>
+        <v>1258</v>
       </c>
       <c r="B13" t="s">
-        <v>1219</v>
+        <v>1255</v>
       </c>
       <c r="C13" t="s">
-        <v>1223</v>
+        <v>1259</v>
       </c>
       <c r="D13" t="s">
-        <v>1224</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>1225</v>
+        <v>1261</v>
       </c>
       <c r="B14" t="s">
         <v>877</v>
       </c>
       <c r="C14" t="s">
-        <v>1226</v>
+        <v>1262</v>
       </c>
       <c r="D14" t="s">
-        <v>1227</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>1228</v>
+        <v>1264</v>
       </c>
       <c r="B15" t="s">
         <v>877</v>
       </c>
       <c r="C15" t="s">
-        <v>1229</v>
+        <v>1265</v>
       </c>
       <c r="D15" t="s">
-        <v>1230</v>
+        <v>1266</v>
       </c>
     </row>
   </sheetData>
@@ -14839,7 +15295,7 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>1231</v>
+        <v>1267</v>
       </c>
       <c r="B1"/>
       <c r="C1"/>
@@ -14847,133 +15303,133 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>1232</v>
+        <v>1268</v>
       </c>
       <c r="B3" t="s">
-        <v>1233</v>
+        <v>1269</v>
       </c>
       <c r="C3" t="s">
-        <v>1234</v>
+        <v>1270</v>
       </c>
       <c r="D3" t="s">
-        <v>1235</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>924</v>
+        <v>956</v>
       </c>
       <c r="B4" t="s">
-        <v>1236</v>
+        <v>1272</v>
       </c>
       <c r="C4" t="s">
-        <v>1237</v>
+        <v>1273</v>
       </c>
       <c r="D4" t="s">
-        <v>1238</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>929</v>
+        <v>961</v>
       </c>
       <c r="B5" t="s">
-        <v>1239</v>
+        <v>1275</v>
       </c>
       <c r="C5" t="s">
-        <v>1240</v>
+        <v>1276</v>
       </c>
       <c r="D5" t="s">
-        <v>1241</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>933</v>
+        <v>965</v>
       </c>
       <c r="B6" t="s">
-        <v>1242</v>
+        <v>1278</v>
       </c>
       <c r="C6" t="s">
-        <v>1243</v>
+        <v>1279</v>
       </c>
       <c r="D6" t="s">
-        <v>1244</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>937</v>
+        <v>969</v>
       </c>
       <c r="B7" t="s">
-        <v>1245</v>
+        <v>1281</v>
       </c>
       <c r="C7" t="s">
-        <v>1246</v>
+        <v>1282</v>
       </c>
       <c r="D7" t="s">
-        <v>1247</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>941</v>
+        <v>973</v>
       </c>
       <c r="B8" t="s">
-        <v>1248</v>
+        <v>1284</v>
       </c>
       <c r="C8" t="s">
-        <v>1249</v>
+        <v>1285</v>
       </c>
       <c r="D8" t="s">
-        <v>1250</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>945</v>
+        <v>977</v>
       </c>
       <c r="B9" t="s">
-        <v>1251</v>
+        <v>1287</v>
       </c>
       <c r="C9" t="s">
-        <v>1252</v>
+        <v>1288</v>
       </c>
       <c r="D9" t="s">
-        <v>1253</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>949</v>
+        <v>981</v>
       </c>
       <c r="B10" t="s">
-        <v>1254</v>
+        <v>1290</v>
       </c>
       <c r="C10" t="s">
-        <v>1255</v>
+        <v>1291</v>
       </c>
       <c r="D10" t="s">
-        <v>1256</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>953</v>
+        <v>985</v>
       </c>
       <c r="B11" t="s">
-        <v>1257</v>
+        <v>1293</v>
       </c>
       <c r="C11" t="s">
-        <v>1258</v>
+        <v>1294</v>
       </c>
       <c r="D11" t="s">
-        <v>1259</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>1260</v>
+        <v>1296</v>
       </c>
       <c r="B13"/>
       <c r="C13"/>
@@ -14981,72 +15437,72 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>1261</v>
+        <v>1297</v>
       </c>
       <c r="B14" t="s">
         <v>28</v>
       </c>
       <c r="C14" t="s">
-        <v>1262</v>
+        <v>1298</v>
       </c>
       <c r="D14" t="s">
-        <v>1263</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>1264</v>
+        <v>1300</v>
       </c>
       <c r="B15" t="s">
         <v>29</v>
       </c>
       <c r="C15" t="s">
-        <v>1265</v>
+        <v>1301</v>
       </c>
       <c r="D15" t="s">
-        <v>1266</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>1267</v>
+        <v>1303</v>
       </c>
       <c r="B16" t="s">
         <v>29</v>
       </c>
       <c r="C16" t="s">
-        <v>1268</v>
+        <v>1304</v>
       </c>
       <c r="D16" t="s">
-        <v>1269</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>1270</v>
+        <v>1306</v>
       </c>
       <c r="B17" t="s">
         <v>29</v>
       </c>
       <c r="C17" t="s">
-        <v>1271</v>
+        <v>1307</v>
       </c>
       <c r="D17" t="s">
-        <v>1272</v>
+        <v>1308</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>1273</v>
+        <v>1309</v>
       </c>
       <c r="B18" t="s">
-        <v>1274</v>
+        <v>1310</v>
       </c>
       <c r="C18" t="s">
-        <v>1275</v>
+        <v>1311</v>
       </c>
       <c r="D18" t="s">
-        <v>1276</v>
+        <v>1312</v>
       </c>
     </row>
   </sheetData>
@@ -15065,7 +15521,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>1277</v>
+        <v>1313</v>
       </c>
       <c r="B1"/>
       <c r="C1"/>
@@ -15075,7 +15531,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1278</v>
+        <v>1314</v>
       </c>
       <c r="B2"/>
       <c r="C2"/>
@@ -15085,99 +15541,99 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1279</v>
+        <v>1315</v>
       </c>
       <c r="B4" t="s">
-        <v>1280</v>
+        <v>1316</v>
       </c>
       <c r="C4" t="s">
-        <v>1281</v>
+        <v>1317</v>
       </c>
       <c r="D4" t="s">
-        <v>1282</v>
+        <v>1318</v>
       </c>
       <c r="E4" t="s">
-        <v>1283</v>
+        <v>1319</v>
       </c>
       <c r="F4" t="s">
-        <v>1284</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1285</v>
+        <v>1321</v>
       </c>
       <c r="B5" t="s">
-        <v>1286</v>
+        <v>1322</v>
       </c>
       <c r="C5" t="s">
-        <v>1287</v>
+        <v>1323</v>
       </c>
       <c r="D5" t="s">
-        <v>1288</v>
+        <v>1324</v>
       </c>
       <c r="E5" t="s">
-        <v>1289</v>
+        <v>1325</v>
       </c>
       <c r="F5" t="s">
-        <v>1290</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>1291</v>
+        <v>1327</v>
       </c>
       <c r="B6" t="s">
-        <v>1292</v>
+        <v>1328</v>
       </c>
       <c r="C6" t="s">
-        <v>1293</v>
+        <v>1329</v>
       </c>
       <c r="D6" t="s">
-        <v>1294</v>
+        <v>1330</v>
       </c>
       <c r="E6" t="s">
-        <v>1295</v>
+        <v>1331</v>
       </c>
       <c r="F6" t="s">
-        <v>1296</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>1297</v>
+        <v>1333</v>
       </c>
       <c r="B7" t="s">
-        <v>1292</v>
+        <v>1328</v>
       </c>
       <c r="C7" t="s">
-        <v>1298</v>
+        <v>1334</v>
       </c>
       <c r="D7" t="s">
-        <v>1299</v>
+        <v>1335</v>
       </c>
       <c r="E7" t="s">
-        <v>1300</v>
+        <v>1336</v>
       </c>
       <c r="F7" t="s">
-        <v>1301</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>1302</v>
+        <v>1338</v>
       </c>
       <c r="B8" t="s">
-        <v>1303</v>
+        <v>1339</v>
       </c>
       <c r="C8" t="s">
-        <v>1304</v>
+        <v>1340</v>
       </c>
       <c r="D8" t="s">
-        <v>1305</v>
+        <v>1341</v>
       </c>
       <c r="E8" t="s">
-        <v>1306</v>
+        <v>1342</v>
       </c>
       <c r="F8" t="s">
         <v>629</v>
@@ -15185,19 +15641,19 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>1307</v>
+        <v>1343</v>
       </c>
       <c r="B9" t="s">
-        <v>1308</v>
+        <v>1344</v>
       </c>
       <c r="C9" t="s">
-        <v>1309</v>
+        <v>1345</v>
       </c>
       <c r="D9" t="s">
-        <v>1310</v>
+        <v>1346</v>
       </c>
       <c r="E9" t="s">
-        <v>1311</v>
+        <v>1347</v>
       </c>
       <c r="F9" t="s">
         <v>369</v>
@@ -15205,39 +15661,39 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>1312</v>
+        <v>1348</v>
       </c>
       <c r="B10" t="s">
-        <v>1313</v>
+        <v>1349</v>
       </c>
       <c r="C10" t="s">
-        <v>1314</v>
+        <v>1350</v>
       </c>
       <c r="D10" t="s">
-        <v>1315</v>
+        <v>1351</v>
       </c>
       <c r="E10" t="s">
-        <v>1316</v>
+        <v>1352</v>
       </c>
       <c r="F10" t="s">
-        <v>1317</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>1318</v>
+        <v>1354</v>
       </c>
       <c r="B11" t="s">
-        <v>1319</v>
+        <v>1355</v>
       </c>
       <c r="C11" t="s">
-        <v>1320</v>
+        <v>1356</v>
       </c>
       <c r="D11" t="s">
-        <v>1321</v>
+        <v>1357</v>
       </c>
       <c r="E11" t="s">
-        <v>1322</v>
+        <v>1358</v>
       </c>
       <c r="F11" t="s">
         <v>47</v>
@@ -15245,99 +15701,99 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>1323</v>
+        <v>1359</v>
       </c>
       <c r="B12" t="s">
-        <v>1324</v>
+        <v>1360</v>
       </c>
       <c r="C12" t="s">
-        <v>1325</v>
+        <v>1361</v>
       </c>
       <c r="D12" t="s">
-        <v>1326</v>
+        <v>1362</v>
       </c>
       <c r="E12" t="s">
-        <v>1327</v>
+        <v>1363</v>
       </c>
       <c r="F12" t="s">
-        <v>1328</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>1329</v>
+        <v>1365</v>
       </c>
       <c r="B13" t="s">
-        <v>1330</v>
+        <v>1366</v>
       </c>
       <c r="C13" t="s">
-        <v>1331</v>
+        <v>1367</v>
       </c>
       <c r="D13" t="s">
-        <v>1332</v>
+        <v>1368</v>
       </c>
       <c r="E13" t="s">
-        <v>1333</v>
+        <v>1369</v>
       </c>
       <c r="F13" t="s">
-        <v>1334</v>
+        <v>1370</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>1335</v>
+        <v>1371</v>
       </c>
       <c r="B14" t="s">
-        <v>1336</v>
+        <v>1372</v>
       </c>
       <c r="C14" t="s">
-        <v>1337</v>
+        <v>1373</v>
       </c>
       <c r="D14" t="s">
-        <v>1338</v>
+        <v>1374</v>
       </c>
       <c r="E14" t="s">
-        <v>1339</v>
+        <v>1375</v>
       </c>
       <c r="F14" t="s">
-        <v>1340</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>1341</v>
+        <v>1377</v>
       </c>
       <c r="B15" t="s">
-        <v>1342</v>
+        <v>1378</v>
       </c>
       <c r="C15" t="s">
-        <v>1343</v>
+        <v>1379</v>
       </c>
       <c r="D15" t="s">
-        <v>1344</v>
+        <v>1380</v>
       </c>
       <c r="E15" t="s">
-        <v>1345</v>
+        <v>1381</v>
       </c>
       <c r="F15" t="s">
-        <v>1346</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>1347</v>
+        <v>1383</v>
       </c>
       <c r="B16" t="s">
-        <v>1348</v>
+        <v>1384</v>
       </c>
       <c r="C16" t="s">
-        <v>1349</v>
+        <v>1385</v>
       </c>
       <c r="D16" t="s">
-        <v>1350</v>
+        <v>1386</v>
       </c>
       <c r="E16" t="s">
-        <v>1351</v>
+        <v>1387</v>
       </c>
       <c r="F16" t="s">
         <v>207</v>
@@ -15345,19 +15801,19 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>1352</v>
+        <v>1388</v>
       </c>
       <c r="B17" t="s">
-        <v>1353</v>
+        <v>1389</v>
       </c>
       <c r="C17" t="s">
-        <v>1354</v>
+        <v>1390</v>
       </c>
       <c r="D17" t="s">
-        <v>1355</v>
+        <v>1391</v>
       </c>
       <c r="E17" t="s">
-        <v>1356</v>
+        <v>1392</v>
       </c>
       <c r="F17" t="s">
         <v>378</v>
@@ -15379,7 +15835,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>1357</v>
+        <v>1393</v>
       </c>
       <c r="B1"/>
       <c r="C1"/>
@@ -15389,7 +15845,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1358</v>
+        <v>1394</v>
       </c>
       <c r="B2"/>
       <c r="C2"/>
@@ -15399,162 +15855,162 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1359</v>
+        <v>1395</v>
       </c>
       <c r="B4" t="s">
-        <v>1257</v>
+        <v>1293</v>
       </c>
       <c r="C4" t="s">
-        <v>1360</v>
+        <v>1396</v>
       </c>
       <c r="D4" t="s">
-        <v>1361</v>
+        <v>1397</v>
       </c>
       <c r="E4" t="s">
-        <v>921</v>
+        <v>953</v>
       </c>
       <c r="F4" t="s">
-        <v>1362</v>
+        <v>1398</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>924</v>
+        <v>956</v>
       </c>
       <c r="B5" t="s">
-        <v>1363</v>
+        <v>1399</v>
       </c>
       <c r="C5" t="s">
-        <v>1364</v>
+        <v>1400</v>
       </c>
       <c r="D5" t="s">
-        <v>1365</v>
+        <v>1401</v>
       </c>
       <c r="E5" t="s">
-        <v>1366</v>
+        <v>1402</v>
       </c>
       <c r="F5" t="s">
-        <v>1367</v>
+        <v>1403</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>929</v>
+        <v>961</v>
       </c>
       <c r="B6" t="s">
-        <v>1368</v>
+        <v>1404</v>
       </c>
       <c r="C6" t="s">
-        <v>1369</v>
+        <v>1405</v>
       </c>
       <c r="D6" t="s">
-        <v>1370</v>
+        <v>1406</v>
       </c>
       <c r="E6" t="s">
-        <v>1371</v>
+        <v>1407</v>
       </c>
       <c r="F6" t="s">
-        <v>1367</v>
+        <v>1403</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>933</v>
+        <v>965</v>
       </c>
       <c r="B7" t="s">
-        <v>1372</v>
+        <v>1408</v>
       </c>
       <c r="C7" t="s">
-        <v>1373</v>
+        <v>1409</v>
       </c>
       <c r="D7" t="s">
-        <v>1374</v>
+        <v>1410</v>
       </c>
       <c r="E7" t="s">
-        <v>1375</v>
+        <v>1411</v>
       </c>
       <c r="F7" t="s">
-        <v>1367</v>
+        <v>1403</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>937</v>
+        <v>969</v>
       </c>
       <c r="B8" t="s">
-        <v>1376</v>
+        <v>1412</v>
       </c>
       <c r="C8" t="s">
-        <v>1377</v>
+        <v>1413</v>
       </c>
       <c r="D8" t="s">
-        <v>1378</v>
+        <v>1414</v>
       </c>
       <c r="E8" t="s">
-        <v>1379</v>
+        <v>1415</v>
       </c>
       <c r="F8" t="s">
-        <v>1367</v>
+        <v>1403</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>941</v>
+        <v>973</v>
       </c>
       <c r="B9" t="s">
-        <v>1380</v>
+        <v>1416</v>
       </c>
       <c r="C9" t="s">
-        <v>1381</v>
+        <v>1417</v>
       </c>
       <c r="D9" t="s">
-        <v>1382</v>
+        <v>1418</v>
       </c>
       <c r="E9" t="s">
         <v>877</v>
       </c>
       <c r="F9" t="s">
-        <v>1383</v>
+        <v>1419</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>945</v>
+        <v>977</v>
       </c>
       <c r="B10" t="s">
-        <v>1384</v>
+        <v>1420</v>
       </c>
       <c r="C10" t="s">
-        <v>1385</v>
+        <v>1421</v>
       </c>
       <c r="D10" t="s">
-        <v>1386</v>
+        <v>1422</v>
       </c>
       <c r="E10" t="s">
-        <v>1387</v>
+        <v>1423</v>
       </c>
       <c r="F10" t="s">
-        <v>1383</v>
+        <v>1419</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>949</v>
+        <v>981</v>
       </c>
       <c r="B11" t="s">
-        <v>1388</v>
+        <v>1424</v>
       </c>
       <c r="C11" t="s">
-        <v>1389</v>
+        <v>1425</v>
       </c>
       <c r="D11" t="s">
-        <v>1390</v>
+        <v>1426</v>
       </c>
       <c r="E11" t="s">
-        <v>1391</v>
+        <v>1427</v>
       </c>
       <c r="F11" t="s">
-        <v>1392</v>
+        <v>1428</v>
       </c>
     </row>
   </sheetData>

--- a/audits/FORTLESS_MASTER_SECURITY_UI_BUG_TRACKER.xlsx
+++ b/audits/FORTLESS_MASTER_SECURITY_UI_BUG_TRACKER.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3486" uniqueCount="1429">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3752" uniqueCount="1512">
   <si>
     <t>FORTLESS   /   ENGINEERING FINDINGS REGISTER</t>
   </si>
@@ -2673,7 +2673,7 @@
     <t>Check: on the live host NODE_ENV is production, cookies carry Secure and backups require a key.</t>
   </si>
   <si>
-    <t>[CONFIG_DEPENDENT] Observed from the running process and .env value NODE_ENV only; no secrets recorded. | AUDIT 3cb35de: SESSION_SECRET is empty in .env, so the process falls back to a random secret stored in data/.development-session-secret (config/index.ts:77). Cookie signing, CSRF tokens, TOTP secrets and per-account panel keys derive from that file, which sits in the data directory next to the database and backups.</t>
+    <t>[CONFIG_DEPENDENT] Observed from the running process and .env value NODE_ENV only; no secrets recorded. | AUDIT 3cb35de: SESSION_SECRET is empty in .env, so the process falls back to a random secret stored in data/.development-session-secret (config/index.ts:77). Cookie signing, CSRF tokens, TOTP secrets and per-account panel keys derive from that file, which sits in the data directory next to the database and backups. | AUDIT fc02778: Batch 3 re-check: SESSION_SECRET file fallback also affects restore (see NEW-375).</t>
   </si>
   <si>
     <t>NEW-362</t>
@@ -2769,6 +2769,249 @@
     <t>Test: the second request for the same address within the cooldown queues no new email.</t>
   </si>
   <si>
+    <t>NEW-366</t>
+  </si>
+  <si>
+    <t>TOTP codes can be replayed inside their validity window</t>
+  </si>
+  <si>
+    <t>fc02778</t>
+  </si>
+  <si>
+    <t>src/modules/identity/auth.ts:133-137,489,539,640,661,683</t>
+  </si>
+  <si>
+    <t>validTotp accepts the current step and one step either side and records no last-used counter, so one code stays valid for up to about 90 seconds and for any number of uses.</t>
+  </si>
+  <si>
+    <t>A shoulder-surfed or phished code can be reused for login, step-up or MFA disable within that window.</t>
+  </si>
+  <si>
+    <t>Store the last accepted time step per factor and reject any code with step &lt;= stored value.</t>
+  </si>
+  <si>
+    <t>Test: the same valid code submitted twice is accepted once and rejected the second time.</t>
+  </si>
+  <si>
+    <t>https://github.com/trencito/fortless/blob/main/audits/AUDIT_INDEPENDENT_3cb35de_2026-10-19.md</t>
+  </si>
+  <si>
+    <t>[CONFIRMED_CODE] Source trace only; no runtime reproduction.</t>
+  </si>
+  <si>
+    <t>NEW-367</t>
+  </si>
+  <si>
+    <t>Step-up, MFA disable, enrollment confirm and password change have no failed-attempt limiting</t>
+  </si>
+  <si>
+    <t>src/modules/identity/auth.ts:397-446,479-501,678-693; src/server.ts (step-up, disable-TOTP, enroll and change-password routes)</t>
+  </si>
+  <si>
+    <t>These flows verify a TOTP code or password but do not count failures per user or session; only the global per-IP rate limit applies. The login lockout does not cover an already authenticated session.</t>
+  </si>
+  <si>
+    <t>A hijacked session (or a pre-registered account, see NEW-363) can brute-force the 6-digit code to disable MFA or pass step-up, within the global IP limit.</t>
+  </si>
+  <si>
+    <t>Count failures per user/session on every secret-verifying endpoint, lock out after a small number of attempts and audit them.</t>
+  </si>
+  <si>
+    <t>Test: more than N wrong codes on step-up or disable returns a lockout error even when the correct code follows.</t>
+  </si>
+  <si>
+    <t>[CONFIRMED_CODE] Source trace; rate numbers are CONFIG_DEPENDENT.</t>
+  </si>
+  <si>
+    <t>NEW-368</t>
+  </si>
+  <si>
+    <t>Active workspace is always the oldest active account; accepting an invite silently changes the session context</t>
+  </si>
+  <si>
+    <t>src/modules/identity/auth.ts:158-160,327,459; audits/proofs/repro-batch3-fc02778.mts</t>
+  </si>
+  <si>
+    <t>getPrimaryAccount and authenticateSession both pick the user's membership with ORDER BY a.created_at ASC LIMIT 1 and there is no workspace-switch endpoint. Reproduced with an in-memory DB: after accepting an invite to an older workspace the same session resolves to that account with role VIEWER.</t>
+  </si>
+  <si>
+    <t>A user who owns a workspace and joins an older one loses access to their own workspace in the UI, and billing/service actions are evaluated against the wrong tenant. Wrong-tenant actions become possible by accident.</t>
+  </si>
+  <si>
+    <t>Store the selected account on the session, add an explicit workspace switch and require it on every request.</t>
+  </si>
+  <si>
+    <t>Test: a user with two memberships keeps their chosen workspace across requests and after accepting an invite.</t>
+  </si>
+  <si>
+    <t>[CONFIRMED_CODE] Reproduced locally with the proof script.</t>
+  </si>
+  <si>
+    <t>NEW-369</t>
+  </si>
+  <si>
+    <t>DNS zone and record mutations require authentication only, not a role permission</t>
+  </si>
+  <si>
+    <t>src/server.ts:1996,2051,2077,2102</t>
+  </si>
+  <si>
+    <t>The zone create, record create, record update and record delete routes use only requireAuth; none checks the member role, so a VIEWER or support-level member of a workspace can create zones and rewrite records.</t>
+  </si>
+  <si>
+    <t>Read-only members can redirect production domains or delete records.</t>
+  </si>
+  <si>
+    <t>Require a manager-level permission (for example dns:manage) on all mutating DNS routes and audit denials.</t>
+  </si>
+  <si>
+    <t>Test: VIEWER receives 403 on every DNS mutation; owner/admin succeed.</t>
+  </si>
+  <si>
+    <t>[CONFIRMED_CODE] Source trace; runtime negative test is TEST_NEEDED.</t>
+  </si>
+  <si>
+    <t>NEW-370</t>
+  </si>
+  <si>
+    <t>Any account can claim any unclaimed domain without proving ownership; real owners are blocked by global uniqueness</t>
+  </si>
+  <si>
+    <t>src/modules/domains/dns.ts:309-357,410-423</t>
+  </si>
+  <si>
+    <t>createDomainZone checks only that the name is syntactically valid and not already claimed. verifyDomainDelegation defaults to mockVerified=true and would mark a zone ACTIVE without a real lookup (currently unreferenced).</t>
+  </si>
+  <si>
+    <t>Domain squatting: an attacker claims a victim's domain first and the victim can no longer add it. If delegation verification is wired up with the default, records for domains the account does not control become active.</t>
+  </si>
+  <si>
+    <t>Require ownership proof (TXT or NS delegation check) before ACTIVE, remove the mock default, allow pending claims to expire and allow a verified owner to take over.</t>
+  </si>
+  <si>
+    <t>Test: a second account that proves control obtains the zone; an unproven claim never reaches ACTIVE.</t>
+  </si>
+  <si>
+    <t>[CONFIRMED_CODE] Overlaps FTL-DNS-202 but is distinct (ownership and squatting).</t>
+  </si>
+  <si>
+    <t>NEW-371</t>
+  </si>
+  <si>
+    <t>Reliability</t>
+  </si>
+  <si>
+    <t>Support attachments above about 0.75 MB fail because the body limit (default 1 MiB) is lower than the advertised 5 MB</t>
+  </si>
+  <si>
+    <t>src/modules/support/tickets.ts:20,174; src/server.ts:169,2195</t>
+  </si>
+  <si>
+    <t>MAX_ATTACHMENT_SIZE_BYTES is 5 MB and the route takes base64 JSON, but Fastify is created without bodyLimit so the 1 MiB default applies; base64 inflates by 4/3.</t>
+  </si>
+  <si>
+    <t>Customers get a generic 413 for files the UI says are allowed.</t>
+  </si>
+  <si>
+    <t>Set a route-level bodyLimit consistent with the cap, or move to multipart streaming with a size limit.</t>
+  </si>
+  <si>
+    <t>Test: a 4.5 MB file uploads; a 5.1 MB file is rejected with a typed size error.</t>
+  </si>
+  <si>
+    <t>[CONFIRMED_CODE] Source trace; TEST_NEEDED at runtime.</t>
+  </si>
+  <si>
+    <t>NEW-372</t>
+  </si>
+  <si>
+    <t>No per-ticket or per-account quota on support attachments</t>
+  </si>
+  <si>
+    <t>src/modules/support/tickets.ts:174-230; data/attachments</t>
+  </si>
+  <si>
+    <t>Only a per-file size cap exists. There is no count or total-bytes limit and no retention or cleanup.</t>
+  </si>
+  <si>
+    <t>An authenticated user can fill the disk with attachments within the global rate limit.</t>
+  </si>
+  <si>
+    <t>Add per-ticket count, per-account total and retention limits, with typed errors.</t>
+  </si>
+  <si>
+    <t>Test: exceeding the per-ticket count or account quota returns a typed 4xx.</t>
+  </si>
+  <si>
+    <t>NEW-373</t>
+  </si>
+  <si>
+    <t>Backup and restore script falls back to a hardcoded encryption key</t>
+  </si>
+  <si>
+    <t>src/scripts/backup-restore.ts:13,40,77</t>
+  </si>
+  <si>
+    <t>FORTLESS_BACKUP_KEY unset falls back to the literal 'default-fortless-backup-secret-key-32b' for both backup and restore.</t>
+  </si>
+  <si>
+    <t>Backups made with --encrypt appear encrypted but are decryptable by anyone who has the repository; that gives false assurance.</t>
+  </si>
+  <si>
+    <t>Fail with a typed error if the key is missing; no default.</t>
+  </si>
+  <si>
+    <t>Test: running with --encrypt and no key exits non-zero without writing a backup.</t>
+  </si>
+  <si>
+    <t>NEW-374</t>
+  </si>
+  <si>
+    <t>No scheduled or off-host backups; the only backup on this host is unencrypted and from 2026-10-17</t>
+  </si>
+  <si>
+    <t>src/modules/backup/backup.ts; src/scripts/backup-restore.ts; data/backups</t>
+  </si>
+  <si>
+    <t>createDatabaseBackup is called only from the manual script. No cron/timer/worker schedule was found. data/backups holds one unencrypted .db from 2026-10-17 plus stray raw.db-shm/-wal files.</t>
+  </si>
+  <si>
+    <t>A disk failure or bad migration loses everything since 2026-10-17, and the existing copy lives on the same host.</t>
+  </si>
+  <si>
+    <t>Schedule encrypted backups with retention, copy off-host, and alert on missing or failed runs; document a restore drill.</t>
+  </si>
+  <si>
+    <t>Test: a scheduled run produces an encrypted backup, prunes by retention and a restore drill passes.</t>
+  </si>
+  <si>
+    <t>[CONFIRMED_CODE] Host observation (CONFIG_DEPENDENT); other schedulers outside the repo were not checked.</t>
+  </si>
+  <si>
+    <t>NEW-375</t>
+  </si>
+  <si>
+    <t>Database restore without the same SESSION_SECRET breaks all MFA, and the secret is not part of the backup</t>
+  </si>
+  <si>
+    <t>src/modules/identity/auth.ts:90-103,141-144,config/index.ts:77; data/.development-session-secret</t>
+  </si>
+  <si>
+    <t>MFA secrets are encrypted with a key derived from SESSION_SECRET and recovery codes are HMACed with it. In this deployment SESSION_SECRET is empty and a random file under data/ is used, which backups do not include.</t>
+  </si>
+  <si>
+    <t>After restoring on a new host, every TOTP factor and recovery code stops working and users are locked out of MFA.</t>
+  </si>
+  <si>
+    <t>Require an explicit SESSION_SECRET in production, include key management in the restore runbook and test restore end to end.</t>
+  </si>
+  <si>
+    <t>Test: restore into a clean environment with the saved secret and verify TOTP login; without it, startup fails loudly.</t>
+  </si>
+  <si>
+    <t>[CONFIRMED_CODE] Source trace; CONFIG_DEPENDENT.</t>
+  </si>
+  <si>
     <t>FORTLESS   /   SECURITY &amp; PRODUCT QUALITY</t>
   </si>
   <si>
@@ -2787,430 +3030,427 @@
     <t>CLOSED &amp; TESTED</t>
   </si>
   <si>
-    <t>110</t>
+    <t>120</t>
+  </si>
+  <si>
+    <t>39</t>
+  </si>
+  <si>
+    <t>58</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>PRIORITY &amp; STATUS</t>
+  </si>
+  <si>
+    <t>RELEASE CONTROL</t>
+  </si>
+  <si>
+    <t>Count</t>
+  </si>
+  <si>
+    <t>NOT CLEARED FOR REAL PAYMENTS Critical billing defects reproduced in source (checkout amount mismatch, inbox event loss, SEMI_ANNUAL settlement, scheduled cancellation). Static review plus local reproductions only.</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>67</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>TESTED</t>
+  </si>
+  <si>
+    <t>CLOSED</t>
+  </si>
+  <si>
+    <t>LATEST VERIFIED COMMIT</t>
+  </si>
+  <si>
+    <t>REGRESSION</t>
+  </si>
+  <si>
+    <t>3cb35de (independent audit batch 1)</t>
+  </si>
+  <si>
+    <t>STATUS CONTRACT</t>
+  </si>
+  <si>
+    <t>Issue present in inspected source</t>
+  </si>
+  <si>
+    <t>Some code fixed; unresolved conditions remain</t>
+  </si>
+  <si>
+    <t>Fix observed in source; still needs regression/runtime validation</t>
+  </si>
+  <si>
+    <t>Question or risk not independently demonstrated</t>
+  </si>
+  <si>
+    <t>Requires an explicit product/security policy</t>
+  </si>
+  <si>
+    <t>Automated/authorized tests executed and evidence stored</t>
+  </si>
+  <si>
+    <t>Fix independently verified and accepted</t>
+  </si>
+  <si>
+    <t>Previously fixed behavior has returned</t>
+  </si>
+  <si>
+    <t>FORTLESS   /   30 SECURITY AUDIT DOMAINS</t>
+  </si>
+  <si>
+    <t>Static source review expanded at 6203687. Coverage is NOT an independent runtime, load, security or pixel-diff test.</t>
+  </si>
+  <si>
+    <t>#</t>
+  </si>
+  <si>
+    <t>Scope</t>
+  </si>
+  <si>
+    <t>Related finding IDs</t>
+  </si>
+  <si>
+    <t>Audit coverage</t>
+  </si>
+  <si>
+    <t>01</t>
+  </si>
+  <si>
+    <t>Authentication</t>
+  </si>
+  <si>
+    <t>Login/register/reset, brute force, enumeration</t>
+  </si>
+  <si>
+    <t>SEC-09, FTL-SEC-205, NEW-362, NEW-363, NEW-364, NEW-365, NEW-366, NEW-367</t>
+  </si>
+  <si>
+    <t>STATIC_PARTIAL</t>
+  </si>
+  <si>
+    <t>02</t>
+  </si>
+  <si>
+    <t>Sessions &amp; Devices</t>
+  </si>
+  <si>
+    <t>Token rotation, expiry, login/logout, revocation</t>
+  </si>
+  <si>
+    <t>SEC-03, SEC-04, FTL-SEC-202, NEW-363, NEW-368</t>
+  </si>
+  <si>
+    <t>03</t>
+  </si>
+  <si>
+    <t>MFA &amp; Passkeys</t>
+  </si>
+  <si>
+    <t>TOTP, WebAuthn, recovery, replay, UV</t>
+  </si>
+  <si>
+    <t>FTL-SEC-201, FTL-SEC-202, FTL-SEC-203, NEW-306, NEW-307, NEW-318, NEW-358, NEW-360</t>
+  </si>
+  <si>
+    <t>04</t>
+  </si>
+  <si>
+    <t>Authorization / RBAC</t>
+  </si>
+  <si>
+    <t>Every API permission and role</t>
+  </si>
+  <si>
+    <t>FTL-UI-201, SSO-01, NEW-322, NEW-328, NEW-359</t>
+  </si>
+  <si>
+    <t>05</t>
+  </si>
+  <si>
+    <t>IDOR / BOLA</t>
+  </si>
+  <si>
+    <t>Cross-account resource access</t>
+  </si>
+  <si>
+    <t>SEC-05, NEW-310, NEW-322</t>
+  </si>
+  <si>
+    <t>06</t>
+  </si>
+  <si>
+    <t>Multi-tenancy</t>
+  </si>
+  <si>
+    <t>Organization/service separation</t>
+  </si>
+  <si>
+    <t>SEC-05, SEC-06, NEW-310, NEW-322</t>
+  </si>
+  <si>
+    <t>07</t>
+  </si>
+  <si>
+    <t>API Security</t>
+  </si>
+  <si>
+    <t>Request validation/mass assignment/rate limiting</t>
+  </si>
+  <si>
+    <t>FTL-SEC-205, NEW-311, NEW-321, NEW-328</t>
+  </si>
+  <si>
+    <t>08</t>
+  </si>
+  <si>
+    <t>CSRF &amp; CORS</t>
+  </si>
+  <si>
+    <t>Origin, cookies, CSRF all writes</t>
+  </si>
+  <si>
+    <t>RUNTIME_REQUIRED</t>
+  </si>
+  <si>
+    <t>09</t>
+  </si>
+  <si>
+    <t>XSS &amp; HTML Injection</t>
+  </si>
+  <si>
+    <t>Ticket/email/console/DOM output</t>
+  </si>
+  <si>
+    <t>UI-06, MAIL-01</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>SQL / Command Injection</t>
+  </si>
+  <si>
+    <t>SQL/shell/path/template injection</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>SSRF</t>
+  </si>
+  <si>
+    <t>Private IP, DNS rebinding, redirects</t>
+  </si>
+  <si>
+    <t>SEC-08, NEW-314</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>Secrets &amp; Credentials</t>
+  </si>
+  <si>
+    <t>Provider keys, vault, rotation</t>
+  </si>
+  <si>
+    <t>NEW-313, SEC-02, NEW-323</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>Pterodactyl API</t>
+  </si>
+  <si>
+    <t>Provider scoping &amp; ownership</t>
+  </si>
+  <si>
+    <t>FTL-PROV-201, FTL-UI-202, NEW-322, NEW-323</t>
+  </si>
+  <si>
+    <t>OIDC callback, native reset, revoke</t>
+  </si>
+  <si>
+    <t>SSO-01, SSO-02, SSO-03</t>
+  </si>
+  <si>
+    <t>Wings &amp; WebSockets</t>
+  </si>
+  <si>
+    <t>Socket tokens, console, revocation</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>File Manager</t>
+  </si>
+  <si>
+    <t>Traversal, archives, symlinks, quota</t>
+  </si>
+  <si>
+    <t>NEW-314, NEW-321</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>Minecraft Installers</t>
+  </si>
+  <si>
+    <t>SHA512, compatibility, redirect, limits</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>Web App Isolation</t>
+  </si>
+  <si>
+    <t>Container isolation, network, privilege</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>Stripe &amp; Payments</t>
+  </si>
+  <si>
+    <t>Signatures, replay, idempotency, ordering</t>
+  </si>
+  <si>
+    <t>FTL-BILL-201, FTL-BILL-203, FTL-BILL-204, FTL-BILL-206, NEW-324, NEW-340, NEW-345, NEW-346, NEW-347, NEW-349, NEW-350</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>Billing &amp; Subscriptions</t>
+  </si>
+  <si>
+    <t>Renewal, refunds, tax, coupons, invoices</t>
+  </si>
+  <si>
+    <t>FTL-BILL-202, FTL-BILL-205, NEW-301, NEW-303, NEW-304, NEW-305, NEW-316, NEW-319, NEW-324, NEW-330, NEW-333, NEW-334, NEW-338, NEW-344, NEW-348, NEW-351, NEW-352, NEW-353, NEW-355, NEW-356</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>Node, cap, retry, lifecycle</t>
+  </si>
+  <si>
+    <t>FTL-PROV-201, FTL-PROV-202, FTL-PROV-203, FTL-PROV-204, NEW-302, NEW-322, NEW-327, NEW-352, NEW-357</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>cPanel / WHM</t>
+  </si>
+  <si>
+    <t>Permission, lifecycle, safe API</t>
+  </si>
+  <si>
+    <t>FTL-PROV-201, SEC-08</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>Proxmox / VPS</t>
+  </si>
+  <si>
+    <t>VM isolation, templates, snapshots</t>
+  </si>
+  <si>
+    <t>FTL-PROV-201, NEW-326, NEW-327</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>DNS &amp; Domains</t>
+  </si>
+  <si>
+    <t>Ownership, delegation, DNS records</t>
+  </si>
+  <si>
+    <t>FTL-DNS-201, FTL-DNS-202, NEW-369, NEW-370</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>Database Security</t>
+  </si>
+  <si>
+    <t>Transactions, migrations, corruption</t>
+  </si>
+  <si>
+    <t>NEW-308, NEW-309, NEW-321</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>Job leases, ordering, retry, dead letters</t>
+  </si>
+  <si>
+    <t>FTL-PROV-203, FTL-BILL-202, NEW-339, NEW-346, NEW-354, NEW-357</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>Infrastructure &amp; Network</t>
+  </si>
+  <si>
+    <t>TLS, reverse proxy, firewall, ports</t>
+  </si>
+  <si>
+    <t>SEC-10, NEW-361</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>Dependency &amp; Supply Chain</t>
+  </si>
+  <si>
+    <t>npm SCA, CI secrets, pinning</t>
+  </si>
+  <si>
+    <t>NOT_STARTED</t>
   </si>
   <si>
     <t>29</t>
   </si>
   <si>
-    <t>58</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>PRIORITY &amp; STATUS</t>
-  </si>
-  <si>
-    <t>RELEASE CONTROL</t>
-  </si>
-  <si>
-    <t>Count</t>
-  </si>
-  <si>
-    <t>NOT CLEARED FOR REAL PAYMENTS Critical billing defects reproduced in source (checkout amount mismatch, inbox event loss, SEMI_ANNUAL settlement, scheduled cancellation). Static review plus local reproductions only.</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>39</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>62</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>TESTED</t>
-  </si>
-  <si>
-    <t>CLOSED</t>
-  </si>
-  <si>
-    <t>LATEST VERIFIED COMMIT</t>
-  </si>
-  <si>
-    <t>REGRESSION</t>
-  </si>
-  <si>
-    <t>3cb35de (independent audit batch 1)</t>
-  </si>
-  <si>
-    <t>STATUS CONTRACT</t>
-  </si>
-  <si>
-    <t>Issue present in inspected source</t>
-  </si>
-  <si>
-    <t>Some code fixed; unresolved conditions remain</t>
-  </si>
-  <si>
-    <t>Fix observed in source; still needs regression/runtime validation</t>
-  </si>
-  <si>
-    <t>Question or risk not independently demonstrated</t>
-  </si>
-  <si>
-    <t>Requires an explicit product/security policy</t>
-  </si>
-  <si>
-    <t>Automated/authorized tests executed and evidence stored</t>
-  </si>
-  <si>
-    <t>Fix independently verified and accepted</t>
-  </si>
-  <si>
-    <t>Previously fixed behavior has returned</t>
-  </si>
-  <si>
-    <t>FORTLESS   /   30 SECURITY AUDIT DOMAINS</t>
-  </si>
-  <si>
-    <t>Static source review expanded at 6203687. Coverage is NOT an independent runtime, load, security or pixel-diff test.</t>
-  </si>
-  <si>
-    <t>#</t>
-  </si>
-  <si>
-    <t>Scope</t>
-  </si>
-  <si>
-    <t>Related finding IDs</t>
-  </si>
-  <si>
-    <t>Audit coverage</t>
-  </si>
-  <si>
-    <t>01</t>
-  </si>
-  <si>
-    <t>Authentication</t>
-  </si>
-  <si>
-    <t>Login/register/reset, brute force, enumeration</t>
-  </si>
-  <si>
-    <t>SEC-09, FTL-SEC-205, NEW-362, NEW-363, NEW-364, NEW-365</t>
-  </si>
-  <si>
-    <t>STATIC_PARTIAL</t>
-  </si>
-  <si>
-    <t>02</t>
-  </si>
-  <si>
-    <t>Sessions &amp; Devices</t>
-  </si>
-  <si>
-    <t>Token rotation, expiry, login/logout, revocation</t>
-  </si>
-  <si>
-    <t>SEC-03, SEC-04, FTL-SEC-202, NEW-363</t>
-  </si>
-  <si>
-    <t>03</t>
-  </si>
-  <si>
-    <t>MFA &amp; Passkeys</t>
-  </si>
-  <si>
-    <t>TOTP, WebAuthn, recovery, replay, UV</t>
-  </si>
-  <si>
-    <t>FTL-SEC-201, FTL-SEC-202, FTL-SEC-203, NEW-306, NEW-307, NEW-318, NEW-358, NEW-360</t>
-  </si>
-  <si>
-    <t>04</t>
-  </si>
-  <si>
-    <t>Authorization / RBAC</t>
-  </si>
-  <si>
-    <t>Every API permission and role</t>
-  </si>
-  <si>
-    <t>FTL-UI-201, SSO-01, NEW-322, NEW-328, NEW-359</t>
-  </si>
-  <si>
-    <t>05</t>
-  </si>
-  <si>
-    <t>IDOR / BOLA</t>
-  </si>
-  <si>
-    <t>Cross-account resource access</t>
-  </si>
-  <si>
-    <t>SEC-05, NEW-310, NEW-322</t>
-  </si>
-  <si>
-    <t>06</t>
-  </si>
-  <si>
-    <t>Multi-tenancy</t>
-  </si>
-  <si>
-    <t>Organization/service separation</t>
-  </si>
-  <si>
-    <t>SEC-05, SEC-06, NEW-310, NEW-322</t>
-  </si>
-  <si>
-    <t>07</t>
-  </si>
-  <si>
-    <t>API Security</t>
-  </si>
-  <si>
-    <t>Request validation/mass assignment/rate limiting</t>
-  </si>
-  <si>
-    <t>FTL-SEC-205, NEW-311, NEW-321, NEW-328</t>
-  </si>
-  <si>
-    <t>08</t>
-  </si>
-  <si>
-    <t>CSRF &amp; CORS</t>
-  </si>
-  <si>
-    <t>Origin, cookies, CSRF all writes</t>
-  </si>
-  <si>
-    <t>RUNTIME_REQUIRED</t>
-  </si>
-  <si>
-    <t>09</t>
-  </si>
-  <si>
-    <t>XSS &amp; HTML Injection</t>
-  </si>
-  <si>
-    <t>Ticket/email/console/DOM output</t>
-  </si>
-  <si>
-    <t>UI-06, MAIL-01</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>SQL / Command Injection</t>
-  </si>
-  <si>
-    <t>SQL/shell/path/template injection</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>SSRF</t>
-  </si>
-  <si>
-    <t>Private IP, DNS rebinding, redirects</t>
-  </si>
-  <si>
-    <t>SEC-08, NEW-314</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>Secrets &amp; Credentials</t>
-  </si>
-  <si>
-    <t>Provider keys, vault, rotation</t>
-  </si>
-  <si>
-    <t>NEW-313, SEC-02, NEW-323</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>Pterodactyl API</t>
-  </si>
-  <si>
-    <t>Provider scoping &amp; ownership</t>
-  </si>
-  <si>
-    <t>FTL-PROV-201, FTL-UI-202, NEW-322, NEW-323</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>OIDC callback, native reset, revoke</t>
-  </si>
-  <si>
-    <t>SSO-01, SSO-02, SSO-03</t>
-  </si>
-  <si>
-    <t>Wings &amp; WebSockets</t>
-  </si>
-  <si>
-    <t>Socket tokens, console, revocation</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>File Manager</t>
-  </si>
-  <si>
-    <t>Traversal, archives, symlinks, quota</t>
-  </si>
-  <si>
-    <t>NEW-314, NEW-321</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>Minecraft Installers</t>
-  </si>
-  <si>
-    <t>SHA512, compatibility, redirect, limits</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>Web App Isolation</t>
-  </si>
-  <si>
-    <t>Container isolation, network, privilege</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>Stripe &amp; Payments</t>
-  </si>
-  <si>
-    <t>Signatures, replay, idempotency, ordering</t>
-  </si>
-  <si>
-    <t>FTL-BILL-201, FTL-BILL-203, FTL-BILL-204, FTL-BILL-206, NEW-324, NEW-340, NEW-345, NEW-346, NEW-347, NEW-349, NEW-350</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>Billing &amp; Subscriptions</t>
-  </si>
-  <si>
-    <t>Renewal, refunds, tax, coupons, invoices</t>
-  </si>
-  <si>
-    <t>FTL-BILL-202, FTL-BILL-205, NEW-301, NEW-303, NEW-304, NEW-305, NEW-316, NEW-319, NEW-324, NEW-330, NEW-333, NEW-334, NEW-338, NEW-344, NEW-348, NEW-351, NEW-352, NEW-353, NEW-355, NEW-356</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>Node, cap, retry, lifecycle</t>
-  </si>
-  <si>
-    <t>FTL-PROV-201, FTL-PROV-202, FTL-PROV-203, FTL-PROV-204, NEW-302, NEW-322, NEW-327, NEW-352, NEW-357</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>cPanel / WHM</t>
-  </si>
-  <si>
-    <t>Permission, lifecycle, safe API</t>
-  </si>
-  <si>
-    <t>FTL-PROV-201, SEC-08</t>
-  </si>
-  <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>Proxmox / VPS</t>
-  </si>
-  <si>
-    <t>VM isolation, templates, snapshots</t>
-  </si>
-  <si>
-    <t>FTL-PROV-201, NEW-326, NEW-327</t>
-  </si>
-  <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>DNS &amp; Domains</t>
-  </si>
-  <si>
-    <t>Ownership, delegation, DNS records</t>
-  </si>
-  <si>
-    <t>FTL-DNS-201, FTL-DNS-202</t>
-  </si>
-  <si>
-    <t>25</t>
-  </si>
-  <si>
-    <t>Database Security</t>
-  </si>
-  <si>
-    <t>Transactions, migrations, corruption</t>
-  </si>
-  <si>
-    <t>NEW-308, NEW-309, NEW-321</t>
-  </si>
-  <si>
-    <t>26</t>
-  </si>
-  <si>
-    <t>Job leases, ordering, retry, dead letters</t>
-  </si>
-  <si>
-    <t>FTL-PROV-203, FTL-BILL-202, NEW-339, NEW-346, NEW-354, NEW-357</t>
-  </si>
-  <si>
-    <t>27</t>
-  </si>
-  <si>
-    <t>Infrastructure &amp; Network</t>
-  </si>
-  <si>
-    <t>TLS, reverse proxy, firewall, ports</t>
-  </si>
-  <si>
-    <t>SEC-10, NEW-361</t>
-  </si>
-  <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>Dependency &amp; Supply Chain</t>
-  </si>
-  <si>
-    <t>npm SCA, CI secrets, pinning</t>
-  </si>
-  <si>
-    <t>NOT_STARTED</t>
-  </si>
-  <si>
     <t>Backups &amp; Recovery</t>
   </si>
   <si>
     <t>Encrypted backups, restore integrity</t>
   </si>
   <si>
-    <t>NEW-308, NEW-309, NEW-313, NEW-327</t>
+    <t>NEW-308, NEW-309, NEW-313, NEW-327, NEW-373, NEW-374, NEW-375</t>
   </si>
   <si>
     <t>30</t>
@@ -3418,6 +3658,15 @@
   </si>
   <si>
     <t>STATIC_SOURCE_REVIEW</t>
+  </si>
+  <si>
+    <t>2026-10-19 07:10</t>
+  </si>
+  <si>
+    <t>Independent audit batch 3: MFA/sessions, DNS, support attachments, backups (NEW-366..NEW-375)</t>
+  </si>
+  <si>
+    <t>MFA, workspace selection, DNS routes, attachments and backup tooling read in source; NEW-368 reproduced locally. No implementation code changed.</t>
   </si>
   <si>
     <t>FORTLESS   /   IMMUTABLE STATUS HISTORY</t>
@@ -4682,7 +4931,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:S113"/>
+  <dimension ref="A1:S123"/>
   <sheetFormatPr defaultRowHeight="0" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" customHeight="1"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
@@ -11071,6 +11320,596 @@
       </c>
       <c r="S113" t="s">
         <v>765</v>
+      </c>
+    </row>
+    <row r="114" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>916</v>
+      </c>
+      <c r="B114" t="s">
+        <v>308</v>
+      </c>
+      <c r="C114" t="s">
+        <v>62</v>
+      </c>
+      <c r="D114" t="s">
+        <v>24</v>
+      </c>
+      <c r="E114" t="s">
+        <v>917</v>
+      </c>
+      <c r="F114" t="s">
+        <v>112</v>
+      </c>
+      <c r="G114" t="s">
+        <v>27</v>
+      </c>
+      <c r="H114" t="s">
+        <v>27</v>
+      </c>
+      <c r="I114" t="s">
+        <v>918</v>
+      </c>
+      <c r="J114" t="s">
+        <v>918</v>
+      </c>
+      <c r="K114" t="s">
+        <v>919</v>
+      </c>
+      <c r="L114" t="s">
+        <v>920</v>
+      </c>
+      <c r="M114" t="s">
+        <v>921</v>
+      </c>
+      <c r="N114" t="s">
+        <v>922</v>
+      </c>
+      <c r="O114" t="s">
+        <v>923</v>
+      </c>
+      <c r="P114" t="s">
+        <v>747</v>
+      </c>
+      <c r="Q114" t="s">
+        <v>924</v>
+      </c>
+      <c r="R114" t="s">
+        <v>36</v>
+      </c>
+      <c r="S114" t="s">
+        <v>925</v>
+      </c>
+    </row>
+    <row r="115" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>926</v>
+      </c>
+      <c r="B115" t="s">
+        <v>308</v>
+      </c>
+      <c r="C115" t="s">
+        <v>62</v>
+      </c>
+      <c r="D115" t="s">
+        <v>24</v>
+      </c>
+      <c r="E115" t="s">
+        <v>927</v>
+      </c>
+      <c r="F115" t="s">
+        <v>112</v>
+      </c>
+      <c r="G115" t="s">
+        <v>27</v>
+      </c>
+      <c r="H115" t="s">
+        <v>27</v>
+      </c>
+      <c r="I115" t="s">
+        <v>918</v>
+      </c>
+      <c r="J115" t="s">
+        <v>918</v>
+      </c>
+      <c r="K115" t="s">
+        <v>928</v>
+      </c>
+      <c r="L115" t="s">
+        <v>929</v>
+      </c>
+      <c r="M115" t="s">
+        <v>930</v>
+      </c>
+      <c r="N115" t="s">
+        <v>931</v>
+      </c>
+      <c r="O115" t="s">
+        <v>932</v>
+      </c>
+      <c r="P115" t="s">
+        <v>747</v>
+      </c>
+      <c r="Q115" t="s">
+        <v>924</v>
+      </c>
+      <c r="R115" t="s">
+        <v>36</v>
+      </c>
+      <c r="S115" t="s">
+        <v>933</v>
+      </c>
+    </row>
+    <row r="116" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>934</v>
+      </c>
+      <c r="B116" t="s">
+        <v>61</v>
+      </c>
+      <c r="C116" t="s">
+        <v>23</v>
+      </c>
+      <c r="D116" t="s">
+        <v>24</v>
+      </c>
+      <c r="E116" t="s">
+        <v>935</v>
+      </c>
+      <c r="F116" t="s">
+        <v>112</v>
+      </c>
+      <c r="G116" t="s">
+        <v>27</v>
+      </c>
+      <c r="H116" t="s">
+        <v>27</v>
+      </c>
+      <c r="I116" t="s">
+        <v>918</v>
+      </c>
+      <c r="J116" t="s">
+        <v>918</v>
+      </c>
+      <c r="K116" t="s">
+        <v>936</v>
+      </c>
+      <c r="L116" t="s">
+        <v>937</v>
+      </c>
+      <c r="M116" t="s">
+        <v>938</v>
+      </c>
+      <c r="N116" t="s">
+        <v>939</v>
+      </c>
+      <c r="O116" t="s">
+        <v>940</v>
+      </c>
+      <c r="P116" t="s">
+        <v>747</v>
+      </c>
+      <c r="Q116" t="s">
+        <v>924</v>
+      </c>
+      <c r="R116" t="s">
+        <v>36</v>
+      </c>
+      <c r="S116" t="s">
+        <v>941</v>
+      </c>
+    </row>
+    <row r="117" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>942</v>
+      </c>
+      <c r="B117" t="s">
+        <v>61</v>
+      </c>
+      <c r="C117" t="s">
+        <v>23</v>
+      </c>
+      <c r="D117" t="s">
+        <v>24</v>
+      </c>
+      <c r="E117" t="s">
+        <v>943</v>
+      </c>
+      <c r="F117" t="s">
+        <v>112</v>
+      </c>
+      <c r="G117" t="s">
+        <v>27</v>
+      </c>
+      <c r="H117" t="s">
+        <v>27</v>
+      </c>
+      <c r="I117" t="s">
+        <v>918</v>
+      </c>
+      <c r="J117" t="s">
+        <v>918</v>
+      </c>
+      <c r="K117" t="s">
+        <v>944</v>
+      </c>
+      <c r="L117" t="s">
+        <v>945</v>
+      </c>
+      <c r="M117" t="s">
+        <v>946</v>
+      </c>
+      <c r="N117" t="s">
+        <v>947</v>
+      </c>
+      <c r="O117" t="s">
+        <v>948</v>
+      </c>
+      <c r="P117" t="s">
+        <v>747</v>
+      </c>
+      <c r="Q117" t="s">
+        <v>924</v>
+      </c>
+      <c r="R117" t="s">
+        <v>36</v>
+      </c>
+      <c r="S117" t="s">
+        <v>949</v>
+      </c>
+    </row>
+    <row r="118" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>950</v>
+      </c>
+      <c r="B118" t="s">
+        <v>61</v>
+      </c>
+      <c r="C118" t="s">
+        <v>23</v>
+      </c>
+      <c r="D118" t="s">
+        <v>24</v>
+      </c>
+      <c r="E118" t="s">
+        <v>951</v>
+      </c>
+      <c r="F118" t="s">
+        <v>112</v>
+      </c>
+      <c r="G118" t="s">
+        <v>27</v>
+      </c>
+      <c r="H118" t="s">
+        <v>27</v>
+      </c>
+      <c r="I118" t="s">
+        <v>918</v>
+      </c>
+      <c r="J118" t="s">
+        <v>918</v>
+      </c>
+      <c r="K118" t="s">
+        <v>952</v>
+      </c>
+      <c r="L118" t="s">
+        <v>953</v>
+      </c>
+      <c r="M118" t="s">
+        <v>954</v>
+      </c>
+      <c r="N118" t="s">
+        <v>955</v>
+      </c>
+      <c r="O118" t="s">
+        <v>956</v>
+      </c>
+      <c r="P118" t="s">
+        <v>747</v>
+      </c>
+      <c r="Q118" t="s">
+        <v>924</v>
+      </c>
+      <c r="R118" t="s">
+        <v>36</v>
+      </c>
+      <c r="S118" t="s">
+        <v>957</v>
+      </c>
+    </row>
+    <row r="119" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>958</v>
+      </c>
+      <c r="B119" t="s">
+        <v>308</v>
+      </c>
+      <c r="C119" t="s">
+        <v>309</v>
+      </c>
+      <c r="D119" t="s">
+        <v>959</v>
+      </c>
+      <c r="E119" t="s">
+        <v>960</v>
+      </c>
+      <c r="F119" t="s">
+        <v>112</v>
+      </c>
+      <c r="G119" t="s">
+        <v>27</v>
+      </c>
+      <c r="H119" t="s">
+        <v>27</v>
+      </c>
+      <c r="I119" t="s">
+        <v>918</v>
+      </c>
+      <c r="J119" t="s">
+        <v>918</v>
+      </c>
+      <c r="K119" t="s">
+        <v>961</v>
+      </c>
+      <c r="L119" t="s">
+        <v>962</v>
+      </c>
+      <c r="M119" t="s">
+        <v>963</v>
+      </c>
+      <c r="N119" t="s">
+        <v>964</v>
+      </c>
+      <c r="O119" t="s">
+        <v>965</v>
+      </c>
+      <c r="P119" t="s">
+        <v>747</v>
+      </c>
+      <c r="Q119" t="s">
+        <v>924</v>
+      </c>
+      <c r="R119" t="s">
+        <v>36</v>
+      </c>
+      <c r="S119" t="s">
+        <v>966</v>
+      </c>
+    </row>
+    <row r="120" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>967</v>
+      </c>
+      <c r="B120" t="s">
+        <v>308</v>
+      </c>
+      <c r="C120" t="s">
+        <v>309</v>
+      </c>
+      <c r="D120" t="s">
+        <v>959</v>
+      </c>
+      <c r="E120" t="s">
+        <v>968</v>
+      </c>
+      <c r="F120" t="s">
+        <v>112</v>
+      </c>
+      <c r="G120" t="s">
+        <v>27</v>
+      </c>
+      <c r="H120" t="s">
+        <v>27</v>
+      </c>
+      <c r="I120" t="s">
+        <v>918</v>
+      </c>
+      <c r="J120" t="s">
+        <v>918</v>
+      </c>
+      <c r="K120" t="s">
+        <v>969</v>
+      </c>
+      <c r="L120" t="s">
+        <v>970</v>
+      </c>
+      <c r="M120" t="s">
+        <v>971</v>
+      </c>
+      <c r="N120" t="s">
+        <v>972</v>
+      </c>
+      <c r="O120" t="s">
+        <v>973</v>
+      </c>
+      <c r="P120" t="s">
+        <v>747</v>
+      </c>
+      <c r="Q120" t="s">
+        <v>924</v>
+      </c>
+      <c r="R120" t="s">
+        <v>36</v>
+      </c>
+      <c r="S120" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="121" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>974</v>
+      </c>
+      <c r="B121" t="s">
+        <v>61</v>
+      </c>
+      <c r="C121" t="s">
+        <v>62</v>
+      </c>
+      <c r="D121" t="s">
+        <v>24</v>
+      </c>
+      <c r="E121" t="s">
+        <v>975</v>
+      </c>
+      <c r="F121" t="s">
+        <v>112</v>
+      </c>
+      <c r="G121" t="s">
+        <v>27</v>
+      </c>
+      <c r="H121" t="s">
+        <v>27</v>
+      </c>
+      <c r="I121" t="s">
+        <v>918</v>
+      </c>
+      <c r="J121" t="s">
+        <v>918</v>
+      </c>
+      <c r="K121" t="s">
+        <v>976</v>
+      </c>
+      <c r="L121" t="s">
+        <v>977</v>
+      </c>
+      <c r="M121" t="s">
+        <v>978</v>
+      </c>
+      <c r="N121" t="s">
+        <v>979</v>
+      </c>
+      <c r="O121" t="s">
+        <v>980</v>
+      </c>
+      <c r="P121" t="s">
+        <v>747</v>
+      </c>
+      <c r="Q121" t="s">
+        <v>924</v>
+      </c>
+      <c r="R121" t="s">
+        <v>36</v>
+      </c>
+      <c r="S121" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="122" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>981</v>
+      </c>
+      <c r="B122" t="s">
+        <v>61</v>
+      </c>
+      <c r="C122" t="s">
+        <v>23</v>
+      </c>
+      <c r="D122" t="s">
+        <v>877</v>
+      </c>
+      <c r="E122" t="s">
+        <v>982</v>
+      </c>
+      <c r="F122" t="s">
+        <v>112</v>
+      </c>
+      <c r="G122" t="s">
+        <v>27</v>
+      </c>
+      <c r="H122" t="s">
+        <v>27</v>
+      </c>
+      <c r="I122" t="s">
+        <v>918</v>
+      </c>
+      <c r="J122" t="s">
+        <v>918</v>
+      </c>
+      <c r="K122" t="s">
+        <v>983</v>
+      </c>
+      <c r="L122" t="s">
+        <v>984</v>
+      </c>
+      <c r="M122" t="s">
+        <v>985</v>
+      </c>
+      <c r="N122" t="s">
+        <v>986</v>
+      </c>
+      <c r="O122" t="s">
+        <v>987</v>
+      </c>
+      <c r="P122" t="s">
+        <v>747</v>
+      </c>
+      <c r="Q122" t="s">
+        <v>924</v>
+      </c>
+      <c r="R122" t="s">
+        <v>36</v>
+      </c>
+      <c r="S122" t="s">
+        <v>988</v>
+      </c>
+    </row>
+    <row r="123" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>989</v>
+      </c>
+      <c r="B123" t="s">
+        <v>308</v>
+      </c>
+      <c r="C123" t="s">
+        <v>62</v>
+      </c>
+      <c r="D123" t="s">
+        <v>877</v>
+      </c>
+      <c r="E123" t="s">
+        <v>990</v>
+      </c>
+      <c r="F123" t="s">
+        <v>112</v>
+      </c>
+      <c r="G123" t="s">
+        <v>27</v>
+      </c>
+      <c r="H123" t="s">
+        <v>27</v>
+      </c>
+      <c r="I123" t="s">
+        <v>918</v>
+      </c>
+      <c r="J123" t="s">
+        <v>918</v>
+      </c>
+      <c r="K123" t="s">
+        <v>991</v>
+      </c>
+      <c r="L123" t="s">
+        <v>992</v>
+      </c>
+      <c r="M123" t="s">
+        <v>993</v>
+      </c>
+      <c r="N123" t="s">
+        <v>994</v>
+      </c>
+      <c r="O123" t="s">
+        <v>995</v>
+      </c>
+      <c r="P123" t="s">
+        <v>747</v>
+      </c>
+      <c r="Q123" t="s">
+        <v>924</v>
+      </c>
+      <c r="R123" t="s">
+        <v>36</v>
+      </c>
+      <c r="S123" t="s">
+        <v>996</v>
       </c>
     </row>
   </sheetData>
@@ -11084,48 +11923,48 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>916</v>
+        <v>997</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>917</v>
+        <v>998</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>918</v>
+        <v>999</v>
       </c>
       <c r="C4" t="s">
-        <v>919</v>
+        <v>1000</v>
       </c>
       <c r="E4" t="s">
-        <v>920</v>
+        <v>1001</v>
       </c>
       <c r="G4" t="s">
-        <v>921</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>922</v>
+        <v>1003</v>
       </c>
       <c r="C5" t="s">
-        <v>923</v>
+        <v>1004</v>
       </c>
       <c r="E5" t="s">
-        <v>924</v>
+        <v>1005</v>
       </c>
       <c r="G5" t="s">
-        <v>925</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>926</v>
+        <v>1007</v>
       </c>
       <c r="F9" t="s">
-        <v>927</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -11133,16 +11972,16 @@
         <v>112</v>
       </c>
       <c r="B10" t="s">
-        <v>923</v>
+        <v>1004</v>
       </c>
       <c r="C10" t="s">
         <v>3</v>
       </c>
       <c r="D10" t="s">
-        <v>928</v>
+        <v>1009</v>
       </c>
       <c r="F10" t="s">
-        <v>929</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -11150,13 +11989,13 @@
         <v>86</v>
       </c>
       <c r="B11" t="s">
-        <v>930</v>
+        <v>1011</v>
       </c>
       <c r="C11" t="s">
         <v>22</v>
       </c>
       <c r="D11" t="s">
-        <v>931</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -11164,13 +12003,13 @@
         <v>95</v>
       </c>
       <c r="B12" t="s">
-        <v>932</v>
+        <v>1012</v>
       </c>
       <c r="C12" t="s">
         <v>61</v>
       </c>
       <c r="D12" t="s">
-        <v>933</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -11178,13 +12017,13 @@
         <v>453</v>
       </c>
       <c r="B13" t="s">
-        <v>934</v>
+        <v>1014</v>
       </c>
       <c r="C13" t="s">
         <v>308</v>
       </c>
       <c r="D13" t="s">
-        <v>935</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
@@ -11192,42 +12031,42 @@
         <v>26</v>
       </c>
       <c r="B14" t="s">
-        <v>924</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>936</v>
+        <v>1016</v>
       </c>
       <c r="B15" t="s">
-        <v>925</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>937</v>
+        <v>1017</v>
       </c>
       <c r="B16" t="s">
-        <v>925</v>
+        <v>1006</v>
       </c>
       <c r="F16" t="s">
-        <v>938</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>939</v>
+        <v>1019</v>
       </c>
       <c r="B17" t="s">
-        <v>925</v>
+        <v>1006</v>
       </c>
       <c r="F17" t="s">
-        <v>940</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>941</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
@@ -11235,7 +12074,7 @@
         <v>112</v>
       </c>
       <c r="C22" t="s">
-        <v>942</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
@@ -11243,7 +12082,7 @@
         <v>86</v>
       </c>
       <c r="C23" t="s">
-        <v>943</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
@@ -11251,7 +12090,7 @@
         <v>26</v>
       </c>
       <c r="C24" t="s">
-        <v>944</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
@@ -11259,7 +12098,7 @@
         <v>95</v>
       </c>
       <c r="C25" t="s">
-        <v>945</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
@@ -11267,31 +12106,31 @@
         <v>453</v>
       </c>
       <c r="C26" t="s">
-        <v>946</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>936</v>
+        <v>1016</v>
       </c>
       <c r="C27" t="s">
-        <v>947</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>937</v>
+        <v>1017</v>
       </c>
       <c r="C28" t="s">
-        <v>948</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>939</v>
+        <v>1019</v>
       </c>
       <c r="C29" t="s">
-        <v>949</v>
+        <v>1029</v>
       </c>
     </row>
   </sheetData>
@@ -11305,7 +12144,7 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>950</v>
+        <v>1030</v>
       </c>
       <c r="B1"/>
       <c r="C1"/>
@@ -11314,7 +12153,7 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>951</v>
+        <v>1031</v>
       </c>
       <c r="B2"/>
       <c r="C2"/>
@@ -11323,529 +12162,529 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>952</v>
+        <v>1032</v>
       </c>
       <c r="B3" t="s">
         <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>953</v>
+        <v>1033</v>
       </c>
       <c r="D3" t="s">
-        <v>954</v>
+        <v>1034</v>
       </c>
       <c r="E3" t="s">
-        <v>955</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>956</v>
+        <v>1036</v>
       </c>
       <c r="B4" t="s">
-        <v>957</v>
+        <v>1037</v>
       </c>
       <c r="C4" t="s">
-        <v>958</v>
+        <v>1038</v>
       </c>
       <c r="D4" t="s">
-        <v>959</v>
+        <v>1039</v>
       </c>
       <c r="E4" t="s">
-        <v>960</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>961</v>
+        <v>1041</v>
       </c>
       <c r="B5" t="s">
-        <v>962</v>
+        <v>1042</v>
       </c>
       <c r="C5" t="s">
-        <v>963</v>
+        <v>1043</v>
       </c>
       <c r="D5" t="s">
-        <v>964</v>
+        <v>1044</v>
       </c>
       <c r="E5" t="s">
-        <v>960</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>965</v>
+        <v>1045</v>
       </c>
       <c r="B6" t="s">
-        <v>966</v>
+        <v>1046</v>
       </c>
       <c r="C6" t="s">
-        <v>967</v>
+        <v>1047</v>
       </c>
       <c r="D6" t="s">
-        <v>968</v>
+        <v>1048</v>
       </c>
       <c r="E6" t="s">
-        <v>960</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>969</v>
+        <v>1049</v>
       </c>
       <c r="B7" t="s">
-        <v>970</v>
+        <v>1050</v>
       </c>
       <c r="C7" t="s">
-        <v>971</v>
+        <v>1051</v>
       </c>
       <c r="D7" t="s">
-        <v>972</v>
+        <v>1052</v>
       </c>
       <c r="E7" t="s">
-        <v>960</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>973</v>
+        <v>1053</v>
       </c>
       <c r="B8" t="s">
-        <v>974</v>
+        <v>1054</v>
       </c>
       <c r="C8" t="s">
-        <v>975</v>
+        <v>1055</v>
       </c>
       <c r="D8" t="s">
-        <v>976</v>
+        <v>1056</v>
       </c>
       <c r="E8" t="s">
-        <v>960</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>977</v>
+        <v>1057</v>
       </c>
       <c r="B9" t="s">
-        <v>978</v>
+        <v>1058</v>
       </c>
       <c r="C9" t="s">
-        <v>979</v>
+        <v>1059</v>
       </c>
       <c r="D9" t="s">
-        <v>980</v>
+        <v>1060</v>
       </c>
       <c r="E9" t="s">
-        <v>960</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>981</v>
+        <v>1061</v>
       </c>
       <c r="B10" t="s">
-        <v>982</v>
+        <v>1062</v>
       </c>
       <c r="C10" t="s">
-        <v>983</v>
+        <v>1063</v>
       </c>
       <c r="D10" t="s">
-        <v>984</v>
+        <v>1064</v>
       </c>
       <c r="E10" t="s">
-        <v>960</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>985</v>
+        <v>1065</v>
       </c>
       <c r="B11" t="s">
-        <v>986</v>
+        <v>1066</v>
       </c>
       <c r="C11" t="s">
-        <v>987</v>
+        <v>1067</v>
       </c>
       <c r="D11" t="s">
         <v>93</v>
       </c>
       <c r="E11" t="s">
-        <v>988</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>989</v>
+        <v>1069</v>
       </c>
       <c r="B12" t="s">
-        <v>990</v>
+        <v>1070</v>
       </c>
       <c r="C12" t="s">
-        <v>991</v>
+        <v>1071</v>
       </c>
       <c r="D12" t="s">
-        <v>992</v>
+        <v>1072</v>
       </c>
       <c r="E12" t="s">
-        <v>960</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>993</v>
+        <v>1073</v>
       </c>
       <c r="B13" t="s">
-        <v>994</v>
+        <v>1074</v>
       </c>
       <c r="C13" t="s">
-        <v>995</v>
+        <v>1075</v>
       </c>
       <c r="D13" t="s">
         <v>403</v>
       </c>
       <c r="E13" t="s">
-        <v>988</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>996</v>
+        <v>1076</v>
       </c>
       <c r="B14" t="s">
-        <v>997</v>
+        <v>1077</v>
       </c>
       <c r="C14" t="s">
-        <v>998</v>
+        <v>1078</v>
       </c>
       <c r="D14" t="s">
-        <v>999</v>
+        <v>1079</v>
       </c>
       <c r="E14" t="s">
-        <v>960</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>1000</v>
+        <v>1080</v>
       </c>
       <c r="B15" t="s">
-        <v>1001</v>
+        <v>1081</v>
       </c>
       <c r="C15" t="s">
-        <v>1002</v>
+        <v>1082</v>
       </c>
       <c r="D15" t="s">
-        <v>1003</v>
+        <v>1083</v>
       </c>
       <c r="E15" t="s">
-        <v>960</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>1004</v>
+        <v>1084</v>
       </c>
       <c r="B16" t="s">
-        <v>1005</v>
+        <v>1085</v>
       </c>
       <c r="C16" t="s">
-        <v>1006</v>
+        <v>1086</v>
       </c>
       <c r="D16" t="s">
-        <v>1007</v>
+        <v>1087</v>
       </c>
       <c r="E16" t="s">
-        <v>960</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>1008</v>
+        <v>1015</v>
       </c>
       <c r="B17" t="s">
         <v>435</v>
       </c>
       <c r="C17" t="s">
-        <v>1009</v>
+        <v>1088</v>
       </c>
       <c r="D17" t="s">
-        <v>1010</v>
+        <v>1089</v>
       </c>
       <c r="E17" t="s">
-        <v>988</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>930</v>
+        <v>1011</v>
       </c>
       <c r="B18" t="s">
-        <v>1011</v>
+        <v>1090</v>
       </c>
       <c r="C18" t="s">
-        <v>1012</v>
+        <v>1091</v>
       </c>
       <c r="D18" t="s">
         <v>316</v>
       </c>
       <c r="E18" t="s">
-        <v>988</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>1013</v>
+        <v>1092</v>
       </c>
       <c r="B19" t="s">
-        <v>1014</v>
+        <v>1093</v>
       </c>
       <c r="C19" t="s">
-        <v>1015</v>
+        <v>1094</v>
       </c>
       <c r="D19" t="s">
-        <v>1016</v>
+        <v>1095</v>
       </c>
       <c r="E19" t="s">
-        <v>988</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>1017</v>
+        <v>1096</v>
       </c>
       <c r="B20" t="s">
-        <v>1018</v>
+        <v>1097</v>
       </c>
       <c r="C20" t="s">
-        <v>1019</v>
+        <v>1098</v>
       </c>
       <c r="D20" t="s">
         <v>475</v>
       </c>
       <c r="E20" t="s">
-        <v>960</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>1020</v>
+        <v>1099</v>
       </c>
       <c r="B21" t="s">
-        <v>1021</v>
+        <v>1100</v>
       </c>
       <c r="C21" t="s">
-        <v>1022</v>
+        <v>1101</v>
       </c>
       <c r="D21" t="s">
         <v>213</v>
       </c>
       <c r="E21" t="s">
-        <v>988</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>1023</v>
+        <v>1102</v>
       </c>
       <c r="B22" t="s">
-        <v>1024</v>
+        <v>1103</v>
       </c>
       <c r="C22" t="s">
-        <v>1025</v>
+        <v>1104</v>
       </c>
       <c r="D22" t="s">
-        <v>1026</v>
+        <v>1105</v>
       </c>
       <c r="E22" t="s">
-        <v>960</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>1027</v>
+        <v>1106</v>
       </c>
       <c r="B23" t="s">
-        <v>1028</v>
+        <v>1107</v>
       </c>
       <c r="C23" t="s">
-        <v>1029</v>
+        <v>1108</v>
       </c>
       <c r="D23" t="s">
-        <v>1030</v>
+        <v>1109</v>
       </c>
       <c r="E23" t="s">
-        <v>960</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>1031</v>
+        <v>1110</v>
       </c>
       <c r="B24" t="s">
         <v>214</v>
       </c>
       <c r="C24" t="s">
-        <v>1032</v>
+        <v>1111</v>
       </c>
       <c r="D24" t="s">
-        <v>1033</v>
+        <v>1112</v>
       </c>
       <c r="E24" t="s">
-        <v>960</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>1034</v>
+        <v>1113</v>
       </c>
       <c r="B25" t="s">
-        <v>1035</v>
+        <v>1114</v>
       </c>
       <c r="C25" t="s">
-        <v>1036</v>
+        <v>1115</v>
       </c>
       <c r="D25" t="s">
-        <v>1037</v>
+        <v>1116</v>
       </c>
       <c r="E25" t="s">
-        <v>988</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>1038</v>
+        <v>1117</v>
       </c>
       <c r="B26" t="s">
-        <v>1039</v>
+        <v>1118</v>
       </c>
       <c r="C26" t="s">
-        <v>1040</v>
+        <v>1119</v>
       </c>
       <c r="D26" t="s">
-        <v>1041</v>
+        <v>1120</v>
       </c>
       <c r="E26" t="s">
-        <v>988</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>1042</v>
+        <v>1121</v>
       </c>
       <c r="B27" t="s">
-        <v>1043</v>
+        <v>1122</v>
       </c>
       <c r="C27" t="s">
-        <v>1044</v>
+        <v>1123</v>
       </c>
       <c r="D27" t="s">
-        <v>1045</v>
+        <v>1124</v>
       </c>
       <c r="E27" t="s">
-        <v>960</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>1046</v>
+        <v>1125</v>
       </c>
       <c r="B28" t="s">
-        <v>1047</v>
+        <v>1126</v>
       </c>
       <c r="C28" t="s">
-        <v>1048</v>
+        <v>1127</v>
       </c>
       <c r="D28" t="s">
-        <v>1049</v>
+        <v>1128</v>
       </c>
       <c r="E28" t="s">
-        <v>960</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>1050</v>
+        <v>1129</v>
       </c>
       <c r="B29" t="s">
         <v>822</v>
       </c>
       <c r="C29" t="s">
-        <v>1051</v>
+        <v>1130</v>
       </c>
       <c r="D29" t="s">
-        <v>1052</v>
+        <v>1131</v>
       </c>
       <c r="E29" t="s">
-        <v>960</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>1053</v>
+        <v>1132</v>
       </c>
       <c r="B30" t="s">
-        <v>1054</v>
+        <v>1133</v>
       </c>
       <c r="C30" t="s">
-        <v>1055</v>
+        <v>1134</v>
       </c>
       <c r="D30" t="s">
-        <v>1056</v>
+        <v>1135</v>
       </c>
       <c r="E30" t="s">
-        <v>988</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>1057</v>
+        <v>1136</v>
       </c>
       <c r="B31" t="s">
-        <v>1058</v>
+        <v>1137</v>
       </c>
       <c r="C31" t="s">
-        <v>1059</v>
+        <v>1138</v>
       </c>
       <c r="D31" t="s">
         <v>93</v>
       </c>
       <c r="E31" t="s">
-        <v>1060</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>923</v>
+        <v>1140</v>
       </c>
       <c r="B32" t="s">
-        <v>1061</v>
+        <v>1141</v>
       </c>
       <c r="C32" t="s">
-        <v>1062</v>
+        <v>1142</v>
       </c>
       <c r="D32" t="s">
-        <v>1063</v>
+        <v>1143</v>
       </c>
       <c r="E32" t="s">
-        <v>960</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>1064</v>
+        <v>1144</v>
       </c>
       <c r="B33" t="s">
-        <v>1065</v>
+        <v>1145</v>
       </c>
       <c r="C33" t="s">
-        <v>1066</v>
+        <v>1146</v>
       </c>
       <c r="D33" t="s">
-        <v>1067</v>
+        <v>1147</v>
       </c>
       <c r="E33" t="s">
-        <v>988</v>
+        <v>1068</v>
       </c>
     </row>
   </sheetData>
@@ -11859,157 +12698,157 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr defaultRowHeight="0" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" customHeight="1"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>1068</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1069</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>1070</v>
+        <v>1150</v>
       </c>
       <c r="B3" t="s">
-        <v>1071</v>
+        <v>1151</v>
       </c>
       <c r="C3" t="s">
-        <v>1072</v>
+        <v>1152</v>
       </c>
       <c r="D3" t="s">
-        <v>1073</v>
+        <v>1153</v>
       </c>
       <c r="E3" t="s">
-        <v>1074</v>
+        <v>1154</v>
       </c>
       <c r="F3" t="s">
-        <v>1075</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1076</v>
+        <v>1156</v>
       </c>
       <c r="B4" t="s">
         <v>28</v>
       </c>
       <c r="C4" t="s">
-        <v>1077</v>
+        <v>1157</v>
       </c>
       <c r="D4" t="s">
-        <v>1078</v>
+        <v>1158</v>
       </c>
       <c r="E4" t="s">
-        <v>1079</v>
+        <v>1159</v>
       </c>
       <c r="F4" t="s">
-        <v>1080</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1081</v>
+        <v>1161</v>
       </c>
       <c r="B5" t="s">
-        <v>1082</v>
+        <v>1162</v>
       </c>
       <c r="C5" t="s">
-        <v>1083</v>
+        <v>1163</v>
       </c>
       <c r="D5" t="s">
-        <v>1084</v>
+        <v>1164</v>
       </c>
       <c r="E5" t="s">
-        <v>1085</v>
+        <v>1165</v>
       </c>
       <c r="F5" t="s">
-        <v>1086</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>1087</v>
+        <v>1167</v>
       </c>
       <c r="B6" t="s">
-        <v>1088</v>
+        <v>1168</v>
       </c>
       <c r="C6" t="s">
-        <v>1089</v>
+        <v>1169</v>
       </c>
       <c r="D6" t="s">
-        <v>1090</v>
+        <v>1170</v>
       </c>
       <c r="E6" t="s">
-        <v>1091</v>
+        <v>1171</v>
       </c>
       <c r="F6" t="s">
-        <v>1092</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>1093</v>
+        <v>1173</v>
       </c>
       <c r="B7" t="s">
-        <v>1094</v>
+        <v>1174</v>
       </c>
       <c r="C7" t="s">
-        <v>1095</v>
+        <v>1175</v>
       </c>
       <c r="D7" t="s">
-        <v>1096</v>
+        <v>1176</v>
       </c>
       <c r="E7" t="s">
-        <v>1091</v>
+        <v>1171</v>
       </c>
       <c r="F7" t="s">
-        <v>1097</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>1098</v>
+        <v>1178</v>
       </c>
       <c r="B8" t="s">
-        <v>1099</v>
+        <v>1179</v>
       </c>
       <c r="C8" t="s">
-        <v>1100</v>
+        <v>1180</v>
       </c>
       <c r="D8" t="s">
-        <v>1101</v>
+        <v>1181</v>
       </c>
       <c r="E8" t="s">
-        <v>1091</v>
+        <v>1171</v>
       </c>
       <c r="F8" t="s">
-        <v>1097</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>1102</v>
+        <v>1182</v>
       </c>
       <c r="B9" t="s">
         <v>29</v>
       </c>
       <c r="C9" t="s">
-        <v>1103</v>
+        <v>1183</v>
       </c>
       <c r="D9" t="s">
-        <v>1104</v>
+        <v>1184</v>
       </c>
       <c r="E9" t="s">
-        <v>1079</v>
+        <v>1159</v>
       </c>
       <c r="F9" t="s">
-        <v>1105</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -12020,93 +12859,93 @@
         <v>29</v>
       </c>
       <c r="C10" t="s">
-        <v>1106</v>
+        <v>1186</v>
       </c>
       <c r="D10" t="s">
-        <v>1107</v>
+        <v>1187</v>
       </c>
       <c r="E10" t="s">
-        <v>1108</v>
+        <v>1188</v>
       </c>
       <c r="F10" t="s">
-        <v>1109</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>1110</v>
+        <v>1190</v>
       </c>
       <c r="B11" t="s">
         <v>55</v>
       </c>
       <c r="C11" t="s">
-        <v>1111</v>
+        <v>1191</v>
       </c>
       <c r="D11" t="s">
-        <v>1112</v>
+        <v>1192</v>
       </c>
       <c r="E11" t="s">
-        <v>1108</v>
+        <v>1188</v>
       </c>
       <c r="F11" t="s">
-        <v>1113</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>1114</v>
+        <v>1194</v>
       </c>
       <c r="B12" t="s">
         <v>161</v>
       </c>
       <c r="C12" t="s">
-        <v>1115</v>
+        <v>1195</v>
       </c>
       <c r="D12" t="s">
-        <v>1116</v>
+        <v>1196</v>
       </c>
       <c r="E12" t="s">
-        <v>1117</v>
+        <v>1197</v>
       </c>
       <c r="F12" t="s">
-        <v>1118</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>1119</v>
+        <v>1199</v>
       </c>
       <c r="B13" t="s">
-        <v>1120</v>
+        <v>1200</v>
       </c>
       <c r="C13" t="s">
-        <v>1121</v>
+        <v>1201</v>
       </c>
       <c r="D13" t="s">
-        <v>1122</v>
+        <v>1202</v>
       </c>
       <c r="E13" t="s">
-        <v>1123</v>
+        <v>1203</v>
       </c>
       <c r="F13" t="s">
-        <v>1124</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>1125</v>
+        <v>1205</v>
       </c>
       <c r="B14" t="s">
         <v>206</v>
       </c>
       <c r="C14" t="s">
-        <v>1126</v>
+        <v>1206</v>
       </c>
       <c r="D14" t="s">
-        <v>1127</v>
+        <v>1207</v>
       </c>
       <c r="E14" t="s">
-        <v>1128</v>
+        <v>1208</v>
       </c>
       <c r="F14" t="s">
         <v>748</v>
@@ -12114,22 +12953,42 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>1129</v>
+        <v>1209</v>
       </c>
       <c r="B15" t="s">
         <v>206</v>
       </c>
       <c r="C15" t="s">
-        <v>1130</v>
+        <v>1210</v>
       </c>
       <c r="D15" t="s">
-        <v>1131</v>
+        <v>1211</v>
       </c>
       <c r="E15" t="s">
-        <v>1132</v>
+        <v>1212</v>
       </c>
       <c r="F15" t="s">
         <v>748</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>1213</v>
+      </c>
+      <c r="B16" t="s">
+        <v>918</v>
+      </c>
+      <c r="C16" t="s">
+        <v>1214</v>
+      </c>
+      <c r="D16" t="s">
+        <v>1215</v>
+      </c>
+      <c r="E16" t="s">
+        <v>1212</v>
+      </c>
+      <c r="F16" t="s">
+        <v>924</v>
       </c>
     </row>
   </sheetData>
@@ -12138,40 +12997,40 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G129"/>
+  <dimension ref="A1:G139"/>
   <sheetFormatPr defaultRowHeight="0" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" customHeight="1"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>1133</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1134</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>1135</v>
+        <v>1218</v>
       </c>
       <c r="B3" t="s">
-        <v>1136</v>
+        <v>1219</v>
       </c>
       <c r="C3" t="s">
-        <v>1137</v>
+        <v>1220</v>
       </c>
       <c r="D3" t="s">
-        <v>1138</v>
+        <v>1221</v>
       </c>
       <c r="E3" t="s">
-        <v>1139</v>
+        <v>1222</v>
       </c>
       <c r="F3" t="s">
-        <v>1140</v>
+        <v>1223</v>
       </c>
       <c r="G3" t="s">
-        <v>1141</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -12191,10 +13050,10 @@
         <v>26</v>
       </c>
       <c r="F4" t="s">
-        <v>1142</v>
+        <v>1225</v>
       </c>
       <c r="G4" t="s">
-        <v>1143</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -12214,10 +13073,10 @@
         <v>26</v>
       </c>
       <c r="F5" t="s">
-        <v>1142</v>
+        <v>1225</v>
       </c>
       <c r="G5" t="s">
-        <v>1144</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -12237,10 +13096,10 @@
         <v>26</v>
       </c>
       <c r="F6" t="s">
-        <v>1142</v>
+        <v>1225</v>
       </c>
       <c r="G6" t="s">
-        <v>1145</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -12260,10 +13119,10 @@
         <v>86</v>
       </c>
       <c r="F7" t="s">
-        <v>1142</v>
+        <v>1225</v>
       </c>
       <c r="G7" t="s">
-        <v>1146</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -12283,10 +13142,10 @@
         <v>26</v>
       </c>
       <c r="F8" t="s">
-        <v>1142</v>
+        <v>1225</v>
       </c>
       <c r="G8" t="s">
-        <v>1147</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -12306,10 +13165,10 @@
         <v>26</v>
       </c>
       <c r="F9" t="s">
-        <v>1142</v>
+        <v>1225</v>
       </c>
       <c r="G9" t="s">
-        <v>1148</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -12329,10 +13188,10 @@
         <v>26</v>
       </c>
       <c r="F10" t="s">
-        <v>1142</v>
+        <v>1225</v>
       </c>
       <c r="G10" t="s">
-        <v>1149</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -12352,10 +13211,10 @@
         <v>86</v>
       </c>
       <c r="F11" t="s">
-        <v>1142</v>
+        <v>1225</v>
       </c>
       <c r="G11" t="s">
-        <v>1150</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -12375,10 +13234,10 @@
         <v>86</v>
       </c>
       <c r="F12" t="s">
-        <v>1142</v>
+        <v>1225</v>
       </c>
       <c r="G12" t="s">
-        <v>1151</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -12398,10 +13257,10 @@
         <v>26</v>
       </c>
       <c r="F13" t="s">
-        <v>1142</v>
+        <v>1225</v>
       </c>
       <c r="G13" t="s">
-        <v>1152</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -12421,10 +13280,10 @@
         <v>26</v>
       </c>
       <c r="F14" t="s">
-        <v>1153</v>
+        <v>1236</v>
       </c>
       <c r="G14" t="s">
-        <v>1154</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -12444,10 +13303,10 @@
         <v>26</v>
       </c>
       <c r="F15" t="s">
-        <v>1153</v>
+        <v>1236</v>
       </c>
       <c r="G15" t="s">
-        <v>1155</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -12467,10 +13326,10 @@
         <v>26</v>
       </c>
       <c r="F16" t="s">
-        <v>1153</v>
+        <v>1236</v>
       </c>
       <c r="G16" t="s">
-        <v>1156</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -12490,10 +13349,10 @@
         <v>26</v>
       </c>
       <c r="F17" t="s">
-        <v>1153</v>
+        <v>1236</v>
       </c>
       <c r="G17" t="s">
-        <v>1157</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -12513,10 +13372,10 @@
         <v>26</v>
       </c>
       <c r="F18" t="s">
-        <v>1153</v>
+        <v>1236</v>
       </c>
       <c r="G18" t="s">
-        <v>1158</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -12536,10 +13395,10 @@
         <v>26</v>
       </c>
       <c r="F19" t="s">
-        <v>1153</v>
+        <v>1236</v>
       </c>
       <c r="G19" t="s">
-        <v>1159</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -12559,10 +13418,10 @@
         <v>86</v>
       </c>
       <c r="F20" t="s">
-        <v>1153</v>
+        <v>1236</v>
       </c>
       <c r="G20" t="s">
-        <v>1160</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -12582,10 +13441,10 @@
         <v>86</v>
       </c>
       <c r="F21" t="s">
-        <v>1153</v>
+        <v>1236</v>
       </c>
       <c r="G21" t="s">
-        <v>1161</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
@@ -12605,10 +13464,10 @@
         <v>26</v>
       </c>
       <c r="F22" t="s">
-        <v>1153</v>
+        <v>1236</v>
       </c>
       <c r="G22" t="s">
-        <v>1162</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
@@ -12628,10 +13487,10 @@
         <v>86</v>
       </c>
       <c r="F23" t="s">
-        <v>1153</v>
+        <v>1236</v>
       </c>
       <c r="G23" t="s">
-        <v>1163</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -12651,10 +13510,10 @@
         <v>86</v>
       </c>
       <c r="F24" t="s">
-        <v>1153</v>
+        <v>1236</v>
       </c>
       <c r="G24" t="s">
-        <v>1164</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
@@ -12674,10 +13533,10 @@
         <v>86</v>
       </c>
       <c r="F25" t="s">
-        <v>1153</v>
+        <v>1236</v>
       </c>
       <c r="G25" t="s">
-        <v>1165</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
@@ -12697,10 +13556,10 @@
         <v>86</v>
       </c>
       <c r="F26" t="s">
-        <v>1153</v>
+        <v>1236</v>
       </c>
       <c r="G26" t="s">
-        <v>1166</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
@@ -12720,10 +13579,10 @@
         <v>26</v>
       </c>
       <c r="F27" t="s">
-        <v>1153</v>
+        <v>1236</v>
       </c>
       <c r="G27" t="s">
-        <v>1167</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
@@ -12743,10 +13602,10 @@
         <v>86</v>
       </c>
       <c r="F28" t="s">
-        <v>1153</v>
+        <v>1236</v>
       </c>
       <c r="G28" t="s">
-        <v>1168</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
@@ -12766,10 +13625,10 @@
         <v>86</v>
       </c>
       <c r="F29" t="s">
-        <v>1153</v>
+        <v>1236</v>
       </c>
       <c r="G29" t="s">
-        <v>1169</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
@@ -12789,10 +13648,10 @@
         <v>26</v>
       </c>
       <c r="F30" t="s">
-        <v>1153</v>
+        <v>1236</v>
       </c>
       <c r="G30" t="s">
-        <v>1170</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
@@ -12812,10 +13671,10 @@
         <v>26</v>
       </c>
       <c r="F31" t="s">
-        <v>1153</v>
+        <v>1236</v>
       </c>
       <c r="G31" t="s">
-        <v>1171</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
@@ -12835,10 +13694,10 @@
         <v>86</v>
       </c>
       <c r="F32" t="s">
-        <v>1153</v>
+        <v>1236</v>
       </c>
       <c r="G32" t="s">
-        <v>1172</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
@@ -12858,10 +13717,10 @@
         <v>86</v>
       </c>
       <c r="F33" t="s">
-        <v>1153</v>
+        <v>1236</v>
       </c>
       <c r="G33" t="s">
-        <v>1173</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
@@ -12881,10 +13740,10 @@
         <v>86</v>
       </c>
       <c r="F34" t="s">
-        <v>1153</v>
+        <v>1236</v>
       </c>
       <c r="G34" t="s">
-        <v>1174</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
@@ -12904,7 +13763,7 @@
         <v>26</v>
       </c>
       <c r="F35" t="s">
-        <v>1175</v>
+        <v>1258</v>
       </c>
       <c r="G35" t="s">
         <v>168</v>
@@ -12927,7 +13786,7 @@
         <v>26</v>
       </c>
       <c r="F36" t="s">
-        <v>1175</v>
+        <v>1258</v>
       </c>
       <c r="G36" t="s">
         <v>177</v>
@@ -12950,7 +13809,7 @@
         <v>26</v>
       </c>
       <c r="F37" t="s">
-        <v>1175</v>
+        <v>1258</v>
       </c>
       <c r="G37" t="s">
         <v>194</v>
@@ -12973,7 +13832,7 @@
         <v>26</v>
       </c>
       <c r="F38" t="s">
-        <v>1175</v>
+        <v>1258</v>
       </c>
       <c r="G38" t="s">
         <v>203</v>
@@ -12996,7 +13855,7 @@
         <v>26</v>
       </c>
       <c r="F39" t="s">
-        <v>1175</v>
+        <v>1258</v>
       </c>
       <c r="G39" t="s">
         <v>222</v>
@@ -13019,7 +13878,7 @@
         <v>26</v>
       </c>
       <c r="F40" t="s">
-        <v>1175</v>
+        <v>1258</v>
       </c>
       <c r="G40" t="s">
         <v>245</v>
@@ -13042,10 +13901,10 @@
         <v>26</v>
       </c>
       <c r="F41" t="s">
-        <v>1175</v>
+        <v>1258</v>
       </c>
       <c r="G41" t="s">
-        <v>1176</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
@@ -13065,10 +13924,10 @@
         <v>26</v>
       </c>
       <c r="F42" t="s">
-        <v>1175</v>
+        <v>1258</v>
       </c>
       <c r="G42" t="s">
-        <v>1177</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
@@ -13088,10 +13947,10 @@
         <v>26</v>
       </c>
       <c r="F43" t="s">
-        <v>1175</v>
+        <v>1258</v>
       </c>
       <c r="G43" t="s">
-        <v>1178</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
@@ -13111,7 +13970,7 @@
         <v>26</v>
       </c>
       <c r="F44" t="s">
-        <v>1175</v>
+        <v>1258</v>
       </c>
       <c r="G44" t="s">
         <v>360</v>
@@ -13134,7 +13993,7 @@
         <v>26</v>
       </c>
       <c r="F45" t="s">
-        <v>1175</v>
+        <v>1258</v>
       </c>
       <c r="G45" t="s">
         <v>368</v>
@@ -13157,10 +14016,10 @@
         <v>26</v>
       </c>
       <c r="F46" t="s">
-        <v>1175</v>
+        <v>1258</v>
       </c>
       <c r="G46" t="s">
-        <v>1179</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
@@ -13180,7 +14039,7 @@
         <v>26</v>
       </c>
       <c r="F47" t="s">
-        <v>1175</v>
+        <v>1258</v>
       </c>
       <c r="G47" t="s">
         <v>386</v>
@@ -13203,10 +14062,10 @@
         <v>26</v>
       </c>
       <c r="F48" t="s">
-        <v>1175</v>
+        <v>1258</v>
       </c>
       <c r="G48" t="s">
-        <v>1180</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
@@ -13226,7 +14085,7 @@
         <v>26</v>
       </c>
       <c r="F49" t="s">
-        <v>1175</v>
+        <v>1258</v>
       </c>
       <c r="G49" t="s">
         <v>402</v>
@@ -13249,7 +14108,7 @@
         <v>26</v>
       </c>
       <c r="F50" t="s">
-        <v>1175</v>
+        <v>1258</v>
       </c>
       <c r="G50" t="s">
         <v>411</v>
@@ -13272,7 +14131,7 @@
         <v>26</v>
       </c>
       <c r="F51" t="s">
-        <v>1175</v>
+        <v>1258</v>
       </c>
       <c r="G51" t="s">
         <v>419</v>
@@ -13295,7 +14154,7 @@
         <v>26</v>
       </c>
       <c r="F52" t="s">
-        <v>1175</v>
+        <v>1258</v>
       </c>
       <c r="G52" t="s">
         <v>426</v>
@@ -13318,7 +14177,7 @@
         <v>26</v>
       </c>
       <c r="F53" t="s">
-        <v>1175</v>
+        <v>1258</v>
       </c>
       <c r="G53" t="s">
         <v>433</v>
@@ -13341,7 +14200,7 @@
         <v>26</v>
       </c>
       <c r="F54" t="s">
-        <v>1175</v>
+        <v>1258</v>
       </c>
       <c r="G54" t="s">
         <v>467</v>
@@ -13364,7 +14223,7 @@
         <v>26</v>
       </c>
       <c r="F55" t="s">
-        <v>1175</v>
+        <v>1258</v>
       </c>
       <c r="G55" t="s">
         <v>485</v>
@@ -13387,7 +14246,7 @@
         <v>26</v>
       </c>
       <c r="F56" t="s">
-        <v>1175</v>
+        <v>1258</v>
       </c>
       <c r="G56" t="s">
         <v>494</v>
@@ -13410,7 +14269,7 @@
         <v>26</v>
       </c>
       <c r="F57" t="s">
-        <v>1175</v>
+        <v>1258</v>
       </c>
       <c r="G57" t="s">
         <v>502</v>
@@ -13433,7 +14292,7 @@
         <v>26</v>
       </c>
       <c r="F58" t="s">
-        <v>1175</v>
+        <v>1258</v>
       </c>
       <c r="G58" t="s">
         <v>511</v>
@@ -13456,7 +14315,7 @@
         <v>26</v>
       </c>
       <c r="F59" t="s">
-        <v>1175</v>
+        <v>1258</v>
       </c>
       <c r="G59" t="s">
         <v>520</v>
@@ -13479,7 +14338,7 @@
         <v>26</v>
       </c>
       <c r="F60" t="s">
-        <v>1175</v>
+        <v>1258</v>
       </c>
       <c r="G60" t="s">
         <v>530</v>
@@ -13502,7 +14361,7 @@
         <v>26</v>
       </c>
       <c r="F61" t="s">
-        <v>1175</v>
+        <v>1258</v>
       </c>
       <c r="G61" t="s">
         <v>539</v>
@@ -13525,7 +14384,7 @@
         <v>26</v>
       </c>
       <c r="F62" t="s">
-        <v>1175</v>
+        <v>1258</v>
       </c>
       <c r="G62" t="s">
         <v>547</v>
@@ -13548,7 +14407,7 @@
         <v>26</v>
       </c>
       <c r="F63" t="s">
-        <v>1175</v>
+        <v>1258</v>
       </c>
       <c r="G63" t="s">
         <v>557</v>
@@ -13571,7 +14430,7 @@
         <v>26</v>
       </c>
       <c r="F64" t="s">
-        <v>1175</v>
+        <v>1258</v>
       </c>
       <c r="G64" t="s">
         <v>567</v>
@@ -13594,7 +14453,7 @@
         <v>26</v>
       </c>
       <c r="F65" t="s">
-        <v>1175</v>
+        <v>1258</v>
       </c>
       <c r="G65" t="s">
         <v>576</v>
@@ -13617,7 +14476,7 @@
         <v>26</v>
       </c>
       <c r="F66" t="s">
-        <v>1175</v>
+        <v>1258</v>
       </c>
       <c r="G66" t="s">
         <v>584</v>
@@ -13640,7 +14499,7 @@
         <v>26</v>
       </c>
       <c r="F67" t="s">
-        <v>1175</v>
+        <v>1258</v>
       </c>
       <c r="G67" t="s">
         <v>594</v>
@@ -13663,7 +14522,7 @@
         <v>26</v>
       </c>
       <c r="F68" t="s">
-        <v>1175</v>
+        <v>1258</v>
       </c>
       <c r="G68" t="s">
         <v>602</v>
@@ -13686,7 +14545,7 @@
         <v>26</v>
       </c>
       <c r="F69" t="s">
-        <v>1175</v>
+        <v>1258</v>
       </c>
       <c r="G69" t="s">
         <v>611</v>
@@ -13709,7 +14568,7 @@
         <v>26</v>
       </c>
       <c r="F70" t="s">
-        <v>1175</v>
+        <v>1258</v>
       </c>
       <c r="G70" t="s">
         <v>618</v>
@@ -13732,10 +14591,10 @@
         <v>26</v>
       </c>
       <c r="F71" t="s">
-        <v>1175</v>
+        <v>1258</v>
       </c>
       <c r="G71" t="s">
-        <v>1181</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
@@ -13755,10 +14614,10 @@
         <v>26</v>
       </c>
       <c r="F72" t="s">
-        <v>1175</v>
+        <v>1258</v>
       </c>
       <c r="G72" t="s">
-        <v>1182</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
@@ -13778,10 +14637,10 @@
         <v>26</v>
       </c>
       <c r="F73" t="s">
-        <v>1175</v>
+        <v>1258</v>
       </c>
       <c r="G73" t="s">
-        <v>1183</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
@@ -13801,10 +14660,10 @@
         <v>26</v>
       </c>
       <c r="F74" t="s">
-        <v>1175</v>
+        <v>1258</v>
       </c>
       <c r="G74" t="s">
-        <v>1184</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
@@ -13824,10 +14683,10 @@
         <v>26</v>
       </c>
       <c r="F75" t="s">
-        <v>1175</v>
+        <v>1258</v>
       </c>
       <c r="G75" t="s">
-        <v>1185</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
@@ -13847,10 +14706,10 @@
         <v>26</v>
       </c>
       <c r="F76" t="s">
-        <v>1175</v>
+        <v>1258</v>
       </c>
       <c r="G76" t="s">
-        <v>1186</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
@@ -13870,10 +14729,10 @@
         <v>26</v>
       </c>
       <c r="F77" t="s">
-        <v>1175</v>
+        <v>1258</v>
       </c>
       <c r="G77" t="s">
-        <v>1187</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
@@ -13893,10 +14752,10 @@
         <v>26</v>
       </c>
       <c r="F78" t="s">
-        <v>1175</v>
+        <v>1258</v>
       </c>
       <c r="G78" t="s">
-        <v>1188</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
@@ -13916,10 +14775,10 @@
         <v>26</v>
       </c>
       <c r="F79" t="s">
-        <v>1175</v>
+        <v>1258</v>
       </c>
       <c r="G79" t="s">
-        <v>1189</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
@@ -13927,7 +14786,7 @@
         <v>27</v>
       </c>
       <c r="B80" t="s">
-        <v>1120</v>
+        <v>1200</v>
       </c>
       <c r="C80" t="s">
         <v>697</v>
@@ -13939,10 +14798,10 @@
         <v>26</v>
       </c>
       <c r="F80" t="s">
-        <v>1190</v>
+        <v>1273</v>
       </c>
       <c r="G80" t="s">
-        <v>1191</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
@@ -13950,7 +14809,7 @@
         <v>27</v>
       </c>
       <c r="B81" t="s">
-        <v>1120</v>
+        <v>1200</v>
       </c>
       <c r="C81" t="s">
         <v>708</v>
@@ -13962,10 +14821,10 @@
         <v>26</v>
       </c>
       <c r="F81" t="s">
-        <v>1190</v>
+        <v>1273</v>
       </c>
       <c r="G81" t="s">
-        <v>1192</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
@@ -13973,7 +14832,7 @@
         <v>27</v>
       </c>
       <c r="B82" t="s">
-        <v>1120</v>
+        <v>1200</v>
       </c>
       <c r="C82" t="s">
         <v>715</v>
@@ -13985,10 +14844,10 @@
         <v>26</v>
       </c>
       <c r="F82" t="s">
-        <v>1190</v>
+        <v>1273</v>
       </c>
       <c r="G82" t="s">
-        <v>1193</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
@@ -13996,7 +14855,7 @@
         <v>27</v>
       </c>
       <c r="B83" t="s">
-        <v>1120</v>
+        <v>1200</v>
       </c>
       <c r="C83" t="s">
         <v>723</v>
@@ -14008,10 +14867,10 @@
         <v>26</v>
       </c>
       <c r="F83" t="s">
-        <v>1190</v>
+        <v>1273</v>
       </c>
       <c r="G83" t="s">
-        <v>1194</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
@@ -14019,7 +14878,7 @@
         <v>27</v>
       </c>
       <c r="B84" t="s">
-        <v>1120</v>
+        <v>1200</v>
       </c>
       <c r="C84" t="s">
         <v>732</v>
@@ -14031,10 +14890,10 @@
         <v>26</v>
       </c>
       <c r="F84" t="s">
-        <v>1190</v>
+        <v>1273</v>
       </c>
       <c r="G84" t="s">
-        <v>1195</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
@@ -14042,7 +14901,7 @@
         <v>27</v>
       </c>
       <c r="B85" t="s">
-        <v>1196</v>
+        <v>1279</v>
       </c>
       <c r="C85" t="s">
         <v>324</v>
@@ -14054,10 +14913,10 @@
         <v>86</v>
       </c>
       <c r="F85" t="s">
-        <v>1197</v>
+        <v>1280</v>
       </c>
       <c r="G85" t="s">
-        <v>1198</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
@@ -14065,7 +14924,7 @@
         <v>27</v>
       </c>
       <c r="B86" t="s">
-        <v>1196</v>
+        <v>1279</v>
       </c>
       <c r="C86" t="s">
         <v>335</v>
@@ -14077,10 +14936,10 @@
         <v>86</v>
       </c>
       <c r="F86" t="s">
-        <v>1197</v>
+        <v>1280</v>
       </c>
       <c r="G86" t="s">
-        <v>1199</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
@@ -14088,7 +14947,7 @@
         <v>27</v>
       </c>
       <c r="B87" t="s">
-        <v>1196</v>
+        <v>1279</v>
       </c>
       <c r="C87" t="s">
         <v>344</v>
@@ -14100,10 +14959,10 @@
         <v>86</v>
       </c>
       <c r="F87" t="s">
-        <v>1197</v>
+        <v>1280</v>
       </c>
       <c r="G87" t="s">
-        <v>1200</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
@@ -14111,7 +14970,7 @@
         <v>27</v>
       </c>
       <c r="B88" t="s">
-        <v>1196</v>
+        <v>1279</v>
       </c>
       <c r="C88" t="s">
         <v>369</v>
@@ -14123,10 +14982,10 @@
         <v>112</v>
       </c>
       <c r="F88" t="s">
-        <v>1197</v>
+        <v>1280</v>
       </c>
       <c r="G88" t="s">
-        <v>1201</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
@@ -14146,10 +15005,10 @@
         <v>26</v>
       </c>
       <c r="F89" t="s">
-        <v>1202</v>
+        <v>1285</v>
       </c>
       <c r="G89" t="s">
-        <v>1203</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
@@ -14157,7 +15016,7 @@
         <v>27</v>
       </c>
       <c r="B90" t="s">
-        <v>1196</v>
+        <v>1279</v>
       </c>
       <c r="C90" t="s">
         <v>619</v>
@@ -14169,10 +15028,10 @@
         <v>112</v>
       </c>
       <c r="F90" t="s">
-        <v>1197</v>
+        <v>1280</v>
       </c>
       <c r="G90" t="s">
-        <v>1204</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
@@ -14180,7 +15039,7 @@
         <v>27</v>
       </c>
       <c r="B91" t="s">
-        <v>1196</v>
+        <v>1279</v>
       </c>
       <c r="C91" t="s">
         <v>639</v>
@@ -14192,10 +15051,10 @@
         <v>86</v>
       </c>
       <c r="F91" t="s">
-        <v>1197</v>
+        <v>1280</v>
       </c>
       <c r="G91" t="s">
-        <v>1205</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
@@ -14203,7 +15062,7 @@
         <v>27</v>
       </c>
       <c r="B92" t="s">
-        <v>1196</v>
+        <v>1279</v>
       </c>
       <c r="C92" t="s">
         <v>648</v>
@@ -14215,10 +15074,10 @@
         <v>112</v>
       </c>
       <c r="F92" t="s">
-        <v>1197</v>
+        <v>1280</v>
       </c>
       <c r="G92" t="s">
-        <v>1206</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
@@ -14238,10 +15097,10 @@
         <v>86</v>
       </c>
       <c r="F93" t="s">
-        <v>1202</v>
+        <v>1285</v>
       </c>
       <c r="G93" t="s">
-        <v>1207</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
@@ -14249,7 +15108,7 @@
         <v>27</v>
       </c>
       <c r="B94" t="s">
-        <v>1196</v>
+        <v>1279</v>
       </c>
       <c r="C94" t="s">
         <v>657</v>
@@ -14261,10 +15120,10 @@
         <v>112</v>
       </c>
       <c r="F94" t="s">
-        <v>1197</v>
+        <v>1280</v>
       </c>
       <c r="G94" t="s">
-        <v>1208</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
@@ -14272,7 +15131,7 @@
         <v>27</v>
       </c>
       <c r="B95" t="s">
-        <v>1196</v>
+        <v>1279</v>
       </c>
       <c r="C95" t="s">
         <v>673</v>
@@ -14284,10 +15143,10 @@
         <v>112</v>
       </c>
       <c r="F95" t="s">
-        <v>1197</v>
+        <v>1280</v>
       </c>
       <c r="G95" t="s">
-        <v>1209</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
@@ -14307,10 +15166,10 @@
         <v>26</v>
       </c>
       <c r="F96" t="s">
-        <v>1202</v>
+        <v>1285</v>
       </c>
       <c r="G96" t="s">
-        <v>1210</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
@@ -14318,7 +15177,7 @@
         <v>27</v>
       </c>
       <c r="B97" t="s">
-        <v>1196</v>
+        <v>1279</v>
       </c>
       <c r="C97" t="s">
         <v>689</v>
@@ -14330,10 +15189,10 @@
         <v>112</v>
       </c>
       <c r="F97" t="s">
-        <v>1197</v>
+        <v>1280</v>
       </c>
       <c r="G97" t="s">
-        <v>1211</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
@@ -14341,7 +15200,7 @@
         <v>27</v>
       </c>
       <c r="B98" t="s">
-        <v>1196</v>
+        <v>1279</v>
       </c>
       <c r="C98" t="s">
         <v>697</v>
@@ -14353,10 +15212,10 @@
         <v>112</v>
       </c>
       <c r="F98" t="s">
-        <v>1197</v>
+        <v>1280</v>
       </c>
       <c r="G98" t="s">
-        <v>1212</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
@@ -14376,10 +15235,10 @@
         <v>26</v>
       </c>
       <c r="F99" t="s">
-        <v>1202</v>
+        <v>1285</v>
       </c>
       <c r="G99" t="s">
-        <v>1213</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
@@ -14387,7 +15246,7 @@
         <v>27</v>
       </c>
       <c r="B100" t="s">
-        <v>1196</v>
+        <v>1279</v>
       </c>
       <c r="C100" t="s">
         <v>708</v>
@@ -14399,10 +15258,10 @@
         <v>112</v>
       </c>
       <c r="F100" t="s">
-        <v>1197</v>
+        <v>1280</v>
       </c>
       <c r="G100" t="s">
-        <v>1214</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
@@ -14422,10 +15281,10 @@
         <v>86</v>
       </c>
       <c r="F101" t="s">
-        <v>1202</v>
+        <v>1285</v>
       </c>
       <c r="G101" t="s">
-        <v>1215</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
@@ -14433,7 +15292,7 @@
         <v>27</v>
       </c>
       <c r="B102" t="s">
-        <v>1196</v>
+        <v>1279</v>
       </c>
       <c r="C102" t="s">
         <v>715</v>
@@ -14445,10 +15304,10 @@
         <v>112</v>
       </c>
       <c r="F102" t="s">
-        <v>1197</v>
+        <v>1280</v>
       </c>
       <c r="G102" t="s">
-        <v>1216</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
@@ -14468,10 +15327,10 @@
         <v>86</v>
       </c>
       <c r="F103" t="s">
-        <v>1202</v>
+        <v>1285</v>
       </c>
       <c r="G103" t="s">
-        <v>1217</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
@@ -14479,7 +15338,7 @@
         <v>27</v>
       </c>
       <c r="B104" t="s">
-        <v>1196</v>
+        <v>1279</v>
       </c>
       <c r="C104" t="s">
         <v>723</v>
@@ -14491,10 +15350,10 @@
         <v>112</v>
       </c>
       <c r="F104" t="s">
-        <v>1197</v>
+        <v>1280</v>
       </c>
       <c r="G104" t="s">
-        <v>1218</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
@@ -14514,10 +15373,10 @@
         <v>26</v>
       </c>
       <c r="F105" t="s">
-        <v>1202</v>
+        <v>1285</v>
       </c>
       <c r="G105" t="s">
-        <v>1219</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
@@ -14525,7 +15384,7 @@
         <v>27</v>
       </c>
       <c r="B106" t="s">
-        <v>1196</v>
+        <v>1279</v>
       </c>
       <c r="C106" t="s">
         <v>732</v>
@@ -14537,10 +15396,10 @@
         <v>112</v>
       </c>
       <c r="F106" t="s">
-        <v>1197</v>
+        <v>1280</v>
       </c>
       <c r="G106" t="s">
-        <v>1220</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
@@ -14560,10 +15419,10 @@
         <v>26</v>
       </c>
       <c r="F107" t="s">
-        <v>1202</v>
+        <v>1285</v>
       </c>
       <c r="G107" t="s">
-        <v>1221</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
@@ -14577,13 +15436,13 @@
         <v>740</v>
       </c>
       <c r="D108" t="s">
-        <v>1222</v>
+        <v>1305</v>
       </c>
       <c r="E108" t="s">
         <v>112</v>
       </c>
       <c r="F108" t="s">
-        <v>1202</v>
+        <v>1285</v>
       </c>
       <c r="G108" t="s">
         <v>741</v>
@@ -14600,13 +15459,13 @@
         <v>750</v>
       </c>
       <c r="D109" t="s">
-        <v>1222</v>
+        <v>1305</v>
       </c>
       <c r="E109" t="s">
         <v>112</v>
       </c>
       <c r="F109" t="s">
-        <v>1202</v>
+        <v>1285</v>
       </c>
       <c r="G109" t="s">
         <v>751</v>
@@ -14623,13 +15482,13 @@
         <v>758</v>
       </c>
       <c r="D110" t="s">
-        <v>1222</v>
+        <v>1305</v>
       </c>
       <c r="E110" t="s">
         <v>112</v>
       </c>
       <c r="F110" t="s">
-        <v>1202</v>
+        <v>1285</v>
       </c>
       <c r="G110" t="s">
         <v>759</v>
@@ -14646,13 +15505,13 @@
         <v>766</v>
       </c>
       <c r="D111" t="s">
-        <v>1222</v>
+        <v>1305</v>
       </c>
       <c r="E111" t="s">
         <v>112</v>
       </c>
       <c r="F111" t="s">
-        <v>1202</v>
+        <v>1285</v>
       </c>
       <c r="G111" t="s">
         <v>767</v>
@@ -14669,13 +15528,13 @@
         <v>774</v>
       </c>
       <c r="D112" t="s">
-        <v>1222</v>
+        <v>1305</v>
       </c>
       <c r="E112" t="s">
         <v>112</v>
       </c>
       <c r="F112" t="s">
-        <v>1202</v>
+        <v>1285</v>
       </c>
       <c r="G112" t="s">
         <v>775</v>
@@ -14692,13 +15551,13 @@
         <v>782</v>
       </c>
       <c r="D113" t="s">
-        <v>1222</v>
+        <v>1305</v>
       </c>
       <c r="E113" t="s">
         <v>112</v>
       </c>
       <c r="F113" t="s">
-        <v>1202</v>
+        <v>1285</v>
       </c>
       <c r="G113" t="s">
         <v>783</v>
@@ -14715,13 +15574,13 @@
         <v>790</v>
       </c>
       <c r="D114" t="s">
-        <v>1222</v>
+        <v>1305</v>
       </c>
       <c r="E114" t="s">
         <v>112</v>
       </c>
       <c r="F114" t="s">
-        <v>1202</v>
+        <v>1285</v>
       </c>
       <c r="G114" t="s">
         <v>791</v>
@@ -14738,13 +15597,13 @@
         <v>798</v>
       </c>
       <c r="D115" t="s">
-        <v>1222</v>
+        <v>1305</v>
       </c>
       <c r="E115" t="s">
         <v>112</v>
       </c>
       <c r="F115" t="s">
-        <v>1202</v>
+        <v>1285</v>
       </c>
       <c r="G115" t="s">
         <v>799</v>
@@ -14761,13 +15620,13 @@
         <v>806</v>
       </c>
       <c r="D116" t="s">
-        <v>1222</v>
+        <v>1305</v>
       </c>
       <c r="E116" t="s">
         <v>112</v>
       </c>
       <c r="F116" t="s">
-        <v>1202</v>
+        <v>1285</v>
       </c>
       <c r="G116" t="s">
         <v>807</v>
@@ -14784,13 +15643,13 @@
         <v>814</v>
       </c>
       <c r="D117" t="s">
-        <v>1222</v>
+        <v>1305</v>
       </c>
       <c r="E117" t="s">
         <v>112</v>
       </c>
       <c r="F117" t="s">
-        <v>1202</v>
+        <v>1285</v>
       </c>
       <c r="G117" t="s">
         <v>815</v>
@@ -14807,13 +15666,13 @@
         <v>821</v>
       </c>
       <c r="D118" t="s">
-        <v>1222</v>
+        <v>1305</v>
       </c>
       <c r="E118" t="s">
         <v>112</v>
       </c>
       <c r="F118" t="s">
-        <v>1202</v>
+        <v>1285</v>
       </c>
       <c r="G118" t="s">
         <v>823</v>
@@ -14830,13 +15689,13 @@
         <v>830</v>
       </c>
       <c r="D119" t="s">
-        <v>1222</v>
+        <v>1305</v>
       </c>
       <c r="E119" t="s">
         <v>112</v>
       </c>
       <c r="F119" t="s">
-        <v>1202</v>
+        <v>1285</v>
       </c>
       <c r="G119" t="s">
         <v>831</v>
@@ -14853,13 +15712,13 @@
         <v>837</v>
       </c>
       <c r="D120" t="s">
-        <v>1222</v>
+        <v>1305</v>
       </c>
       <c r="E120" t="s">
         <v>112</v>
       </c>
       <c r="F120" t="s">
-        <v>1202</v>
+        <v>1285</v>
       </c>
       <c r="G120" t="s">
         <v>838</v>
@@ -14876,13 +15735,13 @@
         <v>844</v>
       </c>
       <c r="D121" t="s">
-        <v>1222</v>
+        <v>1305</v>
       </c>
       <c r="E121" t="s">
         <v>112</v>
       </c>
       <c r="F121" t="s">
-        <v>1202</v>
+        <v>1285</v>
       </c>
       <c r="G121" t="s">
         <v>845</v>
@@ -14899,13 +15758,13 @@
         <v>852</v>
       </c>
       <c r="D122" t="s">
-        <v>1222</v>
+        <v>1305</v>
       </c>
       <c r="E122" t="s">
         <v>26</v>
       </c>
       <c r="F122" t="s">
-        <v>1202</v>
+        <v>1285</v>
       </c>
       <c r="G122" t="s">
         <v>853</v>
@@ -14922,13 +15781,13 @@
         <v>860</v>
       </c>
       <c r="D123" t="s">
-        <v>1222</v>
+        <v>1305</v>
       </c>
       <c r="E123" t="s">
         <v>112</v>
       </c>
       <c r="F123" t="s">
-        <v>1202</v>
+        <v>1285</v>
       </c>
       <c r="G123" t="s">
         <v>861</v>
@@ -14945,13 +15804,13 @@
         <v>868</v>
       </c>
       <c r="D124" t="s">
-        <v>1222</v>
+        <v>1305</v>
       </c>
       <c r="E124" t="s">
         <v>112</v>
       </c>
       <c r="F124" t="s">
-        <v>1202</v>
+        <v>1285</v>
       </c>
       <c r="G124" t="s">
         <v>869</v>
@@ -14968,13 +15827,13 @@
         <v>876</v>
       </c>
       <c r="D125" t="s">
-        <v>1222</v>
+        <v>1305</v>
       </c>
       <c r="E125" t="s">
         <v>112</v>
       </c>
       <c r="F125" t="s">
-        <v>1202</v>
+        <v>1285</v>
       </c>
       <c r="G125" t="s">
         <v>878</v>
@@ -14991,13 +15850,13 @@
         <v>885</v>
       </c>
       <c r="D126" t="s">
-        <v>1222</v>
+        <v>1305</v>
       </c>
       <c r="E126" t="s">
         <v>112</v>
       </c>
       <c r="F126" t="s">
-        <v>1202</v>
+        <v>1285</v>
       </c>
       <c r="G126" t="s">
         <v>886</v>
@@ -15014,13 +15873,13 @@
         <v>893</v>
       </c>
       <c r="D127" t="s">
-        <v>1222</v>
+        <v>1305</v>
       </c>
       <c r="E127" t="s">
         <v>112</v>
       </c>
       <c r="F127" t="s">
-        <v>1202</v>
+        <v>1285</v>
       </c>
       <c r="G127" t="s">
         <v>894</v>
@@ -15037,13 +15896,13 @@
         <v>901</v>
       </c>
       <c r="D128" t="s">
-        <v>1222</v>
+        <v>1305</v>
       </c>
       <c r="E128" t="s">
         <v>453</v>
       </c>
       <c r="F128" t="s">
-        <v>1202</v>
+        <v>1285</v>
       </c>
       <c r="G128" t="s">
         <v>902</v>
@@ -15060,16 +15919,246 @@
         <v>909</v>
       </c>
       <c r="D129" t="s">
-        <v>1222</v>
+        <v>1305</v>
       </c>
       <c r="E129" t="s">
         <v>112</v>
       </c>
       <c r="F129" t="s">
-        <v>1202</v>
+        <v>1285</v>
       </c>
       <c r="G129" t="s">
         <v>910</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>27</v>
+      </c>
+      <c r="B130" t="s">
+        <v>918</v>
+      </c>
+      <c r="C130" t="s">
+        <v>916</v>
+      </c>
+      <c r="D130" t="s">
+        <v>1305</v>
+      </c>
+      <c r="E130" t="s">
+        <v>112</v>
+      </c>
+      <c r="F130" t="s">
+        <v>1285</v>
+      </c>
+      <c r="G130" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>27</v>
+      </c>
+      <c r="B131" t="s">
+        <v>918</v>
+      </c>
+      <c r="C131" t="s">
+        <v>926</v>
+      </c>
+      <c r="D131" t="s">
+        <v>1305</v>
+      </c>
+      <c r="E131" t="s">
+        <v>112</v>
+      </c>
+      <c r="F131" t="s">
+        <v>1285</v>
+      </c>
+      <c r="G131" t="s">
+        <v>927</v>
+      </c>
+    </row>
+    <row r="132" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>27</v>
+      </c>
+      <c r="B132" t="s">
+        <v>918</v>
+      </c>
+      <c r="C132" t="s">
+        <v>934</v>
+      </c>
+      <c r="D132" t="s">
+        <v>1305</v>
+      </c>
+      <c r="E132" t="s">
+        <v>112</v>
+      </c>
+      <c r="F132" t="s">
+        <v>1285</v>
+      </c>
+      <c r="G132" t="s">
+        <v>935</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>27</v>
+      </c>
+      <c r="B133" t="s">
+        <v>918</v>
+      </c>
+      <c r="C133" t="s">
+        <v>942</v>
+      </c>
+      <c r="D133" t="s">
+        <v>1305</v>
+      </c>
+      <c r="E133" t="s">
+        <v>112</v>
+      </c>
+      <c r="F133" t="s">
+        <v>1285</v>
+      </c>
+      <c r="G133" t="s">
+        <v>943</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>27</v>
+      </c>
+      <c r="B134" t="s">
+        <v>918</v>
+      </c>
+      <c r="C134" t="s">
+        <v>950</v>
+      </c>
+      <c r="D134" t="s">
+        <v>1305</v>
+      </c>
+      <c r="E134" t="s">
+        <v>112</v>
+      </c>
+      <c r="F134" t="s">
+        <v>1285</v>
+      </c>
+      <c r="G134" t="s">
+        <v>951</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>27</v>
+      </c>
+      <c r="B135" t="s">
+        <v>918</v>
+      </c>
+      <c r="C135" t="s">
+        <v>958</v>
+      </c>
+      <c r="D135" t="s">
+        <v>1305</v>
+      </c>
+      <c r="E135" t="s">
+        <v>112</v>
+      </c>
+      <c r="F135" t="s">
+        <v>1285</v>
+      </c>
+      <c r="G135" t="s">
+        <v>960</v>
+      </c>
+    </row>
+    <row r="136" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>27</v>
+      </c>
+      <c r="B136" t="s">
+        <v>918</v>
+      </c>
+      <c r="C136" t="s">
+        <v>967</v>
+      </c>
+      <c r="D136" t="s">
+        <v>1305</v>
+      </c>
+      <c r="E136" t="s">
+        <v>112</v>
+      </c>
+      <c r="F136" t="s">
+        <v>1285</v>
+      </c>
+      <c r="G136" t="s">
+        <v>968</v>
+      </c>
+    </row>
+    <row r="137" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>27</v>
+      </c>
+      <c r="B137" t="s">
+        <v>918</v>
+      </c>
+      <c r="C137" t="s">
+        <v>974</v>
+      </c>
+      <c r="D137" t="s">
+        <v>1305</v>
+      </c>
+      <c r="E137" t="s">
+        <v>112</v>
+      </c>
+      <c r="F137" t="s">
+        <v>1285</v>
+      </c>
+      <c r="G137" t="s">
+        <v>975</v>
+      </c>
+    </row>
+    <row r="138" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>27</v>
+      </c>
+      <c r="B138" t="s">
+        <v>918</v>
+      </c>
+      <c r="C138" t="s">
+        <v>981</v>
+      </c>
+      <c r="D138" t="s">
+        <v>1305</v>
+      </c>
+      <c r="E138" t="s">
+        <v>112</v>
+      </c>
+      <c r="F138" t="s">
+        <v>1285</v>
+      </c>
+      <c r="G138" t="s">
+        <v>982</v>
+      </c>
+    </row>
+    <row r="139" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>27</v>
+      </c>
+      <c r="B139" t="s">
+        <v>918</v>
+      </c>
+      <c r="C139" t="s">
+        <v>989</v>
+      </c>
+      <c r="D139" t="s">
+        <v>1305</v>
+      </c>
+      <c r="E139" t="s">
+        <v>112</v>
+      </c>
+      <c r="F139" t="s">
+        <v>1285</v>
+      </c>
+      <c r="G139" t="s">
+        <v>990</v>
       </c>
     </row>
   </sheetData>
@@ -15083,7 +16172,7 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>1223</v>
+        <v>1306</v>
       </c>
       <c r="B1"/>
       <c r="C1"/>
@@ -15091,7 +16180,7 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1224</v>
+        <v>1307</v>
       </c>
       <c r="B2"/>
       <c r="C2"/>
@@ -15102,181 +16191,181 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>1225</v>
+        <v>1308</v>
       </c>
       <c r="C3" t="s">
-        <v>1226</v>
+        <v>1309</v>
       </c>
       <c r="D3" t="s">
-        <v>1227</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1228</v>
+        <v>1311</v>
       </c>
       <c r="B4" t="s">
-        <v>1229</v>
+        <v>1312</v>
       </c>
       <c r="C4" t="s">
-        <v>1230</v>
+        <v>1313</v>
       </c>
       <c r="D4" t="s">
-        <v>1231</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1232</v>
+        <v>1315</v>
       </c>
       <c r="B5" t="s">
-        <v>1229</v>
+        <v>1312</v>
       </c>
       <c r="C5" t="s">
-        <v>1233</v>
+        <v>1316</v>
       </c>
       <c r="D5" t="s">
-        <v>1234</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>1235</v>
+        <v>1318</v>
       </c>
       <c r="B6" t="s">
-        <v>1229</v>
+        <v>1312</v>
       </c>
       <c r="C6" t="s">
-        <v>1236</v>
+        <v>1319</v>
       </c>
       <c r="D6" t="s">
-        <v>1237</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>1238</v>
+        <v>1321</v>
       </c>
       <c r="B7" t="s">
-        <v>1229</v>
+        <v>1312</v>
       </c>
       <c r="C7" t="s">
-        <v>1239</v>
+        <v>1322</v>
       </c>
       <c r="D7" t="s">
-        <v>1240</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>1241</v>
+        <v>1324</v>
       </c>
       <c r="B8" t="s">
-        <v>1229</v>
+        <v>1312</v>
       </c>
       <c r="C8" t="s">
-        <v>1242</v>
+        <v>1325</v>
       </c>
       <c r="D8" t="s">
-        <v>1243</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>1244</v>
+        <v>1327</v>
       </c>
       <c r="B9" t="s">
-        <v>1245</v>
+        <v>1328</v>
       </c>
       <c r="C9" t="s">
-        <v>1246</v>
+        <v>1329</v>
       </c>
       <c r="D9" t="s">
-        <v>1247</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>1248</v>
+        <v>1331</v>
       </c>
       <c r="B10" t="s">
-        <v>1245</v>
+        <v>1328</v>
       </c>
       <c r="C10" t="s">
-        <v>1249</v>
+        <v>1332</v>
       </c>
       <c r="D10" t="s">
-        <v>1250</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>1251</v>
+        <v>1334</v>
       </c>
       <c r="B11" t="s">
-        <v>1245</v>
+        <v>1328</v>
       </c>
       <c r="C11" t="s">
-        <v>1252</v>
+        <v>1335</v>
       </c>
       <c r="D11" t="s">
-        <v>1253</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>1254</v>
+        <v>1337</v>
       </c>
       <c r="B12" t="s">
-        <v>1255</v>
+        <v>1338</v>
       </c>
       <c r="C12" t="s">
-        <v>1256</v>
+        <v>1339</v>
       </c>
       <c r="D12" t="s">
-        <v>1257</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>1258</v>
+        <v>1341</v>
       </c>
       <c r="B13" t="s">
-        <v>1255</v>
+        <v>1338</v>
       </c>
       <c r="C13" t="s">
-        <v>1259</v>
+        <v>1342</v>
       </c>
       <c r="D13" t="s">
-        <v>1260</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>1261</v>
+        <v>1344</v>
       </c>
       <c r="B14" t="s">
         <v>877</v>
       </c>
       <c r="C14" t="s">
-        <v>1262</v>
+        <v>1345</v>
       </c>
       <c r="D14" t="s">
-        <v>1263</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>1264</v>
+        <v>1347</v>
       </c>
       <c r="B15" t="s">
         <v>877</v>
       </c>
       <c r="C15" t="s">
-        <v>1265</v>
+        <v>1348</v>
       </c>
       <c r="D15" t="s">
-        <v>1266</v>
+        <v>1349</v>
       </c>
     </row>
   </sheetData>
@@ -15295,7 +16384,7 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>1267</v>
+        <v>1350</v>
       </c>
       <c r="B1"/>
       <c r="C1"/>
@@ -15303,133 +16392,133 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>1268</v>
+        <v>1351</v>
       </c>
       <c r="B3" t="s">
-        <v>1269</v>
+        <v>1352</v>
       </c>
       <c r="C3" t="s">
-        <v>1270</v>
+        <v>1353</v>
       </c>
       <c r="D3" t="s">
-        <v>1271</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>956</v>
+        <v>1036</v>
       </c>
       <c r="B4" t="s">
-        <v>1272</v>
+        <v>1355</v>
       </c>
       <c r="C4" t="s">
-        <v>1273</v>
+        <v>1356</v>
       </c>
       <c r="D4" t="s">
-        <v>1274</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>961</v>
+        <v>1041</v>
       </c>
       <c r="B5" t="s">
-        <v>1275</v>
+        <v>1358</v>
       </c>
       <c r="C5" t="s">
-        <v>1276</v>
+        <v>1359</v>
       </c>
       <c r="D5" t="s">
-        <v>1277</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>965</v>
+        <v>1045</v>
       </c>
       <c r="B6" t="s">
-        <v>1278</v>
+        <v>1361</v>
       </c>
       <c r="C6" t="s">
-        <v>1279</v>
+        <v>1362</v>
       </c>
       <c r="D6" t="s">
-        <v>1280</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>969</v>
+        <v>1049</v>
       </c>
       <c r="B7" t="s">
-        <v>1281</v>
+        <v>1364</v>
       </c>
       <c r="C7" t="s">
-        <v>1282</v>
+        <v>1365</v>
       </c>
       <c r="D7" t="s">
-        <v>1283</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>973</v>
+        <v>1053</v>
       </c>
       <c r="B8" t="s">
-        <v>1284</v>
+        <v>1367</v>
       </c>
       <c r="C8" t="s">
-        <v>1285</v>
+        <v>1368</v>
       </c>
       <c r="D8" t="s">
-        <v>1286</v>
+        <v>1369</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>977</v>
+        <v>1057</v>
       </c>
       <c r="B9" t="s">
-        <v>1287</v>
+        <v>1370</v>
       </c>
       <c r="C9" t="s">
-        <v>1288</v>
+        <v>1371</v>
       </c>
       <c r="D9" t="s">
-        <v>1289</v>
+        <v>1372</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>981</v>
+        <v>1061</v>
       </c>
       <c r="B10" t="s">
-        <v>1290</v>
+        <v>1373</v>
       </c>
       <c r="C10" t="s">
-        <v>1291</v>
+        <v>1374</v>
       </c>
       <c r="D10" t="s">
-        <v>1292</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>985</v>
+        <v>1065</v>
       </c>
       <c r="B11" t="s">
-        <v>1293</v>
+        <v>1376</v>
       </c>
       <c r="C11" t="s">
-        <v>1294</v>
+        <v>1377</v>
       </c>
       <c r="D11" t="s">
-        <v>1295</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>1296</v>
+        <v>1379</v>
       </c>
       <c r="B13"/>
       <c r="C13"/>
@@ -15437,72 +16526,72 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>1297</v>
+        <v>1380</v>
       </c>
       <c r="B14" t="s">
         <v>28</v>
       </c>
       <c r="C14" t="s">
-        <v>1298</v>
+        <v>1381</v>
       </c>
       <c r="D14" t="s">
-        <v>1299</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>1300</v>
+        <v>1383</v>
       </c>
       <c r="B15" t="s">
         <v>29</v>
       </c>
       <c r="C15" t="s">
-        <v>1301</v>
+        <v>1384</v>
       </c>
       <c r="D15" t="s">
-        <v>1302</v>
+        <v>1385</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>1303</v>
+        <v>1386</v>
       </c>
       <c r="B16" t="s">
         <v>29</v>
       </c>
       <c r="C16" t="s">
-        <v>1304</v>
+        <v>1387</v>
       </c>
       <c r="D16" t="s">
-        <v>1305</v>
+        <v>1388</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>1306</v>
+        <v>1389</v>
       </c>
       <c r="B17" t="s">
         <v>29</v>
       </c>
       <c r="C17" t="s">
-        <v>1307</v>
+        <v>1390</v>
       </c>
       <c r="D17" t="s">
-        <v>1308</v>
+        <v>1391</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>1309</v>
+        <v>1392</v>
       </c>
       <c r="B18" t="s">
-        <v>1310</v>
+        <v>1393</v>
       </c>
       <c r="C18" t="s">
-        <v>1311</v>
+        <v>1394</v>
       </c>
       <c r="D18" t="s">
-        <v>1312</v>
+        <v>1395</v>
       </c>
     </row>
   </sheetData>
@@ -15521,7 +16610,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>1313</v>
+        <v>1396</v>
       </c>
       <c r="B1"/>
       <c r="C1"/>
@@ -15531,7 +16620,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1314</v>
+        <v>1397</v>
       </c>
       <c r="B2"/>
       <c r="C2"/>
@@ -15541,99 +16630,99 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1315</v>
+        <v>1398</v>
       </c>
       <c r="B4" t="s">
-        <v>1316</v>
+        <v>1399</v>
       </c>
       <c r="C4" t="s">
-        <v>1317</v>
+        <v>1400</v>
       </c>
       <c r="D4" t="s">
-        <v>1318</v>
+        <v>1401</v>
       </c>
       <c r="E4" t="s">
-        <v>1319</v>
+        <v>1402</v>
       </c>
       <c r="F4" t="s">
-        <v>1320</v>
+        <v>1403</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1321</v>
+        <v>1404</v>
       </c>
       <c r="B5" t="s">
-        <v>1322</v>
+        <v>1405</v>
       </c>
       <c r="C5" t="s">
-        <v>1323</v>
+        <v>1406</v>
       </c>
       <c r="D5" t="s">
-        <v>1324</v>
+        <v>1407</v>
       </c>
       <c r="E5" t="s">
-        <v>1325</v>
+        <v>1408</v>
       </c>
       <c r="F5" t="s">
-        <v>1326</v>
+        <v>1409</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>1327</v>
+        <v>1410</v>
       </c>
       <c r="B6" t="s">
-        <v>1328</v>
+        <v>1411</v>
       </c>
       <c r="C6" t="s">
-        <v>1329</v>
+        <v>1412</v>
       </c>
       <c r="D6" t="s">
-        <v>1330</v>
+        <v>1413</v>
       </c>
       <c r="E6" t="s">
-        <v>1331</v>
+        <v>1414</v>
       </c>
       <c r="F6" t="s">
-        <v>1332</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>1333</v>
+        <v>1416</v>
       </c>
       <c r="B7" t="s">
-        <v>1328</v>
+        <v>1411</v>
       </c>
       <c r="C7" t="s">
-        <v>1334</v>
+        <v>1417</v>
       </c>
       <c r="D7" t="s">
-        <v>1335</v>
+        <v>1418</v>
       </c>
       <c r="E7" t="s">
-        <v>1336</v>
+        <v>1419</v>
       </c>
       <c r="F7" t="s">
-        <v>1337</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>1338</v>
+        <v>1421</v>
       </c>
       <c r="B8" t="s">
-        <v>1339</v>
+        <v>1422</v>
       </c>
       <c r="C8" t="s">
-        <v>1340</v>
+        <v>1423</v>
       </c>
       <c r="D8" t="s">
-        <v>1341</v>
+        <v>1424</v>
       </c>
       <c r="E8" t="s">
-        <v>1342</v>
+        <v>1425</v>
       </c>
       <c r="F8" t="s">
         <v>629</v>
@@ -15641,19 +16730,19 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>1343</v>
+        <v>1426</v>
       </c>
       <c r="B9" t="s">
-        <v>1344</v>
+        <v>1427</v>
       </c>
       <c r="C9" t="s">
-        <v>1345</v>
+        <v>1428</v>
       </c>
       <c r="D9" t="s">
-        <v>1346</v>
+        <v>1429</v>
       </c>
       <c r="E9" t="s">
-        <v>1347</v>
+        <v>1430</v>
       </c>
       <c r="F9" t="s">
         <v>369</v>
@@ -15661,39 +16750,39 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>1348</v>
+        <v>1431</v>
       </c>
       <c r="B10" t="s">
-        <v>1349</v>
+        <v>1432</v>
       </c>
       <c r="C10" t="s">
-        <v>1350</v>
+        <v>1433</v>
       </c>
       <c r="D10" t="s">
-        <v>1351</v>
+        <v>1434</v>
       </c>
       <c r="E10" t="s">
-        <v>1352</v>
+        <v>1435</v>
       </c>
       <c r="F10" t="s">
-        <v>1353</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>1354</v>
+        <v>1437</v>
       </c>
       <c r="B11" t="s">
-        <v>1355</v>
+        <v>1438</v>
       </c>
       <c r="C11" t="s">
-        <v>1356</v>
+        <v>1439</v>
       </c>
       <c r="D11" t="s">
-        <v>1357</v>
+        <v>1440</v>
       </c>
       <c r="E11" t="s">
-        <v>1358</v>
+        <v>1441</v>
       </c>
       <c r="F11" t="s">
         <v>47</v>
@@ -15701,99 +16790,99 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>1359</v>
+        <v>1442</v>
       </c>
       <c r="B12" t="s">
-        <v>1360</v>
+        <v>1443</v>
       </c>
       <c r="C12" t="s">
-        <v>1361</v>
+        <v>1444</v>
       </c>
       <c r="D12" t="s">
-        <v>1362</v>
+        <v>1445</v>
       </c>
       <c r="E12" t="s">
-        <v>1363</v>
+        <v>1446</v>
       </c>
       <c r="F12" t="s">
-        <v>1364</v>
+        <v>1447</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>1365</v>
+        <v>1448</v>
       </c>
       <c r="B13" t="s">
-        <v>1366</v>
+        <v>1449</v>
       </c>
       <c r="C13" t="s">
-        <v>1367</v>
+        <v>1450</v>
       </c>
       <c r="D13" t="s">
-        <v>1368</v>
+        <v>1451</v>
       </c>
       <c r="E13" t="s">
-        <v>1369</v>
+        <v>1452</v>
       </c>
       <c r="F13" t="s">
-        <v>1370</v>
+        <v>1453</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>1371</v>
+        <v>1454</v>
       </c>
       <c r="B14" t="s">
-        <v>1372</v>
+        <v>1455</v>
       </c>
       <c r="C14" t="s">
-        <v>1373</v>
+        <v>1456</v>
       </c>
       <c r="D14" t="s">
-        <v>1374</v>
+        <v>1457</v>
       </c>
       <c r="E14" t="s">
-        <v>1375</v>
+        <v>1458</v>
       </c>
       <c r="F14" t="s">
-        <v>1376</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>1377</v>
+        <v>1460</v>
       </c>
       <c r="B15" t="s">
-        <v>1378</v>
+        <v>1461</v>
       </c>
       <c r="C15" t="s">
-        <v>1379</v>
+        <v>1462</v>
       </c>
       <c r="D15" t="s">
-        <v>1380</v>
+        <v>1463</v>
       </c>
       <c r="E15" t="s">
-        <v>1381</v>
+        <v>1464</v>
       </c>
       <c r="F15" t="s">
-        <v>1382</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>1383</v>
+        <v>1466</v>
       </c>
       <c r="B16" t="s">
-        <v>1384</v>
+        <v>1467</v>
       </c>
       <c r="C16" t="s">
-        <v>1385</v>
+        <v>1468</v>
       </c>
       <c r="D16" t="s">
-        <v>1386</v>
+        <v>1469</v>
       </c>
       <c r="E16" t="s">
-        <v>1387</v>
+        <v>1470</v>
       </c>
       <c r="F16" t="s">
         <v>207</v>
@@ -15801,19 +16890,19 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>1388</v>
+        <v>1471</v>
       </c>
       <c r="B17" t="s">
-        <v>1389</v>
+        <v>1472</v>
       </c>
       <c r="C17" t="s">
-        <v>1390</v>
+        <v>1473</v>
       </c>
       <c r="D17" t="s">
-        <v>1391</v>
+        <v>1474</v>
       </c>
       <c r="E17" t="s">
-        <v>1392</v>
+        <v>1475</v>
       </c>
       <c r="F17" t="s">
         <v>378</v>
@@ -15835,7 +16924,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>1393</v>
+        <v>1476</v>
       </c>
       <c r="B1"/>
       <c r="C1"/>
@@ -15845,7 +16934,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1394</v>
+        <v>1477</v>
       </c>
       <c r="B2"/>
       <c r="C2"/>
@@ -15855,162 +16944,162 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1395</v>
+        <v>1478</v>
       </c>
       <c r="B4" t="s">
-        <v>1293</v>
+        <v>1376</v>
       </c>
       <c r="C4" t="s">
-        <v>1396</v>
+        <v>1479</v>
       </c>
       <c r="D4" t="s">
-        <v>1397</v>
+        <v>1480</v>
       </c>
       <c r="E4" t="s">
-        <v>953</v>
+        <v>1033</v>
       </c>
       <c r="F4" t="s">
-        <v>1398</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>956</v>
+        <v>1036</v>
       </c>
       <c r="B5" t="s">
-        <v>1399</v>
+        <v>1482</v>
       </c>
       <c r="C5" t="s">
-        <v>1400</v>
+        <v>1483</v>
       </c>
       <c r="D5" t="s">
-        <v>1401</v>
+        <v>1484</v>
       </c>
       <c r="E5" t="s">
-        <v>1402</v>
+        <v>1485</v>
       </c>
       <c r="F5" t="s">
-        <v>1403</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>961</v>
+        <v>1041</v>
       </c>
       <c r="B6" t="s">
-        <v>1404</v>
+        <v>1487</v>
       </c>
       <c r="C6" t="s">
-        <v>1405</v>
+        <v>1488</v>
       </c>
       <c r="D6" t="s">
-        <v>1406</v>
+        <v>1489</v>
       </c>
       <c r="E6" t="s">
-        <v>1407</v>
+        <v>1490</v>
       </c>
       <c r="F6" t="s">
-        <v>1403</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>965</v>
+        <v>1045</v>
       </c>
       <c r="B7" t="s">
-        <v>1408</v>
+        <v>1491</v>
       </c>
       <c r="C7" t="s">
-        <v>1409</v>
+        <v>1492</v>
       </c>
       <c r="D7" t="s">
-        <v>1410</v>
+        <v>1493</v>
       </c>
       <c r="E7" t="s">
-        <v>1411</v>
+        <v>1494</v>
       </c>
       <c r="F7" t="s">
-        <v>1403</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>969</v>
+        <v>1049</v>
       </c>
       <c r="B8" t="s">
-        <v>1412</v>
+        <v>1495</v>
       </c>
       <c r="C8" t="s">
-        <v>1413</v>
+        <v>1496</v>
       </c>
       <c r="D8" t="s">
-        <v>1414</v>
+        <v>1497</v>
       </c>
       <c r="E8" t="s">
-        <v>1415</v>
+        <v>1498</v>
       </c>
       <c r="F8" t="s">
-        <v>1403</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>973</v>
+        <v>1053</v>
       </c>
       <c r="B9" t="s">
-        <v>1416</v>
+        <v>1499</v>
       </c>
       <c r="C9" t="s">
-        <v>1417</v>
+        <v>1500</v>
       </c>
       <c r="D9" t="s">
-        <v>1418</v>
+        <v>1501</v>
       </c>
       <c r="E9" t="s">
         <v>877</v>
       </c>
       <c r="F9" t="s">
-        <v>1419</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>977</v>
+        <v>1057</v>
       </c>
       <c r="B10" t="s">
-        <v>1420</v>
+        <v>1503</v>
       </c>
       <c r="C10" t="s">
-        <v>1421</v>
+        <v>1504</v>
       </c>
       <c r="D10" t="s">
-        <v>1422</v>
+        <v>1505</v>
       </c>
       <c r="E10" t="s">
-        <v>1423</v>
+        <v>1506</v>
       </c>
       <c r="F10" t="s">
-        <v>1419</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>981</v>
+        <v>1061</v>
       </c>
       <c r="B11" t="s">
-        <v>1424</v>
+        <v>1507</v>
       </c>
       <c r="C11" t="s">
-        <v>1425</v>
+        <v>1508</v>
       </c>
       <c r="D11" t="s">
-        <v>1426</v>
+        <v>1509</v>
       </c>
       <c r="E11" t="s">
-        <v>1427</v>
+        <v>1510</v>
       </c>
       <c r="F11" t="s">
-        <v>1428</v>
+        <v>1511</v>
       </c>
     </row>
   </sheetData>

--- a/audits/FORTLESS_MASTER_SECURITY_UI_BUG_TRACKER.xlsx
+++ b/audits/FORTLESS_MASTER_SECURITY_UI_BUG_TRACKER.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3752" uniqueCount="1512">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4070" uniqueCount="1610">
   <si>
     <t>FORTLESS   /   ENGINEERING FINDINGS REGISTER</t>
   </si>
@@ -3012,6 +3012,291 @@
     <t>[CONFIRMED_CODE] Source trace; CONFIG_DEPENDENT.</t>
   </si>
   <si>
+    <t>NEW-376</t>
+  </si>
+  <si>
+    <t>POST /admin/staff upserts existing staff and skips the self-change and last-owner guards that PATCH has</t>
+  </si>
+  <si>
+    <t>645bf61</t>
+  </si>
+  <si>
+    <t>src/server.ts:2743-2761 vs 2763-2794</t>
+  </si>
+  <si>
+    <t>POST uses INSERT ... ON CONFLICT(user_id) DO UPDATE with any role/status. The PATCH route blocks self-modification and refuses to demote or revoke the final active OWNER; the POST route has neither check, so submitting the caller's own email (or the only owner's) with status REVOKED or a lower role succeeds and also clears users.is_staff.</t>
+  </si>
+  <si>
+    <t>The last owner can lock the platform out of staff administration in one request, bypassing the documented guard. Audit still records it but recovery needs direct DB access.</t>
+  </si>
+  <si>
+    <t>Share one membership-change function that enforces self-change and last-owner rules for both routes; make POST insert-only or route updates through the same checks.</t>
+  </si>
+  <si>
+    <t>Test: POST with own email and status REVOKED returns 409; POST demoting the only OWNER returns 409; PATCH and POST behave identically.</t>
+  </si>
+  <si>
+    <t>[CONFIRMED_CODE] Source trace; needs OWNER with step-up to trigger.</t>
+  </si>
+  <si>
+    <t>NEW-377</t>
+  </si>
+  <si>
+    <t>Expired and MFA-pending sessions are never purged: cleanupExpiredSessions has no caller</t>
+  </si>
+  <si>
+    <t>src/modules/identity/auth.ts:720-726</t>
+  </si>
+  <si>
+    <t>cleanupExpiredSessions is exported but nothing in src/ calls it (grep). Only the per-user DELETE of expired rows at login (auth.ts:173) runs.</t>
+  </si>
+  <si>
+    <t>Sessions rows from password-only logins that never finish MFA, and sessions of users who never return, accumulate indefinitely.</t>
+  </si>
+  <si>
+    <t>Run the cleanup from the existing worker/maintenance loop and expose a metric.</t>
+  </si>
+  <si>
+    <t>Test: expired and stale pending-MFA rows are removed after a maintenance tick.</t>
+  </si>
+  <si>
+    <t>[CONFIRMED_CODE] grep shows no caller.</t>
+  </si>
+  <si>
+    <t>NEW-378</t>
+  </si>
+  <si>
+    <t>Staff "sync" with read-only permission mints client keys, calls the panel, writes state and answers success:true on failure</t>
+  </si>
+  <si>
+    <t>src/server.ts:2894-2931</t>
+  </si>
+  <si>
+    <t>POST /admin/services/:id/sync requires only services:read (SUPPORT and AUDITOR roles have it). It calls withAccountClientKey for any account, writes service_observed_states, and on provider error still returns {success:true, synced:false, error:&lt;provider message&gt;}. Config-missing also returns success:true.</t>
+  </si>
+  <si>
+    <t>A read-only role performs a state-changing provider call across tenants; failures look like success and may leak internal provider URLs/messages to the client.</t>
+  </si>
+  <si>
+    <t>Require services:manage (or a dedicated sync permission), return a typed 502/503 on failure, and return a generic message with the detail in logs.</t>
+  </si>
+  <si>
+    <t>Test: AUDITOR gets 403; provider outage returns a non-2xx typed error with no upstream text.</t>
+  </si>
+  <si>
+    <t>NEW-379</t>
+  </si>
+  <si>
+    <t>Manual renewal run needs accounts:manage but no step-up, while refunds and suspensions require it</t>
+  </si>
+  <si>
+    <t>src/server.ts:2838-2841</t>
+  </si>
+  <si>
+    <t>POST /admin/billing/process-renewals only checks accounts:manage; refund (1952), suspend and terminate all add requireRecentStepUp. The run creates invoices and charges for every due subscription.</t>
+  </si>
+  <si>
+    <t>A hijacked ADMINISTRATOR session can trigger platform-wide billing without a fresh verification, and the route has no audit event of its own in the handler.</t>
+  </si>
+  <si>
+    <t>Add requireRecentStepUp, write an audit event with the actor and result counts, and confirm the job is idempotent when run concurrently with the worker.</t>
+  </si>
+  <si>
+    <t>Test: without recent step-up the route returns STEP_UP_REQUIRED; each run writes one audit event.</t>
+  </si>
+  <si>
+    <t>[CONFIRMED_CODE] Policy aspect: POLICY_DECISION on whether the manual trigger should exist.</t>
+  </si>
+  <si>
+    <t>NEW-380</t>
+  </si>
+  <si>
+    <t>Logging &amp; Monitoring</t>
+  </si>
+  <si>
+    <t>Audit export is itself unaudited, needs no step-up and silently truncates at 10 000 rows</t>
+  </si>
+  <si>
+    <t>src/server.ts:2716-2728</t>
+  </si>
+  <si>
+    <t>GET /admin/audit/export has audit:read only, writes no audit event for the export, and uses LIMIT 10000 ORDER BY created_at DESC with no truncation indicator.</t>
+  </si>
+  <si>
+    <t>Bulk export of IPs and actor identifiers leaves no trace, and auditors may believe the file is complete.</t>
+  </si>
+  <si>
+    <t>Audit every export, require step-up, and stream with explicit paging or a visible truncation header/row.</t>
+  </si>
+  <si>
+    <t>Test: export creates an audit event; a database with &gt;10 000 rows returns a truncation marker or all rows.</t>
+  </si>
+  <si>
+    <t>NEW-381</t>
+  </si>
+  <si>
+    <t>File manager mutations report provider timeouts as failures; only archive, unarchive and pull treat them as pending</t>
+  </si>
+  <si>
+    <t>src/modules/provisioning/files.ts:86-176</t>
+  </si>
+  <si>
+    <t>write, createFolder, remove, rename, copy, move, chmod and signedUrl let ProviderNetworkError propagate, while archive/unarchive/pull map it to pending. The audit insert also runs after the provider call, so a failed audit insert after a successful write hides a completed change behind an error.</t>
+  </si>
+  <si>
+    <t>A timeout during delete/rename/write may have completed on Wings, but the user sees failure and retries, which can double-apply or destroy newer data; this breaks the unknown-outcome rule.</t>
+  </si>
+  <si>
+    <t>Return a typed PENDING outcome for every mutating call, re-read state before retry, and write an INTENT audit event before the call.</t>
+  </si>
+  <si>
+    <t>Test: simulated timeout on delete/rename returns pending with an audit entry; no blind retry.</t>
+  </si>
+  <si>
+    <t>NEW-382</t>
+  </si>
+  <si>
+    <t>File read buffers the whole remote file in memory before the 1 MB edit limit is applied</t>
+  </si>
+  <si>
+    <t>src/modules/provisioning/files.ts:81-87; src/modules/provisioning/adapter.ts:603-606</t>
+  </si>
+  <si>
+    <t>readFile requests the contents endpoint with asText and only afterwards compares Buffer.byteLength to MAX_EDIT_BYTES.</t>
+  </si>
+  <si>
+    <t>A viewer with file.read-content can open a multi-GB log or world file and exhaust Node memory or hold the request open.</t>
+  </si>
+  <si>
+    <t>Check the listed size first (file entry size) or stream with a byte cap and abort at the limit.</t>
+  </si>
+  <si>
+    <t>Test: reading a 200 MB file aborts at the cap without buffering it.</t>
+  </si>
+  <si>
+    <t>[CONFIRMED_CODE] Source trace; Wings may apply its own limit (CONFIG_DEPENDENT).</t>
+  </si>
+  <si>
+    <t>NEW-383</t>
+  </si>
+  <si>
+    <t>Correctness</t>
+  </si>
+  <si>
+    <t>DNS record names are case-sensitive in collision checks, so a CNAME can coexist with other records</t>
+  </si>
+  <si>
+    <t>src/modules/domains/dns.ts:469-515,562-600</t>
+  </si>
+  <si>
+    <t>Names are only trimmed; validateDnsRecordLabel accepts uppercase and the CNAME collision queries compare name = ? literally. A CNAME for "WWW" is accepted next to an A record for "www".</t>
+  </si>
+  <si>
+    <t>Produces zones that violate RFC 1912 and behave unpredictably at resolvers.</t>
+  </si>
+  <si>
+    <t>Lowercase names on write and compare case-insensitively; migrate existing rows.</t>
+  </si>
+  <si>
+    <t>Test: creating CNAME "WWW" when "www" has an A record returns CNAME_COLLISION.</t>
+  </si>
+  <si>
+    <t>NEW-384</t>
+  </si>
+  <si>
+    <t>DNS records have no quota, duplicate check or integer enforcement for weight and port</t>
+  </si>
+  <si>
+    <t>src/modules/domains/dns.ts:218-306</t>
+  </si>
+  <si>
+    <t>There is no per-zone or per-account record limit, identical records can be inserted repeatedly, and SRV weight/port are only range-checked (non-integers pass). MX priority uses Number.isInteger but SRV priority does not.</t>
+  </si>
+  <si>
+    <t>Database growth and malformed records; will matter once records are published.</t>
+  </si>
+  <si>
+    <t>Add quotas, unique (zone, type, name, content), and integer checks for all numeric fields.</t>
+  </si>
+  <si>
+    <t>Test: 1.5 as SRV port is rejected; the 1001st record in a zone returns a typed limit error.</t>
+  </si>
+  <si>
+    <t>NEW-385</t>
+  </si>
+  <si>
+    <t>DNS zones and records exist only in SQLite; no code publishes them to an authoritative server while the UI advertises ns1/ns2.fortless.net</t>
+  </si>
+  <si>
+    <t>src/modules/domains/dns.ts:309-357,469-560; src/frontend/client/pages/domains/index.ts:97-98</t>
+  </si>
+  <si>
+    <t>Records are inserted into dns_records and audited. No adapter or worker in src/ (PowerDNS, Cloudflare, Route53, zone-file export) consumes them. The UI tells customers to delegate to the Fortless nameservers.</t>
+  </si>
+  <si>
+    <t>Customers can delegate real domains to nameservers that serve nothing from this data, causing outages, and the UI shows records as if live (no-fake-success rule).</t>
+  </si>
+  <si>
+    <t>Either implement a provider adapter with outbox and verification, or label the feature as a draft/unavailable until it exists.</t>
+  </si>
+  <si>
+    <t>Test: a record created in the UI resolves from the authoritative server within the stated TTL, or the UI states that publishing is not available.</t>
+  </si>
+  <si>
+    <t>[CONFIRMED_CODE] Repo-only; an external sync outside the repository would change the status to CONFIG_DEPENDENT. Overlaps FTL-DNS-202.</t>
+  </si>
+  <si>
+    <t>NEW-386</t>
+  </si>
+  <si>
+    <t>Product Integrity</t>
+  </si>
+  <si>
+    <t>Customer and staff AI endpoints are wired to a keyword-matching mock that returns fabricated confidence values</t>
+  </si>
+  <si>
+    <t>src/server.ts:174,1778,2252,2687; src/modules/ai/adapter.ts:52-120; src/modules/ai/diagnostics.ts:50-60</t>
+  </si>
+  <si>
+    <t>aiAdapter = new MockAiProviderAdapter() is the only adapter. It matches substrings (EADDRINUSE, EULA, OOM) and returns confidence 0.95-0.99 and isGuardrailed:true. The "logs" analysed are supplied by the client in the request body, not read from the service.</t>
+  </si>
+  <si>
+    <t>Responses look like real diagnostics; a caller can steer the output by typing text. Violates the no-placeholder rule if surfaced in the UI (no current UI caller was found).</t>
+  </si>
+  <si>
+    <t>Disable the routes (typed 503) until a real provider is configured, or label results as rule-based and drop confidence.</t>
+  </si>
+  <si>
+    <t>Test: with no AI provider configured the routes return AI_NOT_CONFIGURED.</t>
+  </si>
+  <si>
+    <t>[MOCK_ONLY] Code status; frontend does not call these routes yet.</t>
+  </si>
+  <si>
+    <t>NEW-387</t>
+  </si>
+  <si>
+    <t>A shared service is granted to the recipient account's single panel user, so every OWNER/TECH_ADMIN of that account gains panel-side access</t>
+  </si>
+  <si>
+    <t>src/modules/provisioning/service-members.ts:128-165; src/modules/oidc/oidc.ts:144-169; src/modules/provisioning/service-access.ts:41-61</t>
+  </si>
+  <si>
+    <t>accept() adds the recipient account's panel_email as a Pterodactyl subuser with the preset permissions. Fortless then restricts its own UI/API to the invited user_id, but /panel/open and /oidc/authorize sign any OWNER/TECH_ADMIN of the account into the same panel user.</t>
+  </si>
+  <si>
+    <t>A second administrator of the recipient workspace who was never invited can open the shared server in the panel with the shared preset (possibly admin-level). The comment that the shared user "acts with their own panel key" is only true per account, not per user.</t>
+  </si>
+  <si>
+    <t>Decide whether sharing is per user or per account; if per user, mint per-user panel users or restrict SSO to members, and say so in the invite UI.</t>
+  </si>
+  <si>
+    <t>Test: second TECH_ADMIN of account B cannot reach the shared server in the panel unless explicitly invited.</t>
+  </si>
+  <si>
+    <t>[CONFIRMED_CODE] Source trace; panel-side behaviour is TEST_NEEDED on the sandbox panel.</t>
+  </si>
+  <si>
     <t>FORTLESS   /   SECURITY &amp; PRODUCT QUALITY</t>
   </si>
   <si>
@@ -3030,265 +3315,271 @@
     <t>CLOSED &amp; TESTED</t>
   </si>
   <si>
-    <t>120</t>
+    <t>132</t>
+  </si>
+  <si>
+    <t>48</t>
+  </si>
+  <si>
+    <t>58</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>PRIORITY &amp; STATUS</t>
+  </si>
+  <si>
+    <t>RELEASE CONTROL</t>
+  </si>
+  <si>
+    <t>Count</t>
+  </si>
+  <si>
+    <t>NOT CLEARED FOR REAL PAYMENTS Critical billing defects reproduced in source (checkout amount mismatch, inbox event loss, SEMI_ANNUAL settlement, scheduled cancellation). Static review plus local reproductions only.</t>
+  </si>
+  <si>
+    <t>15</t>
   </si>
   <si>
     <t>39</t>
   </si>
   <si>
-    <t>58</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>PRIORITY &amp; STATUS</t>
-  </si>
-  <si>
-    <t>RELEASE CONTROL</t>
-  </si>
-  <si>
-    <t>Count</t>
-  </si>
-  <si>
-    <t>NOT CLEARED FOR REAL PAYMENTS Critical billing defects reproduced in source (checkout amount mismatch, inbox event loss, SEMI_ANNUAL settlement, scheduled cancellation). Static review plus local reproductions only.</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>67</t>
-  </si>
-  <si>
-    <t>2</t>
+    <t>8</t>
+  </si>
+  <si>
+    <t>69</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>TESTED</t>
+  </si>
+  <si>
+    <t>CLOSED</t>
+  </si>
+  <si>
+    <t>LATEST VERIFIED COMMIT</t>
+  </si>
+  <si>
+    <t>REGRESSION</t>
+  </si>
+  <si>
+    <t>3cb35de (independent audit batch 1)</t>
+  </si>
+  <si>
+    <t>STATUS CONTRACT</t>
+  </si>
+  <si>
+    <t>Issue present in inspected source</t>
+  </si>
+  <si>
+    <t>Some code fixed; unresolved conditions remain</t>
+  </si>
+  <si>
+    <t>Fix observed in source; still needs regression/runtime validation</t>
+  </si>
+  <si>
+    <t>Question or risk not independently demonstrated</t>
+  </si>
+  <si>
+    <t>Requires an explicit product/security policy</t>
+  </si>
+  <si>
+    <t>Automated/authorized tests executed and evidence stored</t>
+  </si>
+  <si>
+    <t>Fix independently verified and accepted</t>
+  </si>
+  <si>
+    <t>Previously fixed behavior has returned</t>
+  </si>
+  <si>
+    <t>FORTLESS   /   30 SECURITY AUDIT DOMAINS</t>
+  </si>
+  <si>
+    <t>Static source review expanded at 6203687. Coverage is NOT an independent runtime, load, security or pixel-diff test.</t>
+  </si>
+  <si>
+    <t>#</t>
+  </si>
+  <si>
+    <t>Scope</t>
+  </si>
+  <si>
+    <t>Related finding IDs</t>
+  </si>
+  <si>
+    <t>Audit coverage</t>
+  </si>
+  <si>
+    <t>01</t>
+  </si>
+  <si>
+    <t>Authentication</t>
+  </si>
+  <si>
+    <t>Login/register/reset, brute force, enumeration</t>
+  </si>
+  <si>
+    <t>SEC-09, FTL-SEC-205, NEW-362, NEW-363, NEW-364, NEW-365, NEW-366, NEW-367</t>
+  </si>
+  <si>
+    <t>STATIC_PARTIAL</t>
+  </si>
+  <si>
+    <t>02</t>
+  </si>
+  <si>
+    <t>Sessions &amp; Devices</t>
+  </si>
+  <si>
+    <t>Token rotation, expiry, login/logout, revocation</t>
+  </si>
+  <si>
+    <t>SEC-03, SEC-04, FTL-SEC-202, NEW-363, NEW-368, NEW-377</t>
+  </si>
+  <si>
+    <t>03</t>
+  </si>
+  <si>
+    <t>MFA &amp; Passkeys</t>
+  </si>
+  <si>
+    <t>TOTP, WebAuthn, recovery, replay, UV</t>
+  </si>
+  <si>
+    <t>FTL-SEC-201, FTL-SEC-202, FTL-SEC-203, NEW-306, NEW-307, NEW-318, NEW-358, NEW-360, NEW-366, NEW-367</t>
+  </si>
+  <si>
+    <t>04</t>
+  </si>
+  <si>
+    <t>Authorization / RBAC</t>
+  </si>
+  <si>
+    <t>Every API permission and role</t>
+  </si>
+  <si>
+    <t>FTL-UI-201, SSO-01, NEW-322, NEW-328, NEW-359, NEW-376, NEW-378, NEW-379, NEW-387</t>
+  </si>
+  <si>
+    <t>05</t>
+  </si>
+  <si>
+    <t>IDOR / BOLA</t>
+  </si>
+  <si>
+    <t>Cross-account resource access</t>
+  </si>
+  <si>
+    <t>SEC-05, NEW-310, NEW-322</t>
+  </si>
+  <si>
+    <t>06</t>
+  </si>
+  <si>
+    <t>Multi-tenancy</t>
+  </si>
+  <si>
+    <t>Organization/service separation</t>
+  </si>
+  <si>
+    <t>SEC-05, SEC-06, NEW-310, NEW-322</t>
+  </si>
+  <si>
+    <t>07</t>
+  </si>
+  <si>
+    <t>API Security</t>
+  </si>
+  <si>
+    <t>Request validation/mass assignment/rate limiting</t>
+  </si>
+  <si>
+    <t>FTL-SEC-205, NEW-311, NEW-321, NEW-328</t>
+  </si>
+  <si>
+    <t>08</t>
+  </si>
+  <si>
+    <t>CSRF &amp; CORS</t>
+  </si>
+  <si>
+    <t>Origin, cookies, CSRF all writes</t>
+  </si>
+  <si>
+    <t>RUNTIME_REQUIRED</t>
+  </si>
+  <si>
+    <t>09</t>
+  </si>
+  <si>
+    <t>XSS &amp; HTML Injection</t>
+  </si>
+  <si>
+    <t>Ticket/email/console/DOM output</t>
+  </si>
+  <si>
+    <t>UI-06, MAIL-01</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>SQL / Command Injection</t>
+  </si>
+  <si>
+    <t>SQL/shell/path/template injection</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>SSRF</t>
+  </si>
+  <si>
+    <t>Private IP, DNS rebinding, redirects</t>
+  </si>
+  <si>
+    <t>SEC-08, NEW-314</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>Secrets &amp; Credentials</t>
+  </si>
+  <si>
+    <t>Provider keys, vault, rotation</t>
+  </si>
+  <si>
+    <t>NEW-313, SEC-02, NEW-323</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>Pterodactyl API</t>
+  </si>
+  <si>
+    <t>Provider scoping &amp; ownership</t>
+  </si>
+  <si>
+    <t>FTL-PROV-201, FTL-UI-202, NEW-322, NEW-323</t>
   </si>
   <si>
     <t>14</t>
   </si>
   <si>
-    <t>TESTED</t>
-  </si>
-  <si>
-    <t>CLOSED</t>
-  </si>
-  <si>
-    <t>LATEST VERIFIED COMMIT</t>
-  </si>
-  <si>
-    <t>REGRESSION</t>
-  </si>
-  <si>
-    <t>3cb35de (independent audit batch 1)</t>
-  </si>
-  <si>
-    <t>STATUS CONTRACT</t>
-  </si>
-  <si>
-    <t>Issue present in inspected source</t>
-  </si>
-  <si>
-    <t>Some code fixed; unresolved conditions remain</t>
-  </si>
-  <si>
-    <t>Fix observed in source; still needs regression/runtime validation</t>
-  </si>
-  <si>
-    <t>Question or risk not independently demonstrated</t>
-  </si>
-  <si>
-    <t>Requires an explicit product/security policy</t>
-  </si>
-  <si>
-    <t>Automated/authorized tests executed and evidence stored</t>
-  </si>
-  <si>
-    <t>Fix independently verified and accepted</t>
-  </si>
-  <si>
-    <t>Previously fixed behavior has returned</t>
-  </si>
-  <si>
-    <t>FORTLESS   /   30 SECURITY AUDIT DOMAINS</t>
-  </si>
-  <si>
-    <t>Static source review expanded at 6203687. Coverage is NOT an independent runtime, load, security or pixel-diff test.</t>
-  </si>
-  <si>
-    <t>#</t>
-  </si>
-  <si>
-    <t>Scope</t>
-  </si>
-  <si>
-    <t>Related finding IDs</t>
-  </si>
-  <si>
-    <t>Audit coverage</t>
-  </si>
-  <si>
-    <t>01</t>
-  </si>
-  <si>
-    <t>Authentication</t>
-  </si>
-  <si>
-    <t>Login/register/reset, brute force, enumeration</t>
-  </si>
-  <si>
-    <t>SEC-09, FTL-SEC-205, NEW-362, NEW-363, NEW-364, NEW-365, NEW-366, NEW-367</t>
-  </si>
-  <si>
-    <t>STATIC_PARTIAL</t>
-  </si>
-  <si>
-    <t>02</t>
-  </si>
-  <si>
-    <t>Sessions &amp; Devices</t>
-  </si>
-  <si>
-    <t>Token rotation, expiry, login/logout, revocation</t>
-  </si>
-  <si>
-    <t>SEC-03, SEC-04, FTL-SEC-202, NEW-363, NEW-368</t>
-  </si>
-  <si>
-    <t>03</t>
-  </si>
-  <si>
-    <t>MFA &amp; Passkeys</t>
-  </si>
-  <si>
-    <t>TOTP, WebAuthn, recovery, replay, UV</t>
-  </si>
-  <si>
-    <t>FTL-SEC-201, FTL-SEC-202, FTL-SEC-203, NEW-306, NEW-307, NEW-318, NEW-358, NEW-360</t>
-  </si>
-  <si>
-    <t>04</t>
-  </si>
-  <si>
-    <t>Authorization / RBAC</t>
-  </si>
-  <si>
-    <t>Every API permission and role</t>
-  </si>
-  <si>
-    <t>FTL-UI-201, SSO-01, NEW-322, NEW-328, NEW-359</t>
-  </si>
-  <si>
-    <t>05</t>
-  </si>
-  <si>
-    <t>IDOR / BOLA</t>
-  </si>
-  <si>
-    <t>Cross-account resource access</t>
-  </si>
-  <si>
-    <t>SEC-05, NEW-310, NEW-322</t>
-  </si>
-  <si>
-    <t>06</t>
-  </si>
-  <si>
-    <t>Multi-tenancy</t>
-  </si>
-  <si>
-    <t>Organization/service separation</t>
-  </si>
-  <si>
-    <t>SEC-05, SEC-06, NEW-310, NEW-322</t>
-  </si>
-  <si>
-    <t>07</t>
-  </si>
-  <si>
-    <t>API Security</t>
-  </si>
-  <si>
-    <t>Request validation/mass assignment/rate limiting</t>
-  </si>
-  <si>
-    <t>FTL-SEC-205, NEW-311, NEW-321, NEW-328</t>
-  </si>
-  <si>
-    <t>08</t>
-  </si>
-  <si>
-    <t>CSRF &amp; CORS</t>
-  </si>
-  <si>
-    <t>Origin, cookies, CSRF all writes</t>
-  </si>
-  <si>
-    <t>RUNTIME_REQUIRED</t>
-  </si>
-  <si>
-    <t>09</t>
-  </si>
-  <si>
-    <t>XSS &amp; HTML Injection</t>
-  </si>
-  <si>
-    <t>Ticket/email/console/DOM output</t>
-  </si>
-  <si>
-    <t>UI-06, MAIL-01</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>SQL / Command Injection</t>
-  </si>
-  <si>
-    <t>SQL/shell/path/template injection</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>SSRF</t>
-  </si>
-  <si>
-    <t>Private IP, DNS rebinding, redirects</t>
-  </si>
-  <si>
-    <t>SEC-08, NEW-314</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>Secrets &amp; Credentials</t>
-  </si>
-  <si>
-    <t>Provider keys, vault, rotation</t>
-  </si>
-  <si>
-    <t>NEW-313, SEC-02, NEW-323</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>Pterodactyl API</t>
-  </si>
-  <si>
-    <t>Provider scoping &amp; ownership</t>
-  </si>
-  <si>
-    <t>FTL-PROV-201, FTL-UI-202, NEW-322, NEW-323</t>
-  </si>
-  <si>
     <t>OIDC callback, native reset, revoke</t>
   </si>
   <si>
-    <t>SSO-01, SSO-02, SSO-03</t>
+    <t>SSO-01, SSO-02, SSO-03, NEW-387</t>
   </si>
   <si>
     <t>Wings &amp; WebSockets</t>
@@ -3306,7 +3597,7 @@
     <t>Traversal, archives, symlinks, quota</t>
   </si>
   <si>
-    <t>NEW-314, NEW-321</t>
+    <t>NEW-314, NEW-321, NEW-381, NEW-382</t>
   </si>
   <si>
     <t>17</t>
@@ -3357,7 +3648,7 @@
     <t>Node, cap, retry, lifecycle</t>
   </si>
   <si>
-    <t>FTL-PROV-201, FTL-PROV-202, FTL-PROV-203, FTL-PROV-204, NEW-302, NEW-322, NEW-327, NEW-352, NEW-357</t>
+    <t>FTL-PROV-201, FTL-PROV-202, FTL-PROV-203, FTL-PROV-204, NEW-302, NEW-322, NEW-327, NEW-352, NEW-357, NEW-386</t>
   </si>
   <si>
     <t>22</t>
@@ -3384,16 +3675,13 @@
     <t>FTL-PROV-201, NEW-326, NEW-327</t>
   </si>
   <si>
-    <t>24</t>
-  </si>
-  <si>
     <t>DNS &amp; Domains</t>
   </si>
   <si>
     <t>Ownership, delegation, DNS records</t>
   </si>
   <si>
-    <t>FTL-DNS-201, FTL-DNS-202, NEW-369, NEW-370</t>
+    <t>FTL-DNS-201, FTL-DNS-202, NEW-369, NEW-370, NEW-383, NEW-384, NEW-385</t>
   </si>
   <si>
     <t>25</t>
@@ -3456,13 +3744,10 @@
     <t>30</t>
   </si>
   <si>
-    <t>Logging &amp; Monitoring</t>
-  </si>
-  <si>
     <t>Audit integrity, alerts, events</t>
   </si>
   <si>
-    <t>SEC-09, NEW-322</t>
+    <t>SEC-09, NEW-322, NEW-380</t>
   </si>
   <si>
     <t>FORTLESS   /   COMMIT &amp; AUDIT HISTORY</t>
@@ -3667,6 +3952,15 @@
   </si>
   <si>
     <t>MFA, workspace selection, DNS routes, attachments and backup tooling read in source; NEW-368 reproduced locally. No implementation code changed.</t>
+  </si>
+  <si>
+    <t>2026-10-19 08:00</t>
+  </si>
+  <si>
+    <t>Independent audit batch 4: staff admin, sessions, DNS records, file manager, AI endpoints, sharing (NEW-376..NEW-387)</t>
+  </si>
+  <si>
+    <t>Staff routes, session lifecycle, DNS record paths, file manager, AI adapter and service sharing read in source. No implementation code changed.</t>
   </si>
   <si>
     <t>FORTLESS   /   IMMUTABLE STATUS HISTORY</t>
@@ -4931,7 +5225,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:S123"/>
+  <dimension ref="A1:S135"/>
   <sheetFormatPr defaultRowHeight="0" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" customHeight="1"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
@@ -11910,6 +12204,714 @@
       </c>
       <c r="S123" t="s">
         <v>996</v>
+      </c>
+    </row>
+    <row r="124" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>997</v>
+      </c>
+      <c r="B124" t="s">
+        <v>61</v>
+      </c>
+      <c r="C124" t="s">
+        <v>62</v>
+      </c>
+      <c r="D124" t="s">
+        <v>24</v>
+      </c>
+      <c r="E124" t="s">
+        <v>998</v>
+      </c>
+      <c r="F124" t="s">
+        <v>112</v>
+      </c>
+      <c r="G124" t="s">
+        <v>27</v>
+      </c>
+      <c r="H124" t="s">
+        <v>27</v>
+      </c>
+      <c r="I124" t="s">
+        <v>999</v>
+      </c>
+      <c r="J124" t="s">
+        <v>999</v>
+      </c>
+      <c r="K124" t="s">
+        <v>1000</v>
+      </c>
+      <c r="L124" t="s">
+        <v>1001</v>
+      </c>
+      <c r="M124" t="s">
+        <v>1002</v>
+      </c>
+      <c r="N124" t="s">
+        <v>1003</v>
+      </c>
+      <c r="O124" t="s">
+        <v>1004</v>
+      </c>
+      <c r="P124" t="s">
+        <v>747</v>
+      </c>
+      <c r="Q124" t="s">
+        <v>924</v>
+      </c>
+      <c r="R124" t="s">
+        <v>36</v>
+      </c>
+      <c r="S124" t="s">
+        <v>1005</v>
+      </c>
+    </row>
+    <row r="125" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>1006</v>
+      </c>
+      <c r="B125" t="s">
+        <v>308</v>
+      </c>
+      <c r="C125" t="s">
+        <v>309</v>
+      </c>
+      <c r="D125" t="s">
+        <v>959</v>
+      </c>
+      <c r="E125" t="s">
+        <v>1007</v>
+      </c>
+      <c r="F125" t="s">
+        <v>112</v>
+      </c>
+      <c r="G125" t="s">
+        <v>27</v>
+      </c>
+      <c r="H125" t="s">
+        <v>27</v>
+      </c>
+      <c r="I125" t="s">
+        <v>999</v>
+      </c>
+      <c r="J125" t="s">
+        <v>999</v>
+      </c>
+      <c r="K125" t="s">
+        <v>1008</v>
+      </c>
+      <c r="L125" t="s">
+        <v>1009</v>
+      </c>
+      <c r="M125" t="s">
+        <v>1010</v>
+      </c>
+      <c r="N125" t="s">
+        <v>1011</v>
+      </c>
+      <c r="O125" t="s">
+        <v>1012</v>
+      </c>
+      <c r="P125" t="s">
+        <v>747</v>
+      </c>
+      <c r="Q125" t="s">
+        <v>924</v>
+      </c>
+      <c r="R125" t="s">
+        <v>36</v>
+      </c>
+      <c r="S125" t="s">
+        <v>1013</v>
+      </c>
+    </row>
+    <row r="126" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>1014</v>
+      </c>
+      <c r="B126" t="s">
+        <v>308</v>
+      </c>
+      <c r="C126" t="s">
+        <v>62</v>
+      </c>
+      <c r="D126" t="s">
+        <v>24</v>
+      </c>
+      <c r="E126" t="s">
+        <v>1015</v>
+      </c>
+      <c r="F126" t="s">
+        <v>112</v>
+      </c>
+      <c r="G126" t="s">
+        <v>27</v>
+      </c>
+      <c r="H126" t="s">
+        <v>27</v>
+      </c>
+      <c r="I126" t="s">
+        <v>999</v>
+      </c>
+      <c r="J126" t="s">
+        <v>999</v>
+      </c>
+      <c r="K126" t="s">
+        <v>1016</v>
+      </c>
+      <c r="L126" t="s">
+        <v>1017</v>
+      </c>
+      <c r="M126" t="s">
+        <v>1018</v>
+      </c>
+      <c r="N126" t="s">
+        <v>1019</v>
+      </c>
+      <c r="O126" t="s">
+        <v>1020</v>
+      </c>
+      <c r="P126" t="s">
+        <v>747</v>
+      </c>
+      <c r="Q126" t="s">
+        <v>924</v>
+      </c>
+      <c r="R126" t="s">
+        <v>36</v>
+      </c>
+      <c r="S126" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="127" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>1021</v>
+      </c>
+      <c r="B127" t="s">
+        <v>308</v>
+      </c>
+      <c r="C127" t="s">
+        <v>309</v>
+      </c>
+      <c r="D127" t="s">
+        <v>24</v>
+      </c>
+      <c r="E127" t="s">
+        <v>1022</v>
+      </c>
+      <c r="F127" t="s">
+        <v>453</v>
+      </c>
+      <c r="G127" t="s">
+        <v>27</v>
+      </c>
+      <c r="H127" t="s">
+        <v>27</v>
+      </c>
+      <c r="I127" t="s">
+        <v>999</v>
+      </c>
+      <c r="J127" t="s">
+        <v>999</v>
+      </c>
+      <c r="K127" t="s">
+        <v>1023</v>
+      </c>
+      <c r="L127" t="s">
+        <v>1024</v>
+      </c>
+      <c r="M127" t="s">
+        <v>1025</v>
+      </c>
+      <c r="N127" t="s">
+        <v>1026</v>
+      </c>
+      <c r="O127" t="s">
+        <v>1027</v>
+      </c>
+      <c r="P127" t="s">
+        <v>747</v>
+      </c>
+      <c r="Q127" t="s">
+        <v>924</v>
+      </c>
+      <c r="R127" t="s">
+        <v>36</v>
+      </c>
+      <c r="S127" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="128" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>1029</v>
+      </c>
+      <c r="B128" t="s">
+        <v>308</v>
+      </c>
+      <c r="C128" t="s">
+        <v>309</v>
+      </c>
+      <c r="D128" t="s">
+        <v>1030</v>
+      </c>
+      <c r="E128" t="s">
+        <v>1031</v>
+      </c>
+      <c r="F128" t="s">
+        <v>112</v>
+      </c>
+      <c r="G128" t="s">
+        <v>27</v>
+      </c>
+      <c r="H128" t="s">
+        <v>27</v>
+      </c>
+      <c r="I128" t="s">
+        <v>999</v>
+      </c>
+      <c r="J128" t="s">
+        <v>999</v>
+      </c>
+      <c r="K128" t="s">
+        <v>1032</v>
+      </c>
+      <c r="L128" t="s">
+        <v>1033</v>
+      </c>
+      <c r="M128" t="s">
+        <v>1034</v>
+      </c>
+      <c r="N128" t="s">
+        <v>1035</v>
+      </c>
+      <c r="O128" t="s">
+        <v>1036</v>
+      </c>
+      <c r="P128" t="s">
+        <v>747</v>
+      </c>
+      <c r="Q128" t="s">
+        <v>924</v>
+      </c>
+      <c r="R128" t="s">
+        <v>36</v>
+      </c>
+      <c r="S128" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="129" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>1037</v>
+      </c>
+      <c r="B129" t="s">
+        <v>308</v>
+      </c>
+      <c r="C129" t="s">
+        <v>62</v>
+      </c>
+      <c r="D129" t="s">
+        <v>959</v>
+      </c>
+      <c r="E129" t="s">
+        <v>1038</v>
+      </c>
+      <c r="F129" t="s">
+        <v>112</v>
+      </c>
+      <c r="G129" t="s">
+        <v>27</v>
+      </c>
+      <c r="H129" t="s">
+        <v>27</v>
+      </c>
+      <c r="I129" t="s">
+        <v>999</v>
+      </c>
+      <c r="J129" t="s">
+        <v>999</v>
+      </c>
+      <c r="K129" t="s">
+        <v>1039</v>
+      </c>
+      <c r="L129" t="s">
+        <v>1040</v>
+      </c>
+      <c r="M129" t="s">
+        <v>1041</v>
+      </c>
+      <c r="N129" t="s">
+        <v>1042</v>
+      </c>
+      <c r="O129" t="s">
+        <v>1043</v>
+      </c>
+      <c r="P129" t="s">
+        <v>747</v>
+      </c>
+      <c r="Q129" t="s">
+        <v>924</v>
+      </c>
+      <c r="R129" t="s">
+        <v>36</v>
+      </c>
+      <c r="S129" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="130" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>1044</v>
+      </c>
+      <c r="B130" t="s">
+        <v>308</v>
+      </c>
+      <c r="C130" t="s">
+        <v>309</v>
+      </c>
+      <c r="D130" t="s">
+        <v>959</v>
+      </c>
+      <c r="E130" t="s">
+        <v>1045</v>
+      </c>
+      <c r="F130" t="s">
+        <v>112</v>
+      </c>
+      <c r="G130" t="s">
+        <v>27</v>
+      </c>
+      <c r="H130" t="s">
+        <v>27</v>
+      </c>
+      <c r="I130" t="s">
+        <v>999</v>
+      </c>
+      <c r="J130" t="s">
+        <v>999</v>
+      </c>
+      <c r="K130" t="s">
+        <v>1046</v>
+      </c>
+      <c r="L130" t="s">
+        <v>1047</v>
+      </c>
+      <c r="M130" t="s">
+        <v>1048</v>
+      </c>
+      <c r="N130" t="s">
+        <v>1049</v>
+      </c>
+      <c r="O130" t="s">
+        <v>1050</v>
+      </c>
+      <c r="P130" t="s">
+        <v>747</v>
+      </c>
+      <c r="Q130" t="s">
+        <v>924</v>
+      </c>
+      <c r="R130" t="s">
+        <v>36</v>
+      </c>
+      <c r="S130" t="s">
+        <v>1051</v>
+      </c>
+    </row>
+    <row r="131" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>1052</v>
+      </c>
+      <c r="B131" t="s">
+        <v>308</v>
+      </c>
+      <c r="C131" t="s">
+        <v>309</v>
+      </c>
+      <c r="D131" t="s">
+        <v>1053</v>
+      </c>
+      <c r="E131" t="s">
+        <v>1054</v>
+      </c>
+      <c r="F131" t="s">
+        <v>112</v>
+      </c>
+      <c r="G131" t="s">
+        <v>27</v>
+      </c>
+      <c r="H131" t="s">
+        <v>27</v>
+      </c>
+      <c r="I131" t="s">
+        <v>999</v>
+      </c>
+      <c r="J131" t="s">
+        <v>999</v>
+      </c>
+      <c r="K131" t="s">
+        <v>1055</v>
+      </c>
+      <c r="L131" t="s">
+        <v>1056</v>
+      </c>
+      <c r="M131" t="s">
+        <v>1057</v>
+      </c>
+      <c r="N131" t="s">
+        <v>1058</v>
+      </c>
+      <c r="O131" t="s">
+        <v>1059</v>
+      </c>
+      <c r="P131" t="s">
+        <v>747</v>
+      </c>
+      <c r="Q131" t="s">
+        <v>924</v>
+      </c>
+      <c r="R131" t="s">
+        <v>36</v>
+      </c>
+      <c r="S131" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="132" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>1060</v>
+      </c>
+      <c r="B132" t="s">
+        <v>308</v>
+      </c>
+      <c r="C132" t="s">
+        <v>309</v>
+      </c>
+      <c r="D132" t="s">
+        <v>959</v>
+      </c>
+      <c r="E132" t="s">
+        <v>1061</v>
+      </c>
+      <c r="F132" t="s">
+        <v>112</v>
+      </c>
+      <c r="G132" t="s">
+        <v>27</v>
+      </c>
+      <c r="H132" t="s">
+        <v>27</v>
+      </c>
+      <c r="I132" t="s">
+        <v>999</v>
+      </c>
+      <c r="J132" t="s">
+        <v>999</v>
+      </c>
+      <c r="K132" t="s">
+        <v>1062</v>
+      </c>
+      <c r="L132" t="s">
+        <v>1063</v>
+      </c>
+      <c r="M132" t="s">
+        <v>1064</v>
+      </c>
+      <c r="N132" t="s">
+        <v>1065</v>
+      </c>
+      <c r="O132" t="s">
+        <v>1066</v>
+      </c>
+      <c r="P132" t="s">
+        <v>747</v>
+      </c>
+      <c r="Q132" t="s">
+        <v>924</v>
+      </c>
+      <c r="R132" t="s">
+        <v>36</v>
+      </c>
+      <c r="S132" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="133" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>1067</v>
+      </c>
+      <c r="B133" t="s">
+        <v>61</v>
+      </c>
+      <c r="C133" t="s">
+        <v>23</v>
+      </c>
+      <c r="D133" t="s">
+        <v>247</v>
+      </c>
+      <c r="E133" t="s">
+        <v>1068</v>
+      </c>
+      <c r="F133" t="s">
+        <v>95</v>
+      </c>
+      <c r="G133" t="s">
+        <v>27</v>
+      </c>
+      <c r="H133" t="s">
+        <v>27</v>
+      </c>
+      <c r="I133" t="s">
+        <v>999</v>
+      </c>
+      <c r="J133" t="s">
+        <v>999</v>
+      </c>
+      <c r="K133" t="s">
+        <v>1069</v>
+      </c>
+      <c r="L133" t="s">
+        <v>1070</v>
+      </c>
+      <c r="M133" t="s">
+        <v>1071</v>
+      </c>
+      <c r="N133" t="s">
+        <v>1072</v>
+      </c>
+      <c r="O133" t="s">
+        <v>1073</v>
+      </c>
+      <c r="P133" t="s">
+        <v>747</v>
+      </c>
+      <c r="Q133" t="s">
+        <v>924</v>
+      </c>
+      <c r="R133" t="s">
+        <v>36</v>
+      </c>
+      <c r="S133" t="s">
+        <v>1074</v>
+      </c>
+    </row>
+    <row r="134" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>1075</v>
+      </c>
+      <c r="B134" t="s">
+        <v>308</v>
+      </c>
+      <c r="C134" t="s">
+        <v>62</v>
+      </c>
+      <c r="D134" t="s">
+        <v>1076</v>
+      </c>
+      <c r="E134" t="s">
+        <v>1077</v>
+      </c>
+      <c r="F134" t="s">
+        <v>112</v>
+      </c>
+      <c r="G134" t="s">
+        <v>27</v>
+      </c>
+      <c r="H134" t="s">
+        <v>27</v>
+      </c>
+      <c r="I134" t="s">
+        <v>999</v>
+      </c>
+      <c r="J134" t="s">
+        <v>999</v>
+      </c>
+      <c r="K134" t="s">
+        <v>1078</v>
+      </c>
+      <c r="L134" t="s">
+        <v>1079</v>
+      </c>
+      <c r="M134" t="s">
+        <v>1080</v>
+      </c>
+      <c r="N134" t="s">
+        <v>1081</v>
+      </c>
+      <c r="O134" t="s">
+        <v>1082</v>
+      </c>
+      <c r="P134" t="s">
+        <v>747</v>
+      </c>
+      <c r="Q134" t="s">
+        <v>924</v>
+      </c>
+      <c r="R134" t="s">
+        <v>36</v>
+      </c>
+      <c r="S134" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="135" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>1084</v>
+      </c>
+      <c r="B135" t="s">
+        <v>308</v>
+      </c>
+      <c r="C135" t="s">
+        <v>62</v>
+      </c>
+      <c r="D135" t="s">
+        <v>630</v>
+      </c>
+      <c r="E135" t="s">
+        <v>1085</v>
+      </c>
+      <c r="F135" t="s">
+        <v>95</v>
+      </c>
+      <c r="G135" t="s">
+        <v>27</v>
+      </c>
+      <c r="H135" t="s">
+        <v>27</v>
+      </c>
+      <c r="I135" t="s">
+        <v>999</v>
+      </c>
+      <c r="J135" t="s">
+        <v>999</v>
+      </c>
+      <c r="K135" t="s">
+        <v>1086</v>
+      </c>
+      <c r="L135" t="s">
+        <v>1087</v>
+      </c>
+      <c r="M135" t="s">
+        <v>1088</v>
+      </c>
+      <c r="N135" t="s">
+        <v>1089</v>
+      </c>
+      <c r="O135" t="s">
+        <v>1090</v>
+      </c>
+      <c r="P135" t="s">
+        <v>747</v>
+      </c>
+      <c r="Q135" t="s">
+        <v>924</v>
+      </c>
+      <c r="R135" t="s">
+        <v>36</v>
+      </c>
+      <c r="S135" t="s">
+        <v>1091</v>
       </c>
     </row>
   </sheetData>
@@ -11923,48 +12925,48 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>997</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>998</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>999</v>
+        <v>1094</v>
       </c>
       <c r="C4" t="s">
-        <v>1000</v>
+        <v>1095</v>
       </c>
       <c r="E4" t="s">
-        <v>1001</v>
+        <v>1096</v>
       </c>
       <c r="G4" t="s">
-        <v>1002</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1003</v>
+        <v>1098</v>
       </c>
       <c r="C5" t="s">
-        <v>1004</v>
+        <v>1099</v>
       </c>
       <c r="E5" t="s">
-        <v>1005</v>
+        <v>1100</v>
       </c>
       <c r="G5" t="s">
-        <v>1006</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>1007</v>
+        <v>1102</v>
       </c>
       <c r="F9" t="s">
-        <v>1008</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -11972,16 +12974,16 @@
         <v>112</v>
       </c>
       <c r="B10" t="s">
-        <v>1004</v>
+        <v>1099</v>
       </c>
       <c r="C10" t="s">
         <v>3</v>
       </c>
       <c r="D10" t="s">
-        <v>1009</v>
+        <v>1104</v>
       </c>
       <c r="F10" t="s">
-        <v>1010</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -11989,13 +12991,13 @@
         <v>86</v>
       </c>
       <c r="B11" t="s">
-        <v>1011</v>
+        <v>1106</v>
       </c>
       <c r="C11" t="s">
         <v>22</v>
       </c>
       <c r="D11" t="s">
-        <v>1004</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -12003,13 +13005,13 @@
         <v>95</v>
       </c>
       <c r="B12" t="s">
-        <v>1012</v>
+        <v>1108</v>
       </c>
       <c r="C12" t="s">
         <v>61</v>
       </c>
       <c r="D12" t="s">
-        <v>1013</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -12017,13 +13019,13 @@
         <v>453</v>
       </c>
       <c r="B13" t="s">
-        <v>1014</v>
+        <v>1110</v>
       </c>
       <c r="C13" t="s">
         <v>308</v>
       </c>
       <c r="D13" t="s">
-        <v>1015</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
@@ -12031,42 +13033,42 @@
         <v>26</v>
       </c>
       <c r="B14" t="s">
-        <v>1005</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>1016</v>
+        <v>1112</v>
       </c>
       <c r="B15" t="s">
-        <v>1006</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>1017</v>
+        <v>1113</v>
       </c>
       <c r="B16" t="s">
-        <v>1006</v>
+        <v>1101</v>
       </c>
       <c r="F16" t="s">
-        <v>1018</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>1019</v>
+        <v>1115</v>
       </c>
       <c r="B17" t="s">
-        <v>1006</v>
+        <v>1101</v>
       </c>
       <c r="F17" t="s">
-        <v>1020</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>1021</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
@@ -12074,7 +13076,7 @@
         <v>112</v>
       </c>
       <c r="C22" t="s">
-        <v>1022</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
@@ -12082,7 +13084,7 @@
         <v>86</v>
       </c>
       <c r="C23" t="s">
-        <v>1023</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
@@ -12090,7 +13092,7 @@
         <v>26</v>
       </c>
       <c r="C24" t="s">
-        <v>1024</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
@@ -12098,7 +13100,7 @@
         <v>95</v>
       </c>
       <c r="C25" t="s">
-        <v>1025</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
@@ -12106,31 +13108,31 @@
         <v>453</v>
       </c>
       <c r="C26" t="s">
-        <v>1026</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>1016</v>
+        <v>1112</v>
       </c>
       <c r="C27" t="s">
-        <v>1027</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>1017</v>
+        <v>1113</v>
       </c>
       <c r="C28" t="s">
-        <v>1028</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>1019</v>
+        <v>1115</v>
       </c>
       <c r="C29" t="s">
-        <v>1029</v>
+        <v>1125</v>
       </c>
     </row>
   </sheetData>
@@ -12144,7 +13146,7 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>1030</v>
+        <v>1126</v>
       </c>
       <c r="B1"/>
       <c r="C1"/>
@@ -12153,7 +13155,7 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1031</v>
+        <v>1127</v>
       </c>
       <c r="B2"/>
       <c r="C2"/>
@@ -12162,529 +13164,529 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>1032</v>
+        <v>1128</v>
       </c>
       <c r="B3" t="s">
         <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>1033</v>
+        <v>1129</v>
       </c>
       <c r="D3" t="s">
-        <v>1034</v>
+        <v>1130</v>
       </c>
       <c r="E3" t="s">
-        <v>1035</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1036</v>
+        <v>1132</v>
       </c>
       <c r="B4" t="s">
-        <v>1037</v>
+        <v>1133</v>
       </c>
       <c r="C4" t="s">
-        <v>1038</v>
+        <v>1134</v>
       </c>
       <c r="D4" t="s">
-        <v>1039</v>
+        <v>1135</v>
       </c>
       <c r="E4" t="s">
-        <v>1040</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1041</v>
+        <v>1137</v>
       </c>
       <c r="B5" t="s">
-        <v>1042</v>
+        <v>1138</v>
       </c>
       <c r="C5" t="s">
-        <v>1043</v>
+        <v>1139</v>
       </c>
       <c r="D5" t="s">
-        <v>1044</v>
+        <v>1140</v>
       </c>
       <c r="E5" t="s">
-        <v>1040</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>1045</v>
+        <v>1141</v>
       </c>
       <c r="B6" t="s">
-        <v>1046</v>
+        <v>1142</v>
       </c>
       <c r="C6" t="s">
-        <v>1047</v>
+        <v>1143</v>
       </c>
       <c r="D6" t="s">
-        <v>1048</v>
+        <v>1144</v>
       </c>
       <c r="E6" t="s">
-        <v>1040</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>1049</v>
+        <v>1145</v>
       </c>
       <c r="B7" t="s">
-        <v>1050</v>
+        <v>1146</v>
       </c>
       <c r="C7" t="s">
-        <v>1051</v>
+        <v>1147</v>
       </c>
       <c r="D7" t="s">
-        <v>1052</v>
+        <v>1148</v>
       </c>
       <c r="E7" t="s">
-        <v>1040</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>1053</v>
+        <v>1149</v>
       </c>
       <c r="B8" t="s">
-        <v>1054</v>
+        <v>1150</v>
       </c>
       <c r="C8" t="s">
-        <v>1055</v>
+        <v>1151</v>
       </c>
       <c r="D8" t="s">
-        <v>1056</v>
+        <v>1152</v>
       </c>
       <c r="E8" t="s">
-        <v>1040</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>1057</v>
+        <v>1153</v>
       </c>
       <c r="B9" t="s">
-        <v>1058</v>
+        <v>1154</v>
       </c>
       <c r="C9" t="s">
-        <v>1059</v>
+        <v>1155</v>
       </c>
       <c r="D9" t="s">
-        <v>1060</v>
+        <v>1156</v>
       </c>
       <c r="E9" t="s">
-        <v>1040</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>1061</v>
+        <v>1157</v>
       </c>
       <c r="B10" t="s">
-        <v>1062</v>
+        <v>1158</v>
       </c>
       <c r="C10" t="s">
-        <v>1063</v>
+        <v>1159</v>
       </c>
       <c r="D10" t="s">
-        <v>1064</v>
+        <v>1160</v>
       </c>
       <c r="E10" t="s">
-        <v>1040</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>1065</v>
+        <v>1161</v>
       </c>
       <c r="B11" t="s">
-        <v>1066</v>
+        <v>1162</v>
       </c>
       <c r="C11" t="s">
-        <v>1067</v>
+        <v>1163</v>
       </c>
       <c r="D11" t="s">
         <v>93</v>
       </c>
       <c r="E11" t="s">
-        <v>1068</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>1069</v>
+        <v>1165</v>
       </c>
       <c r="B12" t="s">
-        <v>1070</v>
+        <v>1166</v>
       </c>
       <c r="C12" t="s">
-        <v>1071</v>
+        <v>1167</v>
       </c>
       <c r="D12" t="s">
-        <v>1072</v>
+        <v>1168</v>
       </c>
       <c r="E12" t="s">
-        <v>1040</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>1073</v>
+        <v>1169</v>
       </c>
       <c r="B13" t="s">
-        <v>1074</v>
+        <v>1170</v>
       </c>
       <c r="C13" t="s">
-        <v>1075</v>
+        <v>1171</v>
       </c>
       <c r="D13" t="s">
         <v>403</v>
       </c>
       <c r="E13" t="s">
-        <v>1068</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>1076</v>
+        <v>1172</v>
       </c>
       <c r="B14" t="s">
-        <v>1077</v>
+        <v>1173</v>
       </c>
       <c r="C14" t="s">
-        <v>1078</v>
+        <v>1174</v>
       </c>
       <c r="D14" t="s">
-        <v>1079</v>
+        <v>1175</v>
       </c>
       <c r="E14" t="s">
-        <v>1040</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>1080</v>
+        <v>1176</v>
       </c>
       <c r="B15" t="s">
-        <v>1081</v>
+        <v>1177</v>
       </c>
       <c r="C15" t="s">
-        <v>1082</v>
+        <v>1178</v>
       </c>
       <c r="D15" t="s">
-        <v>1083</v>
+        <v>1179</v>
       </c>
       <c r="E15" t="s">
-        <v>1040</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>1084</v>
+        <v>1180</v>
       </c>
       <c r="B16" t="s">
-        <v>1085</v>
+        <v>1181</v>
       </c>
       <c r="C16" t="s">
-        <v>1086</v>
+        <v>1182</v>
       </c>
       <c r="D16" t="s">
-        <v>1087</v>
+        <v>1183</v>
       </c>
       <c r="E16" t="s">
-        <v>1040</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>1015</v>
+        <v>1184</v>
       </c>
       <c r="B17" t="s">
         <v>435</v>
       </c>
       <c r="C17" t="s">
-        <v>1088</v>
+        <v>1185</v>
       </c>
       <c r="D17" t="s">
-        <v>1089</v>
+        <v>1186</v>
       </c>
       <c r="E17" t="s">
-        <v>1068</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>1011</v>
+        <v>1106</v>
       </c>
       <c r="B18" t="s">
-        <v>1090</v>
+        <v>1187</v>
       </c>
       <c r="C18" t="s">
-        <v>1091</v>
+        <v>1188</v>
       </c>
       <c r="D18" t="s">
         <v>316</v>
       </c>
       <c r="E18" t="s">
-        <v>1068</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>1092</v>
+        <v>1189</v>
       </c>
       <c r="B19" t="s">
-        <v>1093</v>
+        <v>1190</v>
       </c>
       <c r="C19" t="s">
-        <v>1094</v>
+        <v>1191</v>
       </c>
       <c r="D19" t="s">
-        <v>1095</v>
+        <v>1192</v>
       </c>
       <c r="E19" t="s">
-        <v>1068</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>1096</v>
+        <v>1193</v>
       </c>
       <c r="B20" t="s">
-        <v>1097</v>
+        <v>1194</v>
       </c>
       <c r="C20" t="s">
-        <v>1098</v>
+        <v>1195</v>
       </c>
       <c r="D20" t="s">
         <v>475</v>
       </c>
       <c r="E20" t="s">
-        <v>1040</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>1099</v>
+        <v>1196</v>
       </c>
       <c r="B21" t="s">
-        <v>1100</v>
+        <v>1197</v>
       </c>
       <c r="C21" t="s">
-        <v>1101</v>
+        <v>1198</v>
       </c>
       <c r="D21" t="s">
         <v>213</v>
       </c>
       <c r="E21" t="s">
-        <v>1068</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>1102</v>
+        <v>1199</v>
       </c>
       <c r="B22" t="s">
-        <v>1103</v>
+        <v>1200</v>
       </c>
       <c r="C22" t="s">
-        <v>1104</v>
+        <v>1201</v>
       </c>
       <c r="D22" t="s">
-        <v>1105</v>
+        <v>1202</v>
       </c>
       <c r="E22" t="s">
-        <v>1040</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>1106</v>
+        <v>1203</v>
       </c>
       <c r="B23" t="s">
-        <v>1107</v>
+        <v>1204</v>
       </c>
       <c r="C23" t="s">
-        <v>1108</v>
+        <v>1205</v>
       </c>
       <c r="D23" t="s">
-        <v>1109</v>
+        <v>1206</v>
       </c>
       <c r="E23" t="s">
-        <v>1040</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>1110</v>
+        <v>1207</v>
       </c>
       <c r="B24" t="s">
         <v>214</v>
       </c>
       <c r="C24" t="s">
-        <v>1111</v>
+        <v>1208</v>
       </c>
       <c r="D24" t="s">
-        <v>1112</v>
+        <v>1209</v>
       </c>
       <c r="E24" t="s">
-        <v>1040</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>1113</v>
+        <v>1210</v>
       </c>
       <c r="B25" t="s">
-        <v>1114</v>
+        <v>1211</v>
       </c>
       <c r="C25" t="s">
-        <v>1115</v>
+        <v>1212</v>
       </c>
       <c r="D25" t="s">
-        <v>1116</v>
+        <v>1213</v>
       </c>
       <c r="E25" t="s">
-        <v>1068</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>1117</v>
+        <v>1214</v>
       </c>
       <c r="B26" t="s">
-        <v>1118</v>
+        <v>1215</v>
       </c>
       <c r="C26" t="s">
-        <v>1119</v>
+        <v>1216</v>
       </c>
       <c r="D26" t="s">
-        <v>1120</v>
+        <v>1217</v>
       </c>
       <c r="E26" t="s">
-        <v>1068</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>1121</v>
+        <v>1111</v>
       </c>
       <c r="B27" t="s">
-        <v>1122</v>
+        <v>1218</v>
       </c>
       <c r="C27" t="s">
-        <v>1123</v>
+        <v>1219</v>
       </c>
       <c r="D27" t="s">
-        <v>1124</v>
+        <v>1220</v>
       </c>
       <c r="E27" t="s">
-        <v>1040</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>1125</v>
+        <v>1221</v>
       </c>
       <c r="B28" t="s">
-        <v>1126</v>
+        <v>1222</v>
       </c>
       <c r="C28" t="s">
-        <v>1127</v>
+        <v>1223</v>
       </c>
       <c r="D28" t="s">
-        <v>1128</v>
+        <v>1224</v>
       </c>
       <c r="E28" t="s">
-        <v>1040</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>1129</v>
+        <v>1225</v>
       </c>
       <c r="B29" t="s">
         <v>822</v>
       </c>
       <c r="C29" t="s">
-        <v>1130</v>
+        <v>1226</v>
       </c>
       <c r="D29" t="s">
-        <v>1131</v>
+        <v>1227</v>
       </c>
       <c r="E29" t="s">
-        <v>1040</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>1132</v>
+        <v>1228</v>
       </c>
       <c r="B30" t="s">
-        <v>1133</v>
+        <v>1229</v>
       </c>
       <c r="C30" t="s">
-        <v>1134</v>
+        <v>1230</v>
       </c>
       <c r="D30" t="s">
-        <v>1135</v>
+        <v>1231</v>
       </c>
       <c r="E30" t="s">
-        <v>1068</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>1136</v>
+        <v>1232</v>
       </c>
       <c r="B31" t="s">
-        <v>1137</v>
+        <v>1233</v>
       </c>
       <c r="C31" t="s">
-        <v>1138</v>
+        <v>1234</v>
       </c>
       <c r="D31" t="s">
         <v>93</v>
       </c>
       <c r="E31" t="s">
-        <v>1139</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>1140</v>
+        <v>1236</v>
       </c>
       <c r="B32" t="s">
-        <v>1141</v>
+        <v>1237</v>
       </c>
       <c r="C32" t="s">
-        <v>1142</v>
+        <v>1238</v>
       </c>
       <c r="D32" t="s">
-        <v>1143</v>
+        <v>1239</v>
       </c>
       <c r="E32" t="s">
-        <v>1040</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>1144</v>
+        <v>1240</v>
       </c>
       <c r="B33" t="s">
-        <v>1145</v>
+        <v>1030</v>
       </c>
       <c r="C33" t="s">
-        <v>1146</v>
+        <v>1241</v>
       </c>
       <c r="D33" t="s">
-        <v>1147</v>
+        <v>1242</v>
       </c>
       <c r="E33" t="s">
-        <v>1068</v>
+        <v>1164</v>
       </c>
     </row>
   </sheetData>
@@ -12698,157 +13700,157 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr defaultRowHeight="0" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" customHeight="1"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>1148</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1149</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>1150</v>
+        <v>1245</v>
       </c>
       <c r="B3" t="s">
-        <v>1151</v>
+        <v>1246</v>
       </c>
       <c r="C3" t="s">
-        <v>1152</v>
+        <v>1247</v>
       </c>
       <c r="D3" t="s">
-        <v>1153</v>
+        <v>1248</v>
       </c>
       <c r="E3" t="s">
-        <v>1154</v>
+        <v>1249</v>
       </c>
       <c r="F3" t="s">
-        <v>1155</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1156</v>
+        <v>1251</v>
       </c>
       <c r="B4" t="s">
         <v>28</v>
       </c>
       <c r="C4" t="s">
-        <v>1157</v>
+        <v>1252</v>
       </c>
       <c r="D4" t="s">
-        <v>1158</v>
+        <v>1253</v>
       </c>
       <c r="E4" t="s">
-        <v>1159</v>
+        <v>1254</v>
       </c>
       <c r="F4" t="s">
-        <v>1160</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1161</v>
+        <v>1256</v>
       </c>
       <c r="B5" t="s">
-        <v>1162</v>
+        <v>1257</v>
       </c>
       <c r="C5" t="s">
-        <v>1163</v>
+        <v>1258</v>
       </c>
       <c r="D5" t="s">
-        <v>1164</v>
+        <v>1259</v>
       </c>
       <c r="E5" t="s">
-        <v>1165</v>
+        <v>1260</v>
       </c>
       <c r="F5" t="s">
-        <v>1166</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>1167</v>
+        <v>1262</v>
       </c>
       <c r="B6" t="s">
-        <v>1168</v>
+        <v>1263</v>
       </c>
       <c r="C6" t="s">
-        <v>1169</v>
+        <v>1264</v>
       </c>
       <c r="D6" t="s">
-        <v>1170</v>
+        <v>1265</v>
       </c>
       <c r="E6" t="s">
-        <v>1171</v>
+        <v>1266</v>
       </c>
       <c r="F6" t="s">
-        <v>1172</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>1173</v>
+        <v>1268</v>
       </c>
       <c r="B7" t="s">
-        <v>1174</v>
+        <v>1269</v>
       </c>
       <c r="C7" t="s">
-        <v>1175</v>
+        <v>1270</v>
       </c>
       <c r="D7" t="s">
-        <v>1176</v>
+        <v>1271</v>
       </c>
       <c r="E7" t="s">
-        <v>1171</v>
+        <v>1266</v>
       </c>
       <c r="F7" t="s">
-        <v>1177</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>1178</v>
+        <v>1273</v>
       </c>
       <c r="B8" t="s">
-        <v>1179</v>
+        <v>1274</v>
       </c>
       <c r="C8" t="s">
-        <v>1180</v>
+        <v>1275</v>
       </c>
       <c r="D8" t="s">
-        <v>1181</v>
+        <v>1276</v>
       </c>
       <c r="E8" t="s">
-        <v>1171</v>
+        <v>1266</v>
       </c>
       <c r="F8" t="s">
-        <v>1177</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>1182</v>
+        <v>1277</v>
       </c>
       <c r="B9" t="s">
         <v>29</v>
       </c>
       <c r="C9" t="s">
-        <v>1183</v>
+        <v>1278</v>
       </c>
       <c r="D9" t="s">
-        <v>1184</v>
+        <v>1279</v>
       </c>
       <c r="E9" t="s">
-        <v>1159</v>
+        <v>1254</v>
       </c>
       <c r="F9" t="s">
-        <v>1185</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -12859,93 +13861,93 @@
         <v>29</v>
       </c>
       <c r="C10" t="s">
-        <v>1186</v>
+        <v>1281</v>
       </c>
       <c r="D10" t="s">
-        <v>1187</v>
+        <v>1282</v>
       </c>
       <c r="E10" t="s">
-        <v>1188</v>
+        <v>1283</v>
       </c>
       <c r="F10" t="s">
-        <v>1189</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>1190</v>
+        <v>1285</v>
       </c>
       <c r="B11" t="s">
         <v>55</v>
       </c>
       <c r="C11" t="s">
-        <v>1191</v>
+        <v>1286</v>
       </c>
       <c r="D11" t="s">
-        <v>1192</v>
+        <v>1287</v>
       </c>
       <c r="E11" t="s">
-        <v>1188</v>
+        <v>1283</v>
       </c>
       <c r="F11" t="s">
-        <v>1193</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>1194</v>
+        <v>1289</v>
       </c>
       <c r="B12" t="s">
         <v>161</v>
       </c>
       <c r="C12" t="s">
-        <v>1195</v>
+        <v>1290</v>
       </c>
       <c r="D12" t="s">
-        <v>1196</v>
+        <v>1291</v>
       </c>
       <c r="E12" t="s">
-        <v>1197</v>
+        <v>1292</v>
       </c>
       <c r="F12" t="s">
-        <v>1198</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>1199</v>
+        <v>1294</v>
       </c>
       <c r="B13" t="s">
-        <v>1200</v>
+        <v>1295</v>
       </c>
       <c r="C13" t="s">
-        <v>1201</v>
+        <v>1296</v>
       </c>
       <c r="D13" t="s">
-        <v>1202</v>
+        <v>1297</v>
       </c>
       <c r="E13" t="s">
-        <v>1203</v>
+        <v>1298</v>
       </c>
       <c r="F13" t="s">
-        <v>1204</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>1205</v>
+        <v>1300</v>
       </c>
       <c r="B14" t="s">
         <v>206</v>
       </c>
       <c r="C14" t="s">
-        <v>1206</v>
+        <v>1301</v>
       </c>
       <c r="D14" t="s">
-        <v>1207</v>
+        <v>1302</v>
       </c>
       <c r="E14" t="s">
-        <v>1208</v>
+        <v>1303</v>
       </c>
       <c r="F14" t="s">
         <v>748</v>
@@ -12953,19 +13955,19 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>1209</v>
+        <v>1304</v>
       </c>
       <c r="B15" t="s">
         <v>206</v>
       </c>
       <c r="C15" t="s">
-        <v>1210</v>
+        <v>1305</v>
       </c>
       <c r="D15" t="s">
-        <v>1211</v>
+        <v>1306</v>
       </c>
       <c r="E15" t="s">
-        <v>1212</v>
+        <v>1307</v>
       </c>
       <c r="F15" t="s">
         <v>748</v>
@@ -12973,21 +13975,41 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>1213</v>
+        <v>1308</v>
       </c>
       <c r="B16" t="s">
         <v>918</v>
       </c>
       <c r="C16" t="s">
-        <v>1214</v>
+        <v>1309</v>
       </c>
       <c r="D16" t="s">
-        <v>1215</v>
+        <v>1310</v>
       </c>
       <c r="E16" t="s">
-        <v>1212</v>
+        <v>1307</v>
       </c>
       <c r="F16" t="s">
+        <v>924</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>1311</v>
+      </c>
+      <c r="B17" t="s">
+        <v>999</v>
+      </c>
+      <c r="C17" t="s">
+        <v>1312</v>
+      </c>
+      <c r="D17" t="s">
+        <v>1313</v>
+      </c>
+      <c r="E17" t="s">
+        <v>1307</v>
+      </c>
+      <c r="F17" t="s">
         <v>924</v>
       </c>
     </row>
@@ -12997,40 +14019,40 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G139"/>
+  <dimension ref="A1:G151"/>
   <sheetFormatPr defaultRowHeight="0" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" customHeight="1"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>1216</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1217</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>1218</v>
+        <v>1316</v>
       </c>
       <c r="B3" t="s">
-        <v>1219</v>
+        <v>1317</v>
       </c>
       <c r="C3" t="s">
-        <v>1220</v>
+        <v>1318</v>
       </c>
       <c r="D3" t="s">
-        <v>1221</v>
+        <v>1319</v>
       </c>
       <c r="E3" t="s">
-        <v>1222</v>
+        <v>1320</v>
       </c>
       <c r="F3" t="s">
-        <v>1223</v>
+        <v>1321</v>
       </c>
       <c r="G3" t="s">
-        <v>1224</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -13050,10 +14072,10 @@
         <v>26</v>
       </c>
       <c r="F4" t="s">
-        <v>1225</v>
+        <v>1323</v>
       </c>
       <c r="G4" t="s">
-        <v>1226</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -13073,10 +14095,10 @@
         <v>26</v>
       </c>
       <c r="F5" t="s">
-        <v>1225</v>
+        <v>1323</v>
       </c>
       <c r="G5" t="s">
-        <v>1227</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -13096,10 +14118,10 @@
         <v>26</v>
       </c>
       <c r="F6" t="s">
-        <v>1225</v>
+        <v>1323</v>
       </c>
       <c r="G6" t="s">
-        <v>1228</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -13119,10 +14141,10 @@
         <v>86</v>
       </c>
       <c r="F7" t="s">
-        <v>1225</v>
+        <v>1323</v>
       </c>
       <c r="G7" t="s">
-        <v>1229</v>
+        <v>1327</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -13142,10 +14164,10 @@
         <v>26</v>
       </c>
       <c r="F8" t="s">
-        <v>1225</v>
+        <v>1323</v>
       </c>
       <c r="G8" t="s">
-        <v>1230</v>
+        <v>1328</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -13165,10 +14187,10 @@
         <v>26</v>
       </c>
       <c r="F9" t="s">
-        <v>1225</v>
+        <v>1323</v>
       </c>
       <c r="G9" t="s">
-        <v>1231</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -13188,10 +14210,10 @@
         <v>26</v>
       </c>
       <c r="F10" t="s">
-        <v>1225</v>
+        <v>1323</v>
       </c>
       <c r="G10" t="s">
-        <v>1232</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -13211,10 +14233,10 @@
         <v>86</v>
       </c>
       <c r="F11" t="s">
-        <v>1225</v>
+        <v>1323</v>
       </c>
       <c r="G11" t="s">
-        <v>1233</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -13234,10 +14256,10 @@
         <v>86</v>
       </c>
       <c r="F12" t="s">
-        <v>1225</v>
+        <v>1323</v>
       </c>
       <c r="G12" t="s">
-        <v>1234</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -13257,10 +14279,10 @@
         <v>26</v>
       </c>
       <c r="F13" t="s">
-        <v>1225</v>
+        <v>1323</v>
       </c>
       <c r="G13" t="s">
-        <v>1235</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -13280,10 +14302,10 @@
         <v>26</v>
       </c>
       <c r="F14" t="s">
-        <v>1236</v>
+        <v>1334</v>
       </c>
       <c r="G14" t="s">
-        <v>1237</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -13303,10 +14325,10 @@
         <v>26</v>
       </c>
       <c r="F15" t="s">
-        <v>1236</v>
+        <v>1334</v>
       </c>
       <c r="G15" t="s">
-        <v>1238</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -13326,10 +14348,10 @@
         <v>26</v>
       </c>
       <c r="F16" t="s">
-        <v>1236</v>
+        <v>1334</v>
       </c>
       <c r="G16" t="s">
-        <v>1239</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -13349,10 +14371,10 @@
         <v>26</v>
       </c>
       <c r="F17" t="s">
-        <v>1236</v>
+        <v>1334</v>
       </c>
       <c r="G17" t="s">
-        <v>1240</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -13372,10 +14394,10 @@
         <v>26</v>
       </c>
       <c r="F18" t="s">
-        <v>1236</v>
+        <v>1334</v>
       </c>
       <c r="G18" t="s">
-        <v>1241</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -13395,10 +14417,10 @@
         <v>26</v>
       </c>
       <c r="F19" t="s">
-        <v>1236</v>
+        <v>1334</v>
       </c>
       <c r="G19" t="s">
-        <v>1242</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -13418,10 +14440,10 @@
         <v>86</v>
       </c>
       <c r="F20" t="s">
-        <v>1236</v>
+        <v>1334</v>
       </c>
       <c r="G20" t="s">
-        <v>1243</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -13441,10 +14463,10 @@
         <v>86</v>
       </c>
       <c r="F21" t="s">
-        <v>1236</v>
+        <v>1334</v>
       </c>
       <c r="G21" t="s">
-        <v>1244</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
@@ -13464,10 +14486,10 @@
         <v>26</v>
       </c>
       <c r="F22" t="s">
-        <v>1236</v>
+        <v>1334</v>
       </c>
       <c r="G22" t="s">
-        <v>1245</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
@@ -13487,10 +14509,10 @@
         <v>86</v>
       </c>
       <c r="F23" t="s">
-        <v>1236</v>
+        <v>1334</v>
       </c>
       <c r="G23" t="s">
-        <v>1246</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -13510,10 +14532,10 @@
         <v>86</v>
       </c>
       <c r="F24" t="s">
-        <v>1236</v>
+        <v>1334</v>
       </c>
       <c r="G24" t="s">
-        <v>1247</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
@@ -13533,10 +14555,10 @@
         <v>86</v>
       </c>
       <c r="F25" t="s">
-        <v>1236</v>
+        <v>1334</v>
       </c>
       <c r="G25" t="s">
-        <v>1248</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
@@ -13556,10 +14578,10 @@
         <v>86</v>
       </c>
       <c r="F26" t="s">
-        <v>1236</v>
+        <v>1334</v>
       </c>
       <c r="G26" t="s">
-        <v>1249</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
@@ -13579,10 +14601,10 @@
         <v>26</v>
       </c>
       <c r="F27" t="s">
-        <v>1236</v>
+        <v>1334</v>
       </c>
       <c r="G27" t="s">
-        <v>1250</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
@@ -13602,10 +14624,10 @@
         <v>86</v>
       </c>
       <c r="F28" t="s">
-        <v>1236</v>
+        <v>1334</v>
       </c>
       <c r="G28" t="s">
-        <v>1251</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
@@ -13625,10 +14647,10 @@
         <v>86</v>
       </c>
       <c r="F29" t="s">
-        <v>1236</v>
+        <v>1334</v>
       </c>
       <c r="G29" t="s">
-        <v>1252</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
@@ -13648,10 +14670,10 @@
         <v>26</v>
       </c>
       <c r="F30" t="s">
-        <v>1236</v>
+        <v>1334</v>
       </c>
       <c r="G30" t="s">
-        <v>1253</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
@@ -13671,10 +14693,10 @@
         <v>26</v>
       </c>
       <c r="F31" t="s">
-        <v>1236</v>
+        <v>1334</v>
       </c>
       <c r="G31" t="s">
-        <v>1254</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
@@ -13694,10 +14716,10 @@
         <v>86</v>
       </c>
       <c r="F32" t="s">
-        <v>1236</v>
+        <v>1334</v>
       </c>
       <c r="G32" t="s">
-        <v>1255</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
@@ -13717,10 +14739,10 @@
         <v>86</v>
       </c>
       <c r="F33" t="s">
-        <v>1236</v>
+        <v>1334</v>
       </c>
       <c r="G33" t="s">
-        <v>1256</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
@@ -13740,10 +14762,10 @@
         <v>86</v>
       </c>
       <c r="F34" t="s">
-        <v>1236</v>
+        <v>1334</v>
       </c>
       <c r="G34" t="s">
-        <v>1257</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
@@ -13763,7 +14785,7 @@
         <v>26</v>
       </c>
       <c r="F35" t="s">
-        <v>1258</v>
+        <v>1356</v>
       </c>
       <c r="G35" t="s">
         <v>168</v>
@@ -13786,7 +14808,7 @@
         <v>26</v>
       </c>
       <c r="F36" t="s">
-        <v>1258</v>
+        <v>1356</v>
       </c>
       <c r="G36" t="s">
         <v>177</v>
@@ -13809,7 +14831,7 @@
         <v>26</v>
       </c>
       <c r="F37" t="s">
-        <v>1258</v>
+        <v>1356</v>
       </c>
       <c r="G37" t="s">
         <v>194</v>
@@ -13832,7 +14854,7 @@
         <v>26</v>
       </c>
       <c r="F38" t="s">
-        <v>1258</v>
+        <v>1356</v>
       </c>
       <c r="G38" t="s">
         <v>203</v>
@@ -13855,7 +14877,7 @@
         <v>26</v>
       </c>
       <c r="F39" t="s">
-        <v>1258</v>
+        <v>1356</v>
       </c>
       <c r="G39" t="s">
         <v>222</v>
@@ -13878,7 +14900,7 @@
         <v>26</v>
       </c>
       <c r="F40" t="s">
-        <v>1258</v>
+        <v>1356</v>
       </c>
       <c r="G40" t="s">
         <v>245</v>
@@ -13901,10 +14923,10 @@
         <v>26</v>
       </c>
       <c r="F41" t="s">
-        <v>1258</v>
+        <v>1356</v>
       </c>
       <c r="G41" t="s">
-        <v>1259</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
@@ -13924,10 +14946,10 @@
         <v>26</v>
       </c>
       <c r="F42" t="s">
-        <v>1258</v>
+        <v>1356</v>
       </c>
       <c r="G42" t="s">
-        <v>1260</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
@@ -13947,10 +14969,10 @@
         <v>26</v>
       </c>
       <c r="F43" t="s">
-        <v>1258</v>
+        <v>1356</v>
       </c>
       <c r="G43" t="s">
-        <v>1261</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
@@ -13970,7 +14992,7 @@
         <v>26</v>
       </c>
       <c r="F44" t="s">
-        <v>1258</v>
+        <v>1356</v>
       </c>
       <c r="G44" t="s">
         <v>360</v>
@@ -13993,7 +15015,7 @@
         <v>26</v>
       </c>
       <c r="F45" t="s">
-        <v>1258</v>
+        <v>1356</v>
       </c>
       <c r="G45" t="s">
         <v>368</v>
@@ -14016,10 +15038,10 @@
         <v>26</v>
       </c>
       <c r="F46" t="s">
-        <v>1258</v>
+        <v>1356</v>
       </c>
       <c r="G46" t="s">
-        <v>1262</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
@@ -14039,7 +15061,7 @@
         <v>26</v>
       </c>
       <c r="F47" t="s">
-        <v>1258</v>
+        <v>1356</v>
       </c>
       <c r="G47" t="s">
         <v>386</v>
@@ -14062,10 +15084,10 @@
         <v>26</v>
       </c>
       <c r="F48" t="s">
-        <v>1258</v>
+        <v>1356</v>
       </c>
       <c r="G48" t="s">
-        <v>1263</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
@@ -14085,7 +15107,7 @@
         <v>26</v>
       </c>
       <c r="F49" t="s">
-        <v>1258</v>
+        <v>1356</v>
       </c>
       <c r="G49" t="s">
         <v>402</v>
@@ -14108,7 +15130,7 @@
         <v>26</v>
       </c>
       <c r="F50" t="s">
-        <v>1258</v>
+        <v>1356</v>
       </c>
       <c r="G50" t="s">
         <v>411</v>
@@ -14131,7 +15153,7 @@
         <v>26</v>
       </c>
       <c r="F51" t="s">
-        <v>1258</v>
+        <v>1356</v>
       </c>
       <c r="G51" t="s">
         <v>419</v>
@@ -14154,7 +15176,7 @@
         <v>26</v>
       </c>
       <c r="F52" t="s">
-        <v>1258</v>
+        <v>1356</v>
       </c>
       <c r="G52" t="s">
         <v>426</v>
@@ -14177,7 +15199,7 @@
         <v>26</v>
       </c>
       <c r="F53" t="s">
-        <v>1258</v>
+        <v>1356</v>
       </c>
       <c r="G53" t="s">
         <v>433</v>
@@ -14200,7 +15222,7 @@
         <v>26</v>
       </c>
       <c r="F54" t="s">
-        <v>1258</v>
+        <v>1356</v>
       </c>
       <c r="G54" t="s">
         <v>467</v>
@@ -14223,7 +15245,7 @@
         <v>26</v>
       </c>
       <c r="F55" t="s">
-        <v>1258</v>
+        <v>1356</v>
       </c>
       <c r="G55" t="s">
         <v>485</v>
@@ -14246,7 +15268,7 @@
         <v>26</v>
       </c>
       <c r="F56" t="s">
-        <v>1258</v>
+        <v>1356</v>
       </c>
       <c r="G56" t="s">
         <v>494</v>
@@ -14269,7 +15291,7 @@
         <v>26</v>
       </c>
       <c r="F57" t="s">
-        <v>1258</v>
+        <v>1356</v>
       </c>
       <c r="G57" t="s">
         <v>502</v>
@@ -14292,7 +15314,7 @@
         <v>26</v>
       </c>
       <c r="F58" t="s">
-        <v>1258</v>
+        <v>1356</v>
       </c>
       <c r="G58" t="s">
         <v>511</v>
@@ -14315,7 +15337,7 @@
         <v>26</v>
       </c>
       <c r="F59" t="s">
-        <v>1258</v>
+        <v>1356</v>
       </c>
       <c r="G59" t="s">
         <v>520</v>
@@ -14338,7 +15360,7 @@
         <v>26</v>
       </c>
       <c r="F60" t="s">
-        <v>1258</v>
+        <v>1356</v>
       </c>
       <c r="G60" t="s">
         <v>530</v>
@@ -14361,7 +15383,7 @@
         <v>26</v>
       </c>
       <c r="F61" t="s">
-        <v>1258</v>
+        <v>1356</v>
       </c>
       <c r="G61" t="s">
         <v>539</v>
@@ -14384,7 +15406,7 @@
         <v>26</v>
       </c>
       <c r="F62" t="s">
-        <v>1258</v>
+        <v>1356</v>
       </c>
       <c r="G62" t="s">
         <v>547</v>
@@ -14407,7 +15429,7 @@
         <v>26</v>
       </c>
       <c r="F63" t="s">
-        <v>1258</v>
+        <v>1356</v>
       </c>
       <c r="G63" t="s">
         <v>557</v>
@@ -14430,7 +15452,7 @@
         <v>26</v>
       </c>
       <c r="F64" t="s">
-        <v>1258</v>
+        <v>1356</v>
       </c>
       <c r="G64" t="s">
         <v>567</v>
@@ -14453,7 +15475,7 @@
         <v>26</v>
       </c>
       <c r="F65" t="s">
-        <v>1258</v>
+        <v>1356</v>
       </c>
       <c r="G65" t="s">
         <v>576</v>
@@ -14476,7 +15498,7 @@
         <v>26</v>
       </c>
       <c r="F66" t="s">
-        <v>1258</v>
+        <v>1356</v>
       </c>
       <c r="G66" t="s">
         <v>584</v>
@@ -14499,7 +15521,7 @@
         <v>26</v>
       </c>
       <c r="F67" t="s">
-        <v>1258</v>
+        <v>1356</v>
       </c>
       <c r="G67" t="s">
         <v>594</v>
@@ -14522,7 +15544,7 @@
         <v>26</v>
       </c>
       <c r="F68" t="s">
-        <v>1258</v>
+        <v>1356</v>
       </c>
       <c r="G68" t="s">
         <v>602</v>
@@ -14545,7 +15567,7 @@
         <v>26</v>
       </c>
       <c r="F69" t="s">
-        <v>1258</v>
+        <v>1356</v>
       </c>
       <c r="G69" t="s">
         <v>611</v>
@@ -14568,7 +15590,7 @@
         <v>26</v>
       </c>
       <c r="F70" t="s">
-        <v>1258</v>
+        <v>1356</v>
       </c>
       <c r="G70" t="s">
         <v>618</v>
@@ -14591,10 +15613,10 @@
         <v>26</v>
       </c>
       <c r="F71" t="s">
-        <v>1258</v>
+        <v>1356</v>
       </c>
       <c r="G71" t="s">
-        <v>1264</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
@@ -14614,10 +15636,10 @@
         <v>26</v>
       </c>
       <c r="F72" t="s">
-        <v>1258</v>
+        <v>1356</v>
       </c>
       <c r="G72" t="s">
-        <v>1265</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
@@ -14637,10 +15659,10 @@
         <v>26</v>
       </c>
       <c r="F73" t="s">
-        <v>1258</v>
+        <v>1356</v>
       </c>
       <c r="G73" t="s">
-        <v>1266</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
@@ -14660,10 +15682,10 @@
         <v>26</v>
       </c>
       <c r="F74" t="s">
-        <v>1258</v>
+        <v>1356</v>
       </c>
       <c r="G74" t="s">
-        <v>1267</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
@@ -14683,10 +15705,10 @@
         <v>26</v>
       </c>
       <c r="F75" t="s">
-        <v>1258</v>
+        <v>1356</v>
       </c>
       <c r="G75" t="s">
-        <v>1268</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
@@ -14706,10 +15728,10 @@
         <v>26</v>
       </c>
       <c r="F76" t="s">
-        <v>1258</v>
+        <v>1356</v>
       </c>
       <c r="G76" t="s">
-        <v>1269</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
@@ -14729,10 +15751,10 @@
         <v>26</v>
       </c>
       <c r="F77" t="s">
-        <v>1258</v>
+        <v>1356</v>
       </c>
       <c r="G77" t="s">
-        <v>1270</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
@@ -14752,10 +15774,10 @@
         <v>26</v>
       </c>
       <c r="F78" t="s">
-        <v>1258</v>
+        <v>1356</v>
       </c>
       <c r="G78" t="s">
-        <v>1271</v>
+        <v>1369</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
@@ -14775,10 +15797,10 @@
         <v>26</v>
       </c>
       <c r="F79" t="s">
-        <v>1258</v>
+        <v>1356</v>
       </c>
       <c r="G79" t="s">
-        <v>1272</v>
+        <v>1370</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
@@ -14786,7 +15808,7 @@
         <v>27</v>
       </c>
       <c r="B80" t="s">
-        <v>1200</v>
+        <v>1295</v>
       </c>
       <c r="C80" t="s">
         <v>697</v>
@@ -14798,10 +15820,10 @@
         <v>26</v>
       </c>
       <c r="F80" t="s">
-        <v>1273</v>
+        <v>1371</v>
       </c>
       <c r="G80" t="s">
-        <v>1274</v>
+        <v>1372</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
@@ -14809,7 +15831,7 @@
         <v>27</v>
       </c>
       <c r="B81" t="s">
-        <v>1200</v>
+        <v>1295</v>
       </c>
       <c r="C81" t="s">
         <v>708</v>
@@ -14821,10 +15843,10 @@
         <v>26</v>
       </c>
       <c r="F81" t="s">
-        <v>1273</v>
+        <v>1371</v>
       </c>
       <c r="G81" t="s">
-        <v>1275</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
@@ -14832,7 +15854,7 @@
         <v>27</v>
       </c>
       <c r="B82" t="s">
-        <v>1200</v>
+        <v>1295</v>
       </c>
       <c r="C82" t="s">
         <v>715</v>
@@ -14844,10 +15866,10 @@
         <v>26</v>
       </c>
       <c r="F82" t="s">
-        <v>1273</v>
+        <v>1371</v>
       </c>
       <c r="G82" t="s">
-        <v>1276</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
@@ -14855,7 +15877,7 @@
         <v>27</v>
       </c>
       <c r="B83" t="s">
-        <v>1200</v>
+        <v>1295</v>
       </c>
       <c r="C83" t="s">
         <v>723</v>
@@ -14867,10 +15889,10 @@
         <v>26</v>
       </c>
       <c r="F83" t="s">
-        <v>1273</v>
+        <v>1371</v>
       </c>
       <c r="G83" t="s">
-        <v>1277</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
@@ -14878,7 +15900,7 @@
         <v>27</v>
       </c>
       <c r="B84" t="s">
-        <v>1200</v>
+        <v>1295</v>
       </c>
       <c r="C84" t="s">
         <v>732</v>
@@ -14890,10 +15912,10 @@
         <v>26</v>
       </c>
       <c r="F84" t="s">
-        <v>1273</v>
+        <v>1371</v>
       </c>
       <c r="G84" t="s">
-        <v>1278</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
@@ -14901,7 +15923,7 @@
         <v>27</v>
       </c>
       <c r="B85" t="s">
-        <v>1279</v>
+        <v>1377</v>
       </c>
       <c r="C85" t="s">
         <v>324</v>
@@ -14913,10 +15935,10 @@
         <v>86</v>
       </c>
       <c r="F85" t="s">
-        <v>1280</v>
+        <v>1378</v>
       </c>
       <c r="G85" t="s">
-        <v>1281</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
@@ -14924,7 +15946,7 @@
         <v>27</v>
       </c>
       <c r="B86" t="s">
-        <v>1279</v>
+        <v>1377</v>
       </c>
       <c r="C86" t="s">
         <v>335</v>
@@ -14936,10 +15958,10 @@
         <v>86</v>
       </c>
       <c r="F86" t="s">
-        <v>1280</v>
+        <v>1378</v>
       </c>
       <c r="G86" t="s">
-        <v>1282</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
@@ -14947,7 +15969,7 @@
         <v>27</v>
       </c>
       <c r="B87" t="s">
-        <v>1279</v>
+        <v>1377</v>
       </c>
       <c r="C87" t="s">
         <v>344</v>
@@ -14959,10 +15981,10 @@
         <v>86</v>
       </c>
       <c r="F87" t="s">
-        <v>1280</v>
+        <v>1378</v>
       </c>
       <c r="G87" t="s">
-        <v>1283</v>
+        <v>1381</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
@@ -14970,7 +15992,7 @@
         <v>27</v>
       </c>
       <c r="B88" t="s">
-        <v>1279</v>
+        <v>1377</v>
       </c>
       <c r="C88" t="s">
         <v>369</v>
@@ -14982,10 +16004,10 @@
         <v>112</v>
       </c>
       <c r="F88" t="s">
-        <v>1280</v>
+        <v>1378</v>
       </c>
       <c r="G88" t="s">
-        <v>1284</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
@@ -15005,10 +16027,10 @@
         <v>26</v>
       </c>
       <c r="F89" t="s">
-        <v>1285</v>
+        <v>1383</v>
       </c>
       <c r="G89" t="s">
-        <v>1286</v>
+        <v>1384</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
@@ -15016,7 +16038,7 @@
         <v>27</v>
       </c>
       <c r="B90" t="s">
-        <v>1279</v>
+        <v>1377</v>
       </c>
       <c r="C90" t="s">
         <v>619</v>
@@ -15028,10 +16050,10 @@
         <v>112</v>
       </c>
       <c r="F90" t="s">
-        <v>1280</v>
+        <v>1378</v>
       </c>
       <c r="G90" t="s">
-        <v>1287</v>
+        <v>1385</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
@@ -15039,7 +16061,7 @@
         <v>27</v>
       </c>
       <c r="B91" t="s">
-        <v>1279</v>
+        <v>1377</v>
       </c>
       <c r="C91" t="s">
         <v>639</v>
@@ -15051,10 +16073,10 @@
         <v>86</v>
       </c>
       <c r="F91" t="s">
-        <v>1280</v>
+        <v>1378</v>
       </c>
       <c r="G91" t="s">
-        <v>1288</v>
+        <v>1386</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
@@ -15062,7 +16084,7 @@
         <v>27</v>
       </c>
       <c r="B92" t="s">
-        <v>1279</v>
+        <v>1377</v>
       </c>
       <c r="C92" t="s">
         <v>648</v>
@@ -15074,10 +16096,10 @@
         <v>112</v>
       </c>
       <c r="F92" t="s">
-        <v>1280</v>
+        <v>1378</v>
       </c>
       <c r="G92" t="s">
-        <v>1289</v>
+        <v>1387</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
@@ -15097,10 +16119,10 @@
         <v>86</v>
       </c>
       <c r="F93" t="s">
-        <v>1285</v>
+        <v>1383</v>
       </c>
       <c r="G93" t="s">
-        <v>1290</v>
+        <v>1388</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
@@ -15108,7 +16130,7 @@
         <v>27</v>
       </c>
       <c r="B94" t="s">
-        <v>1279</v>
+        <v>1377</v>
       </c>
       <c r="C94" t="s">
         <v>657</v>
@@ -15120,10 +16142,10 @@
         <v>112</v>
       </c>
       <c r="F94" t="s">
-        <v>1280</v>
+        <v>1378</v>
       </c>
       <c r="G94" t="s">
-        <v>1291</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
@@ -15131,7 +16153,7 @@
         <v>27</v>
       </c>
       <c r="B95" t="s">
-        <v>1279</v>
+        <v>1377</v>
       </c>
       <c r="C95" t="s">
         <v>673</v>
@@ -15143,10 +16165,10 @@
         <v>112</v>
       </c>
       <c r="F95" t="s">
-        <v>1280</v>
+        <v>1378</v>
       </c>
       <c r="G95" t="s">
-        <v>1292</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
@@ -15166,10 +16188,10 @@
         <v>26</v>
       </c>
       <c r="F96" t="s">
-        <v>1285</v>
+        <v>1383</v>
       </c>
       <c r="G96" t="s">
-        <v>1293</v>
+        <v>1391</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
@@ -15177,7 +16199,7 @@
         <v>27</v>
       </c>
       <c r="B97" t="s">
-        <v>1279</v>
+        <v>1377</v>
       </c>
       <c r="C97" t="s">
         <v>689</v>
@@ -15189,10 +16211,10 @@
         <v>112</v>
       </c>
       <c r="F97" t="s">
-        <v>1280</v>
+        <v>1378</v>
       </c>
       <c r="G97" t="s">
-        <v>1294</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
@@ -15200,7 +16222,7 @@
         <v>27</v>
       </c>
       <c r="B98" t="s">
-        <v>1279</v>
+        <v>1377</v>
       </c>
       <c r="C98" t="s">
         <v>697</v>
@@ -15212,10 +16234,10 @@
         <v>112</v>
       </c>
       <c r="F98" t="s">
-        <v>1280</v>
+        <v>1378</v>
       </c>
       <c r="G98" t="s">
-        <v>1295</v>
+        <v>1393</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
@@ -15235,10 +16257,10 @@
         <v>26</v>
       </c>
       <c r="F99" t="s">
-        <v>1285</v>
+        <v>1383</v>
       </c>
       <c r="G99" t="s">
-        <v>1296</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
@@ -15246,7 +16268,7 @@
         <v>27</v>
       </c>
       <c r="B100" t="s">
-        <v>1279</v>
+        <v>1377</v>
       </c>
       <c r="C100" t="s">
         <v>708</v>
@@ -15258,10 +16280,10 @@
         <v>112</v>
       </c>
       <c r="F100" t="s">
-        <v>1280</v>
+        <v>1378</v>
       </c>
       <c r="G100" t="s">
-        <v>1297</v>
+        <v>1395</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
@@ -15281,10 +16303,10 @@
         <v>86</v>
       </c>
       <c r="F101" t="s">
-        <v>1285</v>
+        <v>1383</v>
       </c>
       <c r="G101" t="s">
-        <v>1298</v>
+        <v>1396</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
@@ -15292,7 +16314,7 @@
         <v>27</v>
       </c>
       <c r="B102" t="s">
-        <v>1279</v>
+        <v>1377</v>
       </c>
       <c r="C102" t="s">
         <v>715</v>
@@ -15304,10 +16326,10 @@
         <v>112</v>
       </c>
       <c r="F102" t="s">
-        <v>1280</v>
+        <v>1378</v>
       </c>
       <c r="G102" t="s">
-        <v>1299</v>
+        <v>1397</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
@@ -15327,10 +16349,10 @@
         <v>86</v>
       </c>
       <c r="F103" t="s">
-        <v>1285</v>
+        <v>1383</v>
       </c>
       <c r="G103" t="s">
-        <v>1300</v>
+        <v>1398</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
@@ -15338,7 +16360,7 @@
         <v>27</v>
       </c>
       <c r="B104" t="s">
-        <v>1279</v>
+        <v>1377</v>
       </c>
       <c r="C104" t="s">
         <v>723</v>
@@ -15350,10 +16372,10 @@
         <v>112</v>
       </c>
       <c r="F104" t="s">
-        <v>1280</v>
+        <v>1378</v>
       </c>
       <c r="G104" t="s">
-        <v>1301</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
@@ -15373,10 +16395,10 @@
         <v>26</v>
       </c>
       <c r="F105" t="s">
-        <v>1285</v>
+        <v>1383</v>
       </c>
       <c r="G105" t="s">
-        <v>1302</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
@@ -15384,7 +16406,7 @@
         <v>27</v>
       </c>
       <c r="B106" t="s">
-        <v>1279</v>
+        <v>1377</v>
       </c>
       <c r="C106" t="s">
         <v>732</v>
@@ -15396,10 +16418,10 @@
         <v>112</v>
       </c>
       <c r="F106" t="s">
-        <v>1280</v>
+        <v>1378</v>
       </c>
       <c r="G106" t="s">
-        <v>1303</v>
+        <v>1401</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
@@ -15419,10 +16441,10 @@
         <v>26</v>
       </c>
       <c r="F107" t="s">
-        <v>1285</v>
+        <v>1383</v>
       </c>
       <c r="G107" t="s">
-        <v>1304</v>
+        <v>1402</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
@@ -15436,13 +16458,13 @@
         <v>740</v>
       </c>
       <c r="D108" t="s">
-        <v>1305</v>
+        <v>1403</v>
       </c>
       <c r="E108" t="s">
         <v>112</v>
       </c>
       <c r="F108" t="s">
-        <v>1285</v>
+        <v>1383</v>
       </c>
       <c r="G108" t="s">
         <v>741</v>
@@ -15459,13 +16481,13 @@
         <v>750</v>
       </c>
       <c r="D109" t="s">
-        <v>1305</v>
+        <v>1403</v>
       </c>
       <c r="E109" t="s">
         <v>112</v>
       </c>
       <c r="F109" t="s">
-        <v>1285</v>
+        <v>1383</v>
       </c>
       <c r="G109" t="s">
         <v>751</v>
@@ -15482,13 +16504,13 @@
         <v>758</v>
       </c>
       <c r="D110" t="s">
-        <v>1305</v>
+        <v>1403</v>
       </c>
       <c r="E110" t="s">
         <v>112</v>
       </c>
       <c r="F110" t="s">
-        <v>1285</v>
+        <v>1383</v>
       </c>
       <c r="G110" t="s">
         <v>759</v>
@@ -15505,13 +16527,13 @@
         <v>766</v>
       </c>
       <c r="D111" t="s">
-        <v>1305</v>
+        <v>1403</v>
       </c>
       <c r="E111" t="s">
         <v>112</v>
       </c>
       <c r="F111" t="s">
-        <v>1285</v>
+        <v>1383</v>
       </c>
       <c r="G111" t="s">
         <v>767</v>
@@ -15528,13 +16550,13 @@
         <v>774</v>
       </c>
       <c r="D112" t="s">
-        <v>1305</v>
+        <v>1403</v>
       </c>
       <c r="E112" t="s">
         <v>112</v>
       </c>
       <c r="F112" t="s">
-        <v>1285</v>
+        <v>1383</v>
       </c>
       <c r="G112" t="s">
         <v>775</v>
@@ -15551,13 +16573,13 @@
         <v>782</v>
       </c>
       <c r="D113" t="s">
-        <v>1305</v>
+        <v>1403</v>
       </c>
       <c r="E113" t="s">
         <v>112</v>
       </c>
       <c r="F113" t="s">
-        <v>1285</v>
+        <v>1383</v>
       </c>
       <c r="G113" t="s">
         <v>783</v>
@@ -15574,13 +16596,13 @@
         <v>790</v>
       </c>
       <c r="D114" t="s">
-        <v>1305</v>
+        <v>1403</v>
       </c>
       <c r="E114" t="s">
         <v>112</v>
       </c>
       <c r="F114" t="s">
-        <v>1285</v>
+        <v>1383</v>
       </c>
       <c r="G114" t="s">
         <v>791</v>
@@ -15597,13 +16619,13 @@
         <v>798</v>
       </c>
       <c r="D115" t="s">
-        <v>1305</v>
+        <v>1403</v>
       </c>
       <c r="E115" t="s">
         <v>112</v>
       </c>
       <c r="F115" t="s">
-        <v>1285</v>
+        <v>1383</v>
       </c>
       <c r="G115" t="s">
         <v>799</v>
@@ -15620,13 +16642,13 @@
         <v>806</v>
       </c>
       <c r="D116" t="s">
-        <v>1305</v>
+        <v>1403</v>
       </c>
       <c r="E116" t="s">
         <v>112</v>
       </c>
       <c r="F116" t="s">
-        <v>1285</v>
+        <v>1383</v>
       </c>
       <c r="G116" t="s">
         <v>807</v>
@@ -15643,13 +16665,13 @@
         <v>814</v>
       </c>
       <c r="D117" t="s">
-        <v>1305</v>
+        <v>1403</v>
       </c>
       <c r="E117" t="s">
         <v>112</v>
       </c>
       <c r="F117" t="s">
-        <v>1285</v>
+        <v>1383</v>
       </c>
       <c r="G117" t="s">
         <v>815</v>
@@ -15666,13 +16688,13 @@
         <v>821</v>
       </c>
       <c r="D118" t="s">
-        <v>1305</v>
+        <v>1403</v>
       </c>
       <c r="E118" t="s">
         <v>112</v>
       </c>
       <c r="F118" t="s">
-        <v>1285</v>
+        <v>1383</v>
       </c>
       <c r="G118" t="s">
         <v>823</v>
@@ -15689,13 +16711,13 @@
         <v>830</v>
       </c>
       <c r="D119" t="s">
-        <v>1305</v>
+        <v>1403</v>
       </c>
       <c r="E119" t="s">
         <v>112</v>
       </c>
       <c r="F119" t="s">
-        <v>1285</v>
+        <v>1383</v>
       </c>
       <c r="G119" t="s">
         <v>831</v>
@@ -15712,13 +16734,13 @@
         <v>837</v>
       </c>
       <c r="D120" t="s">
-        <v>1305</v>
+        <v>1403</v>
       </c>
       <c r="E120" t="s">
         <v>112</v>
       </c>
       <c r="F120" t="s">
-        <v>1285</v>
+        <v>1383</v>
       </c>
       <c r="G120" t="s">
         <v>838</v>
@@ -15735,13 +16757,13 @@
         <v>844</v>
       </c>
       <c r="D121" t="s">
-        <v>1305</v>
+        <v>1403</v>
       </c>
       <c r="E121" t="s">
         <v>112</v>
       </c>
       <c r="F121" t="s">
-        <v>1285</v>
+        <v>1383</v>
       </c>
       <c r="G121" t="s">
         <v>845</v>
@@ -15758,13 +16780,13 @@
         <v>852</v>
       </c>
       <c r="D122" t="s">
-        <v>1305</v>
+        <v>1403</v>
       </c>
       <c r="E122" t="s">
         <v>26</v>
       </c>
       <c r="F122" t="s">
-        <v>1285</v>
+        <v>1383</v>
       </c>
       <c r="G122" t="s">
         <v>853</v>
@@ -15781,13 +16803,13 @@
         <v>860</v>
       </c>
       <c r="D123" t="s">
-        <v>1305</v>
+        <v>1403</v>
       </c>
       <c r="E123" t="s">
         <v>112</v>
       </c>
       <c r="F123" t="s">
-        <v>1285</v>
+        <v>1383</v>
       </c>
       <c r="G123" t="s">
         <v>861</v>
@@ -15804,13 +16826,13 @@
         <v>868</v>
       </c>
       <c r="D124" t="s">
-        <v>1305</v>
+        <v>1403</v>
       </c>
       <c r="E124" t="s">
         <v>112</v>
       </c>
       <c r="F124" t="s">
-        <v>1285</v>
+        <v>1383</v>
       </c>
       <c r="G124" t="s">
         <v>869</v>
@@ -15827,13 +16849,13 @@
         <v>876</v>
       </c>
       <c r="D125" t="s">
-        <v>1305</v>
+        <v>1403</v>
       </c>
       <c r="E125" t="s">
         <v>112</v>
       </c>
       <c r="F125" t="s">
-        <v>1285</v>
+        <v>1383</v>
       </c>
       <c r="G125" t="s">
         <v>878</v>
@@ -15850,13 +16872,13 @@
         <v>885</v>
       </c>
       <c r="D126" t="s">
-        <v>1305</v>
+        <v>1403</v>
       </c>
       <c r="E126" t="s">
         <v>112</v>
       </c>
       <c r="F126" t="s">
-        <v>1285</v>
+        <v>1383</v>
       </c>
       <c r="G126" t="s">
         <v>886</v>
@@ -15873,13 +16895,13 @@
         <v>893</v>
       </c>
       <c r="D127" t="s">
-        <v>1305</v>
+        <v>1403</v>
       </c>
       <c r="E127" t="s">
         <v>112</v>
       </c>
       <c r="F127" t="s">
-        <v>1285</v>
+        <v>1383</v>
       </c>
       <c r="G127" t="s">
         <v>894</v>
@@ -15896,13 +16918,13 @@
         <v>901</v>
       </c>
       <c r="D128" t="s">
-        <v>1305</v>
+        <v>1403</v>
       </c>
       <c r="E128" t="s">
         <v>453</v>
       </c>
       <c r="F128" t="s">
-        <v>1285</v>
+        <v>1383</v>
       </c>
       <c r="G128" t="s">
         <v>902</v>
@@ -15919,13 +16941,13 @@
         <v>909</v>
       </c>
       <c r="D129" t="s">
-        <v>1305</v>
+        <v>1403</v>
       </c>
       <c r="E129" t="s">
         <v>112</v>
       </c>
       <c r="F129" t="s">
-        <v>1285</v>
+        <v>1383</v>
       </c>
       <c r="G129" t="s">
         <v>910</v>
@@ -15942,13 +16964,13 @@
         <v>916</v>
       </c>
       <c r="D130" t="s">
-        <v>1305</v>
+        <v>1403</v>
       </c>
       <c r="E130" t="s">
         <v>112</v>
       </c>
       <c r="F130" t="s">
-        <v>1285</v>
+        <v>1383</v>
       </c>
       <c r="G130" t="s">
         <v>917</v>
@@ -15965,13 +16987,13 @@
         <v>926</v>
       </c>
       <c r="D131" t="s">
-        <v>1305</v>
+        <v>1403</v>
       </c>
       <c r="E131" t="s">
         <v>112</v>
       </c>
       <c r="F131" t="s">
-        <v>1285</v>
+        <v>1383</v>
       </c>
       <c r="G131" t="s">
         <v>927</v>
@@ -15988,13 +17010,13 @@
         <v>934</v>
       </c>
       <c r="D132" t="s">
-        <v>1305</v>
+        <v>1403</v>
       </c>
       <c r="E132" t="s">
         <v>112</v>
       </c>
       <c r="F132" t="s">
-        <v>1285</v>
+        <v>1383</v>
       </c>
       <c r="G132" t="s">
         <v>935</v>
@@ -16011,13 +17033,13 @@
         <v>942</v>
       </c>
       <c r="D133" t="s">
-        <v>1305</v>
+        <v>1403</v>
       </c>
       <c r="E133" t="s">
         <v>112</v>
       </c>
       <c r="F133" t="s">
-        <v>1285</v>
+        <v>1383</v>
       </c>
       <c r="G133" t="s">
         <v>943</v>
@@ -16034,13 +17056,13 @@
         <v>950</v>
       </c>
       <c r="D134" t="s">
-        <v>1305</v>
+        <v>1403</v>
       </c>
       <c r="E134" t="s">
         <v>112</v>
       </c>
       <c r="F134" t="s">
-        <v>1285</v>
+        <v>1383</v>
       </c>
       <c r="G134" t="s">
         <v>951</v>
@@ -16057,13 +17079,13 @@
         <v>958</v>
       </c>
       <c r="D135" t="s">
-        <v>1305</v>
+        <v>1403</v>
       </c>
       <c r="E135" t="s">
         <v>112</v>
       </c>
       <c r="F135" t="s">
-        <v>1285</v>
+        <v>1383</v>
       </c>
       <c r="G135" t="s">
         <v>960</v>
@@ -16080,13 +17102,13 @@
         <v>967</v>
       </c>
       <c r="D136" t="s">
-        <v>1305</v>
+        <v>1403</v>
       </c>
       <c r="E136" t="s">
         <v>112</v>
       </c>
       <c r="F136" t="s">
-        <v>1285</v>
+        <v>1383</v>
       </c>
       <c r="G136" t="s">
         <v>968</v>
@@ -16103,13 +17125,13 @@
         <v>974</v>
       </c>
       <c r="D137" t="s">
-        <v>1305</v>
+        <v>1403</v>
       </c>
       <c r="E137" t="s">
         <v>112</v>
       </c>
       <c r="F137" t="s">
-        <v>1285</v>
+        <v>1383</v>
       </c>
       <c r="G137" t="s">
         <v>975</v>
@@ -16126,13 +17148,13 @@
         <v>981</v>
       </c>
       <c r="D138" t="s">
-        <v>1305</v>
+        <v>1403</v>
       </c>
       <c r="E138" t="s">
         <v>112</v>
       </c>
       <c r="F138" t="s">
-        <v>1285</v>
+        <v>1383</v>
       </c>
       <c r="G138" t="s">
         <v>982</v>
@@ -16149,16 +17171,292 @@
         <v>989</v>
       </c>
       <c r="D139" t="s">
-        <v>1305</v>
+        <v>1403</v>
       </c>
       <c r="E139" t="s">
         <v>112</v>
       </c>
       <c r="F139" t="s">
-        <v>1285</v>
+        <v>1383</v>
       </c>
       <c r="G139" t="s">
         <v>990</v>
+      </c>
+    </row>
+    <row r="140" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>27</v>
+      </c>
+      <c r="B140" t="s">
+        <v>999</v>
+      </c>
+      <c r="C140" t="s">
+        <v>997</v>
+      </c>
+      <c r="D140" t="s">
+        <v>1403</v>
+      </c>
+      <c r="E140" t="s">
+        <v>112</v>
+      </c>
+      <c r="F140" t="s">
+        <v>1383</v>
+      </c>
+      <c r="G140" t="s">
+        <v>998</v>
+      </c>
+    </row>
+    <row r="141" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>27</v>
+      </c>
+      <c r="B141" t="s">
+        <v>999</v>
+      </c>
+      <c r="C141" t="s">
+        <v>1006</v>
+      </c>
+      <c r="D141" t="s">
+        <v>1403</v>
+      </c>
+      <c r="E141" t="s">
+        <v>112</v>
+      </c>
+      <c r="F141" t="s">
+        <v>1383</v>
+      </c>
+      <c r="G141" t="s">
+        <v>1007</v>
+      </c>
+    </row>
+    <row r="142" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>27</v>
+      </c>
+      <c r="B142" t="s">
+        <v>999</v>
+      </c>
+      <c r="C142" t="s">
+        <v>1014</v>
+      </c>
+      <c r="D142" t="s">
+        <v>1403</v>
+      </c>
+      <c r="E142" t="s">
+        <v>112</v>
+      </c>
+      <c r="F142" t="s">
+        <v>1383</v>
+      </c>
+      <c r="G142" t="s">
+        <v>1015</v>
+      </c>
+    </row>
+    <row r="143" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>27</v>
+      </c>
+      <c r="B143" t="s">
+        <v>999</v>
+      </c>
+      <c r="C143" t="s">
+        <v>1021</v>
+      </c>
+      <c r="D143" t="s">
+        <v>1403</v>
+      </c>
+      <c r="E143" t="s">
+        <v>453</v>
+      </c>
+      <c r="F143" t="s">
+        <v>1383</v>
+      </c>
+      <c r="G143" t="s">
+        <v>1022</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>27</v>
+      </c>
+      <c r="B144" t="s">
+        <v>999</v>
+      </c>
+      <c r="C144" t="s">
+        <v>1029</v>
+      </c>
+      <c r="D144" t="s">
+        <v>1403</v>
+      </c>
+      <c r="E144" t="s">
+        <v>112</v>
+      </c>
+      <c r="F144" t="s">
+        <v>1383</v>
+      </c>
+      <c r="G144" t="s">
+        <v>1031</v>
+      </c>
+    </row>
+    <row r="145" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
+        <v>27</v>
+      </c>
+      <c r="B145" t="s">
+        <v>999</v>
+      </c>
+      <c r="C145" t="s">
+        <v>1037</v>
+      </c>
+      <c r="D145" t="s">
+        <v>1403</v>
+      </c>
+      <c r="E145" t="s">
+        <v>112</v>
+      </c>
+      <c r="F145" t="s">
+        <v>1383</v>
+      </c>
+      <c r="G145" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="146" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>27</v>
+      </c>
+      <c r="B146" t="s">
+        <v>999</v>
+      </c>
+      <c r="C146" t="s">
+        <v>1044</v>
+      </c>
+      <c r="D146" t="s">
+        <v>1403</v>
+      </c>
+      <c r="E146" t="s">
+        <v>112</v>
+      </c>
+      <c r="F146" t="s">
+        <v>1383</v>
+      </c>
+      <c r="G146" t="s">
+        <v>1045</v>
+      </c>
+    </row>
+    <row r="147" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>27</v>
+      </c>
+      <c r="B147" t="s">
+        <v>999</v>
+      </c>
+      <c r="C147" t="s">
+        <v>1052</v>
+      </c>
+      <c r="D147" t="s">
+        <v>1403</v>
+      </c>
+      <c r="E147" t="s">
+        <v>112</v>
+      </c>
+      <c r="F147" t="s">
+        <v>1383</v>
+      </c>
+      <c r="G147" t="s">
+        <v>1054</v>
+      </c>
+    </row>
+    <row r="148" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>27</v>
+      </c>
+      <c r="B148" t="s">
+        <v>999</v>
+      </c>
+      <c r="C148" t="s">
+        <v>1060</v>
+      </c>
+      <c r="D148" t="s">
+        <v>1403</v>
+      </c>
+      <c r="E148" t="s">
+        <v>112</v>
+      </c>
+      <c r="F148" t="s">
+        <v>1383</v>
+      </c>
+      <c r="G148" t="s">
+        <v>1061</v>
+      </c>
+    </row>
+    <row r="149" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
+        <v>27</v>
+      </c>
+      <c r="B149" t="s">
+        <v>999</v>
+      </c>
+      <c r="C149" t="s">
+        <v>1067</v>
+      </c>
+      <c r="D149" t="s">
+        <v>1403</v>
+      </c>
+      <c r="E149" t="s">
+        <v>95</v>
+      </c>
+      <c r="F149" t="s">
+        <v>1383</v>
+      </c>
+      <c r="G149" t="s">
+        <v>1068</v>
+      </c>
+    </row>
+    <row r="150" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A150" t="s">
+        <v>27</v>
+      </c>
+      <c r="B150" t="s">
+        <v>999</v>
+      </c>
+      <c r="C150" t="s">
+        <v>1075</v>
+      </c>
+      <c r="D150" t="s">
+        <v>1403</v>
+      </c>
+      <c r="E150" t="s">
+        <v>112</v>
+      </c>
+      <c r="F150" t="s">
+        <v>1383</v>
+      </c>
+      <c r="G150" t="s">
+        <v>1077</v>
+      </c>
+    </row>
+    <row r="151" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A151" t="s">
+        <v>27</v>
+      </c>
+      <c r="B151" t="s">
+        <v>999</v>
+      </c>
+      <c r="C151" t="s">
+        <v>1084</v>
+      </c>
+      <c r="D151" t="s">
+        <v>1403</v>
+      </c>
+      <c r="E151" t="s">
+        <v>95</v>
+      </c>
+      <c r="F151" t="s">
+        <v>1383</v>
+      </c>
+      <c r="G151" t="s">
+        <v>1085</v>
       </c>
     </row>
   </sheetData>
@@ -16172,7 +17470,7 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>1306</v>
+        <v>1404</v>
       </c>
       <c r="B1"/>
       <c r="C1"/>
@@ -16180,7 +17478,7 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1307</v>
+        <v>1405</v>
       </c>
       <c r="B2"/>
       <c r="C2"/>
@@ -16191,181 +17489,181 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>1308</v>
+        <v>1406</v>
       </c>
       <c r="C3" t="s">
-        <v>1309</v>
+        <v>1407</v>
       </c>
       <c r="D3" t="s">
-        <v>1310</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1311</v>
+        <v>1409</v>
       </c>
       <c r="B4" t="s">
-        <v>1312</v>
+        <v>1410</v>
       </c>
       <c r="C4" t="s">
-        <v>1313</v>
+        <v>1411</v>
       </c>
       <c r="D4" t="s">
-        <v>1314</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1315</v>
+        <v>1413</v>
       </c>
       <c r="B5" t="s">
-        <v>1312</v>
+        <v>1410</v>
       </c>
       <c r="C5" t="s">
-        <v>1316</v>
+        <v>1414</v>
       </c>
       <c r="D5" t="s">
-        <v>1317</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>1318</v>
+        <v>1416</v>
       </c>
       <c r="B6" t="s">
-        <v>1312</v>
+        <v>1410</v>
       </c>
       <c r="C6" t="s">
-        <v>1319</v>
+        <v>1417</v>
       </c>
       <c r="D6" t="s">
-        <v>1320</v>
+        <v>1418</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>1321</v>
+        <v>1419</v>
       </c>
       <c r="B7" t="s">
-        <v>1312</v>
+        <v>1410</v>
       </c>
       <c r="C7" t="s">
-        <v>1322</v>
+        <v>1420</v>
       </c>
       <c r="D7" t="s">
-        <v>1323</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>1324</v>
+        <v>1422</v>
       </c>
       <c r="B8" t="s">
-        <v>1312</v>
+        <v>1410</v>
       </c>
       <c r="C8" t="s">
-        <v>1325</v>
+        <v>1423</v>
       </c>
       <c r="D8" t="s">
-        <v>1326</v>
+        <v>1424</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>1327</v>
+        <v>1425</v>
       </c>
       <c r="B9" t="s">
-        <v>1328</v>
+        <v>1426</v>
       </c>
       <c r="C9" t="s">
-        <v>1329</v>
+        <v>1427</v>
       </c>
       <c r="D9" t="s">
-        <v>1330</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>1331</v>
+        <v>1429</v>
       </c>
       <c r="B10" t="s">
-        <v>1328</v>
+        <v>1426</v>
       </c>
       <c r="C10" t="s">
-        <v>1332</v>
+        <v>1430</v>
       </c>
       <c r="D10" t="s">
-        <v>1333</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>1334</v>
+        <v>1432</v>
       </c>
       <c r="B11" t="s">
-        <v>1328</v>
+        <v>1426</v>
       </c>
       <c r="C11" t="s">
-        <v>1335</v>
+        <v>1433</v>
       </c>
       <c r="D11" t="s">
-        <v>1336</v>
+        <v>1434</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>1337</v>
+        <v>1435</v>
       </c>
       <c r="B12" t="s">
-        <v>1338</v>
+        <v>1436</v>
       </c>
       <c r="C12" t="s">
-        <v>1339</v>
+        <v>1437</v>
       </c>
       <c r="D12" t="s">
-        <v>1340</v>
+        <v>1438</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>1341</v>
+        <v>1439</v>
       </c>
       <c r="B13" t="s">
-        <v>1338</v>
+        <v>1436</v>
       </c>
       <c r="C13" t="s">
-        <v>1342</v>
+        <v>1440</v>
       </c>
       <c r="D13" t="s">
-        <v>1343</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>1344</v>
+        <v>1442</v>
       </c>
       <c r="B14" t="s">
         <v>877</v>
       </c>
       <c r="C14" t="s">
-        <v>1345</v>
+        <v>1443</v>
       </c>
       <c r="D14" t="s">
-        <v>1346</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>1347</v>
+        <v>1445</v>
       </c>
       <c r="B15" t="s">
         <v>877</v>
       </c>
       <c r="C15" t="s">
-        <v>1348</v>
+        <v>1446</v>
       </c>
       <c r="D15" t="s">
-        <v>1349</v>
+        <v>1447</v>
       </c>
     </row>
   </sheetData>
@@ -16384,7 +17682,7 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>1350</v>
+        <v>1448</v>
       </c>
       <c r="B1"/>
       <c r="C1"/>
@@ -16392,133 +17690,133 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>1351</v>
+        <v>1449</v>
       </c>
       <c r="B3" t="s">
-        <v>1352</v>
+        <v>1450</v>
       </c>
       <c r="C3" t="s">
-        <v>1353</v>
+        <v>1451</v>
       </c>
       <c r="D3" t="s">
-        <v>1354</v>
+        <v>1452</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1036</v>
+        <v>1132</v>
       </c>
       <c r="B4" t="s">
-        <v>1355</v>
+        <v>1453</v>
       </c>
       <c r="C4" t="s">
-        <v>1356</v>
+        <v>1454</v>
       </c>
       <c r="D4" t="s">
-        <v>1357</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1041</v>
+        <v>1137</v>
       </c>
       <c r="B5" t="s">
-        <v>1358</v>
+        <v>1456</v>
       </c>
       <c r="C5" t="s">
-        <v>1359</v>
+        <v>1457</v>
       </c>
       <c r="D5" t="s">
-        <v>1360</v>
+        <v>1458</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>1045</v>
+        <v>1141</v>
       </c>
       <c r="B6" t="s">
-        <v>1361</v>
+        <v>1459</v>
       </c>
       <c r="C6" t="s">
-        <v>1362</v>
+        <v>1460</v>
       </c>
       <c r="D6" t="s">
-        <v>1363</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>1049</v>
+        <v>1145</v>
       </c>
       <c r="B7" t="s">
-        <v>1364</v>
+        <v>1462</v>
       </c>
       <c r="C7" t="s">
-        <v>1365</v>
+        <v>1463</v>
       </c>
       <c r="D7" t="s">
-        <v>1366</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>1053</v>
+        <v>1149</v>
       </c>
       <c r="B8" t="s">
-        <v>1367</v>
+        <v>1465</v>
       </c>
       <c r="C8" t="s">
-        <v>1368</v>
+        <v>1466</v>
       </c>
       <c r="D8" t="s">
-        <v>1369</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>1057</v>
+        <v>1153</v>
       </c>
       <c r="B9" t="s">
-        <v>1370</v>
+        <v>1468</v>
       </c>
       <c r="C9" t="s">
-        <v>1371</v>
+        <v>1469</v>
       </c>
       <c r="D9" t="s">
-        <v>1372</v>
+        <v>1470</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>1061</v>
+        <v>1157</v>
       </c>
       <c r="B10" t="s">
-        <v>1373</v>
+        <v>1471</v>
       </c>
       <c r="C10" t="s">
-        <v>1374</v>
+        <v>1472</v>
       </c>
       <c r="D10" t="s">
-        <v>1375</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>1065</v>
+        <v>1161</v>
       </c>
       <c r="B11" t="s">
-        <v>1376</v>
+        <v>1474</v>
       </c>
       <c r="C11" t="s">
-        <v>1377</v>
+        <v>1475</v>
       </c>
       <c r="D11" t="s">
-        <v>1378</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>1379</v>
+        <v>1477</v>
       </c>
       <c r="B13"/>
       <c r="C13"/>
@@ -16526,72 +17824,72 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>1380</v>
+        <v>1478</v>
       </c>
       <c r="B14" t="s">
         <v>28</v>
       </c>
       <c r="C14" t="s">
-        <v>1381</v>
+        <v>1479</v>
       </c>
       <c r="D14" t="s">
-        <v>1382</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>1383</v>
+        <v>1481</v>
       </c>
       <c r="B15" t="s">
         <v>29</v>
       </c>
       <c r="C15" t="s">
-        <v>1384</v>
+        <v>1482</v>
       </c>
       <c r="D15" t="s">
-        <v>1385</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>1386</v>
+        <v>1484</v>
       </c>
       <c r="B16" t="s">
         <v>29</v>
       </c>
       <c r="C16" t="s">
-        <v>1387</v>
+        <v>1485</v>
       </c>
       <c r="D16" t="s">
-        <v>1388</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>1389</v>
+        <v>1487</v>
       </c>
       <c r="B17" t="s">
         <v>29</v>
       </c>
       <c r="C17" t="s">
-        <v>1390</v>
+        <v>1488</v>
       </c>
       <c r="D17" t="s">
-        <v>1391</v>
+        <v>1489</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>1392</v>
+        <v>1490</v>
       </c>
       <c r="B18" t="s">
-        <v>1393</v>
+        <v>1491</v>
       </c>
       <c r="C18" t="s">
-        <v>1394</v>
+        <v>1492</v>
       </c>
       <c r="D18" t="s">
-        <v>1395</v>
+        <v>1493</v>
       </c>
     </row>
   </sheetData>
@@ -16610,7 +17908,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>1396</v>
+        <v>1494</v>
       </c>
       <c r="B1"/>
       <c r="C1"/>
@@ -16620,7 +17918,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1397</v>
+        <v>1495</v>
       </c>
       <c r="B2"/>
       <c r="C2"/>
@@ -16630,99 +17928,99 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1398</v>
+        <v>1496</v>
       </c>
       <c r="B4" t="s">
-        <v>1399</v>
+        <v>1497</v>
       </c>
       <c r="C4" t="s">
-        <v>1400</v>
+        <v>1498</v>
       </c>
       <c r="D4" t="s">
-        <v>1401</v>
+        <v>1499</v>
       </c>
       <c r="E4" t="s">
-        <v>1402</v>
+        <v>1500</v>
       </c>
       <c r="F4" t="s">
-        <v>1403</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1404</v>
+        <v>1502</v>
       </c>
       <c r="B5" t="s">
-        <v>1405</v>
+        <v>1503</v>
       </c>
       <c r="C5" t="s">
-        <v>1406</v>
+        <v>1504</v>
       </c>
       <c r="D5" t="s">
-        <v>1407</v>
+        <v>1505</v>
       </c>
       <c r="E5" t="s">
-        <v>1408</v>
+        <v>1506</v>
       </c>
       <c r="F5" t="s">
-        <v>1409</v>
+        <v>1507</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>1410</v>
+        <v>1508</v>
       </c>
       <c r="B6" t="s">
-        <v>1411</v>
+        <v>1509</v>
       </c>
       <c r="C6" t="s">
-        <v>1412</v>
+        <v>1510</v>
       </c>
       <c r="D6" t="s">
-        <v>1413</v>
+        <v>1511</v>
       </c>
       <c r="E6" t="s">
-        <v>1414</v>
+        <v>1512</v>
       </c>
       <c r="F6" t="s">
-        <v>1415</v>
+        <v>1513</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>1416</v>
+        <v>1514</v>
       </c>
       <c r="B7" t="s">
-        <v>1411</v>
+        <v>1509</v>
       </c>
       <c r="C7" t="s">
-        <v>1417</v>
+        <v>1515</v>
       </c>
       <c r="D7" t="s">
-        <v>1418</v>
+        <v>1516</v>
       </c>
       <c r="E7" t="s">
-        <v>1419</v>
+        <v>1517</v>
       </c>
       <c r="F7" t="s">
-        <v>1420</v>
+        <v>1518</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>1421</v>
+        <v>1519</v>
       </c>
       <c r="B8" t="s">
-        <v>1422</v>
+        <v>1520</v>
       </c>
       <c r="C8" t="s">
-        <v>1423</v>
+        <v>1521</v>
       </c>
       <c r="D8" t="s">
-        <v>1424</v>
+        <v>1522</v>
       </c>
       <c r="E8" t="s">
-        <v>1425</v>
+        <v>1523</v>
       </c>
       <c r="F8" t="s">
         <v>629</v>
@@ -16730,19 +18028,19 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>1426</v>
+        <v>1524</v>
       </c>
       <c r="B9" t="s">
-        <v>1427</v>
+        <v>1525</v>
       </c>
       <c r="C9" t="s">
-        <v>1428</v>
+        <v>1526</v>
       </c>
       <c r="D9" t="s">
-        <v>1429</v>
+        <v>1527</v>
       </c>
       <c r="E9" t="s">
-        <v>1430</v>
+        <v>1528</v>
       </c>
       <c r="F9" t="s">
         <v>369</v>
@@ -16750,39 +18048,39 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>1431</v>
+        <v>1529</v>
       </c>
       <c r="B10" t="s">
-        <v>1432</v>
+        <v>1530</v>
       </c>
       <c r="C10" t="s">
-        <v>1433</v>
+        <v>1531</v>
       </c>
       <c r="D10" t="s">
-        <v>1434</v>
+        <v>1532</v>
       </c>
       <c r="E10" t="s">
-        <v>1435</v>
+        <v>1533</v>
       </c>
       <c r="F10" t="s">
-        <v>1436</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>1437</v>
+        <v>1535</v>
       </c>
       <c r="B11" t="s">
-        <v>1438</v>
+        <v>1536</v>
       </c>
       <c r="C11" t="s">
-        <v>1439</v>
+        <v>1537</v>
       </c>
       <c r="D11" t="s">
-        <v>1440</v>
+        <v>1538</v>
       </c>
       <c r="E11" t="s">
-        <v>1441</v>
+        <v>1539</v>
       </c>
       <c r="F11" t="s">
         <v>47</v>
@@ -16790,99 +18088,99 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>1442</v>
+        <v>1540</v>
       </c>
       <c r="B12" t="s">
-        <v>1443</v>
+        <v>1541</v>
       </c>
       <c r="C12" t="s">
-        <v>1444</v>
+        <v>1542</v>
       </c>
       <c r="D12" t="s">
-        <v>1445</v>
+        <v>1543</v>
       </c>
       <c r="E12" t="s">
-        <v>1446</v>
+        <v>1544</v>
       </c>
       <c r="F12" t="s">
-        <v>1447</v>
+        <v>1545</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>1448</v>
+        <v>1546</v>
       </c>
       <c r="B13" t="s">
-        <v>1449</v>
+        <v>1547</v>
       </c>
       <c r="C13" t="s">
-        <v>1450</v>
+        <v>1548</v>
       </c>
       <c r="D13" t="s">
-        <v>1451</v>
+        <v>1549</v>
       </c>
       <c r="E13" t="s">
-        <v>1452</v>
+        <v>1550</v>
       </c>
       <c r="F13" t="s">
-        <v>1453</v>
+        <v>1551</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>1454</v>
+        <v>1552</v>
       </c>
       <c r="B14" t="s">
-        <v>1455</v>
+        <v>1553</v>
       </c>
       <c r="C14" t="s">
-        <v>1456</v>
+        <v>1554</v>
       </c>
       <c r="D14" t="s">
-        <v>1457</v>
+        <v>1555</v>
       </c>
       <c r="E14" t="s">
-        <v>1458</v>
+        <v>1556</v>
       </c>
       <c r="F14" t="s">
-        <v>1459</v>
+        <v>1557</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>1460</v>
+        <v>1558</v>
       </c>
       <c r="B15" t="s">
-        <v>1461</v>
+        <v>1559</v>
       </c>
       <c r="C15" t="s">
-        <v>1462</v>
+        <v>1560</v>
       </c>
       <c r="D15" t="s">
-        <v>1463</v>
+        <v>1561</v>
       </c>
       <c r="E15" t="s">
-        <v>1464</v>
+        <v>1562</v>
       </c>
       <c r="F15" t="s">
-        <v>1465</v>
+        <v>1563</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>1466</v>
+        <v>1564</v>
       </c>
       <c r="B16" t="s">
-        <v>1467</v>
+        <v>1565</v>
       </c>
       <c r="C16" t="s">
-        <v>1468</v>
+        <v>1566</v>
       </c>
       <c r="D16" t="s">
-        <v>1469</v>
+        <v>1567</v>
       </c>
       <c r="E16" t="s">
-        <v>1470</v>
+        <v>1568</v>
       </c>
       <c r="F16" t="s">
         <v>207</v>
@@ -16890,19 +18188,19 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>1471</v>
+        <v>1569</v>
       </c>
       <c r="B17" t="s">
-        <v>1472</v>
+        <v>1570</v>
       </c>
       <c r="C17" t="s">
-        <v>1473</v>
+        <v>1571</v>
       </c>
       <c r="D17" t="s">
-        <v>1474</v>
+        <v>1572</v>
       </c>
       <c r="E17" t="s">
-        <v>1475</v>
+        <v>1573</v>
       </c>
       <c r="F17" t="s">
         <v>378</v>
@@ -16924,7 +18222,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>1476</v>
+        <v>1574</v>
       </c>
       <c r="B1"/>
       <c r="C1"/>
@@ -16934,7 +18232,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1477</v>
+        <v>1575</v>
       </c>
       <c r="B2"/>
       <c r="C2"/>
@@ -16944,162 +18242,162 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1478</v>
+        <v>1576</v>
       </c>
       <c r="B4" t="s">
-        <v>1376</v>
+        <v>1474</v>
       </c>
       <c r="C4" t="s">
-        <v>1479</v>
+        <v>1577</v>
       </c>
       <c r="D4" t="s">
-        <v>1480</v>
+        <v>1578</v>
       </c>
       <c r="E4" t="s">
-        <v>1033</v>
+        <v>1129</v>
       </c>
       <c r="F4" t="s">
-        <v>1481</v>
+        <v>1579</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1036</v>
+        <v>1132</v>
       </c>
       <c r="B5" t="s">
-        <v>1482</v>
+        <v>1580</v>
       </c>
       <c r="C5" t="s">
-        <v>1483</v>
+        <v>1581</v>
       </c>
       <c r="D5" t="s">
-        <v>1484</v>
+        <v>1582</v>
       </c>
       <c r="E5" t="s">
-        <v>1485</v>
+        <v>1583</v>
       </c>
       <c r="F5" t="s">
-        <v>1486</v>
+        <v>1584</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>1041</v>
+        <v>1137</v>
       </c>
       <c r="B6" t="s">
-        <v>1487</v>
+        <v>1585</v>
       </c>
       <c r="C6" t="s">
-        <v>1488</v>
+        <v>1586</v>
       </c>
       <c r="D6" t="s">
-        <v>1489</v>
+        <v>1587</v>
       </c>
       <c r="E6" t="s">
-        <v>1490</v>
+        <v>1588</v>
       </c>
       <c r="F6" t="s">
-        <v>1486</v>
+        <v>1584</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>1045</v>
+        <v>1141</v>
       </c>
       <c r="B7" t="s">
-        <v>1491</v>
+        <v>1589</v>
       </c>
       <c r="C7" t="s">
-        <v>1492</v>
+        <v>1590</v>
       </c>
       <c r="D7" t="s">
-        <v>1493</v>
+        <v>1591</v>
       </c>
       <c r="E7" t="s">
-        <v>1494</v>
+        <v>1592</v>
       </c>
       <c r="F7" t="s">
-        <v>1486</v>
+        <v>1584</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>1049</v>
+        <v>1145</v>
       </c>
       <c r="B8" t="s">
-        <v>1495</v>
+        <v>1593</v>
       </c>
       <c r="C8" t="s">
-        <v>1496</v>
+        <v>1594</v>
       </c>
       <c r="D8" t="s">
-        <v>1497</v>
+        <v>1595</v>
       </c>
       <c r="E8" t="s">
-        <v>1498</v>
+        <v>1596</v>
       </c>
       <c r="F8" t="s">
-        <v>1486</v>
+        <v>1584</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>1053</v>
+        <v>1149</v>
       </c>
       <c r="B9" t="s">
-        <v>1499</v>
+        <v>1597</v>
       </c>
       <c r="C9" t="s">
-        <v>1500</v>
+        <v>1598</v>
       </c>
       <c r="D9" t="s">
-        <v>1501</v>
+        <v>1599</v>
       </c>
       <c r="E9" t="s">
         <v>877</v>
       </c>
       <c r="F9" t="s">
-        <v>1502</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>1057</v>
+        <v>1153</v>
       </c>
       <c r="B10" t="s">
-        <v>1503</v>
+        <v>1601</v>
       </c>
       <c r="C10" t="s">
-        <v>1504</v>
+        <v>1602</v>
       </c>
       <c r="D10" t="s">
-        <v>1505</v>
+        <v>1603</v>
       </c>
       <c r="E10" t="s">
-        <v>1506</v>
+        <v>1604</v>
       </c>
       <c r="F10" t="s">
-        <v>1502</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>1061</v>
+        <v>1157</v>
       </c>
       <c r="B11" t="s">
-        <v>1507</v>
+        <v>1605</v>
       </c>
       <c r="C11" t="s">
-        <v>1508</v>
+        <v>1606</v>
       </c>
       <c r="D11" t="s">
-        <v>1509</v>
+        <v>1607</v>
       </c>
       <c r="E11" t="s">
-        <v>1510</v>
+        <v>1608</v>
       </c>
       <c r="F11" t="s">
-        <v>1511</v>
+        <v>1609</v>
       </c>
     </row>
   </sheetData>

--- a/audits/FORTLESS_MASTER_SECURITY_UI_BUG_TRACKER.xlsx
+++ b/audits/FORTLESS_MASTER_SECURITY_UI_BUG_TRACKER.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4070" uniqueCount="1610">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4232" uniqueCount="1660">
   <si>
     <t>FORTLESS   /   ENGINEERING FINDINGS REGISTER</t>
   </si>
@@ -3153,6 +3153,9 @@
     <t>Test: simulated timeout on delete/rename returns pending with an audit entry; no blind retry.</t>
   </si>
   <si>
+    <t>[CONFIRMED_CODE] Source trace. | Batch 5: the same missing pending handling applies to server-panel.ts (backups, network, startup, databases, schedules, reinstall).</t>
+  </si>
+  <si>
     <t>NEW-382</t>
   </si>
   <si>
@@ -3297,6 +3300,144 @@
     <t>[CONFIRMED_CODE] Source trace; panel-side behaviour is TEST_NEEDED on the sandbox panel.</t>
   </si>
   <si>
+    <t>NEW-388</t>
+  </si>
+  <si>
+    <t>Staff relink hands any unlinked panel server to the customer, and the DB update, panel access step and audit event are not atomic</t>
+  </si>
+  <si>
+    <t>2fc2350</t>
+  </si>
+  <si>
+    <t>src/modules/provisioning/runtime-sync.ts:231-265</t>
+  </si>
+  <si>
+    <t>relinkService only checks that the panel server id is not linked to another Fortless service, then calls assignServerOwner (line 253) so the customer's panel user takes over the server, whoever owned it. The services UPDATE (257) and state reset run outside a transaction, then ensureAccountPanelAccess (259) can throw before the audit insert (262).</t>
+  </si>
+  <si>
+    <t>A mistyped id transfers an unrelated panel server (another customer's or an admin-created one) to this account. If the access step fails, services.external_id already points at the new server but no service.relinked audit event exists.</t>
+  </si>
+  <si>
+    <t>Show the current panel owner and require explicit confirmation of it, write an intent audit event first, and apply local changes in one transaction after the provider steps succeed.</t>
+  </si>
+  <si>
+    <t>Test: relinking a server owned by another panel user is refused or needs an explicit confirmation field; a simulated failure in ensureAccountPanelAccess still leaves an audit trail and consistent state.</t>
+  </si>
+  <si>
+    <t>[CONFIRMED_CODE] Source trace; staff action behind services:manage and step-up.</t>
+  </si>
+  <si>
+    <t>NEW-389</t>
+  </si>
+  <si>
+    <t>Panel reconcile deletes every shared member when the subuser listing is empty or malformed</t>
+  </si>
+  <si>
+    <t>src/modules/provisioning/runtime-sync.ts:200-215</t>
+  </si>
+  <si>
+    <t>live = new Set((res?.data ?? []).map(...)); any member whose uuid is not in live is deleted from service_members. A 200 response without a data array (proxy page, API change, partial outage) yields an empty set and revokes all members of that service, with a service.member.revoked_on_panel audit event each.</t>
+  </si>
+  <si>
+    <t>Customers lose shared access in Fortless although they are still subusers on the panel; recovery requires re-inviting, and panel-side access remains unmanaged.</t>
+  </si>
+  <si>
+    <t>Treat a response without Array.isArray(data) as an error, require pagination to be fully read, and revoke only after two consecutive consistent observations.</t>
+  </si>
+  <si>
+    <t>Test: a mocked 200 with {} leaves service_members unchanged and logs a reconcile error.</t>
+  </si>
+  <si>
+    <t>NEW-390</t>
+  </si>
+  <si>
+    <t>Destructive customer operations need no fresh verification or server-side confirmation</t>
+  </si>
+  <si>
+    <t>src/modules/provisioning/server-panel.ts:77-88,189,274-290; src/modules/provisioning/files.ts:94-100; src/server.ts (service panel routes)</t>
+  </si>
+  <si>
+    <t>Reinstall, backup delete, backup restore (truncate:true wipes files), database delete and file delete only check the per-operation permission. No requireRecentStepUp, no typed confirmation, no precondition that a fresh backup exists, unlike the staff equivalents.</t>
+  </si>
+  <si>
+    <t>A hijacked customer session (see NEW-366/NEW-367) can erase a server and its backups in a few requests.</t>
+  </si>
+  <si>
+    <t>Require recent step-up for reinstall, restore, backup delete and database delete, and a server-side confirmation token or typed name for reinstall/restore.</t>
+  </si>
+  <si>
+    <t>Test: these routes return STEP_UP_REQUIRED without a recent step-up.</t>
+  </si>
+  <si>
+    <t>[CONFIRMED_CODE] Source trace; whether this is required is a product decision.</t>
+  </si>
+  <si>
+    <t>NEW-391</t>
+  </si>
+  <si>
+    <t>Database passwords are returned to users with database.view_password without an audit event</t>
+  </si>
+  <si>
+    <t>src/modules/provisioning/server-panel.ts:158-172</t>
+  </si>
+  <si>
+    <t>databases() requests /databases?include=password and returns the plaintext password in the response; only rotate/create/delete write audit events.</t>
+  </si>
+  <si>
+    <t>Credential disclosure to a shared admin leaves no trace.</t>
+  </si>
+  <si>
+    <t>Audit every response that includes passwords, or fetch them only on an explicit reveal action.</t>
+  </si>
+  <si>
+    <t>Test: listing databases as an admin preset writes a service.database.password_viewed event.</t>
+  </si>
+  <si>
+    <t>NEW-392</t>
+  </si>
+  <si>
+    <t>Reinstall completion is inferred from the first running/offline reading, which can precede the real install start</t>
+  </si>
+  <si>
+    <t>src/modules/provisioning/runtime-sync.ts:51-58,73-105</t>
+  </si>
+  <si>
+    <t>After a reinstall request the state is set to INSTALLING locally. The next sync that sees Wings state running or offline calls completeReinstall, writes reinstall_completed and queues the service_ready email, without checking an install-complete signal.</t>
+  </si>
+  <si>
+    <t>The customer may get "service ready" while the reinstall has not started or is still running, and the UI leaves INSTALLING early.</t>
+  </si>
+  <si>
+    <t>Use the panel's installing flag (server status) or the install completion websocket event instead of the Wings state alone.</t>
+  </si>
+  <si>
+    <t>Test: with a mocked panel that reports offline for 30 s before installation begins, the state stays INSTALLING until the install flag clears.</t>
+  </si>
+  <si>
+    <t>[CONFIRMED_CODE] Source trace; behaviour against a real panel is TEST_NEEDED.</t>
+  </si>
+  <si>
+    <t>NEW-393</t>
+  </si>
+  <si>
+    <t>Accepting a service invitation is not retry-safe: the panel subuser is created before the local row and a timeout or DB failure leaves an orphan with real permissions</t>
+  </si>
+  <si>
+    <t>src/modules/provisioning/service-members.ts:128-166</t>
+  </si>
+  <si>
+    <t>accept() calls POST /users on the panel (line 152) and only then inserts service_members. A timeout or a DB error after the panel call leaves a subuser with the preset permissions and no Fortless row; retrying makes the panel refuse (already exists) and the code maps that to PANEL_REFUSED 409.</t>
+  </si>
+  <si>
+    <t>The invitation can become impossible to accept while the invitee already has panel-side access that Fortless neither shows nor revokes (reconcile only handles the opposite direction).</t>
+  </si>
+  <si>
+    <t>Treat ProviderNetworkError as unknown, look up the existing subuser by email before creating, and reconcile panel-only subusers.</t>
+  </si>
+  <si>
+    <t>Test: simulate a timeout after the panel call; the retry adopts the existing subuser and creates the member row once.</t>
+  </si>
+  <si>
     <t>FORTLESS   /   SECURITY &amp; PRODUCT QUALITY</t>
   </si>
   <si>
@@ -3315,10 +3456,10 @@
     <t>CLOSED &amp; TESTED</t>
   </si>
   <si>
-    <t>132</t>
-  </si>
-  <si>
-    <t>48</t>
+    <t>138</t>
+  </si>
+  <si>
+    <t>52</t>
   </si>
   <si>
     <t>58</t>
@@ -3345,336 +3486,339 @@
     <t>39</t>
   </si>
   <si>
-    <t>8</t>
+    <t>9</t>
   </si>
   <si>
     <t>69</t>
   </si>
   <si>
-    <t>3</t>
+    <t>4</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>TESTED</t>
+  </si>
+  <si>
+    <t>CLOSED</t>
+  </si>
+  <si>
+    <t>LATEST VERIFIED COMMIT</t>
+  </si>
+  <si>
+    <t>REGRESSION</t>
+  </si>
+  <si>
+    <t>3cb35de (independent audit batch 1)</t>
+  </si>
+  <si>
+    <t>STATUS CONTRACT</t>
+  </si>
+  <si>
+    <t>Issue present in inspected source</t>
+  </si>
+  <si>
+    <t>Some code fixed; unresolved conditions remain</t>
+  </si>
+  <si>
+    <t>Fix observed in source; still needs regression/runtime validation</t>
+  </si>
+  <si>
+    <t>Question or risk not independently demonstrated</t>
+  </si>
+  <si>
+    <t>Requires an explicit product/security policy</t>
+  </si>
+  <si>
+    <t>Automated/authorized tests executed and evidence stored</t>
+  </si>
+  <si>
+    <t>Fix independently verified and accepted</t>
+  </si>
+  <si>
+    <t>Previously fixed behavior has returned</t>
+  </si>
+  <si>
+    <t>FORTLESS   /   30 SECURITY AUDIT DOMAINS</t>
+  </si>
+  <si>
+    <t>Static source review expanded at 6203687. Coverage is NOT an independent runtime, load, security or pixel-diff test.</t>
+  </si>
+  <si>
+    <t>#</t>
+  </si>
+  <si>
+    <t>Scope</t>
+  </si>
+  <si>
+    <t>Related finding IDs</t>
+  </si>
+  <si>
+    <t>Audit coverage</t>
+  </si>
+  <si>
+    <t>01</t>
+  </si>
+  <si>
+    <t>Authentication</t>
+  </si>
+  <si>
+    <t>Login/register/reset, brute force, enumeration</t>
+  </si>
+  <si>
+    <t>SEC-09, FTL-SEC-205, NEW-362, NEW-363, NEW-364, NEW-365, NEW-366, NEW-367</t>
+  </si>
+  <si>
+    <t>STATIC_PARTIAL</t>
+  </si>
+  <si>
+    <t>02</t>
+  </si>
+  <si>
+    <t>Sessions &amp; Devices</t>
+  </si>
+  <si>
+    <t>Token rotation, expiry, login/logout, revocation</t>
+  </si>
+  <si>
+    <t>SEC-03, SEC-04, FTL-SEC-202, NEW-363, NEW-368, NEW-377</t>
+  </si>
+  <si>
+    <t>03</t>
+  </si>
+  <si>
+    <t>MFA &amp; Passkeys</t>
+  </si>
+  <si>
+    <t>TOTP, WebAuthn, recovery, replay, UV</t>
+  </si>
+  <si>
+    <t>FTL-SEC-201, FTL-SEC-202, FTL-SEC-203, NEW-306, NEW-307, NEW-318, NEW-358, NEW-360, NEW-366, NEW-367</t>
+  </si>
+  <si>
+    <t>04</t>
+  </si>
+  <si>
+    <t>Authorization / RBAC</t>
+  </si>
+  <si>
+    <t>Every API permission and role</t>
+  </si>
+  <si>
+    <t>FTL-UI-201, SSO-01, NEW-322, NEW-328, NEW-359, NEW-376, NEW-378, NEW-379, NEW-387, NEW-390</t>
+  </si>
+  <si>
+    <t>05</t>
+  </si>
+  <si>
+    <t>IDOR / BOLA</t>
+  </si>
+  <si>
+    <t>Cross-account resource access</t>
+  </si>
+  <si>
+    <t>SEC-05, NEW-310, NEW-322</t>
+  </si>
+  <si>
+    <t>06</t>
+  </si>
+  <si>
+    <t>Multi-tenancy</t>
+  </si>
+  <si>
+    <t>Organization/service separation</t>
+  </si>
+  <si>
+    <t>SEC-05, SEC-06, NEW-310, NEW-322</t>
+  </si>
+  <si>
+    <t>07</t>
+  </si>
+  <si>
+    <t>API Security</t>
+  </si>
+  <si>
+    <t>Request validation/mass assignment/rate limiting</t>
+  </si>
+  <si>
+    <t>FTL-SEC-205, NEW-311, NEW-321, NEW-328</t>
+  </si>
+  <si>
+    <t>08</t>
+  </si>
+  <si>
+    <t>CSRF &amp; CORS</t>
+  </si>
+  <si>
+    <t>Origin, cookies, CSRF all writes</t>
+  </si>
+  <si>
+    <t>RUNTIME_REQUIRED</t>
+  </si>
+  <si>
+    <t>09</t>
+  </si>
+  <si>
+    <t>XSS &amp; HTML Injection</t>
+  </si>
+  <si>
+    <t>Ticket/email/console/DOM output</t>
+  </si>
+  <si>
+    <t>UI-06, MAIL-01</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>SQL / Command Injection</t>
+  </si>
+  <si>
+    <t>SQL/shell/path/template injection</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>SSRF</t>
+  </si>
+  <si>
+    <t>Private IP, DNS rebinding, redirects</t>
+  </si>
+  <si>
+    <t>SEC-08, NEW-314</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>Secrets &amp; Credentials</t>
+  </si>
+  <si>
+    <t>Provider keys, vault, rotation</t>
+  </si>
+  <si>
+    <t>NEW-313, SEC-02, NEW-323</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>Pterodactyl API</t>
+  </si>
+  <si>
+    <t>Provider scoping &amp; ownership</t>
+  </si>
+  <si>
+    <t>FTL-PROV-201, FTL-UI-202, NEW-322, NEW-323, NEW-389, NEW-393</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>OIDC callback, native reset, revoke</t>
+  </si>
+  <si>
+    <t>SSO-01, SSO-02, SSO-03, NEW-387</t>
+  </si>
+  <si>
+    <t>Wings &amp; WebSockets</t>
+  </si>
+  <si>
+    <t>Socket tokens, console, revocation</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>File Manager</t>
+  </si>
+  <si>
+    <t>Traversal, archives, symlinks, quota</t>
+  </si>
+  <si>
+    <t>NEW-314, NEW-321, NEW-381, NEW-382</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>Minecraft Installers</t>
+  </si>
+  <si>
+    <t>SHA512, compatibility, redirect, limits</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>Web App Isolation</t>
+  </si>
+  <si>
+    <t>Container isolation, network, privilege</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>Stripe &amp; Payments</t>
+  </si>
+  <si>
+    <t>Signatures, replay, idempotency, ordering</t>
+  </si>
+  <si>
+    <t>FTL-BILL-201, FTL-BILL-203, FTL-BILL-204, FTL-BILL-206, NEW-324, NEW-340, NEW-345, NEW-346, NEW-347, NEW-349, NEW-350</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>Billing &amp; Subscriptions</t>
+  </si>
+  <si>
+    <t>Renewal, refunds, tax, coupons, invoices</t>
+  </si>
+  <si>
+    <t>FTL-BILL-202, FTL-BILL-205, NEW-301, NEW-303, NEW-304, NEW-305, NEW-316, NEW-319, NEW-324, NEW-330, NEW-333, NEW-334, NEW-338, NEW-344, NEW-348, NEW-351, NEW-352, NEW-353, NEW-355, NEW-356</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>Node, cap, retry, lifecycle</t>
+  </si>
+  <si>
+    <t>FTL-PROV-201, FTL-PROV-202, FTL-PROV-203, FTL-PROV-204, NEW-302, NEW-322, NEW-327, NEW-352, NEW-357, NEW-386, NEW-388, NEW-392</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>cPanel / WHM</t>
+  </si>
+  <si>
+    <t>Permission, lifecycle, safe API</t>
+  </si>
+  <si>
+    <t>FTL-PROV-201, SEC-08</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>Proxmox / VPS</t>
+  </si>
+  <si>
+    <t>VM isolation, templates, snapshots</t>
+  </si>
+  <si>
+    <t>FTL-PROV-201, NEW-326, NEW-327</t>
   </si>
   <si>
     <t>24</t>
   </si>
   <si>
-    <t>TESTED</t>
-  </si>
-  <si>
-    <t>CLOSED</t>
-  </si>
-  <si>
-    <t>LATEST VERIFIED COMMIT</t>
-  </si>
-  <si>
-    <t>REGRESSION</t>
-  </si>
-  <si>
-    <t>3cb35de (independent audit batch 1)</t>
-  </si>
-  <si>
-    <t>STATUS CONTRACT</t>
-  </si>
-  <si>
-    <t>Issue present in inspected source</t>
-  </si>
-  <si>
-    <t>Some code fixed; unresolved conditions remain</t>
-  </si>
-  <si>
-    <t>Fix observed in source; still needs regression/runtime validation</t>
-  </si>
-  <si>
-    <t>Question or risk not independently demonstrated</t>
-  </si>
-  <si>
-    <t>Requires an explicit product/security policy</t>
-  </si>
-  <si>
-    <t>Automated/authorized tests executed and evidence stored</t>
-  </si>
-  <si>
-    <t>Fix independently verified and accepted</t>
-  </si>
-  <si>
-    <t>Previously fixed behavior has returned</t>
-  </si>
-  <si>
-    <t>FORTLESS   /   30 SECURITY AUDIT DOMAINS</t>
-  </si>
-  <si>
-    <t>Static source review expanded at 6203687. Coverage is NOT an independent runtime, load, security or pixel-diff test.</t>
-  </si>
-  <si>
-    <t>#</t>
-  </si>
-  <si>
-    <t>Scope</t>
-  </si>
-  <si>
-    <t>Related finding IDs</t>
-  </si>
-  <si>
-    <t>Audit coverage</t>
-  </si>
-  <si>
-    <t>01</t>
-  </si>
-  <si>
-    <t>Authentication</t>
-  </si>
-  <si>
-    <t>Login/register/reset, brute force, enumeration</t>
-  </si>
-  <si>
-    <t>SEC-09, FTL-SEC-205, NEW-362, NEW-363, NEW-364, NEW-365, NEW-366, NEW-367</t>
-  </si>
-  <si>
-    <t>STATIC_PARTIAL</t>
-  </si>
-  <si>
-    <t>02</t>
-  </si>
-  <si>
-    <t>Sessions &amp; Devices</t>
-  </si>
-  <si>
-    <t>Token rotation, expiry, login/logout, revocation</t>
-  </si>
-  <si>
-    <t>SEC-03, SEC-04, FTL-SEC-202, NEW-363, NEW-368, NEW-377</t>
-  </si>
-  <si>
-    <t>03</t>
-  </si>
-  <si>
-    <t>MFA &amp; Passkeys</t>
-  </si>
-  <si>
-    <t>TOTP, WebAuthn, recovery, replay, UV</t>
-  </si>
-  <si>
-    <t>FTL-SEC-201, FTL-SEC-202, FTL-SEC-203, NEW-306, NEW-307, NEW-318, NEW-358, NEW-360, NEW-366, NEW-367</t>
-  </si>
-  <si>
-    <t>04</t>
-  </si>
-  <si>
-    <t>Authorization / RBAC</t>
-  </si>
-  <si>
-    <t>Every API permission and role</t>
-  </si>
-  <si>
-    <t>FTL-UI-201, SSO-01, NEW-322, NEW-328, NEW-359, NEW-376, NEW-378, NEW-379, NEW-387</t>
-  </si>
-  <si>
-    <t>05</t>
-  </si>
-  <si>
-    <t>IDOR / BOLA</t>
-  </si>
-  <si>
-    <t>Cross-account resource access</t>
-  </si>
-  <si>
-    <t>SEC-05, NEW-310, NEW-322</t>
-  </si>
-  <si>
-    <t>06</t>
-  </si>
-  <si>
-    <t>Multi-tenancy</t>
-  </si>
-  <si>
-    <t>Organization/service separation</t>
-  </si>
-  <si>
-    <t>SEC-05, SEC-06, NEW-310, NEW-322</t>
-  </si>
-  <si>
-    <t>07</t>
-  </si>
-  <si>
-    <t>API Security</t>
-  </si>
-  <si>
-    <t>Request validation/mass assignment/rate limiting</t>
-  </si>
-  <si>
-    <t>FTL-SEC-205, NEW-311, NEW-321, NEW-328</t>
-  </si>
-  <si>
-    <t>08</t>
-  </si>
-  <si>
-    <t>CSRF &amp; CORS</t>
-  </si>
-  <si>
-    <t>Origin, cookies, CSRF all writes</t>
-  </si>
-  <si>
-    <t>RUNTIME_REQUIRED</t>
-  </si>
-  <si>
-    <t>09</t>
-  </si>
-  <si>
-    <t>XSS &amp; HTML Injection</t>
-  </si>
-  <si>
-    <t>Ticket/email/console/DOM output</t>
-  </si>
-  <si>
-    <t>UI-06, MAIL-01</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>SQL / Command Injection</t>
-  </si>
-  <si>
-    <t>SQL/shell/path/template injection</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>SSRF</t>
-  </si>
-  <si>
-    <t>Private IP, DNS rebinding, redirects</t>
-  </si>
-  <si>
-    <t>SEC-08, NEW-314</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>Secrets &amp; Credentials</t>
-  </si>
-  <si>
-    <t>Provider keys, vault, rotation</t>
-  </si>
-  <si>
-    <t>NEW-313, SEC-02, NEW-323</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>Pterodactyl API</t>
-  </si>
-  <si>
-    <t>Provider scoping &amp; ownership</t>
-  </si>
-  <si>
-    <t>FTL-PROV-201, FTL-UI-202, NEW-322, NEW-323</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>OIDC callback, native reset, revoke</t>
-  </si>
-  <si>
-    <t>SSO-01, SSO-02, SSO-03, NEW-387</t>
-  </si>
-  <si>
-    <t>Wings &amp; WebSockets</t>
-  </si>
-  <si>
-    <t>Socket tokens, console, revocation</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>File Manager</t>
-  </si>
-  <si>
-    <t>Traversal, archives, symlinks, quota</t>
-  </si>
-  <si>
-    <t>NEW-314, NEW-321, NEW-381, NEW-382</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>Minecraft Installers</t>
-  </si>
-  <si>
-    <t>SHA512, compatibility, redirect, limits</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>Web App Isolation</t>
-  </si>
-  <si>
-    <t>Container isolation, network, privilege</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>Stripe &amp; Payments</t>
-  </si>
-  <si>
-    <t>Signatures, replay, idempotency, ordering</t>
-  </si>
-  <si>
-    <t>FTL-BILL-201, FTL-BILL-203, FTL-BILL-204, FTL-BILL-206, NEW-324, NEW-340, NEW-345, NEW-346, NEW-347, NEW-349, NEW-350</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>Billing &amp; Subscriptions</t>
-  </si>
-  <si>
-    <t>Renewal, refunds, tax, coupons, invoices</t>
-  </si>
-  <si>
-    <t>FTL-BILL-202, FTL-BILL-205, NEW-301, NEW-303, NEW-304, NEW-305, NEW-316, NEW-319, NEW-324, NEW-330, NEW-333, NEW-334, NEW-338, NEW-344, NEW-348, NEW-351, NEW-352, NEW-353, NEW-355, NEW-356</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>Node, cap, retry, lifecycle</t>
-  </si>
-  <si>
-    <t>FTL-PROV-201, FTL-PROV-202, FTL-PROV-203, FTL-PROV-204, NEW-302, NEW-322, NEW-327, NEW-352, NEW-357, NEW-386</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>cPanel / WHM</t>
-  </si>
-  <si>
-    <t>Permission, lifecycle, safe API</t>
-  </si>
-  <si>
-    <t>FTL-PROV-201, SEC-08</t>
-  </si>
-  <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>Proxmox / VPS</t>
-  </si>
-  <si>
-    <t>VM isolation, templates, snapshots</t>
-  </si>
-  <si>
-    <t>FTL-PROV-201, NEW-326, NEW-327</t>
-  </si>
-  <si>
     <t>DNS &amp; Domains</t>
   </si>
   <si>
@@ -3741,13 +3885,10 @@
     <t>NEW-308, NEW-309, NEW-313, NEW-327, NEW-373, NEW-374, NEW-375</t>
   </si>
   <si>
-    <t>30</t>
-  </si>
-  <si>
     <t>Audit integrity, alerts, events</t>
   </si>
   <si>
-    <t>SEC-09, NEW-322, NEW-380</t>
+    <t>SEC-09, NEW-322, NEW-380, NEW-391</t>
   </si>
   <si>
     <t>FORTLESS   /   COMMIT &amp; AUDIT HISTORY</t>
@@ -3961,6 +4102,15 @@
   </si>
   <si>
     <t>Staff routes, session lifecycle, DNS record paths, file manager, AI adapter and service sharing read in source. No implementation code changed.</t>
+  </si>
+  <si>
+    <t>2026-10-19 08:40</t>
+  </si>
+  <si>
+    <t>Independent audit batch 5: panel operations, reconcile, relink, sharing (NEW-388..NEW-393)</t>
+  </si>
+  <si>
+    <t>server-panel, runtime-sync, relink and service-members read in source. No implementation code changed.</t>
   </si>
   <si>
     <t>FORTLESS   /   IMMUTABLE STATUS HISTORY</t>
@@ -5225,7 +5375,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:S135"/>
+  <dimension ref="A1:S141"/>
   <sheetFormatPr defaultRowHeight="0" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" customHeight="1"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
@@ -12557,12 +12707,12 @@
         <v>36</v>
       </c>
       <c r="S129" t="s">
-        <v>765</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="130" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="B130" t="s">
         <v>308</v>
@@ -12574,7 +12724,7 @@
         <v>959</v>
       </c>
       <c r="E130" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="F130" t="s">
         <v>112</v>
@@ -12592,19 +12742,19 @@
         <v>999</v>
       </c>
       <c r="K130" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="L130" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="M130" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="N130" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="O130" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="P130" t="s">
         <v>747</v>
@@ -12616,12 +12766,12 @@
         <v>36</v>
       </c>
       <c r="S130" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="131" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="B131" t="s">
         <v>308</v>
@@ -12630,10 +12780,10 @@
         <v>309</v>
       </c>
       <c r="D131" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="E131" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="F131" t="s">
         <v>112</v>
@@ -12651,19 +12801,19 @@
         <v>999</v>
       </c>
       <c r="K131" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="L131" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="M131" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="N131" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="O131" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="P131" t="s">
         <v>747</v>
@@ -12680,7 +12830,7 @@
     </row>
     <row r="132" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="B132" t="s">
         <v>308</v>
@@ -12692,7 +12842,7 @@
         <v>959</v>
       </c>
       <c r="E132" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="F132" t="s">
         <v>112</v>
@@ -12710,19 +12860,19 @@
         <v>999</v>
       </c>
       <c r="K132" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="L132" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="M132" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="N132" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="O132" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="P132" t="s">
         <v>747</v>
@@ -12739,7 +12889,7 @@
     </row>
     <row r="133" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="B133" t="s">
         <v>61</v>
@@ -12751,7 +12901,7 @@
         <v>247</v>
       </c>
       <c r="E133" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="F133" t="s">
         <v>95</v>
@@ -12769,19 +12919,19 @@
         <v>999</v>
       </c>
       <c r="K133" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="L133" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="M133" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="N133" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="O133" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="P133" t="s">
         <v>747</v>
@@ -12793,12 +12943,12 @@
         <v>36</v>
       </c>
       <c r="S133" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="134" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="B134" t="s">
         <v>308</v>
@@ -12807,10 +12957,10 @@
         <v>62</v>
       </c>
       <c r="D134" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="E134" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="F134" t="s">
         <v>112</v>
@@ -12828,19 +12978,19 @@
         <v>999</v>
       </c>
       <c r="K134" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="L134" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="M134" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="N134" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="O134" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="P134" t="s">
         <v>747</v>
@@ -12852,12 +13002,12 @@
         <v>36</v>
       </c>
       <c r="S134" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="135" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="B135" t="s">
         <v>308</v>
@@ -12869,7 +13019,7 @@
         <v>630</v>
       </c>
       <c r="E135" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="F135" t="s">
         <v>95</v>
@@ -12887,19 +13037,19 @@
         <v>999</v>
       </c>
       <c r="K135" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="L135" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="M135" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="N135" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="O135" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="P135" t="s">
         <v>747</v>
@@ -12911,7 +13061,361 @@
         <v>36</v>
       </c>
       <c r="S135" t="s">
-        <v>1091</v>
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="136" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>1093</v>
+      </c>
+      <c r="B136" t="s">
+        <v>308</v>
+      </c>
+      <c r="C136" t="s">
+        <v>62</v>
+      </c>
+      <c r="D136" t="s">
+        <v>214</v>
+      </c>
+      <c r="E136" t="s">
+        <v>1094</v>
+      </c>
+      <c r="F136" t="s">
+        <v>112</v>
+      </c>
+      <c r="G136" t="s">
+        <v>27</v>
+      </c>
+      <c r="H136" t="s">
+        <v>27</v>
+      </c>
+      <c r="I136" t="s">
+        <v>1095</v>
+      </c>
+      <c r="J136" t="s">
+        <v>1095</v>
+      </c>
+      <c r="K136" t="s">
+        <v>1096</v>
+      </c>
+      <c r="L136" t="s">
+        <v>1097</v>
+      </c>
+      <c r="M136" t="s">
+        <v>1098</v>
+      </c>
+      <c r="N136" t="s">
+        <v>1099</v>
+      </c>
+      <c r="O136" t="s">
+        <v>1100</v>
+      </c>
+      <c r="P136" t="s">
+        <v>747</v>
+      </c>
+      <c r="Q136" t="s">
+        <v>924</v>
+      </c>
+      <c r="R136" t="s">
+        <v>36</v>
+      </c>
+      <c r="S136" t="s">
+        <v>1101</v>
+      </c>
+    </row>
+    <row r="137" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>1102</v>
+      </c>
+      <c r="B137" t="s">
+        <v>308</v>
+      </c>
+      <c r="C137" t="s">
+        <v>62</v>
+      </c>
+      <c r="D137" t="s">
+        <v>214</v>
+      </c>
+      <c r="E137" t="s">
+        <v>1103</v>
+      </c>
+      <c r="F137" t="s">
+        <v>112</v>
+      </c>
+      <c r="G137" t="s">
+        <v>27</v>
+      </c>
+      <c r="H137" t="s">
+        <v>27</v>
+      </c>
+      <c r="I137" t="s">
+        <v>1095</v>
+      </c>
+      <c r="J137" t="s">
+        <v>1095</v>
+      </c>
+      <c r="K137" t="s">
+        <v>1104</v>
+      </c>
+      <c r="L137" t="s">
+        <v>1105</v>
+      </c>
+      <c r="M137" t="s">
+        <v>1106</v>
+      </c>
+      <c r="N137" t="s">
+        <v>1107</v>
+      </c>
+      <c r="O137" t="s">
+        <v>1108</v>
+      </c>
+      <c r="P137" t="s">
+        <v>747</v>
+      </c>
+      <c r="Q137" t="s">
+        <v>924</v>
+      </c>
+      <c r="R137" t="s">
+        <v>36</v>
+      </c>
+      <c r="S137" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="138" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>1109</v>
+      </c>
+      <c r="B138" t="s">
+        <v>308</v>
+      </c>
+      <c r="C138" t="s">
+        <v>62</v>
+      </c>
+      <c r="D138" t="s">
+        <v>630</v>
+      </c>
+      <c r="E138" t="s">
+        <v>1110</v>
+      </c>
+      <c r="F138" t="s">
+        <v>453</v>
+      </c>
+      <c r="G138" t="s">
+        <v>27</v>
+      </c>
+      <c r="H138" t="s">
+        <v>27</v>
+      </c>
+      <c r="I138" t="s">
+        <v>1095</v>
+      </c>
+      <c r="J138" t="s">
+        <v>1095</v>
+      </c>
+      <c r="K138" t="s">
+        <v>1111</v>
+      </c>
+      <c r="L138" t="s">
+        <v>1112</v>
+      </c>
+      <c r="M138" t="s">
+        <v>1113</v>
+      </c>
+      <c r="N138" t="s">
+        <v>1114</v>
+      </c>
+      <c r="O138" t="s">
+        <v>1115</v>
+      </c>
+      <c r="P138" t="s">
+        <v>747</v>
+      </c>
+      <c r="Q138" t="s">
+        <v>924</v>
+      </c>
+      <c r="R138" t="s">
+        <v>36</v>
+      </c>
+      <c r="S138" t="s">
+        <v>1116</v>
+      </c>
+    </row>
+    <row r="139" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>1117</v>
+      </c>
+      <c r="B139" t="s">
+        <v>308</v>
+      </c>
+      <c r="C139" t="s">
+        <v>309</v>
+      </c>
+      <c r="D139" t="s">
+        <v>1030</v>
+      </c>
+      <c r="E139" t="s">
+        <v>1118</v>
+      </c>
+      <c r="F139" t="s">
+        <v>112</v>
+      </c>
+      <c r="G139" t="s">
+        <v>27</v>
+      </c>
+      <c r="H139" t="s">
+        <v>27</v>
+      </c>
+      <c r="I139" t="s">
+        <v>1095</v>
+      </c>
+      <c r="J139" t="s">
+        <v>1095</v>
+      </c>
+      <c r="K139" t="s">
+        <v>1119</v>
+      </c>
+      <c r="L139" t="s">
+        <v>1120</v>
+      </c>
+      <c r="M139" t="s">
+        <v>1121</v>
+      </c>
+      <c r="N139" t="s">
+        <v>1122</v>
+      </c>
+      <c r="O139" t="s">
+        <v>1123</v>
+      </c>
+      <c r="P139" t="s">
+        <v>747</v>
+      </c>
+      <c r="Q139" t="s">
+        <v>924</v>
+      </c>
+      <c r="R139" t="s">
+        <v>36</v>
+      </c>
+      <c r="S139" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="140" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>1124</v>
+      </c>
+      <c r="B140" t="s">
+        <v>308</v>
+      </c>
+      <c r="C140" t="s">
+        <v>309</v>
+      </c>
+      <c r="D140" t="s">
+        <v>214</v>
+      </c>
+      <c r="E140" t="s">
+        <v>1125</v>
+      </c>
+      <c r="F140" t="s">
+        <v>95</v>
+      </c>
+      <c r="G140" t="s">
+        <v>27</v>
+      </c>
+      <c r="H140" t="s">
+        <v>27</v>
+      </c>
+      <c r="I140" t="s">
+        <v>1095</v>
+      </c>
+      <c r="J140" t="s">
+        <v>1095</v>
+      </c>
+      <c r="K140" t="s">
+        <v>1126</v>
+      </c>
+      <c r="L140" t="s">
+        <v>1127</v>
+      </c>
+      <c r="M140" t="s">
+        <v>1128</v>
+      </c>
+      <c r="N140" t="s">
+        <v>1129</v>
+      </c>
+      <c r="O140" t="s">
+        <v>1130</v>
+      </c>
+      <c r="P140" t="s">
+        <v>747</v>
+      </c>
+      <c r="Q140" t="s">
+        <v>924</v>
+      </c>
+      <c r="R140" t="s">
+        <v>36</v>
+      </c>
+      <c r="S140" t="s">
+        <v>1131</v>
+      </c>
+    </row>
+    <row r="141" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>1132</v>
+      </c>
+      <c r="B141" t="s">
+        <v>308</v>
+      </c>
+      <c r="C141" t="s">
+        <v>62</v>
+      </c>
+      <c r="D141" t="s">
+        <v>630</v>
+      </c>
+      <c r="E141" t="s">
+        <v>1133</v>
+      </c>
+      <c r="F141" t="s">
+        <v>112</v>
+      </c>
+      <c r="G141" t="s">
+        <v>27</v>
+      </c>
+      <c r="H141" t="s">
+        <v>27</v>
+      </c>
+      <c r="I141" t="s">
+        <v>1095</v>
+      </c>
+      <c r="J141" t="s">
+        <v>1095</v>
+      </c>
+      <c r="K141" t="s">
+        <v>1134</v>
+      </c>
+      <c r="L141" t="s">
+        <v>1135</v>
+      </c>
+      <c r="M141" t="s">
+        <v>1136</v>
+      </c>
+      <c r="N141" t="s">
+        <v>1137</v>
+      </c>
+      <c r="O141" t="s">
+        <v>1138</v>
+      </c>
+      <c r="P141" t="s">
+        <v>747</v>
+      </c>
+      <c r="Q141" t="s">
+        <v>924</v>
+      </c>
+      <c r="R141" t="s">
+        <v>36</v>
+      </c>
+      <c r="S141" t="s">
+        <v>765</v>
       </c>
     </row>
   </sheetData>
@@ -12925,48 +13429,48 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>1092</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1093</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1094</v>
+        <v>1141</v>
       </c>
       <c r="C4" t="s">
-        <v>1095</v>
+        <v>1142</v>
       </c>
       <c r="E4" t="s">
-        <v>1096</v>
+        <v>1143</v>
       </c>
       <c r="G4" t="s">
-        <v>1097</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1098</v>
+        <v>1145</v>
       </c>
       <c r="C5" t="s">
-        <v>1099</v>
+        <v>1146</v>
       </c>
       <c r="E5" t="s">
-        <v>1100</v>
+        <v>1147</v>
       </c>
       <c r="G5" t="s">
-        <v>1101</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>1102</v>
+        <v>1149</v>
       </c>
       <c r="F9" t="s">
-        <v>1103</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -12974,16 +13478,16 @@
         <v>112</v>
       </c>
       <c r="B10" t="s">
-        <v>1099</v>
+        <v>1146</v>
       </c>
       <c r="C10" t="s">
         <v>3</v>
       </c>
       <c r="D10" t="s">
-        <v>1104</v>
+        <v>1151</v>
       </c>
       <c r="F10" t="s">
-        <v>1105</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -12991,13 +13495,13 @@
         <v>86</v>
       </c>
       <c r="B11" t="s">
-        <v>1106</v>
+        <v>1153</v>
       </c>
       <c r="C11" t="s">
         <v>22</v>
       </c>
       <c r="D11" t="s">
-        <v>1107</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -13005,13 +13509,13 @@
         <v>95</v>
       </c>
       <c r="B12" t="s">
-        <v>1108</v>
+        <v>1155</v>
       </c>
       <c r="C12" t="s">
         <v>61</v>
       </c>
       <c r="D12" t="s">
-        <v>1109</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -13019,13 +13523,13 @@
         <v>453</v>
       </c>
       <c r="B13" t="s">
-        <v>1110</v>
+        <v>1157</v>
       </c>
       <c r="C13" t="s">
         <v>308</v>
       </c>
       <c r="D13" t="s">
-        <v>1111</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
@@ -13033,42 +13537,42 @@
         <v>26</v>
       </c>
       <c r="B14" t="s">
-        <v>1100</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>1112</v>
+        <v>1159</v>
       </c>
       <c r="B15" t="s">
-        <v>1101</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>1113</v>
+        <v>1160</v>
       </c>
       <c r="B16" t="s">
-        <v>1101</v>
+        <v>1148</v>
       </c>
       <c r="F16" t="s">
-        <v>1114</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>1115</v>
+        <v>1162</v>
       </c>
       <c r="B17" t="s">
-        <v>1101</v>
+        <v>1148</v>
       </c>
       <c r="F17" t="s">
-        <v>1116</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>1117</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
@@ -13076,7 +13580,7 @@
         <v>112</v>
       </c>
       <c r="C22" t="s">
-        <v>1118</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
@@ -13084,7 +13588,7 @@
         <v>86</v>
       </c>
       <c r="C23" t="s">
-        <v>1119</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
@@ -13092,7 +13596,7 @@
         <v>26</v>
       </c>
       <c r="C24" t="s">
-        <v>1120</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
@@ -13100,7 +13604,7 @@
         <v>95</v>
       </c>
       <c r="C25" t="s">
-        <v>1121</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
@@ -13108,31 +13612,31 @@
         <v>453</v>
       </c>
       <c r="C26" t="s">
-        <v>1122</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>1112</v>
+        <v>1159</v>
       </c>
       <c r="C27" t="s">
-        <v>1123</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>1113</v>
+        <v>1160</v>
       </c>
       <c r="C28" t="s">
-        <v>1124</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>1115</v>
+        <v>1162</v>
       </c>
       <c r="C29" t="s">
-        <v>1125</v>
+        <v>1172</v>
       </c>
     </row>
   </sheetData>
@@ -13146,7 +13650,7 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>1126</v>
+        <v>1173</v>
       </c>
       <c r="B1"/>
       <c r="C1"/>
@@ -13155,7 +13659,7 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1127</v>
+        <v>1174</v>
       </c>
       <c r="B2"/>
       <c r="C2"/>
@@ -13164,529 +13668,529 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>1128</v>
+        <v>1175</v>
       </c>
       <c r="B3" t="s">
         <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>1129</v>
+        <v>1176</v>
       </c>
       <c r="D3" t="s">
-        <v>1130</v>
+        <v>1177</v>
       </c>
       <c r="E3" t="s">
-        <v>1131</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1132</v>
+        <v>1179</v>
       </c>
       <c r="B4" t="s">
-        <v>1133</v>
+        <v>1180</v>
       </c>
       <c r="C4" t="s">
-        <v>1134</v>
+        <v>1181</v>
       </c>
       <c r="D4" t="s">
-        <v>1135</v>
+        <v>1182</v>
       </c>
       <c r="E4" t="s">
-        <v>1136</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1137</v>
+        <v>1184</v>
       </c>
       <c r="B5" t="s">
-        <v>1138</v>
+        <v>1185</v>
       </c>
       <c r="C5" t="s">
-        <v>1139</v>
+        <v>1186</v>
       </c>
       <c r="D5" t="s">
-        <v>1140</v>
+        <v>1187</v>
       </c>
       <c r="E5" t="s">
-        <v>1136</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>1141</v>
+        <v>1188</v>
       </c>
       <c r="B6" t="s">
-        <v>1142</v>
+        <v>1189</v>
       </c>
       <c r="C6" t="s">
-        <v>1143</v>
+        <v>1190</v>
       </c>
       <c r="D6" t="s">
-        <v>1144</v>
+        <v>1191</v>
       </c>
       <c r="E6" t="s">
-        <v>1136</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>1145</v>
+        <v>1192</v>
       </c>
       <c r="B7" t="s">
-        <v>1146</v>
+        <v>1193</v>
       </c>
       <c r="C7" t="s">
-        <v>1147</v>
+        <v>1194</v>
       </c>
       <c r="D7" t="s">
-        <v>1148</v>
+        <v>1195</v>
       </c>
       <c r="E7" t="s">
-        <v>1136</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>1149</v>
+        <v>1196</v>
       </c>
       <c r="B8" t="s">
-        <v>1150</v>
+        <v>1197</v>
       </c>
       <c r="C8" t="s">
-        <v>1151</v>
+        <v>1198</v>
       </c>
       <c r="D8" t="s">
-        <v>1152</v>
+        <v>1199</v>
       </c>
       <c r="E8" t="s">
-        <v>1136</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>1153</v>
+        <v>1200</v>
       </c>
       <c r="B9" t="s">
-        <v>1154</v>
+        <v>1201</v>
       </c>
       <c r="C9" t="s">
-        <v>1155</v>
+        <v>1202</v>
       </c>
       <c r="D9" t="s">
-        <v>1156</v>
+        <v>1203</v>
       </c>
       <c r="E9" t="s">
-        <v>1136</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>1157</v>
+        <v>1204</v>
       </c>
       <c r="B10" t="s">
-        <v>1158</v>
+        <v>1205</v>
       </c>
       <c r="C10" t="s">
-        <v>1159</v>
+        <v>1206</v>
       </c>
       <c r="D10" t="s">
-        <v>1160</v>
+        <v>1207</v>
       </c>
       <c r="E10" t="s">
-        <v>1136</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>1161</v>
+        <v>1208</v>
       </c>
       <c r="B11" t="s">
-        <v>1162</v>
+        <v>1209</v>
       </c>
       <c r="C11" t="s">
-        <v>1163</v>
+        <v>1210</v>
       </c>
       <c r="D11" t="s">
         <v>93</v>
       </c>
       <c r="E11" t="s">
-        <v>1164</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>1165</v>
+        <v>1212</v>
       </c>
       <c r="B12" t="s">
-        <v>1166</v>
+        <v>1213</v>
       </c>
       <c r="C12" t="s">
-        <v>1167</v>
+        <v>1214</v>
       </c>
       <c r="D12" t="s">
-        <v>1168</v>
+        <v>1215</v>
       </c>
       <c r="E12" t="s">
-        <v>1136</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>1169</v>
+        <v>1216</v>
       </c>
       <c r="B13" t="s">
-        <v>1170</v>
+        <v>1217</v>
       </c>
       <c r="C13" t="s">
-        <v>1171</v>
+        <v>1218</v>
       </c>
       <c r="D13" t="s">
         <v>403</v>
       </c>
       <c r="E13" t="s">
-        <v>1164</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>1172</v>
+        <v>1219</v>
       </c>
       <c r="B14" t="s">
-        <v>1173</v>
+        <v>1220</v>
       </c>
       <c r="C14" t="s">
-        <v>1174</v>
+        <v>1221</v>
       </c>
       <c r="D14" t="s">
-        <v>1175</v>
+        <v>1222</v>
       </c>
       <c r="E14" t="s">
-        <v>1136</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>1176</v>
+        <v>1223</v>
       </c>
       <c r="B15" t="s">
-        <v>1177</v>
+        <v>1224</v>
       </c>
       <c r="C15" t="s">
-        <v>1178</v>
+        <v>1225</v>
       </c>
       <c r="D15" t="s">
-        <v>1179</v>
+        <v>1226</v>
       </c>
       <c r="E15" t="s">
-        <v>1136</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>1180</v>
+        <v>1227</v>
       </c>
       <c r="B16" t="s">
-        <v>1181</v>
+        <v>1228</v>
       </c>
       <c r="C16" t="s">
-        <v>1182</v>
+        <v>1229</v>
       </c>
       <c r="D16" t="s">
+        <v>1230</v>
+      </c>
+      <c r="E16" t="s">
         <v>1183</v>
-      </c>
-      <c r="E16" t="s">
-        <v>1136</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>1184</v>
+        <v>1231</v>
       </c>
       <c r="B17" t="s">
         <v>435</v>
       </c>
       <c r="C17" t="s">
-        <v>1185</v>
+        <v>1232</v>
       </c>
       <c r="D17" t="s">
-        <v>1186</v>
+        <v>1233</v>
       </c>
       <c r="E17" t="s">
-        <v>1164</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>1106</v>
+        <v>1153</v>
       </c>
       <c r="B18" t="s">
-        <v>1187</v>
+        <v>1234</v>
       </c>
       <c r="C18" t="s">
-        <v>1188</v>
+        <v>1235</v>
       </c>
       <c r="D18" t="s">
         <v>316</v>
       </c>
       <c r="E18" t="s">
-        <v>1164</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>1189</v>
+        <v>1236</v>
       </c>
       <c r="B19" t="s">
-        <v>1190</v>
+        <v>1237</v>
       </c>
       <c r="C19" t="s">
-        <v>1191</v>
+        <v>1238</v>
       </c>
       <c r="D19" t="s">
-        <v>1192</v>
+        <v>1239</v>
       </c>
       <c r="E19" t="s">
-        <v>1164</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>1193</v>
+        <v>1240</v>
       </c>
       <c r="B20" t="s">
-        <v>1194</v>
+        <v>1241</v>
       </c>
       <c r="C20" t="s">
-        <v>1195</v>
+        <v>1242</v>
       </c>
       <c r="D20" t="s">
         <v>475</v>
       </c>
       <c r="E20" t="s">
-        <v>1136</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>1196</v>
+        <v>1243</v>
       </c>
       <c r="B21" t="s">
-        <v>1197</v>
+        <v>1244</v>
       </c>
       <c r="C21" t="s">
-        <v>1198</v>
+        <v>1245</v>
       </c>
       <c r="D21" t="s">
         <v>213</v>
       </c>
       <c r="E21" t="s">
-        <v>1164</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>1199</v>
+        <v>1246</v>
       </c>
       <c r="B22" t="s">
-        <v>1200</v>
+        <v>1247</v>
       </c>
       <c r="C22" t="s">
-        <v>1201</v>
+        <v>1248</v>
       </c>
       <c r="D22" t="s">
-        <v>1202</v>
+        <v>1249</v>
       </c>
       <c r="E22" t="s">
-        <v>1136</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>1203</v>
+        <v>1250</v>
       </c>
       <c r="B23" t="s">
-        <v>1204</v>
+        <v>1251</v>
       </c>
       <c r="C23" t="s">
-        <v>1205</v>
+        <v>1252</v>
       </c>
       <c r="D23" t="s">
-        <v>1206</v>
+        <v>1253</v>
       </c>
       <c r="E23" t="s">
-        <v>1136</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>1207</v>
+        <v>1254</v>
       </c>
       <c r="B24" t="s">
         <v>214</v>
       </c>
       <c r="C24" t="s">
-        <v>1208</v>
+        <v>1255</v>
       </c>
       <c r="D24" t="s">
-        <v>1209</v>
+        <v>1256</v>
       </c>
       <c r="E24" t="s">
-        <v>1136</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>1210</v>
+        <v>1257</v>
       </c>
       <c r="B25" t="s">
+        <v>1258</v>
+      </c>
+      <c r="C25" t="s">
+        <v>1259</v>
+      </c>
+      <c r="D25" t="s">
+        <v>1260</v>
+      </c>
+      <c r="E25" t="s">
         <v>1211</v>
-      </c>
-      <c r="C25" t="s">
-        <v>1212</v>
-      </c>
-      <c r="D25" t="s">
-        <v>1213</v>
-      </c>
-      <c r="E25" t="s">
-        <v>1164</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>1214</v>
+        <v>1261</v>
       </c>
       <c r="B26" t="s">
-        <v>1215</v>
+        <v>1262</v>
       </c>
       <c r="C26" t="s">
-        <v>1216</v>
+        <v>1263</v>
       </c>
       <c r="D26" t="s">
-        <v>1217</v>
+        <v>1264</v>
       </c>
       <c r="E26" t="s">
-        <v>1164</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>1111</v>
+        <v>1265</v>
       </c>
       <c r="B27" t="s">
-        <v>1218</v>
+        <v>1266</v>
       </c>
       <c r="C27" t="s">
-        <v>1219</v>
+        <v>1267</v>
       </c>
       <c r="D27" t="s">
-        <v>1220</v>
+        <v>1268</v>
       </c>
       <c r="E27" t="s">
-        <v>1136</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>1221</v>
+        <v>1269</v>
       </c>
       <c r="B28" t="s">
-        <v>1222</v>
+        <v>1270</v>
       </c>
       <c r="C28" t="s">
-        <v>1223</v>
+        <v>1271</v>
       </c>
       <c r="D28" t="s">
-        <v>1224</v>
+        <v>1272</v>
       </c>
       <c r="E28" t="s">
-        <v>1136</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>1225</v>
+        <v>1273</v>
       </c>
       <c r="B29" t="s">
         <v>822</v>
       </c>
       <c r="C29" t="s">
-        <v>1226</v>
+        <v>1274</v>
       </c>
       <c r="D29" t="s">
-        <v>1227</v>
+        <v>1275</v>
       </c>
       <c r="E29" t="s">
-        <v>1136</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>1228</v>
+        <v>1276</v>
       </c>
       <c r="B30" t="s">
-        <v>1229</v>
+        <v>1277</v>
       </c>
       <c r="C30" t="s">
-        <v>1230</v>
+        <v>1278</v>
       </c>
       <c r="D30" t="s">
-        <v>1231</v>
+        <v>1279</v>
       </c>
       <c r="E30" t="s">
-        <v>1164</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>1232</v>
+        <v>1280</v>
       </c>
       <c r="B31" t="s">
-        <v>1233</v>
+        <v>1281</v>
       </c>
       <c r="C31" t="s">
-        <v>1234</v>
+        <v>1282</v>
       </c>
       <c r="D31" t="s">
         <v>93</v>
       </c>
       <c r="E31" t="s">
-        <v>1235</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>1236</v>
+        <v>1284</v>
       </c>
       <c r="B32" t="s">
-        <v>1237</v>
+        <v>1285</v>
       </c>
       <c r="C32" t="s">
-        <v>1238</v>
+        <v>1286</v>
       </c>
       <c r="D32" t="s">
-        <v>1239</v>
+        <v>1287</v>
       </c>
       <c r="E32" t="s">
-        <v>1136</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>1240</v>
+        <v>1158</v>
       </c>
       <c r="B33" t="s">
         <v>1030</v>
       </c>
       <c r="C33" t="s">
-        <v>1241</v>
+        <v>1288</v>
       </c>
       <c r="D33" t="s">
-        <v>1242</v>
+        <v>1289</v>
       </c>
       <c r="E33" t="s">
-        <v>1164</v>
+        <v>1211</v>
       </c>
     </row>
   </sheetData>
@@ -13700,157 +14204,157 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr defaultRowHeight="0" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" customHeight="1"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>1243</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1244</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>1245</v>
+        <v>1292</v>
       </c>
       <c r="B3" t="s">
-        <v>1246</v>
+        <v>1293</v>
       </c>
       <c r="C3" t="s">
-        <v>1247</v>
+        <v>1294</v>
       </c>
       <c r="D3" t="s">
-        <v>1248</v>
+        <v>1295</v>
       </c>
       <c r="E3" t="s">
-        <v>1249</v>
+        <v>1296</v>
       </c>
       <c r="F3" t="s">
-        <v>1250</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1251</v>
+        <v>1298</v>
       </c>
       <c r="B4" t="s">
         <v>28</v>
       </c>
       <c r="C4" t="s">
-        <v>1252</v>
+        <v>1299</v>
       </c>
       <c r="D4" t="s">
-        <v>1253</v>
+        <v>1300</v>
       </c>
       <c r="E4" t="s">
-        <v>1254</v>
+        <v>1301</v>
       </c>
       <c r="F4" t="s">
-        <v>1255</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1256</v>
+        <v>1303</v>
       </c>
       <c r="B5" t="s">
-        <v>1257</v>
+        <v>1304</v>
       </c>
       <c r="C5" t="s">
-        <v>1258</v>
+        <v>1305</v>
       </c>
       <c r="D5" t="s">
-        <v>1259</v>
+        <v>1306</v>
       </c>
       <c r="E5" t="s">
-        <v>1260</v>
+        <v>1307</v>
       </c>
       <c r="F5" t="s">
-        <v>1261</v>
+        <v>1308</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>1262</v>
+        <v>1309</v>
       </c>
       <c r="B6" t="s">
-        <v>1263</v>
+        <v>1310</v>
       </c>
       <c r="C6" t="s">
-        <v>1264</v>
+        <v>1311</v>
       </c>
       <c r="D6" t="s">
-        <v>1265</v>
+        <v>1312</v>
       </c>
       <c r="E6" t="s">
-        <v>1266</v>
+        <v>1313</v>
       </c>
       <c r="F6" t="s">
-        <v>1267</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>1268</v>
+        <v>1315</v>
       </c>
       <c r="B7" t="s">
-        <v>1269</v>
+        <v>1316</v>
       </c>
       <c r="C7" t="s">
-        <v>1270</v>
+        <v>1317</v>
       </c>
       <c r="D7" t="s">
-        <v>1271</v>
+        <v>1318</v>
       </c>
       <c r="E7" t="s">
-        <v>1266</v>
+        <v>1313</v>
       </c>
       <c r="F7" t="s">
-        <v>1272</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>1273</v>
+        <v>1320</v>
       </c>
       <c r="B8" t="s">
-        <v>1274</v>
+        <v>1321</v>
       </c>
       <c r="C8" t="s">
-        <v>1275</v>
+        <v>1322</v>
       </c>
       <c r="D8" t="s">
-        <v>1276</v>
+        <v>1323</v>
       </c>
       <c r="E8" t="s">
-        <v>1266</v>
+        <v>1313</v>
       </c>
       <c r="F8" t="s">
-        <v>1272</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>1277</v>
+        <v>1324</v>
       </c>
       <c r="B9" t="s">
         <v>29</v>
       </c>
       <c r="C9" t="s">
-        <v>1278</v>
+        <v>1325</v>
       </c>
       <c r="D9" t="s">
-        <v>1279</v>
+        <v>1326</v>
       </c>
       <c r="E9" t="s">
-        <v>1254</v>
+        <v>1301</v>
       </c>
       <c r="F9" t="s">
-        <v>1280</v>
+        <v>1327</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -13861,93 +14365,93 @@
         <v>29</v>
       </c>
       <c r="C10" t="s">
-        <v>1281</v>
+        <v>1328</v>
       </c>
       <c r="D10" t="s">
-        <v>1282</v>
+        <v>1329</v>
       </c>
       <c r="E10" t="s">
-        <v>1283</v>
+        <v>1330</v>
       </c>
       <c r="F10" t="s">
-        <v>1284</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>1285</v>
+        <v>1332</v>
       </c>
       <c r="B11" t="s">
         <v>55</v>
       </c>
       <c r="C11" t="s">
-        <v>1286</v>
+        <v>1333</v>
       </c>
       <c r="D11" t="s">
-        <v>1287</v>
+        <v>1334</v>
       </c>
       <c r="E11" t="s">
-        <v>1283</v>
+        <v>1330</v>
       </c>
       <c r="F11" t="s">
-        <v>1288</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>1289</v>
+        <v>1336</v>
       </c>
       <c r="B12" t="s">
         <v>161</v>
       </c>
       <c r="C12" t="s">
-        <v>1290</v>
+        <v>1337</v>
       </c>
       <c r="D12" t="s">
-        <v>1291</v>
+        <v>1338</v>
       </c>
       <c r="E12" t="s">
-        <v>1292</v>
+        <v>1339</v>
       </c>
       <c r="F12" t="s">
-        <v>1293</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>1294</v>
+        <v>1341</v>
       </c>
       <c r="B13" t="s">
-        <v>1295</v>
+        <v>1342</v>
       </c>
       <c r="C13" t="s">
-        <v>1296</v>
+        <v>1343</v>
       </c>
       <c r="D13" t="s">
-        <v>1297</v>
+        <v>1344</v>
       </c>
       <c r="E13" t="s">
-        <v>1298</v>
+        <v>1345</v>
       </c>
       <c r="F13" t="s">
-        <v>1299</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>1300</v>
+        <v>1347</v>
       </c>
       <c r="B14" t="s">
         <v>206</v>
       </c>
       <c r="C14" t="s">
-        <v>1301</v>
+        <v>1348</v>
       </c>
       <c r="D14" t="s">
-        <v>1302</v>
+        <v>1349</v>
       </c>
       <c r="E14" t="s">
-        <v>1303</v>
+        <v>1350</v>
       </c>
       <c r="F14" t="s">
         <v>748</v>
@@ -13955,19 +14459,19 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>1304</v>
+        <v>1351</v>
       </c>
       <c r="B15" t="s">
         <v>206</v>
       </c>
       <c r="C15" t="s">
-        <v>1305</v>
+        <v>1352</v>
       </c>
       <c r="D15" t="s">
-        <v>1306</v>
+        <v>1353</v>
       </c>
       <c r="E15" t="s">
-        <v>1307</v>
+        <v>1354</v>
       </c>
       <c r="F15" t="s">
         <v>748</v>
@@ -13975,19 +14479,19 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>1308</v>
+        <v>1355</v>
       </c>
       <c r="B16" t="s">
         <v>918</v>
       </c>
       <c r="C16" t="s">
-        <v>1309</v>
+        <v>1356</v>
       </c>
       <c r="D16" t="s">
-        <v>1310</v>
+        <v>1357</v>
       </c>
       <c r="E16" t="s">
-        <v>1307</v>
+        <v>1354</v>
       </c>
       <c r="F16" t="s">
         <v>924</v>
@@ -13995,21 +14499,41 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>1311</v>
+        <v>1358</v>
       </c>
       <c r="B17" t="s">
         <v>999</v>
       </c>
       <c r="C17" t="s">
-        <v>1312</v>
+        <v>1359</v>
       </c>
       <c r="D17" t="s">
-        <v>1313</v>
+        <v>1360</v>
       </c>
       <c r="E17" t="s">
-        <v>1307</v>
+        <v>1354</v>
       </c>
       <c r="F17" t="s">
+        <v>924</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>1361</v>
+      </c>
+      <c r="B18" t="s">
+        <v>1095</v>
+      </c>
+      <c r="C18" t="s">
+        <v>1362</v>
+      </c>
+      <c r="D18" t="s">
+        <v>1363</v>
+      </c>
+      <c r="E18" t="s">
+        <v>1354</v>
+      </c>
+      <c r="F18" t="s">
         <v>924</v>
       </c>
     </row>
@@ -14019,40 +14543,40 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G151"/>
+  <dimension ref="A1:G157"/>
   <sheetFormatPr defaultRowHeight="0" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" customHeight="1"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>1314</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1315</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>1316</v>
+        <v>1366</v>
       </c>
       <c r="B3" t="s">
-        <v>1317</v>
+        <v>1367</v>
       </c>
       <c r="C3" t="s">
-        <v>1318</v>
+        <v>1368</v>
       </c>
       <c r="D3" t="s">
-        <v>1319</v>
+        <v>1369</v>
       </c>
       <c r="E3" t="s">
-        <v>1320</v>
+        <v>1370</v>
       </c>
       <c r="F3" t="s">
-        <v>1321</v>
+        <v>1371</v>
       </c>
       <c r="G3" t="s">
-        <v>1322</v>
+        <v>1372</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -14072,10 +14596,10 @@
         <v>26</v>
       </c>
       <c r="F4" t="s">
-        <v>1323</v>
+        <v>1373</v>
       </c>
       <c r="G4" t="s">
-        <v>1324</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -14095,10 +14619,10 @@
         <v>26</v>
       </c>
       <c r="F5" t="s">
-        <v>1323</v>
+        <v>1373</v>
       </c>
       <c r="G5" t="s">
-        <v>1325</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -14118,10 +14642,10 @@
         <v>26</v>
       </c>
       <c r="F6" t="s">
-        <v>1323</v>
+        <v>1373</v>
       </c>
       <c r="G6" t="s">
-        <v>1326</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -14141,10 +14665,10 @@
         <v>86</v>
       </c>
       <c r="F7" t="s">
-        <v>1323</v>
+        <v>1373</v>
       </c>
       <c r="G7" t="s">
-        <v>1327</v>
+        <v>1377</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -14164,10 +14688,10 @@
         <v>26</v>
       </c>
       <c r="F8" t="s">
-        <v>1323</v>
+        <v>1373</v>
       </c>
       <c r="G8" t="s">
-        <v>1328</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -14187,10 +14711,10 @@
         <v>26</v>
       </c>
       <c r="F9" t="s">
-        <v>1323</v>
+        <v>1373</v>
       </c>
       <c r="G9" t="s">
-        <v>1329</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -14210,10 +14734,10 @@
         <v>26</v>
       </c>
       <c r="F10" t="s">
-        <v>1323</v>
+        <v>1373</v>
       </c>
       <c r="G10" t="s">
-        <v>1330</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -14233,10 +14757,10 @@
         <v>86</v>
       </c>
       <c r="F11" t="s">
-        <v>1323</v>
+        <v>1373</v>
       </c>
       <c r="G11" t="s">
-        <v>1331</v>
+        <v>1381</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -14256,10 +14780,10 @@
         <v>86</v>
       </c>
       <c r="F12" t="s">
-        <v>1323</v>
+        <v>1373</v>
       </c>
       <c r="G12" t="s">
-        <v>1332</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -14279,10 +14803,10 @@
         <v>26</v>
       </c>
       <c r="F13" t="s">
-        <v>1323</v>
+        <v>1373</v>
       </c>
       <c r="G13" t="s">
-        <v>1333</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -14302,10 +14826,10 @@
         <v>26</v>
       </c>
       <c r="F14" t="s">
-        <v>1334</v>
+        <v>1384</v>
       </c>
       <c r="G14" t="s">
-        <v>1335</v>
+        <v>1385</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -14325,10 +14849,10 @@
         <v>26</v>
       </c>
       <c r="F15" t="s">
-        <v>1334</v>
+        <v>1384</v>
       </c>
       <c r="G15" t="s">
-        <v>1336</v>
+        <v>1386</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -14348,10 +14872,10 @@
         <v>26</v>
       </c>
       <c r="F16" t="s">
-        <v>1334</v>
+        <v>1384</v>
       </c>
       <c r="G16" t="s">
-        <v>1337</v>
+        <v>1387</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -14371,10 +14895,10 @@
         <v>26</v>
       </c>
       <c r="F17" t="s">
-        <v>1334</v>
+        <v>1384</v>
       </c>
       <c r="G17" t="s">
-        <v>1338</v>
+        <v>1388</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -14394,10 +14918,10 @@
         <v>26</v>
       </c>
       <c r="F18" t="s">
-        <v>1334</v>
+        <v>1384</v>
       </c>
       <c r="G18" t="s">
-        <v>1339</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -14417,10 +14941,10 @@
         <v>26</v>
       </c>
       <c r="F19" t="s">
-        <v>1334</v>
+        <v>1384</v>
       </c>
       <c r="G19" t="s">
-        <v>1340</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -14440,10 +14964,10 @@
         <v>86</v>
       </c>
       <c r="F20" t="s">
-        <v>1334</v>
+        <v>1384</v>
       </c>
       <c r="G20" t="s">
-        <v>1341</v>
+        <v>1391</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -14463,10 +14987,10 @@
         <v>86</v>
       </c>
       <c r="F21" t="s">
-        <v>1334</v>
+        <v>1384</v>
       </c>
       <c r="G21" t="s">
-        <v>1342</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
@@ -14486,10 +15010,10 @@
         <v>26</v>
       </c>
       <c r="F22" t="s">
-        <v>1334</v>
+        <v>1384</v>
       </c>
       <c r="G22" t="s">
-        <v>1343</v>
+        <v>1393</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
@@ -14509,10 +15033,10 @@
         <v>86</v>
       </c>
       <c r="F23" t="s">
-        <v>1334</v>
+        <v>1384</v>
       </c>
       <c r="G23" t="s">
-        <v>1344</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -14532,10 +15056,10 @@
         <v>86</v>
       </c>
       <c r="F24" t="s">
-        <v>1334</v>
+        <v>1384</v>
       </c>
       <c r="G24" t="s">
-        <v>1345</v>
+        <v>1395</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
@@ -14555,10 +15079,10 @@
         <v>86</v>
       </c>
       <c r="F25" t="s">
-        <v>1334</v>
+        <v>1384</v>
       </c>
       <c r="G25" t="s">
-        <v>1346</v>
+        <v>1396</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
@@ -14578,10 +15102,10 @@
         <v>86</v>
       </c>
       <c r="F26" t="s">
-        <v>1334</v>
+        <v>1384</v>
       </c>
       <c r="G26" t="s">
-        <v>1347</v>
+        <v>1397</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
@@ -14601,10 +15125,10 @@
         <v>26</v>
       </c>
       <c r="F27" t="s">
-        <v>1334</v>
+        <v>1384</v>
       </c>
       <c r="G27" t="s">
-        <v>1348</v>
+        <v>1398</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
@@ -14624,10 +15148,10 @@
         <v>86</v>
       </c>
       <c r="F28" t="s">
-        <v>1334</v>
+        <v>1384</v>
       </c>
       <c r="G28" t="s">
-        <v>1349</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
@@ -14647,10 +15171,10 @@
         <v>86</v>
       </c>
       <c r="F29" t="s">
-        <v>1334</v>
+        <v>1384</v>
       </c>
       <c r="G29" t="s">
-        <v>1350</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
@@ -14670,10 +15194,10 @@
         <v>26</v>
       </c>
       <c r="F30" t="s">
-        <v>1334</v>
+        <v>1384</v>
       </c>
       <c r="G30" t="s">
-        <v>1351</v>
+        <v>1401</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
@@ -14693,10 +15217,10 @@
         <v>26</v>
       </c>
       <c r="F31" t="s">
-        <v>1334</v>
+        <v>1384</v>
       </c>
       <c r="G31" t="s">
-        <v>1352</v>
+        <v>1402</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
@@ -14716,10 +15240,10 @@
         <v>86</v>
       </c>
       <c r="F32" t="s">
-        <v>1334</v>
+        <v>1384</v>
       </c>
       <c r="G32" t="s">
-        <v>1353</v>
+        <v>1403</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
@@ -14739,10 +15263,10 @@
         <v>86</v>
       </c>
       <c r="F33" t="s">
-        <v>1334</v>
+        <v>1384</v>
       </c>
       <c r="G33" t="s">
-        <v>1354</v>
+        <v>1404</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
@@ -14762,10 +15286,10 @@
         <v>86</v>
       </c>
       <c r="F34" t="s">
-        <v>1334</v>
+        <v>1384</v>
       </c>
       <c r="G34" t="s">
-        <v>1355</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
@@ -14785,7 +15309,7 @@
         <v>26</v>
       </c>
       <c r="F35" t="s">
-        <v>1356</v>
+        <v>1406</v>
       </c>
       <c r="G35" t="s">
         <v>168</v>
@@ -14808,7 +15332,7 @@
         <v>26</v>
       </c>
       <c r="F36" t="s">
-        <v>1356</v>
+        <v>1406</v>
       </c>
       <c r="G36" t="s">
         <v>177</v>
@@ -14831,7 +15355,7 @@
         <v>26</v>
       </c>
       <c r="F37" t="s">
-        <v>1356</v>
+        <v>1406</v>
       </c>
       <c r="G37" t="s">
         <v>194</v>
@@ -14854,7 +15378,7 @@
         <v>26</v>
       </c>
       <c r="F38" t="s">
-        <v>1356</v>
+        <v>1406</v>
       </c>
       <c r="G38" t="s">
         <v>203</v>
@@ -14877,7 +15401,7 @@
         <v>26</v>
       </c>
       <c r="F39" t="s">
-        <v>1356</v>
+        <v>1406</v>
       </c>
       <c r="G39" t="s">
         <v>222</v>
@@ -14900,7 +15424,7 @@
         <v>26</v>
       </c>
       <c r="F40" t="s">
-        <v>1356</v>
+        <v>1406</v>
       </c>
       <c r="G40" t="s">
         <v>245</v>
@@ -14923,10 +15447,10 @@
         <v>26</v>
       </c>
       <c r="F41" t="s">
-        <v>1356</v>
+        <v>1406</v>
       </c>
       <c r="G41" t="s">
-        <v>1357</v>
+        <v>1407</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
@@ -14946,10 +15470,10 @@
         <v>26</v>
       </c>
       <c r="F42" t="s">
-        <v>1356</v>
+        <v>1406</v>
       </c>
       <c r="G42" t="s">
-        <v>1358</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
@@ -14969,10 +15493,10 @@
         <v>26</v>
       </c>
       <c r="F43" t="s">
-        <v>1356</v>
+        <v>1406</v>
       </c>
       <c r="G43" t="s">
-        <v>1359</v>
+        <v>1409</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
@@ -14992,7 +15516,7 @@
         <v>26</v>
       </c>
       <c r="F44" t="s">
-        <v>1356</v>
+        <v>1406</v>
       </c>
       <c r="G44" t="s">
         <v>360</v>
@@ -15015,7 +15539,7 @@
         <v>26</v>
       </c>
       <c r="F45" t="s">
-        <v>1356</v>
+        <v>1406</v>
       </c>
       <c r="G45" t="s">
         <v>368</v>
@@ -15038,10 +15562,10 @@
         <v>26</v>
       </c>
       <c r="F46" t="s">
-        <v>1356</v>
+        <v>1406</v>
       </c>
       <c r="G46" t="s">
-        <v>1360</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
@@ -15061,7 +15585,7 @@
         <v>26</v>
       </c>
       <c r="F47" t="s">
-        <v>1356</v>
+        <v>1406</v>
       </c>
       <c r="G47" t="s">
         <v>386</v>
@@ -15084,10 +15608,10 @@
         <v>26</v>
       </c>
       <c r="F48" t="s">
-        <v>1356</v>
+        <v>1406</v>
       </c>
       <c r="G48" t="s">
-        <v>1361</v>
+        <v>1411</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
@@ -15107,7 +15631,7 @@
         <v>26</v>
       </c>
       <c r="F49" t="s">
-        <v>1356</v>
+        <v>1406</v>
       </c>
       <c r="G49" t="s">
         <v>402</v>
@@ -15130,7 +15654,7 @@
         <v>26</v>
       </c>
       <c r="F50" t="s">
-        <v>1356</v>
+        <v>1406</v>
       </c>
       <c r="G50" t="s">
         <v>411</v>
@@ -15153,7 +15677,7 @@
         <v>26</v>
       </c>
       <c r="F51" t="s">
-        <v>1356</v>
+        <v>1406</v>
       </c>
       <c r="G51" t="s">
         <v>419</v>
@@ -15176,7 +15700,7 @@
         <v>26</v>
       </c>
       <c r="F52" t="s">
-        <v>1356</v>
+        <v>1406</v>
       </c>
       <c r="G52" t="s">
         <v>426</v>
@@ -15199,7 +15723,7 @@
         <v>26</v>
       </c>
       <c r="F53" t="s">
-        <v>1356</v>
+        <v>1406</v>
       </c>
       <c r="G53" t="s">
         <v>433</v>
@@ -15222,7 +15746,7 @@
         <v>26</v>
       </c>
       <c r="F54" t="s">
-        <v>1356</v>
+        <v>1406</v>
       </c>
       <c r="G54" t="s">
         <v>467</v>
@@ -15245,7 +15769,7 @@
         <v>26</v>
       </c>
       <c r="F55" t="s">
-        <v>1356</v>
+        <v>1406</v>
       </c>
       <c r="G55" t="s">
         <v>485</v>
@@ -15268,7 +15792,7 @@
         <v>26</v>
       </c>
       <c r="F56" t="s">
-        <v>1356</v>
+        <v>1406</v>
       </c>
       <c r="G56" t="s">
         <v>494</v>
@@ -15291,7 +15815,7 @@
         <v>26</v>
       </c>
       <c r="F57" t="s">
-        <v>1356</v>
+        <v>1406</v>
       </c>
       <c r="G57" t="s">
         <v>502</v>
@@ -15314,7 +15838,7 @@
         <v>26</v>
       </c>
       <c r="F58" t="s">
-        <v>1356</v>
+        <v>1406</v>
       </c>
       <c r="G58" t="s">
         <v>511</v>
@@ -15337,7 +15861,7 @@
         <v>26</v>
       </c>
       <c r="F59" t="s">
-        <v>1356</v>
+        <v>1406</v>
       </c>
       <c r="G59" t="s">
         <v>520</v>
@@ -15360,7 +15884,7 @@
         <v>26</v>
       </c>
       <c r="F60" t="s">
-        <v>1356</v>
+        <v>1406</v>
       </c>
       <c r="G60" t="s">
         <v>530</v>
@@ -15383,7 +15907,7 @@
         <v>26</v>
       </c>
       <c r="F61" t="s">
-        <v>1356</v>
+        <v>1406</v>
       </c>
       <c r="G61" t="s">
         <v>539</v>
@@ -15406,7 +15930,7 @@
         <v>26</v>
       </c>
       <c r="F62" t="s">
-        <v>1356</v>
+        <v>1406</v>
       </c>
       <c r="G62" t="s">
         <v>547</v>
@@ -15429,7 +15953,7 @@
         <v>26</v>
       </c>
       <c r="F63" t="s">
-        <v>1356</v>
+        <v>1406</v>
       </c>
       <c r="G63" t="s">
         <v>557</v>
@@ -15452,7 +15976,7 @@
         <v>26</v>
       </c>
       <c r="F64" t="s">
-        <v>1356</v>
+        <v>1406</v>
       </c>
       <c r="G64" t="s">
         <v>567</v>
@@ -15475,7 +15999,7 @@
         <v>26</v>
       </c>
       <c r="F65" t="s">
-        <v>1356</v>
+        <v>1406</v>
       </c>
       <c r="G65" t="s">
         <v>576</v>
@@ -15498,7 +16022,7 @@
         <v>26</v>
       </c>
       <c r="F66" t="s">
-        <v>1356</v>
+        <v>1406</v>
       </c>
       <c r="G66" t="s">
         <v>584</v>
@@ -15521,7 +16045,7 @@
         <v>26</v>
       </c>
       <c r="F67" t="s">
-        <v>1356</v>
+        <v>1406</v>
       </c>
       <c r="G67" t="s">
         <v>594</v>
@@ -15544,7 +16068,7 @@
         <v>26</v>
       </c>
       <c r="F68" t="s">
-        <v>1356</v>
+        <v>1406</v>
       </c>
       <c r="G68" t="s">
         <v>602</v>
@@ -15567,7 +16091,7 @@
         <v>26</v>
       </c>
       <c r="F69" t="s">
-        <v>1356</v>
+        <v>1406</v>
       </c>
       <c r="G69" t="s">
         <v>611</v>
@@ -15590,7 +16114,7 @@
         <v>26</v>
       </c>
       <c r="F70" t="s">
-        <v>1356</v>
+        <v>1406</v>
       </c>
       <c r="G70" t="s">
         <v>618</v>
@@ -15613,10 +16137,10 @@
         <v>26</v>
       </c>
       <c r="F71" t="s">
-        <v>1356</v>
+        <v>1406</v>
       </c>
       <c r="G71" t="s">
-        <v>1362</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
@@ -15636,10 +16160,10 @@
         <v>26</v>
       </c>
       <c r="F72" t="s">
-        <v>1356</v>
+        <v>1406</v>
       </c>
       <c r="G72" t="s">
-        <v>1363</v>
+        <v>1413</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
@@ -15659,10 +16183,10 @@
         <v>26</v>
       </c>
       <c r="F73" t="s">
-        <v>1356</v>
+        <v>1406</v>
       </c>
       <c r="G73" t="s">
-        <v>1364</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
@@ -15682,10 +16206,10 @@
         <v>26</v>
       </c>
       <c r="F74" t="s">
-        <v>1356</v>
+        <v>1406</v>
       </c>
       <c r="G74" t="s">
-        <v>1365</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
@@ -15705,10 +16229,10 @@
         <v>26</v>
       </c>
       <c r="F75" t="s">
-        <v>1356</v>
+        <v>1406</v>
       </c>
       <c r="G75" t="s">
-        <v>1366</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
@@ -15728,10 +16252,10 @@
         <v>26</v>
       </c>
       <c r="F76" t="s">
-        <v>1356</v>
+        <v>1406</v>
       </c>
       <c r="G76" t="s">
-        <v>1367</v>
+        <v>1417</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
@@ -15751,10 +16275,10 @@
         <v>26</v>
       </c>
       <c r="F77" t="s">
-        <v>1356</v>
+        <v>1406</v>
       </c>
       <c r="G77" t="s">
-        <v>1368</v>
+        <v>1418</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
@@ -15774,10 +16298,10 @@
         <v>26</v>
       </c>
       <c r="F78" t="s">
-        <v>1356</v>
+        <v>1406</v>
       </c>
       <c r="G78" t="s">
-        <v>1369</v>
+        <v>1419</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
@@ -15797,10 +16321,10 @@
         <v>26</v>
       </c>
       <c r="F79" t="s">
-        <v>1356</v>
+        <v>1406</v>
       </c>
       <c r="G79" t="s">
-        <v>1370</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
@@ -15808,7 +16332,7 @@
         <v>27</v>
       </c>
       <c r="B80" t="s">
-        <v>1295</v>
+        <v>1342</v>
       </c>
       <c r="C80" t="s">
         <v>697</v>
@@ -15820,10 +16344,10 @@
         <v>26</v>
       </c>
       <c r="F80" t="s">
-        <v>1371</v>
+        <v>1421</v>
       </c>
       <c r="G80" t="s">
-        <v>1372</v>
+        <v>1422</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
@@ -15831,7 +16355,7 @@
         <v>27</v>
       </c>
       <c r="B81" t="s">
-        <v>1295</v>
+        <v>1342</v>
       </c>
       <c r="C81" t="s">
         <v>708</v>
@@ -15843,10 +16367,10 @@
         <v>26</v>
       </c>
       <c r="F81" t="s">
-        <v>1371</v>
+        <v>1421</v>
       </c>
       <c r="G81" t="s">
-        <v>1373</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
@@ -15854,7 +16378,7 @@
         <v>27</v>
       </c>
       <c r="B82" t="s">
-        <v>1295</v>
+        <v>1342</v>
       </c>
       <c r="C82" t="s">
         <v>715</v>
@@ -15866,10 +16390,10 @@
         <v>26</v>
       </c>
       <c r="F82" t="s">
-        <v>1371</v>
+        <v>1421</v>
       </c>
       <c r="G82" t="s">
-        <v>1374</v>
+        <v>1424</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
@@ -15877,7 +16401,7 @@
         <v>27</v>
       </c>
       <c r="B83" t="s">
-        <v>1295</v>
+        <v>1342</v>
       </c>
       <c r="C83" t="s">
         <v>723</v>
@@ -15889,10 +16413,10 @@
         <v>26</v>
       </c>
       <c r="F83" t="s">
-        <v>1371</v>
+        <v>1421</v>
       </c>
       <c r="G83" t="s">
-        <v>1375</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
@@ -15900,7 +16424,7 @@
         <v>27</v>
       </c>
       <c r="B84" t="s">
-        <v>1295</v>
+        <v>1342</v>
       </c>
       <c r="C84" t="s">
         <v>732</v>
@@ -15912,10 +16436,10 @@
         <v>26</v>
       </c>
       <c r="F84" t="s">
-        <v>1371</v>
+        <v>1421</v>
       </c>
       <c r="G84" t="s">
-        <v>1376</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
@@ -15923,7 +16447,7 @@
         <v>27</v>
       </c>
       <c r="B85" t="s">
-        <v>1377</v>
+        <v>1427</v>
       </c>
       <c r="C85" t="s">
         <v>324</v>
@@ -15935,10 +16459,10 @@
         <v>86</v>
       </c>
       <c r="F85" t="s">
-        <v>1378</v>
+        <v>1428</v>
       </c>
       <c r="G85" t="s">
-        <v>1379</v>
+        <v>1429</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
@@ -15946,7 +16470,7 @@
         <v>27</v>
       </c>
       <c r="B86" t="s">
-        <v>1377</v>
+        <v>1427</v>
       </c>
       <c r="C86" t="s">
         <v>335</v>
@@ -15958,10 +16482,10 @@
         <v>86</v>
       </c>
       <c r="F86" t="s">
-        <v>1378</v>
+        <v>1428</v>
       </c>
       <c r="G86" t="s">
-        <v>1380</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
@@ -15969,7 +16493,7 @@
         <v>27</v>
       </c>
       <c r="B87" t="s">
-        <v>1377</v>
+        <v>1427</v>
       </c>
       <c r="C87" t="s">
         <v>344</v>
@@ -15981,10 +16505,10 @@
         <v>86</v>
       </c>
       <c r="F87" t="s">
-        <v>1378</v>
+        <v>1428</v>
       </c>
       <c r="G87" t="s">
-        <v>1381</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
@@ -15992,7 +16516,7 @@
         <v>27</v>
       </c>
       <c r="B88" t="s">
-        <v>1377</v>
+        <v>1427</v>
       </c>
       <c r="C88" t="s">
         <v>369</v>
@@ -16004,10 +16528,10 @@
         <v>112</v>
       </c>
       <c r="F88" t="s">
-        <v>1378</v>
+        <v>1428</v>
       </c>
       <c r="G88" t="s">
-        <v>1382</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
@@ -16027,10 +16551,10 @@
         <v>26</v>
       </c>
       <c r="F89" t="s">
-        <v>1383</v>
+        <v>1433</v>
       </c>
       <c r="G89" t="s">
-        <v>1384</v>
+        <v>1434</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
@@ -16038,7 +16562,7 @@
         <v>27</v>
       </c>
       <c r="B90" t="s">
-        <v>1377</v>
+        <v>1427</v>
       </c>
       <c r="C90" t="s">
         <v>619</v>
@@ -16050,10 +16574,10 @@
         <v>112</v>
       </c>
       <c r="F90" t="s">
-        <v>1378</v>
+        <v>1428</v>
       </c>
       <c r="G90" t="s">
-        <v>1385</v>
+        <v>1435</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
@@ -16061,7 +16585,7 @@
         <v>27</v>
       </c>
       <c r="B91" t="s">
-        <v>1377</v>
+        <v>1427</v>
       </c>
       <c r="C91" t="s">
         <v>639</v>
@@ -16073,10 +16597,10 @@
         <v>86</v>
       </c>
       <c r="F91" t="s">
-        <v>1378</v>
+        <v>1428</v>
       </c>
       <c r="G91" t="s">
-        <v>1386</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
@@ -16084,7 +16608,7 @@
         <v>27</v>
       </c>
       <c r="B92" t="s">
-        <v>1377</v>
+        <v>1427</v>
       </c>
       <c r="C92" t="s">
         <v>648</v>
@@ -16096,10 +16620,10 @@
         <v>112</v>
       </c>
       <c r="F92" t="s">
-        <v>1378</v>
+        <v>1428</v>
       </c>
       <c r="G92" t="s">
-        <v>1387</v>
+        <v>1437</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
@@ -16119,10 +16643,10 @@
         <v>86</v>
       </c>
       <c r="F93" t="s">
-        <v>1383</v>
+        <v>1433</v>
       </c>
       <c r="G93" t="s">
-        <v>1388</v>
+        <v>1438</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
@@ -16130,7 +16654,7 @@
         <v>27</v>
       </c>
       <c r="B94" t="s">
-        <v>1377</v>
+        <v>1427</v>
       </c>
       <c r="C94" t="s">
         <v>657</v>
@@ -16142,10 +16666,10 @@
         <v>112</v>
       </c>
       <c r="F94" t="s">
-        <v>1378</v>
+        <v>1428</v>
       </c>
       <c r="G94" t="s">
-        <v>1389</v>
+        <v>1439</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
@@ -16153,7 +16677,7 @@
         <v>27</v>
       </c>
       <c r="B95" t="s">
-        <v>1377</v>
+        <v>1427</v>
       </c>
       <c r="C95" t="s">
         <v>673</v>
@@ -16165,10 +16689,10 @@
         <v>112</v>
       </c>
       <c r="F95" t="s">
-        <v>1378</v>
+        <v>1428</v>
       </c>
       <c r="G95" t="s">
-        <v>1390</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
@@ -16188,10 +16712,10 @@
         <v>26</v>
       </c>
       <c r="F96" t="s">
-        <v>1383</v>
+        <v>1433</v>
       </c>
       <c r="G96" t="s">
-        <v>1391</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
@@ -16199,7 +16723,7 @@
         <v>27</v>
       </c>
       <c r="B97" t="s">
-        <v>1377</v>
+        <v>1427</v>
       </c>
       <c r="C97" t="s">
         <v>689</v>
@@ -16211,10 +16735,10 @@
         <v>112</v>
       </c>
       <c r="F97" t="s">
-        <v>1378</v>
+        <v>1428</v>
       </c>
       <c r="G97" t="s">
-        <v>1392</v>
+        <v>1442</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
@@ -16222,7 +16746,7 @@
         <v>27</v>
       </c>
       <c r="B98" t="s">
-        <v>1377</v>
+        <v>1427</v>
       </c>
       <c r="C98" t="s">
         <v>697</v>
@@ -16234,10 +16758,10 @@
         <v>112</v>
       </c>
       <c r="F98" t="s">
-        <v>1378</v>
+        <v>1428</v>
       </c>
       <c r="G98" t="s">
-        <v>1393</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
@@ -16257,10 +16781,10 @@
         <v>26</v>
       </c>
       <c r="F99" t="s">
-        <v>1383</v>
+        <v>1433</v>
       </c>
       <c r="G99" t="s">
-        <v>1394</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
@@ -16268,7 +16792,7 @@
         <v>27</v>
       </c>
       <c r="B100" t="s">
-        <v>1377</v>
+        <v>1427</v>
       </c>
       <c r="C100" t="s">
         <v>708</v>
@@ -16280,10 +16804,10 @@
         <v>112</v>
       </c>
       <c r="F100" t="s">
-        <v>1378</v>
+        <v>1428</v>
       </c>
       <c r="G100" t="s">
-        <v>1395</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
@@ -16303,10 +16827,10 @@
         <v>86</v>
       </c>
       <c r="F101" t="s">
-        <v>1383</v>
+        <v>1433</v>
       </c>
       <c r="G101" t="s">
-        <v>1396</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
@@ -16314,7 +16838,7 @@
         <v>27</v>
       </c>
       <c r="B102" t="s">
-        <v>1377</v>
+        <v>1427</v>
       </c>
       <c r="C102" t="s">
         <v>715</v>
@@ -16326,10 +16850,10 @@
         <v>112</v>
       </c>
       <c r="F102" t="s">
-        <v>1378</v>
+        <v>1428</v>
       </c>
       <c r="G102" t="s">
-        <v>1397</v>
+        <v>1447</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
@@ -16349,10 +16873,10 @@
         <v>86</v>
       </c>
       <c r="F103" t="s">
-        <v>1383</v>
+        <v>1433</v>
       </c>
       <c r="G103" t="s">
-        <v>1398</v>
+        <v>1448</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
@@ -16360,7 +16884,7 @@
         <v>27</v>
       </c>
       <c r="B104" t="s">
-        <v>1377</v>
+        <v>1427</v>
       </c>
       <c r="C104" t="s">
         <v>723</v>
@@ -16372,10 +16896,10 @@
         <v>112</v>
       </c>
       <c r="F104" t="s">
-        <v>1378</v>
+        <v>1428</v>
       </c>
       <c r="G104" t="s">
-        <v>1399</v>
+        <v>1449</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
@@ -16395,10 +16919,10 @@
         <v>26</v>
       </c>
       <c r="F105" t="s">
-        <v>1383</v>
+        <v>1433</v>
       </c>
       <c r="G105" t="s">
-        <v>1400</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
@@ -16406,7 +16930,7 @@
         <v>27</v>
       </c>
       <c r="B106" t="s">
-        <v>1377</v>
+        <v>1427</v>
       </c>
       <c r="C106" t="s">
         <v>732</v>
@@ -16418,10 +16942,10 @@
         <v>112</v>
       </c>
       <c r="F106" t="s">
-        <v>1378</v>
+        <v>1428</v>
       </c>
       <c r="G106" t="s">
-        <v>1401</v>
+        <v>1451</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
@@ -16441,10 +16965,10 @@
         <v>26</v>
       </c>
       <c r="F107" t="s">
-        <v>1383</v>
+        <v>1433</v>
       </c>
       <c r="G107" t="s">
-        <v>1402</v>
+        <v>1452</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
@@ -16458,13 +16982,13 @@
         <v>740</v>
       </c>
       <c r="D108" t="s">
-        <v>1403</v>
+        <v>1453</v>
       </c>
       <c r="E108" t="s">
         <v>112</v>
       </c>
       <c r="F108" t="s">
-        <v>1383</v>
+        <v>1433</v>
       </c>
       <c r="G108" t="s">
         <v>741</v>
@@ -16481,13 +17005,13 @@
         <v>750</v>
       </c>
       <c r="D109" t="s">
-        <v>1403</v>
+        <v>1453</v>
       </c>
       <c r="E109" t="s">
         <v>112</v>
       </c>
       <c r="F109" t="s">
-        <v>1383</v>
+        <v>1433</v>
       </c>
       <c r="G109" t="s">
         <v>751</v>
@@ -16504,13 +17028,13 @@
         <v>758</v>
       </c>
       <c r="D110" t="s">
-        <v>1403</v>
+        <v>1453</v>
       </c>
       <c r="E110" t="s">
         <v>112</v>
       </c>
       <c r="F110" t="s">
-        <v>1383</v>
+        <v>1433</v>
       </c>
       <c r="G110" t="s">
         <v>759</v>
@@ -16527,13 +17051,13 @@
         <v>766</v>
       </c>
       <c r="D111" t="s">
-        <v>1403</v>
+        <v>1453</v>
       </c>
       <c r="E111" t="s">
         <v>112</v>
       </c>
       <c r="F111" t="s">
-        <v>1383</v>
+        <v>1433</v>
       </c>
       <c r="G111" t="s">
         <v>767</v>
@@ -16550,13 +17074,13 @@
         <v>774</v>
       </c>
       <c r="D112" t="s">
-        <v>1403</v>
+        <v>1453</v>
       </c>
       <c r="E112" t="s">
         <v>112</v>
       </c>
       <c r="F112" t="s">
-        <v>1383</v>
+        <v>1433</v>
       </c>
       <c r="G112" t="s">
         <v>775</v>
@@ -16573,13 +17097,13 @@
         <v>782</v>
       </c>
       <c r="D113" t="s">
-        <v>1403</v>
+        <v>1453</v>
       </c>
       <c r="E113" t="s">
         <v>112</v>
       </c>
       <c r="F113" t="s">
-        <v>1383</v>
+        <v>1433</v>
       </c>
       <c r="G113" t="s">
         <v>783</v>
@@ -16596,13 +17120,13 @@
         <v>790</v>
       </c>
       <c r="D114" t="s">
-        <v>1403</v>
+        <v>1453</v>
       </c>
       <c r="E114" t="s">
         <v>112</v>
       </c>
       <c r="F114" t="s">
-        <v>1383</v>
+        <v>1433</v>
       </c>
       <c r="G114" t="s">
         <v>791</v>
@@ -16619,13 +17143,13 @@
         <v>798</v>
       </c>
       <c r="D115" t="s">
-        <v>1403</v>
+        <v>1453</v>
       </c>
       <c r="E115" t="s">
         <v>112</v>
       </c>
       <c r="F115" t="s">
-        <v>1383</v>
+        <v>1433</v>
       </c>
       <c r="G115" t="s">
         <v>799</v>
@@ -16642,13 +17166,13 @@
         <v>806</v>
       </c>
       <c r="D116" t="s">
-        <v>1403</v>
+        <v>1453</v>
       </c>
       <c r="E116" t="s">
         <v>112</v>
       </c>
       <c r="F116" t="s">
-        <v>1383</v>
+        <v>1433</v>
       </c>
       <c r="G116" t="s">
         <v>807</v>
@@ -16665,13 +17189,13 @@
         <v>814</v>
       </c>
       <c r="D117" t="s">
-        <v>1403</v>
+        <v>1453</v>
       </c>
       <c r="E117" t="s">
         <v>112</v>
       </c>
       <c r="F117" t="s">
-        <v>1383</v>
+        <v>1433</v>
       </c>
       <c r="G117" t="s">
         <v>815</v>
@@ -16688,13 +17212,13 @@
         <v>821</v>
       </c>
       <c r="D118" t="s">
-        <v>1403</v>
+        <v>1453</v>
       </c>
       <c r="E118" t="s">
         <v>112</v>
       </c>
       <c r="F118" t="s">
-        <v>1383</v>
+        <v>1433</v>
       </c>
       <c r="G118" t="s">
         <v>823</v>
@@ -16711,13 +17235,13 @@
         <v>830</v>
       </c>
       <c r="D119" t="s">
-        <v>1403</v>
+        <v>1453</v>
       </c>
       <c r="E119" t="s">
         <v>112</v>
       </c>
       <c r="F119" t="s">
-        <v>1383</v>
+        <v>1433</v>
       </c>
       <c r="G119" t="s">
         <v>831</v>
@@ -16734,13 +17258,13 @@
         <v>837</v>
       </c>
       <c r="D120" t="s">
-        <v>1403</v>
+        <v>1453</v>
       </c>
       <c r="E120" t="s">
         <v>112</v>
       </c>
       <c r="F120" t="s">
-        <v>1383</v>
+        <v>1433</v>
       </c>
       <c r="G120" t="s">
         <v>838</v>
@@ -16757,13 +17281,13 @@
         <v>844</v>
       </c>
       <c r="D121" t="s">
-        <v>1403</v>
+        <v>1453</v>
       </c>
       <c r="E121" t="s">
         <v>112</v>
       </c>
       <c r="F121" t="s">
-        <v>1383</v>
+        <v>1433</v>
       </c>
       <c r="G121" t="s">
         <v>845</v>
@@ -16780,13 +17304,13 @@
         <v>852</v>
       </c>
       <c r="D122" t="s">
-        <v>1403</v>
+        <v>1453</v>
       </c>
       <c r="E122" t="s">
         <v>26</v>
       </c>
       <c r="F122" t="s">
-        <v>1383</v>
+        <v>1433</v>
       </c>
       <c r="G122" t="s">
         <v>853</v>
@@ -16803,13 +17327,13 @@
         <v>860</v>
       </c>
       <c r="D123" t="s">
-        <v>1403</v>
+        <v>1453</v>
       </c>
       <c r="E123" t="s">
         <v>112</v>
       </c>
       <c r="F123" t="s">
-        <v>1383</v>
+        <v>1433</v>
       </c>
       <c r="G123" t="s">
         <v>861</v>
@@ -16826,13 +17350,13 @@
         <v>868</v>
       </c>
       <c r="D124" t="s">
-        <v>1403</v>
+        <v>1453</v>
       </c>
       <c r="E124" t="s">
         <v>112</v>
       </c>
       <c r="F124" t="s">
-        <v>1383</v>
+        <v>1433</v>
       </c>
       <c r="G124" t="s">
         <v>869</v>
@@ -16849,13 +17373,13 @@
         <v>876</v>
       </c>
       <c r="D125" t="s">
-        <v>1403</v>
+        <v>1453</v>
       </c>
       <c r="E125" t="s">
         <v>112</v>
       </c>
       <c r="F125" t="s">
-        <v>1383</v>
+        <v>1433</v>
       </c>
       <c r="G125" t="s">
         <v>878</v>
@@ -16872,13 +17396,13 @@
         <v>885</v>
       </c>
       <c r="D126" t="s">
-        <v>1403</v>
+        <v>1453</v>
       </c>
       <c r="E126" t="s">
         <v>112</v>
       </c>
       <c r="F126" t="s">
-        <v>1383</v>
+        <v>1433</v>
       </c>
       <c r="G126" t="s">
         <v>886</v>
@@ -16895,13 +17419,13 @@
         <v>893</v>
       </c>
       <c r="D127" t="s">
-        <v>1403</v>
+        <v>1453</v>
       </c>
       <c r="E127" t="s">
         <v>112</v>
       </c>
       <c r="F127" t="s">
-        <v>1383</v>
+        <v>1433</v>
       </c>
       <c r="G127" t="s">
         <v>894</v>
@@ -16918,13 +17442,13 @@
         <v>901</v>
       </c>
       <c r="D128" t="s">
-        <v>1403</v>
+        <v>1453</v>
       </c>
       <c r="E128" t="s">
         <v>453</v>
       </c>
       <c r="F128" t="s">
-        <v>1383</v>
+        <v>1433</v>
       </c>
       <c r="G128" t="s">
         <v>902</v>
@@ -16941,13 +17465,13 @@
         <v>909</v>
       </c>
       <c r="D129" t="s">
-        <v>1403</v>
+        <v>1453</v>
       </c>
       <c r="E129" t="s">
         <v>112</v>
       </c>
       <c r="F129" t="s">
-        <v>1383</v>
+        <v>1433</v>
       </c>
       <c r="G129" t="s">
         <v>910</v>
@@ -16964,13 +17488,13 @@
         <v>916</v>
       </c>
       <c r="D130" t="s">
-        <v>1403</v>
+        <v>1453</v>
       </c>
       <c r="E130" t="s">
         <v>112</v>
       </c>
       <c r="F130" t="s">
-        <v>1383</v>
+        <v>1433</v>
       </c>
       <c r="G130" t="s">
         <v>917</v>
@@ -16987,13 +17511,13 @@
         <v>926</v>
       </c>
       <c r="D131" t="s">
-        <v>1403</v>
+        <v>1453</v>
       </c>
       <c r="E131" t="s">
         <v>112</v>
       </c>
       <c r="F131" t="s">
-        <v>1383</v>
+        <v>1433</v>
       </c>
       <c r="G131" t="s">
         <v>927</v>
@@ -17010,13 +17534,13 @@
         <v>934</v>
       </c>
       <c r="D132" t="s">
-        <v>1403</v>
+        <v>1453</v>
       </c>
       <c r="E132" t="s">
         <v>112</v>
       </c>
       <c r="F132" t="s">
-        <v>1383</v>
+        <v>1433</v>
       </c>
       <c r="G132" t="s">
         <v>935</v>
@@ -17033,13 +17557,13 @@
         <v>942</v>
       </c>
       <c r="D133" t="s">
-        <v>1403</v>
+        <v>1453</v>
       </c>
       <c r="E133" t="s">
         <v>112</v>
       </c>
       <c r="F133" t="s">
-        <v>1383</v>
+        <v>1433</v>
       </c>
       <c r="G133" t="s">
         <v>943</v>
@@ -17056,13 +17580,13 @@
         <v>950</v>
       </c>
       <c r="D134" t="s">
-        <v>1403</v>
+        <v>1453</v>
       </c>
       <c r="E134" t="s">
         <v>112</v>
       </c>
       <c r="F134" t="s">
-        <v>1383</v>
+        <v>1433</v>
       </c>
       <c r="G134" t="s">
         <v>951</v>
@@ -17079,13 +17603,13 @@
         <v>958</v>
       </c>
       <c r="D135" t="s">
-        <v>1403</v>
+        <v>1453</v>
       </c>
       <c r="E135" t="s">
         <v>112</v>
       </c>
       <c r="F135" t="s">
-        <v>1383</v>
+        <v>1433</v>
       </c>
       <c r="G135" t="s">
         <v>960</v>
@@ -17102,13 +17626,13 @@
         <v>967</v>
       </c>
       <c r="D136" t="s">
-        <v>1403</v>
+        <v>1453</v>
       </c>
       <c r="E136" t="s">
         <v>112</v>
       </c>
       <c r="F136" t="s">
-        <v>1383</v>
+        <v>1433</v>
       </c>
       <c r="G136" t="s">
         <v>968</v>
@@ -17125,13 +17649,13 @@
         <v>974</v>
       </c>
       <c r="D137" t="s">
-        <v>1403</v>
+        <v>1453</v>
       </c>
       <c r="E137" t="s">
         <v>112</v>
       </c>
       <c r="F137" t="s">
-        <v>1383</v>
+        <v>1433</v>
       </c>
       <c r="G137" t="s">
         <v>975</v>
@@ -17148,13 +17672,13 @@
         <v>981</v>
       </c>
       <c r="D138" t="s">
-        <v>1403</v>
+        <v>1453</v>
       </c>
       <c r="E138" t="s">
         <v>112</v>
       </c>
       <c r="F138" t="s">
-        <v>1383</v>
+        <v>1433</v>
       </c>
       <c r="G138" t="s">
         <v>982</v>
@@ -17171,13 +17695,13 @@
         <v>989</v>
       </c>
       <c r="D139" t="s">
-        <v>1403</v>
+        <v>1453</v>
       </c>
       <c r="E139" t="s">
         <v>112</v>
       </c>
       <c r="F139" t="s">
-        <v>1383</v>
+        <v>1433</v>
       </c>
       <c r="G139" t="s">
         <v>990</v>
@@ -17194,13 +17718,13 @@
         <v>997</v>
       </c>
       <c r="D140" t="s">
-        <v>1403</v>
+        <v>1453</v>
       </c>
       <c r="E140" t="s">
         <v>112</v>
       </c>
       <c r="F140" t="s">
-        <v>1383</v>
+        <v>1433</v>
       </c>
       <c r="G140" t="s">
         <v>998</v>
@@ -17217,13 +17741,13 @@
         <v>1006</v>
       </c>
       <c r="D141" t="s">
-        <v>1403</v>
+        <v>1453</v>
       </c>
       <c r="E141" t="s">
         <v>112</v>
       </c>
       <c r="F141" t="s">
-        <v>1383</v>
+        <v>1433</v>
       </c>
       <c r="G141" t="s">
         <v>1007</v>
@@ -17240,13 +17764,13 @@
         <v>1014</v>
       </c>
       <c r="D142" t="s">
-        <v>1403</v>
+        <v>1453</v>
       </c>
       <c r="E142" t="s">
         <v>112</v>
       </c>
       <c r="F142" t="s">
-        <v>1383</v>
+        <v>1433</v>
       </c>
       <c r="G142" t="s">
         <v>1015</v>
@@ -17263,13 +17787,13 @@
         <v>1021</v>
       </c>
       <c r="D143" t="s">
-        <v>1403</v>
+        <v>1453</v>
       </c>
       <c r="E143" t="s">
         <v>453</v>
       </c>
       <c r="F143" t="s">
-        <v>1383</v>
+        <v>1433</v>
       </c>
       <c r="G143" t="s">
         <v>1022</v>
@@ -17286,13 +17810,13 @@
         <v>1029</v>
       </c>
       <c r="D144" t="s">
-        <v>1403</v>
+        <v>1453</v>
       </c>
       <c r="E144" t="s">
         <v>112</v>
       </c>
       <c r="F144" t="s">
-        <v>1383</v>
+        <v>1433</v>
       </c>
       <c r="G144" t="s">
         <v>1031</v>
@@ -17309,13 +17833,13 @@
         <v>1037</v>
       </c>
       <c r="D145" t="s">
-        <v>1403</v>
+        <v>1453</v>
       </c>
       <c r="E145" t="s">
         <v>112</v>
       </c>
       <c r="F145" t="s">
-        <v>1383</v>
+        <v>1433</v>
       </c>
       <c r="G145" t="s">
         <v>1038</v>
@@ -17329,19 +17853,19 @@
         <v>999</v>
       </c>
       <c r="C146" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="D146" t="s">
-        <v>1403</v>
+        <v>1453</v>
       </c>
       <c r="E146" t="s">
         <v>112</v>
       </c>
       <c r="F146" t="s">
-        <v>1383</v>
+        <v>1433</v>
       </c>
       <c r="G146" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.25">
@@ -17352,19 +17876,19 @@
         <v>999</v>
       </c>
       <c r="C147" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="D147" t="s">
-        <v>1403</v>
+        <v>1453</v>
       </c>
       <c r="E147" t="s">
         <v>112</v>
       </c>
       <c r="F147" t="s">
-        <v>1383</v>
+        <v>1433</v>
       </c>
       <c r="G147" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.25">
@@ -17375,19 +17899,19 @@
         <v>999</v>
       </c>
       <c r="C148" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="D148" t="s">
-        <v>1403</v>
+        <v>1453</v>
       </c>
       <c r="E148" t="s">
         <v>112</v>
       </c>
       <c r="F148" t="s">
-        <v>1383</v>
+        <v>1433</v>
       </c>
       <c r="G148" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.25">
@@ -17398,19 +17922,19 @@
         <v>999</v>
       </c>
       <c r="C149" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="D149" t="s">
-        <v>1403</v>
+        <v>1453</v>
       </c>
       <c r="E149" t="s">
         <v>95</v>
       </c>
       <c r="F149" t="s">
-        <v>1383</v>
+        <v>1433</v>
       </c>
       <c r="G149" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.25">
@@ -17421,19 +17945,19 @@
         <v>999</v>
       </c>
       <c r="C150" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="D150" t="s">
-        <v>1403</v>
+        <v>1453</v>
       </c>
       <c r="E150" t="s">
         <v>112</v>
       </c>
       <c r="F150" t="s">
-        <v>1383</v>
+        <v>1433</v>
       </c>
       <c r="G150" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.25">
@@ -17444,19 +17968,157 @@
         <v>999</v>
       </c>
       <c r="C151" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="D151" t="s">
-        <v>1403</v>
+        <v>1453</v>
       </c>
       <c r="E151" t="s">
         <v>95</v>
       </c>
       <c r="F151" t="s">
-        <v>1383</v>
+        <v>1433</v>
       </c>
       <c r="G151" t="s">
-        <v>1085</v>
+        <v>1086</v>
+      </c>
+    </row>
+    <row r="152" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A152" t="s">
+        <v>27</v>
+      </c>
+      <c r="B152" t="s">
+        <v>1095</v>
+      </c>
+      <c r="C152" t="s">
+        <v>1093</v>
+      </c>
+      <c r="D152" t="s">
+        <v>1453</v>
+      </c>
+      <c r="E152" t="s">
+        <v>112</v>
+      </c>
+      <c r="F152" t="s">
+        <v>1433</v>
+      </c>
+      <c r="G152" t="s">
+        <v>1094</v>
+      </c>
+    </row>
+    <row r="153" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A153" t="s">
+        <v>27</v>
+      </c>
+      <c r="B153" t="s">
+        <v>1095</v>
+      </c>
+      <c r="C153" t="s">
+        <v>1102</v>
+      </c>
+      <c r="D153" t="s">
+        <v>1453</v>
+      </c>
+      <c r="E153" t="s">
+        <v>112</v>
+      </c>
+      <c r="F153" t="s">
+        <v>1433</v>
+      </c>
+      <c r="G153" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="154" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A154" t="s">
+        <v>27</v>
+      </c>
+      <c r="B154" t="s">
+        <v>1095</v>
+      </c>
+      <c r="C154" t="s">
+        <v>1109</v>
+      </c>
+      <c r="D154" t="s">
+        <v>1453</v>
+      </c>
+      <c r="E154" t="s">
+        <v>453</v>
+      </c>
+      <c r="F154" t="s">
+        <v>1433</v>
+      </c>
+      <c r="G154" t="s">
+        <v>1110</v>
+      </c>
+    </row>
+    <row r="155" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A155" t="s">
+        <v>27</v>
+      </c>
+      <c r="B155" t="s">
+        <v>1095</v>
+      </c>
+      <c r="C155" t="s">
+        <v>1117</v>
+      </c>
+      <c r="D155" t="s">
+        <v>1453</v>
+      </c>
+      <c r="E155" t="s">
+        <v>112</v>
+      </c>
+      <c r="F155" t="s">
+        <v>1433</v>
+      </c>
+      <c r="G155" t="s">
+        <v>1118</v>
+      </c>
+    </row>
+    <row r="156" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A156" t="s">
+        <v>27</v>
+      </c>
+      <c r="B156" t="s">
+        <v>1095</v>
+      </c>
+      <c r="C156" t="s">
+        <v>1124</v>
+      </c>
+      <c r="D156" t="s">
+        <v>1453</v>
+      </c>
+      <c r="E156" t="s">
+        <v>95</v>
+      </c>
+      <c r="F156" t="s">
+        <v>1433</v>
+      </c>
+      <c r="G156" t="s">
+        <v>1125</v>
+      </c>
+    </row>
+    <row r="157" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A157" t="s">
+        <v>27</v>
+      </c>
+      <c r="B157" t="s">
+        <v>1095</v>
+      </c>
+      <c r="C157" t="s">
+        <v>1132</v>
+      </c>
+      <c r="D157" t="s">
+        <v>1453</v>
+      </c>
+      <c r="E157" t="s">
+        <v>112</v>
+      </c>
+      <c r="F157" t="s">
+        <v>1433</v>
+      </c>
+      <c r="G157" t="s">
+        <v>1133</v>
       </c>
     </row>
   </sheetData>
@@ -17470,7 +18132,7 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>1404</v>
+        <v>1454</v>
       </c>
       <c r="B1"/>
       <c r="C1"/>
@@ -17478,7 +18140,7 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1405</v>
+        <v>1455</v>
       </c>
       <c r="B2"/>
       <c r="C2"/>
@@ -17489,181 +18151,181 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>1406</v>
+        <v>1456</v>
       </c>
       <c r="C3" t="s">
-        <v>1407</v>
+        <v>1457</v>
       </c>
       <c r="D3" t="s">
-        <v>1408</v>
+        <v>1458</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1409</v>
+        <v>1459</v>
       </c>
       <c r="B4" t="s">
-        <v>1410</v>
+        <v>1460</v>
       </c>
       <c r="C4" t="s">
-        <v>1411</v>
+        <v>1461</v>
       </c>
       <c r="D4" t="s">
-        <v>1412</v>
+        <v>1462</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1413</v>
+        <v>1463</v>
       </c>
       <c r="B5" t="s">
-        <v>1410</v>
+        <v>1460</v>
       </c>
       <c r="C5" t="s">
-        <v>1414</v>
+        <v>1464</v>
       </c>
       <c r="D5" t="s">
-        <v>1415</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>1416</v>
+        <v>1466</v>
       </c>
       <c r="B6" t="s">
-        <v>1410</v>
+        <v>1460</v>
       </c>
       <c r="C6" t="s">
-        <v>1417</v>
+        <v>1467</v>
       </c>
       <c r="D6" t="s">
-        <v>1418</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>1419</v>
+        <v>1469</v>
       </c>
       <c r="B7" t="s">
-        <v>1410</v>
+        <v>1460</v>
       </c>
       <c r="C7" t="s">
-        <v>1420</v>
+        <v>1470</v>
       </c>
       <c r="D7" t="s">
-        <v>1421</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>1422</v>
+        <v>1472</v>
       </c>
       <c r="B8" t="s">
-        <v>1410</v>
+        <v>1460</v>
       </c>
       <c r="C8" t="s">
-        <v>1423</v>
+        <v>1473</v>
       </c>
       <c r="D8" t="s">
-        <v>1424</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>1425</v>
+        <v>1475</v>
       </c>
       <c r="B9" t="s">
-        <v>1426</v>
+        <v>1476</v>
       </c>
       <c r="C9" t="s">
-        <v>1427</v>
+        <v>1477</v>
       </c>
       <c r="D9" t="s">
-        <v>1428</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>1429</v>
+        <v>1479</v>
       </c>
       <c r="B10" t="s">
-        <v>1426</v>
+        <v>1476</v>
       </c>
       <c r="C10" t="s">
-        <v>1430</v>
+        <v>1480</v>
       </c>
       <c r="D10" t="s">
-        <v>1431</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>1432</v>
+        <v>1482</v>
       </c>
       <c r="B11" t="s">
-        <v>1426</v>
+        <v>1476</v>
       </c>
       <c r="C11" t="s">
-        <v>1433</v>
+        <v>1483</v>
       </c>
       <c r="D11" t="s">
-        <v>1434</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>1435</v>
+        <v>1485</v>
       </c>
       <c r="B12" t="s">
-        <v>1436</v>
+        <v>1486</v>
       </c>
       <c r="C12" t="s">
-        <v>1437</v>
+        <v>1487</v>
       </c>
       <c r="D12" t="s">
-        <v>1438</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>1439</v>
+        <v>1489</v>
       </c>
       <c r="B13" t="s">
-        <v>1436</v>
+        <v>1486</v>
       </c>
       <c r="C13" t="s">
-        <v>1440</v>
+        <v>1490</v>
       </c>
       <c r="D13" t="s">
-        <v>1441</v>
+        <v>1491</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>1442</v>
+        <v>1492</v>
       </c>
       <c r="B14" t="s">
         <v>877</v>
       </c>
       <c r="C14" t="s">
-        <v>1443</v>
+        <v>1493</v>
       </c>
       <c r="D14" t="s">
-        <v>1444</v>
+        <v>1494</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>1445</v>
+        <v>1495</v>
       </c>
       <c r="B15" t="s">
         <v>877</v>
       </c>
       <c r="C15" t="s">
-        <v>1446</v>
+        <v>1496</v>
       </c>
       <c r="D15" t="s">
-        <v>1447</v>
+        <v>1497</v>
       </c>
     </row>
   </sheetData>
@@ -17682,7 +18344,7 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>1448</v>
+        <v>1498</v>
       </c>
       <c r="B1"/>
       <c r="C1"/>
@@ -17690,133 +18352,133 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>1449</v>
+        <v>1499</v>
       </c>
       <c r="B3" t="s">
-        <v>1450</v>
+        <v>1500</v>
       </c>
       <c r="C3" t="s">
-        <v>1451</v>
+        <v>1501</v>
       </c>
       <c r="D3" t="s">
-        <v>1452</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1132</v>
+        <v>1179</v>
       </c>
       <c r="B4" t="s">
-        <v>1453</v>
+        <v>1503</v>
       </c>
       <c r="C4" t="s">
-        <v>1454</v>
+        <v>1504</v>
       </c>
       <c r="D4" t="s">
-        <v>1455</v>
+        <v>1505</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1137</v>
+        <v>1184</v>
       </c>
       <c r="B5" t="s">
-        <v>1456</v>
+        <v>1506</v>
       </c>
       <c r="C5" t="s">
-        <v>1457</v>
+        <v>1507</v>
       </c>
       <c r="D5" t="s">
-        <v>1458</v>
+        <v>1508</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>1141</v>
+        <v>1188</v>
       </c>
       <c r="B6" t="s">
-        <v>1459</v>
+        <v>1509</v>
       </c>
       <c r="C6" t="s">
-        <v>1460</v>
+        <v>1510</v>
       </c>
       <c r="D6" t="s">
-        <v>1461</v>
+        <v>1511</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>1145</v>
+        <v>1192</v>
       </c>
       <c r="B7" t="s">
-        <v>1462</v>
+        <v>1512</v>
       </c>
       <c r="C7" t="s">
-        <v>1463</v>
+        <v>1513</v>
       </c>
       <c r="D7" t="s">
-        <v>1464</v>
+        <v>1514</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>1149</v>
+        <v>1196</v>
       </c>
       <c r="B8" t="s">
-        <v>1465</v>
+        <v>1515</v>
       </c>
       <c r="C8" t="s">
-        <v>1466</v>
+        <v>1516</v>
       </c>
       <c r="D8" t="s">
-        <v>1467</v>
+        <v>1517</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>1153</v>
+        <v>1200</v>
       </c>
       <c r="B9" t="s">
-        <v>1468</v>
+        <v>1518</v>
       </c>
       <c r="C9" t="s">
-        <v>1469</v>
+        <v>1519</v>
       </c>
       <c r="D9" t="s">
-        <v>1470</v>
+        <v>1520</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>1157</v>
+        <v>1204</v>
       </c>
       <c r="B10" t="s">
-        <v>1471</v>
+        <v>1521</v>
       </c>
       <c r="C10" t="s">
-        <v>1472</v>
+        <v>1522</v>
       </c>
       <c r="D10" t="s">
-        <v>1473</v>
+        <v>1523</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>1161</v>
+        <v>1208</v>
       </c>
       <c r="B11" t="s">
-        <v>1474</v>
+        <v>1524</v>
       </c>
       <c r="C11" t="s">
-        <v>1475</v>
+        <v>1525</v>
       </c>
       <c r="D11" t="s">
-        <v>1476</v>
+        <v>1526</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>1477</v>
+        <v>1527</v>
       </c>
       <c r="B13"/>
       <c r="C13"/>
@@ -17824,72 +18486,72 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>1478</v>
+        <v>1528</v>
       </c>
       <c r="B14" t="s">
         <v>28</v>
       </c>
       <c r="C14" t="s">
-        <v>1479</v>
+        <v>1529</v>
       </c>
       <c r="D14" t="s">
-        <v>1480</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>1481</v>
+        <v>1531</v>
       </c>
       <c r="B15" t="s">
         <v>29</v>
       </c>
       <c r="C15" t="s">
-        <v>1482</v>
+        <v>1532</v>
       </c>
       <c r="D15" t="s">
-        <v>1483</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>1484</v>
+        <v>1534</v>
       </c>
       <c r="B16" t="s">
         <v>29</v>
       </c>
       <c r="C16" t="s">
-        <v>1485</v>
+        <v>1535</v>
       </c>
       <c r="D16" t="s">
-        <v>1486</v>
+        <v>1536</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>1487</v>
+        <v>1537</v>
       </c>
       <c r="B17" t="s">
         <v>29</v>
       </c>
       <c r="C17" t="s">
-        <v>1488</v>
+        <v>1538</v>
       </c>
       <c r="D17" t="s">
-        <v>1489</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>1490</v>
+        <v>1540</v>
       </c>
       <c r="B18" t="s">
-        <v>1491</v>
+        <v>1541</v>
       </c>
       <c r="C18" t="s">
-        <v>1492</v>
+        <v>1542</v>
       </c>
       <c r="D18" t="s">
-        <v>1493</v>
+        <v>1543</v>
       </c>
     </row>
   </sheetData>
@@ -17908,7 +18570,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>1494</v>
+        <v>1544</v>
       </c>
       <c r="B1"/>
       <c r="C1"/>
@@ -17918,7 +18580,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1495</v>
+        <v>1545</v>
       </c>
       <c r="B2"/>
       <c r="C2"/>
@@ -17928,99 +18590,99 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1496</v>
+        <v>1546</v>
       </c>
       <c r="B4" t="s">
-        <v>1497</v>
+        <v>1547</v>
       </c>
       <c r="C4" t="s">
-        <v>1498</v>
+        <v>1548</v>
       </c>
       <c r="D4" t="s">
-        <v>1499</v>
+        <v>1549</v>
       </c>
       <c r="E4" t="s">
-        <v>1500</v>
+        <v>1550</v>
       </c>
       <c r="F4" t="s">
-        <v>1501</v>
+        <v>1551</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1502</v>
+        <v>1552</v>
       </c>
       <c r="B5" t="s">
-        <v>1503</v>
+        <v>1553</v>
       </c>
       <c r="C5" t="s">
-        <v>1504</v>
+        <v>1554</v>
       </c>
       <c r="D5" t="s">
-        <v>1505</v>
+        <v>1555</v>
       </c>
       <c r="E5" t="s">
-        <v>1506</v>
+        <v>1556</v>
       </c>
       <c r="F5" t="s">
-        <v>1507</v>
+        <v>1557</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>1508</v>
+        <v>1558</v>
       </c>
       <c r="B6" t="s">
-        <v>1509</v>
+        <v>1559</v>
       </c>
       <c r="C6" t="s">
-        <v>1510</v>
+        <v>1560</v>
       </c>
       <c r="D6" t="s">
-        <v>1511</v>
+        <v>1561</v>
       </c>
       <c r="E6" t="s">
-        <v>1512</v>
+        <v>1562</v>
       </c>
       <c r="F6" t="s">
-        <v>1513</v>
+        <v>1563</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>1514</v>
+        <v>1564</v>
       </c>
       <c r="B7" t="s">
-        <v>1509</v>
+        <v>1559</v>
       </c>
       <c r="C7" t="s">
-        <v>1515</v>
+        <v>1565</v>
       </c>
       <c r="D7" t="s">
-        <v>1516</v>
+        <v>1566</v>
       </c>
       <c r="E7" t="s">
-        <v>1517</v>
+        <v>1567</v>
       </c>
       <c r="F7" t="s">
-        <v>1518</v>
+        <v>1568</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>1519</v>
+        <v>1569</v>
       </c>
       <c r="B8" t="s">
-        <v>1520</v>
+        <v>1570</v>
       </c>
       <c r="C8" t="s">
-        <v>1521</v>
+        <v>1571</v>
       </c>
       <c r="D8" t="s">
-        <v>1522</v>
+        <v>1572</v>
       </c>
       <c r="E8" t="s">
-        <v>1523</v>
+        <v>1573</v>
       </c>
       <c r="F8" t="s">
         <v>629</v>
@@ -18028,19 +18690,19 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>1524</v>
+        <v>1574</v>
       </c>
       <c r="B9" t="s">
-        <v>1525</v>
+        <v>1575</v>
       </c>
       <c r="C9" t="s">
-        <v>1526</v>
+        <v>1576</v>
       </c>
       <c r="D9" t="s">
-        <v>1527</v>
+        <v>1577</v>
       </c>
       <c r="E9" t="s">
-        <v>1528</v>
+        <v>1578</v>
       </c>
       <c r="F9" t="s">
         <v>369</v>
@@ -18048,39 +18710,39 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>1529</v>
+        <v>1579</v>
       </c>
       <c r="B10" t="s">
-        <v>1530</v>
+        <v>1580</v>
       </c>
       <c r="C10" t="s">
-        <v>1531</v>
+        <v>1581</v>
       </c>
       <c r="D10" t="s">
-        <v>1532</v>
+        <v>1582</v>
       </c>
       <c r="E10" t="s">
-        <v>1533</v>
+        <v>1583</v>
       </c>
       <c r="F10" t="s">
-        <v>1534</v>
+        <v>1584</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>1535</v>
+        <v>1585</v>
       </c>
       <c r="B11" t="s">
-        <v>1536</v>
+        <v>1586</v>
       </c>
       <c r="C11" t="s">
-        <v>1537</v>
+        <v>1587</v>
       </c>
       <c r="D11" t="s">
-        <v>1538</v>
+        <v>1588</v>
       </c>
       <c r="E11" t="s">
-        <v>1539</v>
+        <v>1589</v>
       </c>
       <c r="F11" t="s">
         <v>47</v>
@@ -18088,99 +18750,99 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>1540</v>
+        <v>1590</v>
       </c>
       <c r="B12" t="s">
-        <v>1541</v>
+        <v>1591</v>
       </c>
       <c r="C12" t="s">
-        <v>1542</v>
+        <v>1592</v>
       </c>
       <c r="D12" t="s">
-        <v>1543</v>
+        <v>1593</v>
       </c>
       <c r="E12" t="s">
-        <v>1544</v>
+        <v>1594</v>
       </c>
       <c r="F12" t="s">
-        <v>1545</v>
+        <v>1595</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>1546</v>
+        <v>1596</v>
       </c>
       <c r="B13" t="s">
-        <v>1547</v>
+        <v>1597</v>
       </c>
       <c r="C13" t="s">
-        <v>1548</v>
+        <v>1598</v>
       </c>
       <c r="D13" t="s">
-        <v>1549</v>
+        <v>1599</v>
       </c>
       <c r="E13" t="s">
-        <v>1550</v>
+        <v>1600</v>
       </c>
       <c r="F13" t="s">
-        <v>1551</v>
+        <v>1601</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>1552</v>
+        <v>1602</v>
       </c>
       <c r="B14" t="s">
-        <v>1553</v>
+        <v>1603</v>
       </c>
       <c r="C14" t="s">
-        <v>1554</v>
+        <v>1604</v>
       </c>
       <c r="D14" t="s">
-        <v>1555</v>
+        <v>1605</v>
       </c>
       <c r="E14" t="s">
-        <v>1556</v>
+        <v>1606</v>
       </c>
       <c r="F14" t="s">
-        <v>1557</v>
+        <v>1607</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>1558</v>
+        <v>1608</v>
       </c>
       <c r="B15" t="s">
-        <v>1559</v>
+        <v>1609</v>
       </c>
       <c r="C15" t="s">
-        <v>1560</v>
+        <v>1610</v>
       </c>
       <c r="D15" t="s">
-        <v>1561</v>
+        <v>1611</v>
       </c>
       <c r="E15" t="s">
-        <v>1562</v>
+        <v>1612</v>
       </c>
       <c r="F15" t="s">
-        <v>1563</v>
+        <v>1613</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>1564</v>
+        <v>1614</v>
       </c>
       <c r="B16" t="s">
-        <v>1565</v>
+        <v>1615</v>
       </c>
       <c r="C16" t="s">
-        <v>1566</v>
+        <v>1616</v>
       </c>
       <c r="D16" t="s">
-        <v>1567</v>
+        <v>1617</v>
       </c>
       <c r="E16" t="s">
-        <v>1568</v>
+        <v>1618</v>
       </c>
       <c r="F16" t="s">
         <v>207</v>
@@ -18188,19 +18850,19 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>1569</v>
+        <v>1619</v>
       </c>
       <c r="B17" t="s">
-        <v>1570</v>
+        <v>1620</v>
       </c>
       <c r="C17" t="s">
-        <v>1571</v>
+        <v>1621</v>
       </c>
       <c r="D17" t="s">
-        <v>1572</v>
+        <v>1622</v>
       </c>
       <c r="E17" t="s">
-        <v>1573</v>
+        <v>1623</v>
       </c>
       <c r="F17" t="s">
         <v>378</v>
@@ -18222,7 +18884,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>1574</v>
+        <v>1624</v>
       </c>
       <c r="B1"/>
       <c r="C1"/>
@@ -18232,7 +18894,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1575</v>
+        <v>1625</v>
       </c>
       <c r="B2"/>
       <c r="C2"/>
@@ -18242,162 +18904,162 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1576</v>
+        <v>1626</v>
       </c>
       <c r="B4" t="s">
-        <v>1474</v>
+        <v>1524</v>
       </c>
       <c r="C4" t="s">
-        <v>1577</v>
+        <v>1627</v>
       </c>
       <c r="D4" t="s">
-        <v>1578</v>
+        <v>1628</v>
       </c>
       <c r="E4" t="s">
-        <v>1129</v>
+        <v>1176</v>
       </c>
       <c r="F4" t="s">
-        <v>1579</v>
+        <v>1629</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1132</v>
+        <v>1179</v>
       </c>
       <c r="B5" t="s">
-        <v>1580</v>
+        <v>1630</v>
       </c>
       <c r="C5" t="s">
-        <v>1581</v>
+        <v>1631</v>
       </c>
       <c r="D5" t="s">
-        <v>1582</v>
+        <v>1632</v>
       </c>
       <c r="E5" t="s">
-        <v>1583</v>
+        <v>1633</v>
       </c>
       <c r="F5" t="s">
-        <v>1584</v>
+        <v>1634</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>1137</v>
+        <v>1184</v>
       </c>
       <c r="B6" t="s">
-        <v>1585</v>
+        <v>1635</v>
       </c>
       <c r="C6" t="s">
-        <v>1586</v>
+        <v>1636</v>
       </c>
       <c r="D6" t="s">
-        <v>1587</v>
+        <v>1637</v>
       </c>
       <c r="E6" t="s">
-        <v>1588</v>
+        <v>1638</v>
       </c>
       <c r="F6" t="s">
-        <v>1584</v>
+        <v>1634</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>1141</v>
+        <v>1188</v>
       </c>
       <c r="B7" t="s">
-        <v>1589</v>
+        <v>1639</v>
       </c>
       <c r="C7" t="s">
-        <v>1590</v>
+        <v>1640</v>
       </c>
       <c r="D7" t="s">
-        <v>1591</v>
+        <v>1641</v>
       </c>
       <c r="E7" t="s">
-        <v>1592</v>
+        <v>1642</v>
       </c>
       <c r="F7" t="s">
-        <v>1584</v>
+        <v>1634</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>1145</v>
+        <v>1192</v>
       </c>
       <c r="B8" t="s">
-        <v>1593</v>
+        <v>1643</v>
       </c>
       <c r="C8" t="s">
-        <v>1594</v>
+        <v>1644</v>
       </c>
       <c r="D8" t="s">
-        <v>1595</v>
+        <v>1645</v>
       </c>
       <c r="E8" t="s">
-        <v>1596</v>
+        <v>1646</v>
       </c>
       <c r="F8" t="s">
-        <v>1584</v>
+        <v>1634</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>1149</v>
+        <v>1196</v>
       </c>
       <c r="B9" t="s">
-        <v>1597</v>
+        <v>1647</v>
       </c>
       <c r="C9" t="s">
-        <v>1598</v>
+        <v>1648</v>
       </c>
       <c r="D9" t="s">
-        <v>1599</v>
+        <v>1649</v>
       </c>
       <c r="E9" t="s">
         <v>877</v>
       </c>
       <c r="F9" t="s">
-        <v>1600</v>
+        <v>1650</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>1153</v>
+        <v>1200</v>
       </c>
       <c r="B10" t="s">
-        <v>1601</v>
+        <v>1651</v>
       </c>
       <c r="C10" t="s">
-        <v>1602</v>
+        <v>1652</v>
       </c>
       <c r="D10" t="s">
-        <v>1603</v>
+        <v>1653</v>
       </c>
       <c r="E10" t="s">
-        <v>1604</v>
+        <v>1654</v>
       </c>
       <c r="F10" t="s">
-        <v>1600</v>
+        <v>1650</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>1157</v>
+        <v>1204</v>
       </c>
       <c r="B11" t="s">
-        <v>1605</v>
+        <v>1655</v>
       </c>
       <c r="C11" t="s">
-        <v>1606</v>
+        <v>1656</v>
       </c>
       <c r="D11" t="s">
-        <v>1607</v>
+        <v>1657</v>
       </c>
       <c r="E11" t="s">
-        <v>1608</v>
+        <v>1658</v>
       </c>
       <c r="F11" t="s">
-        <v>1609</v>
+        <v>1659</v>
       </c>
     </row>
   </sheetData>

--- a/audits/FORTLESS_MASTER_SECURITY_UI_BUG_TRACKER.xlsx
+++ b/audits/FORTLESS_MASTER_SECURITY_UI_BUG_TRACKER.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4232" uniqueCount="1660">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4290" uniqueCount="1682">
   <si>
     <t>FORTLESS   /   ENGINEERING FINDINGS REGISTER</t>
   </si>
@@ -330,7 +330,7 @@
     <t>no explicit CSP/HSTS/X-Frame-Options/header middleware was identified in reviewed src/server.ts; edge Nginx or CDN configuration was not available in this review. There are inline scripts in public/app.html.</t>
   </si>
   <si>
-    <t>Deployed Nginx/edge security headers not checked</t>
+    <t>Deployed Nginx/edge security headers not checked | Batch 6 live check of the public URL (headers only): x-frame-options, x-content-type-options and referrer-policy are present (nginx); no Content-Security-Policy and no Strict-Transport-Security were returned.</t>
   </si>
   <si>
     <t>UI-01</t>
@@ -2673,7 +2673,7 @@
     <t>Check: on the live host NODE_ENV is production, cookies carry Secure and backups require a key.</t>
   </si>
   <si>
-    <t>[CONFIG_DEPENDENT] Observed from the running process and .env value NODE_ENV only; no secrets recorded. | AUDIT 3cb35de: SESSION_SECRET is empty in .env, so the process falls back to a random secret stored in data/.development-session-secret (config/index.ts:77). Cookie signing, CSRF tokens, TOTP secrets and per-account panel keys derive from that file, which sits in the data directory next to the database and backups. | AUDIT fc02778: Batch 3 re-check: SESSION_SECRET file fallback also affects restore (see NEW-375).</t>
+    <t>[CONFIG_DEPENDENT] Observed from the running process and .env value NODE_ENV only; no secrets recorded. | AUDIT 3cb35de: SESSION_SECRET is empty in .env, so the process falls back to a random secret stored in data/.development-session-secret (config/index.ts:77). Cookie signing, CSRF tokens, TOTP secrets and per-account panel keys derive from that file, which sits in the data directory next to the database and backups. | AUDIT fc02778: Batch 3 re-check: SESSION_SECRET file fallback also affects restore (see NEW-375). | Batch 6: the live Set-Cookie for fortless_device_id has no Secure attribute, consistent with NODE_ENV=development.</t>
   </si>
   <si>
     <t>NEW-362</t>
@@ -3438,6 +3438,57 @@
     <t>Test: simulate a timeout after the panel call; the retry adopts the existing subuser and creates the member row once.</t>
   </si>
   <si>
+    <t>NEW-394</t>
+  </si>
+  <si>
+    <t>Default CORS allowlist includes http://localhost:3021 with credentials, also in production</t>
+  </si>
+  <si>
+    <t>1ce958d</t>
+  </si>
+  <si>
+    <t>src/config/index.ts:39,74; src/server.ts:197-204</t>
+  </si>
+  <si>
+    <t>ALLOWED_ORIGINS defaults to 'https://fortless.net,http://localhost:3021' and the cors plugin is registered with credentials:true; nothing removes the localhost entry when NODE_ENV is production.</t>
+  </si>
+  <si>
+    <t>Any page served from a developer machine or malware on port 3021 is treated as a trusted origin by browsers of anyone running a local service there.</t>
+  </si>
+  <si>
+    <t>Default to the public origin only; add localhost origins through an explicit development setting and fail startup in production if a localhost origin is configured.</t>
+  </si>
+  <si>
+    <t>Test: in production mode the effective allowlist contains no loopback origin.</t>
+  </si>
+  <si>
+    <t>[CONFIRMED_CODE] Source trace; live value of ALLOWED_ORIGINS was not read (CONFIG_DEPENDENT).</t>
+  </si>
+  <si>
+    <t>NEW-395</t>
+  </si>
+  <si>
+    <t>CSRF tokens are not bound to the session and are issued to unauthenticated callers</t>
+  </si>
+  <si>
+    <t>src/server.ts:213-228,274-281,575-581</t>
+  </si>
+  <si>
+    <t>The token is an HMAC of a random nonce under SESSION_SECRET and any validly signed cookie/header pair passes. /api/v1/auth/csrf returns one to anyone. Nothing ties the token to the session or user.</t>
+  </si>
+  <si>
+    <t>An attacker who can set a cookie for the site (for example from a sibling subdomain such as the panel, or via a header injection elsewhere) can choose their own valid pair and bypass the check. SameSite=Lax session cookies reduce, but do not remove, the exposure.</t>
+  </si>
+  <si>
+    <t>Bind the token to the session id (HMAC over session id + nonce) and rotate it at login.</t>
+  </si>
+  <si>
+    <t>Test: a token issued for one session is rejected on another session and when anonymous.</t>
+  </si>
+  <si>
+    <t>[CONFIRMED_CODE] Source trace; defence-in-depth issue.</t>
+  </si>
+  <si>
     <t>FORTLESS   /   SECURITY &amp; PRODUCT QUALITY</t>
   </si>
   <si>
@@ -3456,10 +3507,10 @@
     <t>CLOSED &amp; TESTED</t>
   </si>
   <si>
-    <t>138</t>
-  </si>
-  <si>
-    <t>52</t>
+    <t>140</t>
+  </si>
+  <si>
+    <t>54</t>
   </si>
   <si>
     <t>58</t>
@@ -3495,396 +3546,402 @@
     <t>4</t>
   </si>
   <si>
+    <t>32</t>
+  </si>
+  <si>
+    <t>TESTED</t>
+  </si>
+  <si>
+    <t>CLOSED</t>
+  </si>
+  <si>
+    <t>LATEST VERIFIED COMMIT</t>
+  </si>
+  <si>
+    <t>REGRESSION</t>
+  </si>
+  <si>
+    <t>3cb35de (independent audit batch 1)</t>
+  </si>
+  <si>
+    <t>STATUS CONTRACT</t>
+  </si>
+  <si>
+    <t>Issue present in inspected source</t>
+  </si>
+  <si>
+    <t>Some code fixed; unresolved conditions remain</t>
+  </si>
+  <si>
+    <t>Fix observed in source; still needs regression/runtime validation</t>
+  </si>
+  <si>
+    <t>Question or risk not independently demonstrated</t>
+  </si>
+  <si>
+    <t>Requires an explicit product/security policy</t>
+  </si>
+  <si>
+    <t>Automated/authorized tests executed and evidence stored</t>
+  </si>
+  <si>
+    <t>Fix independently verified and accepted</t>
+  </si>
+  <si>
+    <t>Previously fixed behavior has returned</t>
+  </si>
+  <si>
+    <t>FORTLESS   /   30 SECURITY AUDIT DOMAINS</t>
+  </si>
+  <si>
+    <t>Static source review expanded at 6203687. Coverage is NOT an independent runtime, load, security or pixel-diff test.</t>
+  </si>
+  <si>
+    <t>#</t>
+  </si>
+  <si>
+    <t>Scope</t>
+  </si>
+  <si>
+    <t>Related finding IDs</t>
+  </si>
+  <si>
+    <t>Audit coverage</t>
+  </si>
+  <si>
+    <t>01</t>
+  </si>
+  <si>
+    <t>Authentication</t>
+  </si>
+  <si>
+    <t>Login/register/reset, brute force, enumeration</t>
+  </si>
+  <si>
+    <t>SEC-09, FTL-SEC-205, NEW-362, NEW-363, NEW-364, NEW-365, NEW-366, NEW-367</t>
+  </si>
+  <si>
+    <t>STATIC_PARTIAL</t>
+  </si>
+  <si>
+    <t>02</t>
+  </si>
+  <si>
+    <t>Sessions &amp; Devices</t>
+  </si>
+  <si>
+    <t>Token rotation, expiry, login/logout, revocation</t>
+  </si>
+  <si>
+    <t>SEC-03, SEC-04, FTL-SEC-202, NEW-363, NEW-368, NEW-377</t>
+  </si>
+  <si>
+    <t>03</t>
+  </si>
+  <si>
+    <t>MFA &amp; Passkeys</t>
+  </si>
+  <si>
+    <t>TOTP, WebAuthn, recovery, replay, UV</t>
+  </si>
+  <si>
+    <t>FTL-SEC-201, FTL-SEC-202, FTL-SEC-203, NEW-306, NEW-307, NEW-318, NEW-358, NEW-360, NEW-366, NEW-367</t>
+  </si>
+  <si>
+    <t>04</t>
+  </si>
+  <si>
+    <t>Authorization / RBAC</t>
+  </si>
+  <si>
+    <t>Every API permission and role</t>
+  </si>
+  <si>
+    <t>FTL-UI-201, SSO-01, NEW-322, NEW-328, NEW-359, NEW-376, NEW-378, NEW-379, NEW-387, NEW-390</t>
+  </si>
+  <si>
+    <t>05</t>
+  </si>
+  <si>
+    <t>IDOR / BOLA</t>
+  </si>
+  <si>
+    <t>Cross-account resource access</t>
+  </si>
+  <si>
+    <t>SEC-05, NEW-310, NEW-322</t>
+  </si>
+  <si>
+    <t>06</t>
+  </si>
+  <si>
+    <t>Multi-tenancy</t>
+  </si>
+  <si>
+    <t>Organization/service separation</t>
+  </si>
+  <si>
+    <t>SEC-05, SEC-06, NEW-310, NEW-322</t>
+  </si>
+  <si>
+    <t>07</t>
+  </si>
+  <si>
+    <t>API Security</t>
+  </si>
+  <si>
+    <t>Request validation/mass assignment/rate limiting</t>
+  </si>
+  <si>
+    <t>FTL-SEC-205, NEW-311, NEW-321, NEW-328</t>
+  </si>
+  <si>
+    <t>08</t>
+  </si>
+  <si>
+    <t>CSRF &amp; CORS</t>
+  </si>
+  <si>
+    <t>Origin, cookies, CSRF all writes</t>
+  </si>
+  <si>
+    <t>SEC-09, NEW-394, NEW-395</t>
+  </si>
+  <si>
+    <t>RUNTIME_REQUIRED</t>
+  </si>
+  <si>
+    <t>09</t>
+  </si>
+  <si>
+    <t>XSS &amp; HTML Injection</t>
+  </si>
+  <si>
+    <t>Ticket/email/console/DOM output</t>
+  </si>
+  <si>
+    <t>UI-06, MAIL-01</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>SQL / Command Injection</t>
+  </si>
+  <si>
+    <t>SQL/shell/path/template injection</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>SSRF</t>
+  </si>
+  <si>
+    <t>Private IP, DNS rebinding, redirects</t>
+  </si>
+  <si>
+    <t>SEC-08, NEW-314</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>Secrets &amp; Credentials</t>
+  </si>
+  <si>
+    <t>Provider keys, vault, rotation</t>
+  </si>
+  <si>
+    <t>NEW-313, SEC-02, NEW-323</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>Pterodactyl API</t>
+  </si>
+  <si>
+    <t>Provider scoping &amp; ownership</t>
+  </si>
+  <si>
+    <t>FTL-PROV-201, FTL-UI-202, NEW-322, NEW-323, NEW-389, NEW-393</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>OIDC callback, native reset, revoke</t>
+  </si>
+  <si>
+    <t>SSO-01, SSO-02, SSO-03, NEW-387</t>
+  </si>
+  <si>
+    <t>Wings &amp; WebSockets</t>
+  </si>
+  <si>
+    <t>Socket tokens, console, revocation</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>File Manager</t>
+  </si>
+  <si>
+    <t>Traversal, archives, symlinks, quota</t>
+  </si>
+  <si>
+    <t>NEW-314, NEW-321, NEW-381, NEW-382</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>Minecraft Installers</t>
+  </si>
+  <si>
+    <t>SHA512, compatibility, redirect, limits</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>Web App Isolation</t>
+  </si>
+  <si>
+    <t>Container isolation, network, privilege</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>Stripe &amp; Payments</t>
+  </si>
+  <si>
+    <t>Signatures, replay, idempotency, ordering</t>
+  </si>
+  <si>
+    <t>FTL-BILL-201, FTL-BILL-203, FTL-BILL-204, FTL-BILL-206, NEW-324, NEW-340, NEW-345, NEW-346, NEW-347, NEW-349, NEW-350</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>Billing &amp; Subscriptions</t>
+  </si>
+  <si>
+    <t>Renewal, refunds, tax, coupons, invoices</t>
+  </si>
+  <si>
+    <t>FTL-BILL-202, FTL-BILL-205, NEW-301, NEW-303, NEW-304, NEW-305, NEW-316, NEW-319, NEW-324, NEW-330, NEW-333, NEW-334, NEW-338, NEW-344, NEW-348, NEW-351, NEW-352, NEW-353, NEW-355, NEW-356</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>Node, cap, retry, lifecycle</t>
+  </si>
+  <si>
+    <t>FTL-PROV-201, FTL-PROV-202, FTL-PROV-203, FTL-PROV-204, NEW-302, NEW-322, NEW-327, NEW-352, NEW-357, NEW-386, NEW-388, NEW-392</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>cPanel / WHM</t>
+  </si>
+  <si>
+    <t>Permission, lifecycle, safe API</t>
+  </si>
+  <si>
+    <t>FTL-PROV-201, SEC-08</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>Proxmox / VPS</t>
+  </si>
+  <si>
+    <t>VM isolation, templates, snapshots</t>
+  </si>
+  <si>
+    <t>FTL-PROV-201, NEW-326, NEW-327</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>DNS &amp; Domains</t>
+  </si>
+  <si>
+    <t>Ownership, delegation, DNS records</t>
+  </si>
+  <si>
+    <t>FTL-DNS-201, FTL-DNS-202, NEW-369, NEW-370, NEW-383, NEW-384, NEW-385</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>Database Security</t>
+  </si>
+  <si>
+    <t>Transactions, migrations, corruption</t>
+  </si>
+  <si>
+    <t>NEW-308, NEW-309, NEW-321</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>Job leases, ordering, retry, dead letters</t>
+  </si>
+  <si>
+    <t>FTL-PROV-203, FTL-BILL-202, NEW-339, NEW-346, NEW-354, NEW-357</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>Infrastructure &amp; Network</t>
+  </si>
+  <si>
+    <t>TLS, reverse proxy, firewall, ports</t>
+  </si>
+  <si>
+    <t>SEC-10, NEW-361</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>Dependency &amp; Supply Chain</t>
+  </si>
+  <si>
+    <t>npm SCA, CI secrets, pinning</t>
+  </si>
+  <si>
+    <t>NOT_STARTED</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>Backups &amp; Recovery</t>
+  </si>
+  <si>
+    <t>Encrypted backups, restore integrity</t>
+  </si>
+  <si>
+    <t>NEW-308, NEW-309, NEW-313, NEW-327, NEW-373, NEW-374, NEW-375</t>
+  </si>
+  <si>
     <t>30</t>
   </si>
   <si>
-    <t>TESTED</t>
-  </si>
-  <si>
-    <t>CLOSED</t>
-  </si>
-  <si>
-    <t>LATEST VERIFIED COMMIT</t>
-  </si>
-  <si>
-    <t>REGRESSION</t>
-  </si>
-  <si>
-    <t>3cb35de (independent audit batch 1)</t>
-  </si>
-  <si>
-    <t>STATUS CONTRACT</t>
-  </si>
-  <si>
-    <t>Issue present in inspected source</t>
-  </si>
-  <si>
-    <t>Some code fixed; unresolved conditions remain</t>
-  </si>
-  <si>
-    <t>Fix observed in source; still needs regression/runtime validation</t>
-  </si>
-  <si>
-    <t>Question or risk not independently demonstrated</t>
-  </si>
-  <si>
-    <t>Requires an explicit product/security policy</t>
-  </si>
-  <si>
-    <t>Automated/authorized tests executed and evidence stored</t>
-  </si>
-  <si>
-    <t>Fix independently verified and accepted</t>
-  </si>
-  <si>
-    <t>Previously fixed behavior has returned</t>
-  </si>
-  <si>
-    <t>FORTLESS   /   30 SECURITY AUDIT DOMAINS</t>
-  </si>
-  <si>
-    <t>Static source review expanded at 6203687. Coverage is NOT an independent runtime, load, security or pixel-diff test.</t>
-  </si>
-  <si>
-    <t>#</t>
-  </si>
-  <si>
-    <t>Scope</t>
-  </si>
-  <si>
-    <t>Related finding IDs</t>
-  </si>
-  <si>
-    <t>Audit coverage</t>
-  </si>
-  <si>
-    <t>01</t>
-  </si>
-  <si>
-    <t>Authentication</t>
-  </si>
-  <si>
-    <t>Login/register/reset, brute force, enumeration</t>
-  </si>
-  <si>
-    <t>SEC-09, FTL-SEC-205, NEW-362, NEW-363, NEW-364, NEW-365, NEW-366, NEW-367</t>
-  </si>
-  <si>
-    <t>STATIC_PARTIAL</t>
-  </si>
-  <si>
-    <t>02</t>
-  </si>
-  <si>
-    <t>Sessions &amp; Devices</t>
-  </si>
-  <si>
-    <t>Token rotation, expiry, login/logout, revocation</t>
-  </si>
-  <si>
-    <t>SEC-03, SEC-04, FTL-SEC-202, NEW-363, NEW-368, NEW-377</t>
-  </si>
-  <si>
-    <t>03</t>
-  </si>
-  <si>
-    <t>MFA &amp; Passkeys</t>
-  </si>
-  <si>
-    <t>TOTP, WebAuthn, recovery, replay, UV</t>
-  </si>
-  <si>
-    <t>FTL-SEC-201, FTL-SEC-202, FTL-SEC-203, NEW-306, NEW-307, NEW-318, NEW-358, NEW-360, NEW-366, NEW-367</t>
-  </si>
-  <si>
-    <t>04</t>
-  </si>
-  <si>
-    <t>Authorization / RBAC</t>
-  </si>
-  <si>
-    <t>Every API permission and role</t>
-  </si>
-  <si>
-    <t>FTL-UI-201, SSO-01, NEW-322, NEW-328, NEW-359, NEW-376, NEW-378, NEW-379, NEW-387, NEW-390</t>
-  </si>
-  <si>
-    <t>05</t>
-  </si>
-  <si>
-    <t>IDOR / BOLA</t>
-  </si>
-  <si>
-    <t>Cross-account resource access</t>
-  </si>
-  <si>
-    <t>SEC-05, NEW-310, NEW-322</t>
-  </si>
-  <si>
-    <t>06</t>
-  </si>
-  <si>
-    <t>Multi-tenancy</t>
-  </si>
-  <si>
-    <t>Organization/service separation</t>
-  </si>
-  <si>
-    <t>SEC-05, SEC-06, NEW-310, NEW-322</t>
-  </si>
-  <si>
-    <t>07</t>
-  </si>
-  <si>
-    <t>API Security</t>
-  </si>
-  <si>
-    <t>Request validation/mass assignment/rate limiting</t>
-  </si>
-  <si>
-    <t>FTL-SEC-205, NEW-311, NEW-321, NEW-328</t>
-  </si>
-  <si>
-    <t>08</t>
-  </si>
-  <si>
-    <t>CSRF &amp; CORS</t>
-  </si>
-  <si>
-    <t>Origin, cookies, CSRF all writes</t>
-  </si>
-  <si>
-    <t>RUNTIME_REQUIRED</t>
-  </si>
-  <si>
-    <t>09</t>
-  </si>
-  <si>
-    <t>XSS &amp; HTML Injection</t>
-  </si>
-  <si>
-    <t>Ticket/email/console/DOM output</t>
-  </si>
-  <si>
-    <t>UI-06, MAIL-01</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>SQL / Command Injection</t>
-  </si>
-  <si>
-    <t>SQL/shell/path/template injection</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>SSRF</t>
-  </si>
-  <si>
-    <t>Private IP, DNS rebinding, redirects</t>
-  </si>
-  <si>
-    <t>SEC-08, NEW-314</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>Secrets &amp; Credentials</t>
-  </si>
-  <si>
-    <t>Provider keys, vault, rotation</t>
-  </si>
-  <si>
-    <t>NEW-313, SEC-02, NEW-323</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>Pterodactyl API</t>
-  </si>
-  <si>
-    <t>Provider scoping &amp; ownership</t>
-  </si>
-  <si>
-    <t>FTL-PROV-201, FTL-UI-202, NEW-322, NEW-323, NEW-389, NEW-393</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>OIDC callback, native reset, revoke</t>
-  </si>
-  <si>
-    <t>SSO-01, SSO-02, SSO-03, NEW-387</t>
-  </si>
-  <si>
-    <t>Wings &amp; WebSockets</t>
-  </si>
-  <si>
-    <t>Socket tokens, console, revocation</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>File Manager</t>
-  </si>
-  <si>
-    <t>Traversal, archives, symlinks, quota</t>
-  </si>
-  <si>
-    <t>NEW-314, NEW-321, NEW-381, NEW-382</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>Minecraft Installers</t>
-  </si>
-  <si>
-    <t>SHA512, compatibility, redirect, limits</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>Web App Isolation</t>
-  </si>
-  <si>
-    <t>Container isolation, network, privilege</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>Stripe &amp; Payments</t>
-  </si>
-  <si>
-    <t>Signatures, replay, idempotency, ordering</t>
-  </si>
-  <si>
-    <t>FTL-BILL-201, FTL-BILL-203, FTL-BILL-204, FTL-BILL-206, NEW-324, NEW-340, NEW-345, NEW-346, NEW-347, NEW-349, NEW-350</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>Billing &amp; Subscriptions</t>
-  </si>
-  <si>
-    <t>Renewal, refunds, tax, coupons, invoices</t>
-  </si>
-  <si>
-    <t>FTL-BILL-202, FTL-BILL-205, NEW-301, NEW-303, NEW-304, NEW-305, NEW-316, NEW-319, NEW-324, NEW-330, NEW-333, NEW-334, NEW-338, NEW-344, NEW-348, NEW-351, NEW-352, NEW-353, NEW-355, NEW-356</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>Node, cap, retry, lifecycle</t>
-  </si>
-  <si>
-    <t>FTL-PROV-201, FTL-PROV-202, FTL-PROV-203, FTL-PROV-204, NEW-302, NEW-322, NEW-327, NEW-352, NEW-357, NEW-386, NEW-388, NEW-392</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>cPanel / WHM</t>
-  </si>
-  <si>
-    <t>Permission, lifecycle, safe API</t>
-  </si>
-  <si>
-    <t>FTL-PROV-201, SEC-08</t>
-  </si>
-  <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>Proxmox / VPS</t>
-  </si>
-  <si>
-    <t>VM isolation, templates, snapshots</t>
-  </si>
-  <si>
-    <t>FTL-PROV-201, NEW-326, NEW-327</t>
-  </si>
-  <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>DNS &amp; Domains</t>
-  </si>
-  <si>
-    <t>Ownership, delegation, DNS records</t>
-  </si>
-  <si>
-    <t>FTL-DNS-201, FTL-DNS-202, NEW-369, NEW-370, NEW-383, NEW-384, NEW-385</t>
-  </si>
-  <si>
-    <t>25</t>
-  </si>
-  <si>
-    <t>Database Security</t>
-  </si>
-  <si>
-    <t>Transactions, migrations, corruption</t>
-  </si>
-  <si>
-    <t>NEW-308, NEW-309, NEW-321</t>
-  </si>
-  <si>
-    <t>26</t>
-  </si>
-  <si>
-    <t>Job leases, ordering, retry, dead letters</t>
-  </si>
-  <si>
-    <t>FTL-PROV-203, FTL-BILL-202, NEW-339, NEW-346, NEW-354, NEW-357</t>
-  </si>
-  <si>
-    <t>27</t>
-  </si>
-  <si>
-    <t>Infrastructure &amp; Network</t>
-  </si>
-  <si>
-    <t>TLS, reverse proxy, firewall, ports</t>
-  </si>
-  <si>
-    <t>SEC-10, NEW-361</t>
-  </si>
-  <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>Dependency &amp; Supply Chain</t>
-  </si>
-  <si>
-    <t>npm SCA, CI secrets, pinning</t>
-  </si>
-  <si>
-    <t>NOT_STARTED</t>
-  </si>
-  <si>
-    <t>29</t>
-  </si>
-  <si>
-    <t>Backups &amp; Recovery</t>
-  </si>
-  <si>
-    <t>Encrypted backups, restore integrity</t>
-  </si>
-  <si>
-    <t>NEW-308, NEW-309, NEW-313, NEW-327, NEW-373, NEW-374, NEW-375</t>
-  </si>
-  <si>
     <t>Audit integrity, alerts, events</t>
   </si>
   <si>
@@ -4111,6 +4168,15 @@
   </si>
   <si>
     <t>server-panel, runtime-sync, relink and service-members read in source. No implementation code changed.</t>
+  </si>
+  <si>
+    <t>2026-10-19 09:10</t>
+  </si>
+  <si>
+    <t>Independent audit batch 6: CORS and CSRF configuration, live header check (NEW-394..NEW-395)</t>
+  </si>
+  <si>
+    <t>CORS, CSRF and cookie settings read in source; public response headers checked read-only. No implementation code changed.</t>
   </si>
   <si>
     <t>FORTLESS   /   IMMUTABLE STATUS HISTORY</t>
@@ -5375,7 +5441,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:S141"/>
+  <dimension ref="A1:S143"/>
   <sheetFormatPr defaultRowHeight="0" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" customHeight="1"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
@@ -13416,6 +13482,124 @@
       </c>
       <c r="S141" t="s">
         <v>765</v>
+      </c>
+    </row>
+    <row r="142" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>1139</v>
+      </c>
+      <c r="B142" t="s">
+        <v>308</v>
+      </c>
+      <c r="C142" t="s">
+        <v>309</v>
+      </c>
+      <c r="D142" t="s">
+        <v>24</v>
+      </c>
+      <c r="E142" t="s">
+        <v>1140</v>
+      </c>
+      <c r="F142" t="s">
+        <v>112</v>
+      </c>
+      <c r="G142" t="s">
+        <v>27</v>
+      </c>
+      <c r="H142" t="s">
+        <v>27</v>
+      </c>
+      <c r="I142" t="s">
+        <v>1141</v>
+      </c>
+      <c r="J142" t="s">
+        <v>1141</v>
+      </c>
+      <c r="K142" t="s">
+        <v>1142</v>
+      </c>
+      <c r="L142" t="s">
+        <v>1143</v>
+      </c>
+      <c r="M142" t="s">
+        <v>1144</v>
+      </c>
+      <c r="N142" t="s">
+        <v>1145</v>
+      </c>
+      <c r="O142" t="s">
+        <v>1146</v>
+      </c>
+      <c r="P142" t="s">
+        <v>747</v>
+      </c>
+      <c r="Q142" t="s">
+        <v>924</v>
+      </c>
+      <c r="R142" t="s">
+        <v>36</v>
+      </c>
+      <c r="S142" t="s">
+        <v>1147</v>
+      </c>
+    </row>
+    <row r="143" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>1148</v>
+      </c>
+      <c r="B143" t="s">
+        <v>308</v>
+      </c>
+      <c r="C143" t="s">
+        <v>309</v>
+      </c>
+      <c r="D143" t="s">
+        <v>24</v>
+      </c>
+      <c r="E143" t="s">
+        <v>1149</v>
+      </c>
+      <c r="F143" t="s">
+        <v>112</v>
+      </c>
+      <c r="G143" t="s">
+        <v>27</v>
+      </c>
+      <c r="H143" t="s">
+        <v>27</v>
+      </c>
+      <c r="I143" t="s">
+        <v>1141</v>
+      </c>
+      <c r="J143" t="s">
+        <v>1141</v>
+      </c>
+      <c r="K143" t="s">
+        <v>1150</v>
+      </c>
+      <c r="L143" t="s">
+        <v>1151</v>
+      </c>
+      <c r="M143" t="s">
+        <v>1152</v>
+      </c>
+      <c r="N143" t="s">
+        <v>1153</v>
+      </c>
+      <c r="O143" t="s">
+        <v>1154</v>
+      </c>
+      <c r="P143" t="s">
+        <v>747</v>
+      </c>
+      <c r="Q143" t="s">
+        <v>924</v>
+      </c>
+      <c r="R143" t="s">
+        <v>36</v>
+      </c>
+      <c r="S143" t="s">
+        <v>1155</v>
       </c>
     </row>
   </sheetData>
@@ -13429,48 +13613,48 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>1139</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1140</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1141</v>
+        <v>1158</v>
       </c>
       <c r="C4" t="s">
-        <v>1142</v>
+        <v>1159</v>
       </c>
       <c r="E4" t="s">
-        <v>1143</v>
+        <v>1160</v>
       </c>
       <c r="G4" t="s">
-        <v>1144</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1145</v>
+        <v>1162</v>
       </c>
       <c r="C5" t="s">
-        <v>1146</v>
+        <v>1163</v>
       </c>
       <c r="E5" t="s">
-        <v>1147</v>
+        <v>1164</v>
       </c>
       <c r="G5" t="s">
-        <v>1148</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>1149</v>
+        <v>1166</v>
       </c>
       <c r="F9" t="s">
-        <v>1150</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -13478,16 +13662,16 @@
         <v>112</v>
       </c>
       <c r="B10" t="s">
-        <v>1146</v>
+        <v>1163</v>
       </c>
       <c r="C10" t="s">
         <v>3</v>
       </c>
       <c r="D10" t="s">
-        <v>1151</v>
+        <v>1168</v>
       </c>
       <c r="F10" t="s">
-        <v>1152</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -13495,13 +13679,13 @@
         <v>86</v>
       </c>
       <c r="B11" t="s">
-        <v>1153</v>
+        <v>1170</v>
       </c>
       <c r="C11" t="s">
         <v>22</v>
       </c>
       <c r="D11" t="s">
-        <v>1154</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -13509,13 +13693,13 @@
         <v>95</v>
       </c>
       <c r="B12" t="s">
-        <v>1155</v>
+        <v>1172</v>
       </c>
       <c r="C12" t="s">
         <v>61</v>
       </c>
       <c r="D12" t="s">
-        <v>1156</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -13523,13 +13707,13 @@
         <v>453</v>
       </c>
       <c r="B13" t="s">
-        <v>1157</v>
+        <v>1174</v>
       </c>
       <c r="C13" t="s">
         <v>308</v>
       </c>
       <c r="D13" t="s">
-        <v>1158</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
@@ -13537,42 +13721,42 @@
         <v>26</v>
       </c>
       <c r="B14" t="s">
-        <v>1147</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>1159</v>
+        <v>1176</v>
       </c>
       <c r="B15" t="s">
-        <v>1148</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>1160</v>
+        <v>1177</v>
       </c>
       <c r="B16" t="s">
-        <v>1148</v>
+        <v>1165</v>
       </c>
       <c r="F16" t="s">
-        <v>1161</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>1162</v>
+        <v>1179</v>
       </c>
       <c r="B17" t="s">
-        <v>1148</v>
+        <v>1165</v>
       </c>
       <c r="F17" t="s">
-        <v>1163</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>1164</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
@@ -13580,7 +13764,7 @@
         <v>112</v>
       </c>
       <c r="C22" t="s">
-        <v>1165</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
@@ -13588,7 +13772,7 @@
         <v>86</v>
       </c>
       <c r="C23" t="s">
-        <v>1166</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
@@ -13596,7 +13780,7 @@
         <v>26</v>
       </c>
       <c r="C24" t="s">
-        <v>1167</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
@@ -13604,7 +13788,7 @@
         <v>95</v>
       </c>
       <c r="C25" t="s">
-        <v>1168</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
@@ -13612,31 +13796,31 @@
         <v>453</v>
       </c>
       <c r="C26" t="s">
-        <v>1169</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>1159</v>
+        <v>1176</v>
       </c>
       <c r="C27" t="s">
-        <v>1170</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>1160</v>
+        <v>1177</v>
       </c>
       <c r="C28" t="s">
-        <v>1171</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>1162</v>
+        <v>1179</v>
       </c>
       <c r="C29" t="s">
-        <v>1172</v>
+        <v>1189</v>
       </c>
     </row>
   </sheetData>
@@ -13650,7 +13834,7 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>1173</v>
+        <v>1190</v>
       </c>
       <c r="B1"/>
       <c r="C1"/>
@@ -13659,7 +13843,7 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1174</v>
+        <v>1191</v>
       </c>
       <c r="B2"/>
       <c r="C2"/>
@@ -13668,529 +13852,529 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>1175</v>
+        <v>1192</v>
       </c>
       <c r="B3" t="s">
         <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>1176</v>
+        <v>1193</v>
       </c>
       <c r="D3" t="s">
-        <v>1177</v>
+        <v>1194</v>
       </c>
       <c r="E3" t="s">
-        <v>1178</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1179</v>
+        <v>1196</v>
       </c>
       <c r="B4" t="s">
-        <v>1180</v>
+        <v>1197</v>
       </c>
       <c r="C4" t="s">
-        <v>1181</v>
+        <v>1198</v>
       </c>
       <c r="D4" t="s">
-        <v>1182</v>
+        <v>1199</v>
       </c>
       <c r="E4" t="s">
-        <v>1183</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1184</v>
+        <v>1201</v>
       </c>
       <c r="B5" t="s">
-        <v>1185</v>
+        <v>1202</v>
       </c>
       <c r="C5" t="s">
-        <v>1186</v>
+        <v>1203</v>
       </c>
       <c r="D5" t="s">
-        <v>1187</v>
+        <v>1204</v>
       </c>
       <c r="E5" t="s">
-        <v>1183</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>1188</v>
+        <v>1205</v>
       </c>
       <c r="B6" t="s">
-        <v>1189</v>
+        <v>1206</v>
       </c>
       <c r="C6" t="s">
-        <v>1190</v>
+        <v>1207</v>
       </c>
       <c r="D6" t="s">
-        <v>1191</v>
+        <v>1208</v>
       </c>
       <c r="E6" t="s">
-        <v>1183</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>1192</v>
+        <v>1209</v>
       </c>
       <c r="B7" t="s">
-        <v>1193</v>
+        <v>1210</v>
       </c>
       <c r="C7" t="s">
-        <v>1194</v>
+        <v>1211</v>
       </c>
       <c r="D7" t="s">
-        <v>1195</v>
+        <v>1212</v>
       </c>
       <c r="E7" t="s">
-        <v>1183</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>1196</v>
+        <v>1213</v>
       </c>
       <c r="B8" t="s">
-        <v>1197</v>
+        <v>1214</v>
       </c>
       <c r="C8" t="s">
-        <v>1198</v>
+        <v>1215</v>
       </c>
       <c r="D8" t="s">
-        <v>1199</v>
+        <v>1216</v>
       </c>
       <c r="E8" t="s">
-        <v>1183</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>1217</v>
+      </c>
+      <c r="B9" t="s">
+        <v>1218</v>
+      </c>
+      <c r="C9" t="s">
+        <v>1219</v>
+      </c>
+      <c r="D9" t="s">
+        <v>1220</v>
+      </c>
+      <c r="E9" t="s">
         <v>1200</v>
-      </c>
-      <c r="B9" t="s">
-        <v>1201</v>
-      </c>
-      <c r="C9" t="s">
-        <v>1202</v>
-      </c>
-      <c r="D9" t="s">
-        <v>1203</v>
-      </c>
-      <c r="E9" t="s">
-        <v>1183</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>1204</v>
+        <v>1221</v>
       </c>
       <c r="B10" t="s">
-        <v>1205</v>
+        <v>1222</v>
       </c>
       <c r="C10" t="s">
-        <v>1206</v>
+        <v>1223</v>
       </c>
       <c r="D10" t="s">
-        <v>1207</v>
+        <v>1224</v>
       </c>
       <c r="E10" t="s">
-        <v>1183</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>1208</v>
+        <v>1225</v>
       </c>
       <c r="B11" t="s">
-        <v>1209</v>
+        <v>1226</v>
       </c>
       <c r="C11" t="s">
-        <v>1210</v>
+        <v>1227</v>
       </c>
       <c r="D11" t="s">
-        <v>93</v>
+        <v>1228</v>
       </c>
       <c r="E11" t="s">
-        <v>1211</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>1212</v>
+        <v>1230</v>
       </c>
       <c r="B12" t="s">
-        <v>1213</v>
+        <v>1231</v>
       </c>
       <c r="C12" t="s">
-        <v>1214</v>
+        <v>1232</v>
       </c>
       <c r="D12" t="s">
-        <v>1215</v>
+        <v>1233</v>
       </c>
       <c r="E12" t="s">
-        <v>1183</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>1216</v>
+        <v>1234</v>
       </c>
       <c r="B13" t="s">
-        <v>1217</v>
+        <v>1235</v>
       </c>
       <c r="C13" t="s">
-        <v>1218</v>
+        <v>1236</v>
       </c>
       <c r="D13" t="s">
         <v>403</v>
       </c>
       <c r="E13" t="s">
-        <v>1211</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>1219</v>
+        <v>1237</v>
       </c>
       <c r="B14" t="s">
-        <v>1220</v>
+        <v>1238</v>
       </c>
       <c r="C14" t="s">
-        <v>1221</v>
+        <v>1239</v>
       </c>
       <c r="D14" t="s">
-        <v>1222</v>
+        <v>1240</v>
       </c>
       <c r="E14" t="s">
-        <v>1183</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>1223</v>
+        <v>1241</v>
       </c>
       <c r="B15" t="s">
-        <v>1224</v>
+        <v>1242</v>
       </c>
       <c r="C15" t="s">
-        <v>1225</v>
+        <v>1243</v>
       </c>
       <c r="D15" t="s">
-        <v>1226</v>
+        <v>1244</v>
       </c>
       <c r="E15" t="s">
-        <v>1183</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>1227</v>
+        <v>1245</v>
       </c>
       <c r="B16" t="s">
-        <v>1228</v>
+        <v>1246</v>
       </c>
       <c r="C16" t="s">
-        <v>1229</v>
+        <v>1247</v>
       </c>
       <c r="D16" t="s">
-        <v>1230</v>
+        <v>1248</v>
       </c>
       <c r="E16" t="s">
-        <v>1183</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>1231</v>
+        <v>1249</v>
       </c>
       <c r="B17" t="s">
         <v>435</v>
       </c>
       <c r="C17" t="s">
-        <v>1232</v>
+        <v>1250</v>
       </c>
       <c r="D17" t="s">
-        <v>1233</v>
+        <v>1251</v>
       </c>
       <c r="E17" t="s">
-        <v>1211</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>1153</v>
+        <v>1170</v>
       </c>
       <c r="B18" t="s">
-        <v>1234</v>
+        <v>1252</v>
       </c>
       <c r="C18" t="s">
-        <v>1235</v>
+        <v>1253</v>
       </c>
       <c r="D18" t="s">
         <v>316</v>
       </c>
       <c r="E18" t="s">
-        <v>1211</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>1236</v>
+        <v>1254</v>
       </c>
       <c r="B19" t="s">
-        <v>1237</v>
+        <v>1255</v>
       </c>
       <c r="C19" t="s">
-        <v>1238</v>
+        <v>1256</v>
       </c>
       <c r="D19" t="s">
-        <v>1239</v>
+        <v>1257</v>
       </c>
       <c r="E19" t="s">
-        <v>1211</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>1240</v>
+        <v>1258</v>
       </c>
       <c r="B20" t="s">
-        <v>1241</v>
+        <v>1259</v>
       </c>
       <c r="C20" t="s">
-        <v>1242</v>
+        <v>1260</v>
       </c>
       <c r="D20" t="s">
         <v>475</v>
       </c>
       <c r="E20" t="s">
-        <v>1183</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>1243</v>
+        <v>1261</v>
       </c>
       <c r="B21" t="s">
-        <v>1244</v>
+        <v>1262</v>
       </c>
       <c r="C21" t="s">
-        <v>1245</v>
+        <v>1263</v>
       </c>
       <c r="D21" t="s">
         <v>213</v>
       </c>
       <c r="E21" t="s">
-        <v>1211</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>1246</v>
+        <v>1264</v>
       </c>
       <c r="B22" t="s">
-        <v>1247</v>
+        <v>1265</v>
       </c>
       <c r="C22" t="s">
-        <v>1248</v>
+        <v>1266</v>
       </c>
       <c r="D22" t="s">
-        <v>1249</v>
+        <v>1267</v>
       </c>
       <c r="E22" t="s">
-        <v>1183</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>1250</v>
+        <v>1268</v>
       </c>
       <c r="B23" t="s">
-        <v>1251</v>
+        <v>1269</v>
       </c>
       <c r="C23" t="s">
-        <v>1252</v>
+        <v>1270</v>
       </c>
       <c r="D23" t="s">
-        <v>1253</v>
+        <v>1271</v>
       </c>
       <c r="E23" t="s">
-        <v>1183</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>1254</v>
+        <v>1272</v>
       </c>
       <c r="B24" t="s">
         <v>214</v>
       </c>
       <c r="C24" t="s">
-        <v>1255</v>
+        <v>1273</v>
       </c>
       <c r="D24" t="s">
-        <v>1256</v>
+        <v>1274</v>
       </c>
       <c r="E24" t="s">
-        <v>1183</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>1257</v>
+        <v>1275</v>
       </c>
       <c r="B25" t="s">
-        <v>1258</v>
+        <v>1276</v>
       </c>
       <c r="C25" t="s">
-        <v>1259</v>
+        <v>1277</v>
       </c>
       <c r="D25" t="s">
-        <v>1260</v>
+        <v>1278</v>
       </c>
       <c r="E25" t="s">
-        <v>1211</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>1261</v>
+        <v>1279</v>
       </c>
       <c r="B26" t="s">
-        <v>1262</v>
+        <v>1280</v>
       </c>
       <c r="C26" t="s">
-        <v>1263</v>
+        <v>1281</v>
       </c>
       <c r="D26" t="s">
-        <v>1264</v>
+        <v>1282</v>
       </c>
       <c r="E26" t="s">
-        <v>1211</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>1265</v>
+        <v>1283</v>
       </c>
       <c r="B27" t="s">
-        <v>1266</v>
+        <v>1284</v>
       </c>
       <c r="C27" t="s">
-        <v>1267</v>
+        <v>1285</v>
       </c>
       <c r="D27" t="s">
-        <v>1268</v>
+        <v>1286</v>
       </c>
       <c r="E27" t="s">
-        <v>1183</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>1269</v>
+        <v>1287</v>
       </c>
       <c r="B28" t="s">
-        <v>1270</v>
+        <v>1288</v>
       </c>
       <c r="C28" t="s">
-        <v>1271</v>
+        <v>1289</v>
       </c>
       <c r="D28" t="s">
-        <v>1272</v>
+        <v>1290</v>
       </c>
       <c r="E28" t="s">
-        <v>1183</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>1273</v>
+        <v>1291</v>
       </c>
       <c r="B29" t="s">
         <v>822</v>
       </c>
       <c r="C29" t="s">
-        <v>1274</v>
+        <v>1292</v>
       </c>
       <c r="D29" t="s">
-        <v>1275</v>
+        <v>1293</v>
       </c>
       <c r="E29" t="s">
-        <v>1183</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>1276</v>
+        <v>1294</v>
       </c>
       <c r="B30" t="s">
-        <v>1277</v>
+        <v>1295</v>
       </c>
       <c r="C30" t="s">
-        <v>1278</v>
+        <v>1296</v>
       </c>
       <c r="D30" t="s">
-        <v>1279</v>
+        <v>1297</v>
       </c>
       <c r="E30" t="s">
-        <v>1211</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>1280</v>
+        <v>1298</v>
       </c>
       <c r="B31" t="s">
-        <v>1281</v>
+        <v>1299</v>
       </c>
       <c r="C31" t="s">
-        <v>1282</v>
+        <v>1300</v>
       </c>
       <c r="D31" t="s">
         <v>93</v>
       </c>
       <c r="E31" t="s">
-        <v>1283</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>1284</v>
+        <v>1302</v>
       </c>
       <c r="B32" t="s">
-        <v>1285</v>
+        <v>1303</v>
       </c>
       <c r="C32" t="s">
-        <v>1286</v>
+        <v>1304</v>
       </c>
       <c r="D32" t="s">
-        <v>1287</v>
+        <v>1305</v>
       </c>
       <c r="E32" t="s">
-        <v>1183</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>1158</v>
+        <v>1306</v>
       </c>
       <c r="B33" t="s">
         <v>1030</v>
       </c>
       <c r="C33" t="s">
-        <v>1288</v>
+        <v>1307</v>
       </c>
       <c r="D33" t="s">
-        <v>1289</v>
+        <v>1308</v>
       </c>
       <c r="E33" t="s">
-        <v>1211</v>
+        <v>1229</v>
       </c>
     </row>
   </sheetData>
@@ -14204,157 +14388,157 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr defaultRowHeight="0" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" customHeight="1"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>1290</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1291</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>1292</v>
+        <v>1311</v>
       </c>
       <c r="B3" t="s">
-        <v>1293</v>
+        <v>1312</v>
       </c>
       <c r="C3" t="s">
-        <v>1294</v>
+        <v>1313</v>
       </c>
       <c r="D3" t="s">
-        <v>1295</v>
+        <v>1314</v>
       </c>
       <c r="E3" t="s">
-        <v>1296</v>
+        <v>1315</v>
       </c>
       <c r="F3" t="s">
-        <v>1297</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1298</v>
+        <v>1317</v>
       </c>
       <c r="B4" t="s">
         <v>28</v>
       </c>
       <c r="C4" t="s">
-        <v>1299</v>
+        <v>1318</v>
       </c>
       <c r="D4" t="s">
-        <v>1300</v>
+        <v>1319</v>
       </c>
       <c r="E4" t="s">
-        <v>1301</v>
+        <v>1320</v>
       </c>
       <c r="F4" t="s">
-        <v>1302</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1303</v>
+        <v>1322</v>
       </c>
       <c r="B5" t="s">
-        <v>1304</v>
+        <v>1323</v>
       </c>
       <c r="C5" t="s">
-        <v>1305</v>
+        <v>1324</v>
       </c>
       <c r="D5" t="s">
-        <v>1306</v>
+        <v>1325</v>
       </c>
       <c r="E5" t="s">
-        <v>1307</v>
+        <v>1326</v>
       </c>
       <c r="F5" t="s">
-        <v>1308</v>
+        <v>1327</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>1309</v>
+        <v>1328</v>
       </c>
       <c r="B6" t="s">
-        <v>1310</v>
+        <v>1329</v>
       </c>
       <c r="C6" t="s">
-        <v>1311</v>
+        <v>1330</v>
       </c>
       <c r="D6" t="s">
-        <v>1312</v>
+        <v>1331</v>
       </c>
       <c r="E6" t="s">
-        <v>1313</v>
+        <v>1332</v>
       </c>
       <c r="F6" t="s">
-        <v>1314</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>1315</v>
+        <v>1334</v>
       </c>
       <c r="B7" t="s">
-        <v>1316</v>
+        <v>1335</v>
       </c>
       <c r="C7" t="s">
-        <v>1317</v>
+        <v>1336</v>
       </c>
       <c r="D7" t="s">
-        <v>1318</v>
+        <v>1337</v>
       </c>
       <c r="E7" t="s">
-        <v>1313</v>
+        <v>1332</v>
       </c>
       <c r="F7" t="s">
-        <v>1319</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>1320</v>
+        <v>1339</v>
       </c>
       <c r="B8" t="s">
-        <v>1321</v>
+        <v>1340</v>
       </c>
       <c r="C8" t="s">
-        <v>1322</v>
+        <v>1341</v>
       </c>
       <c r="D8" t="s">
-        <v>1323</v>
+        <v>1342</v>
       </c>
       <c r="E8" t="s">
-        <v>1313</v>
+        <v>1332</v>
       </c>
       <c r="F8" t="s">
-        <v>1319</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>1324</v>
+        <v>1343</v>
       </c>
       <c r="B9" t="s">
         <v>29</v>
       </c>
       <c r="C9" t="s">
-        <v>1325</v>
+        <v>1344</v>
       </c>
       <c r="D9" t="s">
-        <v>1326</v>
+        <v>1345</v>
       </c>
       <c r="E9" t="s">
-        <v>1301</v>
+        <v>1320</v>
       </c>
       <c r="F9" t="s">
-        <v>1327</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -14365,93 +14549,93 @@
         <v>29</v>
       </c>
       <c r="C10" t="s">
-        <v>1328</v>
+        <v>1347</v>
       </c>
       <c r="D10" t="s">
-        <v>1329</v>
+        <v>1348</v>
       </c>
       <c r="E10" t="s">
-        <v>1330</v>
+        <v>1349</v>
       </c>
       <c r="F10" t="s">
-        <v>1331</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>1332</v>
+        <v>1351</v>
       </c>
       <c r="B11" t="s">
         <v>55</v>
       </c>
       <c r="C11" t="s">
-        <v>1333</v>
+        <v>1352</v>
       </c>
       <c r="D11" t="s">
-        <v>1334</v>
+        <v>1353</v>
       </c>
       <c r="E11" t="s">
-        <v>1330</v>
+        <v>1349</v>
       </c>
       <c r="F11" t="s">
-        <v>1335</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>1336</v>
+        <v>1355</v>
       </c>
       <c r="B12" t="s">
         <v>161</v>
       </c>
       <c r="C12" t="s">
-        <v>1337</v>
+        <v>1356</v>
       </c>
       <c r="D12" t="s">
-        <v>1338</v>
+        <v>1357</v>
       </c>
       <c r="E12" t="s">
-        <v>1339</v>
+        <v>1358</v>
       </c>
       <c r="F12" t="s">
-        <v>1340</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>1341</v>
+        <v>1360</v>
       </c>
       <c r="B13" t="s">
-        <v>1342</v>
+        <v>1361</v>
       </c>
       <c r="C13" t="s">
-        <v>1343</v>
+        <v>1362</v>
       </c>
       <c r="D13" t="s">
-        <v>1344</v>
+        <v>1363</v>
       </c>
       <c r="E13" t="s">
-        <v>1345</v>
+        <v>1364</v>
       </c>
       <c r="F13" t="s">
-        <v>1346</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>1347</v>
+        <v>1366</v>
       </c>
       <c r="B14" t="s">
         <v>206</v>
       </c>
       <c r="C14" t="s">
-        <v>1348</v>
+        <v>1367</v>
       </c>
       <c r="D14" t="s">
-        <v>1349</v>
+        <v>1368</v>
       </c>
       <c r="E14" t="s">
-        <v>1350</v>
+        <v>1369</v>
       </c>
       <c r="F14" t="s">
         <v>748</v>
@@ -14459,19 +14643,19 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>1351</v>
+        <v>1370</v>
       </c>
       <c r="B15" t="s">
         <v>206</v>
       </c>
       <c r="C15" t="s">
-        <v>1352</v>
+        <v>1371</v>
       </c>
       <c r="D15" t="s">
-        <v>1353</v>
+        <v>1372</v>
       </c>
       <c r="E15" t="s">
-        <v>1354</v>
+        <v>1373</v>
       </c>
       <c r="F15" t="s">
         <v>748</v>
@@ -14479,19 +14663,19 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>1355</v>
+        <v>1374</v>
       </c>
       <c r="B16" t="s">
         <v>918</v>
       </c>
       <c r="C16" t="s">
-        <v>1356</v>
+        <v>1375</v>
       </c>
       <c r="D16" t="s">
-        <v>1357</v>
+        <v>1376</v>
       </c>
       <c r="E16" t="s">
-        <v>1354</v>
+        <v>1373</v>
       </c>
       <c r="F16" t="s">
         <v>924</v>
@@ -14499,19 +14683,19 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>1358</v>
+        <v>1377</v>
       </c>
       <c r="B17" t="s">
         <v>999</v>
       </c>
       <c r="C17" t="s">
-        <v>1359</v>
+        <v>1378</v>
       </c>
       <c r="D17" t="s">
-        <v>1360</v>
+        <v>1379</v>
       </c>
       <c r="E17" t="s">
-        <v>1354</v>
+        <v>1373</v>
       </c>
       <c r="F17" t="s">
         <v>924</v>
@@ -14519,21 +14703,41 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>1361</v>
+        <v>1380</v>
       </c>
       <c r="B18" t="s">
         <v>1095</v>
       </c>
       <c r="C18" t="s">
-        <v>1362</v>
+        <v>1381</v>
       </c>
       <c r="D18" t="s">
-        <v>1363</v>
+        <v>1382</v>
       </c>
       <c r="E18" t="s">
-        <v>1354</v>
+        <v>1373</v>
       </c>
       <c r="F18" t="s">
+        <v>924</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>1383</v>
+      </c>
+      <c r="B19" t="s">
+        <v>1141</v>
+      </c>
+      <c r="C19" t="s">
+        <v>1384</v>
+      </c>
+      <c r="D19" t="s">
+        <v>1385</v>
+      </c>
+      <c r="E19" t="s">
+        <v>1373</v>
+      </c>
+      <c r="F19" t="s">
         <v>924</v>
       </c>
     </row>
@@ -14543,40 +14747,40 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G157"/>
+  <dimension ref="A1:G159"/>
   <sheetFormatPr defaultRowHeight="0" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" customHeight="1"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>1364</v>
+        <v>1386</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1365</v>
+        <v>1387</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>1366</v>
+        <v>1388</v>
       </c>
       <c r="B3" t="s">
-        <v>1367</v>
+        <v>1389</v>
       </c>
       <c r="C3" t="s">
-        <v>1368</v>
+        <v>1390</v>
       </c>
       <c r="D3" t="s">
-        <v>1369</v>
+        <v>1391</v>
       </c>
       <c r="E3" t="s">
-        <v>1370</v>
+        <v>1392</v>
       </c>
       <c r="F3" t="s">
-        <v>1371</v>
+        <v>1393</v>
       </c>
       <c r="G3" t="s">
-        <v>1372</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -14596,10 +14800,10 @@
         <v>26</v>
       </c>
       <c r="F4" t="s">
-        <v>1373</v>
+        <v>1395</v>
       </c>
       <c r="G4" t="s">
-        <v>1374</v>
+        <v>1396</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -14619,10 +14823,10 @@
         <v>26</v>
       </c>
       <c r="F5" t="s">
-        <v>1373</v>
+        <v>1395</v>
       </c>
       <c r="G5" t="s">
-        <v>1375</v>
+        <v>1397</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -14642,10 +14846,10 @@
         <v>26</v>
       </c>
       <c r="F6" t="s">
-        <v>1373</v>
+        <v>1395</v>
       </c>
       <c r="G6" t="s">
-        <v>1376</v>
+        <v>1398</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -14665,10 +14869,10 @@
         <v>86</v>
       </c>
       <c r="F7" t="s">
-        <v>1373</v>
+        <v>1395</v>
       </c>
       <c r="G7" t="s">
-        <v>1377</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -14688,10 +14892,10 @@
         <v>26</v>
       </c>
       <c r="F8" t="s">
-        <v>1373</v>
+        <v>1395</v>
       </c>
       <c r="G8" t="s">
-        <v>1378</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -14711,10 +14915,10 @@
         <v>26</v>
       </c>
       <c r="F9" t="s">
-        <v>1373</v>
+        <v>1395</v>
       </c>
       <c r="G9" t="s">
-        <v>1379</v>
+        <v>1401</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -14734,10 +14938,10 @@
         <v>26</v>
       </c>
       <c r="F10" t="s">
-        <v>1373</v>
+        <v>1395</v>
       </c>
       <c r="G10" t="s">
-        <v>1380</v>
+        <v>1402</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -14757,10 +14961,10 @@
         <v>86</v>
       </c>
       <c r="F11" t="s">
-        <v>1373</v>
+        <v>1395</v>
       </c>
       <c r="G11" t="s">
-        <v>1381</v>
+        <v>1403</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -14780,10 +14984,10 @@
         <v>86</v>
       </c>
       <c r="F12" t="s">
-        <v>1373</v>
+        <v>1395</v>
       </c>
       <c r="G12" t="s">
-        <v>1382</v>
+        <v>1404</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -14803,10 +15007,10 @@
         <v>26</v>
       </c>
       <c r="F13" t="s">
-        <v>1373</v>
+        <v>1395</v>
       </c>
       <c r="G13" t="s">
-        <v>1383</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -14826,10 +15030,10 @@
         <v>26</v>
       </c>
       <c r="F14" t="s">
-        <v>1384</v>
+        <v>1406</v>
       </c>
       <c r="G14" t="s">
-        <v>1385</v>
+        <v>1407</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -14849,10 +15053,10 @@
         <v>26</v>
       </c>
       <c r="F15" t="s">
-        <v>1384</v>
+        <v>1406</v>
       </c>
       <c r="G15" t="s">
-        <v>1386</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -14872,10 +15076,10 @@
         <v>26</v>
       </c>
       <c r="F16" t="s">
-        <v>1384</v>
+        <v>1406</v>
       </c>
       <c r="G16" t="s">
-        <v>1387</v>
+        <v>1409</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -14895,10 +15099,10 @@
         <v>26</v>
       </c>
       <c r="F17" t="s">
-        <v>1384</v>
+        <v>1406</v>
       </c>
       <c r="G17" t="s">
-        <v>1388</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -14918,10 +15122,10 @@
         <v>26</v>
       </c>
       <c r="F18" t="s">
-        <v>1384</v>
+        <v>1406</v>
       </c>
       <c r="G18" t="s">
-        <v>1389</v>
+        <v>1411</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -14941,10 +15145,10 @@
         <v>26</v>
       </c>
       <c r="F19" t="s">
-        <v>1384</v>
+        <v>1406</v>
       </c>
       <c r="G19" t="s">
-        <v>1390</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -14964,10 +15168,10 @@
         <v>86</v>
       </c>
       <c r="F20" t="s">
-        <v>1384</v>
+        <v>1406</v>
       </c>
       <c r="G20" t="s">
-        <v>1391</v>
+        <v>1413</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -14987,10 +15191,10 @@
         <v>86</v>
       </c>
       <c r="F21" t="s">
-        <v>1384</v>
+        <v>1406</v>
       </c>
       <c r="G21" t="s">
-        <v>1392</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
@@ -15010,10 +15214,10 @@
         <v>26</v>
       </c>
       <c r="F22" t="s">
-        <v>1384</v>
+        <v>1406</v>
       </c>
       <c r="G22" t="s">
-        <v>1393</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
@@ -15033,10 +15237,10 @@
         <v>86</v>
       </c>
       <c r="F23" t="s">
-        <v>1384</v>
+        <v>1406</v>
       </c>
       <c r="G23" t="s">
-        <v>1394</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -15056,10 +15260,10 @@
         <v>86</v>
       </c>
       <c r="F24" t="s">
-        <v>1384</v>
+        <v>1406</v>
       </c>
       <c r="G24" t="s">
-        <v>1395</v>
+        <v>1417</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
@@ -15079,10 +15283,10 @@
         <v>86</v>
       </c>
       <c r="F25" t="s">
-        <v>1384</v>
+        <v>1406</v>
       </c>
       <c r="G25" t="s">
-        <v>1396</v>
+        <v>1418</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
@@ -15102,10 +15306,10 @@
         <v>86</v>
       </c>
       <c r="F26" t="s">
-        <v>1384</v>
+        <v>1406</v>
       </c>
       <c r="G26" t="s">
-        <v>1397</v>
+        <v>1419</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
@@ -15125,10 +15329,10 @@
         <v>26</v>
       </c>
       <c r="F27" t="s">
-        <v>1384</v>
+        <v>1406</v>
       </c>
       <c r="G27" t="s">
-        <v>1398</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
@@ -15148,10 +15352,10 @@
         <v>86</v>
       </c>
       <c r="F28" t="s">
-        <v>1384</v>
+        <v>1406</v>
       </c>
       <c r="G28" t="s">
-        <v>1399</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
@@ -15171,10 +15375,10 @@
         <v>86</v>
       </c>
       <c r="F29" t="s">
-        <v>1384</v>
+        <v>1406</v>
       </c>
       <c r="G29" t="s">
-        <v>1400</v>
+        <v>1422</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
@@ -15194,10 +15398,10 @@
         <v>26</v>
       </c>
       <c r="F30" t="s">
-        <v>1384</v>
+        <v>1406</v>
       </c>
       <c r="G30" t="s">
-        <v>1401</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
@@ -15217,10 +15421,10 @@
         <v>26</v>
       </c>
       <c r="F31" t="s">
-        <v>1384</v>
+        <v>1406</v>
       </c>
       <c r="G31" t="s">
-        <v>1402</v>
+        <v>1424</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
@@ -15240,10 +15444,10 @@
         <v>86</v>
       </c>
       <c r="F32" t="s">
-        <v>1384</v>
+        <v>1406</v>
       </c>
       <c r="G32" t="s">
-        <v>1403</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
@@ -15263,10 +15467,10 @@
         <v>86</v>
       </c>
       <c r="F33" t="s">
-        <v>1384</v>
+        <v>1406</v>
       </c>
       <c r="G33" t="s">
-        <v>1404</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
@@ -15286,10 +15490,10 @@
         <v>86</v>
       </c>
       <c r="F34" t="s">
-        <v>1384</v>
+        <v>1406</v>
       </c>
       <c r="G34" t="s">
-        <v>1405</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
@@ -15309,7 +15513,7 @@
         <v>26</v>
       </c>
       <c r="F35" t="s">
-        <v>1406</v>
+        <v>1428</v>
       </c>
       <c r="G35" t="s">
         <v>168</v>
@@ -15332,7 +15536,7 @@
         <v>26</v>
       </c>
       <c r="F36" t="s">
-        <v>1406</v>
+        <v>1428</v>
       </c>
       <c r="G36" t="s">
         <v>177</v>
@@ -15355,7 +15559,7 @@
         <v>26</v>
       </c>
       <c r="F37" t="s">
-        <v>1406</v>
+        <v>1428</v>
       </c>
       <c r="G37" t="s">
         <v>194</v>
@@ -15378,7 +15582,7 @@
         <v>26</v>
       </c>
       <c r="F38" t="s">
-        <v>1406</v>
+        <v>1428</v>
       </c>
       <c r="G38" t="s">
         <v>203</v>
@@ -15401,7 +15605,7 @@
         <v>26</v>
       </c>
       <c r="F39" t="s">
-        <v>1406</v>
+        <v>1428</v>
       </c>
       <c r="G39" t="s">
         <v>222</v>
@@ -15424,7 +15628,7 @@
         <v>26</v>
       </c>
       <c r="F40" t="s">
-        <v>1406</v>
+        <v>1428</v>
       </c>
       <c r="G40" t="s">
         <v>245</v>
@@ -15447,10 +15651,10 @@
         <v>26</v>
       </c>
       <c r="F41" t="s">
-        <v>1406</v>
+        <v>1428</v>
       </c>
       <c r="G41" t="s">
-        <v>1407</v>
+        <v>1429</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
@@ -15470,10 +15674,10 @@
         <v>26</v>
       </c>
       <c r="F42" t="s">
-        <v>1406</v>
+        <v>1428</v>
       </c>
       <c r="G42" t="s">
-        <v>1408</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
@@ -15493,10 +15697,10 @@
         <v>26</v>
       </c>
       <c r="F43" t="s">
-        <v>1406</v>
+        <v>1428</v>
       </c>
       <c r="G43" t="s">
-        <v>1409</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
@@ -15516,7 +15720,7 @@
         <v>26</v>
       </c>
       <c r="F44" t="s">
-        <v>1406</v>
+        <v>1428</v>
       </c>
       <c r="G44" t="s">
         <v>360</v>
@@ -15539,7 +15743,7 @@
         <v>26</v>
       </c>
       <c r="F45" t="s">
-        <v>1406</v>
+        <v>1428</v>
       </c>
       <c r="G45" t="s">
         <v>368</v>
@@ -15562,10 +15766,10 @@
         <v>26</v>
       </c>
       <c r="F46" t="s">
-        <v>1406</v>
+        <v>1428</v>
       </c>
       <c r="G46" t="s">
-        <v>1410</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
@@ -15585,7 +15789,7 @@
         <v>26</v>
       </c>
       <c r="F47" t="s">
-        <v>1406</v>
+        <v>1428</v>
       </c>
       <c r="G47" t="s">
         <v>386</v>
@@ -15608,10 +15812,10 @@
         <v>26</v>
       </c>
       <c r="F48" t="s">
-        <v>1406</v>
+        <v>1428</v>
       </c>
       <c r="G48" t="s">
-        <v>1411</v>
+        <v>1433</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
@@ -15631,7 +15835,7 @@
         <v>26</v>
       </c>
       <c r="F49" t="s">
-        <v>1406</v>
+        <v>1428</v>
       </c>
       <c r="G49" t="s">
         <v>402</v>
@@ -15654,7 +15858,7 @@
         <v>26</v>
       </c>
       <c r="F50" t="s">
-        <v>1406</v>
+        <v>1428</v>
       </c>
       <c r="G50" t="s">
         <v>411</v>
@@ -15677,7 +15881,7 @@
         <v>26</v>
       </c>
       <c r="F51" t="s">
-        <v>1406</v>
+        <v>1428</v>
       </c>
       <c r="G51" t="s">
         <v>419</v>
@@ -15700,7 +15904,7 @@
         <v>26</v>
       </c>
       <c r="F52" t="s">
-        <v>1406</v>
+        <v>1428</v>
       </c>
       <c r="G52" t="s">
         <v>426</v>
@@ -15723,7 +15927,7 @@
         <v>26</v>
       </c>
       <c r="F53" t="s">
-        <v>1406</v>
+        <v>1428</v>
       </c>
       <c r="G53" t="s">
         <v>433</v>
@@ -15746,7 +15950,7 @@
         <v>26</v>
       </c>
       <c r="F54" t="s">
-        <v>1406</v>
+        <v>1428</v>
       </c>
       <c r="G54" t="s">
         <v>467</v>
@@ -15769,7 +15973,7 @@
         <v>26</v>
       </c>
       <c r="F55" t="s">
-        <v>1406</v>
+        <v>1428</v>
       </c>
       <c r="G55" t="s">
         <v>485</v>
@@ -15792,7 +15996,7 @@
         <v>26</v>
       </c>
       <c r="F56" t="s">
-        <v>1406</v>
+        <v>1428</v>
       </c>
       <c r="G56" t="s">
         <v>494</v>
@@ -15815,7 +16019,7 @@
         <v>26</v>
       </c>
       <c r="F57" t="s">
-        <v>1406</v>
+        <v>1428</v>
       </c>
       <c r="G57" t="s">
         <v>502</v>
@@ -15838,7 +16042,7 @@
         <v>26</v>
       </c>
       <c r="F58" t="s">
-        <v>1406</v>
+        <v>1428</v>
       </c>
       <c r="G58" t="s">
         <v>511</v>
@@ -15861,7 +16065,7 @@
         <v>26</v>
       </c>
       <c r="F59" t="s">
-        <v>1406</v>
+        <v>1428</v>
       </c>
       <c r="G59" t="s">
         <v>520</v>
@@ -15884,7 +16088,7 @@
         <v>26</v>
       </c>
       <c r="F60" t="s">
-        <v>1406</v>
+        <v>1428</v>
       </c>
       <c r="G60" t="s">
         <v>530</v>
@@ -15907,7 +16111,7 @@
         <v>26</v>
       </c>
       <c r="F61" t="s">
-        <v>1406</v>
+        <v>1428</v>
       </c>
       <c r="G61" t="s">
         <v>539</v>
@@ -15930,7 +16134,7 @@
         <v>26</v>
       </c>
       <c r="F62" t="s">
-        <v>1406</v>
+        <v>1428</v>
       </c>
       <c r="G62" t="s">
         <v>547</v>
@@ -15953,7 +16157,7 @@
         <v>26</v>
       </c>
       <c r="F63" t="s">
-        <v>1406</v>
+        <v>1428</v>
       </c>
       <c r="G63" t="s">
         <v>557</v>
@@ -15976,7 +16180,7 @@
         <v>26</v>
       </c>
       <c r="F64" t="s">
-        <v>1406</v>
+        <v>1428</v>
       </c>
       <c r="G64" t="s">
         <v>567</v>
@@ -15999,7 +16203,7 @@
         <v>26</v>
       </c>
       <c r="F65" t="s">
-        <v>1406</v>
+        <v>1428</v>
       </c>
       <c r="G65" t="s">
         <v>576</v>
@@ -16022,7 +16226,7 @@
         <v>26</v>
       </c>
       <c r="F66" t="s">
-        <v>1406</v>
+        <v>1428</v>
       </c>
       <c r="G66" t="s">
         <v>584</v>
@@ -16045,7 +16249,7 @@
         <v>26</v>
       </c>
       <c r="F67" t="s">
-        <v>1406</v>
+        <v>1428</v>
       </c>
       <c r="G67" t="s">
         <v>594</v>
@@ -16068,7 +16272,7 @@
         <v>26</v>
       </c>
       <c r="F68" t="s">
-        <v>1406</v>
+        <v>1428</v>
       </c>
       <c r="G68" t="s">
         <v>602</v>
@@ -16091,7 +16295,7 @@
         <v>26</v>
       </c>
       <c r="F69" t="s">
-        <v>1406</v>
+        <v>1428</v>
       </c>
       <c r="G69" t="s">
         <v>611</v>
@@ -16114,7 +16318,7 @@
         <v>26</v>
       </c>
       <c r="F70" t="s">
-        <v>1406</v>
+        <v>1428</v>
       </c>
       <c r="G70" t="s">
         <v>618</v>
@@ -16137,10 +16341,10 @@
         <v>26</v>
       </c>
       <c r="F71" t="s">
-        <v>1406</v>
+        <v>1428</v>
       </c>
       <c r="G71" t="s">
-        <v>1412</v>
+        <v>1434</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
@@ -16160,10 +16364,10 @@
         <v>26</v>
       </c>
       <c r="F72" t="s">
-        <v>1406</v>
+        <v>1428</v>
       </c>
       <c r="G72" t="s">
-        <v>1413</v>
+        <v>1435</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
@@ -16183,10 +16387,10 @@
         <v>26</v>
       </c>
       <c r="F73" t="s">
-        <v>1406</v>
+        <v>1428</v>
       </c>
       <c r="G73" t="s">
-        <v>1414</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
@@ -16206,10 +16410,10 @@
         <v>26</v>
       </c>
       <c r="F74" t="s">
-        <v>1406</v>
+        <v>1428</v>
       </c>
       <c r="G74" t="s">
-        <v>1415</v>
+        <v>1437</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
@@ -16229,10 +16433,10 @@
         <v>26</v>
       </c>
       <c r="F75" t="s">
-        <v>1406</v>
+        <v>1428</v>
       </c>
       <c r="G75" t="s">
-        <v>1416</v>
+        <v>1438</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
@@ -16252,10 +16456,10 @@
         <v>26</v>
       </c>
       <c r="F76" t="s">
-        <v>1406</v>
+        <v>1428</v>
       </c>
       <c r="G76" t="s">
-        <v>1417</v>
+        <v>1439</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
@@ -16275,10 +16479,10 @@
         <v>26</v>
       </c>
       <c r="F77" t="s">
-        <v>1406</v>
+        <v>1428</v>
       </c>
       <c r="G77" t="s">
-        <v>1418</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
@@ -16298,10 +16502,10 @@
         <v>26</v>
       </c>
       <c r="F78" t="s">
-        <v>1406</v>
+        <v>1428</v>
       </c>
       <c r="G78" t="s">
-        <v>1419</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
@@ -16321,10 +16525,10 @@
         <v>26</v>
       </c>
       <c r="F79" t="s">
-        <v>1406</v>
+        <v>1428</v>
       </c>
       <c r="G79" t="s">
-        <v>1420</v>
+        <v>1442</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
@@ -16332,7 +16536,7 @@
         <v>27</v>
       </c>
       <c r="B80" t="s">
-        <v>1342</v>
+        <v>1361</v>
       </c>
       <c r="C80" t="s">
         <v>697</v>
@@ -16344,10 +16548,10 @@
         <v>26</v>
       </c>
       <c r="F80" t="s">
-        <v>1421</v>
+        <v>1443</v>
       </c>
       <c r="G80" t="s">
-        <v>1422</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
@@ -16355,7 +16559,7 @@
         <v>27</v>
       </c>
       <c r="B81" t="s">
-        <v>1342</v>
+        <v>1361</v>
       </c>
       <c r="C81" t="s">
         <v>708</v>
@@ -16367,10 +16571,10 @@
         <v>26</v>
       </c>
       <c r="F81" t="s">
-        <v>1421</v>
+        <v>1443</v>
       </c>
       <c r="G81" t="s">
-        <v>1423</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
@@ -16378,7 +16582,7 @@
         <v>27</v>
       </c>
       <c r="B82" t="s">
-        <v>1342</v>
+        <v>1361</v>
       </c>
       <c r="C82" t="s">
         <v>715</v>
@@ -16390,10 +16594,10 @@
         <v>26</v>
       </c>
       <c r="F82" t="s">
-        <v>1421</v>
+        <v>1443</v>
       </c>
       <c r="G82" t="s">
-        <v>1424</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
@@ -16401,7 +16605,7 @@
         <v>27</v>
       </c>
       <c r="B83" t="s">
-        <v>1342</v>
+        <v>1361</v>
       </c>
       <c r="C83" t="s">
         <v>723</v>
@@ -16413,10 +16617,10 @@
         <v>26</v>
       </c>
       <c r="F83" t="s">
-        <v>1421</v>
+        <v>1443</v>
       </c>
       <c r="G83" t="s">
-        <v>1425</v>
+        <v>1447</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
@@ -16424,7 +16628,7 @@
         <v>27</v>
       </c>
       <c r="B84" t="s">
-        <v>1342</v>
+        <v>1361</v>
       </c>
       <c r="C84" t="s">
         <v>732</v>
@@ -16436,10 +16640,10 @@
         <v>26</v>
       </c>
       <c r="F84" t="s">
-        <v>1421</v>
+        <v>1443</v>
       </c>
       <c r="G84" t="s">
-        <v>1426</v>
+        <v>1448</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
@@ -16447,7 +16651,7 @@
         <v>27</v>
       </c>
       <c r="B85" t="s">
-        <v>1427</v>
+        <v>1449</v>
       </c>
       <c r="C85" t="s">
         <v>324</v>
@@ -16459,10 +16663,10 @@
         <v>86</v>
       </c>
       <c r="F85" t="s">
-        <v>1428</v>
+        <v>1450</v>
       </c>
       <c r="G85" t="s">
-        <v>1429</v>
+        <v>1451</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
@@ -16470,7 +16674,7 @@
         <v>27</v>
       </c>
       <c r="B86" t="s">
-        <v>1427</v>
+        <v>1449</v>
       </c>
       <c r="C86" t="s">
         <v>335</v>
@@ -16482,10 +16686,10 @@
         <v>86</v>
       </c>
       <c r="F86" t="s">
-        <v>1428</v>
+        <v>1450</v>
       </c>
       <c r="G86" t="s">
-        <v>1430</v>
+        <v>1452</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
@@ -16493,7 +16697,7 @@
         <v>27</v>
       </c>
       <c r="B87" t="s">
-        <v>1427</v>
+        <v>1449</v>
       </c>
       <c r="C87" t="s">
         <v>344</v>
@@ -16505,10 +16709,10 @@
         <v>86</v>
       </c>
       <c r="F87" t="s">
-        <v>1428</v>
+        <v>1450</v>
       </c>
       <c r="G87" t="s">
-        <v>1431</v>
+        <v>1453</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
@@ -16516,7 +16720,7 @@
         <v>27</v>
       </c>
       <c r="B88" t="s">
-        <v>1427</v>
+        <v>1449</v>
       </c>
       <c r="C88" t="s">
         <v>369</v>
@@ -16528,10 +16732,10 @@
         <v>112</v>
       </c>
       <c r="F88" t="s">
-        <v>1428</v>
+        <v>1450</v>
       </c>
       <c r="G88" t="s">
-        <v>1432</v>
+        <v>1454</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
@@ -16551,10 +16755,10 @@
         <v>26</v>
       </c>
       <c r="F89" t="s">
-        <v>1433</v>
+        <v>1455</v>
       </c>
       <c r="G89" t="s">
-        <v>1434</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
@@ -16562,7 +16766,7 @@
         <v>27</v>
       </c>
       <c r="B90" t="s">
-        <v>1427</v>
+        <v>1449</v>
       </c>
       <c r="C90" t="s">
         <v>619</v>
@@ -16574,10 +16778,10 @@
         <v>112</v>
       </c>
       <c r="F90" t="s">
-        <v>1428</v>
+        <v>1450</v>
       </c>
       <c r="G90" t="s">
-        <v>1435</v>
+        <v>1457</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
@@ -16585,7 +16789,7 @@
         <v>27</v>
       </c>
       <c r="B91" t="s">
-        <v>1427</v>
+        <v>1449</v>
       </c>
       <c r="C91" t="s">
         <v>639</v>
@@ -16597,10 +16801,10 @@
         <v>86</v>
       </c>
       <c r="F91" t="s">
-        <v>1428</v>
+        <v>1450</v>
       </c>
       <c r="G91" t="s">
-        <v>1436</v>
+        <v>1458</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
@@ -16608,7 +16812,7 @@
         <v>27</v>
       </c>
       <c r="B92" t="s">
-        <v>1427</v>
+        <v>1449</v>
       </c>
       <c r="C92" t="s">
         <v>648</v>
@@ -16620,10 +16824,10 @@
         <v>112</v>
       </c>
       <c r="F92" t="s">
-        <v>1428</v>
+        <v>1450</v>
       </c>
       <c r="G92" t="s">
-        <v>1437</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
@@ -16643,10 +16847,10 @@
         <v>86</v>
       </c>
       <c r="F93" t="s">
-        <v>1433</v>
+        <v>1455</v>
       </c>
       <c r="G93" t="s">
-        <v>1438</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
@@ -16654,7 +16858,7 @@
         <v>27</v>
       </c>
       <c r="B94" t="s">
-        <v>1427</v>
+        <v>1449</v>
       </c>
       <c r="C94" t="s">
         <v>657</v>
@@ -16666,10 +16870,10 @@
         <v>112</v>
       </c>
       <c r="F94" t="s">
-        <v>1428</v>
+        <v>1450</v>
       </c>
       <c r="G94" t="s">
-        <v>1439</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
@@ -16677,7 +16881,7 @@
         <v>27</v>
       </c>
       <c r="B95" t="s">
-        <v>1427</v>
+        <v>1449</v>
       </c>
       <c r="C95" t="s">
         <v>673</v>
@@ -16689,10 +16893,10 @@
         <v>112</v>
       </c>
       <c r="F95" t="s">
-        <v>1428</v>
+        <v>1450</v>
       </c>
       <c r="G95" t="s">
-        <v>1440</v>
+        <v>1462</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
@@ -16712,10 +16916,10 @@
         <v>26</v>
       </c>
       <c r="F96" t="s">
-        <v>1433</v>
+        <v>1455</v>
       </c>
       <c r="G96" t="s">
-        <v>1441</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
@@ -16723,7 +16927,7 @@
         <v>27</v>
       </c>
       <c r="B97" t="s">
-        <v>1427</v>
+        <v>1449</v>
       </c>
       <c r="C97" t="s">
         <v>689</v>
@@ -16735,10 +16939,10 @@
         <v>112</v>
       </c>
       <c r="F97" t="s">
-        <v>1428</v>
+        <v>1450</v>
       </c>
       <c r="G97" t="s">
-        <v>1442</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
@@ -16746,7 +16950,7 @@
         <v>27</v>
       </c>
       <c r="B98" t="s">
-        <v>1427</v>
+        <v>1449</v>
       </c>
       <c r="C98" t="s">
         <v>697</v>
@@ -16758,10 +16962,10 @@
         <v>112</v>
       </c>
       <c r="F98" t="s">
-        <v>1428</v>
+        <v>1450</v>
       </c>
       <c r="G98" t="s">
-        <v>1443</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
@@ -16781,10 +16985,10 @@
         <v>26</v>
       </c>
       <c r="F99" t="s">
-        <v>1433</v>
+        <v>1455</v>
       </c>
       <c r="G99" t="s">
-        <v>1444</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
@@ -16792,7 +16996,7 @@
         <v>27</v>
       </c>
       <c r="B100" t="s">
-        <v>1427</v>
+        <v>1449</v>
       </c>
       <c r="C100" t="s">
         <v>708</v>
@@ -16804,10 +17008,10 @@
         <v>112</v>
       </c>
       <c r="F100" t="s">
-        <v>1428</v>
+        <v>1450</v>
       </c>
       <c r="G100" t="s">
-        <v>1445</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
@@ -16827,10 +17031,10 @@
         <v>86</v>
       </c>
       <c r="F101" t="s">
-        <v>1433</v>
+        <v>1455</v>
       </c>
       <c r="G101" t="s">
-        <v>1446</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
@@ -16838,7 +17042,7 @@
         <v>27</v>
       </c>
       <c r="B102" t="s">
-        <v>1427</v>
+        <v>1449</v>
       </c>
       <c r="C102" t="s">
         <v>715</v>
@@ -16850,10 +17054,10 @@
         <v>112</v>
       </c>
       <c r="F102" t="s">
-        <v>1428</v>
+        <v>1450</v>
       </c>
       <c r="G102" t="s">
-        <v>1447</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
@@ -16873,10 +17077,10 @@
         <v>86</v>
       </c>
       <c r="F103" t="s">
-        <v>1433</v>
+        <v>1455</v>
       </c>
       <c r="G103" t="s">
-        <v>1448</v>
+        <v>1470</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
@@ -16884,7 +17088,7 @@
         <v>27</v>
       </c>
       <c r="B104" t="s">
-        <v>1427</v>
+        <v>1449</v>
       </c>
       <c r="C104" t="s">
         <v>723</v>
@@ -16896,10 +17100,10 @@
         <v>112</v>
       </c>
       <c r="F104" t="s">
-        <v>1428</v>
+        <v>1450</v>
       </c>
       <c r="G104" t="s">
-        <v>1449</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
@@ -16919,10 +17123,10 @@
         <v>26</v>
       </c>
       <c r="F105" t="s">
-        <v>1433</v>
+        <v>1455</v>
       </c>
       <c r="G105" t="s">
-        <v>1450</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
@@ -16930,7 +17134,7 @@
         <v>27</v>
       </c>
       <c r="B106" t="s">
-        <v>1427</v>
+        <v>1449</v>
       </c>
       <c r="C106" t="s">
         <v>732</v>
@@ -16942,10 +17146,10 @@
         <v>112</v>
       </c>
       <c r="F106" t="s">
-        <v>1428</v>
+        <v>1450</v>
       </c>
       <c r="G106" t="s">
-        <v>1451</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
@@ -16965,10 +17169,10 @@
         <v>26</v>
       </c>
       <c r="F107" t="s">
-        <v>1433</v>
+        <v>1455</v>
       </c>
       <c r="G107" t="s">
-        <v>1452</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
@@ -16982,13 +17186,13 @@
         <v>740</v>
       </c>
       <c r="D108" t="s">
-        <v>1453</v>
+        <v>1475</v>
       </c>
       <c r="E108" t="s">
         <v>112</v>
       </c>
       <c r="F108" t="s">
-        <v>1433</v>
+        <v>1455</v>
       </c>
       <c r="G108" t="s">
         <v>741</v>
@@ -17005,13 +17209,13 @@
         <v>750</v>
       </c>
       <c r="D109" t="s">
-        <v>1453</v>
+        <v>1475</v>
       </c>
       <c r="E109" t="s">
         <v>112</v>
       </c>
       <c r="F109" t="s">
-        <v>1433</v>
+        <v>1455</v>
       </c>
       <c r="G109" t="s">
         <v>751</v>
@@ -17028,13 +17232,13 @@
         <v>758</v>
       </c>
       <c r="D110" t="s">
-        <v>1453</v>
+        <v>1475</v>
       </c>
       <c r="E110" t="s">
         <v>112</v>
       </c>
       <c r="F110" t="s">
-        <v>1433</v>
+        <v>1455</v>
       </c>
       <c r="G110" t="s">
         <v>759</v>
@@ -17051,13 +17255,13 @@
         <v>766</v>
       </c>
       <c r="D111" t="s">
-        <v>1453</v>
+        <v>1475</v>
       </c>
       <c r="E111" t="s">
         <v>112</v>
       </c>
       <c r="F111" t="s">
-        <v>1433</v>
+        <v>1455</v>
       </c>
       <c r="G111" t="s">
         <v>767</v>
@@ -17074,13 +17278,13 @@
         <v>774</v>
       </c>
       <c r="D112" t="s">
-        <v>1453</v>
+        <v>1475</v>
       </c>
       <c r="E112" t="s">
         <v>112</v>
       </c>
       <c r="F112" t="s">
-        <v>1433</v>
+        <v>1455</v>
       </c>
       <c r="G112" t="s">
         <v>775</v>
@@ -17097,13 +17301,13 @@
         <v>782</v>
       </c>
       <c r="D113" t="s">
-        <v>1453</v>
+        <v>1475</v>
       </c>
       <c r="E113" t="s">
         <v>112</v>
       </c>
       <c r="F113" t="s">
-        <v>1433</v>
+        <v>1455</v>
       </c>
       <c r="G113" t="s">
         <v>783</v>
@@ -17120,13 +17324,13 @@
         <v>790</v>
       </c>
       <c r="D114" t="s">
-        <v>1453</v>
+        <v>1475</v>
       </c>
       <c r="E114" t="s">
         <v>112</v>
       </c>
       <c r="F114" t="s">
-        <v>1433</v>
+        <v>1455</v>
       </c>
       <c r="G114" t="s">
         <v>791</v>
@@ -17143,13 +17347,13 @@
         <v>798</v>
       </c>
       <c r="D115" t="s">
-        <v>1453</v>
+        <v>1475</v>
       </c>
       <c r="E115" t="s">
         <v>112</v>
       </c>
       <c r="F115" t="s">
-        <v>1433</v>
+        <v>1455</v>
       </c>
       <c r="G115" t="s">
         <v>799</v>
@@ -17166,13 +17370,13 @@
         <v>806</v>
       </c>
       <c r="D116" t="s">
-        <v>1453</v>
+        <v>1475</v>
       </c>
       <c r="E116" t="s">
         <v>112</v>
       </c>
       <c r="F116" t="s">
-        <v>1433</v>
+        <v>1455</v>
       </c>
       <c r="G116" t="s">
         <v>807</v>
@@ -17189,13 +17393,13 @@
         <v>814</v>
       </c>
       <c r="D117" t="s">
-        <v>1453</v>
+        <v>1475</v>
       </c>
       <c r="E117" t="s">
         <v>112</v>
       </c>
       <c r="F117" t="s">
-        <v>1433</v>
+        <v>1455</v>
       </c>
       <c r="G117" t="s">
         <v>815</v>
@@ -17212,13 +17416,13 @@
         <v>821</v>
       </c>
       <c r="D118" t="s">
-        <v>1453</v>
+        <v>1475</v>
       </c>
       <c r="E118" t="s">
         <v>112</v>
       </c>
       <c r="F118" t="s">
-        <v>1433</v>
+        <v>1455</v>
       </c>
       <c r="G118" t="s">
         <v>823</v>
@@ -17235,13 +17439,13 @@
         <v>830</v>
       </c>
       <c r="D119" t="s">
-        <v>1453</v>
+        <v>1475</v>
       </c>
       <c r="E119" t="s">
         <v>112</v>
       </c>
       <c r="F119" t="s">
-        <v>1433</v>
+        <v>1455</v>
       </c>
       <c r="G119" t="s">
         <v>831</v>
@@ -17258,13 +17462,13 @@
         <v>837</v>
       </c>
       <c r="D120" t="s">
-        <v>1453</v>
+        <v>1475</v>
       </c>
       <c r="E120" t="s">
         <v>112</v>
       </c>
       <c r="F120" t="s">
-        <v>1433</v>
+        <v>1455</v>
       </c>
       <c r="G120" t="s">
         <v>838</v>
@@ -17281,13 +17485,13 @@
         <v>844</v>
       </c>
       <c r="D121" t="s">
-        <v>1453</v>
+        <v>1475</v>
       </c>
       <c r="E121" t="s">
         <v>112</v>
       </c>
       <c r="F121" t="s">
-        <v>1433</v>
+        <v>1455</v>
       </c>
       <c r="G121" t="s">
         <v>845</v>
@@ -17304,13 +17508,13 @@
         <v>852</v>
       </c>
       <c r="D122" t="s">
-        <v>1453</v>
+        <v>1475</v>
       </c>
       <c r="E122" t="s">
         <v>26</v>
       </c>
       <c r="F122" t="s">
-        <v>1433</v>
+        <v>1455</v>
       </c>
       <c r="G122" t="s">
         <v>853</v>
@@ -17327,13 +17531,13 @@
         <v>860</v>
       </c>
       <c r="D123" t="s">
-        <v>1453</v>
+        <v>1475</v>
       </c>
       <c r="E123" t="s">
         <v>112</v>
       </c>
       <c r="F123" t="s">
-        <v>1433</v>
+        <v>1455</v>
       </c>
       <c r="G123" t="s">
         <v>861</v>
@@ -17350,13 +17554,13 @@
         <v>868</v>
       </c>
       <c r="D124" t="s">
-        <v>1453</v>
+        <v>1475</v>
       </c>
       <c r="E124" t="s">
         <v>112</v>
       </c>
       <c r="F124" t="s">
-        <v>1433</v>
+        <v>1455</v>
       </c>
       <c r="G124" t="s">
         <v>869</v>
@@ -17373,13 +17577,13 @@
         <v>876</v>
       </c>
       <c r="D125" t="s">
-        <v>1453</v>
+        <v>1475</v>
       </c>
       <c r="E125" t="s">
         <v>112</v>
       </c>
       <c r="F125" t="s">
-        <v>1433</v>
+        <v>1455</v>
       </c>
       <c r="G125" t="s">
         <v>878</v>
@@ -17396,13 +17600,13 @@
         <v>885</v>
       </c>
       <c r="D126" t="s">
-        <v>1453</v>
+        <v>1475</v>
       </c>
       <c r="E126" t="s">
         <v>112</v>
       </c>
       <c r="F126" t="s">
-        <v>1433</v>
+        <v>1455</v>
       </c>
       <c r="G126" t="s">
         <v>886</v>
@@ -17419,13 +17623,13 @@
         <v>893</v>
       </c>
       <c r="D127" t="s">
-        <v>1453</v>
+        <v>1475</v>
       </c>
       <c r="E127" t="s">
         <v>112</v>
       </c>
       <c r="F127" t="s">
-        <v>1433</v>
+        <v>1455</v>
       </c>
       <c r="G127" t="s">
         <v>894</v>
@@ -17442,13 +17646,13 @@
         <v>901</v>
       </c>
       <c r="D128" t="s">
-        <v>1453</v>
+        <v>1475</v>
       </c>
       <c r="E128" t="s">
         <v>453</v>
       </c>
       <c r="F128" t="s">
-        <v>1433</v>
+        <v>1455</v>
       </c>
       <c r="G128" t="s">
         <v>902</v>
@@ -17465,13 +17669,13 @@
         <v>909</v>
       </c>
       <c r="D129" t="s">
-        <v>1453</v>
+        <v>1475</v>
       </c>
       <c r="E129" t="s">
         <v>112</v>
       </c>
       <c r="F129" t="s">
-        <v>1433</v>
+        <v>1455</v>
       </c>
       <c r="G129" t="s">
         <v>910</v>
@@ -17488,13 +17692,13 @@
         <v>916</v>
       </c>
       <c r="D130" t="s">
-        <v>1453</v>
+        <v>1475</v>
       </c>
       <c r="E130" t="s">
         <v>112</v>
       </c>
       <c r="F130" t="s">
-        <v>1433</v>
+        <v>1455</v>
       </c>
       <c r="G130" t="s">
         <v>917</v>
@@ -17511,13 +17715,13 @@
         <v>926</v>
       </c>
       <c r="D131" t="s">
-        <v>1453</v>
+        <v>1475</v>
       </c>
       <c r="E131" t="s">
         <v>112</v>
       </c>
       <c r="F131" t="s">
-        <v>1433</v>
+        <v>1455</v>
       </c>
       <c r="G131" t="s">
         <v>927</v>
@@ -17534,13 +17738,13 @@
         <v>934</v>
       </c>
       <c r="D132" t="s">
-        <v>1453</v>
+        <v>1475</v>
       </c>
       <c r="E132" t="s">
         <v>112</v>
       </c>
       <c r="F132" t="s">
-        <v>1433</v>
+        <v>1455</v>
       </c>
       <c r="G132" t="s">
         <v>935</v>
@@ -17557,13 +17761,13 @@
         <v>942</v>
       </c>
       <c r="D133" t="s">
-        <v>1453</v>
+        <v>1475</v>
       </c>
       <c r="E133" t="s">
         <v>112</v>
       </c>
       <c r="F133" t="s">
-        <v>1433</v>
+        <v>1455</v>
       </c>
       <c r="G133" t="s">
         <v>943</v>
@@ -17580,13 +17784,13 @@
         <v>950</v>
       </c>
       <c r="D134" t="s">
-        <v>1453</v>
+        <v>1475</v>
       </c>
       <c r="E134" t="s">
         <v>112</v>
       </c>
       <c r="F134" t="s">
-        <v>1433</v>
+        <v>1455</v>
       </c>
       <c r="G134" t="s">
         <v>951</v>
@@ -17603,13 +17807,13 @@
         <v>958</v>
       </c>
       <c r="D135" t="s">
-        <v>1453</v>
+        <v>1475</v>
       </c>
       <c r="E135" t="s">
         <v>112</v>
       </c>
       <c r="F135" t="s">
-        <v>1433</v>
+        <v>1455</v>
       </c>
       <c r="G135" t="s">
         <v>960</v>
@@ -17626,13 +17830,13 @@
         <v>967</v>
       </c>
       <c r="D136" t="s">
-        <v>1453</v>
+        <v>1475</v>
       </c>
       <c r="E136" t="s">
         <v>112</v>
       </c>
       <c r="F136" t="s">
-        <v>1433</v>
+        <v>1455</v>
       </c>
       <c r="G136" t="s">
         <v>968</v>
@@ -17649,13 +17853,13 @@
         <v>974</v>
       </c>
       <c r="D137" t="s">
-        <v>1453</v>
+        <v>1475</v>
       </c>
       <c r="E137" t="s">
         <v>112</v>
       </c>
       <c r="F137" t="s">
-        <v>1433</v>
+        <v>1455</v>
       </c>
       <c r="G137" t="s">
         <v>975</v>
@@ -17672,13 +17876,13 @@
         <v>981</v>
       </c>
       <c r="D138" t="s">
-        <v>1453</v>
+        <v>1475</v>
       </c>
       <c r="E138" t="s">
         <v>112</v>
       </c>
       <c r="F138" t="s">
-        <v>1433</v>
+        <v>1455</v>
       </c>
       <c r="G138" t="s">
         <v>982</v>
@@ -17695,13 +17899,13 @@
         <v>989</v>
       </c>
       <c r="D139" t="s">
-        <v>1453</v>
+        <v>1475</v>
       </c>
       <c r="E139" t="s">
         <v>112</v>
       </c>
       <c r="F139" t="s">
-        <v>1433</v>
+        <v>1455</v>
       </c>
       <c r="G139" t="s">
         <v>990</v>
@@ -17718,13 +17922,13 @@
         <v>997</v>
       </c>
       <c r="D140" t="s">
-        <v>1453</v>
+        <v>1475</v>
       </c>
       <c r="E140" t="s">
         <v>112</v>
       </c>
       <c r="F140" t="s">
-        <v>1433</v>
+        <v>1455</v>
       </c>
       <c r="G140" t="s">
         <v>998</v>
@@ -17741,13 +17945,13 @@
         <v>1006</v>
       </c>
       <c r="D141" t="s">
-        <v>1453</v>
+        <v>1475</v>
       </c>
       <c r="E141" t="s">
         <v>112</v>
       </c>
       <c r="F141" t="s">
-        <v>1433</v>
+        <v>1455</v>
       </c>
       <c r="G141" t="s">
         <v>1007</v>
@@ -17764,13 +17968,13 @@
         <v>1014</v>
       </c>
       <c r="D142" t="s">
-        <v>1453</v>
+        <v>1475</v>
       </c>
       <c r="E142" t="s">
         <v>112</v>
       </c>
       <c r="F142" t="s">
-        <v>1433</v>
+        <v>1455</v>
       </c>
       <c r="G142" t="s">
         <v>1015</v>
@@ -17787,13 +17991,13 @@
         <v>1021</v>
       </c>
       <c r="D143" t="s">
-        <v>1453</v>
+        <v>1475</v>
       </c>
       <c r="E143" t="s">
         <v>453</v>
       </c>
       <c r="F143" t="s">
-        <v>1433</v>
+        <v>1455</v>
       </c>
       <c r="G143" t="s">
         <v>1022</v>
@@ -17810,13 +18014,13 @@
         <v>1029</v>
       </c>
       <c r="D144" t="s">
-        <v>1453</v>
+        <v>1475</v>
       </c>
       <c r="E144" t="s">
         <v>112</v>
       </c>
       <c r="F144" t="s">
-        <v>1433</v>
+        <v>1455</v>
       </c>
       <c r="G144" t="s">
         <v>1031</v>
@@ -17833,13 +18037,13 @@
         <v>1037</v>
       </c>
       <c r="D145" t="s">
-        <v>1453</v>
+        <v>1475</v>
       </c>
       <c r="E145" t="s">
         <v>112</v>
       </c>
       <c r="F145" t="s">
-        <v>1433</v>
+        <v>1455</v>
       </c>
       <c r="G145" t="s">
         <v>1038</v>
@@ -17856,13 +18060,13 @@
         <v>1045</v>
       </c>
       <c r="D146" t="s">
-        <v>1453</v>
+        <v>1475</v>
       </c>
       <c r="E146" t="s">
         <v>112</v>
       </c>
       <c r="F146" t="s">
-        <v>1433</v>
+        <v>1455</v>
       </c>
       <c r="G146" t="s">
         <v>1046</v>
@@ -17879,13 +18083,13 @@
         <v>1053</v>
       </c>
       <c r="D147" t="s">
-        <v>1453</v>
+        <v>1475</v>
       </c>
       <c r="E147" t="s">
         <v>112</v>
       </c>
       <c r="F147" t="s">
-        <v>1433</v>
+        <v>1455</v>
       </c>
       <c r="G147" t="s">
         <v>1055</v>
@@ -17902,13 +18106,13 @@
         <v>1061</v>
       </c>
       <c r="D148" t="s">
-        <v>1453</v>
+        <v>1475</v>
       </c>
       <c r="E148" t="s">
         <v>112</v>
       </c>
       <c r="F148" t="s">
-        <v>1433</v>
+        <v>1455</v>
       </c>
       <c r="G148" t="s">
         <v>1062</v>
@@ -17925,13 +18129,13 @@
         <v>1068</v>
       </c>
       <c r="D149" t="s">
-        <v>1453</v>
+        <v>1475</v>
       </c>
       <c r="E149" t="s">
         <v>95</v>
       </c>
       <c r="F149" t="s">
-        <v>1433</v>
+        <v>1455</v>
       </c>
       <c r="G149" t="s">
         <v>1069</v>
@@ -17948,13 +18152,13 @@
         <v>1076</v>
       </c>
       <c r="D150" t="s">
-        <v>1453</v>
+        <v>1475</v>
       </c>
       <c r="E150" t="s">
         <v>112</v>
       </c>
       <c r="F150" t="s">
-        <v>1433</v>
+        <v>1455</v>
       </c>
       <c r="G150" t="s">
         <v>1078</v>
@@ -17971,13 +18175,13 @@
         <v>1085</v>
       </c>
       <c r="D151" t="s">
-        <v>1453</v>
+        <v>1475</v>
       </c>
       <c r="E151" t="s">
         <v>95</v>
       </c>
       <c r="F151" t="s">
-        <v>1433</v>
+        <v>1455</v>
       </c>
       <c r="G151" t="s">
         <v>1086</v>
@@ -17994,13 +18198,13 @@
         <v>1093</v>
       </c>
       <c r="D152" t="s">
-        <v>1453</v>
+        <v>1475</v>
       </c>
       <c r="E152" t="s">
         <v>112</v>
       </c>
       <c r="F152" t="s">
-        <v>1433</v>
+        <v>1455</v>
       </c>
       <c r="G152" t="s">
         <v>1094</v>
@@ -18017,13 +18221,13 @@
         <v>1102</v>
       </c>
       <c r="D153" t="s">
-        <v>1453</v>
+        <v>1475</v>
       </c>
       <c r="E153" t="s">
         <v>112</v>
       </c>
       <c r="F153" t="s">
-        <v>1433</v>
+        <v>1455</v>
       </c>
       <c r="G153" t="s">
         <v>1103</v>
@@ -18040,13 +18244,13 @@
         <v>1109</v>
       </c>
       <c r="D154" t="s">
-        <v>1453</v>
+        <v>1475</v>
       </c>
       <c r="E154" t="s">
         <v>453</v>
       </c>
       <c r="F154" t="s">
-        <v>1433</v>
+        <v>1455</v>
       </c>
       <c r="G154" t="s">
         <v>1110</v>
@@ -18063,13 +18267,13 @@
         <v>1117</v>
       </c>
       <c r="D155" t="s">
-        <v>1453</v>
+        <v>1475</v>
       </c>
       <c r="E155" t="s">
         <v>112</v>
       </c>
       <c r="F155" t="s">
-        <v>1433</v>
+        <v>1455</v>
       </c>
       <c r="G155" t="s">
         <v>1118</v>
@@ -18086,13 +18290,13 @@
         <v>1124</v>
       </c>
       <c r="D156" t="s">
-        <v>1453</v>
+        <v>1475</v>
       </c>
       <c r="E156" t="s">
         <v>95</v>
       </c>
       <c r="F156" t="s">
-        <v>1433</v>
+        <v>1455</v>
       </c>
       <c r="G156" t="s">
         <v>1125</v>
@@ -18109,16 +18313,62 @@
         <v>1132</v>
       </c>
       <c r="D157" t="s">
-        <v>1453</v>
+        <v>1475</v>
       </c>
       <c r="E157" t="s">
         <v>112</v>
       </c>
       <c r="F157" t="s">
-        <v>1433</v>
+        <v>1455</v>
       </c>
       <c r="G157" t="s">
         <v>1133</v>
+      </c>
+    </row>
+    <row r="158" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A158" t="s">
+        <v>27</v>
+      </c>
+      <c r="B158" t="s">
+        <v>1141</v>
+      </c>
+      <c r="C158" t="s">
+        <v>1139</v>
+      </c>
+      <c r="D158" t="s">
+        <v>1475</v>
+      </c>
+      <c r="E158" t="s">
+        <v>112</v>
+      </c>
+      <c r="F158" t="s">
+        <v>1455</v>
+      </c>
+      <c r="G158" t="s">
+        <v>1140</v>
+      </c>
+    </row>
+    <row r="159" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A159" t="s">
+        <v>27</v>
+      </c>
+      <c r="B159" t="s">
+        <v>1141</v>
+      </c>
+      <c r="C159" t="s">
+        <v>1148</v>
+      </c>
+      <c r="D159" t="s">
+        <v>1475</v>
+      </c>
+      <c r="E159" t="s">
+        <v>112</v>
+      </c>
+      <c r="F159" t="s">
+        <v>1455</v>
+      </c>
+      <c r="G159" t="s">
+        <v>1149</v>
       </c>
     </row>
   </sheetData>
@@ -18132,7 +18382,7 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>1454</v>
+        <v>1476</v>
       </c>
       <c r="B1"/>
       <c r="C1"/>
@@ -18140,7 +18390,7 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1455</v>
+        <v>1477</v>
       </c>
       <c r="B2"/>
       <c r="C2"/>
@@ -18151,181 +18401,181 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>1456</v>
+        <v>1478</v>
       </c>
       <c r="C3" t="s">
-        <v>1457</v>
+        <v>1479</v>
       </c>
       <c r="D3" t="s">
-        <v>1458</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1459</v>
+        <v>1481</v>
       </c>
       <c r="B4" t="s">
-        <v>1460</v>
+        <v>1482</v>
       </c>
       <c r="C4" t="s">
-        <v>1461</v>
+        <v>1483</v>
       </c>
       <c r="D4" t="s">
-        <v>1462</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1463</v>
+        <v>1485</v>
       </c>
       <c r="B5" t="s">
-        <v>1460</v>
+        <v>1482</v>
       </c>
       <c r="C5" t="s">
-        <v>1464</v>
+        <v>1486</v>
       </c>
       <c r="D5" t="s">
-        <v>1465</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>1466</v>
+        <v>1488</v>
       </c>
       <c r="B6" t="s">
-        <v>1460</v>
+        <v>1482</v>
       </c>
       <c r="C6" t="s">
-        <v>1467</v>
+        <v>1489</v>
       </c>
       <c r="D6" t="s">
-        <v>1468</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>1469</v>
+        <v>1491</v>
       </c>
       <c r="B7" t="s">
-        <v>1460</v>
+        <v>1482</v>
       </c>
       <c r="C7" t="s">
-        <v>1470</v>
+        <v>1492</v>
       </c>
       <c r="D7" t="s">
-        <v>1471</v>
+        <v>1493</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>1472</v>
+        <v>1494</v>
       </c>
       <c r="B8" t="s">
-        <v>1460</v>
+        <v>1482</v>
       </c>
       <c r="C8" t="s">
-        <v>1473</v>
+        <v>1495</v>
       </c>
       <c r="D8" t="s">
-        <v>1474</v>
+        <v>1496</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>1475</v>
+        <v>1497</v>
       </c>
       <c r="B9" t="s">
-        <v>1476</v>
+        <v>1498</v>
       </c>
       <c r="C9" t="s">
-        <v>1477</v>
+        <v>1499</v>
       </c>
       <c r="D9" t="s">
-        <v>1478</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>1479</v>
+        <v>1501</v>
       </c>
       <c r="B10" t="s">
-        <v>1476</v>
+        <v>1498</v>
       </c>
       <c r="C10" t="s">
-        <v>1480</v>
+        <v>1502</v>
       </c>
       <c r="D10" t="s">
-        <v>1481</v>
+        <v>1503</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>1482</v>
+        <v>1504</v>
       </c>
       <c r="B11" t="s">
-        <v>1476</v>
+        <v>1498</v>
       </c>
       <c r="C11" t="s">
-        <v>1483</v>
+        <v>1505</v>
       </c>
       <c r="D11" t="s">
-        <v>1484</v>
+        <v>1506</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>1485</v>
+        <v>1507</v>
       </c>
       <c r="B12" t="s">
-        <v>1486</v>
+        <v>1508</v>
       </c>
       <c r="C12" t="s">
-        <v>1487</v>
+        <v>1509</v>
       </c>
       <c r="D12" t="s">
-        <v>1488</v>
+        <v>1510</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>1489</v>
+        <v>1511</v>
       </c>
       <c r="B13" t="s">
-        <v>1486</v>
+        <v>1508</v>
       </c>
       <c r="C13" t="s">
-        <v>1490</v>
+        <v>1512</v>
       </c>
       <c r="D13" t="s">
-        <v>1491</v>
+        <v>1513</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>1492</v>
+        <v>1514</v>
       </c>
       <c r="B14" t="s">
         <v>877</v>
       </c>
       <c r="C14" t="s">
-        <v>1493</v>
+        <v>1515</v>
       </c>
       <c r="D14" t="s">
-        <v>1494</v>
+        <v>1516</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>1495</v>
+        <v>1517</v>
       </c>
       <c r="B15" t="s">
         <v>877</v>
       </c>
       <c r="C15" t="s">
-        <v>1496</v>
+        <v>1518</v>
       </c>
       <c r="D15" t="s">
-        <v>1497</v>
+        <v>1519</v>
       </c>
     </row>
   </sheetData>
@@ -18344,7 +18594,7 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>1498</v>
+        <v>1520</v>
       </c>
       <c r="B1"/>
       <c r="C1"/>
@@ -18352,133 +18602,133 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>1499</v>
+        <v>1521</v>
       </c>
       <c r="B3" t="s">
-        <v>1500</v>
+        <v>1522</v>
       </c>
       <c r="C3" t="s">
-        <v>1501</v>
+        <v>1523</v>
       </c>
       <c r="D3" t="s">
-        <v>1502</v>
+        <v>1524</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1179</v>
+        <v>1196</v>
       </c>
       <c r="B4" t="s">
-        <v>1503</v>
+        <v>1525</v>
       </c>
       <c r="C4" t="s">
-        <v>1504</v>
+        <v>1526</v>
       </c>
       <c r="D4" t="s">
-        <v>1505</v>
+        <v>1527</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1184</v>
+        <v>1201</v>
       </c>
       <c r="B5" t="s">
-        <v>1506</v>
+        <v>1528</v>
       </c>
       <c r="C5" t="s">
-        <v>1507</v>
+        <v>1529</v>
       </c>
       <c r="D5" t="s">
-        <v>1508</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>1188</v>
+        <v>1205</v>
       </c>
       <c r="B6" t="s">
-        <v>1509</v>
+        <v>1531</v>
       </c>
       <c r="C6" t="s">
-        <v>1510</v>
+        <v>1532</v>
       </c>
       <c r="D6" t="s">
-        <v>1511</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>1192</v>
+        <v>1209</v>
       </c>
       <c r="B7" t="s">
-        <v>1512</v>
+        <v>1534</v>
       </c>
       <c r="C7" t="s">
-        <v>1513</v>
+        <v>1535</v>
       </c>
       <c r="D7" t="s">
-        <v>1514</v>
+        <v>1536</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>1196</v>
+        <v>1213</v>
       </c>
       <c r="B8" t="s">
-        <v>1515</v>
+        <v>1537</v>
       </c>
       <c r="C8" t="s">
-        <v>1516</v>
+        <v>1538</v>
       </c>
       <c r="D8" t="s">
-        <v>1517</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>1200</v>
+        <v>1217</v>
       </c>
       <c r="B9" t="s">
-        <v>1518</v>
+        <v>1540</v>
       </c>
       <c r="C9" t="s">
-        <v>1519</v>
+        <v>1541</v>
       </c>
       <c r="D9" t="s">
-        <v>1520</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>1204</v>
+        <v>1221</v>
       </c>
       <c r="B10" t="s">
-        <v>1521</v>
+        <v>1543</v>
       </c>
       <c r="C10" t="s">
-        <v>1522</v>
+        <v>1544</v>
       </c>
       <c r="D10" t="s">
-        <v>1523</v>
+        <v>1545</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>1208</v>
+        <v>1225</v>
       </c>
       <c r="B11" t="s">
-        <v>1524</v>
+        <v>1546</v>
       </c>
       <c r="C11" t="s">
-        <v>1525</v>
+        <v>1547</v>
       </c>
       <c r="D11" t="s">
-        <v>1526</v>
+        <v>1548</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>1527</v>
+        <v>1549</v>
       </c>
       <c r="B13"/>
       <c r="C13"/>
@@ -18486,72 +18736,72 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>1528</v>
+        <v>1550</v>
       </c>
       <c r="B14" t="s">
         <v>28</v>
       </c>
       <c r="C14" t="s">
-        <v>1529</v>
+        <v>1551</v>
       </c>
       <c r="D14" t="s">
-        <v>1530</v>
+        <v>1552</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>1531</v>
+        <v>1553</v>
       </c>
       <c r="B15" t="s">
         <v>29</v>
       </c>
       <c r="C15" t="s">
-        <v>1532</v>
+        <v>1554</v>
       </c>
       <c r="D15" t="s">
-        <v>1533</v>
+        <v>1555</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>1534</v>
+        <v>1556</v>
       </c>
       <c r="B16" t="s">
         <v>29</v>
       </c>
       <c r="C16" t="s">
-        <v>1535</v>
+        <v>1557</v>
       </c>
       <c r="D16" t="s">
-        <v>1536</v>
+        <v>1558</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>1537</v>
+        <v>1559</v>
       </c>
       <c r="B17" t="s">
         <v>29</v>
       </c>
       <c r="C17" t="s">
-        <v>1538</v>
+        <v>1560</v>
       </c>
       <c r="D17" t="s">
-        <v>1539</v>
+        <v>1561</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>1540</v>
+        <v>1562</v>
       </c>
       <c r="B18" t="s">
-        <v>1541</v>
+        <v>1563</v>
       </c>
       <c r="C18" t="s">
-        <v>1542</v>
+        <v>1564</v>
       </c>
       <c r="D18" t="s">
-        <v>1543</v>
+        <v>1565</v>
       </c>
     </row>
   </sheetData>
@@ -18570,7 +18820,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>1544</v>
+        <v>1566</v>
       </c>
       <c r="B1"/>
       <c r="C1"/>
@@ -18580,7 +18830,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1545</v>
+        <v>1567</v>
       </c>
       <c r="B2"/>
       <c r="C2"/>
@@ -18590,99 +18840,99 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1546</v>
+        <v>1568</v>
       </c>
       <c r="B4" t="s">
-        <v>1547</v>
+        <v>1569</v>
       </c>
       <c r="C4" t="s">
-        <v>1548</v>
+        <v>1570</v>
       </c>
       <c r="D4" t="s">
-        <v>1549</v>
+        <v>1571</v>
       </c>
       <c r="E4" t="s">
-        <v>1550</v>
+        <v>1572</v>
       </c>
       <c r="F4" t="s">
-        <v>1551</v>
+        <v>1573</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1552</v>
+        <v>1574</v>
       </c>
       <c r="B5" t="s">
-        <v>1553</v>
+        <v>1575</v>
       </c>
       <c r="C5" t="s">
-        <v>1554</v>
+        <v>1576</v>
       </c>
       <c r="D5" t="s">
-        <v>1555</v>
+        <v>1577</v>
       </c>
       <c r="E5" t="s">
-        <v>1556</v>
+        <v>1578</v>
       </c>
       <c r="F5" t="s">
-        <v>1557</v>
+        <v>1579</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>1558</v>
+        <v>1580</v>
       </c>
       <c r="B6" t="s">
-        <v>1559</v>
+        <v>1581</v>
       </c>
       <c r="C6" t="s">
-        <v>1560</v>
+        <v>1582</v>
       </c>
       <c r="D6" t="s">
-        <v>1561</v>
+        <v>1583</v>
       </c>
       <c r="E6" t="s">
-        <v>1562</v>
+        <v>1584</v>
       </c>
       <c r="F6" t="s">
-        <v>1563</v>
+        <v>1585</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>1564</v>
+        <v>1586</v>
       </c>
       <c r="B7" t="s">
-        <v>1559</v>
+        <v>1581</v>
       </c>
       <c r="C7" t="s">
-        <v>1565</v>
+        <v>1587</v>
       </c>
       <c r="D7" t="s">
-        <v>1566</v>
+        <v>1588</v>
       </c>
       <c r="E7" t="s">
-        <v>1567</v>
+        <v>1589</v>
       </c>
       <c r="F7" t="s">
-        <v>1568</v>
+        <v>1590</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>1569</v>
+        <v>1591</v>
       </c>
       <c r="B8" t="s">
-        <v>1570</v>
+        <v>1592</v>
       </c>
       <c r="C8" t="s">
-        <v>1571</v>
+        <v>1593</v>
       </c>
       <c r="D8" t="s">
-        <v>1572</v>
+        <v>1594</v>
       </c>
       <c r="E8" t="s">
-        <v>1573</v>
+        <v>1595</v>
       </c>
       <c r="F8" t="s">
         <v>629</v>
@@ -18690,19 +18940,19 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>1574</v>
+        <v>1596</v>
       </c>
       <c r="B9" t="s">
-        <v>1575</v>
+        <v>1597</v>
       </c>
       <c r="C9" t="s">
-        <v>1576</v>
+        <v>1598</v>
       </c>
       <c r="D9" t="s">
-        <v>1577</v>
+        <v>1599</v>
       </c>
       <c r="E9" t="s">
-        <v>1578</v>
+        <v>1600</v>
       </c>
       <c r="F9" t="s">
         <v>369</v>
@@ -18710,39 +18960,39 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>1579</v>
+        <v>1601</v>
       </c>
       <c r="B10" t="s">
-        <v>1580</v>
+        <v>1602</v>
       </c>
       <c r="C10" t="s">
-        <v>1581</v>
+        <v>1603</v>
       </c>
       <c r="D10" t="s">
-        <v>1582</v>
+        <v>1604</v>
       </c>
       <c r="E10" t="s">
-        <v>1583</v>
+        <v>1605</v>
       </c>
       <c r="F10" t="s">
-        <v>1584</v>
+        <v>1606</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>1585</v>
+        <v>1607</v>
       </c>
       <c r="B11" t="s">
-        <v>1586</v>
+        <v>1608</v>
       </c>
       <c r="C11" t="s">
-        <v>1587</v>
+        <v>1609</v>
       </c>
       <c r="D11" t="s">
-        <v>1588</v>
+        <v>1610</v>
       </c>
       <c r="E11" t="s">
-        <v>1589</v>
+        <v>1611</v>
       </c>
       <c r="F11" t="s">
         <v>47</v>
@@ -18750,99 +19000,99 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>1590</v>
+        <v>1612</v>
       </c>
       <c r="B12" t="s">
-        <v>1591</v>
+        <v>1613</v>
       </c>
       <c r="C12" t="s">
-        <v>1592</v>
+        <v>1614</v>
       </c>
       <c r="D12" t="s">
-        <v>1593</v>
+        <v>1615</v>
       </c>
       <c r="E12" t="s">
-        <v>1594</v>
+        <v>1616</v>
       </c>
       <c r="F12" t="s">
-        <v>1595</v>
+        <v>1617</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>1596</v>
+        <v>1618</v>
       </c>
       <c r="B13" t="s">
-        <v>1597</v>
+        <v>1619</v>
       </c>
       <c r="C13" t="s">
-        <v>1598</v>
+        <v>1620</v>
       </c>
       <c r="D13" t="s">
-        <v>1599</v>
+        <v>1621</v>
       </c>
       <c r="E13" t="s">
-        <v>1600</v>
+        <v>1622</v>
       </c>
       <c r="F13" t="s">
-        <v>1601</v>
+        <v>1623</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>1602</v>
+        <v>1624</v>
       </c>
       <c r="B14" t="s">
-        <v>1603</v>
+        <v>1625</v>
       </c>
       <c r="C14" t="s">
-        <v>1604</v>
+        <v>1626</v>
       </c>
       <c r="D14" t="s">
-        <v>1605</v>
+        <v>1627</v>
       </c>
       <c r="E14" t="s">
-        <v>1606</v>
+        <v>1628</v>
       </c>
       <c r="F14" t="s">
-        <v>1607</v>
+        <v>1629</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>1608</v>
+        <v>1630</v>
       </c>
       <c r="B15" t="s">
-        <v>1609</v>
+        <v>1631</v>
       </c>
       <c r="C15" t="s">
-        <v>1610</v>
+        <v>1632</v>
       </c>
       <c r="D15" t="s">
-        <v>1611</v>
+        <v>1633</v>
       </c>
       <c r="E15" t="s">
-        <v>1612</v>
+        <v>1634</v>
       </c>
       <c r="F15" t="s">
-        <v>1613</v>
+        <v>1635</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>1614</v>
+        <v>1636</v>
       </c>
       <c r="B16" t="s">
-        <v>1615</v>
+        <v>1637</v>
       </c>
       <c r="C16" t="s">
-        <v>1616</v>
+        <v>1638</v>
       </c>
       <c r="D16" t="s">
-        <v>1617</v>
+        <v>1639</v>
       </c>
       <c r="E16" t="s">
-        <v>1618</v>
+        <v>1640</v>
       </c>
       <c r="F16" t="s">
         <v>207</v>
@@ -18850,19 +19100,19 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>1619</v>
+        <v>1641</v>
       </c>
       <c r="B17" t="s">
-        <v>1620</v>
+        <v>1642</v>
       </c>
       <c r="C17" t="s">
-        <v>1621</v>
+        <v>1643</v>
       </c>
       <c r="D17" t="s">
-        <v>1622</v>
+        <v>1644</v>
       </c>
       <c r="E17" t="s">
-        <v>1623</v>
+        <v>1645</v>
       </c>
       <c r="F17" t="s">
         <v>378</v>
@@ -18884,7 +19134,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>1624</v>
+        <v>1646</v>
       </c>
       <c r="B1"/>
       <c r="C1"/>
@@ -18894,7 +19144,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1625</v>
+        <v>1647</v>
       </c>
       <c r="B2"/>
       <c r="C2"/>
@@ -18904,162 +19154,162 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1626</v>
+        <v>1648</v>
       </c>
       <c r="B4" t="s">
-        <v>1524</v>
+        <v>1546</v>
       </c>
       <c r="C4" t="s">
-        <v>1627</v>
+        <v>1649</v>
       </c>
       <c r="D4" t="s">
-        <v>1628</v>
+        <v>1650</v>
       </c>
       <c r="E4" t="s">
-        <v>1176</v>
+        <v>1193</v>
       </c>
       <c r="F4" t="s">
-        <v>1629</v>
+        <v>1651</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1179</v>
+        <v>1196</v>
       </c>
       <c r="B5" t="s">
-        <v>1630</v>
+        <v>1652</v>
       </c>
       <c r="C5" t="s">
-        <v>1631</v>
+        <v>1653</v>
       </c>
       <c r="D5" t="s">
-        <v>1632</v>
+        <v>1654</v>
       </c>
       <c r="E5" t="s">
-        <v>1633</v>
+        <v>1655</v>
       </c>
       <c r="F5" t="s">
-        <v>1634</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>1184</v>
+        <v>1201</v>
       </c>
       <c r="B6" t="s">
-        <v>1635</v>
+        <v>1657</v>
       </c>
       <c r="C6" t="s">
-        <v>1636</v>
+        <v>1658</v>
       </c>
       <c r="D6" t="s">
-        <v>1637</v>
+        <v>1659</v>
       </c>
       <c r="E6" t="s">
-        <v>1638</v>
+        <v>1660</v>
       </c>
       <c r="F6" t="s">
-        <v>1634</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>1188</v>
+        <v>1205</v>
       </c>
       <c r="B7" t="s">
-        <v>1639</v>
+        <v>1661</v>
       </c>
       <c r="C7" t="s">
-        <v>1640</v>
+        <v>1662</v>
       </c>
       <c r="D7" t="s">
-        <v>1641</v>
+        <v>1663</v>
       </c>
       <c r="E7" t="s">
-        <v>1642</v>
+        <v>1664</v>
       </c>
       <c r="F7" t="s">
-        <v>1634</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>1192</v>
+        <v>1209</v>
       </c>
       <c r="B8" t="s">
-        <v>1643</v>
+        <v>1665</v>
       </c>
       <c r="C8" t="s">
-        <v>1644</v>
+        <v>1666</v>
       </c>
       <c r="D8" t="s">
-        <v>1645</v>
+        <v>1667</v>
       </c>
       <c r="E8" t="s">
-        <v>1646</v>
+        <v>1668</v>
       </c>
       <c r="F8" t="s">
-        <v>1634</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>1196</v>
+        <v>1213</v>
       </c>
       <c r="B9" t="s">
-        <v>1647</v>
+        <v>1669</v>
       </c>
       <c r="C9" t="s">
-        <v>1648</v>
+        <v>1670</v>
       </c>
       <c r="D9" t="s">
-        <v>1649</v>
+        <v>1671</v>
       </c>
       <c r="E9" t="s">
         <v>877</v>
       </c>
       <c r="F9" t="s">
-        <v>1650</v>
+        <v>1672</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>1200</v>
+        <v>1217</v>
       </c>
       <c r="B10" t="s">
-        <v>1651</v>
+        <v>1673</v>
       </c>
       <c r="C10" t="s">
-        <v>1652</v>
+        <v>1674</v>
       </c>
       <c r="D10" t="s">
-        <v>1653</v>
+        <v>1675</v>
       </c>
       <c r="E10" t="s">
-        <v>1654</v>
+        <v>1676</v>
       </c>
       <c r="F10" t="s">
-        <v>1650</v>
+        <v>1672</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>1204</v>
+        <v>1221</v>
       </c>
       <c r="B11" t="s">
-        <v>1655</v>
+        <v>1677</v>
       </c>
       <c r="C11" t="s">
-        <v>1656</v>
+        <v>1678</v>
       </c>
       <c r="D11" t="s">
-        <v>1657</v>
+        <v>1679</v>
       </c>
       <c r="E11" t="s">
-        <v>1658</v>
+        <v>1680</v>
       </c>
       <c r="F11" t="s">
-        <v>1659</v>
+        <v>1681</v>
       </c>
     </row>
   </sheetData>

--- a/audits/FORTLESS_MASTER_SECURITY_UI_BUG_TRACKER.xlsx
+++ b/audits/FORTLESS_MASTER_SECURITY_UI_BUG_TRACKER.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4290" uniqueCount="1682">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4478" uniqueCount="1738">
   <si>
     <t>FORTLESS   /   ENGINEERING FINDINGS REGISTER</t>
   </si>
@@ -3009,7 +3009,7 @@
     <t>Test: restore into a clean environment with the saved secret and verify TOTP login; without it, startup fails loudly.</t>
   </si>
   <si>
-    <t>[CONFIRMED_CODE] Source trace; CONFIG_DEPENDENT.</t>
+    <t>[CONFIRMED_CODE] Source trace; CONFIG_DEPENDENT. | Batch 7: the panel client keys (panel_client_keys) are encrypted with a key derived from the same SESSION_SECRET, see NEW-397.</t>
   </si>
   <si>
     <t>NEW-376</t>
@@ -3489,6 +3489,171 @@
     <t>[CONFIRMED_CODE] Source trace; defence-in-depth issue.</t>
   </si>
   <si>
+    <t>NEW-396</t>
+  </si>
+  <si>
+    <t>Panel access outlives Fortless authorization: remember-me login, no back-channel logout, and the panel password-reset page is live</t>
+  </si>
+  <si>
+    <t>d036b0f</t>
+  </si>
+  <si>
+    <t>panel-sso/FortlessSsoController.php:129-133; panel-sso/INSTALL.md (Known gaps); src/modules/provisioning/panel-link.ts:18-36</t>
+  </si>
+  <si>
+    <t>The callback calls Auth::guard('web')-&gt;login($user, true) (remember = true) and the panel keeps its own session; Fortless never revokes it when the Fortless session ends, MFA is reset, the member loses OWNER/TECH_ADMIN, or the account is LOCKED/FLAGGED_FRAUD. The panel user's email is the account owner's real email, and a read-only request to the live panel's /auth/password returned HTTP 200, so the owner's mailbox can set a panel password and sign in directly. INSTALL.md lists this as a known gap and says SSO also bypasses panel 2FA.</t>
+  </si>
+  <si>
+    <t>Someone who loses Fortless access (removed admin, locked or fraud-flagged account, reset MFA) can keep operating the servers through the panel, and a mailbox compromise bypasses Fortless MFA, step-up and account locks entirely.</t>
+  </si>
+  <si>
+    <t>Disable the panel password-reset and local login for customer users (or set an unknown password and block the route), shorten the panel session, do not use remember, and add a back-channel step that kills panel sessions or rotates the user when Fortless revokes access.</t>
+  </si>
+  <si>
+    <t>Test: after a Fortless member is demoted or the account is locked, the panel session and the stored client key stop working within a defined time; /auth/password cannot set a password for external_id fortless_acc_* users.</t>
+  </si>
+  <si>
+    <t>[CONFIRMED_CODE] Repo copy of the controller read; one unauthenticated GET to the live panel was used for the status code. The panel files deployed on the remote host were not readable from here, so drift from the repo copy is TEST_NEEDED.</t>
+  </si>
+  <si>
+    <t>NEW-397</t>
+  </si>
+  <si>
+    <t>Per-account panel API keys are not IP-bound unless an optional setting is present, and every mint revokes the previous key</t>
+  </si>
+  <si>
+    <t>panel-sso/FortlessKeyMintController.php:63-70; panel-sso/INSTALL.md section 5</t>
+  </si>
+  <si>
+    <t>createToken(self::MEMO, $ips ?: null) leaves the key unrestricted when FORTLESS_KEYMINT_ALLOWED_IPS is empty, and the endpoint itself is protected by the HMAC and a 30 per minute throttle only. Each mint deletes the earlier key with the same memo.</t>
+  </si>
+  <si>
+    <t>A leaked stored key (database plus SESSION_SECRET, see NEW-375 and the unencrypted backup in NEW-374) works from anywhere. Two Fortless processes minting at once revoke each other's key, producing intermittent 401s that the one-retry logic may not absorb.</t>
+  </si>
+  <si>
+    <t>Refuse to mint when the allowlist is empty, serialize minting per account, and add an expiry/rotation schedule.</t>
+  </si>
+  <si>
+    <t>Test: with an empty allowlist the endpoint returns 503; concurrent mints for one account yield one valid key.</t>
+  </si>
+  <si>
+    <t>[CONFIRMED_CODE] Source trace of the repo copy; panel configuration is CONFIG_DEPENDENT.</t>
+  </si>
+  <si>
+    <t>NEW-398</t>
+  </si>
+  <si>
+    <t>Secrets &amp; Credentials</t>
+  </si>
+  <si>
+    <t>Verification, reset and invitation tokens are stored in plaintext in email_outbox.payload_json and never scrubbed</t>
+  </si>
+  <si>
+    <t>src/modules/identity/auth.ts:236,294,359; src/modules/identity/teams.ts:135; src/modules/email/outbox.ts (queueEmail, processEmailOutbox)</t>
+  </si>
+  <si>
+    <t>The authentication tables keep only token digests, but the raw verifyUrl, resetUrl and inviteUrl are placed in the outbox payload. SENT rows keep payload_json indefinitely and nothing else in src/ deletes or redacts it; the rows are also included in backups.</t>
+  </si>
+  <si>
+    <t>Anyone with read access to the database, a backup (an unencrypted one exists, NEW-374) or a log of rows can use any still-valid reset, verification or invitation link. Digest-only storage is defeated.</t>
+  </si>
+  <si>
+    <t>Keep the token only in memory for the send, or encrypt/redact the payload as soon as the row is SENT or dead-lettered, and add retention.</t>
+  </si>
+  <si>
+    <t>Test: after delivery the payload contains no URL with a token; a dead-lettered security email is redacted on expiry.</t>
+  </si>
+  <si>
+    <t>NEW-399</t>
+  </si>
+  <si>
+    <t>Customer activity export returns every audit event of the account, including staff-internal reasons, to any workspace role</t>
+  </si>
+  <si>
+    <t>src/server.ts:1915-1945; src/modules/admin/read-model.ts:307-316</t>
+  </si>
+  <si>
+    <t>GET /api/v1/activity/export has requireAuth only and selects all audit_events for the account (limit 1000) with the raw metadata column. Staff actions such as account status changes (reason text), relinks and refunds write their reasons into the same table.</t>
+  </si>
+  <si>
+    <t>A VIEWER can download internal staff notes (for example a fraud-flag reason) and other members' actions as CSV.</t>
+  </si>
+  <si>
+    <t>Require a manager role, export only an allow-listed set of customer-facing actions, and strip staff metadata.</t>
+  </si>
+  <si>
+    <t>Test: VIEWER gets 403; an account flagged by staff does not expose the staff reason in the export.</t>
+  </si>
+  <si>
+    <t>NEW-400</t>
+  </si>
+  <si>
+    <t>CSV exports do not neutralize spreadsheet formulas</t>
+  </si>
+  <si>
+    <t>src/server.ts:1930-1938,2716-2728</t>
+  </si>
+  <si>
+    <t>escapeCsv and csvCell only double quotes. Values starting with =, +, - or @ (for example file names recorded in service.file.* metadata, ticket-derived fields, DNS record content) are written as-is in the activity and admin audit exports.</t>
+  </si>
+  <si>
+    <t>A customer who names a file =HYPERLINK(...) plants a formula that runs when staff or the customer opens the export in a spreadsheet.</t>
+  </si>
+  <si>
+    <t>Prefix such cells with a single quote or tab and test with the usual payloads.</t>
+  </si>
+  <si>
+    <t>Test: an audit row with metadata starting with = is exported with a neutralizing prefix.</t>
+  </si>
+  <si>
+    <t>NEW-401</t>
+  </si>
+  <si>
+    <t>Email templates are filled by replacing sample text in order, so customer-controlled values can be rewritten by later replacements</t>
+  </si>
+  <si>
+    <t>src/modules/email/outbox.ts:99-127,142-157</t>
+  </si>
+  <si>
+    <t>renderEmail replaces each sample string (for example "Frankfurt", "€3.90", "tkt_0912", "Alex Morgan") sequentially with the real value. A real value that contains a later sample string, such as a service or workspace name containing "Frankfurt", is replaced again; the order also decides which field wins if the same sample appears twice.</t>
+  </si>
+  <si>
+    <t>Wrong names, amounts or regions can appear in invoices and receipts emails, and a customer-controlled name can change other fields of an email sent from the Fortless domain.</t>
+  </si>
+  <si>
+    <t>Move to explicit placeholders for every canonical template field and render once, with a test per template.</t>
+  </si>
+  <si>
+    <t>Test: a workspace name equal to a later sample string is rendered verbatim.</t>
+  </si>
+  <si>
+    <t>[CONFIRMED_CODE] Source trace; no runtime reproduction.</t>
+  </si>
+  <si>
+    <t>NEW-402</t>
+  </si>
+  <si>
+    <t>Email outbox lease of 60 seconds can duplicate security emails when SMTP is slow</t>
+  </si>
+  <si>
+    <t>src/modules/email/outbox.ts:222-235,330-345,396-420</t>
+  </si>
+  <si>
+    <t>Leases expire after 60 s while an SMTP send may take longer; the lease-recovery step makes the row PENDING again and a second worker can send it. A periodic runner exists in src/index.ts, so the dispatch timer is only an accelerator.</t>
+  </si>
+  <si>
+    <t>Slow SMTP produces duplicate password-reset or verification emails.</t>
+  </si>
+  <si>
+    <t>Extend the lease while sending or set the lease above the SMTP timeout, and alert on the age of the oldest PENDING row.</t>
+  </si>
+  <si>
+    <t>Test: a send that takes longer than the lease is not delivered twice.</t>
+  </si>
+  <si>
+    <t>[CONFIRMED_CODE] Source trace; duplicate needs a send slower than the lease (TEST_NEEDED).</t>
+  </si>
+  <si>
     <t>FORTLESS   /   SECURITY &amp; PRODUCT QUALITY</t>
   </si>
   <si>
@@ -3507,10 +3672,10 @@
     <t>CLOSED &amp; TESTED</t>
   </si>
   <si>
-    <t>140</t>
-  </si>
-  <si>
-    <t>54</t>
+    <t>147</t>
+  </si>
+  <si>
+    <t>59</t>
   </si>
   <si>
     <t>58</t>
@@ -3537,16 +3702,16 @@
     <t>39</t>
   </si>
   <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>69</t>
+    <t>11</t>
+  </si>
+  <si>
+    <t>70</t>
   </si>
   <si>
     <t>4</t>
   </si>
   <si>
-    <t>32</t>
+    <t>38</t>
   </si>
   <si>
     <t>TESTED</t>
@@ -3657,7 +3822,7 @@
     <t>Every API permission and role</t>
   </si>
   <si>
-    <t>FTL-UI-201, SSO-01, NEW-322, NEW-328, NEW-359, NEW-376, NEW-378, NEW-379, NEW-387, NEW-390</t>
+    <t>FTL-UI-201, SSO-01, NEW-322, NEW-328, NEW-359, NEW-376, NEW-378, NEW-379, NEW-387, NEW-390, NEW-399</t>
   </si>
   <si>
     <t>05</t>
@@ -3732,9 +3897,6 @@
     <t>SQL/shell/path/template injection</t>
   </si>
   <si>
-    <t>11</t>
-  </si>
-  <si>
     <t>SSRF</t>
   </si>
   <si>
@@ -3747,13 +3909,10 @@
     <t>12</t>
   </si>
   <si>
-    <t>Secrets &amp; Credentials</t>
-  </si>
-  <si>
     <t>Provider keys, vault, rotation</t>
   </si>
   <si>
-    <t>NEW-313, SEC-02, NEW-323</t>
+    <t>NEW-313, SEC-02, NEW-323, NEW-398, NEW-397</t>
   </si>
   <si>
     <t>13</t>
@@ -3774,7 +3933,7 @@
     <t>OIDC callback, native reset, revoke</t>
   </si>
   <si>
-    <t>SSO-01, SSO-02, SSO-03, NEW-387</t>
+    <t>SSO-01, SSO-02, SSO-03, NEW-387, NEW-396, NEW-397</t>
   </si>
   <si>
     <t>Wings &amp; WebSockets</t>
@@ -3900,7 +4059,7 @@
     <t>Job leases, ordering, retry, dead letters</t>
   </si>
   <si>
-    <t>FTL-PROV-203, FTL-BILL-202, NEW-339, NEW-346, NEW-354, NEW-357</t>
+    <t>FTL-PROV-203, FTL-BILL-202, NEW-339, NEW-346, NEW-354, NEW-357, NEW-401, NEW-402</t>
   </si>
   <si>
     <t>27</t>
@@ -3945,7 +4104,7 @@
     <t>Audit integrity, alerts, events</t>
   </si>
   <si>
-    <t>SEC-09, NEW-322, NEW-380, NEW-391</t>
+    <t>SEC-09, NEW-322, NEW-380, NEW-391, NEW-400</t>
   </si>
   <si>
     <t>FORTLESS   /   COMMIT &amp; AUDIT HISTORY</t>
@@ -4177,6 +4336,15 @@
   </si>
   <si>
     <t>CORS, CSRF and cookie settings read in source; public response headers checked read-only. No implementation code changed.</t>
+  </si>
+  <si>
+    <t>2026-10-19 10:00</t>
+  </si>
+  <si>
+    <t>Independent audit batch 7: panel SSO and key-mint, email and notification paths, exports (NEW-396..NEW-402)</t>
+  </si>
+  <si>
+    <t>Panel SSO patch files, email outbox, notification and export paths read in source; one unauthenticated GET to the live panel for status only. No implementation code changed.</t>
   </si>
   <si>
     <t>FORTLESS   /   IMMUTABLE STATUS HISTORY</t>
@@ -5441,7 +5609,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:S143"/>
+  <dimension ref="A1:S150"/>
   <sheetFormatPr defaultRowHeight="0" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" customHeight="1"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
@@ -13600,6 +13768,419 @@
       </c>
       <c r="S143" t="s">
         <v>1155</v>
+      </c>
+    </row>
+    <row r="144" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>1156</v>
+      </c>
+      <c r="B144" t="s">
+        <v>61</v>
+      </c>
+      <c r="C144" t="s">
+        <v>23</v>
+      </c>
+      <c r="D144" t="s">
+        <v>435</v>
+      </c>
+      <c r="E144" t="s">
+        <v>1157</v>
+      </c>
+      <c r="F144" t="s">
+        <v>112</v>
+      </c>
+      <c r="G144" t="s">
+        <v>27</v>
+      </c>
+      <c r="H144" t="s">
+        <v>27</v>
+      </c>
+      <c r="I144" t="s">
+        <v>1158</v>
+      </c>
+      <c r="J144" t="s">
+        <v>1158</v>
+      </c>
+      <c r="K144" t="s">
+        <v>1159</v>
+      </c>
+      <c r="L144" t="s">
+        <v>1160</v>
+      </c>
+      <c r="M144" t="s">
+        <v>1161</v>
+      </c>
+      <c r="N144" t="s">
+        <v>1162</v>
+      </c>
+      <c r="O144" t="s">
+        <v>1163</v>
+      </c>
+      <c r="P144" t="s">
+        <v>747</v>
+      </c>
+      <c r="Q144" t="s">
+        <v>924</v>
+      </c>
+      <c r="R144" t="s">
+        <v>36</v>
+      </c>
+      <c r="S144" t="s">
+        <v>1164</v>
+      </c>
+    </row>
+    <row r="145" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
+        <v>1165</v>
+      </c>
+      <c r="B145" t="s">
+        <v>308</v>
+      </c>
+      <c r="C145" t="s">
+        <v>62</v>
+      </c>
+      <c r="D145" t="s">
+        <v>435</v>
+      </c>
+      <c r="E145" t="s">
+        <v>1166</v>
+      </c>
+      <c r="F145" t="s">
+        <v>95</v>
+      </c>
+      <c r="G145" t="s">
+        <v>27</v>
+      </c>
+      <c r="H145" t="s">
+        <v>27</v>
+      </c>
+      <c r="I145" t="s">
+        <v>1158</v>
+      </c>
+      <c r="J145" t="s">
+        <v>1158</v>
+      </c>
+      <c r="K145" t="s">
+        <v>1167</v>
+      </c>
+      <c r="L145" t="s">
+        <v>1168</v>
+      </c>
+      <c r="M145" t="s">
+        <v>1169</v>
+      </c>
+      <c r="N145" t="s">
+        <v>1170</v>
+      </c>
+      <c r="O145" t="s">
+        <v>1171</v>
+      </c>
+      <c r="P145" t="s">
+        <v>747</v>
+      </c>
+      <c r="Q145" t="s">
+        <v>924</v>
+      </c>
+      <c r="R145" t="s">
+        <v>36</v>
+      </c>
+      <c r="S145" t="s">
+        <v>1172</v>
+      </c>
+    </row>
+    <row r="146" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>1173</v>
+      </c>
+      <c r="B146" t="s">
+        <v>308</v>
+      </c>
+      <c r="C146" t="s">
+        <v>62</v>
+      </c>
+      <c r="D146" t="s">
+        <v>1174</v>
+      </c>
+      <c r="E146" t="s">
+        <v>1175</v>
+      </c>
+      <c r="F146" t="s">
+        <v>112</v>
+      </c>
+      <c r="G146" t="s">
+        <v>27</v>
+      </c>
+      <c r="H146" t="s">
+        <v>27</v>
+      </c>
+      <c r="I146" t="s">
+        <v>1158</v>
+      </c>
+      <c r="J146" t="s">
+        <v>1158</v>
+      </c>
+      <c r="K146" t="s">
+        <v>1176</v>
+      </c>
+      <c r="L146" t="s">
+        <v>1177</v>
+      </c>
+      <c r="M146" t="s">
+        <v>1178</v>
+      </c>
+      <c r="N146" t="s">
+        <v>1179</v>
+      </c>
+      <c r="O146" t="s">
+        <v>1180</v>
+      </c>
+      <c r="P146" t="s">
+        <v>747</v>
+      </c>
+      <c r="Q146" t="s">
+        <v>924</v>
+      </c>
+      <c r="R146" t="s">
+        <v>36</v>
+      </c>
+      <c r="S146" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="147" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>1181</v>
+      </c>
+      <c r="B147" t="s">
+        <v>308</v>
+      </c>
+      <c r="C147" t="s">
+        <v>62</v>
+      </c>
+      <c r="D147" t="s">
+        <v>630</v>
+      </c>
+      <c r="E147" t="s">
+        <v>1182</v>
+      </c>
+      <c r="F147" t="s">
+        <v>112</v>
+      </c>
+      <c r="G147" t="s">
+        <v>27</v>
+      </c>
+      <c r="H147" t="s">
+        <v>27</v>
+      </c>
+      <c r="I147" t="s">
+        <v>1158</v>
+      </c>
+      <c r="J147" t="s">
+        <v>1158</v>
+      </c>
+      <c r="K147" t="s">
+        <v>1183</v>
+      </c>
+      <c r="L147" t="s">
+        <v>1184</v>
+      </c>
+      <c r="M147" t="s">
+        <v>1185</v>
+      </c>
+      <c r="N147" t="s">
+        <v>1186</v>
+      </c>
+      <c r="O147" t="s">
+        <v>1187</v>
+      </c>
+      <c r="P147" t="s">
+        <v>747</v>
+      </c>
+      <c r="Q147" t="s">
+        <v>924</v>
+      </c>
+      <c r="R147" t="s">
+        <v>36</v>
+      </c>
+      <c r="S147" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="148" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>1188</v>
+      </c>
+      <c r="B148" t="s">
+        <v>308</v>
+      </c>
+      <c r="C148" t="s">
+        <v>309</v>
+      </c>
+      <c r="D148" t="s">
+        <v>24</v>
+      </c>
+      <c r="E148" t="s">
+        <v>1189</v>
+      </c>
+      <c r="F148" t="s">
+        <v>112</v>
+      </c>
+      <c r="G148" t="s">
+        <v>27</v>
+      </c>
+      <c r="H148" t="s">
+        <v>27</v>
+      </c>
+      <c r="I148" t="s">
+        <v>1158</v>
+      </c>
+      <c r="J148" t="s">
+        <v>1158</v>
+      </c>
+      <c r="K148" t="s">
+        <v>1190</v>
+      </c>
+      <c r="L148" t="s">
+        <v>1191</v>
+      </c>
+      <c r="M148" t="s">
+        <v>1192</v>
+      </c>
+      <c r="N148" t="s">
+        <v>1193</v>
+      </c>
+      <c r="O148" t="s">
+        <v>1194</v>
+      </c>
+      <c r="P148" t="s">
+        <v>747</v>
+      </c>
+      <c r="Q148" t="s">
+        <v>924</v>
+      </c>
+      <c r="R148" t="s">
+        <v>36</v>
+      </c>
+      <c r="S148" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="149" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
+        <v>1195</v>
+      </c>
+      <c r="B149" t="s">
+        <v>308</v>
+      </c>
+      <c r="C149" t="s">
+        <v>309</v>
+      </c>
+      <c r="D149" t="s">
+        <v>1054</v>
+      </c>
+      <c r="E149" t="s">
+        <v>1196</v>
+      </c>
+      <c r="F149" t="s">
+        <v>112</v>
+      </c>
+      <c r="G149" t="s">
+        <v>27</v>
+      </c>
+      <c r="H149" t="s">
+        <v>27</v>
+      </c>
+      <c r="I149" t="s">
+        <v>1158</v>
+      </c>
+      <c r="J149" t="s">
+        <v>1158</v>
+      </c>
+      <c r="K149" t="s">
+        <v>1197</v>
+      </c>
+      <c r="L149" t="s">
+        <v>1198</v>
+      </c>
+      <c r="M149" t="s">
+        <v>1199</v>
+      </c>
+      <c r="N149" t="s">
+        <v>1200</v>
+      </c>
+      <c r="O149" t="s">
+        <v>1201</v>
+      </c>
+      <c r="P149" t="s">
+        <v>747</v>
+      </c>
+      <c r="Q149" t="s">
+        <v>924</v>
+      </c>
+      <c r="R149" t="s">
+        <v>36</v>
+      </c>
+      <c r="S149" t="s">
+        <v>1202</v>
+      </c>
+    </row>
+    <row r="150" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A150" t="s">
+        <v>1203</v>
+      </c>
+      <c r="B150" t="s">
+        <v>308</v>
+      </c>
+      <c r="C150" t="s">
+        <v>309</v>
+      </c>
+      <c r="D150" t="s">
+        <v>959</v>
+      </c>
+      <c r="E150" t="s">
+        <v>1204</v>
+      </c>
+      <c r="F150" t="s">
+        <v>95</v>
+      </c>
+      <c r="G150" t="s">
+        <v>27</v>
+      </c>
+      <c r="H150" t="s">
+        <v>27</v>
+      </c>
+      <c r="I150" t="s">
+        <v>1158</v>
+      </c>
+      <c r="J150" t="s">
+        <v>1158</v>
+      </c>
+      <c r="K150" t="s">
+        <v>1205</v>
+      </c>
+      <c r="L150" t="s">
+        <v>1206</v>
+      </c>
+      <c r="M150" t="s">
+        <v>1207</v>
+      </c>
+      <c r="N150" t="s">
+        <v>1208</v>
+      </c>
+      <c r="O150" t="s">
+        <v>1209</v>
+      </c>
+      <c r="P150" t="s">
+        <v>747</v>
+      </c>
+      <c r="Q150" t="s">
+        <v>924</v>
+      </c>
+      <c r="R150" t="s">
+        <v>36</v>
+      </c>
+      <c r="S150" t="s">
+        <v>1210</v>
       </c>
     </row>
   </sheetData>
@@ -13613,48 +14194,48 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>1156</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1157</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1158</v>
+        <v>1213</v>
       </c>
       <c r="C4" t="s">
-        <v>1159</v>
+        <v>1214</v>
       </c>
       <c r="E4" t="s">
-        <v>1160</v>
+        <v>1215</v>
       </c>
       <c r="G4" t="s">
-        <v>1161</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1162</v>
+        <v>1217</v>
       </c>
       <c r="C5" t="s">
-        <v>1163</v>
+        <v>1218</v>
       </c>
       <c r="E5" t="s">
-        <v>1164</v>
+        <v>1219</v>
       </c>
       <c r="G5" t="s">
-        <v>1165</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>1166</v>
+        <v>1221</v>
       </c>
       <c r="F9" t="s">
-        <v>1167</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -13662,16 +14243,16 @@
         <v>112</v>
       </c>
       <c r="B10" t="s">
-        <v>1163</v>
+        <v>1218</v>
       </c>
       <c r="C10" t="s">
         <v>3</v>
       </c>
       <c r="D10" t="s">
-        <v>1168</v>
+        <v>1223</v>
       </c>
       <c r="F10" t="s">
-        <v>1169</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -13679,13 +14260,13 @@
         <v>86</v>
       </c>
       <c r="B11" t="s">
-        <v>1170</v>
+        <v>1225</v>
       </c>
       <c r="C11" t="s">
         <v>22</v>
       </c>
       <c r="D11" t="s">
-        <v>1171</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -13693,13 +14274,13 @@
         <v>95</v>
       </c>
       <c r="B12" t="s">
-        <v>1172</v>
+        <v>1227</v>
       </c>
       <c r="C12" t="s">
         <v>61</v>
       </c>
       <c r="D12" t="s">
-        <v>1173</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -13707,13 +14288,13 @@
         <v>453</v>
       </c>
       <c r="B13" t="s">
-        <v>1174</v>
+        <v>1229</v>
       </c>
       <c r="C13" t="s">
         <v>308</v>
       </c>
       <c r="D13" t="s">
-        <v>1175</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
@@ -13721,42 +14302,42 @@
         <v>26</v>
       </c>
       <c r="B14" t="s">
-        <v>1164</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>1176</v>
+        <v>1231</v>
       </c>
       <c r="B15" t="s">
-        <v>1165</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>1177</v>
+        <v>1232</v>
       </c>
       <c r="B16" t="s">
-        <v>1165</v>
+        <v>1220</v>
       </c>
       <c r="F16" t="s">
-        <v>1178</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>1179</v>
+        <v>1234</v>
       </c>
       <c r="B17" t="s">
-        <v>1165</v>
+        <v>1220</v>
       </c>
       <c r="F17" t="s">
-        <v>1180</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>1181</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
@@ -13764,7 +14345,7 @@
         <v>112</v>
       </c>
       <c r="C22" t="s">
-        <v>1182</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
@@ -13772,7 +14353,7 @@
         <v>86</v>
       </c>
       <c r="C23" t="s">
-        <v>1183</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
@@ -13780,7 +14361,7 @@
         <v>26</v>
       </c>
       <c r="C24" t="s">
-        <v>1184</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
@@ -13788,7 +14369,7 @@
         <v>95</v>
       </c>
       <c r="C25" t="s">
-        <v>1185</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
@@ -13796,31 +14377,31 @@
         <v>453</v>
       </c>
       <c r="C26" t="s">
-        <v>1186</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>1176</v>
+        <v>1231</v>
       </c>
       <c r="C27" t="s">
-        <v>1187</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>1177</v>
+        <v>1232</v>
       </c>
       <c r="C28" t="s">
-        <v>1188</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>1179</v>
+        <v>1234</v>
       </c>
       <c r="C29" t="s">
-        <v>1189</v>
+        <v>1244</v>
       </c>
     </row>
   </sheetData>
@@ -13834,7 +14415,7 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>1190</v>
+        <v>1245</v>
       </c>
       <c r="B1"/>
       <c r="C1"/>
@@ -13843,7 +14424,7 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1191</v>
+        <v>1246</v>
       </c>
       <c r="B2"/>
       <c r="C2"/>
@@ -13852,529 +14433,529 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>1192</v>
+        <v>1247</v>
       </c>
       <c r="B3" t="s">
         <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>1193</v>
+        <v>1248</v>
       </c>
       <c r="D3" t="s">
-        <v>1194</v>
+        <v>1249</v>
       </c>
       <c r="E3" t="s">
-        <v>1195</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1196</v>
+        <v>1251</v>
       </c>
       <c r="B4" t="s">
-        <v>1197</v>
+        <v>1252</v>
       </c>
       <c r="C4" t="s">
-        <v>1198</v>
+        <v>1253</v>
       </c>
       <c r="D4" t="s">
-        <v>1199</v>
+        <v>1254</v>
       </c>
       <c r="E4" t="s">
-        <v>1200</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1201</v>
+        <v>1256</v>
       </c>
       <c r="B5" t="s">
-        <v>1202</v>
+        <v>1257</v>
       </c>
       <c r="C5" t="s">
-        <v>1203</v>
+        <v>1258</v>
       </c>
       <c r="D5" t="s">
-        <v>1204</v>
+        <v>1259</v>
       </c>
       <c r="E5" t="s">
-        <v>1200</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>1205</v>
+        <v>1260</v>
       </c>
       <c r="B6" t="s">
-        <v>1206</v>
+        <v>1261</v>
       </c>
       <c r="C6" t="s">
-        <v>1207</v>
+        <v>1262</v>
       </c>
       <c r="D6" t="s">
-        <v>1208</v>
+        <v>1263</v>
       </c>
       <c r="E6" t="s">
-        <v>1200</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>1209</v>
+        <v>1264</v>
       </c>
       <c r="B7" t="s">
-        <v>1210</v>
+        <v>1265</v>
       </c>
       <c r="C7" t="s">
-        <v>1211</v>
+        <v>1266</v>
       </c>
       <c r="D7" t="s">
-        <v>1212</v>
+        <v>1267</v>
       </c>
       <c r="E7" t="s">
-        <v>1200</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>1213</v>
+        <v>1268</v>
       </c>
       <c r="B8" t="s">
-        <v>1214</v>
+        <v>1269</v>
       </c>
       <c r="C8" t="s">
-        <v>1215</v>
+        <v>1270</v>
       </c>
       <c r="D8" t="s">
-        <v>1216</v>
+        <v>1271</v>
       </c>
       <c r="E8" t="s">
-        <v>1200</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>1217</v>
+        <v>1272</v>
       </c>
       <c r="B9" t="s">
-        <v>1218</v>
+        <v>1273</v>
       </c>
       <c r="C9" t="s">
-        <v>1219</v>
+        <v>1274</v>
       </c>
       <c r="D9" t="s">
-        <v>1220</v>
+        <v>1275</v>
       </c>
       <c r="E9" t="s">
-        <v>1200</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>1221</v>
+        <v>1276</v>
       </c>
       <c r="B10" t="s">
-        <v>1222</v>
+        <v>1277</v>
       </c>
       <c r="C10" t="s">
-        <v>1223</v>
+        <v>1278</v>
       </c>
       <c r="D10" t="s">
-        <v>1224</v>
+        <v>1279</v>
       </c>
       <c r="E10" t="s">
-        <v>1200</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>1225</v>
+        <v>1280</v>
       </c>
       <c r="B11" t="s">
-        <v>1226</v>
+        <v>1281</v>
       </c>
       <c r="C11" t="s">
-        <v>1227</v>
+        <v>1282</v>
       </c>
       <c r="D11" t="s">
-        <v>1228</v>
+        <v>1283</v>
       </c>
       <c r="E11" t="s">
-        <v>1229</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>1230</v>
+        <v>1285</v>
       </c>
       <c r="B12" t="s">
-        <v>1231</v>
+        <v>1286</v>
       </c>
       <c r="C12" t="s">
-        <v>1232</v>
+        <v>1287</v>
       </c>
       <c r="D12" t="s">
-        <v>1233</v>
+        <v>1288</v>
       </c>
       <c r="E12" t="s">
-        <v>1200</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>1234</v>
+        <v>1289</v>
       </c>
       <c r="B13" t="s">
-        <v>1235</v>
+        <v>1290</v>
       </c>
       <c r="C13" t="s">
-        <v>1236</v>
+        <v>1291</v>
       </c>
       <c r="D13" t="s">
         <v>403</v>
       </c>
       <c r="E13" t="s">
-        <v>1229</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>1237</v>
+        <v>1227</v>
       </c>
       <c r="B14" t="s">
-        <v>1238</v>
+        <v>1292</v>
       </c>
       <c r="C14" t="s">
-        <v>1239</v>
+        <v>1293</v>
       </c>
       <c r="D14" t="s">
-        <v>1240</v>
+        <v>1294</v>
       </c>
       <c r="E14" t="s">
-        <v>1200</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>1241</v>
+        <v>1295</v>
       </c>
       <c r="B15" t="s">
-        <v>1242</v>
+        <v>1174</v>
       </c>
       <c r="C15" t="s">
-        <v>1243</v>
+        <v>1296</v>
       </c>
       <c r="D15" t="s">
-        <v>1244</v>
+        <v>1297</v>
       </c>
       <c r="E15" t="s">
-        <v>1200</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>1245</v>
+        <v>1298</v>
       </c>
       <c r="B16" t="s">
-        <v>1246</v>
+        <v>1299</v>
       </c>
       <c r="C16" t="s">
-        <v>1247</v>
+        <v>1300</v>
       </c>
       <c r="D16" t="s">
-        <v>1248</v>
+        <v>1301</v>
       </c>
       <c r="E16" t="s">
-        <v>1200</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>1249</v>
+        <v>1302</v>
       </c>
       <c r="B17" t="s">
         <v>435</v>
       </c>
       <c r="C17" t="s">
-        <v>1250</v>
+        <v>1303</v>
       </c>
       <c r="D17" t="s">
-        <v>1251</v>
+        <v>1304</v>
       </c>
       <c r="E17" t="s">
-        <v>1229</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>1170</v>
+        <v>1225</v>
       </c>
       <c r="B18" t="s">
-        <v>1252</v>
+        <v>1305</v>
       </c>
       <c r="C18" t="s">
-        <v>1253</v>
+        <v>1306</v>
       </c>
       <c r="D18" t="s">
         <v>316</v>
       </c>
       <c r="E18" t="s">
-        <v>1229</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>1254</v>
+        <v>1307</v>
       </c>
       <c r="B19" t="s">
-        <v>1255</v>
+        <v>1308</v>
       </c>
       <c r="C19" t="s">
-        <v>1256</v>
+        <v>1309</v>
       </c>
       <c r="D19" t="s">
-        <v>1257</v>
+        <v>1310</v>
       </c>
       <c r="E19" t="s">
-        <v>1229</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>1258</v>
+        <v>1311</v>
       </c>
       <c r="B20" t="s">
-        <v>1259</v>
+        <v>1312</v>
       </c>
       <c r="C20" t="s">
-        <v>1260</v>
+        <v>1313</v>
       </c>
       <c r="D20" t="s">
         <v>475</v>
       </c>
       <c r="E20" t="s">
-        <v>1200</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>1261</v>
+        <v>1314</v>
       </c>
       <c r="B21" t="s">
-        <v>1262</v>
+        <v>1315</v>
       </c>
       <c r="C21" t="s">
-        <v>1263</v>
+        <v>1316</v>
       </c>
       <c r="D21" t="s">
         <v>213</v>
       </c>
       <c r="E21" t="s">
-        <v>1229</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>1264</v>
+        <v>1317</v>
       </c>
       <c r="B22" t="s">
-        <v>1265</v>
+        <v>1318</v>
       </c>
       <c r="C22" t="s">
-        <v>1266</v>
+        <v>1319</v>
       </c>
       <c r="D22" t="s">
-        <v>1267</v>
+        <v>1320</v>
       </c>
       <c r="E22" t="s">
-        <v>1200</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>1268</v>
+        <v>1321</v>
       </c>
       <c r="B23" t="s">
-        <v>1269</v>
+        <v>1322</v>
       </c>
       <c r="C23" t="s">
-        <v>1270</v>
+        <v>1323</v>
       </c>
       <c r="D23" t="s">
-        <v>1271</v>
+        <v>1324</v>
       </c>
       <c r="E23" t="s">
-        <v>1200</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>1272</v>
+        <v>1325</v>
       </c>
       <c r="B24" t="s">
         <v>214</v>
       </c>
       <c r="C24" t="s">
-        <v>1273</v>
+        <v>1326</v>
       </c>
       <c r="D24" t="s">
-        <v>1274</v>
+        <v>1327</v>
       </c>
       <c r="E24" t="s">
-        <v>1200</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>1275</v>
+        <v>1328</v>
       </c>
       <c r="B25" t="s">
-        <v>1276</v>
+        <v>1329</v>
       </c>
       <c r="C25" t="s">
-        <v>1277</v>
+        <v>1330</v>
       </c>
       <c r="D25" t="s">
-        <v>1278</v>
+        <v>1331</v>
       </c>
       <c r="E25" t="s">
-        <v>1229</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>1279</v>
+        <v>1332</v>
       </c>
       <c r="B26" t="s">
-        <v>1280</v>
+        <v>1333</v>
       </c>
       <c r="C26" t="s">
-        <v>1281</v>
+        <v>1334</v>
       </c>
       <c r="D26" t="s">
-        <v>1282</v>
+        <v>1335</v>
       </c>
       <c r="E26" t="s">
-        <v>1229</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>1283</v>
+        <v>1336</v>
       </c>
       <c r="B27" t="s">
-        <v>1284</v>
+        <v>1337</v>
       </c>
       <c r="C27" t="s">
-        <v>1285</v>
+        <v>1338</v>
       </c>
       <c r="D27" t="s">
-        <v>1286</v>
+        <v>1339</v>
       </c>
       <c r="E27" t="s">
-        <v>1200</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>1287</v>
+        <v>1340</v>
       </c>
       <c r="B28" t="s">
-        <v>1288</v>
+        <v>1341</v>
       </c>
       <c r="C28" t="s">
-        <v>1289</v>
+        <v>1342</v>
       </c>
       <c r="D28" t="s">
-        <v>1290</v>
+        <v>1343</v>
       </c>
       <c r="E28" t="s">
-        <v>1200</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>1291</v>
+        <v>1344</v>
       </c>
       <c r="B29" t="s">
         <v>822</v>
       </c>
       <c r="C29" t="s">
-        <v>1292</v>
+        <v>1345</v>
       </c>
       <c r="D29" t="s">
-        <v>1293</v>
+        <v>1346</v>
       </c>
       <c r="E29" t="s">
-        <v>1200</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>1294</v>
+        <v>1347</v>
       </c>
       <c r="B30" t="s">
-        <v>1295</v>
+        <v>1348</v>
       </c>
       <c r="C30" t="s">
-        <v>1296</v>
+        <v>1349</v>
       </c>
       <c r="D30" t="s">
-        <v>1297</v>
+        <v>1350</v>
       </c>
       <c r="E30" t="s">
-        <v>1229</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>1298</v>
+        <v>1351</v>
       </c>
       <c r="B31" t="s">
-        <v>1299</v>
+        <v>1352</v>
       </c>
       <c r="C31" t="s">
-        <v>1300</v>
+        <v>1353</v>
       </c>
       <c r="D31" t="s">
         <v>93</v>
       </c>
       <c r="E31" t="s">
-        <v>1301</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>1302</v>
+        <v>1355</v>
       </c>
       <c r="B32" t="s">
-        <v>1303</v>
+        <v>1356</v>
       </c>
       <c r="C32" t="s">
-        <v>1304</v>
+        <v>1357</v>
       </c>
       <c r="D32" t="s">
-        <v>1305</v>
+        <v>1358</v>
       </c>
       <c r="E32" t="s">
-        <v>1200</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>1306</v>
+        <v>1359</v>
       </c>
       <c r="B33" t="s">
         <v>1030</v>
       </c>
       <c r="C33" t="s">
-        <v>1307</v>
+        <v>1360</v>
       </c>
       <c r="D33" t="s">
-        <v>1308</v>
+        <v>1361</v>
       </c>
       <c r="E33" t="s">
-        <v>1229</v>
+        <v>1284</v>
       </c>
     </row>
   </sheetData>
@@ -14388,157 +14969,157 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr defaultRowHeight="0" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" customHeight="1"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>1309</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1310</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>1311</v>
+        <v>1364</v>
       </c>
       <c r="B3" t="s">
-        <v>1312</v>
+        <v>1365</v>
       </c>
       <c r="C3" t="s">
-        <v>1313</v>
+        <v>1366</v>
       </c>
       <c r="D3" t="s">
-        <v>1314</v>
+        <v>1367</v>
       </c>
       <c r="E3" t="s">
-        <v>1315</v>
+        <v>1368</v>
       </c>
       <c r="F3" t="s">
-        <v>1316</v>
+        <v>1369</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1317</v>
+        <v>1370</v>
       </c>
       <c r="B4" t="s">
         <v>28</v>
       </c>
       <c r="C4" t="s">
-        <v>1318</v>
+        <v>1371</v>
       </c>
       <c r="D4" t="s">
-        <v>1319</v>
+        <v>1372</v>
       </c>
       <c r="E4" t="s">
-        <v>1320</v>
+        <v>1373</v>
       </c>
       <c r="F4" t="s">
-        <v>1321</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1322</v>
+        <v>1375</v>
       </c>
       <c r="B5" t="s">
-        <v>1323</v>
+        <v>1376</v>
       </c>
       <c r="C5" t="s">
-        <v>1324</v>
+        <v>1377</v>
       </c>
       <c r="D5" t="s">
-        <v>1325</v>
+        <v>1378</v>
       </c>
       <c r="E5" t="s">
-        <v>1326</v>
+        <v>1379</v>
       </c>
       <c r="F5" t="s">
-        <v>1327</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>1328</v>
+        <v>1381</v>
       </c>
       <c r="B6" t="s">
-        <v>1329</v>
+        <v>1382</v>
       </c>
       <c r="C6" t="s">
-        <v>1330</v>
+        <v>1383</v>
       </c>
       <c r="D6" t="s">
-        <v>1331</v>
+        <v>1384</v>
       </c>
       <c r="E6" t="s">
-        <v>1332</v>
+        <v>1385</v>
       </c>
       <c r="F6" t="s">
-        <v>1333</v>
+        <v>1386</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>1334</v>
+        <v>1387</v>
       </c>
       <c r="B7" t="s">
-        <v>1335</v>
+        <v>1388</v>
       </c>
       <c r="C7" t="s">
-        <v>1336</v>
+        <v>1389</v>
       </c>
       <c r="D7" t="s">
-        <v>1337</v>
+        <v>1390</v>
       </c>
       <c r="E7" t="s">
-        <v>1332</v>
+        <v>1385</v>
       </c>
       <c r="F7" t="s">
-        <v>1338</v>
+        <v>1391</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>1339</v>
+        <v>1392</v>
       </c>
       <c r="B8" t="s">
-        <v>1340</v>
+        <v>1393</v>
       </c>
       <c r="C8" t="s">
-        <v>1341</v>
+        <v>1394</v>
       </c>
       <c r="D8" t="s">
-        <v>1342</v>
+        <v>1395</v>
       </c>
       <c r="E8" t="s">
-        <v>1332</v>
+        <v>1385</v>
       </c>
       <c r="F8" t="s">
-        <v>1338</v>
+        <v>1391</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>1343</v>
+        <v>1396</v>
       </c>
       <c r="B9" t="s">
         <v>29</v>
       </c>
       <c r="C9" t="s">
-        <v>1344</v>
+        <v>1397</v>
       </c>
       <c r="D9" t="s">
-        <v>1345</v>
+        <v>1398</v>
       </c>
       <c r="E9" t="s">
-        <v>1320</v>
+        <v>1373</v>
       </c>
       <c r="F9" t="s">
-        <v>1346</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -14549,93 +15130,93 @@
         <v>29</v>
       </c>
       <c r="C10" t="s">
-        <v>1347</v>
+        <v>1400</v>
       </c>
       <c r="D10" t="s">
-        <v>1348</v>
+        <v>1401</v>
       </c>
       <c r="E10" t="s">
-        <v>1349</v>
+        <v>1402</v>
       </c>
       <c r="F10" t="s">
-        <v>1350</v>
+        <v>1403</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>1351</v>
+        <v>1404</v>
       </c>
       <c r="B11" t="s">
         <v>55</v>
       </c>
       <c r="C11" t="s">
-        <v>1352</v>
+        <v>1405</v>
       </c>
       <c r="D11" t="s">
-        <v>1353</v>
+        <v>1406</v>
       </c>
       <c r="E11" t="s">
-        <v>1349</v>
+        <v>1402</v>
       </c>
       <c r="F11" t="s">
-        <v>1354</v>
+        <v>1407</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>1355</v>
+        <v>1408</v>
       </c>
       <c r="B12" t="s">
         <v>161</v>
       </c>
       <c r="C12" t="s">
-        <v>1356</v>
+        <v>1409</v>
       </c>
       <c r="D12" t="s">
-        <v>1357</v>
+        <v>1410</v>
       </c>
       <c r="E12" t="s">
-        <v>1358</v>
+        <v>1411</v>
       </c>
       <c r="F12" t="s">
-        <v>1359</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>1360</v>
+        <v>1413</v>
       </c>
       <c r="B13" t="s">
-        <v>1361</v>
+        <v>1414</v>
       </c>
       <c r="C13" t="s">
-        <v>1362</v>
+        <v>1415</v>
       </c>
       <c r="D13" t="s">
-        <v>1363</v>
+        <v>1416</v>
       </c>
       <c r="E13" t="s">
-        <v>1364</v>
+        <v>1417</v>
       </c>
       <c r="F13" t="s">
-        <v>1365</v>
+        <v>1418</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>1366</v>
+        <v>1419</v>
       </c>
       <c r="B14" t="s">
         <v>206</v>
       </c>
       <c r="C14" t="s">
-        <v>1367</v>
+        <v>1420</v>
       </c>
       <c r="D14" t="s">
-        <v>1368</v>
+        <v>1421</v>
       </c>
       <c r="E14" t="s">
-        <v>1369</v>
+        <v>1422</v>
       </c>
       <c r="F14" t="s">
         <v>748</v>
@@ -14643,19 +15224,19 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>1370</v>
+        <v>1423</v>
       </c>
       <c r="B15" t="s">
         <v>206</v>
       </c>
       <c r="C15" t="s">
-        <v>1371</v>
+        <v>1424</v>
       </c>
       <c r="D15" t="s">
-        <v>1372</v>
+        <v>1425</v>
       </c>
       <c r="E15" t="s">
-        <v>1373</v>
+        <v>1426</v>
       </c>
       <c r="F15" t="s">
         <v>748</v>
@@ -14663,19 +15244,19 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>1374</v>
+        <v>1427</v>
       </c>
       <c r="B16" t="s">
         <v>918</v>
       </c>
       <c r="C16" t="s">
-        <v>1375</v>
+        <v>1428</v>
       </c>
       <c r="D16" t="s">
-        <v>1376</v>
+        <v>1429</v>
       </c>
       <c r="E16" t="s">
-        <v>1373</v>
+        <v>1426</v>
       </c>
       <c r="F16" t="s">
         <v>924</v>
@@ -14683,19 +15264,19 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>1377</v>
+        <v>1430</v>
       </c>
       <c r="B17" t="s">
         <v>999</v>
       </c>
       <c r="C17" t="s">
-        <v>1378</v>
+        <v>1431</v>
       </c>
       <c r="D17" t="s">
-        <v>1379</v>
+        <v>1432</v>
       </c>
       <c r="E17" t="s">
-        <v>1373</v>
+        <v>1426</v>
       </c>
       <c r="F17" t="s">
         <v>924</v>
@@ -14703,19 +15284,19 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>1380</v>
+        <v>1433</v>
       </c>
       <c r="B18" t="s">
         <v>1095</v>
       </c>
       <c r="C18" t="s">
-        <v>1381</v>
+        <v>1434</v>
       </c>
       <c r="D18" t="s">
-        <v>1382</v>
+        <v>1435</v>
       </c>
       <c r="E18" t="s">
-        <v>1373</v>
+        <v>1426</v>
       </c>
       <c r="F18" t="s">
         <v>924</v>
@@ -14723,21 +15304,41 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>1383</v>
+        <v>1436</v>
       </c>
       <c r="B19" t="s">
         <v>1141</v>
       </c>
       <c r="C19" t="s">
-        <v>1384</v>
+        <v>1437</v>
       </c>
       <c r="D19" t="s">
-        <v>1385</v>
+        <v>1438</v>
       </c>
       <c r="E19" t="s">
-        <v>1373</v>
+        <v>1426</v>
       </c>
       <c r="F19" t="s">
+        <v>924</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>1439</v>
+      </c>
+      <c r="B20" t="s">
+        <v>1158</v>
+      </c>
+      <c r="C20" t="s">
+        <v>1440</v>
+      </c>
+      <c r="D20" t="s">
+        <v>1441</v>
+      </c>
+      <c r="E20" t="s">
+        <v>1426</v>
+      </c>
+      <c r="F20" t="s">
         <v>924</v>
       </c>
     </row>
@@ -14747,40 +15348,40 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G159"/>
+  <dimension ref="A1:G166"/>
   <sheetFormatPr defaultRowHeight="0" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" customHeight="1"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>1386</v>
+        <v>1442</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1387</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>1388</v>
+        <v>1444</v>
       </c>
       <c r="B3" t="s">
-        <v>1389</v>
+        <v>1445</v>
       </c>
       <c r="C3" t="s">
-        <v>1390</v>
+        <v>1446</v>
       </c>
       <c r="D3" t="s">
-        <v>1391</v>
+        <v>1447</v>
       </c>
       <c r="E3" t="s">
-        <v>1392</v>
+        <v>1448</v>
       </c>
       <c r="F3" t="s">
-        <v>1393</v>
+        <v>1449</v>
       </c>
       <c r="G3" t="s">
-        <v>1394</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -14800,10 +15401,10 @@
         <v>26</v>
       </c>
       <c r="F4" t="s">
-        <v>1395</v>
+        <v>1451</v>
       </c>
       <c r="G4" t="s">
-        <v>1396</v>
+        <v>1452</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -14823,10 +15424,10 @@
         <v>26</v>
       </c>
       <c r="F5" t="s">
-        <v>1395</v>
+        <v>1451</v>
       </c>
       <c r="G5" t="s">
-        <v>1397</v>
+        <v>1453</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -14846,10 +15447,10 @@
         <v>26</v>
       </c>
       <c r="F6" t="s">
-        <v>1395</v>
+        <v>1451</v>
       </c>
       <c r="G6" t="s">
-        <v>1398</v>
+        <v>1454</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -14869,10 +15470,10 @@
         <v>86</v>
       </c>
       <c r="F7" t="s">
-        <v>1395</v>
+        <v>1451</v>
       </c>
       <c r="G7" t="s">
-        <v>1399</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -14892,10 +15493,10 @@
         <v>26</v>
       </c>
       <c r="F8" t="s">
-        <v>1395</v>
+        <v>1451</v>
       </c>
       <c r="G8" t="s">
-        <v>1400</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -14915,10 +15516,10 @@
         <v>26</v>
       </c>
       <c r="F9" t="s">
-        <v>1395</v>
+        <v>1451</v>
       </c>
       <c r="G9" t="s">
-        <v>1401</v>
+        <v>1457</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -14938,10 +15539,10 @@
         <v>26</v>
       </c>
       <c r="F10" t="s">
-        <v>1395</v>
+        <v>1451</v>
       </c>
       <c r="G10" t="s">
-        <v>1402</v>
+        <v>1458</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -14961,10 +15562,10 @@
         <v>86</v>
       </c>
       <c r="F11" t="s">
-        <v>1395</v>
+        <v>1451</v>
       </c>
       <c r="G11" t="s">
-        <v>1403</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -14984,10 +15585,10 @@
         <v>86</v>
       </c>
       <c r="F12" t="s">
-        <v>1395</v>
+        <v>1451</v>
       </c>
       <c r="G12" t="s">
-        <v>1404</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -15007,10 +15608,10 @@
         <v>26</v>
       </c>
       <c r="F13" t="s">
-        <v>1395</v>
+        <v>1451</v>
       </c>
       <c r="G13" t="s">
-        <v>1405</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -15030,10 +15631,10 @@
         <v>26</v>
       </c>
       <c r="F14" t="s">
-        <v>1406</v>
+        <v>1462</v>
       </c>
       <c r="G14" t="s">
-        <v>1407</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -15053,10 +15654,10 @@
         <v>26</v>
       </c>
       <c r="F15" t="s">
-        <v>1406</v>
+        <v>1462</v>
       </c>
       <c r="G15" t="s">
-        <v>1408</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -15076,10 +15677,10 @@
         <v>26</v>
       </c>
       <c r="F16" t="s">
-        <v>1406</v>
+        <v>1462</v>
       </c>
       <c r="G16" t="s">
-        <v>1409</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -15099,10 +15700,10 @@
         <v>26</v>
       </c>
       <c r="F17" t="s">
-        <v>1406</v>
+        <v>1462</v>
       </c>
       <c r="G17" t="s">
-        <v>1410</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -15122,10 +15723,10 @@
         <v>26</v>
       </c>
       <c r="F18" t="s">
-        <v>1406</v>
+        <v>1462</v>
       </c>
       <c r="G18" t="s">
-        <v>1411</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -15145,10 +15746,10 @@
         <v>26</v>
       </c>
       <c r="F19" t="s">
-        <v>1406</v>
+        <v>1462</v>
       </c>
       <c r="G19" t="s">
-        <v>1412</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -15168,10 +15769,10 @@
         <v>86</v>
       </c>
       <c r="F20" t="s">
-        <v>1406</v>
+        <v>1462</v>
       </c>
       <c r="G20" t="s">
-        <v>1413</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -15191,10 +15792,10 @@
         <v>86</v>
       </c>
       <c r="F21" t="s">
-        <v>1406</v>
+        <v>1462</v>
       </c>
       <c r="G21" t="s">
-        <v>1414</v>
+        <v>1470</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
@@ -15214,10 +15815,10 @@
         <v>26</v>
       </c>
       <c r="F22" t="s">
-        <v>1406</v>
+        <v>1462</v>
       </c>
       <c r="G22" t="s">
-        <v>1415</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
@@ -15237,10 +15838,10 @@
         <v>86</v>
       </c>
       <c r="F23" t="s">
-        <v>1406</v>
+        <v>1462</v>
       </c>
       <c r="G23" t="s">
-        <v>1416</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -15260,10 +15861,10 @@
         <v>86</v>
       </c>
       <c r="F24" t="s">
-        <v>1406</v>
+        <v>1462</v>
       </c>
       <c r="G24" t="s">
-        <v>1417</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
@@ -15283,10 +15884,10 @@
         <v>86</v>
       </c>
       <c r="F25" t="s">
-        <v>1406</v>
+        <v>1462</v>
       </c>
       <c r="G25" t="s">
-        <v>1418</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
@@ -15306,10 +15907,10 @@
         <v>86</v>
       </c>
       <c r="F26" t="s">
-        <v>1406</v>
+        <v>1462</v>
       </c>
       <c r="G26" t="s">
-        <v>1419</v>
+        <v>1475</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
@@ -15329,10 +15930,10 @@
         <v>26</v>
       </c>
       <c r="F27" t="s">
-        <v>1406</v>
+        <v>1462</v>
       </c>
       <c r="G27" t="s">
-        <v>1420</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
@@ -15352,10 +15953,10 @@
         <v>86</v>
       </c>
       <c r="F28" t="s">
-        <v>1406</v>
+        <v>1462</v>
       </c>
       <c r="G28" t="s">
-        <v>1421</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
@@ -15375,10 +15976,10 @@
         <v>86</v>
       </c>
       <c r="F29" t="s">
-        <v>1406</v>
+        <v>1462</v>
       </c>
       <c r="G29" t="s">
-        <v>1422</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
@@ -15398,10 +15999,10 @@
         <v>26</v>
       </c>
       <c r="F30" t="s">
-        <v>1406</v>
+        <v>1462</v>
       </c>
       <c r="G30" t="s">
-        <v>1423</v>
+        <v>1479</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
@@ -15421,10 +16022,10 @@
         <v>26</v>
       </c>
       <c r="F31" t="s">
-        <v>1406</v>
+        <v>1462</v>
       </c>
       <c r="G31" t="s">
-        <v>1424</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
@@ -15444,10 +16045,10 @@
         <v>86</v>
       </c>
       <c r="F32" t="s">
-        <v>1406</v>
+        <v>1462</v>
       </c>
       <c r="G32" t="s">
-        <v>1425</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
@@ -15467,10 +16068,10 @@
         <v>86</v>
       </c>
       <c r="F33" t="s">
-        <v>1406</v>
+        <v>1462</v>
       </c>
       <c r="G33" t="s">
-        <v>1426</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
@@ -15490,10 +16091,10 @@
         <v>86</v>
       </c>
       <c r="F34" t="s">
-        <v>1406</v>
+        <v>1462</v>
       </c>
       <c r="G34" t="s">
-        <v>1427</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
@@ -15513,7 +16114,7 @@
         <v>26</v>
       </c>
       <c r="F35" t="s">
-        <v>1428</v>
+        <v>1484</v>
       </c>
       <c r="G35" t="s">
         <v>168</v>
@@ -15536,7 +16137,7 @@
         <v>26</v>
       </c>
       <c r="F36" t="s">
-        <v>1428</v>
+        <v>1484</v>
       </c>
       <c r="G36" t="s">
         <v>177</v>
@@ -15559,7 +16160,7 @@
         <v>26</v>
       </c>
       <c r="F37" t="s">
-        <v>1428</v>
+        <v>1484</v>
       </c>
       <c r="G37" t="s">
         <v>194</v>
@@ -15582,7 +16183,7 @@
         <v>26</v>
       </c>
       <c r="F38" t="s">
-        <v>1428</v>
+        <v>1484</v>
       </c>
       <c r="G38" t="s">
         <v>203</v>
@@ -15605,7 +16206,7 @@
         <v>26</v>
       </c>
       <c r="F39" t="s">
-        <v>1428</v>
+        <v>1484</v>
       </c>
       <c r="G39" t="s">
         <v>222</v>
@@ -15628,7 +16229,7 @@
         <v>26</v>
       </c>
       <c r="F40" t="s">
-        <v>1428</v>
+        <v>1484</v>
       </c>
       <c r="G40" t="s">
         <v>245</v>
@@ -15651,10 +16252,10 @@
         <v>26</v>
       </c>
       <c r="F41" t="s">
-        <v>1428</v>
+        <v>1484</v>
       </c>
       <c r="G41" t="s">
-        <v>1429</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
@@ -15674,10 +16275,10 @@
         <v>26</v>
       </c>
       <c r="F42" t="s">
-        <v>1428</v>
+        <v>1484</v>
       </c>
       <c r="G42" t="s">
-        <v>1430</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
@@ -15697,10 +16298,10 @@
         <v>26</v>
       </c>
       <c r="F43" t="s">
-        <v>1428</v>
+        <v>1484</v>
       </c>
       <c r="G43" t="s">
-        <v>1431</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
@@ -15720,7 +16321,7 @@
         <v>26</v>
       </c>
       <c r="F44" t="s">
-        <v>1428</v>
+        <v>1484</v>
       </c>
       <c r="G44" t="s">
         <v>360</v>
@@ -15743,7 +16344,7 @@
         <v>26</v>
       </c>
       <c r="F45" t="s">
-        <v>1428</v>
+        <v>1484</v>
       </c>
       <c r="G45" t="s">
         <v>368</v>
@@ -15766,10 +16367,10 @@
         <v>26</v>
       </c>
       <c r="F46" t="s">
-        <v>1428</v>
+        <v>1484</v>
       </c>
       <c r="G46" t="s">
-        <v>1432</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
@@ -15789,7 +16390,7 @@
         <v>26</v>
       </c>
       <c r="F47" t="s">
-        <v>1428</v>
+        <v>1484</v>
       </c>
       <c r="G47" t="s">
         <v>386</v>
@@ -15812,10 +16413,10 @@
         <v>26</v>
       </c>
       <c r="F48" t="s">
-        <v>1428</v>
+        <v>1484</v>
       </c>
       <c r="G48" t="s">
-        <v>1433</v>
+        <v>1489</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
@@ -15835,7 +16436,7 @@
         <v>26</v>
       </c>
       <c r="F49" t="s">
-        <v>1428</v>
+        <v>1484</v>
       </c>
       <c r="G49" t="s">
         <v>402</v>
@@ -15858,7 +16459,7 @@
         <v>26</v>
       </c>
       <c r="F50" t="s">
-        <v>1428</v>
+        <v>1484</v>
       </c>
       <c r="G50" t="s">
         <v>411</v>
@@ -15881,7 +16482,7 @@
         <v>26</v>
       </c>
       <c r="F51" t="s">
-        <v>1428</v>
+        <v>1484</v>
       </c>
       <c r="G51" t="s">
         <v>419</v>
@@ -15904,7 +16505,7 @@
         <v>26</v>
       </c>
       <c r="F52" t="s">
-        <v>1428</v>
+        <v>1484</v>
       </c>
       <c r="G52" t="s">
         <v>426</v>
@@ -15927,7 +16528,7 @@
         <v>26</v>
       </c>
       <c r="F53" t="s">
-        <v>1428</v>
+        <v>1484</v>
       </c>
       <c r="G53" t="s">
         <v>433</v>
@@ -15950,7 +16551,7 @@
         <v>26</v>
       </c>
       <c r="F54" t="s">
-        <v>1428</v>
+        <v>1484</v>
       </c>
       <c r="G54" t="s">
         <v>467</v>
@@ -15973,7 +16574,7 @@
         <v>26</v>
       </c>
       <c r="F55" t="s">
-        <v>1428</v>
+        <v>1484</v>
       </c>
       <c r="G55" t="s">
         <v>485</v>
@@ -15996,7 +16597,7 @@
         <v>26</v>
       </c>
       <c r="F56" t="s">
-        <v>1428</v>
+        <v>1484</v>
       </c>
       <c r="G56" t="s">
         <v>494</v>
@@ -16019,7 +16620,7 @@
         <v>26</v>
       </c>
       <c r="F57" t="s">
-        <v>1428</v>
+        <v>1484</v>
       </c>
       <c r="G57" t="s">
         <v>502</v>
@@ -16042,7 +16643,7 @@
         <v>26</v>
       </c>
       <c r="F58" t="s">
-        <v>1428</v>
+        <v>1484</v>
       </c>
       <c r="G58" t="s">
         <v>511</v>
@@ -16065,7 +16666,7 @@
         <v>26</v>
       </c>
       <c r="F59" t="s">
-        <v>1428</v>
+        <v>1484</v>
       </c>
       <c r="G59" t="s">
         <v>520</v>
@@ -16088,7 +16689,7 @@
         <v>26</v>
       </c>
       <c r="F60" t="s">
-        <v>1428</v>
+        <v>1484</v>
       </c>
       <c r="G60" t="s">
         <v>530</v>
@@ -16111,7 +16712,7 @@
         <v>26</v>
       </c>
       <c r="F61" t="s">
-        <v>1428</v>
+        <v>1484</v>
       </c>
       <c r="G61" t="s">
         <v>539</v>
@@ -16134,7 +16735,7 @@
         <v>26</v>
       </c>
       <c r="F62" t="s">
-        <v>1428</v>
+        <v>1484</v>
       </c>
       <c r="G62" t="s">
         <v>547</v>
@@ -16157,7 +16758,7 @@
         <v>26</v>
       </c>
       <c r="F63" t="s">
-        <v>1428</v>
+        <v>1484</v>
       </c>
       <c r="G63" t="s">
         <v>557</v>
@@ -16180,7 +16781,7 @@
         <v>26</v>
       </c>
       <c r="F64" t="s">
-        <v>1428</v>
+        <v>1484</v>
       </c>
       <c r="G64" t="s">
         <v>567</v>
@@ -16203,7 +16804,7 @@
         <v>26</v>
       </c>
       <c r="F65" t="s">
-        <v>1428</v>
+        <v>1484</v>
       </c>
       <c r="G65" t="s">
         <v>576</v>
@@ -16226,7 +16827,7 @@
         <v>26</v>
       </c>
       <c r="F66" t="s">
-        <v>1428</v>
+        <v>1484</v>
       </c>
       <c r="G66" t="s">
         <v>584</v>
@@ -16249,7 +16850,7 @@
         <v>26</v>
       </c>
       <c r="F67" t="s">
-        <v>1428</v>
+        <v>1484</v>
       </c>
       <c r="G67" t="s">
         <v>594</v>
@@ -16272,7 +16873,7 @@
         <v>26</v>
       </c>
       <c r="F68" t="s">
-        <v>1428</v>
+        <v>1484</v>
       </c>
       <c r="G68" t="s">
         <v>602</v>
@@ -16295,7 +16896,7 @@
         <v>26</v>
       </c>
       <c r="F69" t="s">
-        <v>1428</v>
+        <v>1484</v>
       </c>
       <c r="G69" t="s">
         <v>611</v>
@@ -16318,7 +16919,7 @@
         <v>26</v>
       </c>
       <c r="F70" t="s">
-        <v>1428</v>
+        <v>1484</v>
       </c>
       <c r="G70" t="s">
         <v>618</v>
@@ -16341,10 +16942,10 @@
         <v>26</v>
       </c>
       <c r="F71" t="s">
-        <v>1428</v>
+        <v>1484</v>
       </c>
       <c r="G71" t="s">
-        <v>1434</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
@@ -16364,10 +16965,10 @@
         <v>26</v>
       </c>
       <c r="F72" t="s">
-        <v>1428</v>
+        <v>1484</v>
       </c>
       <c r="G72" t="s">
-        <v>1435</v>
+        <v>1491</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
@@ -16387,10 +16988,10 @@
         <v>26</v>
       </c>
       <c r="F73" t="s">
-        <v>1428</v>
+        <v>1484</v>
       </c>
       <c r="G73" t="s">
-        <v>1436</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
@@ -16410,10 +17011,10 @@
         <v>26</v>
       </c>
       <c r="F74" t="s">
-        <v>1428</v>
+        <v>1484</v>
       </c>
       <c r="G74" t="s">
-        <v>1437</v>
+        <v>1493</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
@@ -16433,10 +17034,10 @@
         <v>26</v>
       </c>
       <c r="F75" t="s">
-        <v>1428</v>
+        <v>1484</v>
       </c>
       <c r="G75" t="s">
-        <v>1438</v>
+        <v>1494</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
@@ -16456,10 +17057,10 @@
         <v>26</v>
       </c>
       <c r="F76" t="s">
-        <v>1428</v>
+        <v>1484</v>
       </c>
       <c r="G76" t="s">
-        <v>1439</v>
+        <v>1495</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
@@ -16479,10 +17080,10 @@
         <v>26</v>
       </c>
       <c r="F77" t="s">
-        <v>1428</v>
+        <v>1484</v>
       </c>
       <c r="G77" t="s">
-        <v>1440</v>
+        <v>1496</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
@@ -16502,10 +17103,10 @@
         <v>26</v>
       </c>
       <c r="F78" t="s">
-        <v>1428</v>
+        <v>1484</v>
       </c>
       <c r="G78" t="s">
-        <v>1441</v>
+        <v>1497</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
@@ -16525,10 +17126,10 @@
         <v>26</v>
       </c>
       <c r="F79" t="s">
-        <v>1428</v>
+        <v>1484</v>
       </c>
       <c r="G79" t="s">
-        <v>1442</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
@@ -16536,7 +17137,7 @@
         <v>27</v>
       </c>
       <c r="B80" t="s">
-        <v>1361</v>
+        <v>1414</v>
       </c>
       <c r="C80" t="s">
         <v>697</v>
@@ -16548,10 +17149,10 @@
         <v>26</v>
       </c>
       <c r="F80" t="s">
-        <v>1443</v>
+        <v>1499</v>
       </c>
       <c r="G80" t="s">
-        <v>1444</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
@@ -16559,7 +17160,7 @@
         <v>27</v>
       </c>
       <c r="B81" t="s">
-        <v>1361</v>
+        <v>1414</v>
       </c>
       <c r="C81" t="s">
         <v>708</v>
@@ -16571,10 +17172,10 @@
         <v>26</v>
       </c>
       <c r="F81" t="s">
-        <v>1443</v>
+        <v>1499</v>
       </c>
       <c r="G81" t="s">
-        <v>1445</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
@@ -16582,7 +17183,7 @@
         <v>27</v>
       </c>
       <c r="B82" t="s">
-        <v>1361</v>
+        <v>1414</v>
       </c>
       <c r="C82" t="s">
         <v>715</v>
@@ -16594,10 +17195,10 @@
         <v>26</v>
       </c>
       <c r="F82" t="s">
-        <v>1443</v>
+        <v>1499</v>
       </c>
       <c r="G82" t="s">
-        <v>1446</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
@@ -16605,7 +17206,7 @@
         <v>27</v>
       </c>
       <c r="B83" t="s">
-        <v>1361</v>
+        <v>1414</v>
       </c>
       <c r="C83" t="s">
         <v>723</v>
@@ -16617,10 +17218,10 @@
         <v>26</v>
       </c>
       <c r="F83" t="s">
-        <v>1443</v>
+        <v>1499</v>
       </c>
       <c r="G83" t="s">
-        <v>1447</v>
+        <v>1503</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
@@ -16628,7 +17229,7 @@
         <v>27</v>
       </c>
       <c r="B84" t="s">
-        <v>1361</v>
+        <v>1414</v>
       </c>
       <c r="C84" t="s">
         <v>732</v>
@@ -16640,10 +17241,10 @@
         <v>26</v>
       </c>
       <c r="F84" t="s">
-        <v>1443</v>
+        <v>1499</v>
       </c>
       <c r="G84" t="s">
-        <v>1448</v>
+        <v>1504</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
@@ -16651,7 +17252,7 @@
         <v>27</v>
       </c>
       <c r="B85" t="s">
-        <v>1449</v>
+        <v>1505</v>
       </c>
       <c r="C85" t="s">
         <v>324</v>
@@ -16663,10 +17264,10 @@
         <v>86</v>
       </c>
       <c r="F85" t="s">
-        <v>1450</v>
+        <v>1506</v>
       </c>
       <c r="G85" t="s">
-        <v>1451</v>
+        <v>1507</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
@@ -16674,7 +17275,7 @@
         <v>27</v>
       </c>
       <c r="B86" t="s">
-        <v>1449</v>
+        <v>1505</v>
       </c>
       <c r="C86" t="s">
         <v>335</v>
@@ -16686,10 +17287,10 @@
         <v>86</v>
       </c>
       <c r="F86" t="s">
-        <v>1450</v>
+        <v>1506</v>
       </c>
       <c r="G86" t="s">
-        <v>1452</v>
+        <v>1508</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
@@ -16697,7 +17298,7 @@
         <v>27</v>
       </c>
       <c r="B87" t="s">
-        <v>1449</v>
+        <v>1505</v>
       </c>
       <c r="C87" t="s">
         <v>344</v>
@@ -16709,10 +17310,10 @@
         <v>86</v>
       </c>
       <c r="F87" t="s">
-        <v>1450</v>
+        <v>1506</v>
       </c>
       <c r="G87" t="s">
-        <v>1453</v>
+        <v>1509</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
@@ -16720,7 +17321,7 @@
         <v>27</v>
       </c>
       <c r="B88" t="s">
-        <v>1449</v>
+        <v>1505</v>
       </c>
       <c r="C88" t="s">
         <v>369</v>
@@ -16732,10 +17333,10 @@
         <v>112</v>
       </c>
       <c r="F88" t="s">
-        <v>1450</v>
+        <v>1506</v>
       </c>
       <c r="G88" t="s">
-        <v>1454</v>
+        <v>1510</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
@@ -16755,10 +17356,10 @@
         <v>26</v>
       </c>
       <c r="F89" t="s">
-        <v>1455</v>
+        <v>1511</v>
       </c>
       <c r="G89" t="s">
-        <v>1456</v>
+        <v>1512</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
@@ -16766,7 +17367,7 @@
         <v>27</v>
       </c>
       <c r="B90" t="s">
-        <v>1449</v>
+        <v>1505</v>
       </c>
       <c r="C90" t="s">
         <v>619</v>
@@ -16778,10 +17379,10 @@
         <v>112</v>
       </c>
       <c r="F90" t="s">
-        <v>1450</v>
+        <v>1506</v>
       </c>
       <c r="G90" t="s">
-        <v>1457</v>
+        <v>1513</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
@@ -16789,7 +17390,7 @@
         <v>27</v>
       </c>
       <c r="B91" t="s">
-        <v>1449</v>
+        <v>1505</v>
       </c>
       <c r="C91" t="s">
         <v>639</v>
@@ -16801,10 +17402,10 @@
         <v>86</v>
       </c>
       <c r="F91" t="s">
-        <v>1450</v>
+        <v>1506</v>
       </c>
       <c r="G91" t="s">
-        <v>1458</v>
+        <v>1514</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
@@ -16812,7 +17413,7 @@
         <v>27</v>
       </c>
       <c r="B92" t="s">
-        <v>1449</v>
+        <v>1505</v>
       </c>
       <c r="C92" t="s">
         <v>648</v>
@@ -16824,10 +17425,10 @@
         <v>112</v>
       </c>
       <c r="F92" t="s">
-        <v>1450</v>
+        <v>1506</v>
       </c>
       <c r="G92" t="s">
-        <v>1459</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
@@ -16847,10 +17448,10 @@
         <v>86</v>
       </c>
       <c r="F93" t="s">
-        <v>1455</v>
+        <v>1511</v>
       </c>
       <c r="G93" t="s">
-        <v>1460</v>
+        <v>1516</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
@@ -16858,7 +17459,7 @@
         <v>27</v>
       </c>
       <c r="B94" t="s">
-        <v>1449</v>
+        <v>1505</v>
       </c>
       <c r="C94" t="s">
         <v>657</v>
@@ -16870,10 +17471,10 @@
         <v>112</v>
       </c>
       <c r="F94" t="s">
-        <v>1450</v>
+        <v>1506</v>
       </c>
       <c r="G94" t="s">
-        <v>1461</v>
+        <v>1517</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
@@ -16881,7 +17482,7 @@
         <v>27</v>
       </c>
       <c r="B95" t="s">
-        <v>1449</v>
+        <v>1505</v>
       </c>
       <c r="C95" t="s">
         <v>673</v>
@@ -16893,10 +17494,10 @@
         <v>112</v>
       </c>
       <c r="F95" t="s">
-        <v>1450</v>
+        <v>1506</v>
       </c>
       <c r="G95" t="s">
-        <v>1462</v>
+        <v>1518</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
@@ -16916,10 +17517,10 @@
         <v>26</v>
       </c>
       <c r="F96" t="s">
-        <v>1455</v>
+        <v>1511</v>
       </c>
       <c r="G96" t="s">
-        <v>1463</v>
+        <v>1519</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
@@ -16927,7 +17528,7 @@
         <v>27</v>
       </c>
       <c r="B97" t="s">
-        <v>1449</v>
+        <v>1505</v>
       </c>
       <c r="C97" t="s">
         <v>689</v>
@@ -16939,10 +17540,10 @@
         <v>112</v>
       </c>
       <c r="F97" t="s">
-        <v>1450</v>
+        <v>1506</v>
       </c>
       <c r="G97" t="s">
-        <v>1464</v>
+        <v>1520</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
@@ -16950,7 +17551,7 @@
         <v>27</v>
       </c>
       <c r="B98" t="s">
-        <v>1449</v>
+        <v>1505</v>
       </c>
       <c r="C98" t="s">
         <v>697</v>
@@ -16962,10 +17563,10 @@
         <v>112</v>
       </c>
       <c r="F98" t="s">
-        <v>1450</v>
+        <v>1506</v>
       </c>
       <c r="G98" t="s">
-        <v>1465</v>
+        <v>1521</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
@@ -16985,10 +17586,10 @@
         <v>26</v>
       </c>
       <c r="F99" t="s">
-        <v>1455</v>
+        <v>1511</v>
       </c>
       <c r="G99" t="s">
-        <v>1466</v>
+        <v>1522</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
@@ -16996,7 +17597,7 @@
         <v>27</v>
       </c>
       <c r="B100" t="s">
-        <v>1449</v>
+        <v>1505</v>
       </c>
       <c r="C100" t="s">
         <v>708</v>
@@ -17008,10 +17609,10 @@
         <v>112</v>
       </c>
       <c r="F100" t="s">
-        <v>1450</v>
+        <v>1506</v>
       </c>
       <c r="G100" t="s">
-        <v>1467</v>
+        <v>1523</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
@@ -17031,10 +17632,10 @@
         <v>86</v>
       </c>
       <c r="F101" t="s">
-        <v>1455</v>
+        <v>1511</v>
       </c>
       <c r="G101" t="s">
-        <v>1468</v>
+        <v>1524</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
@@ -17042,7 +17643,7 @@
         <v>27</v>
       </c>
       <c r="B102" t="s">
-        <v>1449</v>
+        <v>1505</v>
       </c>
       <c r="C102" t="s">
         <v>715</v>
@@ -17054,10 +17655,10 @@
         <v>112</v>
       </c>
       <c r="F102" t="s">
-        <v>1450</v>
+        <v>1506</v>
       </c>
       <c r="G102" t="s">
-        <v>1469</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
@@ -17077,10 +17678,10 @@
         <v>86</v>
       </c>
       <c r="F103" t="s">
-        <v>1455</v>
+        <v>1511</v>
       </c>
       <c r="G103" t="s">
-        <v>1470</v>
+        <v>1526</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
@@ -17088,7 +17689,7 @@
         <v>27</v>
       </c>
       <c r="B104" t="s">
-        <v>1449</v>
+        <v>1505</v>
       </c>
       <c r="C104" t="s">
         <v>723</v>
@@ -17100,10 +17701,10 @@
         <v>112</v>
       </c>
       <c r="F104" t="s">
-        <v>1450</v>
+        <v>1506</v>
       </c>
       <c r="G104" t="s">
-        <v>1471</v>
+        <v>1527</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
@@ -17123,10 +17724,10 @@
         <v>26</v>
       </c>
       <c r="F105" t="s">
-        <v>1455</v>
+        <v>1511</v>
       </c>
       <c r="G105" t="s">
-        <v>1472</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
@@ -17134,7 +17735,7 @@
         <v>27</v>
       </c>
       <c r="B106" t="s">
-        <v>1449</v>
+        <v>1505</v>
       </c>
       <c r="C106" t="s">
         <v>732</v>
@@ -17146,10 +17747,10 @@
         <v>112</v>
       </c>
       <c r="F106" t="s">
-        <v>1450</v>
+        <v>1506</v>
       </c>
       <c r="G106" t="s">
-        <v>1473</v>
+        <v>1529</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
@@ -17169,10 +17770,10 @@
         <v>26</v>
       </c>
       <c r="F107" t="s">
-        <v>1455</v>
+        <v>1511</v>
       </c>
       <c r="G107" t="s">
-        <v>1474</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
@@ -17186,13 +17787,13 @@
         <v>740</v>
       </c>
       <c r="D108" t="s">
-        <v>1475</v>
+        <v>1531</v>
       </c>
       <c r="E108" t="s">
         <v>112</v>
       </c>
       <c r="F108" t="s">
-        <v>1455</v>
+        <v>1511</v>
       </c>
       <c r="G108" t="s">
         <v>741</v>
@@ -17209,13 +17810,13 @@
         <v>750</v>
       </c>
       <c r="D109" t="s">
-        <v>1475</v>
+        <v>1531</v>
       </c>
       <c r="E109" t="s">
         <v>112</v>
       </c>
       <c r="F109" t="s">
-        <v>1455</v>
+        <v>1511</v>
       </c>
       <c r="G109" t="s">
         <v>751</v>
@@ -17232,13 +17833,13 @@
         <v>758</v>
       </c>
       <c r="D110" t="s">
-        <v>1475</v>
+        <v>1531</v>
       </c>
       <c r="E110" t="s">
         <v>112</v>
       </c>
       <c r="F110" t="s">
-        <v>1455</v>
+        <v>1511</v>
       </c>
       <c r="G110" t="s">
         <v>759</v>
@@ -17255,13 +17856,13 @@
         <v>766</v>
       </c>
       <c r="D111" t="s">
-        <v>1475</v>
+        <v>1531</v>
       </c>
       <c r="E111" t="s">
         <v>112</v>
       </c>
       <c r="F111" t="s">
-        <v>1455</v>
+        <v>1511</v>
       </c>
       <c r="G111" t="s">
         <v>767</v>
@@ -17278,13 +17879,13 @@
         <v>774</v>
       </c>
       <c r="D112" t="s">
-        <v>1475</v>
+        <v>1531</v>
       </c>
       <c r="E112" t="s">
         <v>112</v>
       </c>
       <c r="F112" t="s">
-        <v>1455</v>
+        <v>1511</v>
       </c>
       <c r="G112" t="s">
         <v>775</v>
@@ -17301,13 +17902,13 @@
         <v>782</v>
       </c>
       <c r="D113" t="s">
-        <v>1475</v>
+        <v>1531</v>
       </c>
       <c r="E113" t="s">
         <v>112</v>
       </c>
       <c r="F113" t="s">
-        <v>1455</v>
+        <v>1511</v>
       </c>
       <c r="G113" t="s">
         <v>783</v>
@@ -17324,13 +17925,13 @@
         <v>790</v>
       </c>
       <c r="D114" t="s">
-        <v>1475</v>
+        <v>1531</v>
       </c>
       <c r="E114" t="s">
         <v>112</v>
       </c>
       <c r="F114" t="s">
-        <v>1455</v>
+        <v>1511</v>
       </c>
       <c r="G114" t="s">
         <v>791</v>
@@ -17347,13 +17948,13 @@
         <v>798</v>
       </c>
       <c r="D115" t="s">
-        <v>1475</v>
+        <v>1531</v>
       </c>
       <c r="E115" t="s">
         <v>112</v>
       </c>
       <c r="F115" t="s">
-        <v>1455</v>
+        <v>1511</v>
       </c>
       <c r="G115" t="s">
         <v>799</v>
@@ -17370,13 +17971,13 @@
         <v>806</v>
       </c>
       <c r="D116" t="s">
-        <v>1475</v>
+        <v>1531</v>
       </c>
       <c r="E116" t="s">
         <v>112</v>
       </c>
       <c r="F116" t="s">
-        <v>1455</v>
+        <v>1511</v>
       </c>
       <c r="G116" t="s">
         <v>807</v>
@@ -17393,13 +17994,13 @@
         <v>814</v>
       </c>
       <c r="D117" t="s">
-        <v>1475</v>
+        <v>1531</v>
       </c>
       <c r="E117" t="s">
         <v>112</v>
       </c>
       <c r="F117" t="s">
-        <v>1455</v>
+        <v>1511</v>
       </c>
       <c r="G117" t="s">
         <v>815</v>
@@ -17416,13 +18017,13 @@
         <v>821</v>
       </c>
       <c r="D118" t="s">
-        <v>1475</v>
+        <v>1531</v>
       </c>
       <c r="E118" t="s">
         <v>112</v>
       </c>
       <c r="F118" t="s">
-        <v>1455</v>
+        <v>1511</v>
       </c>
       <c r="G118" t="s">
         <v>823</v>
@@ -17439,13 +18040,13 @@
         <v>830</v>
       </c>
       <c r="D119" t="s">
-        <v>1475</v>
+        <v>1531</v>
       </c>
       <c r="E119" t="s">
         <v>112</v>
       </c>
       <c r="F119" t="s">
-        <v>1455</v>
+        <v>1511</v>
       </c>
       <c r="G119" t="s">
         <v>831</v>
@@ -17462,13 +18063,13 @@
         <v>837</v>
       </c>
       <c r="D120" t="s">
-        <v>1475</v>
+        <v>1531</v>
       </c>
       <c r="E120" t="s">
         <v>112</v>
       </c>
       <c r="F120" t="s">
-        <v>1455</v>
+        <v>1511</v>
       </c>
       <c r="G120" t="s">
         <v>838</v>
@@ -17485,13 +18086,13 @@
         <v>844</v>
       </c>
       <c r="D121" t="s">
-        <v>1475</v>
+        <v>1531</v>
       </c>
       <c r="E121" t="s">
         <v>112</v>
       </c>
       <c r="F121" t="s">
-        <v>1455</v>
+        <v>1511</v>
       </c>
       <c r="G121" t="s">
         <v>845</v>
@@ -17508,13 +18109,13 @@
         <v>852</v>
       </c>
       <c r="D122" t="s">
-        <v>1475</v>
+        <v>1531</v>
       </c>
       <c r="E122" t="s">
         <v>26</v>
       </c>
       <c r="F122" t="s">
-        <v>1455</v>
+        <v>1511</v>
       </c>
       <c r="G122" t="s">
         <v>853</v>
@@ -17531,13 +18132,13 @@
         <v>860</v>
       </c>
       <c r="D123" t="s">
-        <v>1475</v>
+        <v>1531</v>
       </c>
       <c r="E123" t="s">
         <v>112</v>
       </c>
       <c r="F123" t="s">
-        <v>1455</v>
+        <v>1511</v>
       </c>
       <c r="G123" t="s">
         <v>861</v>
@@ -17554,13 +18155,13 @@
         <v>868</v>
       </c>
       <c r="D124" t="s">
-        <v>1475</v>
+        <v>1531</v>
       </c>
       <c r="E124" t="s">
         <v>112</v>
       </c>
       <c r="F124" t="s">
-        <v>1455</v>
+        <v>1511</v>
       </c>
       <c r="G124" t="s">
         <v>869</v>
@@ -17577,13 +18178,13 @@
         <v>876</v>
       </c>
       <c r="D125" t="s">
-        <v>1475</v>
+        <v>1531</v>
       </c>
       <c r="E125" t="s">
         <v>112</v>
       </c>
       <c r="F125" t="s">
-        <v>1455</v>
+        <v>1511</v>
       </c>
       <c r="G125" t="s">
         <v>878</v>
@@ -17600,13 +18201,13 @@
         <v>885</v>
       </c>
       <c r="D126" t="s">
-        <v>1475</v>
+        <v>1531</v>
       </c>
       <c r="E126" t="s">
         <v>112</v>
       </c>
       <c r="F126" t="s">
-        <v>1455</v>
+        <v>1511</v>
       </c>
       <c r="G126" t="s">
         <v>886</v>
@@ -17623,13 +18224,13 @@
         <v>893</v>
       </c>
       <c r="D127" t="s">
-        <v>1475</v>
+        <v>1531</v>
       </c>
       <c r="E127" t="s">
         <v>112</v>
       </c>
       <c r="F127" t="s">
-        <v>1455</v>
+        <v>1511</v>
       </c>
       <c r="G127" t="s">
         <v>894</v>
@@ -17646,13 +18247,13 @@
         <v>901</v>
       </c>
       <c r="D128" t="s">
-        <v>1475</v>
+        <v>1531</v>
       </c>
       <c r="E128" t="s">
         <v>453</v>
       </c>
       <c r="F128" t="s">
-        <v>1455</v>
+        <v>1511</v>
       </c>
       <c r="G128" t="s">
         <v>902</v>
@@ -17669,13 +18270,13 @@
         <v>909</v>
       </c>
       <c r="D129" t="s">
-        <v>1475</v>
+        <v>1531</v>
       </c>
       <c r="E129" t="s">
         <v>112</v>
       </c>
       <c r="F129" t="s">
-        <v>1455</v>
+        <v>1511</v>
       </c>
       <c r="G129" t="s">
         <v>910</v>
@@ -17692,13 +18293,13 @@
         <v>916</v>
       </c>
       <c r="D130" t="s">
-        <v>1475</v>
+        <v>1531</v>
       </c>
       <c r="E130" t="s">
         <v>112</v>
       </c>
       <c r="F130" t="s">
-        <v>1455</v>
+        <v>1511</v>
       </c>
       <c r="G130" t="s">
         <v>917</v>
@@ -17715,13 +18316,13 @@
         <v>926</v>
       </c>
       <c r="D131" t="s">
-        <v>1475</v>
+        <v>1531</v>
       </c>
       <c r="E131" t="s">
         <v>112</v>
       </c>
       <c r="F131" t="s">
-        <v>1455</v>
+        <v>1511</v>
       </c>
       <c r="G131" t="s">
         <v>927</v>
@@ -17738,13 +18339,13 @@
         <v>934</v>
       </c>
       <c r="D132" t="s">
-        <v>1475</v>
+        <v>1531</v>
       </c>
       <c r="E132" t="s">
         <v>112</v>
       </c>
       <c r="F132" t="s">
-        <v>1455</v>
+        <v>1511</v>
       </c>
       <c r="G132" t="s">
         <v>935</v>
@@ -17761,13 +18362,13 @@
         <v>942</v>
       </c>
       <c r="D133" t="s">
-        <v>1475</v>
+        <v>1531</v>
       </c>
       <c r="E133" t="s">
         <v>112</v>
       </c>
       <c r="F133" t="s">
-        <v>1455</v>
+        <v>1511</v>
       </c>
       <c r="G133" t="s">
         <v>943</v>
@@ -17784,13 +18385,13 @@
         <v>950</v>
       </c>
       <c r="D134" t="s">
-        <v>1475</v>
+        <v>1531</v>
       </c>
       <c r="E134" t="s">
         <v>112</v>
       </c>
       <c r="F134" t="s">
-        <v>1455</v>
+        <v>1511</v>
       </c>
       <c r="G134" t="s">
         <v>951</v>
@@ -17807,13 +18408,13 @@
         <v>958</v>
       </c>
       <c r="D135" t="s">
-        <v>1475</v>
+        <v>1531</v>
       </c>
       <c r="E135" t="s">
         <v>112</v>
       </c>
       <c r="F135" t="s">
-        <v>1455</v>
+        <v>1511</v>
       </c>
       <c r="G135" t="s">
         <v>960</v>
@@ -17830,13 +18431,13 @@
         <v>967</v>
       </c>
       <c r="D136" t="s">
-        <v>1475</v>
+        <v>1531</v>
       </c>
       <c r="E136" t="s">
         <v>112</v>
       </c>
       <c r="F136" t="s">
-        <v>1455</v>
+        <v>1511</v>
       </c>
       <c r="G136" t="s">
         <v>968</v>
@@ -17853,13 +18454,13 @@
         <v>974</v>
       </c>
       <c r="D137" t="s">
-        <v>1475</v>
+        <v>1531</v>
       </c>
       <c r="E137" t="s">
         <v>112</v>
       </c>
       <c r="F137" t="s">
-        <v>1455</v>
+        <v>1511</v>
       </c>
       <c r="G137" t="s">
         <v>975</v>
@@ -17876,13 +18477,13 @@
         <v>981</v>
       </c>
       <c r="D138" t="s">
-        <v>1475</v>
+        <v>1531</v>
       </c>
       <c r="E138" t="s">
         <v>112</v>
       </c>
       <c r="F138" t="s">
-        <v>1455</v>
+        <v>1511</v>
       </c>
       <c r="G138" t="s">
         <v>982</v>
@@ -17899,13 +18500,13 @@
         <v>989</v>
       </c>
       <c r="D139" t="s">
-        <v>1475</v>
+        <v>1531</v>
       </c>
       <c r="E139" t="s">
         <v>112</v>
       </c>
       <c r="F139" t="s">
-        <v>1455</v>
+        <v>1511</v>
       </c>
       <c r="G139" t="s">
         <v>990</v>
@@ -17922,13 +18523,13 @@
         <v>997</v>
       </c>
       <c r="D140" t="s">
-        <v>1475</v>
+        <v>1531</v>
       </c>
       <c r="E140" t="s">
         <v>112</v>
       </c>
       <c r="F140" t="s">
-        <v>1455</v>
+        <v>1511</v>
       </c>
       <c r="G140" t="s">
         <v>998</v>
@@ -17945,13 +18546,13 @@
         <v>1006</v>
       </c>
       <c r="D141" t="s">
-        <v>1475</v>
+        <v>1531</v>
       </c>
       <c r="E141" t="s">
         <v>112</v>
       </c>
       <c r="F141" t="s">
-        <v>1455</v>
+        <v>1511</v>
       </c>
       <c r="G141" t="s">
         <v>1007</v>
@@ -17968,13 +18569,13 @@
         <v>1014</v>
       </c>
       <c r="D142" t="s">
-        <v>1475</v>
+        <v>1531</v>
       </c>
       <c r="E142" t="s">
         <v>112</v>
       </c>
       <c r="F142" t="s">
-        <v>1455</v>
+        <v>1511</v>
       </c>
       <c r="G142" t="s">
         <v>1015</v>
@@ -17991,13 +18592,13 @@
         <v>1021</v>
       </c>
       <c r="D143" t="s">
-        <v>1475</v>
+        <v>1531</v>
       </c>
       <c r="E143" t="s">
         <v>453</v>
       </c>
       <c r="F143" t="s">
-        <v>1455</v>
+        <v>1511</v>
       </c>
       <c r="G143" t="s">
         <v>1022</v>
@@ -18014,13 +18615,13 @@
         <v>1029</v>
       </c>
       <c r="D144" t="s">
-        <v>1475</v>
+        <v>1531</v>
       </c>
       <c r="E144" t="s">
         <v>112</v>
       </c>
       <c r="F144" t="s">
-        <v>1455</v>
+        <v>1511</v>
       </c>
       <c r="G144" t="s">
         <v>1031</v>
@@ -18037,13 +18638,13 @@
         <v>1037</v>
       </c>
       <c r="D145" t="s">
-        <v>1475</v>
+        <v>1531</v>
       </c>
       <c r="E145" t="s">
         <v>112</v>
       </c>
       <c r="F145" t="s">
-        <v>1455</v>
+        <v>1511</v>
       </c>
       <c r="G145" t="s">
         <v>1038</v>
@@ -18060,13 +18661,13 @@
         <v>1045</v>
       </c>
       <c r="D146" t="s">
-        <v>1475</v>
+        <v>1531</v>
       </c>
       <c r="E146" t="s">
         <v>112</v>
       </c>
       <c r="F146" t="s">
-        <v>1455</v>
+        <v>1511</v>
       </c>
       <c r="G146" t="s">
         <v>1046</v>
@@ -18083,13 +18684,13 @@
         <v>1053</v>
       </c>
       <c r="D147" t="s">
-        <v>1475</v>
+        <v>1531</v>
       </c>
       <c r="E147" t="s">
         <v>112</v>
       </c>
       <c r="F147" t="s">
-        <v>1455</v>
+        <v>1511</v>
       </c>
       <c r="G147" t="s">
         <v>1055</v>
@@ -18106,13 +18707,13 @@
         <v>1061</v>
       </c>
       <c r="D148" t="s">
-        <v>1475</v>
+        <v>1531</v>
       </c>
       <c r="E148" t="s">
         <v>112</v>
       </c>
       <c r="F148" t="s">
-        <v>1455</v>
+        <v>1511</v>
       </c>
       <c r="G148" t="s">
         <v>1062</v>
@@ -18129,13 +18730,13 @@
         <v>1068</v>
       </c>
       <c r="D149" t="s">
-        <v>1475</v>
+        <v>1531</v>
       </c>
       <c r="E149" t="s">
         <v>95</v>
       </c>
       <c r="F149" t="s">
-        <v>1455</v>
+        <v>1511</v>
       </c>
       <c r="G149" t="s">
         <v>1069</v>
@@ -18152,13 +18753,13 @@
         <v>1076</v>
       </c>
       <c r="D150" t="s">
-        <v>1475</v>
+        <v>1531</v>
       </c>
       <c r="E150" t="s">
         <v>112</v>
       </c>
       <c r="F150" t="s">
-        <v>1455</v>
+        <v>1511</v>
       </c>
       <c r="G150" t="s">
         <v>1078</v>
@@ -18175,13 +18776,13 @@
         <v>1085</v>
       </c>
       <c r="D151" t="s">
-        <v>1475</v>
+        <v>1531</v>
       </c>
       <c r="E151" t="s">
         <v>95</v>
       </c>
       <c r="F151" t="s">
-        <v>1455</v>
+        <v>1511</v>
       </c>
       <c r="G151" t="s">
         <v>1086</v>
@@ -18198,13 +18799,13 @@
         <v>1093</v>
       </c>
       <c r="D152" t="s">
-        <v>1475</v>
+        <v>1531</v>
       </c>
       <c r="E152" t="s">
         <v>112</v>
       </c>
       <c r="F152" t="s">
-        <v>1455</v>
+        <v>1511</v>
       </c>
       <c r="G152" t="s">
         <v>1094</v>
@@ -18221,13 +18822,13 @@
         <v>1102</v>
       </c>
       <c r="D153" t="s">
-        <v>1475</v>
+        <v>1531</v>
       </c>
       <c r="E153" t="s">
         <v>112</v>
       </c>
       <c r="F153" t="s">
-        <v>1455</v>
+        <v>1511</v>
       </c>
       <c r="G153" t="s">
         <v>1103</v>
@@ -18244,13 +18845,13 @@
         <v>1109</v>
       </c>
       <c r="D154" t="s">
-        <v>1475</v>
+        <v>1531</v>
       </c>
       <c r="E154" t="s">
         <v>453</v>
       </c>
       <c r="F154" t="s">
-        <v>1455</v>
+        <v>1511</v>
       </c>
       <c r="G154" t="s">
         <v>1110</v>
@@ -18267,13 +18868,13 @@
         <v>1117</v>
       </c>
       <c r="D155" t="s">
-        <v>1475</v>
+        <v>1531</v>
       </c>
       <c r="E155" t="s">
         <v>112</v>
       </c>
       <c r="F155" t="s">
-        <v>1455</v>
+        <v>1511</v>
       </c>
       <c r="G155" t="s">
         <v>1118</v>
@@ -18290,13 +18891,13 @@
         <v>1124</v>
       </c>
       <c r="D156" t="s">
-        <v>1475</v>
+        <v>1531</v>
       </c>
       <c r="E156" t="s">
         <v>95</v>
       </c>
       <c r="F156" t="s">
-        <v>1455</v>
+        <v>1511</v>
       </c>
       <c r="G156" t="s">
         <v>1125</v>
@@ -18313,13 +18914,13 @@
         <v>1132</v>
       </c>
       <c r="D157" t="s">
-        <v>1475</v>
+        <v>1531</v>
       </c>
       <c r="E157" t="s">
         <v>112</v>
       </c>
       <c r="F157" t="s">
-        <v>1455</v>
+        <v>1511</v>
       </c>
       <c r="G157" t="s">
         <v>1133</v>
@@ -18336,13 +18937,13 @@
         <v>1139</v>
       </c>
       <c r="D158" t="s">
-        <v>1475</v>
+        <v>1531</v>
       </c>
       <c r="E158" t="s">
         <v>112</v>
       </c>
       <c r="F158" t="s">
-        <v>1455</v>
+        <v>1511</v>
       </c>
       <c r="G158" t="s">
         <v>1140</v>
@@ -18359,16 +18960,177 @@
         <v>1148</v>
       </c>
       <c r="D159" t="s">
-        <v>1475</v>
+        <v>1531</v>
       </c>
       <c r="E159" t="s">
         <v>112</v>
       </c>
       <c r="F159" t="s">
-        <v>1455</v>
+        <v>1511</v>
       </c>
       <c r="G159" t="s">
         <v>1149</v>
+      </c>
+    </row>
+    <row r="160" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A160" t="s">
+        <v>27</v>
+      </c>
+      <c r="B160" t="s">
+        <v>1158</v>
+      </c>
+      <c r="C160" t="s">
+        <v>1156</v>
+      </c>
+      <c r="D160" t="s">
+        <v>1531</v>
+      </c>
+      <c r="E160" t="s">
+        <v>112</v>
+      </c>
+      <c r="F160" t="s">
+        <v>1511</v>
+      </c>
+      <c r="G160" t="s">
+        <v>1157</v>
+      </c>
+    </row>
+    <row r="161" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A161" t="s">
+        <v>27</v>
+      </c>
+      <c r="B161" t="s">
+        <v>1158</v>
+      </c>
+      <c r="C161" t="s">
+        <v>1165</v>
+      </c>
+      <c r="D161" t="s">
+        <v>1531</v>
+      </c>
+      <c r="E161" t="s">
+        <v>95</v>
+      </c>
+      <c r="F161" t="s">
+        <v>1511</v>
+      </c>
+      <c r="G161" t="s">
+        <v>1166</v>
+      </c>
+    </row>
+    <row r="162" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A162" t="s">
+        <v>27</v>
+      </c>
+      <c r="B162" t="s">
+        <v>1158</v>
+      </c>
+      <c r="C162" t="s">
+        <v>1173</v>
+      </c>
+      <c r="D162" t="s">
+        <v>1531</v>
+      </c>
+      <c r="E162" t="s">
+        <v>112</v>
+      </c>
+      <c r="F162" t="s">
+        <v>1511</v>
+      </c>
+      <c r="G162" t="s">
+        <v>1175</v>
+      </c>
+    </row>
+    <row r="163" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A163" t="s">
+        <v>27</v>
+      </c>
+      <c r="B163" t="s">
+        <v>1158</v>
+      </c>
+      <c r="C163" t="s">
+        <v>1181</v>
+      </c>
+      <c r="D163" t="s">
+        <v>1531</v>
+      </c>
+      <c r="E163" t="s">
+        <v>112</v>
+      </c>
+      <c r="F163" t="s">
+        <v>1511</v>
+      </c>
+      <c r="G163" t="s">
+        <v>1182</v>
+      </c>
+    </row>
+    <row r="164" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A164" t="s">
+        <v>27</v>
+      </c>
+      <c r="B164" t="s">
+        <v>1158</v>
+      </c>
+      <c r="C164" t="s">
+        <v>1188</v>
+      </c>
+      <c r="D164" t="s">
+        <v>1531</v>
+      </c>
+      <c r="E164" t="s">
+        <v>112</v>
+      </c>
+      <c r="F164" t="s">
+        <v>1511</v>
+      </c>
+      <c r="G164" t="s">
+        <v>1189</v>
+      </c>
+    </row>
+    <row r="165" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A165" t="s">
+        <v>27</v>
+      </c>
+      <c r="B165" t="s">
+        <v>1158</v>
+      </c>
+      <c r="C165" t="s">
+        <v>1195</v>
+      </c>
+      <c r="D165" t="s">
+        <v>1531</v>
+      </c>
+      <c r="E165" t="s">
+        <v>112</v>
+      </c>
+      <c r="F165" t="s">
+        <v>1511</v>
+      </c>
+      <c r="G165" t="s">
+        <v>1196</v>
+      </c>
+    </row>
+    <row r="166" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A166" t="s">
+        <v>27</v>
+      </c>
+      <c r="B166" t="s">
+        <v>1158</v>
+      </c>
+      <c r="C166" t="s">
+        <v>1203</v>
+      </c>
+      <c r="D166" t="s">
+        <v>1531</v>
+      </c>
+      <c r="E166" t="s">
+        <v>95</v>
+      </c>
+      <c r="F166" t="s">
+        <v>1511</v>
+      </c>
+      <c r="G166" t="s">
+        <v>1204</v>
       </c>
     </row>
   </sheetData>
@@ -18382,7 +19144,7 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>1476</v>
+        <v>1532</v>
       </c>
       <c r="B1"/>
       <c r="C1"/>
@@ -18390,7 +19152,7 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1477</v>
+        <v>1533</v>
       </c>
       <c r="B2"/>
       <c r="C2"/>
@@ -18401,181 +19163,181 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>1478</v>
+        <v>1534</v>
       </c>
       <c r="C3" t="s">
-        <v>1479</v>
+        <v>1535</v>
       </c>
       <c r="D3" t="s">
-        <v>1480</v>
+        <v>1536</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1481</v>
+        <v>1537</v>
       </c>
       <c r="B4" t="s">
-        <v>1482</v>
+        <v>1538</v>
       </c>
       <c r="C4" t="s">
-        <v>1483</v>
+        <v>1539</v>
       </c>
       <c r="D4" t="s">
-        <v>1484</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1485</v>
+        <v>1541</v>
       </c>
       <c r="B5" t="s">
-        <v>1482</v>
+        <v>1538</v>
       </c>
       <c r="C5" t="s">
-        <v>1486</v>
+        <v>1542</v>
       </c>
       <c r="D5" t="s">
-        <v>1487</v>
+        <v>1543</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>1488</v>
+        <v>1544</v>
       </c>
       <c r="B6" t="s">
-        <v>1482</v>
+        <v>1538</v>
       </c>
       <c r="C6" t="s">
-        <v>1489</v>
+        <v>1545</v>
       </c>
       <c r="D6" t="s">
-        <v>1490</v>
+        <v>1546</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>1491</v>
+        <v>1547</v>
       </c>
       <c r="B7" t="s">
-        <v>1482</v>
+        <v>1538</v>
       </c>
       <c r="C7" t="s">
-        <v>1492</v>
+        <v>1548</v>
       </c>
       <c r="D7" t="s">
-        <v>1493</v>
+        <v>1549</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>1494</v>
+        <v>1550</v>
       </c>
       <c r="B8" t="s">
-        <v>1482</v>
+        <v>1538</v>
       </c>
       <c r="C8" t="s">
-        <v>1495</v>
+        <v>1551</v>
       </c>
       <c r="D8" t="s">
-        <v>1496</v>
+        <v>1552</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>1497</v>
+        <v>1553</v>
       </c>
       <c r="B9" t="s">
-        <v>1498</v>
+        <v>1554</v>
       </c>
       <c r="C9" t="s">
-        <v>1499</v>
+        <v>1555</v>
       </c>
       <c r="D9" t="s">
-        <v>1500</v>
+        <v>1556</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>1501</v>
+        <v>1557</v>
       </c>
       <c r="B10" t="s">
-        <v>1498</v>
+        <v>1554</v>
       </c>
       <c r="C10" t="s">
-        <v>1502</v>
+        <v>1558</v>
       </c>
       <c r="D10" t="s">
-        <v>1503</v>
+        <v>1559</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>1504</v>
+        <v>1560</v>
       </c>
       <c r="B11" t="s">
-        <v>1498</v>
+        <v>1554</v>
       </c>
       <c r="C11" t="s">
-        <v>1505</v>
+        <v>1561</v>
       </c>
       <c r="D11" t="s">
-        <v>1506</v>
+        <v>1562</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>1507</v>
+        <v>1563</v>
       </c>
       <c r="B12" t="s">
-        <v>1508</v>
+        <v>1564</v>
       </c>
       <c r="C12" t="s">
-        <v>1509</v>
+        <v>1565</v>
       </c>
       <c r="D12" t="s">
-        <v>1510</v>
+        <v>1566</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>1511</v>
+        <v>1567</v>
       </c>
       <c r="B13" t="s">
-        <v>1508</v>
+        <v>1564</v>
       </c>
       <c r="C13" t="s">
-        <v>1512</v>
+        <v>1568</v>
       </c>
       <c r="D13" t="s">
-        <v>1513</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>1514</v>
+        <v>1570</v>
       </c>
       <c r="B14" t="s">
         <v>877</v>
       </c>
       <c r="C14" t="s">
-        <v>1515</v>
+        <v>1571</v>
       </c>
       <c r="D14" t="s">
-        <v>1516</v>
+        <v>1572</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>1517</v>
+        <v>1573</v>
       </c>
       <c r="B15" t="s">
         <v>877</v>
       </c>
       <c r="C15" t="s">
-        <v>1518</v>
+        <v>1574</v>
       </c>
       <c r="D15" t="s">
-        <v>1519</v>
+        <v>1575</v>
       </c>
     </row>
   </sheetData>
@@ -18594,7 +19356,7 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>1520</v>
+        <v>1576</v>
       </c>
       <c r="B1"/>
       <c r="C1"/>
@@ -18602,133 +19364,133 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>1521</v>
+        <v>1577</v>
       </c>
       <c r="B3" t="s">
-        <v>1522</v>
+        <v>1578</v>
       </c>
       <c r="C3" t="s">
-        <v>1523</v>
+        <v>1579</v>
       </c>
       <c r="D3" t="s">
-        <v>1524</v>
+        <v>1580</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1196</v>
+        <v>1251</v>
       </c>
       <c r="B4" t="s">
-        <v>1525</v>
+        <v>1581</v>
       </c>
       <c r="C4" t="s">
-        <v>1526</v>
+        <v>1582</v>
       </c>
       <c r="D4" t="s">
-        <v>1527</v>
+        <v>1583</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1201</v>
+        <v>1256</v>
       </c>
       <c r="B5" t="s">
-        <v>1528</v>
+        <v>1584</v>
       </c>
       <c r="C5" t="s">
-        <v>1529</v>
+        <v>1585</v>
       </c>
       <c r="D5" t="s">
-        <v>1530</v>
+        <v>1586</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>1205</v>
+        <v>1260</v>
       </c>
       <c r="B6" t="s">
-        <v>1531</v>
+        <v>1587</v>
       </c>
       <c r="C6" t="s">
-        <v>1532</v>
+        <v>1588</v>
       </c>
       <c r="D6" t="s">
-        <v>1533</v>
+        <v>1589</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>1209</v>
+        <v>1264</v>
       </c>
       <c r="B7" t="s">
-        <v>1534</v>
+        <v>1590</v>
       </c>
       <c r="C7" t="s">
-        <v>1535</v>
+        <v>1591</v>
       </c>
       <c r="D7" t="s">
-        <v>1536</v>
+        <v>1592</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>1213</v>
+        <v>1268</v>
       </c>
       <c r="B8" t="s">
-        <v>1537</v>
+        <v>1593</v>
       </c>
       <c r="C8" t="s">
-        <v>1538</v>
+        <v>1594</v>
       </c>
       <c r="D8" t="s">
-        <v>1539</v>
+        <v>1595</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>1217</v>
+        <v>1272</v>
       </c>
       <c r="B9" t="s">
-        <v>1540</v>
+        <v>1596</v>
       </c>
       <c r="C9" t="s">
-        <v>1541</v>
+        <v>1597</v>
       </c>
       <c r="D9" t="s">
-        <v>1542</v>
+        <v>1598</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>1221</v>
+        <v>1276</v>
       </c>
       <c r="B10" t="s">
-        <v>1543</v>
+        <v>1599</v>
       </c>
       <c r="C10" t="s">
-        <v>1544</v>
+        <v>1600</v>
       </c>
       <c r="D10" t="s">
-        <v>1545</v>
+        <v>1601</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>1225</v>
+        <v>1280</v>
       </c>
       <c r="B11" t="s">
-        <v>1546</v>
+        <v>1602</v>
       </c>
       <c r="C11" t="s">
-        <v>1547</v>
+        <v>1603</v>
       </c>
       <c r="D11" t="s">
-        <v>1548</v>
+        <v>1604</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>1549</v>
+        <v>1605</v>
       </c>
       <c r="B13"/>
       <c r="C13"/>
@@ -18736,72 +19498,72 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>1550</v>
+        <v>1606</v>
       </c>
       <c r="B14" t="s">
         <v>28</v>
       </c>
       <c r="C14" t="s">
-        <v>1551</v>
+        <v>1607</v>
       </c>
       <c r="D14" t="s">
-        <v>1552</v>
+        <v>1608</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>1553</v>
+        <v>1609</v>
       </c>
       <c r="B15" t="s">
         <v>29</v>
       </c>
       <c r="C15" t="s">
-        <v>1554</v>
+        <v>1610</v>
       </c>
       <c r="D15" t="s">
-        <v>1555</v>
+        <v>1611</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>1556</v>
+        <v>1612</v>
       </c>
       <c r="B16" t="s">
         <v>29</v>
       </c>
       <c r="C16" t="s">
-        <v>1557</v>
+        <v>1613</v>
       </c>
       <c r="D16" t="s">
-        <v>1558</v>
+        <v>1614</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>1559</v>
+        <v>1615</v>
       </c>
       <c r="B17" t="s">
         <v>29</v>
       </c>
       <c r="C17" t="s">
-        <v>1560</v>
+        <v>1616</v>
       </c>
       <c r="D17" t="s">
-        <v>1561</v>
+        <v>1617</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>1562</v>
+        <v>1618</v>
       </c>
       <c r="B18" t="s">
-        <v>1563</v>
+        <v>1619</v>
       </c>
       <c r="C18" t="s">
-        <v>1564</v>
+        <v>1620</v>
       </c>
       <c r="D18" t="s">
-        <v>1565</v>
+        <v>1621</v>
       </c>
     </row>
   </sheetData>
@@ -18820,7 +19582,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>1566</v>
+        <v>1622</v>
       </c>
       <c r="B1"/>
       <c r="C1"/>
@@ -18830,7 +19592,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1567</v>
+        <v>1623</v>
       </c>
       <c r="B2"/>
       <c r="C2"/>
@@ -18840,99 +19602,99 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1568</v>
+        <v>1624</v>
       </c>
       <c r="B4" t="s">
-        <v>1569</v>
+        <v>1625</v>
       </c>
       <c r="C4" t="s">
-        <v>1570</v>
+        <v>1626</v>
       </c>
       <c r="D4" t="s">
-        <v>1571</v>
+        <v>1627</v>
       </c>
       <c r="E4" t="s">
-        <v>1572</v>
+        <v>1628</v>
       </c>
       <c r="F4" t="s">
-        <v>1573</v>
+        <v>1629</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1574</v>
+        <v>1630</v>
       </c>
       <c r="B5" t="s">
-        <v>1575</v>
+        <v>1631</v>
       </c>
       <c r="C5" t="s">
-        <v>1576</v>
+        <v>1632</v>
       </c>
       <c r="D5" t="s">
-        <v>1577</v>
+        <v>1633</v>
       </c>
       <c r="E5" t="s">
-        <v>1578</v>
+        <v>1634</v>
       </c>
       <c r="F5" t="s">
-        <v>1579</v>
+        <v>1635</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>1580</v>
+        <v>1636</v>
       </c>
       <c r="B6" t="s">
-        <v>1581</v>
+        <v>1637</v>
       </c>
       <c r="C6" t="s">
-        <v>1582</v>
+        <v>1638</v>
       </c>
       <c r="D6" t="s">
-        <v>1583</v>
+        <v>1639</v>
       </c>
       <c r="E6" t="s">
-        <v>1584</v>
+        <v>1640</v>
       </c>
       <c r="F6" t="s">
-        <v>1585</v>
+        <v>1641</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>1586</v>
+        <v>1642</v>
       </c>
       <c r="B7" t="s">
-        <v>1581</v>
+        <v>1637</v>
       </c>
       <c r="C7" t="s">
-        <v>1587</v>
+        <v>1643</v>
       </c>
       <c r="D7" t="s">
-        <v>1588</v>
+        <v>1644</v>
       </c>
       <c r="E7" t="s">
-        <v>1589</v>
+        <v>1645</v>
       </c>
       <c r="F7" t="s">
-        <v>1590</v>
+        <v>1646</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>1591</v>
+        <v>1647</v>
       </c>
       <c r="B8" t="s">
-        <v>1592</v>
+        <v>1648</v>
       </c>
       <c r="C8" t="s">
-        <v>1593</v>
+        <v>1649</v>
       </c>
       <c r="D8" t="s">
-        <v>1594</v>
+        <v>1650</v>
       </c>
       <c r="E8" t="s">
-        <v>1595</v>
+        <v>1651</v>
       </c>
       <c r="F8" t="s">
         <v>629</v>
@@ -18940,19 +19702,19 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>1596</v>
+        <v>1652</v>
       </c>
       <c r="B9" t="s">
-        <v>1597</v>
+        <v>1653</v>
       </c>
       <c r="C9" t="s">
-        <v>1598</v>
+        <v>1654</v>
       </c>
       <c r="D9" t="s">
-        <v>1599</v>
+        <v>1655</v>
       </c>
       <c r="E9" t="s">
-        <v>1600</v>
+        <v>1656</v>
       </c>
       <c r="F9" t="s">
         <v>369</v>
@@ -18960,39 +19722,39 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>1601</v>
+        <v>1657</v>
       </c>
       <c r="B10" t="s">
-        <v>1602</v>
+        <v>1658</v>
       </c>
       <c r="C10" t="s">
-        <v>1603</v>
+        <v>1659</v>
       </c>
       <c r="D10" t="s">
-        <v>1604</v>
+        <v>1660</v>
       </c>
       <c r="E10" t="s">
-        <v>1605</v>
+        <v>1661</v>
       </c>
       <c r="F10" t="s">
-        <v>1606</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>1607</v>
+        <v>1663</v>
       </c>
       <c r="B11" t="s">
-        <v>1608</v>
+        <v>1664</v>
       </c>
       <c r="C11" t="s">
-        <v>1609</v>
+        <v>1665</v>
       </c>
       <c r="D11" t="s">
-        <v>1610</v>
+        <v>1666</v>
       </c>
       <c r="E11" t="s">
-        <v>1611</v>
+        <v>1667</v>
       </c>
       <c r="F11" t="s">
         <v>47</v>
@@ -19000,99 +19762,99 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>1612</v>
+        <v>1668</v>
       </c>
       <c r="B12" t="s">
-        <v>1613</v>
+        <v>1669</v>
       </c>
       <c r="C12" t="s">
-        <v>1614</v>
+        <v>1670</v>
       </c>
       <c r="D12" t="s">
-        <v>1615</v>
+        <v>1671</v>
       </c>
       <c r="E12" t="s">
-        <v>1616</v>
+        <v>1672</v>
       </c>
       <c r="F12" t="s">
-        <v>1617</v>
+        <v>1673</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>1618</v>
+        <v>1674</v>
       </c>
       <c r="B13" t="s">
-        <v>1619</v>
+        <v>1675</v>
       </c>
       <c r="C13" t="s">
-        <v>1620</v>
+        <v>1676</v>
       </c>
       <c r="D13" t="s">
-        <v>1621</v>
+        <v>1677</v>
       </c>
       <c r="E13" t="s">
-        <v>1622</v>
+        <v>1678</v>
       </c>
       <c r="F13" t="s">
-        <v>1623</v>
+        <v>1679</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>1624</v>
+        <v>1680</v>
       </c>
       <c r="B14" t="s">
-        <v>1625</v>
+        <v>1681</v>
       </c>
       <c r="C14" t="s">
-        <v>1626</v>
+        <v>1682</v>
       </c>
       <c r="D14" t="s">
-        <v>1627</v>
+        <v>1683</v>
       </c>
       <c r="E14" t="s">
-        <v>1628</v>
+        <v>1684</v>
       </c>
       <c r="F14" t="s">
-        <v>1629</v>
+        <v>1685</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>1630</v>
+        <v>1686</v>
       </c>
       <c r="B15" t="s">
-        <v>1631</v>
+        <v>1687</v>
       </c>
       <c r="C15" t="s">
-        <v>1632</v>
+        <v>1688</v>
       </c>
       <c r="D15" t="s">
-        <v>1633</v>
+        <v>1689</v>
       </c>
       <c r="E15" t="s">
-        <v>1634</v>
+        <v>1690</v>
       </c>
       <c r="F15" t="s">
-        <v>1635</v>
+        <v>1691</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>1636</v>
+        <v>1692</v>
       </c>
       <c r="B16" t="s">
-        <v>1637</v>
+        <v>1693</v>
       </c>
       <c r="C16" t="s">
-        <v>1638</v>
+        <v>1694</v>
       </c>
       <c r="D16" t="s">
-        <v>1639</v>
+        <v>1695</v>
       </c>
       <c r="E16" t="s">
-        <v>1640</v>
+        <v>1696</v>
       </c>
       <c r="F16" t="s">
         <v>207</v>
@@ -19100,19 +19862,19 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>1641</v>
+        <v>1697</v>
       </c>
       <c r="B17" t="s">
-        <v>1642</v>
+        <v>1698</v>
       </c>
       <c r="C17" t="s">
-        <v>1643</v>
+        <v>1699</v>
       </c>
       <c r="D17" t="s">
-        <v>1644</v>
+        <v>1700</v>
       </c>
       <c r="E17" t="s">
-        <v>1645</v>
+        <v>1701</v>
       </c>
       <c r="F17" t="s">
         <v>378</v>
@@ -19134,7 +19896,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>1646</v>
+        <v>1702</v>
       </c>
       <c r="B1"/>
       <c r="C1"/>
@@ -19144,7 +19906,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1647</v>
+        <v>1703</v>
       </c>
       <c r="B2"/>
       <c r="C2"/>
@@ -19154,162 +19916,162 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1648</v>
+        <v>1704</v>
       </c>
       <c r="B4" t="s">
-        <v>1546</v>
+        <v>1602</v>
       </c>
       <c r="C4" t="s">
-        <v>1649</v>
+        <v>1705</v>
       </c>
       <c r="D4" t="s">
-        <v>1650</v>
+        <v>1706</v>
       </c>
       <c r="E4" t="s">
-        <v>1193</v>
+        <v>1248</v>
       </c>
       <c r="F4" t="s">
-        <v>1651</v>
+        <v>1707</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1196</v>
+        <v>1251</v>
       </c>
       <c r="B5" t="s">
-        <v>1652</v>
+        <v>1708</v>
       </c>
       <c r="C5" t="s">
-        <v>1653</v>
+        <v>1709</v>
       </c>
       <c r="D5" t="s">
-        <v>1654</v>
+        <v>1710</v>
       </c>
       <c r="E5" t="s">
-        <v>1655</v>
+        <v>1711</v>
       </c>
       <c r="F5" t="s">
-        <v>1656</v>
+        <v>1712</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>1201</v>
+        <v>1256</v>
       </c>
       <c r="B6" t="s">
-        <v>1657</v>
+        <v>1713</v>
       </c>
       <c r="C6" t="s">
-        <v>1658</v>
+        <v>1714</v>
       </c>
       <c r="D6" t="s">
-        <v>1659</v>
+        <v>1715</v>
       </c>
       <c r="E6" t="s">
-        <v>1660</v>
+        <v>1716</v>
       </c>
       <c r="F6" t="s">
-        <v>1656</v>
+        <v>1712</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>1205</v>
+        <v>1260</v>
       </c>
       <c r="B7" t="s">
-        <v>1661</v>
+        <v>1717</v>
       </c>
       <c r="C7" t="s">
-        <v>1662</v>
+        <v>1718</v>
       </c>
       <c r="D7" t="s">
-        <v>1663</v>
+        <v>1719</v>
       </c>
       <c r="E7" t="s">
-        <v>1664</v>
+        <v>1720</v>
       </c>
       <c r="F7" t="s">
-        <v>1656</v>
+        <v>1712</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>1209</v>
+        <v>1264</v>
       </c>
       <c r="B8" t="s">
-        <v>1665</v>
+        <v>1721</v>
       </c>
       <c r="C8" t="s">
-        <v>1666</v>
+        <v>1722</v>
       </c>
       <c r="D8" t="s">
-        <v>1667</v>
+        <v>1723</v>
       </c>
       <c r="E8" t="s">
-        <v>1668</v>
+        <v>1724</v>
       </c>
       <c r="F8" t="s">
-        <v>1656</v>
+        <v>1712</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>1213</v>
+        <v>1268</v>
       </c>
       <c r="B9" t="s">
-        <v>1669</v>
+        <v>1725</v>
       </c>
       <c r="C9" t="s">
-        <v>1670</v>
+        <v>1726</v>
       </c>
       <c r="D9" t="s">
-        <v>1671</v>
+        <v>1727</v>
       </c>
       <c r="E9" t="s">
         <v>877</v>
       </c>
       <c r="F9" t="s">
-        <v>1672</v>
+        <v>1728</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>1217</v>
+        <v>1272</v>
       </c>
       <c r="B10" t="s">
-        <v>1673</v>
+        <v>1729</v>
       </c>
       <c r="C10" t="s">
-        <v>1674</v>
+        <v>1730</v>
       </c>
       <c r="D10" t="s">
-        <v>1675</v>
+        <v>1731</v>
       </c>
       <c r="E10" t="s">
-        <v>1676</v>
+        <v>1732</v>
       </c>
       <c r="F10" t="s">
-        <v>1672</v>
+        <v>1728</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>1221</v>
+        <v>1276</v>
       </c>
       <c r="B11" t="s">
-        <v>1677</v>
+        <v>1733</v>
       </c>
       <c r="C11" t="s">
-        <v>1678</v>
+        <v>1734</v>
       </c>
       <c r="D11" t="s">
-        <v>1679</v>
+        <v>1735</v>
       </c>
       <c r="E11" t="s">
-        <v>1680</v>
+        <v>1736</v>
       </c>
       <c r="F11" t="s">
-        <v>1681</v>
+        <v>1737</v>
       </c>
     </row>
   </sheetData>

--- a/audits/FORTLESS_MASTER_SECURITY_UI_BUG_TRACKER.xlsx
+++ b/audits/FORTLESS_MASTER_SECURITY_UI_BUG_TRACKER.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4478" uniqueCount="1738">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4666" uniqueCount="1797">
   <si>
     <t>FORTLESS   /   ENGINEERING FINDINGS REGISTER</t>
   </si>
@@ -2844,7 +2844,7 @@
     <t>Test: a user with two memberships keeps their chosen workspace across requests and after accepting an invite.</t>
   </si>
   <si>
-    <t>[CONFIRMED_CODE] Reproduced locally with the proof script.</t>
+    <t>[CONFIRMED_CODE] Reproduced locally with the proof script. | Batch 8: if the oldest workspace is LOCKED the session silently moves to the next ACTIVE workspace (authenticateSession query), with no message.</t>
   </si>
   <si>
     <t>NEW-369</t>
@@ -3585,6 +3585,9 @@
     <t>Test: VIEWER gets 403; an account flagged by staff does not expose the staff reason in the export.</t>
   </si>
   <si>
+    <t>[CONFIRMED_CODE] Source trace. | Batch 8: GET /api/v1/audit (src/server.ts:2441) has the same exposure and also returns ip_address and the raw metadata of all members to every role.</t>
+  </si>
+  <si>
     <t>NEW-400</t>
   </si>
   <si>
@@ -3654,6 +3657,171 @@
     <t>[CONFIRMED_CODE] Source trace; duplicate needs a send slower than the lease (TEST_NEEDED).</t>
   </si>
   <si>
+    <t>NEW-403</t>
+  </si>
+  <si>
+    <t>Quote tax country and B2B flag are chosen by the client; the checkout UI hardcodes DE and ignores the billing profile</t>
+  </si>
+  <si>
+    <t>a236de9</t>
+  </si>
+  <si>
+    <t>src/frontend/client/pages/deploy/index.ts:236-246; src/server.ts:1162-1178; src/modules/pricing/quote.ts:46-80,215</t>
+  </si>
+  <si>
+    <t>POST /quotes takes billingCountry, isB2B and taxId from the request body and resolveTaxRate looks the VAT rate up from that country. The deploy page always sends billingCountry "DE" and isB2B false, and never reads the saved billing profile. A direct API call can pick any country in VAT_RATES.</t>
+  </si>
+  <si>
+    <t>Customers can choose the lowest listed VAT rate, and every UI order is taxed as German consumer sales even for business or non-DE customers, so invoices carry the wrong jurisdiction (compliance exposure).</t>
+  </si>
+  <si>
+    <t>Derive country and B2B status from the validated billing profile server-side and ignore body values; require the profile before checkout.</t>
+  </si>
+  <si>
+    <t>Test: a quote request with a different country than the billing profile uses the profile rate; checkout without a profile is refused.</t>
+  </si>
+  <si>
+    <t>[CONFIRMED_CODE] Source trace; distinct from NEW-304 (unverified tax ID).</t>
+  </si>
+  <si>
+    <t>NEW-404</t>
+  </si>
+  <si>
+    <t>The shared-service "viewer" preset can send console commands and read file contents and database listings</t>
+  </si>
+  <si>
+    <t>src/modules/provisioning/service-access.ts:5-8; src/frontend/client/pages/services/index.ts:104-125</t>
+  </si>
+  <si>
+    <t>PERMISSION_PRESETS.viewer includes websocket.connect and control.console (Pterodactyl uses control.console to send commands), file.read-content and database.read. The console tab renders with an input whenever websocket.connect is allowed, and the same permissions are pushed to the panel subuser.</t>
+  </si>
+  <si>
+    <t>A person invited as a "viewer" can type commands (stop, op, deletion commands in many games) and read configuration files that contain credentials, so the preset is not read-only.</t>
+  </si>
+  <si>
+    <t>Remove control.console from viewer (or split into console.read vs send), hide the input without it, and review file.read-content for viewers.</t>
+  </si>
+  <si>
+    <t>Test: a viewer-preset member cannot send a command through the websocket and the input is not rendered.</t>
+  </si>
+  <si>
+    <t>[CONFIRMED_CODE] Source trace; whether Wings accepts commands from a connection with only control.console TEST_NEEDED on the sandbox panel.</t>
+  </si>
+  <si>
+    <t>NEW-405</t>
+  </si>
+  <si>
+    <t>The cached CSRF token is never refreshed, so every write fails after the one-hour cookie expires until the page is reloaded</t>
+  </si>
+  <si>
+    <t>src/frontend/core/api/client.ts:16-31,57-87; src/server.ts:575-581</t>
+  </si>
+  <si>
+    <t>The server sets the fortless_csrf cookie with maxAge 3600. The client caches the token in memory for the page lifetime; invalidateCsrfToken has no caller outside client.ts and a 403 CSRF_INVALID is surfaced as a generic error.</t>
+  </si>
+  <si>
+    <t>A tab left open for more than an hour (console, file editor, support reply) loses unsaved work on the next save with an unexplained "CSRF validation failed".</t>
+  </si>
+  <si>
+    <t>Retry once after fetching a fresh token on CSRF_INVALID, or align the cookie lifetime with the session.</t>
+  </si>
+  <si>
+    <t>Test: after the cookie expires a save succeeds without a reload.</t>
+  </si>
+  <si>
+    <t>[CONFIRMED_CODE] grep shows no caller of invalidateCsrfToken; runtime behaviour TEST_NEEDED in a browser.</t>
+  </si>
+  <si>
+    <t>NEW-406</t>
+  </si>
+  <si>
+    <t>Admin settings page states security values that are wrong or hardcoded, and shows infrastructure details to every staff role</t>
+  </si>
+  <si>
+    <t>src/server.ts:2936-2990; src/modules/identity/auth.ts:64,66</t>
+  </si>
+  <si>
+    <t>The response hardcodes sessionTtlHours 72, stepUpTtlMinutes 15, staffMfaMandatory true and antiSsrBlacklistActive true; the code uses a 14 day session (SESSION_TTL_MS, cookie maxAge) and a 10 minute step-up window. The route needs only admin:access, which every staff role has, and returns nodeEnv, panel URL, SMTP host and user.</t>
+  </si>
+  <si>
+    <t>Operators and auditors are told sessions last 72 hours and step-up lasts 15 minutes when staff sessions last 14 days; BILLING or AUDITOR staff can read infrastructure and mail configuration.</t>
+  </si>
+  <si>
+    <t>Read the values from the constants actually enforced and restrict the infrastructure block to a settings permission.</t>
+  </si>
+  <si>
+    <t>Test: the response matches the enforced TTLs; a BILLING role does not receive SMTP or panel details.</t>
+  </si>
+  <si>
+    <t>NEW-407</t>
+  </si>
+  <si>
+    <t>Global search checks staff permissions that do not exist, hiding admin pages and omitting shared services</t>
+  </si>
+  <si>
+    <t>src/server.ts:2311-2425</t>
+  </si>
+  <si>
+    <t>The admin entries for Orders and Billing require "billing:read", which is not a StaffPermission (the cast hides it), so no role ever sees them. The staff entry requires staff:manage while the navigation uses staff:read. Service search only covers services owned by the active account, not those shared with the user.</t>
+  </si>
+  <si>
+    <t>Search silently omits pages for the roles that should reach them, and shared-server users cannot find their servers.</t>
+  </si>
+  <si>
+    <t>Use the real permission names (type-checked) and include service_members in the service query.</t>
+  </si>
+  <si>
+    <t>Test: a BILLING staff member finds Admin: Billing; a shared member finds the shared server.</t>
+  </si>
+  <si>
+    <t>NEW-408</t>
+  </si>
+  <si>
+    <t>The customer app shows every action to every role and billing and audit data to all roles; only the backend refuses</t>
+  </si>
+  <si>
+    <t>src/frontend/client (role checks only in billing:86, settings:700 and services access.permissions); src/server.ts:1426-1460,1803-1830,2441-2480</t>
+  </si>
+  <si>
+    <t>Subscription cancel, member invite/revoke, DNS editing and deploy are rendered for VIEWER, TECH_ADMIN and BILLING_MANAGER; just the billing-details button is disabled by role. GET invoices, orders, subscriptions and /api/v1/audit (with ip_address and raw metadata) have requireAuth only.</t>
+  </si>
+  <si>
+    <t>VIEWERs read financial records and the full audit trail; users meet 403 toasts after trying actions, and DNS actions that the backend allows (NEW-369) look permitted.</t>
+  </si>
+  <si>
+    <t>Define a role-by-resource policy (read billing, read audit), enforce it on the routes, and have the frontend hide or disable actions from a server-provided capability set.</t>
+  </si>
+  <si>
+    <t>Test: VIEWER receives 403 for invoices and audit if that is the policy, and the UI hides the corresponding buttons.</t>
+  </si>
+  <si>
+    <t>[CONFIRMED_CODE] Source trace; whether VIEWER should read billing is a product decision.</t>
+  </si>
+  <si>
+    <t>NEW-409</t>
+  </si>
+  <si>
+    <t>Locking or fraud-flagging an account only ends its Fortless login; services, shares, panel access and keys keep working</t>
+  </si>
+  <si>
+    <t>src/modules/admin/read-model.ts:294-318; src/modules/payments/webhooks.ts:189; src/modules/provisioning/service-access.ts:41-61; src/modules/provisioning/console.ts</t>
+  </si>
+  <si>
+    <t>updateAccountStatus only updates accounts.status and writes an audit row. authenticateSession then rejects members of that account, but no service is suspended, no service_members row or invitation is revoked, no panel session or stored client key is revoked, and getServiceAccess / resolveOwnedService never look at the owning account status. The dispute webhook sets FLAGGED_FRAUD the same way.</t>
+  </si>
+  <si>
+    <t>A fraud-flagged account's servers keep running and keep billing state unchanged; members it shared servers with keep full console and file access, and the owner's existing panel session (NEW-396) keeps working. The lock does not contain the risk it signals.</t>
+  </si>
+  <si>
+    <t>Define what LOCKED and FLAGGED_FRAUD mean for services (suspend, read-only, or continue), enforce it in getServiceAccess, and revoke shares, panel sessions and keys on lock.</t>
+  </si>
+  <si>
+    <t>Test: after lock, console, files and panel actions are refused for owner and shared members; unlock restores them.</t>
+  </si>
+  <si>
+    <t>[CONFIRMED_CODE] Source trace; panel-side behaviour TEST_NEEDED.</t>
+  </si>
+  <si>
     <t>FORTLESS   /   SECURITY &amp; PRODUCT QUALITY</t>
   </si>
   <si>
@@ -3672,10 +3840,10 @@
     <t>CLOSED &amp; TESTED</t>
   </si>
   <si>
-    <t>147</t>
-  </si>
-  <si>
-    <t>59</t>
+    <t>154</t>
+  </si>
+  <si>
+    <t>65</t>
   </si>
   <si>
     <t>58</t>
@@ -3705,13 +3873,13 @@
     <t>11</t>
   </si>
   <si>
-    <t>70</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>38</t>
+    <t>73</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>42</t>
   </si>
   <si>
     <t>TESTED</t>
@@ -3822,7 +3990,7 @@
     <t>Every API permission and role</t>
   </si>
   <si>
-    <t>FTL-UI-201, SSO-01, NEW-322, NEW-328, NEW-359, NEW-376, NEW-378, NEW-379, NEW-387, NEW-390, NEW-399</t>
+    <t>FTL-UI-201, SSO-01, NEW-322, NEW-328, NEW-359, NEW-376, NEW-378, NEW-379, NEW-387, NEW-390, NEW-399, NEW-404, NEW-408, NEW-409</t>
   </si>
   <si>
     <t>05</t>
@@ -3858,7 +4026,7 @@
     <t>Request validation/mass assignment/rate limiting</t>
   </si>
   <si>
-    <t>FTL-SEC-205, NEW-311, NEW-321, NEW-328</t>
+    <t>FTL-SEC-205, NEW-311, NEW-321, NEW-328, NEW-407</t>
   </si>
   <si>
     <t>08</t>
@@ -3870,7 +4038,7 @@
     <t>Origin, cookies, CSRF all writes</t>
   </si>
   <si>
-    <t>SEC-09, NEW-394, NEW-395</t>
+    <t>SEC-09, NEW-394, NEW-395, NEW-405</t>
   </si>
   <si>
     <t>RUNTIME_REQUIRED</t>
@@ -3993,7 +4161,7 @@
     <t>Renewal, refunds, tax, coupons, invoices</t>
   </si>
   <si>
-    <t>FTL-BILL-202, FTL-BILL-205, NEW-301, NEW-303, NEW-304, NEW-305, NEW-316, NEW-319, NEW-324, NEW-330, NEW-333, NEW-334, NEW-338, NEW-344, NEW-348, NEW-351, NEW-352, NEW-353, NEW-355, NEW-356</t>
+    <t>FTL-BILL-202, FTL-BILL-205, NEW-301, NEW-303, NEW-304, NEW-305, NEW-316, NEW-319, NEW-324, NEW-330, NEW-333, NEW-334, NEW-338, NEW-344, NEW-348, NEW-351, NEW-352, NEW-353, NEW-355, NEW-356, NEW-403</t>
   </si>
   <si>
     <t>21</t>
@@ -4104,7 +4272,7 @@
     <t>Audit integrity, alerts, events</t>
   </si>
   <si>
-    <t>SEC-09, NEW-322, NEW-380, NEW-391, NEW-400</t>
+    <t>SEC-09, NEW-322, NEW-380, NEW-391, NEW-400, NEW-406</t>
   </si>
   <si>
     <t>FORTLESS   /   COMMIT &amp; AUDIT HISTORY</t>
@@ -4345,6 +4513,15 @@
   </si>
   <si>
     <t>Panel SSO patch files, email outbox, notification and export paths read in source; one unauthenticated GET to the live panel for status only. No implementation code changed.</t>
+  </si>
+  <si>
+    <t>2026-10-19 11:00</t>
+  </si>
+  <si>
+    <t>Independent audit batch 8: frontend permissions and failure states, role x state matrix (NEW-403..NEW-409)</t>
+  </si>
+  <si>
+    <t>Customer and admin frontend pages, API client, search, settings and account-lock paths read in source. No implementation code changed.</t>
   </si>
   <si>
     <t>FORTLESS   /   IMMUTABLE STATUS HISTORY</t>
@@ -5609,7 +5786,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:S150"/>
+  <dimension ref="A1:S157"/>
   <sheetFormatPr defaultRowHeight="0" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" customHeight="1"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
@@ -14003,12 +14180,12 @@
         <v>36</v>
       </c>
       <c r="S147" t="s">
-        <v>765</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="148" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>1188</v>
+        <v>1189</v>
       </c>
       <c r="B148" t="s">
         <v>308</v>
@@ -14020,7 +14197,7 @@
         <v>24</v>
       </c>
       <c r="E148" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="F148" t="s">
         <v>112</v>
@@ -14038,19 +14215,19 @@
         <v>1158</v>
       </c>
       <c r="K148" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
       <c r="L148" t="s">
-        <v>1191</v>
+        <v>1192</v>
       </c>
       <c r="M148" t="s">
-        <v>1192</v>
+        <v>1193</v>
       </c>
       <c r="N148" t="s">
-        <v>1193</v>
+        <v>1194</v>
       </c>
       <c r="O148" t="s">
-        <v>1194</v>
+        <v>1195</v>
       </c>
       <c r="P148" t="s">
         <v>747</v>
@@ -14067,7 +14244,7 @@
     </row>
     <row r="149" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="B149" t="s">
         <v>308</v>
@@ -14079,7 +14256,7 @@
         <v>1054</v>
       </c>
       <c r="E149" t="s">
-        <v>1196</v>
+        <v>1197</v>
       </c>
       <c r="F149" t="s">
         <v>112</v>
@@ -14097,19 +14274,19 @@
         <v>1158</v>
       </c>
       <c r="K149" t="s">
-        <v>1197</v>
+        <v>1198</v>
       </c>
       <c r="L149" t="s">
-        <v>1198</v>
+        <v>1199</v>
       </c>
       <c r="M149" t="s">
-        <v>1199</v>
+        <v>1200</v>
       </c>
       <c r="N149" t="s">
-        <v>1200</v>
+        <v>1201</v>
       </c>
       <c r="O149" t="s">
-        <v>1201</v>
+        <v>1202</v>
       </c>
       <c r="P149" t="s">
         <v>747</v>
@@ -14121,12 +14298,12 @@
         <v>36</v>
       </c>
       <c r="S149" t="s">
-        <v>1202</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="150" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>1203</v>
+        <v>1204</v>
       </c>
       <c r="B150" t="s">
         <v>308</v>
@@ -14138,7 +14315,7 @@
         <v>959</v>
       </c>
       <c r="E150" t="s">
-        <v>1204</v>
+        <v>1205</v>
       </c>
       <c r="F150" t="s">
         <v>95</v>
@@ -14156,19 +14333,19 @@
         <v>1158</v>
       </c>
       <c r="K150" t="s">
-        <v>1205</v>
+        <v>1206</v>
       </c>
       <c r="L150" t="s">
-        <v>1206</v>
+        <v>1207</v>
       </c>
       <c r="M150" t="s">
-        <v>1207</v>
+        <v>1208</v>
       </c>
       <c r="N150" t="s">
-        <v>1208</v>
+        <v>1209</v>
       </c>
       <c r="O150" t="s">
-        <v>1209</v>
+        <v>1210</v>
       </c>
       <c r="P150" t="s">
         <v>747</v>
@@ -14180,7 +14357,420 @@
         <v>36</v>
       </c>
       <c r="S150" t="s">
-        <v>1210</v>
+        <v>1211</v>
+      </c>
+    </row>
+    <row r="151" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A151" t="s">
+        <v>1212</v>
+      </c>
+      <c r="B151" t="s">
+        <v>61</v>
+      </c>
+      <c r="C151" t="s">
+        <v>62</v>
+      </c>
+      <c r="D151" t="s">
+        <v>569</v>
+      </c>
+      <c r="E151" t="s">
+        <v>1213</v>
+      </c>
+      <c r="F151" t="s">
+        <v>112</v>
+      </c>
+      <c r="G151" t="s">
+        <v>27</v>
+      </c>
+      <c r="H151" t="s">
+        <v>27</v>
+      </c>
+      <c r="I151" t="s">
+        <v>1214</v>
+      </c>
+      <c r="J151" t="s">
+        <v>1214</v>
+      </c>
+      <c r="K151" t="s">
+        <v>1215</v>
+      </c>
+      <c r="L151" t="s">
+        <v>1216</v>
+      </c>
+      <c r="M151" t="s">
+        <v>1217</v>
+      </c>
+      <c r="N151" t="s">
+        <v>1218</v>
+      </c>
+      <c r="O151" t="s">
+        <v>1219</v>
+      </c>
+      <c r="P151" t="s">
+        <v>747</v>
+      </c>
+      <c r="Q151" t="s">
+        <v>924</v>
+      </c>
+      <c r="R151" t="s">
+        <v>36</v>
+      </c>
+      <c r="S151" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="152" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A152" t="s">
+        <v>1221</v>
+      </c>
+      <c r="B152" t="s">
+        <v>61</v>
+      </c>
+      <c r="C152" t="s">
+        <v>62</v>
+      </c>
+      <c r="D152" t="s">
+        <v>630</v>
+      </c>
+      <c r="E152" t="s">
+        <v>1222</v>
+      </c>
+      <c r="F152" t="s">
+        <v>112</v>
+      </c>
+      <c r="G152" t="s">
+        <v>27</v>
+      </c>
+      <c r="H152" t="s">
+        <v>27</v>
+      </c>
+      <c r="I152" t="s">
+        <v>1214</v>
+      </c>
+      <c r="J152" t="s">
+        <v>1214</v>
+      </c>
+      <c r="K152" t="s">
+        <v>1223</v>
+      </c>
+      <c r="L152" t="s">
+        <v>1224</v>
+      </c>
+      <c r="M152" t="s">
+        <v>1225</v>
+      </c>
+      <c r="N152" t="s">
+        <v>1226</v>
+      </c>
+      <c r="O152" t="s">
+        <v>1227</v>
+      </c>
+      <c r="P152" t="s">
+        <v>747</v>
+      </c>
+      <c r="Q152" t="s">
+        <v>924</v>
+      </c>
+      <c r="R152" t="s">
+        <v>36</v>
+      </c>
+      <c r="S152" t="s">
+        <v>1228</v>
+      </c>
+    </row>
+    <row r="153" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A153" t="s">
+        <v>1229</v>
+      </c>
+      <c r="B153" t="s">
+        <v>308</v>
+      </c>
+      <c r="C153" t="s">
+        <v>62</v>
+      </c>
+      <c r="D153" t="s">
+        <v>959</v>
+      </c>
+      <c r="E153" t="s">
+        <v>1230</v>
+      </c>
+      <c r="F153" t="s">
+        <v>112</v>
+      </c>
+      <c r="G153" t="s">
+        <v>27</v>
+      </c>
+      <c r="H153" t="s">
+        <v>27</v>
+      </c>
+      <c r="I153" t="s">
+        <v>1214</v>
+      </c>
+      <c r="J153" t="s">
+        <v>1214</v>
+      </c>
+      <c r="K153" t="s">
+        <v>1231</v>
+      </c>
+      <c r="L153" t="s">
+        <v>1232</v>
+      </c>
+      <c r="M153" t="s">
+        <v>1233</v>
+      </c>
+      <c r="N153" t="s">
+        <v>1234</v>
+      </c>
+      <c r="O153" t="s">
+        <v>1235</v>
+      </c>
+      <c r="P153" t="s">
+        <v>747</v>
+      </c>
+      <c r="Q153" t="s">
+        <v>924</v>
+      </c>
+      <c r="R153" t="s">
+        <v>36</v>
+      </c>
+      <c r="S153" t="s">
+        <v>1236</v>
+      </c>
+    </row>
+    <row r="154" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A154" t="s">
+        <v>1237</v>
+      </c>
+      <c r="B154" t="s">
+        <v>308</v>
+      </c>
+      <c r="C154" t="s">
+        <v>309</v>
+      </c>
+      <c r="D154" t="s">
+        <v>1077</v>
+      </c>
+      <c r="E154" t="s">
+        <v>1238</v>
+      </c>
+      <c r="F154" t="s">
+        <v>112</v>
+      </c>
+      <c r="G154" t="s">
+        <v>27</v>
+      </c>
+      <c r="H154" t="s">
+        <v>27</v>
+      </c>
+      <c r="I154" t="s">
+        <v>1214</v>
+      </c>
+      <c r="J154" t="s">
+        <v>1214</v>
+      </c>
+      <c r="K154" t="s">
+        <v>1239</v>
+      </c>
+      <c r="L154" t="s">
+        <v>1240</v>
+      </c>
+      <c r="M154" t="s">
+        <v>1241</v>
+      </c>
+      <c r="N154" t="s">
+        <v>1242</v>
+      </c>
+      <c r="O154" t="s">
+        <v>1243</v>
+      </c>
+      <c r="P154" t="s">
+        <v>747</v>
+      </c>
+      <c r="Q154" t="s">
+        <v>924</v>
+      </c>
+      <c r="R154" t="s">
+        <v>36</v>
+      </c>
+      <c r="S154" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="155" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A155" t="s">
+        <v>1244</v>
+      </c>
+      <c r="B155" t="s">
+        <v>308</v>
+      </c>
+      <c r="C155" t="s">
+        <v>309</v>
+      </c>
+      <c r="D155" t="s">
+        <v>1054</v>
+      </c>
+      <c r="E155" t="s">
+        <v>1245</v>
+      </c>
+      <c r="F155" t="s">
+        <v>112</v>
+      </c>
+      <c r="G155" t="s">
+        <v>27</v>
+      </c>
+      <c r="H155" t="s">
+        <v>27</v>
+      </c>
+      <c r="I155" t="s">
+        <v>1214</v>
+      </c>
+      <c r="J155" t="s">
+        <v>1214</v>
+      </c>
+      <c r="K155" t="s">
+        <v>1246</v>
+      </c>
+      <c r="L155" t="s">
+        <v>1247</v>
+      </c>
+      <c r="M155" t="s">
+        <v>1248</v>
+      </c>
+      <c r="N155" t="s">
+        <v>1249</v>
+      </c>
+      <c r="O155" t="s">
+        <v>1250</v>
+      </c>
+      <c r="P155" t="s">
+        <v>747</v>
+      </c>
+      <c r="Q155" t="s">
+        <v>924</v>
+      </c>
+      <c r="R155" t="s">
+        <v>36</v>
+      </c>
+      <c r="S155" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="156" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A156" t="s">
+        <v>1251</v>
+      </c>
+      <c r="B156" t="s">
+        <v>308</v>
+      </c>
+      <c r="C156" t="s">
+        <v>62</v>
+      </c>
+      <c r="D156" t="s">
+        <v>630</v>
+      </c>
+      <c r="E156" t="s">
+        <v>1252</v>
+      </c>
+      <c r="F156" t="s">
+        <v>453</v>
+      </c>
+      <c r="G156" t="s">
+        <v>27</v>
+      </c>
+      <c r="H156" t="s">
+        <v>27</v>
+      </c>
+      <c r="I156" t="s">
+        <v>1214</v>
+      </c>
+      <c r="J156" t="s">
+        <v>1214</v>
+      </c>
+      <c r="K156" t="s">
+        <v>1253</v>
+      </c>
+      <c r="L156" t="s">
+        <v>1254</v>
+      </c>
+      <c r="M156" t="s">
+        <v>1255</v>
+      </c>
+      <c r="N156" t="s">
+        <v>1256</v>
+      </c>
+      <c r="O156" t="s">
+        <v>1257</v>
+      </c>
+      <c r="P156" t="s">
+        <v>747</v>
+      </c>
+      <c r="Q156" t="s">
+        <v>924</v>
+      </c>
+      <c r="R156" t="s">
+        <v>36</v>
+      </c>
+      <c r="S156" t="s">
+        <v>1258</v>
+      </c>
+    </row>
+    <row r="157" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A157" t="s">
+        <v>1259</v>
+      </c>
+      <c r="B157" t="s">
+        <v>61</v>
+      </c>
+      <c r="C157" t="s">
+        <v>23</v>
+      </c>
+      <c r="D157" t="s">
+        <v>630</v>
+      </c>
+      <c r="E157" t="s">
+        <v>1260</v>
+      </c>
+      <c r="F157" t="s">
+        <v>112</v>
+      </c>
+      <c r="G157" t="s">
+        <v>27</v>
+      </c>
+      <c r="H157" t="s">
+        <v>27</v>
+      </c>
+      <c r="I157" t="s">
+        <v>1214</v>
+      </c>
+      <c r="J157" t="s">
+        <v>1214</v>
+      </c>
+      <c r="K157" t="s">
+        <v>1261</v>
+      </c>
+      <c r="L157" t="s">
+        <v>1262</v>
+      </c>
+      <c r="M157" t="s">
+        <v>1263</v>
+      </c>
+      <c r="N157" t="s">
+        <v>1264</v>
+      </c>
+      <c r="O157" t="s">
+        <v>1265</v>
+      </c>
+      <c r="P157" t="s">
+        <v>747</v>
+      </c>
+      <c r="Q157" t="s">
+        <v>924</v>
+      </c>
+      <c r="R157" t="s">
+        <v>36</v>
+      </c>
+      <c r="S157" t="s">
+        <v>1266</v>
       </c>
     </row>
   </sheetData>
@@ -14194,48 +14784,48 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>1211</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1212</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1213</v>
+        <v>1269</v>
       </c>
       <c r="C4" t="s">
-        <v>1214</v>
+        <v>1270</v>
       </c>
       <c r="E4" t="s">
-        <v>1215</v>
+        <v>1271</v>
       </c>
       <c r="G4" t="s">
-        <v>1216</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1217</v>
+        <v>1273</v>
       </c>
       <c r="C5" t="s">
-        <v>1218</v>
+        <v>1274</v>
       </c>
       <c r="E5" t="s">
-        <v>1219</v>
+        <v>1275</v>
       </c>
       <c r="G5" t="s">
-        <v>1220</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>1221</v>
+        <v>1277</v>
       </c>
       <c r="F9" t="s">
-        <v>1222</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -14243,16 +14833,16 @@
         <v>112</v>
       </c>
       <c r="B10" t="s">
-        <v>1218</v>
+        <v>1274</v>
       </c>
       <c r="C10" t="s">
         <v>3</v>
       </c>
       <c r="D10" t="s">
-        <v>1223</v>
+        <v>1279</v>
       </c>
       <c r="F10" t="s">
-        <v>1224</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -14260,13 +14850,13 @@
         <v>86</v>
       </c>
       <c r="B11" t="s">
-        <v>1225</v>
+        <v>1281</v>
       </c>
       <c r="C11" t="s">
         <v>22</v>
       </c>
       <c r="D11" t="s">
-        <v>1226</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -14274,13 +14864,13 @@
         <v>95</v>
       </c>
       <c r="B12" t="s">
-        <v>1227</v>
+        <v>1283</v>
       </c>
       <c r="C12" t="s">
         <v>61</v>
       </c>
       <c r="D12" t="s">
-        <v>1228</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -14288,13 +14878,13 @@
         <v>453</v>
       </c>
       <c r="B13" t="s">
-        <v>1229</v>
+        <v>1285</v>
       </c>
       <c r="C13" t="s">
         <v>308</v>
       </c>
       <c r="D13" t="s">
-        <v>1230</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
@@ -14302,42 +14892,42 @@
         <v>26</v>
       </c>
       <c r="B14" t="s">
-        <v>1219</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>1231</v>
+        <v>1287</v>
       </c>
       <c r="B15" t="s">
-        <v>1220</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>1232</v>
+        <v>1288</v>
       </c>
       <c r="B16" t="s">
-        <v>1220</v>
+        <v>1276</v>
       </c>
       <c r="F16" t="s">
-        <v>1233</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>1234</v>
+        <v>1290</v>
       </c>
       <c r="B17" t="s">
-        <v>1220</v>
+        <v>1276</v>
       </c>
       <c r="F17" t="s">
-        <v>1235</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>1236</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
@@ -14345,7 +14935,7 @@
         <v>112</v>
       </c>
       <c r="C22" t="s">
-        <v>1237</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
@@ -14353,7 +14943,7 @@
         <v>86</v>
       </c>
       <c r="C23" t="s">
-        <v>1238</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
@@ -14361,7 +14951,7 @@
         <v>26</v>
       </c>
       <c r="C24" t="s">
-        <v>1239</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
@@ -14369,7 +14959,7 @@
         <v>95</v>
       </c>
       <c r="C25" t="s">
-        <v>1240</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
@@ -14377,31 +14967,31 @@
         <v>453</v>
       </c>
       <c r="C26" t="s">
-        <v>1241</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>1231</v>
+        <v>1287</v>
       </c>
       <c r="C27" t="s">
-        <v>1242</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>1232</v>
+        <v>1288</v>
       </c>
       <c r="C28" t="s">
-        <v>1243</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>1234</v>
+        <v>1290</v>
       </c>
       <c r="C29" t="s">
-        <v>1244</v>
+        <v>1300</v>
       </c>
     </row>
   </sheetData>
@@ -14415,7 +15005,7 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>1245</v>
+        <v>1301</v>
       </c>
       <c r="B1"/>
       <c r="C1"/>
@@ -14424,7 +15014,7 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1246</v>
+        <v>1302</v>
       </c>
       <c r="B2"/>
       <c r="C2"/>
@@ -14433,529 +15023,529 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>1247</v>
+        <v>1303</v>
       </c>
       <c r="B3" t="s">
         <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>1248</v>
+        <v>1304</v>
       </c>
       <c r="D3" t="s">
-        <v>1249</v>
+        <v>1305</v>
       </c>
       <c r="E3" t="s">
-        <v>1250</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1251</v>
+        <v>1307</v>
       </c>
       <c r="B4" t="s">
-        <v>1252</v>
+        <v>1308</v>
       </c>
       <c r="C4" t="s">
-        <v>1253</v>
+        <v>1309</v>
       </c>
       <c r="D4" t="s">
-        <v>1254</v>
+        <v>1310</v>
       </c>
       <c r="E4" t="s">
-        <v>1255</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1256</v>
+        <v>1312</v>
       </c>
       <c r="B5" t="s">
-        <v>1257</v>
+        <v>1313</v>
       </c>
       <c r="C5" t="s">
-        <v>1258</v>
+        <v>1314</v>
       </c>
       <c r="D5" t="s">
-        <v>1259</v>
+        <v>1315</v>
       </c>
       <c r="E5" t="s">
-        <v>1255</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>1260</v>
+        <v>1316</v>
       </c>
       <c r="B6" t="s">
-        <v>1261</v>
+        <v>1317</v>
       </c>
       <c r="C6" t="s">
-        <v>1262</v>
+        <v>1318</v>
       </c>
       <c r="D6" t="s">
-        <v>1263</v>
+        <v>1319</v>
       </c>
       <c r="E6" t="s">
-        <v>1255</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>1264</v>
+        <v>1320</v>
       </c>
       <c r="B7" t="s">
-        <v>1265</v>
+        <v>1321</v>
       </c>
       <c r="C7" t="s">
-        <v>1266</v>
+        <v>1322</v>
       </c>
       <c r="D7" t="s">
-        <v>1267</v>
+        <v>1323</v>
       </c>
       <c r="E7" t="s">
-        <v>1255</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>1268</v>
+        <v>1324</v>
       </c>
       <c r="B8" t="s">
-        <v>1269</v>
+        <v>1325</v>
       </c>
       <c r="C8" t="s">
-        <v>1270</v>
+        <v>1326</v>
       </c>
       <c r="D8" t="s">
-        <v>1271</v>
+        <v>1327</v>
       </c>
       <c r="E8" t="s">
-        <v>1255</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>1272</v>
+        <v>1328</v>
       </c>
       <c r="B9" t="s">
-        <v>1273</v>
+        <v>1329</v>
       </c>
       <c r="C9" t="s">
-        <v>1274</v>
+        <v>1330</v>
       </c>
       <c r="D9" t="s">
-        <v>1275</v>
+        <v>1331</v>
       </c>
       <c r="E9" t="s">
-        <v>1255</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>1276</v>
+        <v>1332</v>
       </c>
       <c r="B10" t="s">
-        <v>1277</v>
+        <v>1333</v>
       </c>
       <c r="C10" t="s">
-        <v>1278</v>
+        <v>1334</v>
       </c>
       <c r="D10" t="s">
-        <v>1279</v>
+        <v>1335</v>
       </c>
       <c r="E10" t="s">
-        <v>1255</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>1280</v>
+        <v>1336</v>
       </c>
       <c r="B11" t="s">
-        <v>1281</v>
+        <v>1337</v>
       </c>
       <c r="C11" t="s">
-        <v>1282</v>
+        <v>1338</v>
       </c>
       <c r="D11" t="s">
-        <v>1283</v>
+        <v>1339</v>
       </c>
       <c r="E11" t="s">
-        <v>1284</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>1285</v>
+        <v>1341</v>
       </c>
       <c r="B12" t="s">
-        <v>1286</v>
+        <v>1342</v>
       </c>
       <c r="C12" t="s">
-        <v>1287</v>
+        <v>1343</v>
       </c>
       <c r="D12" t="s">
-        <v>1288</v>
+        <v>1344</v>
       </c>
       <c r="E12" t="s">
-        <v>1255</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>1289</v>
+        <v>1345</v>
       </c>
       <c r="B13" t="s">
-        <v>1290</v>
+        <v>1346</v>
       </c>
       <c r="C13" t="s">
-        <v>1291</v>
+        <v>1347</v>
       </c>
       <c r="D13" t="s">
         <v>403</v>
       </c>
       <c r="E13" t="s">
-        <v>1284</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>1227</v>
+        <v>1283</v>
       </c>
       <c r="B14" t="s">
-        <v>1292</v>
+        <v>1348</v>
       </c>
       <c r="C14" t="s">
-        <v>1293</v>
+        <v>1349</v>
       </c>
       <c r="D14" t="s">
-        <v>1294</v>
+        <v>1350</v>
       </c>
       <c r="E14" t="s">
-        <v>1255</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>1295</v>
+        <v>1351</v>
       </c>
       <c r="B15" t="s">
         <v>1174</v>
       </c>
       <c r="C15" t="s">
-        <v>1296</v>
+        <v>1352</v>
       </c>
       <c r="D15" t="s">
-        <v>1297</v>
+        <v>1353</v>
       </c>
       <c r="E15" t="s">
-        <v>1255</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>1298</v>
+        <v>1354</v>
       </c>
       <c r="B16" t="s">
-        <v>1299</v>
+        <v>1355</v>
       </c>
       <c r="C16" t="s">
-        <v>1300</v>
+        <v>1356</v>
       </c>
       <c r="D16" t="s">
-        <v>1301</v>
+        <v>1357</v>
       </c>
       <c r="E16" t="s">
-        <v>1255</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>1302</v>
+        <v>1358</v>
       </c>
       <c r="B17" t="s">
         <v>435</v>
       </c>
       <c r="C17" t="s">
-        <v>1303</v>
+        <v>1359</v>
       </c>
       <c r="D17" t="s">
-        <v>1304</v>
+        <v>1360</v>
       </c>
       <c r="E17" t="s">
-        <v>1284</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>1225</v>
+        <v>1281</v>
       </c>
       <c r="B18" t="s">
-        <v>1305</v>
+        <v>1361</v>
       </c>
       <c r="C18" t="s">
-        <v>1306</v>
+        <v>1362</v>
       </c>
       <c r="D18" t="s">
         <v>316</v>
       </c>
       <c r="E18" t="s">
-        <v>1284</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>1307</v>
+        <v>1363</v>
       </c>
       <c r="B19" t="s">
-        <v>1308</v>
+        <v>1364</v>
       </c>
       <c r="C19" t="s">
-        <v>1309</v>
+        <v>1365</v>
       </c>
       <c r="D19" t="s">
-        <v>1310</v>
+        <v>1366</v>
       </c>
       <c r="E19" t="s">
-        <v>1284</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>1311</v>
+        <v>1367</v>
       </c>
       <c r="B20" t="s">
-        <v>1312</v>
+        <v>1368</v>
       </c>
       <c r="C20" t="s">
-        <v>1313</v>
+        <v>1369</v>
       </c>
       <c r="D20" t="s">
         <v>475</v>
       </c>
       <c r="E20" t="s">
-        <v>1255</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>1314</v>
+        <v>1370</v>
       </c>
       <c r="B21" t="s">
-        <v>1315</v>
+        <v>1371</v>
       </c>
       <c r="C21" t="s">
-        <v>1316</v>
+        <v>1372</v>
       </c>
       <c r="D21" t="s">
         <v>213</v>
       </c>
       <c r="E21" t="s">
-        <v>1284</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>1317</v>
+        <v>1373</v>
       </c>
       <c r="B22" t="s">
-        <v>1318</v>
+        <v>1374</v>
       </c>
       <c r="C22" t="s">
-        <v>1319</v>
+        <v>1375</v>
       </c>
       <c r="D22" t="s">
-        <v>1320</v>
+        <v>1376</v>
       </c>
       <c r="E22" t="s">
-        <v>1255</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>1321</v>
+        <v>1377</v>
       </c>
       <c r="B23" t="s">
-        <v>1322</v>
+        <v>1378</v>
       </c>
       <c r="C23" t="s">
-        <v>1323</v>
+        <v>1379</v>
       </c>
       <c r="D23" t="s">
-        <v>1324</v>
+        <v>1380</v>
       </c>
       <c r="E23" t="s">
-        <v>1255</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>1325</v>
+        <v>1381</v>
       </c>
       <c r="B24" t="s">
         <v>214</v>
       </c>
       <c r="C24" t="s">
-        <v>1326</v>
+        <v>1382</v>
       </c>
       <c r="D24" t="s">
-        <v>1327</v>
+        <v>1383</v>
       </c>
       <c r="E24" t="s">
-        <v>1255</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>1328</v>
+        <v>1384</v>
       </c>
       <c r="B25" t="s">
-        <v>1329</v>
+        <v>1385</v>
       </c>
       <c r="C25" t="s">
-        <v>1330</v>
+        <v>1386</v>
       </c>
       <c r="D25" t="s">
-        <v>1331</v>
+        <v>1387</v>
       </c>
       <c r="E25" t="s">
-        <v>1284</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>1332</v>
+        <v>1388</v>
       </c>
       <c r="B26" t="s">
-        <v>1333</v>
+        <v>1389</v>
       </c>
       <c r="C26" t="s">
-        <v>1334</v>
+        <v>1390</v>
       </c>
       <c r="D26" t="s">
-        <v>1335</v>
+        <v>1391</v>
       </c>
       <c r="E26" t="s">
-        <v>1284</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>1336</v>
+        <v>1392</v>
       </c>
       <c r="B27" t="s">
-        <v>1337</v>
+        <v>1393</v>
       </c>
       <c r="C27" t="s">
-        <v>1338</v>
+        <v>1394</v>
       </c>
       <c r="D27" t="s">
-        <v>1339</v>
+        <v>1395</v>
       </c>
       <c r="E27" t="s">
-        <v>1255</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>1340</v>
+        <v>1396</v>
       </c>
       <c r="B28" t="s">
-        <v>1341</v>
+        <v>1397</v>
       </c>
       <c r="C28" t="s">
-        <v>1342</v>
+        <v>1398</v>
       </c>
       <c r="D28" t="s">
-        <v>1343</v>
+        <v>1399</v>
       </c>
       <c r="E28" t="s">
-        <v>1255</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>1344</v>
+        <v>1400</v>
       </c>
       <c r="B29" t="s">
         <v>822</v>
       </c>
       <c r="C29" t="s">
-        <v>1345</v>
+        <v>1401</v>
       </c>
       <c r="D29" t="s">
-        <v>1346</v>
+        <v>1402</v>
       </c>
       <c r="E29" t="s">
-        <v>1255</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>1347</v>
+        <v>1403</v>
       </c>
       <c r="B30" t="s">
-        <v>1348</v>
+        <v>1404</v>
       </c>
       <c r="C30" t="s">
-        <v>1349</v>
+        <v>1405</v>
       </c>
       <c r="D30" t="s">
-        <v>1350</v>
+        <v>1406</v>
       </c>
       <c r="E30" t="s">
-        <v>1284</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>1351</v>
+        <v>1407</v>
       </c>
       <c r="B31" t="s">
-        <v>1352</v>
+        <v>1408</v>
       </c>
       <c r="C31" t="s">
-        <v>1353</v>
+        <v>1409</v>
       </c>
       <c r="D31" t="s">
         <v>93</v>
       </c>
       <c r="E31" t="s">
-        <v>1354</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>1355</v>
+        <v>1411</v>
       </c>
       <c r="B32" t="s">
-        <v>1356</v>
+        <v>1412</v>
       </c>
       <c r="C32" t="s">
-        <v>1357</v>
+        <v>1413</v>
       </c>
       <c r="D32" t="s">
-        <v>1358</v>
+        <v>1414</v>
       </c>
       <c r="E32" t="s">
-        <v>1255</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>1359</v>
+        <v>1415</v>
       </c>
       <c r="B33" t="s">
         <v>1030</v>
       </c>
       <c r="C33" t="s">
-        <v>1360</v>
+        <v>1416</v>
       </c>
       <c r="D33" t="s">
-        <v>1361</v>
+        <v>1417</v>
       </c>
       <c r="E33" t="s">
-        <v>1284</v>
+        <v>1340</v>
       </c>
     </row>
   </sheetData>
@@ -14969,157 +15559,157 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr defaultRowHeight="0" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" customHeight="1"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>1362</v>
+        <v>1418</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1363</v>
+        <v>1419</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>1364</v>
+        <v>1420</v>
       </c>
       <c r="B3" t="s">
-        <v>1365</v>
+        <v>1421</v>
       </c>
       <c r="C3" t="s">
-        <v>1366</v>
+        <v>1422</v>
       </c>
       <c r="D3" t="s">
-        <v>1367</v>
+        <v>1423</v>
       </c>
       <c r="E3" t="s">
-        <v>1368</v>
+        <v>1424</v>
       </c>
       <c r="F3" t="s">
-        <v>1369</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1370</v>
+        <v>1426</v>
       </c>
       <c r="B4" t="s">
         <v>28</v>
       </c>
       <c r="C4" t="s">
-        <v>1371</v>
+        <v>1427</v>
       </c>
       <c r="D4" t="s">
-        <v>1372</v>
+        <v>1428</v>
       </c>
       <c r="E4" t="s">
-        <v>1373</v>
+        <v>1429</v>
       </c>
       <c r="F4" t="s">
-        <v>1374</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1375</v>
+        <v>1431</v>
       </c>
       <c r="B5" t="s">
-        <v>1376</v>
+        <v>1432</v>
       </c>
       <c r="C5" t="s">
-        <v>1377</v>
+        <v>1433</v>
       </c>
       <c r="D5" t="s">
-        <v>1378</v>
+        <v>1434</v>
       </c>
       <c r="E5" t="s">
-        <v>1379</v>
+        <v>1435</v>
       </c>
       <c r="F5" t="s">
-        <v>1380</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>1381</v>
+        <v>1437</v>
       </c>
       <c r="B6" t="s">
-        <v>1382</v>
+        <v>1438</v>
       </c>
       <c r="C6" t="s">
-        <v>1383</v>
+        <v>1439</v>
       </c>
       <c r="D6" t="s">
-        <v>1384</v>
+        <v>1440</v>
       </c>
       <c r="E6" t="s">
-        <v>1385</v>
+        <v>1441</v>
       </c>
       <c r="F6" t="s">
-        <v>1386</v>
+        <v>1442</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>1387</v>
+        <v>1443</v>
       </c>
       <c r="B7" t="s">
-        <v>1388</v>
+        <v>1444</v>
       </c>
       <c r="C7" t="s">
-        <v>1389</v>
+        <v>1445</v>
       </c>
       <c r="D7" t="s">
-        <v>1390</v>
+        <v>1446</v>
       </c>
       <c r="E7" t="s">
-        <v>1385</v>
+        <v>1441</v>
       </c>
       <c r="F7" t="s">
-        <v>1391</v>
+        <v>1447</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>1392</v>
+        <v>1448</v>
       </c>
       <c r="B8" t="s">
-        <v>1393</v>
+        <v>1449</v>
       </c>
       <c r="C8" t="s">
-        <v>1394</v>
+        <v>1450</v>
       </c>
       <c r="D8" t="s">
-        <v>1395</v>
+        <v>1451</v>
       </c>
       <c r="E8" t="s">
-        <v>1385</v>
+        <v>1441</v>
       </c>
       <c r="F8" t="s">
-        <v>1391</v>
+        <v>1447</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>1396</v>
+        <v>1452</v>
       </c>
       <c r="B9" t="s">
         <v>29</v>
       </c>
       <c r="C9" t="s">
-        <v>1397</v>
+        <v>1453</v>
       </c>
       <c r="D9" t="s">
-        <v>1398</v>
+        <v>1454</v>
       </c>
       <c r="E9" t="s">
-        <v>1373</v>
+        <v>1429</v>
       </c>
       <c r="F9" t="s">
-        <v>1399</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -15130,93 +15720,93 @@
         <v>29</v>
       </c>
       <c r="C10" t="s">
-        <v>1400</v>
+        <v>1456</v>
       </c>
       <c r="D10" t="s">
-        <v>1401</v>
+        <v>1457</v>
       </c>
       <c r="E10" t="s">
-        <v>1402</v>
+        <v>1458</v>
       </c>
       <c r="F10" t="s">
-        <v>1403</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>1404</v>
+        <v>1460</v>
       </c>
       <c r="B11" t="s">
         <v>55</v>
       </c>
       <c r="C11" t="s">
-        <v>1405</v>
+        <v>1461</v>
       </c>
       <c r="D11" t="s">
-        <v>1406</v>
+        <v>1462</v>
       </c>
       <c r="E11" t="s">
-        <v>1402</v>
+        <v>1458</v>
       </c>
       <c r="F11" t="s">
-        <v>1407</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>1408</v>
+        <v>1464</v>
       </c>
       <c r="B12" t="s">
         <v>161</v>
       </c>
       <c r="C12" t="s">
-        <v>1409</v>
+        <v>1465</v>
       </c>
       <c r="D12" t="s">
-        <v>1410</v>
+        <v>1466</v>
       </c>
       <c r="E12" t="s">
-        <v>1411</v>
+        <v>1467</v>
       </c>
       <c r="F12" t="s">
-        <v>1412</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>1413</v>
+        <v>1469</v>
       </c>
       <c r="B13" t="s">
-        <v>1414</v>
+        <v>1470</v>
       </c>
       <c r="C13" t="s">
-        <v>1415</v>
+        <v>1471</v>
       </c>
       <c r="D13" t="s">
-        <v>1416</v>
+        <v>1472</v>
       </c>
       <c r="E13" t="s">
-        <v>1417</v>
+        <v>1473</v>
       </c>
       <c r="F13" t="s">
-        <v>1418</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>1419</v>
+        <v>1475</v>
       </c>
       <c r="B14" t="s">
         <v>206</v>
       </c>
       <c r="C14" t="s">
-        <v>1420</v>
+        <v>1476</v>
       </c>
       <c r="D14" t="s">
-        <v>1421</v>
+        <v>1477</v>
       </c>
       <c r="E14" t="s">
-        <v>1422</v>
+        <v>1478</v>
       </c>
       <c r="F14" t="s">
         <v>748</v>
@@ -15224,19 +15814,19 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>1423</v>
+        <v>1479</v>
       </c>
       <c r="B15" t="s">
         <v>206</v>
       </c>
       <c r="C15" t="s">
-        <v>1424</v>
+        <v>1480</v>
       </c>
       <c r="D15" t="s">
-        <v>1425</v>
+        <v>1481</v>
       </c>
       <c r="E15" t="s">
-        <v>1426</v>
+        <v>1482</v>
       </c>
       <c r="F15" t="s">
         <v>748</v>
@@ -15244,19 +15834,19 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>1427</v>
+        <v>1483</v>
       </c>
       <c r="B16" t="s">
         <v>918</v>
       </c>
       <c r="C16" t="s">
-        <v>1428</v>
+        <v>1484</v>
       </c>
       <c r="D16" t="s">
-        <v>1429</v>
+        <v>1485</v>
       </c>
       <c r="E16" t="s">
-        <v>1426</v>
+        <v>1482</v>
       </c>
       <c r="F16" t="s">
         <v>924</v>
@@ -15264,19 +15854,19 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>1430</v>
+        <v>1486</v>
       </c>
       <c r="B17" t="s">
         <v>999</v>
       </c>
       <c r="C17" t="s">
-        <v>1431</v>
+        <v>1487</v>
       </c>
       <c r="D17" t="s">
-        <v>1432</v>
+        <v>1488</v>
       </c>
       <c r="E17" t="s">
-        <v>1426</v>
+        <v>1482</v>
       </c>
       <c r="F17" t="s">
         <v>924</v>
@@ -15284,19 +15874,19 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>1433</v>
+        <v>1489</v>
       </c>
       <c r="B18" t="s">
         <v>1095</v>
       </c>
       <c r="C18" t="s">
-        <v>1434</v>
+        <v>1490</v>
       </c>
       <c r="D18" t="s">
-        <v>1435</v>
+        <v>1491</v>
       </c>
       <c r="E18" t="s">
-        <v>1426</v>
+        <v>1482</v>
       </c>
       <c r="F18" t="s">
         <v>924</v>
@@ -15304,19 +15894,19 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>1436</v>
+        <v>1492</v>
       </c>
       <c r="B19" t="s">
         <v>1141</v>
       </c>
       <c r="C19" t="s">
-        <v>1437</v>
+        <v>1493</v>
       </c>
       <c r="D19" t="s">
-        <v>1438</v>
+        <v>1494</v>
       </c>
       <c r="E19" t="s">
-        <v>1426</v>
+        <v>1482</v>
       </c>
       <c r="F19" t="s">
         <v>924</v>
@@ -15324,21 +15914,41 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>1439</v>
+        <v>1495</v>
       </c>
       <c r="B20" t="s">
         <v>1158</v>
       </c>
       <c r="C20" t="s">
-        <v>1440</v>
+        <v>1496</v>
       </c>
       <c r="D20" t="s">
-        <v>1441</v>
+        <v>1497</v>
       </c>
       <c r="E20" t="s">
-        <v>1426</v>
+        <v>1482</v>
       </c>
       <c r="F20" t="s">
+        <v>924</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>1498</v>
+      </c>
+      <c r="B21" t="s">
+        <v>1214</v>
+      </c>
+      <c r="C21" t="s">
+        <v>1499</v>
+      </c>
+      <c r="D21" t="s">
+        <v>1500</v>
+      </c>
+      <c r="E21" t="s">
+        <v>1482</v>
+      </c>
+      <c r="F21" t="s">
         <v>924</v>
       </c>
     </row>
@@ -15348,40 +15958,40 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G166"/>
+  <dimension ref="A1:G173"/>
   <sheetFormatPr defaultRowHeight="0" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" customHeight="1"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>1442</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1443</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>1444</v>
+        <v>1503</v>
       </c>
       <c r="B3" t="s">
-        <v>1445</v>
+        <v>1504</v>
       </c>
       <c r="C3" t="s">
-        <v>1446</v>
+        <v>1505</v>
       </c>
       <c r="D3" t="s">
-        <v>1447</v>
+        <v>1506</v>
       </c>
       <c r="E3" t="s">
-        <v>1448</v>
+        <v>1507</v>
       </c>
       <c r="F3" t="s">
-        <v>1449</v>
+        <v>1508</v>
       </c>
       <c r="G3" t="s">
-        <v>1450</v>
+        <v>1509</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -15401,10 +16011,10 @@
         <v>26</v>
       </c>
       <c r="F4" t="s">
-        <v>1451</v>
+        <v>1510</v>
       </c>
       <c r="G4" t="s">
-        <v>1452</v>
+        <v>1511</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -15424,10 +16034,10 @@
         <v>26</v>
       </c>
       <c r="F5" t="s">
-        <v>1451</v>
+        <v>1510</v>
       </c>
       <c r="G5" t="s">
-        <v>1453</v>
+        <v>1512</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -15447,10 +16057,10 @@
         <v>26</v>
       </c>
       <c r="F6" t="s">
-        <v>1451</v>
+        <v>1510</v>
       </c>
       <c r="G6" t="s">
-        <v>1454</v>
+        <v>1513</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -15470,10 +16080,10 @@
         <v>86</v>
       </c>
       <c r="F7" t="s">
-        <v>1451</v>
+        <v>1510</v>
       </c>
       <c r="G7" t="s">
-        <v>1455</v>
+        <v>1514</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -15493,10 +16103,10 @@
         <v>26</v>
       </c>
       <c r="F8" t="s">
-        <v>1451</v>
+        <v>1510</v>
       </c>
       <c r="G8" t="s">
-        <v>1456</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -15516,10 +16126,10 @@
         <v>26</v>
       </c>
       <c r="F9" t="s">
-        <v>1451</v>
+        <v>1510</v>
       </c>
       <c r="G9" t="s">
-        <v>1457</v>
+        <v>1516</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -15539,10 +16149,10 @@
         <v>26</v>
       </c>
       <c r="F10" t="s">
-        <v>1451</v>
+        <v>1510</v>
       </c>
       <c r="G10" t="s">
-        <v>1458</v>
+        <v>1517</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -15562,10 +16172,10 @@
         <v>86</v>
       </c>
       <c r="F11" t="s">
-        <v>1451</v>
+        <v>1510</v>
       </c>
       <c r="G11" t="s">
-        <v>1459</v>
+        <v>1518</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -15585,10 +16195,10 @@
         <v>86</v>
       </c>
       <c r="F12" t="s">
-        <v>1451</v>
+        <v>1510</v>
       </c>
       <c r="G12" t="s">
-        <v>1460</v>
+        <v>1519</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -15608,10 +16218,10 @@
         <v>26</v>
       </c>
       <c r="F13" t="s">
-        <v>1451</v>
+        <v>1510</v>
       </c>
       <c r="G13" t="s">
-        <v>1461</v>
+        <v>1520</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -15631,10 +16241,10 @@
         <v>26</v>
       </c>
       <c r="F14" t="s">
-        <v>1462</v>
+        <v>1521</v>
       </c>
       <c r="G14" t="s">
-        <v>1463</v>
+        <v>1522</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -15654,10 +16264,10 @@
         <v>26</v>
       </c>
       <c r="F15" t="s">
-        <v>1462</v>
+        <v>1521</v>
       </c>
       <c r="G15" t="s">
-        <v>1464</v>
+        <v>1523</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -15677,10 +16287,10 @@
         <v>26</v>
       </c>
       <c r="F16" t="s">
-        <v>1462</v>
+        <v>1521</v>
       </c>
       <c r="G16" t="s">
-        <v>1465</v>
+        <v>1524</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -15700,10 +16310,10 @@
         <v>26</v>
       </c>
       <c r="F17" t="s">
-        <v>1462</v>
+        <v>1521</v>
       </c>
       <c r="G17" t="s">
-        <v>1466</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -15723,10 +16333,10 @@
         <v>26</v>
       </c>
       <c r="F18" t="s">
-        <v>1462</v>
+        <v>1521</v>
       </c>
       <c r="G18" t="s">
-        <v>1467</v>
+        <v>1526</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -15746,10 +16356,10 @@
         <v>26</v>
       </c>
       <c r="F19" t="s">
-        <v>1462</v>
+        <v>1521</v>
       </c>
       <c r="G19" t="s">
-        <v>1468</v>
+        <v>1527</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -15769,10 +16379,10 @@
         <v>86</v>
       </c>
       <c r="F20" t="s">
-        <v>1462</v>
+        <v>1521</v>
       </c>
       <c r="G20" t="s">
-        <v>1469</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -15792,10 +16402,10 @@
         <v>86</v>
       </c>
       <c r="F21" t="s">
-        <v>1462</v>
+        <v>1521</v>
       </c>
       <c r="G21" t="s">
-        <v>1470</v>
+        <v>1529</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
@@ -15815,10 +16425,10 @@
         <v>26</v>
       </c>
       <c r="F22" t="s">
-        <v>1462</v>
+        <v>1521</v>
       </c>
       <c r="G22" t="s">
-        <v>1471</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
@@ -15838,10 +16448,10 @@
         <v>86</v>
       </c>
       <c r="F23" t="s">
-        <v>1462</v>
+        <v>1521</v>
       </c>
       <c r="G23" t="s">
-        <v>1472</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -15861,10 +16471,10 @@
         <v>86</v>
       </c>
       <c r="F24" t="s">
-        <v>1462</v>
+        <v>1521</v>
       </c>
       <c r="G24" t="s">
-        <v>1473</v>
+        <v>1532</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
@@ -15884,10 +16494,10 @@
         <v>86</v>
       </c>
       <c r="F25" t="s">
-        <v>1462</v>
+        <v>1521</v>
       </c>
       <c r="G25" t="s">
-        <v>1474</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
@@ -15907,10 +16517,10 @@
         <v>86</v>
       </c>
       <c r="F26" t="s">
-        <v>1462</v>
+        <v>1521</v>
       </c>
       <c r="G26" t="s">
-        <v>1475</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
@@ -15930,10 +16540,10 @@
         <v>26</v>
       </c>
       <c r="F27" t="s">
-        <v>1462</v>
+        <v>1521</v>
       </c>
       <c r="G27" t="s">
-        <v>1476</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
@@ -15953,10 +16563,10 @@
         <v>86</v>
       </c>
       <c r="F28" t="s">
-        <v>1462</v>
+        <v>1521</v>
       </c>
       <c r="G28" t="s">
-        <v>1477</v>
+        <v>1536</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
@@ -15976,10 +16586,10 @@
         <v>86</v>
       </c>
       <c r="F29" t="s">
-        <v>1462</v>
+        <v>1521</v>
       </c>
       <c r="G29" t="s">
-        <v>1478</v>
+        <v>1537</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
@@ -15999,10 +16609,10 @@
         <v>26</v>
       </c>
       <c r="F30" t="s">
-        <v>1462</v>
+        <v>1521</v>
       </c>
       <c r="G30" t="s">
-        <v>1479</v>
+        <v>1538</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
@@ -16022,10 +16632,10 @@
         <v>26</v>
       </c>
       <c r="F31" t="s">
-        <v>1462</v>
+        <v>1521</v>
       </c>
       <c r="G31" t="s">
-        <v>1480</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
@@ -16045,10 +16655,10 @@
         <v>86</v>
       </c>
       <c r="F32" t="s">
-        <v>1462</v>
+        <v>1521</v>
       </c>
       <c r="G32" t="s">
-        <v>1481</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
@@ -16068,10 +16678,10 @@
         <v>86</v>
       </c>
       <c r="F33" t="s">
-        <v>1462</v>
+        <v>1521</v>
       </c>
       <c r="G33" t="s">
-        <v>1482</v>
+        <v>1541</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
@@ -16091,10 +16701,10 @@
         <v>86</v>
       </c>
       <c r="F34" t="s">
-        <v>1462</v>
+        <v>1521</v>
       </c>
       <c r="G34" t="s">
-        <v>1483</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
@@ -16114,7 +16724,7 @@
         <v>26</v>
       </c>
       <c r="F35" t="s">
-        <v>1484</v>
+        <v>1543</v>
       </c>
       <c r="G35" t="s">
         <v>168</v>
@@ -16137,7 +16747,7 @@
         <v>26</v>
       </c>
       <c r="F36" t="s">
-        <v>1484</v>
+        <v>1543</v>
       </c>
       <c r="G36" t="s">
         <v>177</v>
@@ -16160,7 +16770,7 @@
         <v>26</v>
       </c>
       <c r="F37" t="s">
-        <v>1484</v>
+        <v>1543</v>
       </c>
       <c r="G37" t="s">
         <v>194</v>
@@ -16183,7 +16793,7 @@
         <v>26</v>
       </c>
       <c r="F38" t="s">
-        <v>1484</v>
+        <v>1543</v>
       </c>
       <c r="G38" t="s">
         <v>203</v>
@@ -16206,7 +16816,7 @@
         <v>26</v>
       </c>
       <c r="F39" t="s">
-        <v>1484</v>
+        <v>1543</v>
       </c>
       <c r="G39" t="s">
         <v>222</v>
@@ -16229,7 +16839,7 @@
         <v>26</v>
       </c>
       <c r="F40" t="s">
-        <v>1484</v>
+        <v>1543</v>
       </c>
       <c r="G40" t="s">
         <v>245</v>
@@ -16252,10 +16862,10 @@
         <v>26</v>
       </c>
       <c r="F41" t="s">
-        <v>1484</v>
+        <v>1543</v>
       </c>
       <c r="G41" t="s">
-        <v>1485</v>
+        <v>1544</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
@@ -16275,10 +16885,10 @@
         <v>26</v>
       </c>
       <c r="F42" t="s">
-        <v>1484</v>
+        <v>1543</v>
       </c>
       <c r="G42" t="s">
-        <v>1486</v>
+        <v>1545</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
@@ -16298,10 +16908,10 @@
         <v>26</v>
       </c>
       <c r="F43" t="s">
-        <v>1484</v>
+        <v>1543</v>
       </c>
       <c r="G43" t="s">
-        <v>1487</v>
+        <v>1546</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
@@ -16321,7 +16931,7 @@
         <v>26</v>
       </c>
       <c r="F44" t="s">
-        <v>1484</v>
+        <v>1543</v>
       </c>
       <c r="G44" t="s">
         <v>360</v>
@@ -16344,7 +16954,7 @@
         <v>26</v>
       </c>
       <c r="F45" t="s">
-        <v>1484</v>
+        <v>1543</v>
       </c>
       <c r="G45" t="s">
         <v>368</v>
@@ -16367,10 +16977,10 @@
         <v>26</v>
       </c>
       <c r="F46" t="s">
-        <v>1484</v>
+        <v>1543</v>
       </c>
       <c r="G46" t="s">
-        <v>1488</v>
+        <v>1547</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
@@ -16390,7 +17000,7 @@
         <v>26</v>
       </c>
       <c r="F47" t="s">
-        <v>1484</v>
+        <v>1543</v>
       </c>
       <c r="G47" t="s">
         <v>386</v>
@@ -16413,10 +17023,10 @@
         <v>26</v>
       </c>
       <c r="F48" t="s">
-        <v>1484</v>
+        <v>1543</v>
       </c>
       <c r="G48" t="s">
-        <v>1489</v>
+        <v>1548</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
@@ -16436,7 +17046,7 @@
         <v>26</v>
       </c>
       <c r="F49" t="s">
-        <v>1484</v>
+        <v>1543</v>
       </c>
       <c r="G49" t="s">
         <v>402</v>
@@ -16459,7 +17069,7 @@
         <v>26</v>
       </c>
       <c r="F50" t="s">
-        <v>1484</v>
+        <v>1543</v>
       </c>
       <c r="G50" t="s">
         <v>411</v>
@@ -16482,7 +17092,7 @@
         <v>26</v>
       </c>
       <c r="F51" t="s">
-        <v>1484</v>
+        <v>1543</v>
       </c>
       <c r="G51" t="s">
         <v>419</v>
@@ -16505,7 +17115,7 @@
         <v>26</v>
       </c>
       <c r="F52" t="s">
-        <v>1484</v>
+        <v>1543</v>
       </c>
       <c r="G52" t="s">
         <v>426</v>
@@ -16528,7 +17138,7 @@
         <v>26</v>
       </c>
       <c r="F53" t="s">
-        <v>1484</v>
+        <v>1543</v>
       </c>
       <c r="G53" t="s">
         <v>433</v>
@@ -16551,7 +17161,7 @@
         <v>26</v>
       </c>
       <c r="F54" t="s">
-        <v>1484</v>
+        <v>1543</v>
       </c>
       <c r="G54" t="s">
         <v>467</v>
@@ -16574,7 +17184,7 @@
         <v>26</v>
       </c>
       <c r="F55" t="s">
-        <v>1484</v>
+        <v>1543</v>
       </c>
       <c r="G55" t="s">
         <v>485</v>
@@ -16597,7 +17207,7 @@
         <v>26</v>
       </c>
       <c r="F56" t="s">
-        <v>1484</v>
+        <v>1543</v>
       </c>
       <c r="G56" t="s">
         <v>494</v>
@@ -16620,7 +17230,7 @@
         <v>26</v>
       </c>
       <c r="F57" t="s">
-        <v>1484</v>
+        <v>1543</v>
       </c>
       <c r="G57" t="s">
         <v>502</v>
@@ -16643,7 +17253,7 @@
         <v>26</v>
       </c>
       <c r="F58" t="s">
-        <v>1484</v>
+        <v>1543</v>
       </c>
       <c r="G58" t="s">
         <v>511</v>
@@ -16666,7 +17276,7 @@
         <v>26</v>
       </c>
       <c r="F59" t="s">
-        <v>1484</v>
+        <v>1543</v>
       </c>
       <c r="G59" t="s">
         <v>520</v>
@@ -16689,7 +17299,7 @@
         <v>26</v>
       </c>
       <c r="F60" t="s">
-        <v>1484</v>
+        <v>1543</v>
       </c>
       <c r="G60" t="s">
         <v>530</v>
@@ -16712,7 +17322,7 @@
         <v>26</v>
       </c>
       <c r="F61" t="s">
-        <v>1484</v>
+        <v>1543</v>
       </c>
       <c r="G61" t="s">
         <v>539</v>
@@ -16735,7 +17345,7 @@
         <v>26</v>
       </c>
       <c r="F62" t="s">
-        <v>1484</v>
+        <v>1543</v>
       </c>
       <c r="G62" t="s">
         <v>547</v>
@@ -16758,7 +17368,7 @@
         <v>26</v>
       </c>
       <c r="F63" t="s">
-        <v>1484</v>
+        <v>1543</v>
       </c>
       <c r="G63" t="s">
         <v>557</v>
@@ -16781,7 +17391,7 @@
         <v>26</v>
       </c>
       <c r="F64" t="s">
-        <v>1484</v>
+        <v>1543</v>
       </c>
       <c r="G64" t="s">
         <v>567</v>
@@ -16804,7 +17414,7 @@
         <v>26</v>
       </c>
       <c r="F65" t="s">
-        <v>1484</v>
+        <v>1543</v>
       </c>
       <c r="G65" t="s">
         <v>576</v>
@@ -16827,7 +17437,7 @@
         <v>26</v>
       </c>
       <c r="F66" t="s">
-        <v>1484</v>
+        <v>1543</v>
       </c>
       <c r="G66" t="s">
         <v>584</v>
@@ -16850,7 +17460,7 @@
         <v>26</v>
       </c>
       <c r="F67" t="s">
-        <v>1484</v>
+        <v>1543</v>
       </c>
       <c r="G67" t="s">
         <v>594</v>
@@ -16873,7 +17483,7 @@
         <v>26</v>
       </c>
       <c r="F68" t="s">
-        <v>1484</v>
+        <v>1543</v>
       </c>
       <c r="G68" t="s">
         <v>602</v>
@@ -16896,7 +17506,7 @@
         <v>26</v>
       </c>
       <c r="F69" t="s">
-        <v>1484</v>
+        <v>1543</v>
       </c>
       <c r="G69" t="s">
         <v>611</v>
@@ -16919,7 +17529,7 @@
         <v>26</v>
       </c>
       <c r="F70" t="s">
-        <v>1484</v>
+        <v>1543</v>
       </c>
       <c r="G70" t="s">
         <v>618</v>
@@ -16942,10 +17552,10 @@
         <v>26</v>
       </c>
       <c r="F71" t="s">
-        <v>1484</v>
+        <v>1543</v>
       </c>
       <c r="G71" t="s">
-        <v>1490</v>
+        <v>1549</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
@@ -16965,10 +17575,10 @@
         <v>26</v>
       </c>
       <c r="F72" t="s">
-        <v>1484</v>
+        <v>1543</v>
       </c>
       <c r="G72" t="s">
-        <v>1491</v>
+        <v>1550</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
@@ -16988,10 +17598,10 @@
         <v>26</v>
       </c>
       <c r="F73" t="s">
-        <v>1484</v>
+        <v>1543</v>
       </c>
       <c r="G73" t="s">
-        <v>1492</v>
+        <v>1551</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
@@ -17011,10 +17621,10 @@
         <v>26</v>
       </c>
       <c r="F74" t="s">
-        <v>1484</v>
+        <v>1543</v>
       </c>
       <c r="G74" t="s">
-        <v>1493</v>
+        <v>1552</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
@@ -17034,10 +17644,10 @@
         <v>26</v>
       </c>
       <c r="F75" t="s">
-        <v>1484</v>
+        <v>1543</v>
       </c>
       <c r="G75" t="s">
-        <v>1494</v>
+        <v>1553</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
@@ -17057,10 +17667,10 @@
         <v>26</v>
       </c>
       <c r="F76" t="s">
-        <v>1484</v>
+        <v>1543</v>
       </c>
       <c r="G76" t="s">
-        <v>1495</v>
+        <v>1554</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
@@ -17080,10 +17690,10 @@
         <v>26</v>
       </c>
       <c r="F77" t="s">
-        <v>1484</v>
+        <v>1543</v>
       </c>
       <c r="G77" t="s">
-        <v>1496</v>
+        <v>1555</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
@@ -17103,10 +17713,10 @@
         <v>26</v>
       </c>
       <c r="F78" t="s">
-        <v>1484</v>
+        <v>1543</v>
       </c>
       <c r="G78" t="s">
-        <v>1497</v>
+        <v>1556</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
@@ -17126,10 +17736,10 @@
         <v>26</v>
       </c>
       <c r="F79" t="s">
-        <v>1484</v>
+        <v>1543</v>
       </c>
       <c r="G79" t="s">
-        <v>1498</v>
+        <v>1557</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
@@ -17137,7 +17747,7 @@
         <v>27</v>
       </c>
       <c r="B80" t="s">
-        <v>1414</v>
+        <v>1470</v>
       </c>
       <c r="C80" t="s">
         <v>697</v>
@@ -17149,10 +17759,10 @@
         <v>26</v>
       </c>
       <c r="F80" t="s">
-        <v>1499</v>
+        <v>1558</v>
       </c>
       <c r="G80" t="s">
-        <v>1500</v>
+        <v>1559</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
@@ -17160,7 +17770,7 @@
         <v>27</v>
       </c>
       <c r="B81" t="s">
-        <v>1414</v>
+        <v>1470</v>
       </c>
       <c r="C81" t="s">
         <v>708</v>
@@ -17172,10 +17782,10 @@
         <v>26</v>
       </c>
       <c r="F81" t="s">
-        <v>1499</v>
+        <v>1558</v>
       </c>
       <c r="G81" t="s">
-        <v>1501</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
@@ -17183,7 +17793,7 @@
         <v>27</v>
       </c>
       <c r="B82" t="s">
-        <v>1414</v>
+        <v>1470</v>
       </c>
       <c r="C82" t="s">
         <v>715</v>
@@ -17195,10 +17805,10 @@
         <v>26</v>
       </c>
       <c r="F82" t="s">
-        <v>1499</v>
+        <v>1558</v>
       </c>
       <c r="G82" t="s">
-        <v>1502</v>
+        <v>1561</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
@@ -17206,7 +17816,7 @@
         <v>27</v>
       </c>
       <c r="B83" t="s">
-        <v>1414</v>
+        <v>1470</v>
       </c>
       <c r="C83" t="s">
         <v>723</v>
@@ -17218,10 +17828,10 @@
         <v>26</v>
       </c>
       <c r="F83" t="s">
-        <v>1499</v>
+        <v>1558</v>
       </c>
       <c r="G83" t="s">
-        <v>1503</v>
+        <v>1562</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
@@ -17229,7 +17839,7 @@
         <v>27</v>
       </c>
       <c r="B84" t="s">
-        <v>1414</v>
+        <v>1470</v>
       </c>
       <c r="C84" t="s">
         <v>732</v>
@@ -17241,10 +17851,10 @@
         <v>26</v>
       </c>
       <c r="F84" t="s">
-        <v>1499</v>
+        <v>1558</v>
       </c>
       <c r="G84" t="s">
-        <v>1504</v>
+        <v>1563</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
@@ -17252,7 +17862,7 @@
         <v>27</v>
       </c>
       <c r="B85" t="s">
-        <v>1505</v>
+        <v>1564</v>
       </c>
       <c r="C85" t="s">
         <v>324</v>
@@ -17264,10 +17874,10 @@
         <v>86</v>
       </c>
       <c r="F85" t="s">
-        <v>1506</v>
+        <v>1565</v>
       </c>
       <c r="G85" t="s">
-        <v>1507</v>
+        <v>1566</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
@@ -17275,7 +17885,7 @@
         <v>27</v>
       </c>
       <c r="B86" t="s">
-        <v>1505</v>
+        <v>1564</v>
       </c>
       <c r="C86" t="s">
         <v>335</v>
@@ -17287,10 +17897,10 @@
         <v>86</v>
       </c>
       <c r="F86" t="s">
-        <v>1506</v>
+        <v>1565</v>
       </c>
       <c r="G86" t="s">
-        <v>1508</v>
+        <v>1567</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
@@ -17298,7 +17908,7 @@
         <v>27</v>
       </c>
       <c r="B87" t="s">
-        <v>1505</v>
+        <v>1564</v>
       </c>
       <c r="C87" t="s">
         <v>344</v>
@@ -17310,10 +17920,10 @@
         <v>86</v>
       </c>
       <c r="F87" t="s">
-        <v>1506</v>
+        <v>1565</v>
       </c>
       <c r="G87" t="s">
-        <v>1509</v>
+        <v>1568</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
@@ -17321,7 +17931,7 @@
         <v>27</v>
       </c>
       <c r="B88" t="s">
-        <v>1505</v>
+        <v>1564</v>
       </c>
       <c r="C88" t="s">
         <v>369</v>
@@ -17333,10 +17943,10 @@
         <v>112</v>
       </c>
       <c r="F88" t="s">
-        <v>1506</v>
+        <v>1565</v>
       </c>
       <c r="G88" t="s">
-        <v>1510</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
@@ -17356,10 +17966,10 @@
         <v>26</v>
       </c>
       <c r="F89" t="s">
-        <v>1511</v>
+        <v>1570</v>
       </c>
       <c r="G89" t="s">
-        <v>1512</v>
+        <v>1571</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
@@ -17367,7 +17977,7 @@
         <v>27</v>
       </c>
       <c r="B90" t="s">
-        <v>1505</v>
+        <v>1564</v>
       </c>
       <c r="C90" t="s">
         <v>619</v>
@@ -17379,10 +17989,10 @@
         <v>112</v>
       </c>
       <c r="F90" t="s">
-        <v>1506</v>
+        <v>1565</v>
       </c>
       <c r="G90" t="s">
-        <v>1513</v>
+        <v>1572</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
@@ -17390,7 +18000,7 @@
         <v>27</v>
       </c>
       <c r="B91" t="s">
-        <v>1505</v>
+        <v>1564</v>
       </c>
       <c r="C91" t="s">
         <v>639</v>
@@ -17402,10 +18012,10 @@
         <v>86</v>
       </c>
       <c r="F91" t="s">
-        <v>1506</v>
+        <v>1565</v>
       </c>
       <c r="G91" t="s">
-        <v>1514</v>
+        <v>1573</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
@@ -17413,7 +18023,7 @@
         <v>27</v>
       </c>
       <c r="B92" t="s">
-        <v>1505</v>
+        <v>1564</v>
       </c>
       <c r="C92" t="s">
         <v>648</v>
@@ -17425,10 +18035,10 @@
         <v>112</v>
       </c>
       <c r="F92" t="s">
-        <v>1506</v>
+        <v>1565</v>
       </c>
       <c r="G92" t="s">
-        <v>1515</v>
+        <v>1574</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
@@ -17448,10 +18058,10 @@
         <v>86</v>
       </c>
       <c r="F93" t="s">
-        <v>1511</v>
+        <v>1570</v>
       </c>
       <c r="G93" t="s">
-        <v>1516</v>
+        <v>1575</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
@@ -17459,7 +18069,7 @@
         <v>27</v>
       </c>
       <c r="B94" t="s">
-        <v>1505</v>
+        <v>1564</v>
       </c>
       <c r="C94" t="s">
         <v>657</v>
@@ -17471,10 +18081,10 @@
         <v>112</v>
       </c>
       <c r="F94" t="s">
-        <v>1506</v>
+        <v>1565</v>
       </c>
       <c r="G94" t="s">
-        <v>1517</v>
+        <v>1576</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
@@ -17482,7 +18092,7 @@
         <v>27</v>
       </c>
       <c r="B95" t="s">
-        <v>1505</v>
+        <v>1564</v>
       </c>
       <c r="C95" t="s">
         <v>673</v>
@@ -17494,10 +18104,10 @@
         <v>112</v>
       </c>
       <c r="F95" t="s">
-        <v>1506</v>
+        <v>1565</v>
       </c>
       <c r="G95" t="s">
-        <v>1518</v>
+        <v>1577</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
@@ -17517,10 +18127,10 @@
         <v>26</v>
       </c>
       <c r="F96" t="s">
-        <v>1511</v>
+        <v>1570</v>
       </c>
       <c r="G96" t="s">
-        <v>1519</v>
+        <v>1578</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
@@ -17528,7 +18138,7 @@
         <v>27</v>
       </c>
       <c r="B97" t="s">
-        <v>1505</v>
+        <v>1564</v>
       </c>
       <c r="C97" t="s">
         <v>689</v>
@@ -17540,10 +18150,10 @@
         <v>112</v>
       </c>
       <c r="F97" t="s">
-        <v>1506</v>
+        <v>1565</v>
       </c>
       <c r="G97" t="s">
-        <v>1520</v>
+        <v>1579</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
@@ -17551,7 +18161,7 @@
         <v>27</v>
       </c>
       <c r="B98" t="s">
-        <v>1505</v>
+        <v>1564</v>
       </c>
       <c r="C98" t="s">
         <v>697</v>
@@ -17563,10 +18173,10 @@
         <v>112</v>
       </c>
       <c r="F98" t="s">
-        <v>1506</v>
+        <v>1565</v>
       </c>
       <c r="G98" t="s">
-        <v>1521</v>
+        <v>1580</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
@@ -17586,10 +18196,10 @@
         <v>26</v>
       </c>
       <c r="F99" t="s">
-        <v>1511</v>
+        <v>1570</v>
       </c>
       <c r="G99" t="s">
-        <v>1522</v>
+        <v>1581</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
@@ -17597,7 +18207,7 @@
         <v>27</v>
       </c>
       <c r="B100" t="s">
-        <v>1505</v>
+        <v>1564</v>
       </c>
       <c r="C100" t="s">
         <v>708</v>
@@ -17609,10 +18219,10 @@
         <v>112</v>
       </c>
       <c r="F100" t="s">
-        <v>1506</v>
+        <v>1565</v>
       </c>
       <c r="G100" t="s">
-        <v>1523</v>
+        <v>1582</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
@@ -17632,10 +18242,10 @@
         <v>86</v>
       </c>
       <c r="F101" t="s">
-        <v>1511</v>
+        <v>1570</v>
       </c>
       <c r="G101" t="s">
-        <v>1524</v>
+        <v>1583</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
@@ -17643,7 +18253,7 @@
         <v>27</v>
       </c>
       <c r="B102" t="s">
-        <v>1505</v>
+        <v>1564</v>
       </c>
       <c r="C102" t="s">
         <v>715</v>
@@ -17655,10 +18265,10 @@
         <v>112</v>
       </c>
       <c r="F102" t="s">
-        <v>1506</v>
+        <v>1565</v>
       </c>
       <c r="G102" t="s">
-        <v>1525</v>
+        <v>1584</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
@@ -17678,10 +18288,10 @@
         <v>86</v>
       </c>
       <c r="F103" t="s">
-        <v>1511</v>
+        <v>1570</v>
       </c>
       <c r="G103" t="s">
-        <v>1526</v>
+        <v>1585</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
@@ -17689,7 +18299,7 @@
         <v>27</v>
       </c>
       <c r="B104" t="s">
-        <v>1505</v>
+        <v>1564</v>
       </c>
       <c r="C104" t="s">
         <v>723</v>
@@ -17701,10 +18311,10 @@
         <v>112</v>
       </c>
       <c r="F104" t="s">
-        <v>1506</v>
+        <v>1565</v>
       </c>
       <c r="G104" t="s">
-        <v>1527</v>
+        <v>1586</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
@@ -17724,10 +18334,10 @@
         <v>26</v>
       </c>
       <c r="F105" t="s">
-        <v>1511</v>
+        <v>1570</v>
       </c>
       <c r="G105" t="s">
-        <v>1528</v>
+        <v>1587</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
@@ -17735,7 +18345,7 @@
         <v>27</v>
       </c>
       <c r="B106" t="s">
-        <v>1505</v>
+        <v>1564</v>
       </c>
       <c r="C106" t="s">
         <v>732</v>
@@ -17747,10 +18357,10 @@
         <v>112</v>
       </c>
       <c r="F106" t="s">
-        <v>1506</v>
+        <v>1565</v>
       </c>
       <c r="G106" t="s">
-        <v>1529</v>
+        <v>1588</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
@@ -17770,10 +18380,10 @@
         <v>26</v>
       </c>
       <c r="F107" t="s">
-        <v>1511</v>
+        <v>1570</v>
       </c>
       <c r="G107" t="s">
-        <v>1530</v>
+        <v>1589</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
@@ -17787,13 +18397,13 @@
         <v>740</v>
       </c>
       <c r="D108" t="s">
-        <v>1531</v>
+        <v>1590</v>
       </c>
       <c r="E108" t="s">
         <v>112</v>
       </c>
       <c r="F108" t="s">
-        <v>1511</v>
+        <v>1570</v>
       </c>
       <c r="G108" t="s">
         <v>741</v>
@@ -17810,13 +18420,13 @@
         <v>750</v>
       </c>
       <c r="D109" t="s">
-        <v>1531</v>
+        <v>1590</v>
       </c>
       <c r="E109" t="s">
         <v>112</v>
       </c>
       <c r="F109" t="s">
-        <v>1511</v>
+        <v>1570</v>
       </c>
       <c r="G109" t="s">
         <v>751</v>
@@ -17833,13 +18443,13 @@
         <v>758</v>
       </c>
       <c r="D110" t="s">
-        <v>1531</v>
+        <v>1590</v>
       </c>
       <c r="E110" t="s">
         <v>112</v>
       </c>
       <c r="F110" t="s">
-        <v>1511</v>
+        <v>1570</v>
       </c>
       <c r="G110" t="s">
         <v>759</v>
@@ -17856,13 +18466,13 @@
         <v>766</v>
       </c>
       <c r="D111" t="s">
-        <v>1531</v>
+        <v>1590</v>
       </c>
       <c r="E111" t="s">
         <v>112</v>
       </c>
       <c r="F111" t="s">
-        <v>1511</v>
+        <v>1570</v>
       </c>
       <c r="G111" t="s">
         <v>767</v>
@@ -17879,13 +18489,13 @@
         <v>774</v>
       </c>
       <c r="D112" t="s">
-        <v>1531</v>
+        <v>1590</v>
       </c>
       <c r="E112" t="s">
         <v>112</v>
       </c>
       <c r="F112" t="s">
-        <v>1511</v>
+        <v>1570</v>
       </c>
       <c r="G112" t="s">
         <v>775</v>
@@ -17902,13 +18512,13 @@
         <v>782</v>
       </c>
       <c r="D113" t="s">
-        <v>1531</v>
+        <v>1590</v>
       </c>
       <c r="E113" t="s">
         <v>112</v>
       </c>
       <c r="F113" t="s">
-        <v>1511</v>
+        <v>1570</v>
       </c>
       <c r="G113" t="s">
         <v>783</v>
@@ -17925,13 +18535,13 @@
         <v>790</v>
       </c>
       <c r="D114" t="s">
-        <v>1531</v>
+        <v>1590</v>
       </c>
       <c r="E114" t="s">
         <v>112</v>
       </c>
       <c r="F114" t="s">
-        <v>1511</v>
+        <v>1570</v>
       </c>
       <c r="G114" t="s">
         <v>791</v>
@@ -17948,13 +18558,13 @@
         <v>798</v>
       </c>
       <c r="D115" t="s">
-        <v>1531</v>
+        <v>1590</v>
       </c>
       <c r="E115" t="s">
         <v>112</v>
       </c>
       <c r="F115" t="s">
-        <v>1511</v>
+        <v>1570</v>
       </c>
       <c r="G115" t="s">
         <v>799</v>
@@ -17971,13 +18581,13 @@
         <v>806</v>
       </c>
       <c r="D116" t="s">
-        <v>1531</v>
+        <v>1590</v>
       </c>
       <c r="E116" t="s">
         <v>112</v>
       </c>
       <c r="F116" t="s">
-        <v>1511</v>
+        <v>1570</v>
       </c>
       <c r="G116" t="s">
         <v>807</v>
@@ -17994,13 +18604,13 @@
         <v>814</v>
       </c>
       <c r="D117" t="s">
-        <v>1531</v>
+        <v>1590</v>
       </c>
       <c r="E117" t="s">
         <v>112</v>
       </c>
       <c r="F117" t="s">
-        <v>1511</v>
+        <v>1570</v>
       </c>
       <c r="G117" t="s">
         <v>815</v>
@@ -18017,13 +18627,13 @@
         <v>821</v>
       </c>
       <c r="D118" t="s">
-        <v>1531</v>
+        <v>1590</v>
       </c>
       <c r="E118" t="s">
         <v>112</v>
       </c>
       <c r="F118" t="s">
-        <v>1511</v>
+        <v>1570</v>
       </c>
       <c r="G118" t="s">
         <v>823</v>
@@ -18040,13 +18650,13 @@
         <v>830</v>
       </c>
       <c r="D119" t="s">
-        <v>1531</v>
+        <v>1590</v>
       </c>
       <c r="E119" t="s">
         <v>112</v>
       </c>
       <c r="F119" t="s">
-        <v>1511</v>
+        <v>1570</v>
       </c>
       <c r="G119" t="s">
         <v>831</v>
@@ -18063,13 +18673,13 @@
         <v>837</v>
       </c>
       <c r="D120" t="s">
-        <v>1531</v>
+        <v>1590</v>
       </c>
       <c r="E120" t="s">
         <v>112</v>
       </c>
       <c r="F120" t="s">
-        <v>1511</v>
+        <v>1570</v>
       </c>
       <c r="G120" t="s">
         <v>838</v>
@@ -18086,13 +18696,13 @@
         <v>844</v>
       </c>
       <c r="D121" t="s">
-        <v>1531</v>
+        <v>1590</v>
       </c>
       <c r="E121" t="s">
         <v>112</v>
       </c>
       <c r="F121" t="s">
-        <v>1511</v>
+        <v>1570</v>
       </c>
       <c r="G121" t="s">
         <v>845</v>
@@ -18109,13 +18719,13 @@
         <v>852</v>
       </c>
       <c r="D122" t="s">
-        <v>1531</v>
+        <v>1590</v>
       </c>
       <c r="E122" t="s">
         <v>26</v>
       </c>
       <c r="F122" t="s">
-        <v>1511</v>
+        <v>1570</v>
       </c>
       <c r="G122" t="s">
         <v>853</v>
@@ -18132,13 +18742,13 @@
         <v>860</v>
       </c>
       <c r="D123" t="s">
-        <v>1531</v>
+        <v>1590</v>
       </c>
       <c r="E123" t="s">
         <v>112</v>
       </c>
       <c r="F123" t="s">
-        <v>1511</v>
+        <v>1570</v>
       </c>
       <c r="G123" t="s">
         <v>861</v>
@@ -18155,13 +18765,13 @@
         <v>868</v>
       </c>
       <c r="D124" t="s">
-        <v>1531</v>
+        <v>1590</v>
       </c>
       <c r="E124" t="s">
         <v>112</v>
       </c>
       <c r="F124" t="s">
-        <v>1511</v>
+        <v>1570</v>
       </c>
       <c r="G124" t="s">
         <v>869</v>
@@ -18178,13 +18788,13 @@
         <v>876</v>
       </c>
       <c r="D125" t="s">
-        <v>1531</v>
+        <v>1590</v>
       </c>
       <c r="E125" t="s">
         <v>112</v>
       </c>
       <c r="F125" t="s">
-        <v>1511</v>
+        <v>1570</v>
       </c>
       <c r="G125" t="s">
         <v>878</v>
@@ -18201,13 +18811,13 @@
         <v>885</v>
       </c>
       <c r="D126" t="s">
-        <v>1531</v>
+        <v>1590</v>
       </c>
       <c r="E126" t="s">
         <v>112</v>
       </c>
       <c r="F126" t="s">
-        <v>1511</v>
+        <v>1570</v>
       </c>
       <c r="G126" t="s">
         <v>886</v>
@@ -18224,13 +18834,13 @@
         <v>893</v>
       </c>
       <c r="D127" t="s">
-        <v>1531</v>
+        <v>1590</v>
       </c>
       <c r="E127" t="s">
         <v>112</v>
       </c>
       <c r="F127" t="s">
-        <v>1511</v>
+        <v>1570</v>
       </c>
       <c r="G127" t="s">
         <v>894</v>
@@ -18247,13 +18857,13 @@
         <v>901</v>
       </c>
       <c r="D128" t="s">
-        <v>1531</v>
+        <v>1590</v>
       </c>
       <c r="E128" t="s">
         <v>453</v>
       </c>
       <c r="F128" t="s">
-        <v>1511</v>
+        <v>1570</v>
       </c>
       <c r="G128" t="s">
         <v>902</v>
@@ -18270,13 +18880,13 @@
         <v>909</v>
       </c>
       <c r="D129" t="s">
-        <v>1531</v>
+        <v>1590</v>
       </c>
       <c r="E129" t="s">
         <v>112</v>
       </c>
       <c r="F129" t="s">
-        <v>1511</v>
+        <v>1570</v>
       </c>
       <c r="G129" t="s">
         <v>910</v>
@@ -18293,13 +18903,13 @@
         <v>916</v>
       </c>
       <c r="D130" t="s">
-        <v>1531</v>
+        <v>1590</v>
       </c>
       <c r="E130" t="s">
         <v>112</v>
       </c>
       <c r="F130" t="s">
-        <v>1511</v>
+        <v>1570</v>
       </c>
       <c r="G130" t="s">
         <v>917</v>
@@ -18316,13 +18926,13 @@
         <v>926</v>
       </c>
       <c r="D131" t="s">
-        <v>1531</v>
+        <v>1590</v>
       </c>
       <c r="E131" t="s">
         <v>112</v>
       </c>
       <c r="F131" t="s">
-        <v>1511</v>
+        <v>1570</v>
       </c>
       <c r="G131" t="s">
         <v>927</v>
@@ -18339,13 +18949,13 @@
         <v>934</v>
       </c>
       <c r="D132" t="s">
-        <v>1531</v>
+        <v>1590</v>
       </c>
       <c r="E132" t="s">
         <v>112</v>
       </c>
       <c r="F132" t="s">
-        <v>1511</v>
+        <v>1570</v>
       </c>
       <c r="G132" t="s">
         <v>935</v>
@@ -18362,13 +18972,13 @@
         <v>942</v>
       </c>
       <c r="D133" t="s">
-        <v>1531</v>
+        <v>1590</v>
       </c>
       <c r="E133" t="s">
         <v>112</v>
       </c>
       <c r="F133" t="s">
-        <v>1511</v>
+        <v>1570</v>
       </c>
       <c r="G133" t="s">
         <v>943</v>
@@ -18385,13 +18995,13 @@
         <v>950</v>
       </c>
       <c r="D134" t="s">
-        <v>1531</v>
+        <v>1590</v>
       </c>
       <c r="E134" t="s">
         <v>112</v>
       </c>
       <c r="F134" t="s">
-        <v>1511</v>
+        <v>1570</v>
       </c>
       <c r="G134" t="s">
         <v>951</v>
@@ -18408,13 +19018,13 @@
         <v>958</v>
       </c>
       <c r="D135" t="s">
-        <v>1531</v>
+        <v>1590</v>
       </c>
       <c r="E135" t="s">
         <v>112</v>
       </c>
       <c r="F135" t="s">
-        <v>1511</v>
+        <v>1570</v>
       </c>
       <c r="G135" t="s">
         <v>960</v>
@@ -18431,13 +19041,13 @@
         <v>967</v>
       </c>
       <c r="D136" t="s">
-        <v>1531</v>
+        <v>1590</v>
       </c>
       <c r="E136" t="s">
         <v>112</v>
       </c>
       <c r="F136" t="s">
-        <v>1511</v>
+        <v>1570</v>
       </c>
       <c r="G136" t="s">
         <v>968</v>
@@ -18454,13 +19064,13 @@
         <v>974</v>
       </c>
       <c r="D137" t="s">
-        <v>1531</v>
+        <v>1590</v>
       </c>
       <c r="E137" t="s">
         <v>112</v>
       </c>
       <c r="F137" t="s">
-        <v>1511</v>
+        <v>1570</v>
       </c>
       <c r="G137" t="s">
         <v>975</v>
@@ -18477,13 +19087,13 @@
         <v>981</v>
       </c>
       <c r="D138" t="s">
-        <v>1531</v>
+        <v>1590</v>
       </c>
       <c r="E138" t="s">
         <v>112</v>
       </c>
       <c r="F138" t="s">
-        <v>1511</v>
+        <v>1570</v>
       </c>
       <c r="G138" t="s">
         <v>982</v>
@@ -18500,13 +19110,13 @@
         <v>989</v>
       </c>
       <c r="D139" t="s">
-        <v>1531</v>
+        <v>1590</v>
       </c>
       <c r="E139" t="s">
         <v>112</v>
       </c>
       <c r="F139" t="s">
-        <v>1511</v>
+        <v>1570</v>
       </c>
       <c r="G139" t="s">
         <v>990</v>
@@ -18523,13 +19133,13 @@
         <v>997</v>
       </c>
       <c r="D140" t="s">
-        <v>1531</v>
+        <v>1590</v>
       </c>
       <c r="E140" t="s">
         <v>112</v>
       </c>
       <c r="F140" t="s">
-        <v>1511</v>
+        <v>1570</v>
       </c>
       <c r="G140" t="s">
         <v>998</v>
@@ -18546,13 +19156,13 @@
         <v>1006</v>
       </c>
       <c r="D141" t="s">
-        <v>1531</v>
+        <v>1590</v>
       </c>
       <c r="E141" t="s">
         <v>112</v>
       </c>
       <c r="F141" t="s">
-        <v>1511</v>
+        <v>1570</v>
       </c>
       <c r="G141" t="s">
         <v>1007</v>
@@ -18569,13 +19179,13 @@
         <v>1014</v>
       </c>
       <c r="D142" t="s">
-        <v>1531</v>
+        <v>1590</v>
       </c>
       <c r="E142" t="s">
         <v>112</v>
       </c>
       <c r="F142" t="s">
-        <v>1511</v>
+        <v>1570</v>
       </c>
       <c r="G142" t="s">
         <v>1015</v>
@@ -18592,13 +19202,13 @@
         <v>1021</v>
       </c>
       <c r="D143" t="s">
-        <v>1531</v>
+        <v>1590</v>
       </c>
       <c r="E143" t="s">
         <v>453</v>
       </c>
       <c r="F143" t="s">
-        <v>1511</v>
+        <v>1570</v>
       </c>
       <c r="G143" t="s">
         <v>1022</v>
@@ -18615,13 +19225,13 @@
         <v>1029</v>
       </c>
       <c r="D144" t="s">
-        <v>1531</v>
+        <v>1590</v>
       </c>
       <c r="E144" t="s">
         <v>112</v>
       </c>
       <c r="F144" t="s">
-        <v>1511</v>
+        <v>1570</v>
       </c>
       <c r="G144" t="s">
         <v>1031</v>
@@ -18638,13 +19248,13 @@
         <v>1037</v>
       </c>
       <c r="D145" t="s">
-        <v>1531</v>
+        <v>1590</v>
       </c>
       <c r="E145" t="s">
         <v>112</v>
       </c>
       <c r="F145" t="s">
-        <v>1511</v>
+        <v>1570</v>
       </c>
       <c r="G145" t="s">
         <v>1038</v>
@@ -18661,13 +19271,13 @@
         <v>1045</v>
       </c>
       <c r="D146" t="s">
-        <v>1531</v>
+        <v>1590</v>
       </c>
       <c r="E146" t="s">
         <v>112</v>
       </c>
       <c r="F146" t="s">
-        <v>1511</v>
+        <v>1570</v>
       </c>
       <c r="G146" t="s">
         <v>1046</v>
@@ -18684,13 +19294,13 @@
         <v>1053</v>
       </c>
       <c r="D147" t="s">
-        <v>1531</v>
+        <v>1590</v>
       </c>
       <c r="E147" t="s">
         <v>112</v>
       </c>
       <c r="F147" t="s">
-        <v>1511</v>
+        <v>1570</v>
       </c>
       <c r="G147" t="s">
         <v>1055</v>
@@ -18707,13 +19317,13 @@
         <v>1061</v>
       </c>
       <c r="D148" t="s">
-        <v>1531</v>
+        <v>1590</v>
       </c>
       <c r="E148" t="s">
         <v>112</v>
       </c>
       <c r="F148" t="s">
-        <v>1511</v>
+        <v>1570</v>
       </c>
       <c r="G148" t="s">
         <v>1062</v>
@@ -18730,13 +19340,13 @@
         <v>1068</v>
       </c>
       <c r="D149" t="s">
-        <v>1531</v>
+        <v>1590</v>
       </c>
       <c r="E149" t="s">
         <v>95</v>
       </c>
       <c r="F149" t="s">
-        <v>1511</v>
+        <v>1570</v>
       </c>
       <c r="G149" t="s">
         <v>1069</v>
@@ -18753,13 +19363,13 @@
         <v>1076</v>
       </c>
       <c r="D150" t="s">
-        <v>1531</v>
+        <v>1590</v>
       </c>
       <c r="E150" t="s">
         <v>112</v>
       </c>
       <c r="F150" t="s">
-        <v>1511</v>
+        <v>1570</v>
       </c>
       <c r="G150" t="s">
         <v>1078</v>
@@ -18776,13 +19386,13 @@
         <v>1085</v>
       </c>
       <c r="D151" t="s">
-        <v>1531</v>
+        <v>1590</v>
       </c>
       <c r="E151" t="s">
         <v>95</v>
       </c>
       <c r="F151" t="s">
-        <v>1511</v>
+        <v>1570</v>
       </c>
       <c r="G151" t="s">
         <v>1086</v>
@@ -18799,13 +19409,13 @@
         <v>1093</v>
       </c>
       <c r="D152" t="s">
-        <v>1531</v>
+        <v>1590</v>
       </c>
       <c r="E152" t="s">
         <v>112</v>
       </c>
       <c r="F152" t="s">
-        <v>1511</v>
+        <v>1570</v>
       </c>
       <c r="G152" t="s">
         <v>1094</v>
@@ -18822,13 +19432,13 @@
         <v>1102</v>
       </c>
       <c r="D153" t="s">
-        <v>1531</v>
+        <v>1590</v>
       </c>
       <c r="E153" t="s">
         <v>112</v>
       </c>
       <c r="F153" t="s">
-        <v>1511</v>
+        <v>1570</v>
       </c>
       <c r="G153" t="s">
         <v>1103</v>
@@ -18845,13 +19455,13 @@
         <v>1109</v>
       </c>
       <c r="D154" t="s">
-        <v>1531</v>
+        <v>1590</v>
       </c>
       <c r="E154" t="s">
         <v>453</v>
       </c>
       <c r="F154" t="s">
-        <v>1511</v>
+        <v>1570</v>
       </c>
       <c r="G154" t="s">
         <v>1110</v>
@@ -18868,13 +19478,13 @@
         <v>1117</v>
       </c>
       <c r="D155" t="s">
-        <v>1531</v>
+        <v>1590</v>
       </c>
       <c r="E155" t="s">
         <v>112</v>
       </c>
       <c r="F155" t="s">
-        <v>1511</v>
+        <v>1570</v>
       </c>
       <c r="G155" t="s">
         <v>1118</v>
@@ -18891,13 +19501,13 @@
         <v>1124</v>
       </c>
       <c r="D156" t="s">
-        <v>1531</v>
+        <v>1590</v>
       </c>
       <c r="E156" t="s">
         <v>95</v>
       </c>
       <c r="F156" t="s">
-        <v>1511</v>
+        <v>1570</v>
       </c>
       <c r="G156" t="s">
         <v>1125</v>
@@ -18914,13 +19524,13 @@
         <v>1132</v>
       </c>
       <c r="D157" t="s">
-        <v>1531</v>
+        <v>1590</v>
       </c>
       <c r="E157" t="s">
         <v>112</v>
       </c>
       <c r="F157" t="s">
-        <v>1511</v>
+        <v>1570</v>
       </c>
       <c r="G157" t="s">
         <v>1133</v>
@@ -18937,13 +19547,13 @@
         <v>1139</v>
       </c>
       <c r="D158" t="s">
-        <v>1531</v>
+        <v>1590</v>
       </c>
       <c r="E158" t="s">
         <v>112</v>
       </c>
       <c r="F158" t="s">
-        <v>1511</v>
+        <v>1570</v>
       </c>
       <c r="G158" t="s">
         <v>1140</v>
@@ -18960,13 +19570,13 @@
         <v>1148</v>
       </c>
       <c r="D159" t="s">
-        <v>1531</v>
+        <v>1590</v>
       </c>
       <c r="E159" t="s">
         <v>112</v>
       </c>
       <c r="F159" t="s">
-        <v>1511</v>
+        <v>1570</v>
       </c>
       <c r="G159" t="s">
         <v>1149</v>
@@ -18983,13 +19593,13 @@
         <v>1156</v>
       </c>
       <c r="D160" t="s">
-        <v>1531</v>
+        <v>1590</v>
       </c>
       <c r="E160" t="s">
         <v>112</v>
       </c>
       <c r="F160" t="s">
-        <v>1511</v>
+        <v>1570</v>
       </c>
       <c r="G160" t="s">
         <v>1157</v>
@@ -19006,13 +19616,13 @@
         <v>1165</v>
       </c>
       <c r="D161" t="s">
-        <v>1531</v>
+        <v>1590</v>
       </c>
       <c r="E161" t="s">
         <v>95</v>
       </c>
       <c r="F161" t="s">
-        <v>1511</v>
+        <v>1570</v>
       </c>
       <c r="G161" t="s">
         <v>1166</v>
@@ -19029,13 +19639,13 @@
         <v>1173</v>
       </c>
       <c r="D162" t="s">
-        <v>1531</v>
+        <v>1590</v>
       </c>
       <c r="E162" t="s">
         <v>112</v>
       </c>
       <c r="F162" t="s">
-        <v>1511</v>
+        <v>1570</v>
       </c>
       <c r="G162" t="s">
         <v>1175</v>
@@ -19052,13 +19662,13 @@
         <v>1181</v>
       </c>
       <c r="D163" t="s">
-        <v>1531</v>
+        <v>1590</v>
       </c>
       <c r="E163" t="s">
         <v>112</v>
       </c>
       <c r="F163" t="s">
-        <v>1511</v>
+        <v>1570</v>
       </c>
       <c r="G163" t="s">
         <v>1182</v>
@@ -19072,19 +19682,19 @@
         <v>1158</v>
       </c>
       <c r="C164" t="s">
-        <v>1188</v>
+        <v>1189</v>
       </c>
       <c r="D164" t="s">
-        <v>1531</v>
+        <v>1590</v>
       </c>
       <c r="E164" t="s">
         <v>112</v>
       </c>
       <c r="F164" t="s">
-        <v>1511</v>
+        <v>1570</v>
       </c>
       <c r="G164" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.25">
@@ -19095,19 +19705,19 @@
         <v>1158</v>
       </c>
       <c r="C165" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="D165" t="s">
-        <v>1531</v>
+        <v>1590</v>
       </c>
       <c r="E165" t="s">
         <v>112</v>
       </c>
       <c r="F165" t="s">
-        <v>1511</v>
+        <v>1570</v>
       </c>
       <c r="G165" t="s">
-        <v>1196</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.25">
@@ -19118,19 +19728,180 @@
         <v>1158</v>
       </c>
       <c r="C166" t="s">
-        <v>1203</v>
+        <v>1204</v>
       </c>
       <c r="D166" t="s">
-        <v>1531</v>
+        <v>1590</v>
       </c>
       <c r="E166" t="s">
         <v>95</v>
       </c>
       <c r="F166" t="s">
-        <v>1511</v>
+        <v>1570</v>
       </c>
       <c r="G166" t="s">
-        <v>1204</v>
+        <v>1205</v>
+      </c>
+    </row>
+    <row r="167" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A167" t="s">
+        <v>27</v>
+      </c>
+      <c r="B167" t="s">
+        <v>1214</v>
+      </c>
+      <c r="C167" t="s">
+        <v>1212</v>
+      </c>
+      <c r="D167" t="s">
+        <v>1590</v>
+      </c>
+      <c r="E167" t="s">
+        <v>112</v>
+      </c>
+      <c r="F167" t="s">
+        <v>1570</v>
+      </c>
+      <c r="G167" t="s">
+        <v>1213</v>
+      </c>
+    </row>
+    <row r="168" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A168" t="s">
+        <v>27</v>
+      </c>
+      <c r="B168" t="s">
+        <v>1214</v>
+      </c>
+      <c r="C168" t="s">
+        <v>1221</v>
+      </c>
+      <c r="D168" t="s">
+        <v>1590</v>
+      </c>
+      <c r="E168" t="s">
+        <v>112</v>
+      </c>
+      <c r="F168" t="s">
+        <v>1570</v>
+      </c>
+      <c r="G168" t="s">
+        <v>1222</v>
+      </c>
+    </row>
+    <row r="169" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A169" t="s">
+        <v>27</v>
+      </c>
+      <c r="B169" t="s">
+        <v>1214</v>
+      </c>
+      <c r="C169" t="s">
+        <v>1229</v>
+      </c>
+      <c r="D169" t="s">
+        <v>1590</v>
+      </c>
+      <c r="E169" t="s">
+        <v>112</v>
+      </c>
+      <c r="F169" t="s">
+        <v>1570</v>
+      </c>
+      <c r="G169" t="s">
+        <v>1230</v>
+      </c>
+    </row>
+    <row r="170" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A170" t="s">
+        <v>27</v>
+      </c>
+      <c r="B170" t="s">
+        <v>1214</v>
+      </c>
+      <c r="C170" t="s">
+        <v>1237</v>
+      </c>
+      <c r="D170" t="s">
+        <v>1590</v>
+      </c>
+      <c r="E170" t="s">
+        <v>112</v>
+      </c>
+      <c r="F170" t="s">
+        <v>1570</v>
+      </c>
+      <c r="G170" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="171" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A171" t="s">
+        <v>27</v>
+      </c>
+      <c r="B171" t="s">
+        <v>1214</v>
+      </c>
+      <c r="C171" t="s">
+        <v>1244</v>
+      </c>
+      <c r="D171" t="s">
+        <v>1590</v>
+      </c>
+      <c r="E171" t="s">
+        <v>112</v>
+      </c>
+      <c r="F171" t="s">
+        <v>1570</v>
+      </c>
+      <c r="G171" t="s">
+        <v>1245</v>
+      </c>
+    </row>
+    <row r="172" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A172" t="s">
+        <v>27</v>
+      </c>
+      <c r="B172" t="s">
+        <v>1214</v>
+      </c>
+      <c r="C172" t="s">
+        <v>1251</v>
+      </c>
+      <c r="D172" t="s">
+        <v>1590</v>
+      </c>
+      <c r="E172" t="s">
+        <v>453</v>
+      </c>
+      <c r="F172" t="s">
+        <v>1570</v>
+      </c>
+      <c r="G172" t="s">
+        <v>1252</v>
+      </c>
+    </row>
+    <row r="173" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A173" t="s">
+        <v>27</v>
+      </c>
+      <c r="B173" t="s">
+        <v>1214</v>
+      </c>
+      <c r="C173" t="s">
+        <v>1259</v>
+      </c>
+      <c r="D173" t="s">
+        <v>1590</v>
+      </c>
+      <c r="E173" t="s">
+        <v>112</v>
+      </c>
+      <c r="F173" t="s">
+        <v>1570</v>
+      </c>
+      <c r="G173" t="s">
+        <v>1260</v>
       </c>
     </row>
   </sheetData>
@@ -19144,7 +19915,7 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>1532</v>
+        <v>1591</v>
       </c>
       <c r="B1"/>
       <c r="C1"/>
@@ -19152,7 +19923,7 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1533</v>
+        <v>1592</v>
       </c>
       <c r="B2"/>
       <c r="C2"/>
@@ -19163,181 +19934,181 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>1534</v>
+        <v>1593</v>
       </c>
       <c r="C3" t="s">
-        <v>1535</v>
+        <v>1594</v>
       </c>
       <c r="D3" t="s">
-        <v>1536</v>
+        <v>1595</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1537</v>
+        <v>1596</v>
       </c>
       <c r="B4" t="s">
-        <v>1538</v>
+        <v>1597</v>
       </c>
       <c r="C4" t="s">
-        <v>1539</v>
+        <v>1598</v>
       </c>
       <c r="D4" t="s">
-        <v>1540</v>
+        <v>1599</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1541</v>
+        <v>1600</v>
       </c>
       <c r="B5" t="s">
-        <v>1538</v>
+        <v>1597</v>
       </c>
       <c r="C5" t="s">
-        <v>1542</v>
+        <v>1601</v>
       </c>
       <c r="D5" t="s">
-        <v>1543</v>
+        <v>1602</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>1544</v>
+        <v>1603</v>
       </c>
       <c r="B6" t="s">
-        <v>1538</v>
+        <v>1597</v>
       </c>
       <c r="C6" t="s">
-        <v>1545</v>
+        <v>1604</v>
       </c>
       <c r="D6" t="s">
-        <v>1546</v>
+        <v>1605</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>1547</v>
+        <v>1606</v>
       </c>
       <c r="B7" t="s">
-        <v>1538</v>
+        <v>1597</v>
       </c>
       <c r="C7" t="s">
-        <v>1548</v>
+        <v>1607</v>
       </c>
       <c r="D7" t="s">
-        <v>1549</v>
+        <v>1608</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>1550</v>
+        <v>1609</v>
       </c>
       <c r="B8" t="s">
-        <v>1538</v>
+        <v>1597</v>
       </c>
       <c r="C8" t="s">
-        <v>1551</v>
+        <v>1610</v>
       </c>
       <c r="D8" t="s">
-        <v>1552</v>
+        <v>1611</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>1553</v>
+        <v>1612</v>
       </c>
       <c r="B9" t="s">
-        <v>1554</v>
+        <v>1613</v>
       </c>
       <c r="C9" t="s">
-        <v>1555</v>
+        <v>1614</v>
       </c>
       <c r="D9" t="s">
-        <v>1556</v>
+        <v>1615</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>1557</v>
+        <v>1616</v>
       </c>
       <c r="B10" t="s">
-        <v>1554</v>
+        <v>1613</v>
       </c>
       <c r="C10" t="s">
-        <v>1558</v>
+        <v>1617</v>
       </c>
       <c r="D10" t="s">
-        <v>1559</v>
+        <v>1618</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>1560</v>
+        <v>1619</v>
       </c>
       <c r="B11" t="s">
-        <v>1554</v>
+        <v>1613</v>
       </c>
       <c r="C11" t="s">
-        <v>1561</v>
+        <v>1620</v>
       </c>
       <c r="D11" t="s">
-        <v>1562</v>
+        <v>1621</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>1563</v>
+        <v>1622</v>
       </c>
       <c r="B12" t="s">
-        <v>1564</v>
+        <v>1623</v>
       </c>
       <c r="C12" t="s">
-        <v>1565</v>
+        <v>1624</v>
       </c>
       <c r="D12" t="s">
-        <v>1566</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>1567</v>
+        <v>1626</v>
       </c>
       <c r="B13" t="s">
-        <v>1564</v>
+        <v>1623</v>
       </c>
       <c r="C13" t="s">
-        <v>1568</v>
+        <v>1627</v>
       </c>
       <c r="D13" t="s">
-        <v>1569</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>1570</v>
+        <v>1629</v>
       </c>
       <c r="B14" t="s">
         <v>877</v>
       </c>
       <c r="C14" t="s">
-        <v>1571</v>
+        <v>1630</v>
       </c>
       <c r="D14" t="s">
-        <v>1572</v>
+        <v>1631</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>1573</v>
+        <v>1632</v>
       </c>
       <c r="B15" t="s">
         <v>877</v>
       </c>
       <c r="C15" t="s">
-        <v>1574</v>
+        <v>1633</v>
       </c>
       <c r="D15" t="s">
-        <v>1575</v>
+        <v>1634</v>
       </c>
     </row>
   </sheetData>
@@ -19356,7 +20127,7 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>1576</v>
+        <v>1635</v>
       </c>
       <c r="B1"/>
       <c r="C1"/>
@@ -19364,133 +20135,133 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>1577</v>
+        <v>1636</v>
       </c>
       <c r="B3" t="s">
-        <v>1578</v>
+        <v>1637</v>
       </c>
       <c r="C3" t="s">
-        <v>1579</v>
+        <v>1638</v>
       </c>
       <c r="D3" t="s">
-        <v>1580</v>
+        <v>1639</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1251</v>
+        <v>1307</v>
       </c>
       <c r="B4" t="s">
-        <v>1581</v>
+        <v>1640</v>
       </c>
       <c r="C4" t="s">
-        <v>1582</v>
+        <v>1641</v>
       </c>
       <c r="D4" t="s">
-        <v>1583</v>
+        <v>1642</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1256</v>
+        <v>1312</v>
       </c>
       <c r="B5" t="s">
-        <v>1584</v>
+        <v>1643</v>
       </c>
       <c r="C5" t="s">
-        <v>1585</v>
+        <v>1644</v>
       </c>
       <c r="D5" t="s">
-        <v>1586</v>
+        <v>1645</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>1260</v>
+        <v>1316</v>
       </c>
       <c r="B6" t="s">
-        <v>1587</v>
+        <v>1646</v>
       </c>
       <c r="C6" t="s">
-        <v>1588</v>
+        <v>1647</v>
       </c>
       <c r="D6" t="s">
-        <v>1589</v>
+        <v>1648</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>1264</v>
+        <v>1320</v>
       </c>
       <c r="B7" t="s">
-        <v>1590</v>
+        <v>1649</v>
       </c>
       <c r="C7" t="s">
-        <v>1591</v>
+        <v>1650</v>
       </c>
       <c r="D7" t="s">
-        <v>1592</v>
+        <v>1651</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>1268</v>
+        <v>1324</v>
       </c>
       <c r="B8" t="s">
-        <v>1593</v>
+        <v>1652</v>
       </c>
       <c r="C8" t="s">
-        <v>1594</v>
+        <v>1653</v>
       </c>
       <c r="D8" t="s">
-        <v>1595</v>
+        <v>1654</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>1272</v>
+        <v>1328</v>
       </c>
       <c r="B9" t="s">
-        <v>1596</v>
+        <v>1655</v>
       </c>
       <c r="C9" t="s">
-        <v>1597</v>
+        <v>1656</v>
       </c>
       <c r="D9" t="s">
-        <v>1598</v>
+        <v>1657</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>1276</v>
+        <v>1332</v>
       </c>
       <c r="B10" t="s">
-        <v>1599</v>
+        <v>1658</v>
       </c>
       <c r="C10" t="s">
-        <v>1600</v>
+        <v>1659</v>
       </c>
       <c r="D10" t="s">
-        <v>1601</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>1280</v>
+        <v>1336</v>
       </c>
       <c r="B11" t="s">
-        <v>1602</v>
+        <v>1661</v>
       </c>
       <c r="C11" t="s">
-        <v>1603</v>
+        <v>1662</v>
       </c>
       <c r="D11" t="s">
-        <v>1604</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>1605</v>
+        <v>1664</v>
       </c>
       <c r="B13"/>
       <c r="C13"/>
@@ -19498,72 +20269,72 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>1606</v>
+        <v>1665</v>
       </c>
       <c r="B14" t="s">
         <v>28</v>
       </c>
       <c r="C14" t="s">
-        <v>1607</v>
+        <v>1666</v>
       </c>
       <c r="D14" t="s">
-        <v>1608</v>
+        <v>1667</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>1609</v>
+        <v>1668</v>
       </c>
       <c r="B15" t="s">
         <v>29</v>
       </c>
       <c r="C15" t="s">
-        <v>1610</v>
+        <v>1669</v>
       </c>
       <c r="D15" t="s">
-        <v>1611</v>
+        <v>1670</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>1612</v>
+        <v>1671</v>
       </c>
       <c r="B16" t="s">
         <v>29</v>
       </c>
       <c r="C16" t="s">
-        <v>1613</v>
+        <v>1672</v>
       </c>
       <c r="D16" t="s">
-        <v>1614</v>
+        <v>1673</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>1615</v>
+        <v>1674</v>
       </c>
       <c r="B17" t="s">
         <v>29</v>
       </c>
       <c r="C17" t="s">
-        <v>1616</v>
+        <v>1675</v>
       </c>
       <c r="D17" t="s">
-        <v>1617</v>
+        <v>1676</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>1618</v>
+        <v>1677</v>
       </c>
       <c r="B18" t="s">
-        <v>1619</v>
+        <v>1678</v>
       </c>
       <c r="C18" t="s">
-        <v>1620</v>
+        <v>1679</v>
       </c>
       <c r="D18" t="s">
-        <v>1621</v>
+        <v>1680</v>
       </c>
     </row>
   </sheetData>
@@ -19582,7 +20353,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>1622</v>
+        <v>1681</v>
       </c>
       <c r="B1"/>
       <c r="C1"/>
@@ -19592,7 +20363,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1623</v>
+        <v>1682</v>
       </c>
       <c r="B2"/>
       <c r="C2"/>
@@ -19602,99 +20373,99 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1624</v>
+        <v>1683</v>
       </c>
       <c r="B4" t="s">
-        <v>1625</v>
+        <v>1684</v>
       </c>
       <c r="C4" t="s">
-        <v>1626</v>
+        <v>1685</v>
       </c>
       <c r="D4" t="s">
-        <v>1627</v>
+        <v>1686</v>
       </c>
       <c r="E4" t="s">
-        <v>1628</v>
+        <v>1687</v>
       </c>
       <c r="F4" t="s">
-        <v>1629</v>
+        <v>1688</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1630</v>
+        <v>1689</v>
       </c>
       <c r="B5" t="s">
-        <v>1631</v>
+        <v>1690</v>
       </c>
       <c r="C5" t="s">
-        <v>1632</v>
+        <v>1691</v>
       </c>
       <c r="D5" t="s">
-        <v>1633</v>
+        <v>1692</v>
       </c>
       <c r="E5" t="s">
-        <v>1634</v>
+        <v>1693</v>
       </c>
       <c r="F5" t="s">
-        <v>1635</v>
+        <v>1694</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>1636</v>
+        <v>1695</v>
       </c>
       <c r="B6" t="s">
-        <v>1637</v>
+        <v>1696</v>
       </c>
       <c r="C6" t="s">
-        <v>1638</v>
+        <v>1697</v>
       </c>
       <c r="D6" t="s">
-        <v>1639</v>
+        <v>1698</v>
       </c>
       <c r="E6" t="s">
-        <v>1640</v>
+        <v>1699</v>
       </c>
       <c r="F6" t="s">
-        <v>1641</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>1642</v>
+        <v>1701</v>
       </c>
       <c r="B7" t="s">
-        <v>1637</v>
+        <v>1696</v>
       </c>
       <c r="C7" t="s">
-        <v>1643</v>
+        <v>1702</v>
       </c>
       <c r="D7" t="s">
-        <v>1644</v>
+        <v>1703</v>
       </c>
       <c r="E7" t="s">
-        <v>1645</v>
+        <v>1704</v>
       </c>
       <c r="F7" t="s">
-        <v>1646</v>
+        <v>1705</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>1647</v>
+        <v>1706</v>
       </c>
       <c r="B8" t="s">
-        <v>1648</v>
+        <v>1707</v>
       </c>
       <c r="C8" t="s">
-        <v>1649</v>
+        <v>1708</v>
       </c>
       <c r="D8" t="s">
-        <v>1650</v>
+        <v>1709</v>
       </c>
       <c r="E8" t="s">
-        <v>1651</v>
+        <v>1710</v>
       </c>
       <c r="F8" t="s">
         <v>629</v>
@@ -19702,19 +20473,19 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>1652</v>
+        <v>1711</v>
       </c>
       <c r="B9" t="s">
-        <v>1653</v>
+        <v>1712</v>
       </c>
       <c r="C9" t="s">
-        <v>1654</v>
+        <v>1713</v>
       </c>
       <c r="D9" t="s">
-        <v>1655</v>
+        <v>1714</v>
       </c>
       <c r="E9" t="s">
-        <v>1656</v>
+        <v>1715</v>
       </c>
       <c r="F9" t="s">
         <v>369</v>
@@ -19722,39 +20493,39 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>1657</v>
+        <v>1716</v>
       </c>
       <c r="B10" t="s">
-        <v>1658</v>
+        <v>1717</v>
       </c>
       <c r="C10" t="s">
-        <v>1659</v>
+        <v>1718</v>
       </c>
       <c r="D10" t="s">
-        <v>1660</v>
+        <v>1719</v>
       </c>
       <c r="E10" t="s">
-        <v>1661</v>
+        <v>1720</v>
       </c>
       <c r="F10" t="s">
-        <v>1662</v>
+        <v>1721</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>1663</v>
+        <v>1722</v>
       </c>
       <c r="B11" t="s">
-        <v>1664</v>
+        <v>1723</v>
       </c>
       <c r="C11" t="s">
-        <v>1665</v>
+        <v>1724</v>
       </c>
       <c r="D11" t="s">
-        <v>1666</v>
+        <v>1725</v>
       </c>
       <c r="E11" t="s">
-        <v>1667</v>
+        <v>1726</v>
       </c>
       <c r="F11" t="s">
         <v>47</v>
@@ -19762,99 +20533,99 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>1668</v>
+        <v>1727</v>
       </c>
       <c r="B12" t="s">
-        <v>1669</v>
+        <v>1728</v>
       </c>
       <c r="C12" t="s">
-        <v>1670</v>
+        <v>1729</v>
       </c>
       <c r="D12" t="s">
-        <v>1671</v>
+        <v>1730</v>
       </c>
       <c r="E12" t="s">
-        <v>1672</v>
+        <v>1731</v>
       </c>
       <c r="F12" t="s">
-        <v>1673</v>
+        <v>1732</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>1674</v>
+        <v>1733</v>
       </c>
       <c r="B13" t="s">
-        <v>1675</v>
+        <v>1734</v>
       </c>
       <c r="C13" t="s">
-        <v>1676</v>
+        <v>1735</v>
       </c>
       <c r="D13" t="s">
-        <v>1677</v>
+        <v>1736</v>
       </c>
       <c r="E13" t="s">
-        <v>1678</v>
+        <v>1737</v>
       </c>
       <c r="F13" t="s">
-        <v>1679</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>1680</v>
+        <v>1739</v>
       </c>
       <c r="B14" t="s">
-        <v>1681</v>
+        <v>1740</v>
       </c>
       <c r="C14" t="s">
-        <v>1682</v>
+        <v>1741</v>
       </c>
       <c r="D14" t="s">
-        <v>1683</v>
+        <v>1742</v>
       </c>
       <c r="E14" t="s">
-        <v>1684</v>
+        <v>1743</v>
       </c>
       <c r="F14" t="s">
-        <v>1685</v>
+        <v>1744</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>1686</v>
+        <v>1745</v>
       </c>
       <c r="B15" t="s">
-        <v>1687</v>
+        <v>1746</v>
       </c>
       <c r="C15" t="s">
-        <v>1688</v>
+        <v>1747</v>
       </c>
       <c r="D15" t="s">
-        <v>1689</v>
+        <v>1748</v>
       </c>
       <c r="E15" t="s">
-        <v>1690</v>
+        <v>1749</v>
       </c>
       <c r="F15" t="s">
-        <v>1691</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>1692</v>
+        <v>1751</v>
       </c>
       <c r="B16" t="s">
-        <v>1693</v>
+        <v>1752</v>
       </c>
       <c r="C16" t="s">
-        <v>1694</v>
+        <v>1753</v>
       </c>
       <c r="D16" t="s">
-        <v>1695</v>
+        <v>1754</v>
       </c>
       <c r="E16" t="s">
-        <v>1696</v>
+        <v>1755</v>
       </c>
       <c r="F16" t="s">
         <v>207</v>
@@ -19862,19 +20633,19 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>1697</v>
+        <v>1756</v>
       </c>
       <c r="B17" t="s">
-        <v>1698</v>
+        <v>1757</v>
       </c>
       <c r="C17" t="s">
-        <v>1699</v>
+        <v>1758</v>
       </c>
       <c r="D17" t="s">
-        <v>1700</v>
+        <v>1759</v>
       </c>
       <c r="E17" t="s">
-        <v>1701</v>
+        <v>1760</v>
       </c>
       <c r="F17" t="s">
         <v>378</v>
@@ -19896,7 +20667,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>1702</v>
+        <v>1761</v>
       </c>
       <c r="B1"/>
       <c r="C1"/>
@@ -19906,7 +20677,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1703</v>
+        <v>1762</v>
       </c>
       <c r="B2"/>
       <c r="C2"/>
@@ -19916,162 +20687,162 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1704</v>
+        <v>1763</v>
       </c>
       <c r="B4" t="s">
-        <v>1602</v>
+        <v>1661</v>
       </c>
       <c r="C4" t="s">
-        <v>1705</v>
+        <v>1764</v>
       </c>
       <c r="D4" t="s">
-        <v>1706</v>
+        <v>1765</v>
       </c>
       <c r="E4" t="s">
-        <v>1248</v>
+        <v>1304</v>
       </c>
       <c r="F4" t="s">
-        <v>1707</v>
+        <v>1766</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1251</v>
+        <v>1307</v>
       </c>
       <c r="B5" t="s">
-        <v>1708</v>
+        <v>1767</v>
       </c>
       <c r="C5" t="s">
-        <v>1709</v>
+        <v>1768</v>
       </c>
       <c r="D5" t="s">
-        <v>1710</v>
+        <v>1769</v>
       </c>
       <c r="E5" t="s">
-        <v>1711</v>
+        <v>1770</v>
       </c>
       <c r="F5" t="s">
-        <v>1712</v>
+        <v>1771</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>1256</v>
+        <v>1312</v>
       </c>
       <c r="B6" t="s">
-        <v>1713</v>
+        <v>1772</v>
       </c>
       <c r="C6" t="s">
-        <v>1714</v>
+        <v>1773</v>
       </c>
       <c r="D6" t="s">
-        <v>1715</v>
+        <v>1774</v>
       </c>
       <c r="E6" t="s">
-        <v>1716</v>
+        <v>1775</v>
       </c>
       <c r="F6" t="s">
-        <v>1712</v>
+        <v>1771</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>1260</v>
+        <v>1316</v>
       </c>
       <c r="B7" t="s">
-        <v>1717</v>
+        <v>1776</v>
       </c>
       <c r="C7" t="s">
-        <v>1718</v>
+        <v>1777</v>
       </c>
       <c r="D7" t="s">
-        <v>1719</v>
+        <v>1778</v>
       </c>
       <c r="E7" t="s">
-        <v>1720</v>
+        <v>1779</v>
       </c>
       <c r="F7" t="s">
-        <v>1712</v>
+        <v>1771</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>1264</v>
+        <v>1320</v>
       </c>
       <c r="B8" t="s">
-        <v>1721</v>
+        <v>1780</v>
       </c>
       <c r="C8" t="s">
-        <v>1722</v>
+        <v>1781</v>
       </c>
       <c r="D8" t="s">
-        <v>1723</v>
+        <v>1782</v>
       </c>
       <c r="E8" t="s">
-        <v>1724</v>
+        <v>1783</v>
       </c>
       <c r="F8" t="s">
-        <v>1712</v>
+        <v>1771</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>1268</v>
+        <v>1324</v>
       </c>
       <c r="B9" t="s">
-        <v>1725</v>
+        <v>1784</v>
       </c>
       <c r="C9" t="s">
-        <v>1726</v>
+        <v>1785</v>
       </c>
       <c r="D9" t="s">
-        <v>1727</v>
+        <v>1786</v>
       </c>
       <c r="E9" t="s">
         <v>877</v>
       </c>
       <c r="F9" t="s">
-        <v>1728</v>
+        <v>1787</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>1272</v>
+        <v>1328</v>
       </c>
       <c r="B10" t="s">
-        <v>1729</v>
+        <v>1788</v>
       </c>
       <c r="C10" t="s">
-        <v>1730</v>
+        <v>1789</v>
       </c>
       <c r="D10" t="s">
-        <v>1731</v>
+        <v>1790</v>
       </c>
       <c r="E10" t="s">
-        <v>1732</v>
+        <v>1791</v>
       </c>
       <c r="F10" t="s">
-        <v>1728</v>
+        <v>1787</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>1276</v>
+        <v>1332</v>
       </c>
       <c r="B11" t="s">
-        <v>1733</v>
+        <v>1792</v>
       </c>
       <c r="C11" t="s">
-        <v>1734</v>
+        <v>1793</v>
       </c>
       <c r="D11" t="s">
-        <v>1735</v>
+        <v>1794</v>
       </c>
       <c r="E11" t="s">
-        <v>1736</v>
+        <v>1795</v>
       </c>
       <c r="F11" t="s">
-        <v>1737</v>
+        <v>1796</v>
       </c>
     </row>
   </sheetData>

--- a/audits/FORTLESS_MASTER_SECURITY_UI_BUG_TRACKER.xlsx
+++ b/audits/FORTLESS_MASTER_SECURITY_UI_BUG_TRACKER.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4666" uniqueCount="1797">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4776" uniqueCount="1835">
   <si>
     <t>FORTLESS   /   ENGINEERING FINDINGS REGISTER</t>
   </si>
@@ -2868,7 +2868,7 @@
     <t>Test: VIEWER receives 403 on every DNS mutation; owner/admin succeed.</t>
   </si>
   <si>
-    <t>[CONFIRMED_CODE] Source trace; runtime negative test is TEST_NEEDED.</t>
+    <t>[CONFIRMED_CODE] Source trace; runtime negative test is TEST_NEEDED. | Batch 9: REPRODUCED locally (in-memory/temp DB, fake provider) by audits/proofs/repro-batch9-89e3b45.mts: a VIEWER member created a zone and an A record, HTTP 201 for both.</t>
   </si>
   <si>
     <t>NEW-370</t>
@@ -3036,7 +3036,7 @@
     <t>Test: POST with own email and status REVOKED returns 409; POST demoting the only OWNER returns 409; PATCH and POST behave identically.</t>
   </si>
   <si>
-    <t>[CONFIRMED_CODE] Source trace; needs OWNER with step-up to trigger.</t>
+    <t>[CONFIRMED_CODE] Source trace; needs OWNER with step-up to trigger. | Batch 9: REPRODUCED locally (in-memory/temp DB, fake provider) by audits/proofs/repro-batch9-89e3b45.mts: POST /admin/staff with the caller's own email and status REVOKED returned 201 and left 0 active OWNERs.</t>
   </si>
   <si>
     <t>NEW-377</t>
@@ -3348,6 +3348,9 @@
     <t>Test: a mocked 200 with {} leaves service_members unchanged and logs a reconcile error.</t>
   </si>
   <si>
+    <t>[CONFIRMED_CODE] Source trace. | Batch 9: REPRODUCED locally (in-memory/temp DB, fake provider) by audits/proofs/repro-batch9-89e3b45.mts: a /users body without a data array deleted the only shared member (membersRevoked=1).</t>
+  </si>
+  <si>
     <t>NEW-390</t>
   </si>
   <si>
@@ -3585,7 +3588,7 @@
     <t>Test: VIEWER gets 403; an account flagged by staff does not expose the staff reason in the export.</t>
   </si>
   <si>
-    <t>[CONFIRMED_CODE] Source trace. | Batch 8: GET /api/v1/audit (src/server.ts:2441) has the same exposure and also returns ip_address and the raw metadata of all members to every role.</t>
+    <t>[CONFIRMED_CODE] Source trace. | Batch 8: GET /api/v1/audit (src/server.ts:2441) has the same exposure and also returns ip_address and the raw metadata of all members to every role. | Batch 9: REPRODUCED locally (in-memory/temp DB, fake provider) by audits/proofs/repro-batch9-89e3b45.mts: a VIEWER's activity export contained the staff-written reason.</t>
   </si>
   <si>
     <t>NEW-400</t>
@@ -3705,7 +3708,7 @@
     <t>Test: a viewer-preset member cannot send a command through the websocket and the input is not rendered.</t>
   </si>
   <si>
-    <t>[CONFIRMED_CODE] Source trace; whether Wings accepts commands from a connection with only control.console TEST_NEEDED on the sandbox panel.</t>
+    <t>[CONFIRMED_CODE] Source trace; whether Wings accepts commands from a connection with only control.console TEST_NEEDED on the sandbox panel. | Batch 9: REPRODUCED locally (in-memory/temp DB, fake provider) by audits/proofs/repro-batch9-89e3b45.mts: the viewer preset contains control.console and file.read-content.</t>
   </si>
   <si>
     <t>NEW-405</t>
@@ -3753,6 +3756,9 @@
     <t>Test: the response matches the enforced TTLs; a BILLING role does not receive SMTP or panel details.</t>
   </si>
   <si>
+    <t>[CONFIRMED_CODE] Source trace. | Batch 9: team invitations use a 15 minute step-up window (src/server.ts:1033) while requireRecentStepUp and /auth/step-up use 10 minutes.</t>
+  </si>
+  <si>
     <t>NEW-407</t>
   </si>
   <si>
@@ -3795,7 +3801,7 @@
     <t>Test: VIEWER receives 403 for invoices and audit if that is the policy, and the UI hides the corresponding buttons.</t>
   </si>
   <si>
-    <t>[CONFIRMED_CODE] Source trace; whether VIEWER should read billing is a product decision.</t>
+    <t>[CONFIRMED_CODE] Source trace; whether VIEWER should read billing is a product decision. | Batch 9: REPRODUCED locally (in-memory/temp DB, fake provider) by audits/proofs/repro-batch9-89e3b45.mts: a VIEWER listed invoices, HTTP 200.</t>
   </si>
   <si>
     <t>NEW-409</t>
@@ -3819,7 +3825,109 @@
     <t>Test: after lock, console, files and panel actions are refused for owner and shared members; unlock restores them.</t>
   </si>
   <si>
-    <t>[CONFIRMED_CODE] Source trace; panel-side behaviour TEST_NEEDED.</t>
+    <t>[CONFIRMED_CODE] Source trace; panel-side behaviour TEST_NEEDED. | Batch 9: REPRODUCED locally (in-memory/temp DB, fake provider) by audits/proofs/repro-batch9-89e3b45.mts: after FLAGGED_FRAUD the service stayed ACTIVE and the shared member kept MEMBER access.</t>
+  </si>
+  <si>
+    <t>NEW-410</t>
+  </si>
+  <si>
+    <t>Minecraft Installers</t>
+  </si>
+  <si>
+    <t>Game profile edits are audited by slug only, and the download-host allowlist accepts any hostname or IP</t>
+  </si>
+  <si>
+    <t>89e3b45</t>
+  </si>
+  <si>
+    <t>src/server.ts:1710-1740; src/modules/provisioning/game-profiles.ts:44,75-80</t>
+  </si>
+  <si>
+    <t>admin.game_profile_updated writes only {slug}. A change to installSources.downloadHosts, dir, facets or configSchema is live for every customer immediately and cannot be reconstructed. HOST accepts any [a-z0-9.-]{3,253} string, including IP literals and internal names, and the installer only compares the URL hostname with that list.</t>
+  </si>
+  <si>
+    <t>A staff mistake or a compromised catalog:manage account (INFRASTRUCTURE and ADMINISTRATOR have it) can redirect where every customer's mod downloads come from, or point Fortless at an internal host, with no before/after record.</t>
+  </si>
+  <si>
+    <t>Store a versioned copy and a field-level diff in the audit event, require step-up for edits to install sources, and reject IP literals and non-public names in downloadHosts.</t>
+  </si>
+  <si>
+    <t>Test: updating downloadHosts writes an audit event with old and new values; host "127.0.0.1" is refused.</t>
+  </si>
+  <si>
+    <t>NEW-411</t>
+  </si>
+  <si>
+    <t>Mod install buffers up to 100 MB in memory per request with no concurrency limit</t>
+  </si>
+  <si>
+    <t>src/modules/provisioning/game-tools.ts:19,198-210; src/server.ts:1714</t>
+  </si>
+  <si>
+    <t>installMod collects every chunk into an array and Buffer.concat copies it again for hashing and upload, so one request can hold about 200 MB. Access needs only file.create (operator and admin presets); the global limit is 100 requests per minute per IP and nothing limits parallel installs per service or process.</t>
+  </si>
+  <si>
+    <t>A handful of parallel installs from one member, or a few members, can exhaust Node memory and take the web process down for all tenants.</t>
+  </si>
+  <si>
+    <t>Stream to a temporary file with the hash computed on the fly, cap concurrency globally and per service, and add a per-account install quota.</t>
+  </si>
+  <si>
+    <t>Test: 20 parallel installs keep RSS under a defined bound; excess returns 429.</t>
+  </si>
+  <si>
+    <t>[CONFIRMED_CODE] Source trace; memory impact is TEST_NEEDED on staging (plan item 10).</t>
+  </si>
+  <si>
+    <t>NEW-412</t>
+  </si>
+  <si>
+    <t>Staff suspend, unsuspend and terminate call the provider inline, treat timeouts as failure and record 127.0.0.1 as the client IP</t>
+  </si>
+  <si>
+    <t>src/modules/provisioning/services.ts:296-345,350-400,403-515; src/server.ts:2585-2631</t>
+  </si>
+  <si>
+    <t>suspendService and unsuspendService await the adapter before the database transaction (no outbox, no unknown-outcome handling), and the audit insert for suspend, unsuspend, terminate and terminate_failed uses the literal ip_address 127.0.0.1 instead of the request IP, although the routes know req.ip.</t>
+  </si>
+  <si>
+    <t>After a timeout the panel may be suspended while Fortless still shows ACTIVE (or the reverse) and a retry repeats the call; investigations cannot tie the staff action to the staff member's real address.</t>
+  </si>
+  <si>
+    <t>Move provider side effects to the outbox with a correlation tag, query the provider before retry, and pass the request IP into the service functions.</t>
+  </si>
+  <si>
+    <t>Test: a simulated timeout leaves the state PENDING and reconciles; the audit row carries the caller IP.</t>
+  </si>
+  <si>
+    <t>[CONFIRMED_CODE] Source trace; staging behaviour is plan item 12.</t>
+  </si>
+  <si>
+    <t>NEW-413</t>
+  </si>
+  <si>
+    <t>Wings &amp; WebSockets</t>
+  </si>
+  <si>
+    <t>Console access cannot be revoked from Fortless: an open websocket keeps working until the Wings token lapses</t>
+  </si>
+  <si>
+    <t>src/frontend/client/pages/services/console.ts:96-120; src/modules/provisioning/console.ts:132-148; src/modules/provisioning/adapter.ts:573-582</t>
+  </si>
+  <si>
+    <t>Fortless returns the panel's websocket token and URL; the browser connects directly to Wings. Suspension, member removal, account lock (NEW-409) or role changes are only checked when a new token is requested. The client refreshes the token on "token expiring" and merely shows "Session expired" when the refresh is refused; the socket URL is not pinned to a known node host.</t>
+  </si>
+  <si>
+    <t>A member who lost access, or a customer on a locked account, keeps issuing console commands until the existing token expires, and Fortless has no way to cut the connection.</t>
+  </si>
+  <si>
+    <t>Document and test the real revocation latency on Wings (token TTL and denylist), disconnect the socket on any refused refresh, and revoke Wings tokens when access changes.</t>
+  </si>
+  <si>
+    <t>Test: after the removal, no console frame is accepted within the agreed bound (plan item 1).</t>
+  </si>
+  <si>
+    <t>[CONFIRMED_CODE] Source trace; Wings behaviour is TEST_NEEDED.</t>
   </si>
   <si>
     <t>FORTLESS   /   SECURITY &amp; PRODUCT QUALITY</t>
@@ -3840,10 +3948,10 @@
     <t>CLOSED &amp; TESTED</t>
   </si>
   <si>
-    <t>154</t>
-  </si>
-  <si>
-    <t>65</t>
+    <t>158</t>
+  </si>
+  <si>
+    <t>68</t>
   </si>
   <si>
     <t>58</t>
@@ -3870,201 +3978,204 @@
     <t>39</t>
   </si>
   <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>73</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>46</t>
+  </si>
+  <si>
+    <t>TESTED</t>
+  </si>
+  <si>
+    <t>CLOSED</t>
+  </si>
+  <si>
+    <t>LATEST VERIFIED COMMIT</t>
+  </si>
+  <si>
+    <t>REGRESSION</t>
+  </si>
+  <si>
+    <t>3cb35de (independent audit batch 1)</t>
+  </si>
+  <si>
+    <t>STATUS CONTRACT</t>
+  </si>
+  <si>
+    <t>Issue present in inspected source</t>
+  </si>
+  <si>
+    <t>Some code fixed; unresolved conditions remain</t>
+  </si>
+  <si>
+    <t>Fix observed in source; still needs regression/runtime validation</t>
+  </si>
+  <si>
+    <t>Question or risk not independently demonstrated</t>
+  </si>
+  <si>
+    <t>Requires an explicit product/security policy</t>
+  </si>
+  <si>
+    <t>Automated/authorized tests executed and evidence stored</t>
+  </si>
+  <si>
+    <t>Fix independently verified and accepted</t>
+  </si>
+  <si>
+    <t>Previously fixed behavior has returned</t>
+  </si>
+  <si>
+    <t>FORTLESS   /   30 SECURITY AUDIT DOMAINS</t>
+  </si>
+  <si>
+    <t>Static source review and local reproductions at 89e3b45. Coverage is NOT a safety claim; see audits/COVERAGE_MATRIX_EXPLORATORY_AUDIT.md.</t>
+  </si>
+  <si>
+    <t>#</t>
+  </si>
+  <si>
+    <t>Scope</t>
+  </si>
+  <si>
+    <t>Related finding IDs</t>
+  </si>
+  <si>
+    <t>Audit coverage</t>
+  </si>
+  <si>
+    <t>01</t>
+  </si>
+  <si>
+    <t>Authentication</t>
+  </si>
+  <si>
+    <t>Login/register/reset, brute force, enumeration</t>
+  </si>
+  <si>
+    <t>SEC-09, FTL-SEC-205, NEW-362, NEW-363, NEW-364, NEW-365, NEW-366, NEW-367</t>
+  </si>
+  <si>
+    <t>STATIC_PARTIAL</t>
+  </si>
+  <si>
+    <t>02</t>
+  </si>
+  <si>
+    <t>Sessions &amp; Devices</t>
+  </si>
+  <si>
+    <t>Token rotation, expiry, login/logout, revocation</t>
+  </si>
+  <si>
+    <t>SEC-03, SEC-04, FTL-SEC-202, NEW-363, NEW-368, NEW-377</t>
+  </si>
+  <si>
+    <t>03</t>
+  </si>
+  <si>
+    <t>MFA &amp; Passkeys</t>
+  </si>
+  <si>
+    <t>TOTP, WebAuthn, recovery, replay, UV</t>
+  </si>
+  <si>
+    <t>FTL-SEC-201, FTL-SEC-202, FTL-SEC-203, NEW-306, NEW-307, NEW-318, NEW-358, NEW-360, NEW-366, NEW-367</t>
+  </si>
+  <si>
+    <t>04</t>
+  </si>
+  <si>
+    <t>Authorization / RBAC</t>
+  </si>
+  <si>
+    <t>Every API permission and role</t>
+  </si>
+  <si>
+    <t>FTL-UI-201, SSO-01, NEW-322, NEW-328, NEW-359, NEW-376, NEW-378, NEW-379, NEW-387, NEW-390, NEW-399, NEW-404, NEW-408, NEW-409, NEW-369, NEW-376, NEW-409</t>
+  </si>
+  <si>
+    <t>05</t>
+  </si>
+  <si>
+    <t>IDOR / BOLA</t>
+  </si>
+  <si>
+    <t>Cross-account resource access</t>
+  </si>
+  <si>
+    <t>SEC-05, NEW-310, NEW-322</t>
+  </si>
+  <si>
+    <t>06</t>
+  </si>
+  <si>
+    <t>Multi-tenancy</t>
+  </si>
+  <si>
+    <t>Organization/service separation</t>
+  </si>
+  <si>
+    <t>SEC-05, SEC-06, NEW-310, NEW-322</t>
+  </si>
+  <si>
+    <t>07</t>
+  </si>
+  <si>
+    <t>API Security</t>
+  </si>
+  <si>
+    <t>Request validation/mass assignment/rate limiting</t>
+  </si>
+  <si>
+    <t>FTL-SEC-205, NEW-311, NEW-321, NEW-328, NEW-407</t>
+  </si>
+  <si>
+    <t>08</t>
+  </si>
+  <si>
+    <t>CSRF &amp; CORS</t>
+  </si>
+  <si>
+    <t>Origin, cookies, CSRF all writes</t>
+  </si>
+  <si>
+    <t>SEC-09, NEW-394, NEW-395, NEW-405</t>
+  </si>
+  <si>
+    <t>RUNTIME_REQUIRED</t>
+  </si>
+  <si>
+    <t>09</t>
+  </si>
+  <si>
+    <t>XSS &amp; HTML Injection</t>
+  </si>
+  <si>
+    <t>Ticket/email/console/DOM output</t>
+  </si>
+  <si>
+    <t>UI-06, MAIL-01</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>SQL / Command Injection</t>
+  </si>
+  <si>
+    <t>SQL/shell/path/template injection</t>
+  </si>
+  <si>
     <t>11</t>
   </si>
   <si>
-    <t>73</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>42</t>
-  </si>
-  <si>
-    <t>TESTED</t>
-  </si>
-  <si>
-    <t>CLOSED</t>
-  </si>
-  <si>
-    <t>LATEST VERIFIED COMMIT</t>
-  </si>
-  <si>
-    <t>REGRESSION</t>
-  </si>
-  <si>
-    <t>3cb35de (independent audit batch 1)</t>
-  </si>
-  <si>
-    <t>STATUS CONTRACT</t>
-  </si>
-  <si>
-    <t>Issue present in inspected source</t>
-  </si>
-  <si>
-    <t>Some code fixed; unresolved conditions remain</t>
-  </si>
-  <si>
-    <t>Fix observed in source; still needs regression/runtime validation</t>
-  </si>
-  <si>
-    <t>Question or risk not independently demonstrated</t>
-  </si>
-  <si>
-    <t>Requires an explicit product/security policy</t>
-  </si>
-  <si>
-    <t>Automated/authorized tests executed and evidence stored</t>
-  </si>
-  <si>
-    <t>Fix independently verified and accepted</t>
-  </si>
-  <si>
-    <t>Previously fixed behavior has returned</t>
-  </si>
-  <si>
-    <t>FORTLESS   /   30 SECURITY AUDIT DOMAINS</t>
-  </si>
-  <si>
-    <t>Static source review expanded at 6203687. Coverage is NOT an independent runtime, load, security or pixel-diff test.</t>
-  </si>
-  <si>
-    <t>#</t>
-  </si>
-  <si>
-    <t>Scope</t>
-  </si>
-  <si>
-    <t>Related finding IDs</t>
-  </si>
-  <si>
-    <t>Audit coverage</t>
-  </si>
-  <si>
-    <t>01</t>
-  </si>
-  <si>
-    <t>Authentication</t>
-  </si>
-  <si>
-    <t>Login/register/reset, brute force, enumeration</t>
-  </si>
-  <si>
-    <t>SEC-09, FTL-SEC-205, NEW-362, NEW-363, NEW-364, NEW-365, NEW-366, NEW-367</t>
-  </si>
-  <si>
-    <t>STATIC_PARTIAL</t>
-  </si>
-  <si>
-    <t>02</t>
-  </si>
-  <si>
-    <t>Sessions &amp; Devices</t>
-  </si>
-  <si>
-    <t>Token rotation, expiry, login/logout, revocation</t>
-  </si>
-  <si>
-    <t>SEC-03, SEC-04, FTL-SEC-202, NEW-363, NEW-368, NEW-377</t>
-  </si>
-  <si>
-    <t>03</t>
-  </si>
-  <si>
-    <t>MFA &amp; Passkeys</t>
-  </si>
-  <si>
-    <t>TOTP, WebAuthn, recovery, replay, UV</t>
-  </si>
-  <si>
-    <t>FTL-SEC-201, FTL-SEC-202, FTL-SEC-203, NEW-306, NEW-307, NEW-318, NEW-358, NEW-360, NEW-366, NEW-367</t>
-  </si>
-  <si>
-    <t>04</t>
-  </si>
-  <si>
-    <t>Authorization / RBAC</t>
-  </si>
-  <si>
-    <t>Every API permission and role</t>
-  </si>
-  <si>
-    <t>FTL-UI-201, SSO-01, NEW-322, NEW-328, NEW-359, NEW-376, NEW-378, NEW-379, NEW-387, NEW-390, NEW-399, NEW-404, NEW-408, NEW-409</t>
-  </si>
-  <si>
-    <t>05</t>
-  </si>
-  <si>
-    <t>IDOR / BOLA</t>
-  </si>
-  <si>
-    <t>Cross-account resource access</t>
-  </si>
-  <si>
-    <t>SEC-05, NEW-310, NEW-322</t>
-  </si>
-  <si>
-    <t>06</t>
-  </si>
-  <si>
-    <t>Multi-tenancy</t>
-  </si>
-  <si>
-    <t>Organization/service separation</t>
-  </si>
-  <si>
-    <t>SEC-05, SEC-06, NEW-310, NEW-322</t>
-  </si>
-  <si>
-    <t>07</t>
-  </si>
-  <si>
-    <t>API Security</t>
-  </si>
-  <si>
-    <t>Request validation/mass assignment/rate limiting</t>
-  </si>
-  <si>
-    <t>FTL-SEC-205, NEW-311, NEW-321, NEW-328, NEW-407</t>
-  </si>
-  <si>
-    <t>08</t>
-  </si>
-  <si>
-    <t>CSRF &amp; CORS</t>
-  </si>
-  <si>
-    <t>Origin, cookies, CSRF all writes</t>
-  </si>
-  <si>
-    <t>SEC-09, NEW-394, NEW-395, NEW-405</t>
-  </si>
-  <si>
-    <t>RUNTIME_REQUIRED</t>
-  </si>
-  <si>
-    <t>09</t>
-  </si>
-  <si>
-    <t>XSS &amp; HTML Injection</t>
-  </si>
-  <si>
-    <t>Ticket/email/console/DOM output</t>
-  </si>
-  <si>
-    <t>UI-06, MAIL-01</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>SQL / Command Injection</t>
-  </si>
-  <si>
-    <t>SQL/shell/path/template injection</t>
-  </si>
-  <si>
     <t>SSRF</t>
   </si>
   <si>
@@ -4074,9 +4185,6 @@
     <t>SEC-08, NEW-314</t>
   </si>
   <si>
-    <t>12</t>
-  </si>
-  <si>
     <t>Provider keys, vault, rotation</t>
   </si>
   <si>
@@ -4104,12 +4212,12 @@
     <t>SSO-01, SSO-02, SSO-03, NEW-387, NEW-396, NEW-397</t>
   </si>
   <si>
-    <t>Wings &amp; WebSockets</t>
-  </si>
-  <si>
     <t>Socket tokens, console, revocation</t>
   </si>
   <si>
+    <t>FTL-UI-206, NEW-413, NEW-404</t>
+  </si>
+  <si>
     <t>16</t>
   </si>
   <si>
@@ -4125,12 +4233,12 @@
     <t>17</t>
   </si>
   <si>
-    <t>Minecraft Installers</t>
-  </si>
-  <si>
     <t>SHA512, compatibility, redirect, limits</t>
   </si>
   <si>
+    <t>NEW-314, NEW-410, NEW-411</t>
+  </si>
+  <si>
     <t>18</t>
   </si>
   <si>
@@ -4170,7 +4278,7 @@
     <t>Node, cap, retry, lifecycle</t>
   </si>
   <si>
-    <t>FTL-PROV-201, FTL-PROV-202, FTL-PROV-203, FTL-PROV-204, NEW-302, NEW-322, NEW-327, NEW-352, NEW-357, NEW-386, NEW-388, NEW-392</t>
+    <t>FTL-PROV-201, FTL-PROV-202, FTL-PROV-203, FTL-PROV-204, NEW-302, NEW-322, NEW-327, NEW-352, NEW-357, NEW-386, NEW-388, NEW-392, NEW-412</t>
   </si>
   <si>
     <t>22</t>
@@ -4227,7 +4335,7 @@
     <t>Job leases, ordering, retry, dead letters</t>
   </si>
   <si>
-    <t>FTL-PROV-203, FTL-BILL-202, NEW-339, NEW-346, NEW-354, NEW-357, NEW-401, NEW-402</t>
+    <t>FTL-PROV-203, FTL-BILL-202, NEW-339, NEW-346, NEW-354, NEW-357, NEW-401, NEW-402, NEW-389</t>
   </si>
   <si>
     <t>27</t>
@@ -4251,9 +4359,6 @@
     <t>npm SCA, CI secrets, pinning</t>
   </si>
   <si>
-    <t>NOT_STARTED</t>
-  </si>
-  <si>
     <t>29</t>
   </si>
   <si>
@@ -4522,6 +4627,15 @@
   </si>
   <si>
     <t>Customer and admin frontend pages, API client, search, settings and account-lock paths read in source. No implementation code changed.</t>
+  </si>
+  <si>
+    <t>2026-10-19 12:00</t>
+  </si>
+  <si>
+    <t>Independent audit batch 9: Wings, console, game tools, admin service actions, local reproductions (NEW-410..NEW-413)</t>
+  </si>
+  <si>
+    <t>Console client, game tools and profiles, suspend/terminate paths read in source; seven findings reproduced locally with a temp database and a fake provider. No implementation code changed.</t>
   </si>
   <si>
     <t>FORTLESS   /   IMMUTABLE STATUS HISTORY</t>
@@ -5786,7 +5900,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:S157"/>
+  <dimension ref="A1:S161"/>
   <sheetFormatPr defaultRowHeight="0" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" customHeight="1"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
@@ -13590,12 +13704,12 @@
         <v>36</v>
       </c>
       <c r="S137" t="s">
-        <v>765</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="138" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="B138" t="s">
         <v>308</v>
@@ -13607,7 +13721,7 @@
         <v>630</v>
       </c>
       <c r="E138" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="F138" t="s">
         <v>453</v>
@@ -13625,19 +13739,19 @@
         <v>1095</v>
       </c>
       <c r="K138" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="L138" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="M138" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="N138" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="O138" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="P138" t="s">
         <v>747</v>
@@ -13649,12 +13763,12 @@
         <v>36</v>
       </c>
       <c r="S138" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="139" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="B139" t="s">
         <v>308</v>
@@ -13666,7 +13780,7 @@
         <v>1030</v>
       </c>
       <c r="E139" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="F139" t="s">
         <v>112</v>
@@ -13684,19 +13798,19 @@
         <v>1095</v>
       </c>
       <c r="K139" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="L139" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="M139" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="N139" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="O139" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="P139" t="s">
         <v>747</v>
@@ -13713,7 +13827,7 @@
     </row>
     <row r="140" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="B140" t="s">
         <v>308</v>
@@ -13725,7 +13839,7 @@
         <v>214</v>
       </c>
       <c r="E140" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="F140" t="s">
         <v>95</v>
@@ -13743,19 +13857,19 @@
         <v>1095</v>
       </c>
       <c r="K140" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="L140" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="M140" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="N140" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="O140" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="P140" t="s">
         <v>747</v>
@@ -13767,12 +13881,12 @@
         <v>36</v>
       </c>
       <c r="S140" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="141" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>1132</v>
+        <v>1133</v>
       </c>
       <c r="B141" t="s">
         <v>308</v>
@@ -13784,7 +13898,7 @@
         <v>630</v>
       </c>
       <c r="E141" t="s">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="F141" t="s">
         <v>112</v>
@@ -13802,19 +13916,19 @@
         <v>1095</v>
       </c>
       <c r="K141" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
       <c r="L141" t="s">
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="M141" t="s">
-        <v>1136</v>
+        <v>1137</v>
       </c>
       <c r="N141" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="O141" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="P141" t="s">
         <v>747</v>
@@ -13831,7 +13945,7 @@
     </row>
     <row r="142" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="B142" t="s">
         <v>308</v>
@@ -13843,7 +13957,7 @@
         <v>24</v>
       </c>
       <c r="E142" t="s">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="F142" t="s">
         <v>112</v>
@@ -13855,25 +13969,25 @@
         <v>27</v>
       </c>
       <c r="I142" t="s">
-        <v>1141</v>
+        <v>1142</v>
       </c>
       <c r="J142" t="s">
-        <v>1141</v>
+        <v>1142</v>
       </c>
       <c r="K142" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="L142" t="s">
-        <v>1143</v>
+        <v>1144</v>
       </c>
       <c r="M142" t="s">
-        <v>1144</v>
+        <v>1145</v>
       </c>
       <c r="N142" t="s">
-        <v>1145</v>
+        <v>1146</v>
       </c>
       <c r="O142" t="s">
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="P142" t="s">
         <v>747</v>
@@ -13885,12 +13999,12 @@
         <v>36</v>
       </c>
       <c r="S142" t="s">
-        <v>1147</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="143" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="B143" t="s">
         <v>308</v>
@@ -13902,7 +14016,7 @@
         <v>24</v>
       </c>
       <c r="E143" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="F143" t="s">
         <v>112</v>
@@ -13914,25 +14028,25 @@
         <v>27</v>
       </c>
       <c r="I143" t="s">
-        <v>1141</v>
+        <v>1142</v>
       </c>
       <c r="J143" t="s">
-        <v>1141</v>
+        <v>1142</v>
       </c>
       <c r="K143" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="L143" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="M143" t="s">
-        <v>1152</v>
+        <v>1153</v>
       </c>
       <c r="N143" t="s">
-        <v>1153</v>
+        <v>1154</v>
       </c>
       <c r="O143" t="s">
-        <v>1154</v>
+        <v>1155</v>
       </c>
       <c r="P143" t="s">
         <v>747</v>
@@ -13944,12 +14058,12 @@
         <v>36</v>
       </c>
       <c r="S143" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="144" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="B144" t="s">
         <v>61</v>
@@ -13961,7 +14075,7 @@
         <v>435</v>
       </c>
       <c r="E144" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="F144" t="s">
         <v>112</v>
@@ -13973,25 +14087,25 @@
         <v>27</v>
       </c>
       <c r="I144" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="J144" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="K144" t="s">
-        <v>1159</v>
+        <v>1160</v>
       </c>
       <c r="L144" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="M144" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="N144" t="s">
-        <v>1162</v>
+        <v>1163</v>
       </c>
       <c r="O144" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="P144" t="s">
         <v>747</v>
@@ -14003,12 +14117,12 @@
         <v>36</v>
       </c>
       <c r="S144" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="145" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="B145" t="s">
         <v>308</v>
@@ -14020,7 +14134,7 @@
         <v>435</v>
       </c>
       <c r="E145" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="F145" t="s">
         <v>95</v>
@@ -14032,25 +14146,25 @@
         <v>27</v>
       </c>
       <c r="I145" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="J145" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="K145" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="L145" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="M145" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="N145" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="O145" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="P145" t="s">
         <v>747</v>
@@ -14062,12 +14176,12 @@
         <v>36</v>
       </c>
       <c r="S145" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="146" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="B146" t="s">
         <v>308</v>
@@ -14076,10 +14190,10 @@
         <v>62</v>
       </c>
       <c r="D146" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="E146" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="F146" t="s">
         <v>112</v>
@@ -14091,25 +14205,25 @@
         <v>27</v>
       </c>
       <c r="I146" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="J146" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="K146" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="L146" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="M146" t="s">
-        <v>1178</v>
+        <v>1179</v>
       </c>
       <c r="N146" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="O146" t="s">
-        <v>1180</v>
+        <v>1181</v>
       </c>
       <c r="P146" t="s">
         <v>747</v>
@@ -14126,7 +14240,7 @@
     </row>
     <row r="147" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>1181</v>
+        <v>1182</v>
       </c>
       <c r="B147" t="s">
         <v>308</v>
@@ -14138,7 +14252,7 @@
         <v>630</v>
       </c>
       <c r="E147" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="F147" t="s">
         <v>112</v>
@@ -14150,25 +14264,25 @@
         <v>27</v>
       </c>
       <c r="I147" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="J147" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="K147" t="s">
-        <v>1183</v>
+        <v>1184</v>
       </c>
       <c r="L147" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="M147" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="N147" t="s">
-        <v>1186</v>
+        <v>1187</v>
       </c>
       <c r="O147" t="s">
-        <v>1187</v>
+        <v>1188</v>
       </c>
       <c r="P147" t="s">
         <v>747</v>
@@ -14180,12 +14294,12 @@
         <v>36</v>
       </c>
       <c r="S147" t="s">
-        <v>1188</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="148" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="B148" t="s">
         <v>308</v>
@@ -14197,7 +14311,7 @@
         <v>24</v>
       </c>
       <c r="E148" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
       <c r="F148" t="s">
         <v>112</v>
@@ -14209,25 +14323,25 @@
         <v>27</v>
       </c>
       <c r="I148" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="J148" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="K148" t="s">
-        <v>1191</v>
+        <v>1192</v>
       </c>
       <c r="L148" t="s">
-        <v>1192</v>
+        <v>1193</v>
       </c>
       <c r="M148" t="s">
-        <v>1193</v>
+        <v>1194</v>
       </c>
       <c r="N148" t="s">
-        <v>1194</v>
+        <v>1195</v>
       </c>
       <c r="O148" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="P148" t="s">
         <v>747</v>
@@ -14244,7 +14358,7 @@
     </row>
     <row r="149" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>1196</v>
+        <v>1197</v>
       </c>
       <c r="B149" t="s">
         <v>308</v>
@@ -14256,7 +14370,7 @@
         <v>1054</v>
       </c>
       <c r="E149" t="s">
-        <v>1197</v>
+        <v>1198</v>
       </c>
       <c r="F149" t="s">
         <v>112</v>
@@ -14268,25 +14382,25 @@
         <v>27</v>
       </c>
       <c r="I149" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="J149" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="K149" t="s">
-        <v>1198</v>
+        <v>1199</v>
       </c>
       <c r="L149" t="s">
-        <v>1199</v>
+        <v>1200</v>
       </c>
       <c r="M149" t="s">
-        <v>1200</v>
+        <v>1201</v>
       </c>
       <c r="N149" t="s">
-        <v>1201</v>
+        <v>1202</v>
       </c>
       <c r="O149" t="s">
-        <v>1202</v>
+        <v>1203</v>
       </c>
       <c r="P149" t="s">
         <v>747</v>
@@ -14298,12 +14412,12 @@
         <v>36</v>
       </c>
       <c r="S149" t="s">
-        <v>1203</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="150" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>1204</v>
+        <v>1205</v>
       </c>
       <c r="B150" t="s">
         <v>308</v>
@@ -14315,7 +14429,7 @@
         <v>959</v>
       </c>
       <c r="E150" t="s">
-        <v>1205</v>
+        <v>1206</v>
       </c>
       <c r="F150" t="s">
         <v>95</v>
@@ -14327,25 +14441,25 @@
         <v>27</v>
       </c>
       <c r="I150" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="J150" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="K150" t="s">
-        <v>1206</v>
+        <v>1207</v>
       </c>
       <c r="L150" t="s">
-        <v>1207</v>
+        <v>1208</v>
       </c>
       <c r="M150" t="s">
-        <v>1208</v>
+        <v>1209</v>
       </c>
       <c r="N150" t="s">
-        <v>1209</v>
+        <v>1210</v>
       </c>
       <c r="O150" t="s">
-        <v>1210</v>
+        <v>1211</v>
       </c>
       <c r="P150" t="s">
         <v>747</v>
@@ -14357,12 +14471,12 @@
         <v>36</v>
       </c>
       <c r="S150" t="s">
-        <v>1211</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="151" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>1212</v>
+        <v>1213</v>
       </c>
       <c r="B151" t="s">
         <v>61</v>
@@ -14374,7 +14488,7 @@
         <v>569</v>
       </c>
       <c r="E151" t="s">
-        <v>1213</v>
+        <v>1214</v>
       </c>
       <c r="F151" t="s">
         <v>112</v>
@@ -14386,25 +14500,25 @@
         <v>27</v>
       </c>
       <c r="I151" t="s">
-        <v>1214</v>
+        <v>1215</v>
       </c>
       <c r="J151" t="s">
-        <v>1214</v>
+        <v>1215</v>
       </c>
       <c r="K151" t="s">
-        <v>1215</v>
+        <v>1216</v>
       </c>
       <c r="L151" t="s">
-        <v>1216</v>
+        <v>1217</v>
       </c>
       <c r="M151" t="s">
-        <v>1217</v>
+        <v>1218</v>
       </c>
       <c r="N151" t="s">
-        <v>1218</v>
+        <v>1219</v>
       </c>
       <c r="O151" t="s">
-        <v>1219</v>
+        <v>1220</v>
       </c>
       <c r="P151" t="s">
         <v>747</v>
@@ -14416,12 +14530,12 @@
         <v>36</v>
       </c>
       <c r="S151" t="s">
-        <v>1220</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="152" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>1221</v>
+        <v>1222</v>
       </c>
       <c r="B152" t="s">
         <v>61</v>
@@ -14433,7 +14547,7 @@
         <v>630</v>
       </c>
       <c r="E152" t="s">
-        <v>1222</v>
+        <v>1223</v>
       </c>
       <c r="F152" t="s">
         <v>112</v>
@@ -14445,25 +14559,25 @@
         <v>27</v>
       </c>
       <c r="I152" t="s">
-        <v>1214</v>
+        <v>1215</v>
       </c>
       <c r="J152" t="s">
-        <v>1214</v>
+        <v>1215</v>
       </c>
       <c r="K152" t="s">
-        <v>1223</v>
+        <v>1224</v>
       </c>
       <c r="L152" t="s">
-        <v>1224</v>
+        <v>1225</v>
       </c>
       <c r="M152" t="s">
-        <v>1225</v>
+        <v>1226</v>
       </c>
       <c r="N152" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
       <c r="O152" t="s">
-        <v>1227</v>
+        <v>1228</v>
       </c>
       <c r="P152" t="s">
         <v>747</v>
@@ -14475,12 +14589,12 @@
         <v>36</v>
       </c>
       <c r="S152" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="153" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="B153" t="s">
         <v>308</v>
@@ -14492,7 +14606,7 @@
         <v>959</v>
       </c>
       <c r="E153" t="s">
-        <v>1230</v>
+        <v>1231</v>
       </c>
       <c r="F153" t="s">
         <v>112</v>
@@ -14504,25 +14618,25 @@
         <v>27</v>
       </c>
       <c r="I153" t="s">
-        <v>1214</v>
+        <v>1215</v>
       </c>
       <c r="J153" t="s">
-        <v>1214</v>
+        <v>1215</v>
       </c>
       <c r="K153" t="s">
-        <v>1231</v>
+        <v>1232</v>
       </c>
       <c r="L153" t="s">
-        <v>1232</v>
+        <v>1233</v>
       </c>
       <c r="M153" t="s">
-        <v>1233</v>
+        <v>1234</v>
       </c>
       <c r="N153" t="s">
-        <v>1234</v>
+        <v>1235</v>
       </c>
       <c r="O153" t="s">
-        <v>1235</v>
+        <v>1236</v>
       </c>
       <c r="P153" t="s">
         <v>747</v>
@@ -14534,12 +14648,12 @@
         <v>36</v>
       </c>
       <c r="S153" t="s">
-        <v>1236</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="154" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>1237</v>
+        <v>1238</v>
       </c>
       <c r="B154" t="s">
         <v>308</v>
@@ -14551,7 +14665,7 @@
         <v>1077</v>
       </c>
       <c r="E154" t="s">
-        <v>1238</v>
+        <v>1239</v>
       </c>
       <c r="F154" t="s">
         <v>112</v>
@@ -14563,25 +14677,25 @@
         <v>27</v>
       </c>
       <c r="I154" t="s">
-        <v>1214</v>
+        <v>1215</v>
       </c>
       <c r="J154" t="s">
-        <v>1214</v>
+        <v>1215</v>
       </c>
       <c r="K154" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
       <c r="L154" t="s">
-        <v>1240</v>
+        <v>1241</v>
       </c>
       <c r="M154" t="s">
-        <v>1241</v>
+        <v>1242</v>
       </c>
       <c r="N154" t="s">
-        <v>1242</v>
+        <v>1243</v>
       </c>
       <c r="O154" t="s">
-        <v>1243</v>
+        <v>1244</v>
       </c>
       <c r="P154" t="s">
         <v>747</v>
@@ -14593,12 +14707,12 @@
         <v>36</v>
       </c>
       <c r="S154" t="s">
-        <v>765</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="155" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
       <c r="B155" t="s">
         <v>308</v>
@@ -14610,7 +14724,7 @@
         <v>1054</v>
       </c>
       <c r="E155" t="s">
-        <v>1245</v>
+        <v>1247</v>
       </c>
       <c r="F155" t="s">
         <v>112</v>
@@ -14622,25 +14736,25 @@
         <v>27</v>
       </c>
       <c r="I155" t="s">
-        <v>1214</v>
+        <v>1215</v>
       </c>
       <c r="J155" t="s">
-        <v>1214</v>
+        <v>1215</v>
       </c>
       <c r="K155" t="s">
-        <v>1246</v>
+        <v>1248</v>
       </c>
       <c r="L155" t="s">
-        <v>1247</v>
+        <v>1249</v>
       </c>
       <c r="M155" t="s">
-        <v>1248</v>
+        <v>1250</v>
       </c>
       <c r="N155" t="s">
-        <v>1249</v>
+        <v>1251</v>
       </c>
       <c r="O155" t="s">
-        <v>1250</v>
+        <v>1252</v>
       </c>
       <c r="P155" t="s">
         <v>747</v>
@@ -14657,7 +14771,7 @@
     </row>
     <row r="156" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>1251</v>
+        <v>1253</v>
       </c>
       <c r="B156" t="s">
         <v>308</v>
@@ -14669,7 +14783,7 @@
         <v>630</v>
       </c>
       <c r="E156" t="s">
-        <v>1252</v>
+        <v>1254</v>
       </c>
       <c r="F156" t="s">
         <v>453</v>
@@ -14681,25 +14795,25 @@
         <v>27</v>
       </c>
       <c r="I156" t="s">
-        <v>1214</v>
+        <v>1215</v>
       </c>
       <c r="J156" t="s">
-        <v>1214</v>
+        <v>1215</v>
       </c>
       <c r="K156" t="s">
-        <v>1253</v>
+        <v>1255</v>
       </c>
       <c r="L156" t="s">
-        <v>1254</v>
+        <v>1256</v>
       </c>
       <c r="M156" t="s">
-        <v>1255</v>
+        <v>1257</v>
       </c>
       <c r="N156" t="s">
-        <v>1256</v>
+        <v>1258</v>
       </c>
       <c r="O156" t="s">
-        <v>1257</v>
+        <v>1259</v>
       </c>
       <c r="P156" t="s">
         <v>747</v>
@@ -14711,12 +14825,12 @@
         <v>36</v>
       </c>
       <c r="S156" t="s">
-        <v>1258</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="157" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>1259</v>
+        <v>1261</v>
       </c>
       <c r="B157" t="s">
         <v>61</v>
@@ -14728,7 +14842,7 @@
         <v>630</v>
       </c>
       <c r="E157" t="s">
-        <v>1260</v>
+        <v>1262</v>
       </c>
       <c r="F157" t="s">
         <v>112</v>
@@ -14740,25 +14854,25 @@
         <v>27</v>
       </c>
       <c r="I157" t="s">
-        <v>1214</v>
+        <v>1215</v>
       </c>
       <c r="J157" t="s">
-        <v>1214</v>
+        <v>1215</v>
       </c>
       <c r="K157" t="s">
-        <v>1261</v>
+        <v>1263</v>
       </c>
       <c r="L157" t="s">
-        <v>1262</v>
+        <v>1264</v>
       </c>
       <c r="M157" t="s">
-        <v>1263</v>
+        <v>1265</v>
       </c>
       <c r="N157" t="s">
-        <v>1264</v>
+        <v>1266</v>
       </c>
       <c r="O157" t="s">
-        <v>1265</v>
+        <v>1267</v>
       </c>
       <c r="P157" t="s">
         <v>747</v>
@@ -14770,7 +14884,243 @@
         <v>36</v>
       </c>
       <c r="S157" t="s">
-        <v>1266</v>
+        <v>1268</v>
+      </c>
+    </row>
+    <row r="158" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A158" t="s">
+        <v>1269</v>
+      </c>
+      <c r="B158" t="s">
+        <v>308</v>
+      </c>
+      <c r="C158" t="s">
+        <v>309</v>
+      </c>
+      <c r="D158" t="s">
+        <v>1270</v>
+      </c>
+      <c r="E158" t="s">
+        <v>1271</v>
+      </c>
+      <c r="F158" t="s">
+        <v>112</v>
+      </c>
+      <c r="G158" t="s">
+        <v>27</v>
+      </c>
+      <c r="H158" t="s">
+        <v>27</v>
+      </c>
+      <c r="I158" t="s">
+        <v>1272</v>
+      </c>
+      <c r="J158" t="s">
+        <v>1272</v>
+      </c>
+      <c r="K158" t="s">
+        <v>1273</v>
+      </c>
+      <c r="L158" t="s">
+        <v>1274</v>
+      </c>
+      <c r="M158" t="s">
+        <v>1275</v>
+      </c>
+      <c r="N158" t="s">
+        <v>1276</v>
+      </c>
+      <c r="O158" t="s">
+        <v>1277</v>
+      </c>
+      <c r="P158" t="s">
+        <v>747</v>
+      </c>
+      <c r="Q158" t="s">
+        <v>924</v>
+      </c>
+      <c r="R158" t="s">
+        <v>36</v>
+      </c>
+      <c r="S158" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="159" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A159" t="s">
+        <v>1278</v>
+      </c>
+      <c r="B159" t="s">
+        <v>308</v>
+      </c>
+      <c r="C159" t="s">
+        <v>62</v>
+      </c>
+      <c r="D159" t="s">
+        <v>1270</v>
+      </c>
+      <c r="E159" t="s">
+        <v>1279</v>
+      </c>
+      <c r="F159" t="s">
+        <v>112</v>
+      </c>
+      <c r="G159" t="s">
+        <v>27</v>
+      </c>
+      <c r="H159" t="s">
+        <v>27</v>
+      </c>
+      <c r="I159" t="s">
+        <v>1272</v>
+      </c>
+      <c r="J159" t="s">
+        <v>1272</v>
+      </c>
+      <c r="K159" t="s">
+        <v>1280</v>
+      </c>
+      <c r="L159" t="s">
+        <v>1281</v>
+      </c>
+      <c r="M159" t="s">
+        <v>1282</v>
+      </c>
+      <c r="N159" t="s">
+        <v>1283</v>
+      </c>
+      <c r="O159" t="s">
+        <v>1284</v>
+      </c>
+      <c r="P159" t="s">
+        <v>747</v>
+      </c>
+      <c r="Q159" t="s">
+        <v>924</v>
+      </c>
+      <c r="R159" t="s">
+        <v>36</v>
+      </c>
+      <c r="S159" t="s">
+        <v>1285</v>
+      </c>
+    </row>
+    <row r="160" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A160" t="s">
+        <v>1286</v>
+      </c>
+      <c r="B160" t="s">
+        <v>308</v>
+      </c>
+      <c r="C160" t="s">
+        <v>62</v>
+      </c>
+      <c r="D160" t="s">
+        <v>214</v>
+      </c>
+      <c r="E160" t="s">
+        <v>1287</v>
+      </c>
+      <c r="F160" t="s">
+        <v>112</v>
+      </c>
+      <c r="G160" t="s">
+        <v>27</v>
+      </c>
+      <c r="H160" t="s">
+        <v>27</v>
+      </c>
+      <c r="I160" t="s">
+        <v>1272</v>
+      </c>
+      <c r="J160" t="s">
+        <v>1272</v>
+      </c>
+      <c r="K160" t="s">
+        <v>1288</v>
+      </c>
+      <c r="L160" t="s">
+        <v>1289</v>
+      </c>
+      <c r="M160" t="s">
+        <v>1290</v>
+      </c>
+      <c r="N160" t="s">
+        <v>1291</v>
+      </c>
+      <c r="O160" t="s">
+        <v>1292</v>
+      </c>
+      <c r="P160" t="s">
+        <v>747</v>
+      </c>
+      <c r="Q160" t="s">
+        <v>924</v>
+      </c>
+      <c r="R160" t="s">
+        <v>36</v>
+      </c>
+      <c r="S160" t="s">
+        <v>1293</v>
+      </c>
+    </row>
+    <row r="161" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A161" t="s">
+        <v>1294</v>
+      </c>
+      <c r="B161" t="s">
+        <v>308</v>
+      </c>
+      <c r="C161" t="s">
+        <v>62</v>
+      </c>
+      <c r="D161" t="s">
+        <v>1295</v>
+      </c>
+      <c r="E161" t="s">
+        <v>1296</v>
+      </c>
+      <c r="F161" t="s">
+        <v>95</v>
+      </c>
+      <c r="G161" t="s">
+        <v>27</v>
+      </c>
+      <c r="H161" t="s">
+        <v>27</v>
+      </c>
+      <c r="I161" t="s">
+        <v>1272</v>
+      </c>
+      <c r="J161" t="s">
+        <v>1272</v>
+      </c>
+      <c r="K161" t="s">
+        <v>1297</v>
+      </c>
+      <c r="L161" t="s">
+        <v>1298</v>
+      </c>
+      <c r="M161" t="s">
+        <v>1299</v>
+      </c>
+      <c r="N161" t="s">
+        <v>1300</v>
+      </c>
+      <c r="O161" t="s">
+        <v>1301</v>
+      </c>
+      <c r="P161" t="s">
+        <v>747</v>
+      </c>
+      <c r="Q161" t="s">
+        <v>924</v>
+      </c>
+      <c r="R161" t="s">
+        <v>36</v>
+      </c>
+      <c r="S161" t="s">
+        <v>1302</v>
       </c>
     </row>
   </sheetData>
@@ -14784,48 +15134,48 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>1267</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1268</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1269</v>
+        <v>1305</v>
       </c>
       <c r="C4" t="s">
-        <v>1270</v>
+        <v>1306</v>
       </c>
       <c r="E4" t="s">
-        <v>1271</v>
+        <v>1307</v>
       </c>
       <c r="G4" t="s">
-        <v>1272</v>
+        <v>1308</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1273</v>
+        <v>1309</v>
       </c>
       <c r="C5" t="s">
-        <v>1274</v>
+        <v>1310</v>
       </c>
       <c r="E5" t="s">
-        <v>1275</v>
+        <v>1311</v>
       </c>
       <c r="G5" t="s">
-        <v>1276</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>1277</v>
+        <v>1313</v>
       </c>
       <c r="F9" t="s">
-        <v>1278</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -14833,16 +15183,16 @@
         <v>112</v>
       </c>
       <c r="B10" t="s">
-        <v>1274</v>
+        <v>1310</v>
       </c>
       <c r="C10" t="s">
         <v>3</v>
       </c>
       <c r="D10" t="s">
-        <v>1279</v>
+        <v>1315</v>
       </c>
       <c r="F10" t="s">
-        <v>1280</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -14850,13 +15200,13 @@
         <v>86</v>
       </c>
       <c r="B11" t="s">
-        <v>1281</v>
+        <v>1317</v>
       </c>
       <c r="C11" t="s">
         <v>22</v>
       </c>
       <c r="D11" t="s">
-        <v>1282</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -14864,13 +15214,13 @@
         <v>95</v>
       </c>
       <c r="B12" t="s">
-        <v>1283</v>
+        <v>1319</v>
       </c>
       <c r="C12" t="s">
         <v>61</v>
       </c>
       <c r="D12" t="s">
-        <v>1284</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -14878,13 +15228,13 @@
         <v>453</v>
       </c>
       <c r="B13" t="s">
-        <v>1285</v>
+        <v>1321</v>
       </c>
       <c r="C13" t="s">
         <v>308</v>
       </c>
       <c r="D13" t="s">
-        <v>1286</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
@@ -14892,42 +15242,42 @@
         <v>26</v>
       </c>
       <c r="B14" t="s">
-        <v>1275</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>1287</v>
+        <v>1323</v>
       </c>
       <c r="B15" t="s">
-        <v>1276</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>1288</v>
+        <v>1324</v>
       </c>
       <c r="B16" t="s">
-        <v>1276</v>
+        <v>1312</v>
       </c>
       <c r="F16" t="s">
-        <v>1289</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>1290</v>
+        <v>1326</v>
       </c>
       <c r="B17" t="s">
-        <v>1276</v>
+        <v>1312</v>
       </c>
       <c r="F17" t="s">
-        <v>1291</v>
+        <v>1327</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>1292</v>
+        <v>1328</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
@@ -14935,7 +15285,7 @@
         <v>112</v>
       </c>
       <c r="C22" t="s">
-        <v>1293</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
@@ -14943,7 +15293,7 @@
         <v>86</v>
       </c>
       <c r="C23" t="s">
-        <v>1294</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
@@ -14951,7 +15301,7 @@
         <v>26</v>
       </c>
       <c r="C24" t="s">
-        <v>1295</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
@@ -14959,7 +15309,7 @@
         <v>95</v>
       </c>
       <c r="C25" t="s">
-        <v>1296</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
@@ -14967,31 +15317,31 @@
         <v>453</v>
       </c>
       <c r="C26" t="s">
-        <v>1297</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>1287</v>
+        <v>1323</v>
       </c>
       <c r="C27" t="s">
-        <v>1298</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>1288</v>
+        <v>1324</v>
       </c>
       <c r="C28" t="s">
-        <v>1299</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>1290</v>
+        <v>1326</v>
       </c>
       <c r="C29" t="s">
-        <v>1300</v>
+        <v>1336</v>
       </c>
     </row>
   </sheetData>
@@ -15005,7 +15355,7 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>1301</v>
+        <v>1337</v>
       </c>
       <c r="B1"/>
       <c r="C1"/>
@@ -15014,7 +15364,7 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1302</v>
+        <v>1338</v>
       </c>
       <c r="B2"/>
       <c r="C2"/>
@@ -15023,529 +15373,529 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>1303</v>
+        <v>1339</v>
       </c>
       <c r="B3" t="s">
         <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>1304</v>
+        <v>1340</v>
       </c>
       <c r="D3" t="s">
-        <v>1305</v>
+        <v>1341</v>
       </c>
       <c r="E3" t="s">
-        <v>1306</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1307</v>
+        <v>1343</v>
       </c>
       <c r="B4" t="s">
-        <v>1308</v>
+        <v>1344</v>
       </c>
       <c r="C4" t="s">
-        <v>1309</v>
+        <v>1345</v>
       </c>
       <c r="D4" t="s">
-        <v>1310</v>
+        <v>1346</v>
       </c>
       <c r="E4" t="s">
-        <v>1311</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1312</v>
+        <v>1348</v>
       </c>
       <c r="B5" t="s">
-        <v>1313</v>
+        <v>1349</v>
       </c>
       <c r="C5" t="s">
-        <v>1314</v>
+        <v>1350</v>
       </c>
       <c r="D5" t="s">
-        <v>1315</v>
+        <v>1351</v>
       </c>
       <c r="E5" t="s">
-        <v>1311</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>1316</v>
+        <v>1352</v>
       </c>
       <c r="B6" t="s">
-        <v>1317</v>
+        <v>1353</v>
       </c>
       <c r="C6" t="s">
-        <v>1318</v>
+        <v>1354</v>
       </c>
       <c r="D6" t="s">
-        <v>1319</v>
+        <v>1355</v>
       </c>
       <c r="E6" t="s">
-        <v>1311</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>1320</v>
+        <v>1356</v>
       </c>
       <c r="B7" t="s">
-        <v>1321</v>
+        <v>1357</v>
       </c>
       <c r="C7" t="s">
-        <v>1322</v>
+        <v>1358</v>
       </c>
       <c r="D7" t="s">
-        <v>1323</v>
+        <v>1359</v>
       </c>
       <c r="E7" t="s">
-        <v>1311</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>1324</v>
+        <v>1360</v>
       </c>
       <c r="B8" t="s">
-        <v>1325</v>
+        <v>1361</v>
       </c>
       <c r="C8" t="s">
-        <v>1326</v>
+        <v>1362</v>
       </c>
       <c r="D8" t="s">
-        <v>1327</v>
+        <v>1363</v>
       </c>
       <c r="E8" t="s">
-        <v>1311</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>1328</v>
+        <v>1364</v>
       </c>
       <c r="B9" t="s">
-        <v>1329</v>
+        <v>1365</v>
       </c>
       <c r="C9" t="s">
-        <v>1330</v>
+        <v>1366</v>
       </c>
       <c r="D9" t="s">
-        <v>1331</v>
+        <v>1367</v>
       </c>
       <c r="E9" t="s">
-        <v>1311</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>1332</v>
+        <v>1368</v>
       </c>
       <c r="B10" t="s">
-        <v>1333</v>
+        <v>1369</v>
       </c>
       <c r="C10" t="s">
-        <v>1334</v>
+        <v>1370</v>
       </c>
       <c r="D10" t="s">
-        <v>1335</v>
+        <v>1371</v>
       </c>
       <c r="E10" t="s">
-        <v>1311</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>1336</v>
+        <v>1372</v>
       </c>
       <c r="B11" t="s">
-        <v>1337</v>
+        <v>1373</v>
       </c>
       <c r="C11" t="s">
-        <v>1338</v>
+        <v>1374</v>
       </c>
       <c r="D11" t="s">
-        <v>1339</v>
+        <v>1375</v>
       </c>
       <c r="E11" t="s">
-        <v>1340</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>1341</v>
+        <v>1377</v>
       </c>
       <c r="B12" t="s">
-        <v>1342</v>
+        <v>1378</v>
       </c>
       <c r="C12" t="s">
-        <v>1343</v>
+        <v>1379</v>
       </c>
       <c r="D12" t="s">
-        <v>1344</v>
+        <v>1380</v>
       </c>
       <c r="E12" t="s">
-        <v>1311</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>1345</v>
+        <v>1381</v>
       </c>
       <c r="B13" t="s">
-        <v>1346</v>
+        <v>1382</v>
       </c>
       <c r="C13" t="s">
-        <v>1347</v>
+        <v>1383</v>
       </c>
       <c r="D13" t="s">
         <v>403</v>
       </c>
       <c r="E13" t="s">
-        <v>1340</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>1283</v>
+        <v>1384</v>
       </c>
       <c r="B14" t="s">
-        <v>1348</v>
+        <v>1385</v>
       </c>
       <c r="C14" t="s">
-        <v>1349</v>
+        <v>1386</v>
       </c>
       <c r="D14" t="s">
-        <v>1350</v>
+        <v>1387</v>
       </c>
       <c r="E14" t="s">
-        <v>1311</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>1351</v>
+        <v>1319</v>
       </c>
       <c r="B15" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="C15" t="s">
-        <v>1352</v>
+        <v>1388</v>
       </c>
       <c r="D15" t="s">
-        <v>1353</v>
+        <v>1389</v>
       </c>
       <c r="E15" t="s">
-        <v>1311</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>1354</v>
+        <v>1390</v>
       </c>
       <c r="B16" t="s">
-        <v>1355</v>
+        <v>1391</v>
       </c>
       <c r="C16" t="s">
-        <v>1356</v>
+        <v>1392</v>
       </c>
       <c r="D16" t="s">
-        <v>1357</v>
+        <v>1393</v>
       </c>
       <c r="E16" t="s">
-        <v>1311</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>1358</v>
+        <v>1394</v>
       </c>
       <c r="B17" t="s">
         <v>435</v>
       </c>
       <c r="C17" t="s">
-        <v>1359</v>
+        <v>1395</v>
       </c>
       <c r="D17" t="s">
-        <v>1360</v>
+        <v>1396</v>
       </c>
       <c r="E17" t="s">
-        <v>1340</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>1281</v>
+        <v>1317</v>
       </c>
       <c r="B18" t="s">
-        <v>1361</v>
+        <v>1295</v>
       </c>
       <c r="C18" t="s">
-        <v>1362</v>
+        <v>1397</v>
       </c>
       <c r="D18" t="s">
-        <v>316</v>
+        <v>1398</v>
       </c>
       <c r="E18" t="s">
-        <v>1340</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>1363</v>
+        <v>1399</v>
       </c>
       <c r="B19" t="s">
-        <v>1364</v>
+        <v>1400</v>
       </c>
       <c r="C19" t="s">
-        <v>1365</v>
+        <v>1401</v>
       </c>
       <c r="D19" t="s">
-        <v>1366</v>
+        <v>1402</v>
       </c>
       <c r="E19" t="s">
-        <v>1340</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>1367</v>
+        <v>1403</v>
       </c>
       <c r="B20" t="s">
-        <v>1368</v>
+        <v>1270</v>
       </c>
       <c r="C20" t="s">
-        <v>1369</v>
+        <v>1404</v>
       </c>
       <c r="D20" t="s">
-        <v>475</v>
+        <v>1405</v>
       </c>
       <c r="E20" t="s">
-        <v>1311</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>1370</v>
+        <v>1406</v>
       </c>
       <c r="B21" t="s">
-        <v>1371</v>
+        <v>1407</v>
       </c>
       <c r="C21" t="s">
-        <v>1372</v>
+        <v>1408</v>
       </c>
       <c r="D21" t="s">
         <v>213</v>
       </c>
       <c r="E21" t="s">
-        <v>1340</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>1373</v>
+        <v>1409</v>
       </c>
       <c r="B22" t="s">
-        <v>1374</v>
+        <v>1410</v>
       </c>
       <c r="C22" t="s">
-        <v>1375</v>
+        <v>1411</v>
       </c>
       <c r="D22" t="s">
-        <v>1376</v>
+        <v>1412</v>
       </c>
       <c r="E22" t="s">
-        <v>1311</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>1377</v>
+        <v>1413</v>
       </c>
       <c r="B23" t="s">
-        <v>1378</v>
+        <v>1414</v>
       </c>
       <c r="C23" t="s">
-        <v>1379</v>
+        <v>1415</v>
       </c>
       <c r="D23" t="s">
-        <v>1380</v>
+        <v>1416</v>
       </c>
       <c r="E23" t="s">
-        <v>1311</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>1381</v>
+        <v>1417</v>
       </c>
       <c r="B24" t="s">
         <v>214</v>
       </c>
       <c r="C24" t="s">
-        <v>1382</v>
+        <v>1418</v>
       </c>
       <c r="D24" t="s">
-        <v>1383</v>
+        <v>1419</v>
       </c>
       <c r="E24" t="s">
-        <v>1311</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>1384</v>
+        <v>1420</v>
       </c>
       <c r="B25" t="s">
-        <v>1385</v>
+        <v>1421</v>
       </c>
       <c r="C25" t="s">
-        <v>1386</v>
+        <v>1422</v>
       </c>
       <c r="D25" t="s">
-        <v>1387</v>
+        <v>1423</v>
       </c>
       <c r="E25" t="s">
-        <v>1340</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>1388</v>
+        <v>1424</v>
       </c>
       <c r="B26" t="s">
-        <v>1389</v>
+        <v>1425</v>
       </c>
       <c r="C26" t="s">
-        <v>1390</v>
+        <v>1426</v>
       </c>
       <c r="D26" t="s">
-        <v>1391</v>
+        <v>1427</v>
       </c>
       <c r="E26" t="s">
-        <v>1340</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>1392</v>
+        <v>1428</v>
       </c>
       <c r="B27" t="s">
-        <v>1393</v>
+        <v>1429</v>
       </c>
       <c r="C27" t="s">
-        <v>1394</v>
+        <v>1430</v>
       </c>
       <c r="D27" t="s">
-        <v>1395</v>
+        <v>1431</v>
       </c>
       <c r="E27" t="s">
-        <v>1311</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>1396</v>
+        <v>1432</v>
       </c>
       <c r="B28" t="s">
-        <v>1397</v>
+        <v>1433</v>
       </c>
       <c r="C28" t="s">
-        <v>1398</v>
+        <v>1434</v>
       </c>
       <c r="D28" t="s">
-        <v>1399</v>
+        <v>1435</v>
       </c>
       <c r="E28" t="s">
-        <v>1311</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>1400</v>
+        <v>1436</v>
       </c>
       <c r="B29" t="s">
         <v>822</v>
       </c>
       <c r="C29" t="s">
-        <v>1401</v>
+        <v>1437</v>
       </c>
       <c r="D29" t="s">
-        <v>1402</v>
+        <v>1438</v>
       </c>
       <c r="E29" t="s">
-        <v>1311</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>1403</v>
+        <v>1439</v>
       </c>
       <c r="B30" t="s">
-        <v>1404</v>
+        <v>1440</v>
       </c>
       <c r="C30" t="s">
-        <v>1405</v>
+        <v>1441</v>
       </c>
       <c r="D30" t="s">
-        <v>1406</v>
+        <v>1442</v>
       </c>
       <c r="E30" t="s">
-        <v>1340</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>1407</v>
+        <v>1443</v>
       </c>
       <c r="B31" t="s">
-        <v>1408</v>
+        <v>1444</v>
       </c>
       <c r="C31" t="s">
-        <v>1409</v>
+        <v>1445</v>
       </c>
       <c r="D31" t="s">
         <v>93</v>
       </c>
       <c r="E31" t="s">
-        <v>1410</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>1411</v>
+        <v>1446</v>
       </c>
       <c r="B32" t="s">
-        <v>1412</v>
+        <v>1447</v>
       </c>
       <c r="C32" t="s">
-        <v>1413</v>
+        <v>1448</v>
       </c>
       <c r="D32" t="s">
-        <v>1414</v>
+        <v>1449</v>
       </c>
       <c r="E32" t="s">
-        <v>1311</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>1415</v>
+        <v>1450</v>
       </c>
       <c r="B33" t="s">
         <v>1030</v>
       </c>
       <c r="C33" t="s">
-        <v>1416</v>
+        <v>1451</v>
       </c>
       <c r="D33" t="s">
-        <v>1417</v>
+        <v>1452</v>
       </c>
       <c r="E33" t="s">
-        <v>1340</v>
+        <v>1376</v>
       </c>
     </row>
   </sheetData>
@@ -15559,157 +15909,157 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr defaultRowHeight="0" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" customHeight="1"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>1418</v>
+        <v>1453</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1419</v>
+        <v>1454</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>1420</v>
+        <v>1455</v>
       </c>
       <c r="B3" t="s">
-        <v>1421</v>
+        <v>1456</v>
       </c>
       <c r="C3" t="s">
-        <v>1422</v>
+        <v>1457</v>
       </c>
       <c r="D3" t="s">
-        <v>1423</v>
+        <v>1458</v>
       </c>
       <c r="E3" t="s">
-        <v>1424</v>
+        <v>1459</v>
       </c>
       <c r="F3" t="s">
-        <v>1425</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1426</v>
+        <v>1461</v>
       </c>
       <c r="B4" t="s">
         <v>28</v>
       </c>
       <c r="C4" t="s">
-        <v>1427</v>
+        <v>1462</v>
       </c>
       <c r="D4" t="s">
-        <v>1428</v>
+        <v>1463</v>
       </c>
       <c r="E4" t="s">
-        <v>1429</v>
+        <v>1464</v>
       </c>
       <c r="F4" t="s">
-        <v>1430</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1431</v>
+        <v>1466</v>
       </c>
       <c r="B5" t="s">
-        <v>1432</v>
+        <v>1467</v>
       </c>
       <c r="C5" t="s">
-        <v>1433</v>
+        <v>1468</v>
       </c>
       <c r="D5" t="s">
-        <v>1434</v>
+        <v>1469</v>
       </c>
       <c r="E5" t="s">
-        <v>1435</v>
+        <v>1470</v>
       </c>
       <c r="F5" t="s">
-        <v>1436</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>1437</v>
+        <v>1472</v>
       </c>
       <c r="B6" t="s">
-        <v>1438</v>
+        <v>1473</v>
       </c>
       <c r="C6" t="s">
-        <v>1439</v>
+        <v>1474</v>
       </c>
       <c r="D6" t="s">
-        <v>1440</v>
+        <v>1475</v>
       </c>
       <c r="E6" t="s">
-        <v>1441</v>
+        <v>1476</v>
       </c>
       <c r="F6" t="s">
-        <v>1442</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>1443</v>
+        <v>1478</v>
       </c>
       <c r="B7" t="s">
-        <v>1444</v>
+        <v>1479</v>
       </c>
       <c r="C7" t="s">
-        <v>1445</v>
+        <v>1480</v>
       </c>
       <c r="D7" t="s">
-        <v>1446</v>
+        <v>1481</v>
       </c>
       <c r="E7" t="s">
-        <v>1441</v>
+        <v>1476</v>
       </c>
       <c r="F7" t="s">
-        <v>1447</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>1448</v>
+        <v>1483</v>
       </c>
       <c r="B8" t="s">
-        <v>1449</v>
+        <v>1484</v>
       </c>
       <c r="C8" t="s">
-        <v>1450</v>
+        <v>1485</v>
       </c>
       <c r="D8" t="s">
-        <v>1451</v>
+        <v>1486</v>
       </c>
       <c r="E8" t="s">
-        <v>1441</v>
+        <v>1476</v>
       </c>
       <c r="F8" t="s">
-        <v>1447</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>1452</v>
+        <v>1487</v>
       </c>
       <c r="B9" t="s">
         <v>29</v>
       </c>
       <c r="C9" t="s">
-        <v>1453</v>
+        <v>1488</v>
       </c>
       <c r="D9" t="s">
-        <v>1454</v>
+        <v>1489</v>
       </c>
       <c r="E9" t="s">
-        <v>1429</v>
+        <v>1464</v>
       </c>
       <c r="F9" t="s">
-        <v>1455</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -15720,93 +16070,93 @@
         <v>29</v>
       </c>
       <c r="C10" t="s">
-        <v>1456</v>
+        <v>1491</v>
       </c>
       <c r="D10" t="s">
-        <v>1457</v>
+        <v>1492</v>
       </c>
       <c r="E10" t="s">
-        <v>1458</v>
+        <v>1493</v>
       </c>
       <c r="F10" t="s">
-        <v>1459</v>
+        <v>1494</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>1460</v>
+        <v>1495</v>
       </c>
       <c r="B11" t="s">
         <v>55</v>
       </c>
       <c r="C11" t="s">
-        <v>1461</v>
+        <v>1496</v>
       </c>
       <c r="D11" t="s">
-        <v>1462</v>
+        <v>1497</v>
       </c>
       <c r="E11" t="s">
-        <v>1458</v>
+        <v>1493</v>
       </c>
       <c r="F11" t="s">
-        <v>1463</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>1464</v>
+        <v>1499</v>
       </c>
       <c r="B12" t="s">
         <v>161</v>
       </c>
       <c r="C12" t="s">
-        <v>1465</v>
+        <v>1500</v>
       </c>
       <c r="D12" t="s">
-        <v>1466</v>
+        <v>1501</v>
       </c>
       <c r="E12" t="s">
-        <v>1467</v>
+        <v>1502</v>
       </c>
       <c r="F12" t="s">
-        <v>1468</v>
+        <v>1503</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>1469</v>
+        <v>1504</v>
       </c>
       <c r="B13" t="s">
-        <v>1470</v>
+        <v>1505</v>
       </c>
       <c r="C13" t="s">
-        <v>1471</v>
+        <v>1506</v>
       </c>
       <c r="D13" t="s">
-        <v>1472</v>
+        <v>1507</v>
       </c>
       <c r="E13" t="s">
-        <v>1473</v>
+        <v>1508</v>
       </c>
       <c r="F13" t="s">
-        <v>1474</v>
+        <v>1509</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>1475</v>
+        <v>1510</v>
       </c>
       <c r="B14" t="s">
         <v>206</v>
       </c>
       <c r="C14" t="s">
-        <v>1476</v>
+        <v>1511</v>
       </c>
       <c r="D14" t="s">
-        <v>1477</v>
+        <v>1512</v>
       </c>
       <c r="E14" t="s">
-        <v>1478</v>
+        <v>1513</v>
       </c>
       <c r="F14" t="s">
         <v>748</v>
@@ -15814,19 +16164,19 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>1479</v>
+        <v>1514</v>
       </c>
       <c r="B15" t="s">
         <v>206</v>
       </c>
       <c r="C15" t="s">
-        <v>1480</v>
+        <v>1515</v>
       </c>
       <c r="D15" t="s">
-        <v>1481</v>
+        <v>1516</v>
       </c>
       <c r="E15" t="s">
-        <v>1482</v>
+        <v>1517</v>
       </c>
       <c r="F15" t="s">
         <v>748</v>
@@ -15834,19 +16184,19 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>1483</v>
+        <v>1518</v>
       </c>
       <c r="B16" t="s">
         <v>918</v>
       </c>
       <c r="C16" t="s">
-        <v>1484</v>
+        <v>1519</v>
       </c>
       <c r="D16" t="s">
-        <v>1485</v>
+        <v>1520</v>
       </c>
       <c r="E16" t="s">
-        <v>1482</v>
+        <v>1517</v>
       </c>
       <c r="F16" t="s">
         <v>924</v>
@@ -15854,19 +16204,19 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>1486</v>
+        <v>1521</v>
       </c>
       <c r="B17" t="s">
         <v>999</v>
       </c>
       <c r="C17" t="s">
-        <v>1487</v>
+        <v>1522</v>
       </c>
       <c r="D17" t="s">
-        <v>1488</v>
+        <v>1523</v>
       </c>
       <c r="E17" t="s">
-        <v>1482</v>
+        <v>1517</v>
       </c>
       <c r="F17" t="s">
         <v>924</v>
@@ -15874,19 +16224,19 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>1489</v>
+        <v>1524</v>
       </c>
       <c r="B18" t="s">
         <v>1095</v>
       </c>
       <c r="C18" t="s">
-        <v>1490</v>
+        <v>1525</v>
       </c>
       <c r="D18" t="s">
-        <v>1491</v>
+        <v>1526</v>
       </c>
       <c r="E18" t="s">
-        <v>1482</v>
+        <v>1517</v>
       </c>
       <c r="F18" t="s">
         <v>924</v>
@@ -15894,19 +16244,19 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>1492</v>
+        <v>1527</v>
       </c>
       <c r="B19" t="s">
-        <v>1141</v>
+        <v>1142</v>
       </c>
       <c r="C19" t="s">
-        <v>1493</v>
+        <v>1528</v>
       </c>
       <c r="D19" t="s">
-        <v>1494</v>
+        <v>1529</v>
       </c>
       <c r="E19" t="s">
-        <v>1482</v>
+        <v>1517</v>
       </c>
       <c r="F19" t="s">
         <v>924</v>
@@ -15914,19 +16264,19 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>1495</v>
+        <v>1530</v>
       </c>
       <c r="B20" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="C20" t="s">
-        <v>1496</v>
+        <v>1531</v>
       </c>
       <c r="D20" t="s">
-        <v>1497</v>
+        <v>1532</v>
       </c>
       <c r="E20" t="s">
-        <v>1482</v>
+        <v>1517</v>
       </c>
       <c r="F20" t="s">
         <v>924</v>
@@ -15934,21 +16284,41 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>1498</v>
+        <v>1533</v>
       </c>
       <c r="B21" t="s">
-        <v>1214</v>
+        <v>1215</v>
       </c>
       <c r="C21" t="s">
-        <v>1499</v>
+        <v>1534</v>
       </c>
       <c r="D21" t="s">
-        <v>1500</v>
+        <v>1535</v>
       </c>
       <c r="E21" t="s">
-        <v>1482</v>
+        <v>1517</v>
       </c>
       <c r="F21" t="s">
+        <v>924</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>1536</v>
+      </c>
+      <c r="B22" t="s">
+        <v>1272</v>
+      </c>
+      <c r="C22" t="s">
+        <v>1537</v>
+      </c>
+      <c r="D22" t="s">
+        <v>1538</v>
+      </c>
+      <c r="E22" t="s">
+        <v>1517</v>
+      </c>
+      <c r="F22" t="s">
         <v>924</v>
       </c>
     </row>
@@ -15958,40 +16328,40 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G173"/>
+  <dimension ref="A1:G177"/>
   <sheetFormatPr defaultRowHeight="0" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" customHeight="1"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>1501</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1502</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>1503</v>
+        <v>1541</v>
       </c>
       <c r="B3" t="s">
-        <v>1504</v>
+        <v>1542</v>
       </c>
       <c r="C3" t="s">
-        <v>1505</v>
+        <v>1543</v>
       </c>
       <c r="D3" t="s">
-        <v>1506</v>
+        <v>1544</v>
       </c>
       <c r="E3" t="s">
-        <v>1507</v>
+        <v>1545</v>
       </c>
       <c r="F3" t="s">
-        <v>1508</v>
+        <v>1546</v>
       </c>
       <c r="G3" t="s">
-        <v>1509</v>
+        <v>1547</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -16011,10 +16381,10 @@
         <v>26</v>
       </c>
       <c r="F4" t="s">
-        <v>1510</v>
+        <v>1548</v>
       </c>
       <c r="G4" t="s">
-        <v>1511</v>
+        <v>1549</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -16034,10 +16404,10 @@
         <v>26</v>
       </c>
       <c r="F5" t="s">
-        <v>1510</v>
+        <v>1548</v>
       </c>
       <c r="G5" t="s">
-        <v>1512</v>
+        <v>1550</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -16057,10 +16427,10 @@
         <v>26</v>
       </c>
       <c r="F6" t="s">
-        <v>1510</v>
+        <v>1548</v>
       </c>
       <c r="G6" t="s">
-        <v>1513</v>
+        <v>1551</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -16080,10 +16450,10 @@
         <v>86</v>
       </c>
       <c r="F7" t="s">
-        <v>1510</v>
+        <v>1548</v>
       </c>
       <c r="G7" t="s">
-        <v>1514</v>
+        <v>1552</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -16103,10 +16473,10 @@
         <v>26</v>
       </c>
       <c r="F8" t="s">
-        <v>1510</v>
+        <v>1548</v>
       </c>
       <c r="G8" t="s">
-        <v>1515</v>
+        <v>1553</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -16126,10 +16496,10 @@
         <v>26</v>
       </c>
       <c r="F9" t="s">
-        <v>1510</v>
+        <v>1548</v>
       </c>
       <c r="G9" t="s">
-        <v>1516</v>
+        <v>1554</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -16149,10 +16519,10 @@
         <v>26</v>
       </c>
       <c r="F10" t="s">
-        <v>1510</v>
+        <v>1548</v>
       </c>
       <c r="G10" t="s">
-        <v>1517</v>
+        <v>1555</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -16172,10 +16542,10 @@
         <v>86</v>
       </c>
       <c r="F11" t="s">
-        <v>1510</v>
+        <v>1548</v>
       </c>
       <c r="G11" t="s">
-        <v>1518</v>
+        <v>1556</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -16195,10 +16565,10 @@
         <v>86</v>
       </c>
       <c r="F12" t="s">
-        <v>1510</v>
+        <v>1548</v>
       </c>
       <c r="G12" t="s">
-        <v>1519</v>
+        <v>1557</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -16218,10 +16588,10 @@
         <v>26</v>
       </c>
       <c r="F13" t="s">
-        <v>1510</v>
+        <v>1548</v>
       </c>
       <c r="G13" t="s">
-        <v>1520</v>
+        <v>1558</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -16241,10 +16611,10 @@
         <v>26</v>
       </c>
       <c r="F14" t="s">
-        <v>1521</v>
+        <v>1559</v>
       </c>
       <c r="G14" t="s">
-        <v>1522</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -16264,10 +16634,10 @@
         <v>26</v>
       </c>
       <c r="F15" t="s">
-        <v>1521</v>
+        <v>1559</v>
       </c>
       <c r="G15" t="s">
-        <v>1523</v>
+        <v>1561</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -16287,10 +16657,10 @@
         <v>26</v>
       </c>
       <c r="F16" t="s">
-        <v>1521</v>
+        <v>1559</v>
       </c>
       <c r="G16" t="s">
-        <v>1524</v>
+        <v>1562</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -16310,10 +16680,10 @@
         <v>26</v>
       </c>
       <c r="F17" t="s">
-        <v>1521</v>
+        <v>1559</v>
       </c>
       <c r="G17" t="s">
-        <v>1525</v>
+        <v>1563</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -16333,10 +16703,10 @@
         <v>26</v>
       </c>
       <c r="F18" t="s">
-        <v>1521</v>
+        <v>1559</v>
       </c>
       <c r="G18" t="s">
-        <v>1526</v>
+        <v>1564</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -16356,10 +16726,10 @@
         <v>26</v>
       </c>
       <c r="F19" t="s">
-        <v>1521</v>
+        <v>1559</v>
       </c>
       <c r="G19" t="s">
-        <v>1527</v>
+        <v>1565</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -16379,10 +16749,10 @@
         <v>86</v>
       </c>
       <c r="F20" t="s">
-        <v>1521</v>
+        <v>1559</v>
       </c>
       <c r="G20" t="s">
-        <v>1528</v>
+        <v>1566</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -16402,10 +16772,10 @@
         <v>86</v>
       </c>
       <c r="F21" t="s">
-        <v>1521</v>
+        <v>1559</v>
       </c>
       <c r="G21" t="s">
-        <v>1529</v>
+        <v>1567</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
@@ -16425,10 +16795,10 @@
         <v>26</v>
       </c>
       <c r="F22" t="s">
-        <v>1521</v>
+        <v>1559</v>
       </c>
       <c r="G22" t="s">
-        <v>1530</v>
+        <v>1568</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
@@ -16448,10 +16818,10 @@
         <v>86</v>
       </c>
       <c r="F23" t="s">
-        <v>1521</v>
+        <v>1559</v>
       </c>
       <c r="G23" t="s">
-        <v>1531</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -16471,10 +16841,10 @@
         <v>86</v>
       </c>
       <c r="F24" t="s">
-        <v>1521</v>
+        <v>1559</v>
       </c>
       <c r="G24" t="s">
-        <v>1532</v>
+        <v>1570</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
@@ -16494,10 +16864,10 @@
         <v>86</v>
       </c>
       <c r="F25" t="s">
-        <v>1521</v>
+        <v>1559</v>
       </c>
       <c r="G25" t="s">
-        <v>1533</v>
+        <v>1571</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
@@ -16517,10 +16887,10 @@
         <v>86</v>
       </c>
       <c r="F26" t="s">
-        <v>1521</v>
+        <v>1559</v>
       </c>
       <c r="G26" t="s">
-        <v>1534</v>
+        <v>1572</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
@@ -16540,10 +16910,10 @@
         <v>26</v>
       </c>
       <c r="F27" t="s">
-        <v>1521</v>
+        <v>1559</v>
       </c>
       <c r="G27" t="s">
-        <v>1535</v>
+        <v>1573</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
@@ -16563,10 +16933,10 @@
         <v>86</v>
       </c>
       <c r="F28" t="s">
-        <v>1521</v>
+        <v>1559</v>
       </c>
       <c r="G28" t="s">
-        <v>1536</v>
+        <v>1574</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
@@ -16586,10 +16956,10 @@
         <v>86</v>
       </c>
       <c r="F29" t="s">
-        <v>1521</v>
+        <v>1559</v>
       </c>
       <c r="G29" t="s">
-        <v>1537</v>
+        <v>1575</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
@@ -16609,10 +16979,10 @@
         <v>26</v>
       </c>
       <c r="F30" t="s">
-        <v>1521</v>
+        <v>1559</v>
       </c>
       <c r="G30" t="s">
-        <v>1538</v>
+        <v>1576</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
@@ -16632,10 +17002,10 @@
         <v>26</v>
       </c>
       <c r="F31" t="s">
-        <v>1521</v>
+        <v>1559</v>
       </c>
       <c r="G31" t="s">
-        <v>1539</v>
+        <v>1577</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
@@ -16655,10 +17025,10 @@
         <v>86</v>
       </c>
       <c r="F32" t="s">
-        <v>1521</v>
+        <v>1559</v>
       </c>
       <c r="G32" t="s">
-        <v>1540</v>
+        <v>1578</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
@@ -16678,10 +17048,10 @@
         <v>86</v>
       </c>
       <c r="F33" t="s">
-        <v>1521</v>
+        <v>1559</v>
       </c>
       <c r="G33" t="s">
-        <v>1541</v>
+        <v>1579</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
@@ -16701,10 +17071,10 @@
         <v>86</v>
       </c>
       <c r="F34" t="s">
-        <v>1521</v>
+        <v>1559</v>
       </c>
       <c r="G34" t="s">
-        <v>1542</v>
+        <v>1580</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
@@ -16724,7 +17094,7 @@
         <v>26</v>
       </c>
       <c r="F35" t="s">
-        <v>1543</v>
+        <v>1581</v>
       </c>
       <c r="G35" t="s">
         <v>168</v>
@@ -16747,7 +17117,7 @@
         <v>26</v>
       </c>
       <c r="F36" t="s">
-        <v>1543</v>
+        <v>1581</v>
       </c>
       <c r="G36" t="s">
         <v>177</v>
@@ -16770,7 +17140,7 @@
         <v>26</v>
       </c>
       <c r="F37" t="s">
-        <v>1543</v>
+        <v>1581</v>
       </c>
       <c r="G37" t="s">
         <v>194</v>
@@ -16793,7 +17163,7 @@
         <v>26</v>
       </c>
       <c r="F38" t="s">
-        <v>1543</v>
+        <v>1581</v>
       </c>
       <c r="G38" t="s">
         <v>203</v>
@@ -16816,7 +17186,7 @@
         <v>26</v>
       </c>
       <c r="F39" t="s">
-        <v>1543</v>
+        <v>1581</v>
       </c>
       <c r="G39" t="s">
         <v>222</v>
@@ -16839,7 +17209,7 @@
         <v>26</v>
       </c>
       <c r="F40" t="s">
-        <v>1543</v>
+        <v>1581</v>
       </c>
       <c r="G40" t="s">
         <v>245</v>
@@ -16862,10 +17232,10 @@
         <v>26</v>
       </c>
       <c r="F41" t="s">
-        <v>1543</v>
+        <v>1581</v>
       </c>
       <c r="G41" t="s">
-        <v>1544</v>
+        <v>1582</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
@@ -16885,10 +17255,10 @@
         <v>26</v>
       </c>
       <c r="F42" t="s">
-        <v>1543</v>
+        <v>1581</v>
       </c>
       <c r="G42" t="s">
-        <v>1545</v>
+        <v>1583</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
@@ -16908,10 +17278,10 @@
         <v>26</v>
       </c>
       <c r="F43" t="s">
-        <v>1543</v>
+        <v>1581</v>
       </c>
       <c r="G43" t="s">
-        <v>1546</v>
+        <v>1584</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
@@ -16931,7 +17301,7 @@
         <v>26</v>
       </c>
       <c r="F44" t="s">
-        <v>1543</v>
+        <v>1581</v>
       </c>
       <c r="G44" t="s">
         <v>360</v>
@@ -16954,7 +17324,7 @@
         <v>26</v>
       </c>
       <c r="F45" t="s">
-        <v>1543</v>
+        <v>1581</v>
       </c>
       <c r="G45" t="s">
         <v>368</v>
@@ -16977,10 +17347,10 @@
         <v>26</v>
       </c>
       <c r="F46" t="s">
-        <v>1543</v>
+        <v>1581</v>
       </c>
       <c r="G46" t="s">
-        <v>1547</v>
+        <v>1585</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
@@ -17000,7 +17370,7 @@
         <v>26</v>
       </c>
       <c r="F47" t="s">
-        <v>1543</v>
+        <v>1581</v>
       </c>
       <c r="G47" t="s">
         <v>386</v>
@@ -17023,10 +17393,10 @@
         <v>26</v>
       </c>
       <c r="F48" t="s">
-        <v>1543</v>
+        <v>1581</v>
       </c>
       <c r="G48" t="s">
-        <v>1548</v>
+        <v>1586</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
@@ -17046,7 +17416,7 @@
         <v>26</v>
       </c>
       <c r="F49" t="s">
-        <v>1543</v>
+        <v>1581</v>
       </c>
       <c r="G49" t="s">
         <v>402</v>
@@ -17069,7 +17439,7 @@
         <v>26</v>
       </c>
       <c r="F50" t="s">
-        <v>1543</v>
+        <v>1581</v>
       </c>
       <c r="G50" t="s">
         <v>411</v>
@@ -17092,7 +17462,7 @@
         <v>26</v>
       </c>
       <c r="F51" t="s">
-        <v>1543</v>
+        <v>1581</v>
       </c>
       <c r="G51" t="s">
         <v>419</v>
@@ -17115,7 +17485,7 @@
         <v>26</v>
       </c>
       <c r="F52" t="s">
-        <v>1543</v>
+        <v>1581</v>
       </c>
       <c r="G52" t="s">
         <v>426</v>
@@ -17138,7 +17508,7 @@
         <v>26</v>
       </c>
       <c r="F53" t="s">
-        <v>1543</v>
+        <v>1581</v>
       </c>
       <c r="G53" t="s">
         <v>433</v>
@@ -17161,7 +17531,7 @@
         <v>26</v>
       </c>
       <c r="F54" t="s">
-        <v>1543</v>
+        <v>1581</v>
       </c>
       <c r="G54" t="s">
         <v>467</v>
@@ -17184,7 +17554,7 @@
         <v>26</v>
       </c>
       <c r="F55" t="s">
-        <v>1543</v>
+        <v>1581</v>
       </c>
       <c r="G55" t="s">
         <v>485</v>
@@ -17207,7 +17577,7 @@
         <v>26</v>
       </c>
       <c r="F56" t="s">
-        <v>1543</v>
+        <v>1581</v>
       </c>
       <c r="G56" t="s">
         <v>494</v>
@@ -17230,7 +17600,7 @@
         <v>26</v>
       </c>
       <c r="F57" t="s">
-        <v>1543</v>
+        <v>1581</v>
       </c>
       <c r="G57" t="s">
         <v>502</v>
@@ -17253,7 +17623,7 @@
         <v>26</v>
       </c>
       <c r="F58" t="s">
-        <v>1543</v>
+        <v>1581</v>
       </c>
       <c r="G58" t="s">
         <v>511</v>
@@ -17276,7 +17646,7 @@
         <v>26</v>
       </c>
       <c r="F59" t="s">
-        <v>1543</v>
+        <v>1581</v>
       </c>
       <c r="G59" t="s">
         <v>520</v>
@@ -17299,7 +17669,7 @@
         <v>26</v>
       </c>
       <c r="F60" t="s">
-        <v>1543</v>
+        <v>1581</v>
       </c>
       <c r="G60" t="s">
         <v>530</v>
@@ -17322,7 +17692,7 @@
         <v>26</v>
       </c>
       <c r="F61" t="s">
-        <v>1543</v>
+        <v>1581</v>
       </c>
       <c r="G61" t="s">
         <v>539</v>
@@ -17345,7 +17715,7 @@
         <v>26</v>
       </c>
       <c r="F62" t="s">
-        <v>1543</v>
+        <v>1581</v>
       </c>
       <c r="G62" t="s">
         <v>547</v>
@@ -17368,7 +17738,7 @@
         <v>26</v>
       </c>
       <c r="F63" t="s">
-        <v>1543</v>
+        <v>1581</v>
       </c>
       <c r="G63" t="s">
         <v>557</v>
@@ -17391,7 +17761,7 @@
         <v>26</v>
       </c>
       <c r="F64" t="s">
-        <v>1543</v>
+        <v>1581</v>
       </c>
       <c r="G64" t="s">
         <v>567</v>
@@ -17414,7 +17784,7 @@
         <v>26</v>
       </c>
       <c r="F65" t="s">
-        <v>1543</v>
+        <v>1581</v>
       </c>
       <c r="G65" t="s">
         <v>576</v>
@@ -17437,7 +17807,7 @@
         <v>26</v>
       </c>
       <c r="F66" t="s">
-        <v>1543</v>
+        <v>1581</v>
       </c>
       <c r="G66" t="s">
         <v>584</v>
@@ -17460,7 +17830,7 @@
         <v>26</v>
       </c>
       <c r="F67" t="s">
-        <v>1543</v>
+        <v>1581</v>
       </c>
       <c r="G67" t="s">
         <v>594</v>
@@ -17483,7 +17853,7 @@
         <v>26</v>
       </c>
       <c r="F68" t="s">
-        <v>1543</v>
+        <v>1581</v>
       </c>
       <c r="G68" t="s">
         <v>602</v>
@@ -17506,7 +17876,7 @@
         <v>26</v>
       </c>
       <c r="F69" t="s">
-        <v>1543</v>
+        <v>1581</v>
       </c>
       <c r="G69" t="s">
         <v>611</v>
@@ -17529,7 +17899,7 @@
         <v>26</v>
       </c>
       <c r="F70" t="s">
-        <v>1543</v>
+        <v>1581</v>
       </c>
       <c r="G70" t="s">
         <v>618</v>
@@ -17552,10 +17922,10 @@
         <v>26</v>
       </c>
       <c r="F71" t="s">
-        <v>1543</v>
+        <v>1581</v>
       </c>
       <c r="G71" t="s">
-        <v>1549</v>
+        <v>1587</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
@@ -17575,10 +17945,10 @@
         <v>26</v>
       </c>
       <c r="F72" t="s">
-        <v>1543</v>
+        <v>1581</v>
       </c>
       <c r="G72" t="s">
-        <v>1550</v>
+        <v>1588</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
@@ -17598,10 +17968,10 @@
         <v>26</v>
       </c>
       <c r="F73" t="s">
-        <v>1543</v>
+        <v>1581</v>
       </c>
       <c r="G73" t="s">
-        <v>1551</v>
+        <v>1589</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
@@ -17621,10 +17991,10 @@
         <v>26</v>
       </c>
       <c r="F74" t="s">
-        <v>1543</v>
+        <v>1581</v>
       </c>
       <c r="G74" t="s">
-        <v>1552</v>
+        <v>1590</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
@@ -17644,10 +18014,10 @@
         <v>26</v>
       </c>
       <c r="F75" t="s">
-        <v>1543</v>
+        <v>1581</v>
       </c>
       <c r="G75" t="s">
-        <v>1553</v>
+        <v>1591</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
@@ -17667,10 +18037,10 @@
         <v>26</v>
       </c>
       <c r="F76" t="s">
-        <v>1543</v>
+        <v>1581</v>
       </c>
       <c r="G76" t="s">
-        <v>1554</v>
+        <v>1592</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
@@ -17690,10 +18060,10 @@
         <v>26</v>
       </c>
       <c r="F77" t="s">
-        <v>1543</v>
+        <v>1581</v>
       </c>
       <c r="G77" t="s">
-        <v>1555</v>
+        <v>1593</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
@@ -17713,10 +18083,10 @@
         <v>26</v>
       </c>
       <c r="F78" t="s">
-        <v>1543</v>
+        <v>1581</v>
       </c>
       <c r="G78" t="s">
-        <v>1556</v>
+        <v>1594</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
@@ -17736,10 +18106,10 @@
         <v>26</v>
       </c>
       <c r="F79" t="s">
-        <v>1543</v>
+        <v>1581</v>
       </c>
       <c r="G79" t="s">
-        <v>1557</v>
+        <v>1595</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
@@ -17747,7 +18117,7 @@
         <v>27</v>
       </c>
       <c r="B80" t="s">
-        <v>1470</v>
+        <v>1505</v>
       </c>
       <c r="C80" t="s">
         <v>697</v>
@@ -17759,10 +18129,10 @@
         <v>26</v>
       </c>
       <c r="F80" t="s">
-        <v>1558</v>
+        <v>1596</v>
       </c>
       <c r="G80" t="s">
-        <v>1559</v>
+        <v>1597</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
@@ -17770,7 +18140,7 @@
         <v>27</v>
       </c>
       <c r="B81" t="s">
-        <v>1470</v>
+        <v>1505</v>
       </c>
       <c r="C81" t="s">
         <v>708</v>
@@ -17782,10 +18152,10 @@
         <v>26</v>
       </c>
       <c r="F81" t="s">
-        <v>1558</v>
+        <v>1596</v>
       </c>
       <c r="G81" t="s">
-        <v>1560</v>
+        <v>1598</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
@@ -17793,7 +18163,7 @@
         <v>27</v>
       </c>
       <c r="B82" t="s">
-        <v>1470</v>
+        <v>1505</v>
       </c>
       <c r="C82" t="s">
         <v>715</v>
@@ -17805,10 +18175,10 @@
         <v>26</v>
       </c>
       <c r="F82" t="s">
-        <v>1558</v>
+        <v>1596</v>
       </c>
       <c r="G82" t="s">
-        <v>1561</v>
+        <v>1599</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
@@ -17816,7 +18186,7 @@
         <v>27</v>
       </c>
       <c r="B83" t="s">
-        <v>1470</v>
+        <v>1505</v>
       </c>
       <c r="C83" t="s">
         <v>723</v>
@@ -17828,10 +18198,10 @@
         <v>26</v>
       </c>
       <c r="F83" t="s">
-        <v>1558</v>
+        <v>1596</v>
       </c>
       <c r="G83" t="s">
-        <v>1562</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
@@ -17839,7 +18209,7 @@
         <v>27</v>
       </c>
       <c r="B84" t="s">
-        <v>1470</v>
+        <v>1505</v>
       </c>
       <c r="C84" t="s">
         <v>732</v>
@@ -17851,10 +18221,10 @@
         <v>26</v>
       </c>
       <c r="F84" t="s">
-        <v>1558</v>
+        <v>1596</v>
       </c>
       <c r="G84" t="s">
-        <v>1563</v>
+        <v>1601</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
@@ -17862,7 +18232,7 @@
         <v>27</v>
       </c>
       <c r="B85" t="s">
-        <v>1564</v>
+        <v>1602</v>
       </c>
       <c r="C85" t="s">
         <v>324</v>
@@ -17874,10 +18244,10 @@
         <v>86</v>
       </c>
       <c r="F85" t="s">
-        <v>1565</v>
+        <v>1603</v>
       </c>
       <c r="G85" t="s">
-        <v>1566</v>
+        <v>1604</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
@@ -17885,7 +18255,7 @@
         <v>27</v>
       </c>
       <c r="B86" t="s">
-        <v>1564</v>
+        <v>1602</v>
       </c>
       <c r="C86" t="s">
         <v>335</v>
@@ -17897,10 +18267,10 @@
         <v>86</v>
       </c>
       <c r="F86" t="s">
-        <v>1565</v>
+        <v>1603</v>
       </c>
       <c r="G86" t="s">
-        <v>1567</v>
+        <v>1605</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
@@ -17908,7 +18278,7 @@
         <v>27</v>
       </c>
       <c r="B87" t="s">
-        <v>1564</v>
+        <v>1602</v>
       </c>
       <c r="C87" t="s">
         <v>344</v>
@@ -17920,10 +18290,10 @@
         <v>86</v>
       </c>
       <c r="F87" t="s">
-        <v>1565</v>
+        <v>1603</v>
       </c>
       <c r="G87" t="s">
-        <v>1568</v>
+        <v>1606</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
@@ -17931,7 +18301,7 @@
         <v>27</v>
       </c>
       <c r="B88" t="s">
-        <v>1564</v>
+        <v>1602</v>
       </c>
       <c r="C88" t="s">
         <v>369</v>
@@ -17943,10 +18313,10 @@
         <v>112</v>
       </c>
       <c r="F88" t="s">
-        <v>1565</v>
+        <v>1603</v>
       </c>
       <c r="G88" t="s">
-        <v>1569</v>
+        <v>1607</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
@@ -17966,10 +18336,10 @@
         <v>26</v>
       </c>
       <c r="F89" t="s">
-        <v>1570</v>
+        <v>1608</v>
       </c>
       <c r="G89" t="s">
-        <v>1571</v>
+        <v>1609</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
@@ -17977,7 +18347,7 @@
         <v>27</v>
       </c>
       <c r="B90" t="s">
-        <v>1564</v>
+        <v>1602</v>
       </c>
       <c r="C90" t="s">
         <v>619</v>
@@ -17989,10 +18359,10 @@
         <v>112</v>
       </c>
       <c r="F90" t="s">
-        <v>1565</v>
+        <v>1603</v>
       </c>
       <c r="G90" t="s">
-        <v>1572</v>
+        <v>1610</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
@@ -18000,7 +18370,7 @@
         <v>27</v>
       </c>
       <c r="B91" t="s">
-        <v>1564</v>
+        <v>1602</v>
       </c>
       <c r="C91" t="s">
         <v>639</v>
@@ -18012,10 +18382,10 @@
         <v>86</v>
       </c>
       <c r="F91" t="s">
-        <v>1565</v>
+        <v>1603</v>
       </c>
       <c r="G91" t="s">
-        <v>1573</v>
+        <v>1611</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
@@ -18023,7 +18393,7 @@
         <v>27</v>
       </c>
       <c r="B92" t="s">
-        <v>1564</v>
+        <v>1602</v>
       </c>
       <c r="C92" t="s">
         <v>648</v>
@@ -18035,10 +18405,10 @@
         <v>112</v>
       </c>
       <c r="F92" t="s">
-        <v>1565</v>
+        <v>1603</v>
       </c>
       <c r="G92" t="s">
-        <v>1574</v>
+        <v>1612</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
@@ -18058,10 +18428,10 @@
         <v>86</v>
       </c>
       <c r="F93" t="s">
-        <v>1570</v>
+        <v>1608</v>
       </c>
       <c r="G93" t="s">
-        <v>1575</v>
+        <v>1613</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
@@ -18069,7 +18439,7 @@
         <v>27</v>
       </c>
       <c r="B94" t="s">
-        <v>1564</v>
+        <v>1602</v>
       </c>
       <c r="C94" t="s">
         <v>657</v>
@@ -18081,10 +18451,10 @@
         <v>112</v>
       </c>
       <c r="F94" t="s">
-        <v>1565</v>
+        <v>1603</v>
       </c>
       <c r="G94" t="s">
-        <v>1576</v>
+        <v>1614</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
@@ -18092,7 +18462,7 @@
         <v>27</v>
       </c>
       <c r="B95" t="s">
-        <v>1564</v>
+        <v>1602</v>
       </c>
       <c r="C95" t="s">
         <v>673</v>
@@ -18104,10 +18474,10 @@
         <v>112</v>
       </c>
       <c r="F95" t="s">
-        <v>1565</v>
+        <v>1603</v>
       </c>
       <c r="G95" t="s">
-        <v>1577</v>
+        <v>1615</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
@@ -18127,10 +18497,10 @@
         <v>26</v>
       </c>
       <c r="F96" t="s">
-        <v>1570</v>
+        <v>1608</v>
       </c>
       <c r="G96" t="s">
-        <v>1578</v>
+        <v>1616</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
@@ -18138,7 +18508,7 @@
         <v>27</v>
       </c>
       <c r="B97" t="s">
-        <v>1564</v>
+        <v>1602</v>
       </c>
       <c r="C97" t="s">
         <v>689</v>
@@ -18150,10 +18520,10 @@
         <v>112</v>
       </c>
       <c r="F97" t="s">
-        <v>1565</v>
+        <v>1603</v>
       </c>
       <c r="G97" t="s">
-        <v>1579</v>
+        <v>1617</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
@@ -18161,7 +18531,7 @@
         <v>27</v>
       </c>
       <c r="B98" t="s">
-        <v>1564</v>
+        <v>1602</v>
       </c>
       <c r="C98" t="s">
         <v>697</v>
@@ -18173,10 +18543,10 @@
         <v>112</v>
       </c>
       <c r="F98" t="s">
-        <v>1565</v>
+        <v>1603</v>
       </c>
       <c r="G98" t="s">
-        <v>1580</v>
+        <v>1618</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
@@ -18196,10 +18566,10 @@
         <v>26</v>
       </c>
       <c r="F99" t="s">
-        <v>1570</v>
+        <v>1608</v>
       </c>
       <c r="G99" t="s">
-        <v>1581</v>
+        <v>1619</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
@@ -18207,7 +18577,7 @@
         <v>27</v>
       </c>
       <c r="B100" t="s">
-        <v>1564</v>
+        <v>1602</v>
       </c>
       <c r="C100" t="s">
         <v>708</v>
@@ -18219,10 +18589,10 @@
         <v>112</v>
       </c>
       <c r="F100" t="s">
-        <v>1565</v>
+        <v>1603</v>
       </c>
       <c r="G100" t="s">
-        <v>1582</v>
+        <v>1620</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
@@ -18242,10 +18612,10 @@
         <v>86</v>
       </c>
       <c r="F101" t="s">
-        <v>1570</v>
+        <v>1608</v>
       </c>
       <c r="G101" t="s">
-        <v>1583</v>
+        <v>1621</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
@@ -18253,7 +18623,7 @@
         <v>27</v>
       </c>
       <c r="B102" t="s">
-        <v>1564</v>
+        <v>1602</v>
       </c>
       <c r="C102" t="s">
         <v>715</v>
@@ -18265,10 +18635,10 @@
         <v>112</v>
       </c>
       <c r="F102" t="s">
-        <v>1565</v>
+        <v>1603</v>
       </c>
       <c r="G102" t="s">
-        <v>1584</v>
+        <v>1622</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
@@ -18288,10 +18658,10 @@
         <v>86</v>
       </c>
       <c r="F103" t="s">
-        <v>1570</v>
+        <v>1608</v>
       </c>
       <c r="G103" t="s">
-        <v>1585</v>
+        <v>1623</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
@@ -18299,7 +18669,7 @@
         <v>27</v>
       </c>
       <c r="B104" t="s">
-        <v>1564</v>
+        <v>1602</v>
       </c>
       <c r="C104" t="s">
         <v>723</v>
@@ -18311,10 +18681,10 @@
         <v>112</v>
       </c>
       <c r="F104" t="s">
-        <v>1565</v>
+        <v>1603</v>
       </c>
       <c r="G104" t="s">
-        <v>1586</v>
+        <v>1624</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
@@ -18334,10 +18704,10 @@
         <v>26</v>
       </c>
       <c r="F105" t="s">
-        <v>1570</v>
+        <v>1608</v>
       </c>
       <c r="G105" t="s">
-        <v>1587</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
@@ -18345,7 +18715,7 @@
         <v>27</v>
       </c>
       <c r="B106" t="s">
-        <v>1564</v>
+        <v>1602</v>
       </c>
       <c r="C106" t="s">
         <v>732</v>
@@ -18357,10 +18727,10 @@
         <v>112</v>
       </c>
       <c r="F106" t="s">
-        <v>1565</v>
+        <v>1603</v>
       </c>
       <c r="G106" t="s">
-        <v>1588</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
@@ -18380,10 +18750,10 @@
         <v>26</v>
       </c>
       <c r="F107" t="s">
-        <v>1570</v>
+        <v>1608</v>
       </c>
       <c r="G107" t="s">
-        <v>1589</v>
+        <v>1627</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
@@ -18397,13 +18767,13 @@
         <v>740</v>
       </c>
       <c r="D108" t="s">
-        <v>1590</v>
+        <v>1628</v>
       </c>
       <c r="E108" t="s">
         <v>112</v>
       </c>
       <c r="F108" t="s">
-        <v>1570</v>
+        <v>1608</v>
       </c>
       <c r="G108" t="s">
         <v>741</v>
@@ -18420,13 +18790,13 @@
         <v>750</v>
       </c>
       <c r="D109" t="s">
-        <v>1590</v>
+        <v>1628</v>
       </c>
       <c r="E109" t="s">
         <v>112</v>
       </c>
       <c r="F109" t="s">
-        <v>1570</v>
+        <v>1608</v>
       </c>
       <c r="G109" t="s">
         <v>751</v>
@@ -18443,13 +18813,13 @@
         <v>758</v>
       </c>
       <c r="D110" t="s">
-        <v>1590</v>
+        <v>1628</v>
       </c>
       <c r="E110" t="s">
         <v>112</v>
       </c>
       <c r="F110" t="s">
-        <v>1570</v>
+        <v>1608</v>
       </c>
       <c r="G110" t="s">
         <v>759</v>
@@ -18466,13 +18836,13 @@
         <v>766</v>
       </c>
       <c r="D111" t="s">
-        <v>1590</v>
+        <v>1628</v>
       </c>
       <c r="E111" t="s">
         <v>112</v>
       </c>
       <c r="F111" t="s">
-        <v>1570</v>
+        <v>1608</v>
       </c>
       <c r="G111" t="s">
         <v>767</v>
@@ -18489,13 +18859,13 @@
         <v>774</v>
       </c>
       <c r="D112" t="s">
-        <v>1590</v>
+        <v>1628</v>
       </c>
       <c r="E112" t="s">
         <v>112</v>
       </c>
       <c r="F112" t="s">
-        <v>1570</v>
+        <v>1608</v>
       </c>
       <c r="G112" t="s">
         <v>775</v>
@@ -18512,13 +18882,13 @@
         <v>782</v>
       </c>
       <c r="D113" t="s">
-        <v>1590</v>
+        <v>1628</v>
       </c>
       <c r="E113" t="s">
         <v>112</v>
       </c>
       <c r="F113" t="s">
-        <v>1570</v>
+        <v>1608</v>
       </c>
       <c r="G113" t="s">
         <v>783</v>
@@ -18535,13 +18905,13 @@
         <v>790</v>
       </c>
       <c r="D114" t="s">
-        <v>1590</v>
+        <v>1628</v>
       </c>
       <c r="E114" t="s">
         <v>112</v>
       </c>
       <c r="F114" t="s">
-        <v>1570</v>
+        <v>1608</v>
       </c>
       <c r="G114" t="s">
         <v>791</v>
@@ -18558,13 +18928,13 @@
         <v>798</v>
       </c>
       <c r="D115" t="s">
-        <v>1590</v>
+        <v>1628</v>
       </c>
       <c r="E115" t="s">
         <v>112</v>
       </c>
       <c r="F115" t="s">
-        <v>1570</v>
+        <v>1608</v>
       </c>
       <c r="G115" t="s">
         <v>799</v>
@@ -18581,13 +18951,13 @@
         <v>806</v>
       </c>
       <c r="D116" t="s">
-        <v>1590</v>
+        <v>1628</v>
       </c>
       <c r="E116" t="s">
         <v>112</v>
       </c>
       <c r="F116" t="s">
-        <v>1570</v>
+        <v>1608</v>
       </c>
       <c r="G116" t="s">
         <v>807</v>
@@ -18604,13 +18974,13 @@
         <v>814</v>
       </c>
       <c r="D117" t="s">
-        <v>1590</v>
+        <v>1628</v>
       </c>
       <c r="E117" t="s">
         <v>112</v>
       </c>
       <c r="F117" t="s">
-        <v>1570</v>
+        <v>1608</v>
       </c>
       <c r="G117" t="s">
         <v>815</v>
@@ -18627,13 +18997,13 @@
         <v>821</v>
       </c>
       <c r="D118" t="s">
-        <v>1590</v>
+        <v>1628</v>
       </c>
       <c r="E118" t="s">
         <v>112</v>
       </c>
       <c r="F118" t="s">
-        <v>1570</v>
+        <v>1608</v>
       </c>
       <c r="G118" t="s">
         <v>823</v>
@@ -18650,13 +19020,13 @@
         <v>830</v>
       </c>
       <c r="D119" t="s">
-        <v>1590</v>
+        <v>1628</v>
       </c>
       <c r="E119" t="s">
         <v>112</v>
       </c>
       <c r="F119" t="s">
-        <v>1570</v>
+        <v>1608</v>
       </c>
       <c r="G119" t="s">
         <v>831</v>
@@ -18673,13 +19043,13 @@
         <v>837</v>
       </c>
       <c r="D120" t="s">
-        <v>1590</v>
+        <v>1628</v>
       </c>
       <c r="E120" t="s">
         <v>112</v>
       </c>
       <c r="F120" t="s">
-        <v>1570</v>
+        <v>1608</v>
       </c>
       <c r="G120" t="s">
         <v>838</v>
@@ -18696,13 +19066,13 @@
         <v>844</v>
       </c>
       <c r="D121" t="s">
-        <v>1590</v>
+        <v>1628</v>
       </c>
       <c r="E121" t="s">
         <v>112</v>
       </c>
       <c r="F121" t="s">
-        <v>1570</v>
+        <v>1608</v>
       </c>
       <c r="G121" t="s">
         <v>845</v>
@@ -18719,13 +19089,13 @@
         <v>852</v>
       </c>
       <c r="D122" t="s">
-        <v>1590</v>
+        <v>1628</v>
       </c>
       <c r="E122" t="s">
         <v>26</v>
       </c>
       <c r="F122" t="s">
-        <v>1570</v>
+        <v>1608</v>
       </c>
       <c r="G122" t="s">
         <v>853</v>
@@ -18742,13 +19112,13 @@
         <v>860</v>
       </c>
       <c r="D123" t="s">
-        <v>1590</v>
+        <v>1628</v>
       </c>
       <c r="E123" t="s">
         <v>112</v>
       </c>
       <c r="F123" t="s">
-        <v>1570</v>
+        <v>1608</v>
       </c>
       <c r="G123" t="s">
         <v>861</v>
@@ -18765,13 +19135,13 @@
         <v>868</v>
       </c>
       <c r="D124" t="s">
-        <v>1590</v>
+        <v>1628</v>
       </c>
       <c r="E124" t="s">
         <v>112</v>
       </c>
       <c r="F124" t="s">
-        <v>1570</v>
+        <v>1608</v>
       </c>
       <c r="G124" t="s">
         <v>869</v>
@@ -18788,13 +19158,13 @@
         <v>876</v>
       </c>
       <c r="D125" t="s">
-        <v>1590</v>
+        <v>1628</v>
       </c>
       <c r="E125" t="s">
         <v>112</v>
       </c>
       <c r="F125" t="s">
-        <v>1570</v>
+        <v>1608</v>
       </c>
       <c r="G125" t="s">
         <v>878</v>
@@ -18811,13 +19181,13 @@
         <v>885</v>
       </c>
       <c r="D126" t="s">
-        <v>1590</v>
+        <v>1628</v>
       </c>
       <c r="E126" t="s">
         <v>112</v>
       </c>
       <c r="F126" t="s">
-        <v>1570</v>
+        <v>1608</v>
       </c>
       <c r="G126" t="s">
         <v>886</v>
@@ -18834,13 +19204,13 @@
         <v>893</v>
       </c>
       <c r="D127" t="s">
-        <v>1590</v>
+        <v>1628</v>
       </c>
       <c r="E127" t="s">
         <v>112</v>
       </c>
       <c r="F127" t="s">
-        <v>1570</v>
+        <v>1608</v>
       </c>
       <c r="G127" t="s">
         <v>894</v>
@@ -18857,13 +19227,13 @@
         <v>901</v>
       </c>
       <c r="D128" t="s">
-        <v>1590</v>
+        <v>1628</v>
       </c>
       <c r="E128" t="s">
         <v>453</v>
       </c>
       <c r="F128" t="s">
-        <v>1570</v>
+        <v>1608</v>
       </c>
       <c r="G128" t="s">
         <v>902</v>
@@ -18880,13 +19250,13 @@
         <v>909</v>
       </c>
       <c r="D129" t="s">
-        <v>1590</v>
+        <v>1628</v>
       </c>
       <c r="E129" t="s">
         <v>112</v>
       </c>
       <c r="F129" t="s">
-        <v>1570</v>
+        <v>1608</v>
       </c>
       <c r="G129" t="s">
         <v>910</v>
@@ -18903,13 +19273,13 @@
         <v>916</v>
       </c>
       <c r="D130" t="s">
-        <v>1590</v>
+        <v>1628</v>
       </c>
       <c r="E130" t="s">
         <v>112</v>
       </c>
       <c r="F130" t="s">
-        <v>1570</v>
+        <v>1608</v>
       </c>
       <c r="G130" t="s">
         <v>917</v>
@@ -18926,13 +19296,13 @@
         <v>926</v>
       </c>
       <c r="D131" t="s">
-        <v>1590</v>
+        <v>1628</v>
       </c>
       <c r="E131" t="s">
         <v>112</v>
       </c>
       <c r="F131" t="s">
-        <v>1570</v>
+        <v>1608</v>
       </c>
       <c r="G131" t="s">
         <v>927</v>
@@ -18949,13 +19319,13 @@
         <v>934</v>
       </c>
       <c r="D132" t="s">
-        <v>1590</v>
+        <v>1628</v>
       </c>
       <c r="E132" t="s">
         <v>112</v>
       </c>
       <c r="F132" t="s">
-        <v>1570</v>
+        <v>1608</v>
       </c>
       <c r="G132" t="s">
         <v>935</v>
@@ -18972,13 +19342,13 @@
         <v>942</v>
       </c>
       <c r="D133" t="s">
-        <v>1590</v>
+        <v>1628</v>
       </c>
       <c r="E133" t="s">
         <v>112</v>
       </c>
       <c r="F133" t="s">
-        <v>1570</v>
+        <v>1608</v>
       </c>
       <c r="G133" t="s">
         <v>943</v>
@@ -18995,13 +19365,13 @@
         <v>950</v>
       </c>
       <c r="D134" t="s">
-        <v>1590</v>
+        <v>1628</v>
       </c>
       <c r="E134" t="s">
         <v>112</v>
       </c>
       <c r="F134" t="s">
-        <v>1570</v>
+        <v>1608</v>
       </c>
       <c r="G134" t="s">
         <v>951</v>
@@ -19018,13 +19388,13 @@
         <v>958</v>
       </c>
       <c r="D135" t="s">
-        <v>1590</v>
+        <v>1628</v>
       </c>
       <c r="E135" t="s">
         <v>112</v>
       </c>
       <c r="F135" t="s">
-        <v>1570</v>
+        <v>1608</v>
       </c>
       <c r="G135" t="s">
         <v>960</v>
@@ -19041,13 +19411,13 @@
         <v>967</v>
       </c>
       <c r="D136" t="s">
-        <v>1590</v>
+        <v>1628</v>
       </c>
       <c r="E136" t="s">
         <v>112</v>
       </c>
       <c r="F136" t="s">
-        <v>1570</v>
+        <v>1608</v>
       </c>
       <c r="G136" t="s">
         <v>968</v>
@@ -19064,13 +19434,13 @@
         <v>974</v>
       </c>
       <c r="D137" t="s">
-        <v>1590</v>
+        <v>1628</v>
       </c>
       <c r="E137" t="s">
         <v>112</v>
       </c>
       <c r="F137" t="s">
-        <v>1570</v>
+        <v>1608</v>
       </c>
       <c r="G137" t="s">
         <v>975</v>
@@ -19087,13 +19457,13 @@
         <v>981</v>
       </c>
       <c r="D138" t="s">
-        <v>1590</v>
+        <v>1628</v>
       </c>
       <c r="E138" t="s">
         <v>112</v>
       </c>
       <c r="F138" t="s">
-        <v>1570</v>
+        <v>1608</v>
       </c>
       <c r="G138" t="s">
         <v>982</v>
@@ -19110,13 +19480,13 @@
         <v>989</v>
       </c>
       <c r="D139" t="s">
-        <v>1590</v>
+        <v>1628</v>
       </c>
       <c r="E139" t="s">
         <v>112</v>
       </c>
       <c r="F139" t="s">
-        <v>1570</v>
+        <v>1608</v>
       </c>
       <c r="G139" t="s">
         <v>990</v>
@@ -19133,13 +19503,13 @@
         <v>997</v>
       </c>
       <c r="D140" t="s">
-        <v>1590</v>
+        <v>1628</v>
       </c>
       <c r="E140" t="s">
         <v>112</v>
       </c>
       <c r="F140" t="s">
-        <v>1570</v>
+        <v>1608</v>
       </c>
       <c r="G140" t="s">
         <v>998</v>
@@ -19156,13 +19526,13 @@
         <v>1006</v>
       </c>
       <c r="D141" t="s">
-        <v>1590</v>
+        <v>1628</v>
       </c>
       <c r="E141" t="s">
         <v>112</v>
       </c>
       <c r="F141" t="s">
-        <v>1570</v>
+        <v>1608</v>
       </c>
       <c r="G141" t="s">
         <v>1007</v>
@@ -19179,13 +19549,13 @@
         <v>1014</v>
       </c>
       <c r="D142" t="s">
-        <v>1590</v>
+        <v>1628</v>
       </c>
       <c r="E142" t="s">
         <v>112</v>
       </c>
       <c r="F142" t="s">
-        <v>1570</v>
+        <v>1608</v>
       </c>
       <c r="G142" t="s">
         <v>1015</v>
@@ -19202,13 +19572,13 @@
         <v>1021</v>
       </c>
       <c r="D143" t="s">
-        <v>1590</v>
+        <v>1628</v>
       </c>
       <c r="E143" t="s">
         <v>453</v>
       </c>
       <c r="F143" t="s">
-        <v>1570</v>
+        <v>1608</v>
       </c>
       <c r="G143" t="s">
         <v>1022</v>
@@ -19225,13 +19595,13 @@
         <v>1029</v>
       </c>
       <c r="D144" t="s">
-        <v>1590</v>
+        <v>1628</v>
       </c>
       <c r="E144" t="s">
         <v>112</v>
       </c>
       <c r="F144" t="s">
-        <v>1570</v>
+        <v>1608</v>
       </c>
       <c r="G144" t="s">
         <v>1031</v>
@@ -19248,13 +19618,13 @@
         <v>1037</v>
       </c>
       <c r="D145" t="s">
-        <v>1590</v>
+        <v>1628</v>
       </c>
       <c r="E145" t="s">
         <v>112</v>
       </c>
       <c r="F145" t="s">
-        <v>1570</v>
+        <v>1608</v>
       </c>
       <c r="G145" t="s">
         <v>1038</v>
@@ -19271,13 +19641,13 @@
         <v>1045</v>
       </c>
       <c r="D146" t="s">
-        <v>1590</v>
+        <v>1628</v>
       </c>
       <c r="E146" t="s">
         <v>112</v>
       </c>
       <c r="F146" t="s">
-        <v>1570</v>
+        <v>1608</v>
       </c>
       <c r="G146" t="s">
         <v>1046</v>
@@ -19294,13 +19664,13 @@
         <v>1053</v>
       </c>
       <c r="D147" t="s">
-        <v>1590</v>
+        <v>1628</v>
       </c>
       <c r="E147" t="s">
         <v>112</v>
       </c>
       <c r="F147" t="s">
-        <v>1570</v>
+        <v>1608</v>
       </c>
       <c r="G147" t="s">
         <v>1055</v>
@@ -19317,13 +19687,13 @@
         <v>1061</v>
       </c>
       <c r="D148" t="s">
-        <v>1590</v>
+        <v>1628</v>
       </c>
       <c r="E148" t="s">
         <v>112</v>
       </c>
       <c r="F148" t="s">
-        <v>1570</v>
+        <v>1608</v>
       </c>
       <c r="G148" t="s">
         <v>1062</v>
@@ -19340,13 +19710,13 @@
         <v>1068</v>
       </c>
       <c r="D149" t="s">
-        <v>1590</v>
+        <v>1628</v>
       </c>
       <c r="E149" t="s">
         <v>95</v>
       </c>
       <c r="F149" t="s">
-        <v>1570</v>
+        <v>1608</v>
       </c>
       <c r="G149" t="s">
         <v>1069</v>
@@ -19363,13 +19733,13 @@
         <v>1076</v>
       </c>
       <c r="D150" t="s">
-        <v>1590</v>
+        <v>1628</v>
       </c>
       <c r="E150" t="s">
         <v>112</v>
       </c>
       <c r="F150" t="s">
-        <v>1570</v>
+        <v>1608</v>
       </c>
       <c r="G150" t="s">
         <v>1078</v>
@@ -19386,13 +19756,13 @@
         <v>1085</v>
       </c>
       <c r="D151" t="s">
-        <v>1590</v>
+        <v>1628</v>
       </c>
       <c r="E151" t="s">
         <v>95</v>
       </c>
       <c r="F151" t="s">
-        <v>1570</v>
+        <v>1608</v>
       </c>
       <c r="G151" t="s">
         <v>1086</v>
@@ -19409,13 +19779,13 @@
         <v>1093</v>
       </c>
       <c r="D152" t="s">
-        <v>1590</v>
+        <v>1628</v>
       </c>
       <c r="E152" t="s">
         <v>112</v>
       </c>
       <c r="F152" t="s">
-        <v>1570</v>
+        <v>1608</v>
       </c>
       <c r="G152" t="s">
         <v>1094</v>
@@ -19432,13 +19802,13 @@
         <v>1102</v>
       </c>
       <c r="D153" t="s">
-        <v>1590</v>
+        <v>1628</v>
       </c>
       <c r="E153" t="s">
         <v>112</v>
       </c>
       <c r="F153" t="s">
-        <v>1570</v>
+        <v>1608</v>
       </c>
       <c r="G153" t="s">
         <v>1103</v>
@@ -19452,19 +19822,19 @@
         <v>1095</v>
       </c>
       <c r="C154" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="D154" t="s">
-        <v>1590</v>
+        <v>1628</v>
       </c>
       <c r="E154" t="s">
         <v>453</v>
       </c>
       <c r="F154" t="s">
-        <v>1570</v>
+        <v>1608</v>
       </c>
       <c r="G154" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.25">
@@ -19475,19 +19845,19 @@
         <v>1095</v>
       </c>
       <c r="C155" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="D155" t="s">
-        <v>1590</v>
+        <v>1628</v>
       </c>
       <c r="E155" t="s">
         <v>112</v>
       </c>
       <c r="F155" t="s">
-        <v>1570</v>
+        <v>1608</v>
       </c>
       <c r="G155" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.25">
@@ -19498,19 +19868,19 @@
         <v>1095</v>
       </c>
       <c r="C156" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="D156" t="s">
-        <v>1590</v>
+        <v>1628</v>
       </c>
       <c r="E156" t="s">
         <v>95</v>
       </c>
       <c r="F156" t="s">
-        <v>1570</v>
+        <v>1608</v>
       </c>
       <c r="G156" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.25">
@@ -19521,19 +19891,19 @@
         <v>1095</v>
       </c>
       <c r="C157" t="s">
-        <v>1132</v>
+        <v>1133</v>
       </c>
       <c r="D157" t="s">
-        <v>1590</v>
+        <v>1628</v>
       </c>
       <c r="E157" t="s">
         <v>112</v>
       </c>
       <c r="F157" t="s">
-        <v>1570</v>
+        <v>1608</v>
       </c>
       <c r="G157" t="s">
-        <v>1133</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.25">
@@ -19541,22 +19911,22 @@
         <v>27</v>
       </c>
       <c r="B158" t="s">
+        <v>1142</v>
+      </c>
+      <c r="C158" t="s">
+        <v>1140</v>
+      </c>
+      <c r="D158" t="s">
+        <v>1628</v>
+      </c>
+      <c r="E158" t="s">
+        <v>112</v>
+      </c>
+      <c r="F158" t="s">
+        <v>1608</v>
+      </c>
+      <c r="G158" t="s">
         <v>1141</v>
-      </c>
-      <c r="C158" t="s">
-        <v>1139</v>
-      </c>
-      <c r="D158" t="s">
-        <v>1590</v>
-      </c>
-      <c r="E158" t="s">
-        <v>112</v>
-      </c>
-      <c r="F158" t="s">
-        <v>1570</v>
-      </c>
-      <c r="G158" t="s">
-        <v>1140</v>
       </c>
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.25">
@@ -19564,22 +19934,22 @@
         <v>27</v>
       </c>
       <c r="B159" t="s">
-        <v>1141</v>
+        <v>1142</v>
       </c>
       <c r="C159" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="D159" t="s">
-        <v>1590</v>
+        <v>1628</v>
       </c>
       <c r="E159" t="s">
         <v>112</v>
       </c>
       <c r="F159" t="s">
-        <v>1570</v>
+        <v>1608</v>
       </c>
       <c r="G159" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.25">
@@ -19587,22 +19957,22 @@
         <v>27</v>
       </c>
       <c r="B160" t="s">
+        <v>1159</v>
+      </c>
+      <c r="C160" t="s">
+        <v>1157</v>
+      </c>
+      <c r="D160" t="s">
+        <v>1628</v>
+      </c>
+      <c r="E160" t="s">
+        <v>112</v>
+      </c>
+      <c r="F160" t="s">
+        <v>1608</v>
+      </c>
+      <c r="G160" t="s">
         <v>1158</v>
-      </c>
-      <c r="C160" t="s">
-        <v>1156</v>
-      </c>
-      <c r="D160" t="s">
-        <v>1590</v>
-      </c>
-      <c r="E160" t="s">
-        <v>112</v>
-      </c>
-      <c r="F160" t="s">
-        <v>1570</v>
-      </c>
-      <c r="G160" t="s">
-        <v>1157</v>
       </c>
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.25">
@@ -19610,22 +19980,22 @@
         <v>27</v>
       </c>
       <c r="B161" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="C161" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="D161" t="s">
-        <v>1590</v>
+        <v>1628</v>
       </c>
       <c r="E161" t="s">
         <v>95</v>
       </c>
       <c r="F161" t="s">
-        <v>1570</v>
+        <v>1608</v>
       </c>
       <c r="G161" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.25">
@@ -19633,22 +20003,22 @@
         <v>27</v>
       </c>
       <c r="B162" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="C162" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="D162" t="s">
-        <v>1590</v>
+        <v>1628</v>
       </c>
       <c r="E162" t="s">
         <v>112</v>
       </c>
       <c r="F162" t="s">
-        <v>1570</v>
+        <v>1608</v>
       </c>
       <c r="G162" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.25">
@@ -19656,22 +20026,22 @@
         <v>27</v>
       </c>
       <c r="B163" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="C163" t="s">
-        <v>1181</v>
+        <v>1182</v>
       </c>
       <c r="D163" t="s">
-        <v>1590</v>
+        <v>1628</v>
       </c>
       <c r="E163" t="s">
         <v>112</v>
       </c>
       <c r="F163" t="s">
-        <v>1570</v>
+        <v>1608</v>
       </c>
       <c r="G163" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.25">
@@ -19679,22 +20049,22 @@
         <v>27</v>
       </c>
       <c r="B164" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="C164" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="D164" t="s">
-        <v>1590</v>
+        <v>1628</v>
       </c>
       <c r="E164" t="s">
         <v>112</v>
       </c>
       <c r="F164" t="s">
-        <v>1570</v>
+        <v>1608</v>
       </c>
       <c r="G164" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.25">
@@ -19702,22 +20072,22 @@
         <v>27</v>
       </c>
       <c r="B165" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="C165" t="s">
-        <v>1196</v>
+        <v>1197</v>
       </c>
       <c r="D165" t="s">
-        <v>1590</v>
+        <v>1628</v>
       </c>
       <c r="E165" t="s">
         <v>112</v>
       </c>
       <c r="F165" t="s">
-        <v>1570</v>
+        <v>1608</v>
       </c>
       <c r="G165" t="s">
-        <v>1197</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.25">
@@ -19725,22 +20095,22 @@
         <v>27</v>
       </c>
       <c r="B166" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="C166" t="s">
-        <v>1204</v>
+        <v>1205</v>
       </c>
       <c r="D166" t="s">
-        <v>1590</v>
+        <v>1628</v>
       </c>
       <c r="E166" t="s">
         <v>95</v>
       </c>
       <c r="F166" t="s">
-        <v>1570</v>
+        <v>1608</v>
       </c>
       <c r="G166" t="s">
-        <v>1205</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.25">
@@ -19748,22 +20118,22 @@
         <v>27</v>
       </c>
       <c r="B167" t="s">
+        <v>1215</v>
+      </c>
+      <c r="C167" t="s">
+        <v>1213</v>
+      </c>
+      <c r="D167" t="s">
+        <v>1628</v>
+      </c>
+      <c r="E167" t="s">
+        <v>112</v>
+      </c>
+      <c r="F167" t="s">
+        <v>1608</v>
+      </c>
+      <c r="G167" t="s">
         <v>1214</v>
-      </c>
-      <c r="C167" t="s">
-        <v>1212</v>
-      </c>
-      <c r="D167" t="s">
-        <v>1590</v>
-      </c>
-      <c r="E167" t="s">
-        <v>112</v>
-      </c>
-      <c r="F167" t="s">
-        <v>1570</v>
-      </c>
-      <c r="G167" t="s">
-        <v>1213</v>
       </c>
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.25">
@@ -19771,22 +20141,22 @@
         <v>27</v>
       </c>
       <c r="B168" t="s">
-        <v>1214</v>
+        <v>1215</v>
       </c>
       <c r="C168" t="s">
-        <v>1221</v>
+        <v>1222</v>
       </c>
       <c r="D168" t="s">
-        <v>1590</v>
+        <v>1628</v>
       </c>
       <c r="E168" t="s">
         <v>112</v>
       </c>
       <c r="F168" t="s">
-        <v>1570</v>
+        <v>1608</v>
       </c>
       <c r="G168" t="s">
-        <v>1222</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.25">
@@ -19794,22 +20164,22 @@
         <v>27</v>
       </c>
       <c r="B169" t="s">
-        <v>1214</v>
+        <v>1215</v>
       </c>
       <c r="C169" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="D169" t="s">
-        <v>1590</v>
+        <v>1628</v>
       </c>
       <c r="E169" t="s">
         <v>112</v>
       </c>
       <c r="F169" t="s">
-        <v>1570</v>
+        <v>1608</v>
       </c>
       <c r="G169" t="s">
-        <v>1230</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.25">
@@ -19817,22 +20187,22 @@
         <v>27</v>
       </c>
       <c r="B170" t="s">
-        <v>1214</v>
+        <v>1215</v>
       </c>
       <c r="C170" t="s">
-        <v>1237</v>
+        <v>1238</v>
       </c>
       <c r="D170" t="s">
-        <v>1590</v>
+        <v>1628</v>
       </c>
       <c r="E170" t="s">
         <v>112</v>
       </c>
       <c r="F170" t="s">
-        <v>1570</v>
+        <v>1608</v>
       </c>
       <c r="G170" t="s">
-        <v>1238</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.25">
@@ -19840,22 +20210,22 @@
         <v>27</v>
       </c>
       <c r="B171" t="s">
-        <v>1214</v>
+        <v>1215</v>
       </c>
       <c r="C171" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
       <c r="D171" t="s">
-        <v>1590</v>
+        <v>1628</v>
       </c>
       <c r="E171" t="s">
         <v>112</v>
       </c>
       <c r="F171" t="s">
-        <v>1570</v>
+        <v>1608</v>
       </c>
       <c r="G171" t="s">
-        <v>1245</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="172" spans="1:7" x14ac:dyDescent="0.25">
@@ -19863,22 +20233,22 @@
         <v>27</v>
       </c>
       <c r="B172" t="s">
-        <v>1214</v>
+        <v>1215</v>
       </c>
       <c r="C172" t="s">
-        <v>1251</v>
+        <v>1253</v>
       </c>
       <c r="D172" t="s">
-        <v>1590</v>
+        <v>1628</v>
       </c>
       <c r="E172" t="s">
         <v>453</v>
       </c>
       <c r="F172" t="s">
-        <v>1570</v>
+        <v>1608</v>
       </c>
       <c r="G172" t="s">
-        <v>1252</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="173" spans="1:7" x14ac:dyDescent="0.25">
@@ -19886,22 +20256,114 @@
         <v>27</v>
       </c>
       <c r="B173" t="s">
-        <v>1214</v>
+        <v>1215</v>
       </c>
       <c r="C173" t="s">
-        <v>1259</v>
+        <v>1261</v>
       </c>
       <c r="D173" t="s">
-        <v>1590</v>
+        <v>1628</v>
       </c>
       <c r="E173" t="s">
         <v>112</v>
       </c>
       <c r="F173" t="s">
-        <v>1570</v>
+        <v>1608</v>
       </c>
       <c r="G173" t="s">
-        <v>1260</v>
+        <v>1262</v>
+      </c>
+    </row>
+    <row r="174" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A174" t="s">
+        <v>27</v>
+      </c>
+      <c r="B174" t="s">
+        <v>1272</v>
+      </c>
+      <c r="C174" t="s">
+        <v>1269</v>
+      </c>
+      <c r="D174" t="s">
+        <v>1628</v>
+      </c>
+      <c r="E174" t="s">
+        <v>112</v>
+      </c>
+      <c r="F174" t="s">
+        <v>1608</v>
+      </c>
+      <c r="G174" t="s">
+        <v>1271</v>
+      </c>
+    </row>
+    <row r="175" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A175" t="s">
+        <v>27</v>
+      </c>
+      <c r="B175" t="s">
+        <v>1272</v>
+      </c>
+      <c r="C175" t="s">
+        <v>1278</v>
+      </c>
+      <c r="D175" t="s">
+        <v>1628</v>
+      </c>
+      <c r="E175" t="s">
+        <v>112</v>
+      </c>
+      <c r="F175" t="s">
+        <v>1608</v>
+      </c>
+      <c r="G175" t="s">
+        <v>1279</v>
+      </c>
+    </row>
+    <row r="176" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A176" t="s">
+        <v>27</v>
+      </c>
+      <c r="B176" t="s">
+        <v>1272</v>
+      </c>
+      <c r="C176" t="s">
+        <v>1286</v>
+      </c>
+      <c r="D176" t="s">
+        <v>1628</v>
+      </c>
+      <c r="E176" t="s">
+        <v>112</v>
+      </c>
+      <c r="F176" t="s">
+        <v>1608</v>
+      </c>
+      <c r="G176" t="s">
+        <v>1287</v>
+      </c>
+    </row>
+    <row r="177" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A177" t="s">
+        <v>27</v>
+      </c>
+      <c r="B177" t="s">
+        <v>1272</v>
+      </c>
+      <c r="C177" t="s">
+        <v>1294</v>
+      </c>
+      <c r="D177" t="s">
+        <v>1628</v>
+      </c>
+      <c r="E177" t="s">
+        <v>95</v>
+      </c>
+      <c r="F177" t="s">
+        <v>1608</v>
+      </c>
+      <c r="G177" t="s">
+        <v>1296</v>
       </c>
     </row>
   </sheetData>
@@ -19915,7 +20377,7 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>1591</v>
+        <v>1629</v>
       </c>
       <c r="B1"/>
       <c r="C1"/>
@@ -19923,7 +20385,7 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1592</v>
+        <v>1630</v>
       </c>
       <c r="B2"/>
       <c r="C2"/>
@@ -19934,181 +20396,181 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>1593</v>
+        <v>1631</v>
       </c>
       <c r="C3" t="s">
-        <v>1594</v>
+        <v>1632</v>
       </c>
       <c r="D3" t="s">
-        <v>1595</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1596</v>
+        <v>1634</v>
       </c>
       <c r="B4" t="s">
-        <v>1597</v>
+        <v>1635</v>
       </c>
       <c r="C4" t="s">
-        <v>1598</v>
+        <v>1636</v>
       </c>
       <c r="D4" t="s">
-        <v>1599</v>
+        <v>1637</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1600</v>
+        <v>1638</v>
       </c>
       <c r="B5" t="s">
-        <v>1597</v>
+        <v>1635</v>
       </c>
       <c r="C5" t="s">
-        <v>1601</v>
+        <v>1639</v>
       </c>
       <c r="D5" t="s">
-        <v>1602</v>
+        <v>1640</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>1603</v>
+        <v>1641</v>
       </c>
       <c r="B6" t="s">
-        <v>1597</v>
+        <v>1635</v>
       </c>
       <c r="C6" t="s">
-        <v>1604</v>
+        <v>1642</v>
       </c>
       <c r="D6" t="s">
-        <v>1605</v>
+        <v>1643</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>1606</v>
+        <v>1644</v>
       </c>
       <c r="B7" t="s">
-        <v>1597</v>
+        <v>1635</v>
       </c>
       <c r="C7" t="s">
-        <v>1607</v>
+        <v>1645</v>
       </c>
       <c r="D7" t="s">
-        <v>1608</v>
+        <v>1646</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>1609</v>
+        <v>1647</v>
       </c>
       <c r="B8" t="s">
-        <v>1597</v>
+        <v>1635</v>
       </c>
       <c r="C8" t="s">
-        <v>1610</v>
+        <v>1648</v>
       </c>
       <c r="D8" t="s">
-        <v>1611</v>
+        <v>1649</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>1612</v>
+        <v>1650</v>
       </c>
       <c r="B9" t="s">
-        <v>1613</v>
+        <v>1651</v>
       </c>
       <c r="C9" t="s">
-        <v>1614</v>
+        <v>1652</v>
       </c>
       <c r="D9" t="s">
-        <v>1615</v>
+        <v>1653</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>1616</v>
+        <v>1654</v>
       </c>
       <c r="B10" t="s">
-        <v>1613</v>
+        <v>1651</v>
       </c>
       <c r="C10" t="s">
-        <v>1617</v>
+        <v>1655</v>
       </c>
       <c r="D10" t="s">
-        <v>1618</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>1619</v>
+        <v>1657</v>
       </c>
       <c r="B11" t="s">
-        <v>1613</v>
+        <v>1651</v>
       </c>
       <c r="C11" t="s">
-        <v>1620</v>
+        <v>1658</v>
       </c>
       <c r="D11" t="s">
-        <v>1621</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>1622</v>
+        <v>1660</v>
       </c>
       <c r="B12" t="s">
-        <v>1623</v>
+        <v>1661</v>
       </c>
       <c r="C12" t="s">
-        <v>1624</v>
+        <v>1662</v>
       </c>
       <c r="D12" t="s">
-        <v>1625</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>1626</v>
+        <v>1664</v>
       </c>
       <c r="B13" t="s">
-        <v>1623</v>
+        <v>1661</v>
       </c>
       <c r="C13" t="s">
-        <v>1627</v>
+        <v>1665</v>
       </c>
       <c r="D13" t="s">
-        <v>1628</v>
+        <v>1666</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>1629</v>
+        <v>1667</v>
       </c>
       <c r="B14" t="s">
         <v>877</v>
       </c>
       <c r="C14" t="s">
-        <v>1630</v>
+        <v>1668</v>
       </c>
       <c r="D14" t="s">
-        <v>1631</v>
+        <v>1669</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>1632</v>
+        <v>1670</v>
       </c>
       <c r="B15" t="s">
         <v>877</v>
       </c>
       <c r="C15" t="s">
-        <v>1633</v>
+        <v>1671</v>
       </c>
       <c r="D15" t="s">
-        <v>1634</v>
+        <v>1672</v>
       </c>
     </row>
   </sheetData>
@@ -20127,7 +20589,7 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>1635</v>
+        <v>1673</v>
       </c>
       <c r="B1"/>
       <c r="C1"/>
@@ -20135,133 +20597,133 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>1636</v>
+        <v>1674</v>
       </c>
       <c r="B3" t="s">
-        <v>1637</v>
+        <v>1675</v>
       </c>
       <c r="C3" t="s">
-        <v>1638</v>
+        <v>1676</v>
       </c>
       <c r="D3" t="s">
-        <v>1639</v>
+        <v>1677</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1307</v>
+        <v>1343</v>
       </c>
       <c r="B4" t="s">
-        <v>1640</v>
+        <v>1678</v>
       </c>
       <c r="C4" t="s">
-        <v>1641</v>
+        <v>1679</v>
       </c>
       <c r="D4" t="s">
-        <v>1642</v>
+        <v>1680</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1312</v>
+        <v>1348</v>
       </c>
       <c r="B5" t="s">
-        <v>1643</v>
+        <v>1681</v>
       </c>
       <c r="C5" t="s">
-        <v>1644</v>
+        <v>1682</v>
       </c>
       <c r="D5" t="s">
-        <v>1645</v>
+        <v>1683</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>1316</v>
+        <v>1352</v>
       </c>
       <c r="B6" t="s">
-        <v>1646</v>
+        <v>1684</v>
       </c>
       <c r="C6" t="s">
-        <v>1647</v>
+        <v>1685</v>
       </c>
       <c r="D6" t="s">
-        <v>1648</v>
+        <v>1686</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>1320</v>
+        <v>1356</v>
       </c>
       <c r="B7" t="s">
-        <v>1649</v>
+        <v>1687</v>
       </c>
       <c r="C7" t="s">
-        <v>1650</v>
+        <v>1688</v>
       </c>
       <c r="D7" t="s">
-        <v>1651</v>
+        <v>1689</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>1324</v>
+        <v>1360</v>
       </c>
       <c r="B8" t="s">
-        <v>1652</v>
+        <v>1690</v>
       </c>
       <c r="C8" t="s">
-        <v>1653</v>
+        <v>1691</v>
       </c>
       <c r="D8" t="s">
-        <v>1654</v>
+        <v>1692</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>1328</v>
+        <v>1364</v>
       </c>
       <c r="B9" t="s">
-        <v>1655</v>
+        <v>1693</v>
       </c>
       <c r="C9" t="s">
-        <v>1656</v>
+        <v>1694</v>
       </c>
       <c r="D9" t="s">
-        <v>1657</v>
+        <v>1695</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>1332</v>
+        <v>1368</v>
       </c>
       <c r="B10" t="s">
-        <v>1658</v>
+        <v>1696</v>
       </c>
       <c r="C10" t="s">
-        <v>1659</v>
+        <v>1697</v>
       </c>
       <c r="D10" t="s">
-        <v>1660</v>
+        <v>1698</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>1336</v>
+        <v>1372</v>
       </c>
       <c r="B11" t="s">
-        <v>1661</v>
+        <v>1699</v>
       </c>
       <c r="C11" t="s">
-        <v>1662</v>
+        <v>1700</v>
       </c>
       <c r="D11" t="s">
-        <v>1663</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>1664</v>
+        <v>1702</v>
       </c>
       <c r="B13"/>
       <c r="C13"/>
@@ -20269,72 +20731,72 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>1665</v>
+        <v>1703</v>
       </c>
       <c r="B14" t="s">
         <v>28</v>
       </c>
       <c r="C14" t="s">
-        <v>1666</v>
+        <v>1704</v>
       </c>
       <c r="D14" t="s">
-        <v>1667</v>
+        <v>1705</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>1668</v>
+        <v>1706</v>
       </c>
       <c r="B15" t="s">
         <v>29</v>
       </c>
       <c r="C15" t="s">
-        <v>1669</v>
+        <v>1707</v>
       </c>
       <c r="D15" t="s">
-        <v>1670</v>
+        <v>1708</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>1671</v>
+        <v>1709</v>
       </c>
       <c r="B16" t="s">
         <v>29</v>
       </c>
       <c r="C16" t="s">
-        <v>1672</v>
+        <v>1710</v>
       </c>
       <c r="D16" t="s">
-        <v>1673</v>
+        <v>1711</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>1674</v>
+        <v>1712</v>
       </c>
       <c r="B17" t="s">
         <v>29</v>
       </c>
       <c r="C17" t="s">
-        <v>1675</v>
+        <v>1713</v>
       </c>
       <c r="D17" t="s">
-        <v>1676</v>
+        <v>1714</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>1677</v>
+        <v>1715</v>
       </c>
       <c r="B18" t="s">
-        <v>1678</v>
+        <v>1716</v>
       </c>
       <c r="C18" t="s">
-        <v>1679</v>
+        <v>1717</v>
       </c>
       <c r="D18" t="s">
-        <v>1680</v>
+        <v>1718</v>
       </c>
     </row>
   </sheetData>
@@ -20353,7 +20815,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>1681</v>
+        <v>1719</v>
       </c>
       <c r="B1"/>
       <c r="C1"/>
@@ -20363,7 +20825,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1682</v>
+        <v>1720</v>
       </c>
       <c r="B2"/>
       <c r="C2"/>
@@ -20373,99 +20835,99 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1683</v>
+        <v>1721</v>
       </c>
       <c r="B4" t="s">
-        <v>1684</v>
+        <v>1722</v>
       </c>
       <c r="C4" t="s">
-        <v>1685</v>
+        <v>1723</v>
       </c>
       <c r="D4" t="s">
-        <v>1686</v>
+        <v>1724</v>
       </c>
       <c r="E4" t="s">
-        <v>1687</v>
+        <v>1725</v>
       </c>
       <c r="F4" t="s">
-        <v>1688</v>
+        <v>1726</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1689</v>
+        <v>1727</v>
       </c>
       <c r="B5" t="s">
-        <v>1690</v>
+        <v>1728</v>
       </c>
       <c r="C5" t="s">
-        <v>1691</v>
+        <v>1729</v>
       </c>
       <c r="D5" t="s">
-        <v>1692</v>
+        <v>1730</v>
       </c>
       <c r="E5" t="s">
-        <v>1693</v>
+        <v>1731</v>
       </c>
       <c r="F5" t="s">
-        <v>1694</v>
+        <v>1732</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>1695</v>
+        <v>1733</v>
       </c>
       <c r="B6" t="s">
-        <v>1696</v>
+        <v>1734</v>
       </c>
       <c r="C6" t="s">
-        <v>1697</v>
+        <v>1735</v>
       </c>
       <c r="D6" t="s">
-        <v>1698</v>
+        <v>1736</v>
       </c>
       <c r="E6" t="s">
-        <v>1699</v>
+        <v>1737</v>
       </c>
       <c r="F6" t="s">
-        <v>1700</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>1701</v>
+        <v>1739</v>
       </c>
       <c r="B7" t="s">
-        <v>1696</v>
+        <v>1734</v>
       </c>
       <c r="C7" t="s">
-        <v>1702</v>
+        <v>1740</v>
       </c>
       <c r="D7" t="s">
-        <v>1703</v>
+        <v>1741</v>
       </c>
       <c r="E7" t="s">
-        <v>1704</v>
+        <v>1742</v>
       </c>
       <c r="F7" t="s">
-        <v>1705</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>1706</v>
+        <v>1744</v>
       </c>
       <c r="B8" t="s">
-        <v>1707</v>
+        <v>1745</v>
       </c>
       <c r="C8" t="s">
-        <v>1708</v>
+        <v>1746</v>
       </c>
       <c r="D8" t="s">
-        <v>1709</v>
+        <v>1747</v>
       </c>
       <c r="E8" t="s">
-        <v>1710</v>
+        <v>1748</v>
       </c>
       <c r="F8" t="s">
         <v>629</v>
@@ -20473,19 +20935,19 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>1711</v>
+        <v>1749</v>
       </c>
       <c r="B9" t="s">
-        <v>1712</v>
+        <v>1750</v>
       </c>
       <c r="C9" t="s">
-        <v>1713</v>
+        <v>1751</v>
       </c>
       <c r="D9" t="s">
-        <v>1714</v>
+        <v>1752</v>
       </c>
       <c r="E9" t="s">
-        <v>1715</v>
+        <v>1753</v>
       </c>
       <c r="F9" t="s">
         <v>369</v>
@@ -20493,39 +20955,39 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>1716</v>
+        <v>1754</v>
       </c>
       <c r="B10" t="s">
-        <v>1717</v>
+        <v>1755</v>
       </c>
       <c r="C10" t="s">
-        <v>1718</v>
+        <v>1756</v>
       </c>
       <c r="D10" t="s">
-        <v>1719</v>
+        <v>1757</v>
       </c>
       <c r="E10" t="s">
-        <v>1720</v>
+        <v>1758</v>
       </c>
       <c r="F10" t="s">
-        <v>1721</v>
+        <v>1759</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>1722</v>
+        <v>1760</v>
       </c>
       <c r="B11" t="s">
-        <v>1723</v>
+        <v>1761</v>
       </c>
       <c r="C11" t="s">
-        <v>1724</v>
+        <v>1762</v>
       </c>
       <c r="D11" t="s">
-        <v>1725</v>
+        <v>1763</v>
       </c>
       <c r="E11" t="s">
-        <v>1726</v>
+        <v>1764</v>
       </c>
       <c r="F11" t="s">
         <v>47</v>
@@ -20533,99 +20995,99 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>1727</v>
+        <v>1765</v>
       </c>
       <c r="B12" t="s">
-        <v>1728</v>
+        <v>1766</v>
       </c>
       <c r="C12" t="s">
-        <v>1729</v>
+        <v>1767</v>
       </c>
       <c r="D12" t="s">
-        <v>1730</v>
+        <v>1768</v>
       </c>
       <c r="E12" t="s">
-        <v>1731</v>
+        <v>1769</v>
       </c>
       <c r="F12" t="s">
-        <v>1732</v>
+        <v>1770</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>1733</v>
+        <v>1771</v>
       </c>
       <c r="B13" t="s">
-        <v>1734</v>
+        <v>1772</v>
       </c>
       <c r="C13" t="s">
-        <v>1735</v>
+        <v>1773</v>
       </c>
       <c r="D13" t="s">
-        <v>1736</v>
+        <v>1774</v>
       </c>
       <c r="E13" t="s">
-        <v>1737</v>
+        <v>1775</v>
       </c>
       <c r="F13" t="s">
-        <v>1738</v>
+        <v>1776</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>1739</v>
+        <v>1777</v>
       </c>
       <c r="B14" t="s">
-        <v>1740</v>
+        <v>1778</v>
       </c>
       <c r="C14" t="s">
-        <v>1741</v>
+        <v>1779</v>
       </c>
       <c r="D14" t="s">
-        <v>1742</v>
+        <v>1780</v>
       </c>
       <c r="E14" t="s">
-        <v>1743</v>
+        <v>1781</v>
       </c>
       <c r="F14" t="s">
-        <v>1744</v>
+        <v>1782</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>1745</v>
+        <v>1783</v>
       </c>
       <c r="B15" t="s">
-        <v>1746</v>
+        <v>1784</v>
       </c>
       <c r="C15" t="s">
-        <v>1747</v>
+        <v>1785</v>
       </c>
       <c r="D15" t="s">
-        <v>1748</v>
+        <v>1786</v>
       </c>
       <c r="E15" t="s">
-        <v>1749</v>
+        <v>1787</v>
       </c>
       <c r="F15" t="s">
-        <v>1750</v>
+        <v>1788</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>1751</v>
+        <v>1789</v>
       </c>
       <c r="B16" t="s">
-        <v>1752</v>
+        <v>1790</v>
       </c>
       <c r="C16" t="s">
-        <v>1753</v>
+        <v>1791</v>
       </c>
       <c r="D16" t="s">
-        <v>1754</v>
+        <v>1792</v>
       </c>
       <c r="E16" t="s">
-        <v>1755</v>
+        <v>1793</v>
       </c>
       <c r="F16" t="s">
         <v>207</v>
@@ -20633,19 +21095,19 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>1756</v>
+        <v>1794</v>
       </c>
       <c r="B17" t="s">
-        <v>1757</v>
+        <v>1795</v>
       </c>
       <c r="C17" t="s">
-        <v>1758</v>
+        <v>1796</v>
       </c>
       <c r="D17" t="s">
-        <v>1759</v>
+        <v>1797</v>
       </c>
       <c r="E17" t="s">
-        <v>1760</v>
+        <v>1798</v>
       </c>
       <c r="F17" t="s">
         <v>378</v>
@@ -20667,7 +21129,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>1761</v>
+        <v>1799</v>
       </c>
       <c r="B1"/>
       <c r="C1"/>
@@ -20677,7 +21139,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1762</v>
+        <v>1800</v>
       </c>
       <c r="B2"/>
       <c r="C2"/>
@@ -20687,162 +21149,162 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1763</v>
+        <v>1801</v>
       </c>
       <c r="B4" t="s">
-        <v>1661</v>
+        <v>1699</v>
       </c>
       <c r="C4" t="s">
-        <v>1764</v>
+        <v>1802</v>
       </c>
       <c r="D4" t="s">
-        <v>1765</v>
+        <v>1803</v>
       </c>
       <c r="E4" t="s">
-        <v>1304</v>
+        <v>1340</v>
       </c>
       <c r="F4" t="s">
-        <v>1766</v>
+        <v>1804</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1307</v>
+        <v>1343</v>
       </c>
       <c r="B5" t="s">
-        <v>1767</v>
+        <v>1805</v>
       </c>
       <c r="C5" t="s">
-        <v>1768</v>
+        <v>1806</v>
       </c>
       <c r="D5" t="s">
-        <v>1769</v>
+        <v>1807</v>
       </c>
       <c r="E5" t="s">
-        <v>1770</v>
+        <v>1808</v>
       </c>
       <c r="F5" t="s">
-        <v>1771</v>
+        <v>1809</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>1312</v>
+        <v>1348</v>
       </c>
       <c r="B6" t="s">
-        <v>1772</v>
+        <v>1810</v>
       </c>
       <c r="C6" t="s">
-        <v>1773</v>
+        <v>1811</v>
       </c>
       <c r="D6" t="s">
-        <v>1774</v>
+        <v>1812</v>
       </c>
       <c r="E6" t="s">
-        <v>1775</v>
+        <v>1813</v>
       </c>
       <c r="F6" t="s">
-        <v>1771</v>
+        <v>1809</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>1316</v>
+        <v>1352</v>
       </c>
       <c r="B7" t="s">
-        <v>1776</v>
+        <v>1814</v>
       </c>
       <c r="C7" t="s">
-        <v>1777</v>
+        <v>1815</v>
       </c>
       <c r="D7" t="s">
-        <v>1778</v>
+        <v>1816</v>
       </c>
       <c r="E7" t="s">
-        <v>1779</v>
+        <v>1817</v>
       </c>
       <c r="F7" t="s">
-        <v>1771</v>
+        <v>1809</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>1320</v>
+        <v>1356</v>
       </c>
       <c r="B8" t="s">
-        <v>1780</v>
+        <v>1818</v>
       </c>
       <c r="C8" t="s">
-        <v>1781</v>
+        <v>1819</v>
       </c>
       <c r="D8" t="s">
-        <v>1782</v>
+        <v>1820</v>
       </c>
       <c r="E8" t="s">
-        <v>1783</v>
+        <v>1821</v>
       </c>
       <c r="F8" t="s">
-        <v>1771</v>
+        <v>1809</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>1324</v>
+        <v>1360</v>
       </c>
       <c r="B9" t="s">
-        <v>1784</v>
+        <v>1822</v>
       </c>
       <c r="C9" t="s">
-        <v>1785</v>
+        <v>1823</v>
       </c>
       <c r="D9" t="s">
-        <v>1786</v>
+        <v>1824</v>
       </c>
       <c r="E9" t="s">
         <v>877</v>
       </c>
       <c r="F9" t="s">
-        <v>1787</v>
+        <v>1825</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>1328</v>
+        <v>1364</v>
       </c>
       <c r="B10" t="s">
-        <v>1788</v>
+        <v>1826</v>
       </c>
       <c r="C10" t="s">
-        <v>1789</v>
+        <v>1827</v>
       </c>
       <c r="D10" t="s">
-        <v>1790</v>
+        <v>1828</v>
       </c>
       <c r="E10" t="s">
-        <v>1791</v>
+        <v>1829</v>
       </c>
       <c r="F10" t="s">
-        <v>1787</v>
+        <v>1825</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>1332</v>
+        <v>1368</v>
       </c>
       <c r="B11" t="s">
-        <v>1792</v>
+        <v>1830</v>
       </c>
       <c r="C11" t="s">
-        <v>1793</v>
+        <v>1831</v>
       </c>
       <c r="D11" t="s">
-        <v>1794</v>
+        <v>1832</v>
       </c>
       <c r="E11" t="s">
-        <v>1795</v>
+        <v>1833</v>
       </c>
       <c r="F11" t="s">
-        <v>1796</v>
+        <v>1834</v>
       </c>
     </row>
   </sheetData>

--- a/audits/FORTLESS_MASTER_SECURITY_UI_BUG_TRACKER.xlsx
+++ b/audits/FORTLESS_MASTER_SECURITY_UI_BUG_TRACKER.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5920" uniqueCount="2082">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5940" uniqueCount="2088">
   <si>
     <t>FORTLESS   /   ENGINEERING FINDINGS REGISTER</t>
   </si>
@@ -3468,6 +3468,9 @@
     <t>Reinstall completion is inferred from the first running/offline reading, which can precede the real install start</t>
   </si>
   <si>
+    <t>9802654</t>
+  </si>
+  <si>
     <t>src/modules/provisioning/runtime-sync.ts:51-58,73-105</t>
   </si>
   <si>
@@ -3483,7 +3486,7 @@
     <t>Test: with a mocked panel that reports offline for 30 s before installation begins, the state stays INSTALLING until the install flag clears.</t>
   </si>
   <si>
-    <t>[CONFIRMED_CODE] Source trace; behaviour against a real panel is TEST_NEEDED. | REMEDIATION ea7fa6d: Reinstall completion now waits for the panel install flag (adapter reports installing/installFailed; failed install -&gt; ERROR). Test: tests/sync.test.ts 'NEW-392'. Panel behaviour itself still needs a staging reinstall.</t>
+    <t>[CONFIRMED_CODE] Source trace; behaviour against a real panel is TEST_NEEDED. | REMEDIATION ea7fa6d: Reinstall completion now waits for the panel install flag (adapter reports installing/installFailed; failed install -&gt; ERROR). Test: tests/sync.test.ts 'NEW-392'. Panel behaviour itself still needs a staging reinstall. | REMEDIATION 9802654: [SANDBOX_VERIFIED] test panel, 2026-10-19 (npm run test:sandbox:panel, 8/8): a freshly created server reports the install flag while installing and it clears when the install ends; the flag is read through the app's own adapter.</t>
   </si>
   <si>
     <t>NEW-393</t>
@@ -3609,7 +3612,7 @@
     <t>Test: with an empty allowlist the endpoint returns 503; concurrent mints for one account yield one valid key.</t>
   </si>
   <si>
-    <t>[CONFIRMED_CODE] Source trace of the repo copy; panel configuration is CONFIG_DEPENDENT. | REMEDIATION ea7fa6d: Key mint serialized per account (concurrent callers share one mint; tests/console.test.ts 'NEW-397') and the panel patch refuses to mint when FORTLESS_KEYMINT_ALLOWED_IPS is empty. Needs deployment of patched panel-sso files.</t>
+    <t>[CONFIRMED_CODE] Source trace of the repo copy; panel configuration is CONFIG_DEPENDENT. | REMEDIATION ea7fa6d: Key mint serialized per account (concurrent callers share one mint; tests/console.test.ts 'NEW-397') and the panel patch refuses to mint when FORTLESS_KEYMINT_ALLOWED_IPS is empty. Needs deployment of patched panel-sso files. | REMEDIATION 9802654: [SANDBOX_VERIFIED] test panel: key mint returns a client key, a second mint replaces it and the old key is rejected; the new key lists files, returns console credentials and round-trips a file write/read/delete. Concurrent-mint serialisation is covered by tests/console.test.ts.</t>
   </si>
   <si>
     <t>NEW-398</t>
@@ -4821,6 +4824,15 @@
     <t>1 findings updated with code and tests; statuses follow the workbook rules (TESTED needs passing local tests, NEEDS_VERIFICATION needs real infrastructure).</t>
   </si>
   <si>
+    <t>2026-10-19 14:46</t>
+  </si>
+  <si>
+    <t>Test-panel sandbox evidence for NEW-392 and NEW-397</t>
+  </si>
+  <si>
+    <t>2 findings updated with code and tests; statuses follow the workbook rules (TESTED needs passing local tests, NEEDS_VERIFICATION needs real infrastructure).</t>
+  </si>
+  <si>
     <t>FORTLESS   /   IMMUTABLE STATUS HISTORY</t>
   </si>
   <si>
@@ -5647,6 +5659,12 @@
   </si>
   <si>
     <t>[PRODUCTION_VERIFIED, read-only] 2026-10-19 curl -I https://fortless.net/ and /login: CSP (script-src by hash, object-src none, frame-ancestors self), HSTS, nosniff, COOP, Permissions-Policy, X-Frame-Options and no-store on the login page are served at the edge. Leftover: nosniff and Referrer-Policy are sent twice with conflicting Referrer-Policy values (strict-origin-when-cross-origin from the app, same-origin from the edge); remove the edge copy.</t>
+  </si>
+  <si>
+    <t>[SANDBOX_VERIFIED] test panel, 2026-10-19 (npm run test:sandbox:panel, 8/8): a freshly created server reports the install flag while installing and it clears when the install ends; the flag is read through the app's own adapter.</t>
+  </si>
+  <si>
+    <t>[SANDBOX_VERIFIED] test panel: key mint returns a client key, a second mint replaces it and the old key is rejected; the new key lists files, returns console credentials and round-trips a file write/read/delete. Concurrent-mint serialisation is covered by tests/console.test.ts.</t>
   </si>
   <si>
     <t>FORTLESS   /   PRODUCT IDEAS (NOT BUGS)</t>
@@ -14595,22 +14613,22 @@
         <v>1116</v>
       </c>
       <c r="J140" t="s">
-        <v>1107</v>
+        <v>1149</v>
       </c>
       <c r="K140" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="L140" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="M140" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="N140" t="s">
-        <v>1152</v>
+        <v>1153</v>
       </c>
       <c r="O140" t="s">
-        <v>1153</v>
+        <v>1154</v>
       </c>
       <c r="P140" t="s">
         <v>755</v>
@@ -14622,12 +14640,12 @@
         <v>36</v>
       </c>
       <c r="S140" t="s">
-        <v>1154</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="141" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="B141" t="s">
         <v>313</v>
@@ -14639,7 +14657,7 @@
         <v>637</v>
       </c>
       <c r="E141" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="F141" t="s">
         <v>86</v>
@@ -14657,19 +14675,19 @@
         <v>899</v>
       </c>
       <c r="K141" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="L141" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="M141" t="s">
-        <v>1159</v>
+        <v>1160</v>
       </c>
       <c r="N141" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="O141" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="P141" t="s">
         <v>755</v>
@@ -14681,12 +14699,12 @@
         <v>36</v>
       </c>
       <c r="S141" t="s">
-        <v>1162</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="142" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="B142" t="s">
         <v>313</v>
@@ -14698,7 +14716,7 @@
         <v>24</v>
       </c>
       <c r="E142" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="F142" t="s">
         <v>26</v>
@@ -14710,25 +14728,25 @@
         <v>27</v>
       </c>
       <c r="I142" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="J142" t="s">
         <v>800</v>
       </c>
       <c r="K142" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="L142" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="M142" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="N142" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="O142" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="P142" t="s">
         <v>755</v>
@@ -14740,12 +14758,12 @@
         <v>36</v>
       </c>
       <c r="S142" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="143" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="B143" t="s">
         <v>313</v>
@@ -14757,7 +14775,7 @@
         <v>24</v>
       </c>
       <c r="E143" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="F143" t="s">
         <v>26</v>
@@ -14769,25 +14787,25 @@
         <v>27</v>
       </c>
       <c r="I143" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="J143" t="s">
         <v>899</v>
       </c>
       <c r="K143" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="L143" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="M143" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="N143" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="O143" t="s">
-        <v>1178</v>
+        <v>1179</v>
       </c>
       <c r="P143" t="s">
         <v>755</v>
@@ -14799,12 +14817,12 @@
         <v>36</v>
       </c>
       <c r="S143" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="144" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>1180</v>
+        <v>1181</v>
       </c>
       <c r="B144" t="s">
         <v>61</v>
@@ -14816,7 +14834,7 @@
         <v>441</v>
       </c>
       <c r="E144" t="s">
-        <v>1181</v>
+        <v>1182</v>
       </c>
       <c r="F144" t="s">
         <v>86</v>
@@ -14828,25 +14846,25 @@
         <v>27</v>
       </c>
       <c r="I144" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="J144" t="s">
         <v>87</v>
       </c>
       <c r="K144" t="s">
-        <v>1183</v>
+        <v>1184</v>
       </c>
       <c r="L144" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="M144" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="N144" t="s">
-        <v>1186</v>
+        <v>1187</v>
       </c>
       <c r="O144" t="s">
-        <v>1187</v>
+        <v>1188</v>
       </c>
       <c r="P144" t="s">
         <v>755</v>
@@ -14858,12 +14876,12 @@
         <v>36</v>
       </c>
       <c r="S144" t="s">
-        <v>1188</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="145" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="B145" t="s">
         <v>313</v>
@@ -14875,7 +14893,7 @@
         <v>441</v>
       </c>
       <c r="E145" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
       <c r="F145" t="s">
         <v>26</v>
@@ -14887,25 +14905,25 @@
         <v>27</v>
       </c>
       <c r="I145" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="J145" t="s">
-        <v>1107</v>
+        <v>1149</v>
       </c>
       <c r="K145" t="s">
-        <v>1191</v>
+        <v>1192</v>
       </c>
       <c r="L145" t="s">
-        <v>1192</v>
+        <v>1193</v>
       </c>
       <c r="M145" t="s">
-        <v>1193</v>
+        <v>1194</v>
       </c>
       <c r="N145" t="s">
-        <v>1194</v>
+        <v>1195</v>
       </c>
       <c r="O145" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="P145" t="s">
         <v>755</v>
@@ -14917,12 +14935,12 @@
         <v>36</v>
       </c>
       <c r="S145" t="s">
-        <v>1196</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="146" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>1197</v>
+        <v>1198</v>
       </c>
       <c r="B146" t="s">
         <v>313</v>
@@ -14931,10 +14949,10 @@
         <v>62</v>
       </c>
       <c r="D146" t="s">
-        <v>1198</v>
+        <v>1199</v>
       </c>
       <c r="E146" t="s">
-        <v>1199</v>
+        <v>1200</v>
       </c>
       <c r="F146" t="s">
         <v>26</v>
@@ -14946,25 +14964,25 @@
         <v>27</v>
       </c>
       <c r="I146" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="J146" t="s">
         <v>800</v>
       </c>
       <c r="K146" t="s">
-        <v>1200</v>
+        <v>1201</v>
       </c>
       <c r="L146" t="s">
-        <v>1201</v>
+        <v>1202</v>
       </c>
       <c r="M146" t="s">
-        <v>1202</v>
+        <v>1203</v>
       </c>
       <c r="N146" t="s">
-        <v>1203</v>
+        <v>1204</v>
       </c>
       <c r="O146" t="s">
-        <v>1204</v>
+        <v>1205</v>
       </c>
       <c r="P146" t="s">
         <v>755</v>
@@ -14976,12 +14994,12 @@
         <v>36</v>
       </c>
       <c r="S146" t="s">
-        <v>1205</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="147" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>1206</v>
+        <v>1207</v>
       </c>
       <c r="B147" t="s">
         <v>313</v>
@@ -14993,7 +15011,7 @@
         <v>637</v>
       </c>
       <c r="E147" t="s">
-        <v>1207</v>
+        <v>1208</v>
       </c>
       <c r="F147" t="s">
         <v>26</v>
@@ -15005,25 +15023,25 @@
         <v>27</v>
       </c>
       <c r="I147" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="J147" t="s">
         <v>899</v>
       </c>
       <c r="K147" t="s">
-        <v>1208</v>
+        <v>1209</v>
       </c>
       <c r="L147" t="s">
-        <v>1209</v>
+        <v>1210</v>
       </c>
       <c r="M147" t="s">
-        <v>1210</v>
+        <v>1211</v>
       </c>
       <c r="N147" t="s">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="O147" t="s">
-        <v>1212</v>
+        <v>1213</v>
       </c>
       <c r="P147" t="s">
         <v>755</v>
@@ -15035,12 +15053,12 @@
         <v>36</v>
       </c>
       <c r="S147" t="s">
-        <v>1213</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="148" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>1214</v>
+        <v>1215</v>
       </c>
       <c r="B148" t="s">
         <v>313</v>
@@ -15052,7 +15070,7 @@
         <v>24</v>
       </c>
       <c r="E148" t="s">
-        <v>1215</v>
+        <v>1216</v>
       </c>
       <c r="F148" t="s">
         <v>26</v>
@@ -15064,25 +15082,25 @@
         <v>27</v>
       </c>
       <c r="I148" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="J148" t="s">
         <v>899</v>
       </c>
       <c r="K148" t="s">
-        <v>1216</v>
+        <v>1217</v>
       </c>
       <c r="L148" t="s">
-        <v>1217</v>
+        <v>1218</v>
       </c>
       <c r="M148" t="s">
-        <v>1218</v>
+        <v>1219</v>
       </c>
       <c r="N148" t="s">
-        <v>1219</v>
+        <v>1220</v>
       </c>
       <c r="O148" t="s">
-        <v>1220</v>
+        <v>1221</v>
       </c>
       <c r="P148" t="s">
         <v>755</v>
@@ -15094,12 +15112,12 @@
         <v>36</v>
       </c>
       <c r="S148" t="s">
-        <v>1221</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="149" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>1222</v>
+        <v>1223</v>
       </c>
       <c r="B149" t="s">
         <v>313</v>
@@ -15111,7 +15129,7 @@
         <v>1072</v>
       </c>
       <c r="E149" t="s">
-        <v>1223</v>
+        <v>1224</v>
       </c>
       <c r="F149" t="s">
         <v>26</v>
@@ -15123,25 +15141,25 @@
         <v>27</v>
       </c>
       <c r="I149" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="J149" t="s">
         <v>899</v>
       </c>
       <c r="K149" t="s">
-        <v>1224</v>
+        <v>1225</v>
       </c>
       <c r="L149" t="s">
-        <v>1225</v>
+        <v>1226</v>
       </c>
       <c r="M149" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
       <c r="N149" t="s">
-        <v>1227</v>
+        <v>1228</v>
       </c>
       <c r="O149" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
       <c r="P149" t="s">
         <v>755</v>
@@ -15153,12 +15171,12 @@
         <v>36</v>
       </c>
       <c r="S149" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="150" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>1230</v>
+        <v>1231</v>
       </c>
       <c r="B150" t="s">
         <v>313</v>
@@ -15170,7 +15188,7 @@
         <v>973</v>
       </c>
       <c r="E150" t="s">
-        <v>1231</v>
+        <v>1232</v>
       </c>
       <c r="F150" t="s">
         <v>26</v>
@@ -15182,25 +15200,25 @@
         <v>27</v>
       </c>
       <c r="I150" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="J150" t="s">
         <v>899</v>
       </c>
       <c r="K150" t="s">
-        <v>1232</v>
+        <v>1233</v>
       </c>
       <c r="L150" t="s">
-        <v>1233</v>
+        <v>1234</v>
       </c>
       <c r="M150" t="s">
-        <v>1234</v>
+        <v>1235</v>
       </c>
       <c r="N150" t="s">
-        <v>1235</v>
+        <v>1236</v>
       </c>
       <c r="O150" t="s">
-        <v>1236</v>
+        <v>1237</v>
       </c>
       <c r="P150" t="s">
         <v>755</v>
@@ -15212,12 +15230,12 @@
         <v>36</v>
       </c>
       <c r="S150" t="s">
-        <v>1237</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="151" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>1238</v>
+        <v>1239</v>
       </c>
       <c r="B151" t="s">
         <v>61</v>
@@ -15229,7 +15247,7 @@
         <v>575</v>
       </c>
       <c r="E151" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
       <c r="F151" t="s">
         <v>26</v>
@@ -15241,25 +15259,25 @@
         <v>27</v>
       </c>
       <c r="I151" t="s">
-        <v>1240</v>
+        <v>1241</v>
       </c>
       <c r="J151" t="s">
         <v>260</v>
       </c>
       <c r="K151" t="s">
-        <v>1241</v>
+        <v>1242</v>
       </c>
       <c r="L151" t="s">
-        <v>1242</v>
+        <v>1243</v>
       </c>
       <c r="M151" t="s">
-        <v>1243</v>
+        <v>1244</v>
       </c>
       <c r="N151" t="s">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="O151" t="s">
-        <v>1245</v>
+        <v>1246</v>
       </c>
       <c r="P151" t="s">
         <v>755</v>
@@ -15271,12 +15289,12 @@
         <v>36</v>
       </c>
       <c r="S151" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="152" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>1247</v>
+        <v>1248</v>
       </c>
       <c r="B152" t="s">
         <v>61</v>
@@ -15288,7 +15306,7 @@
         <v>637</v>
       </c>
       <c r="E152" t="s">
-        <v>1248</v>
+        <v>1249</v>
       </c>
       <c r="F152" t="s">
         <v>26</v>
@@ -15300,25 +15318,25 @@
         <v>27</v>
       </c>
       <c r="I152" t="s">
-        <v>1240</v>
+        <v>1241</v>
       </c>
       <c r="J152" t="s">
         <v>260</v>
       </c>
       <c r="K152" t="s">
-        <v>1249</v>
+        <v>1250</v>
       </c>
       <c r="L152" t="s">
-        <v>1250</v>
+        <v>1251</v>
       </c>
       <c r="M152" t="s">
-        <v>1251</v>
+        <v>1252</v>
       </c>
       <c r="N152" t="s">
-        <v>1252</v>
+        <v>1253</v>
       </c>
       <c r="O152" t="s">
-        <v>1253</v>
+        <v>1254</v>
       </c>
       <c r="P152" t="s">
         <v>755</v>
@@ -15330,12 +15348,12 @@
         <v>36</v>
       </c>
       <c r="S152" t="s">
-        <v>1254</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="153" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
       <c r="B153" t="s">
         <v>313</v>
@@ -15347,7 +15365,7 @@
         <v>973</v>
       </c>
       <c r="E153" t="s">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="F153" t="s">
         <v>26</v>
@@ -15359,25 +15377,25 @@
         <v>27</v>
       </c>
       <c r="I153" t="s">
-        <v>1240</v>
+        <v>1241</v>
       </c>
       <c r="J153" t="s">
         <v>899</v>
       </c>
       <c r="K153" t="s">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="L153" t="s">
-        <v>1258</v>
+        <v>1259</v>
       </c>
       <c r="M153" t="s">
-        <v>1259</v>
+        <v>1260</v>
       </c>
       <c r="N153" t="s">
-        <v>1260</v>
+        <v>1261</v>
       </c>
       <c r="O153" t="s">
-        <v>1261</v>
+        <v>1262</v>
       </c>
       <c r="P153" t="s">
         <v>755</v>
@@ -15389,12 +15407,12 @@
         <v>36</v>
       </c>
       <c r="S153" t="s">
-        <v>1262</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="154" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>1263</v>
+        <v>1264</v>
       </c>
       <c r="B154" t="s">
         <v>313</v>
@@ -15406,7 +15424,7 @@
         <v>1097</v>
       </c>
       <c r="E154" t="s">
-        <v>1264</v>
+        <v>1265</v>
       </c>
       <c r="F154" t="s">
         <v>26</v>
@@ -15418,25 +15436,25 @@
         <v>27</v>
       </c>
       <c r="I154" t="s">
-        <v>1240</v>
+        <v>1241</v>
       </c>
       <c r="J154" t="s">
         <v>899</v>
       </c>
       <c r="K154" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="L154" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="M154" t="s">
-        <v>1267</v>
+        <v>1268</v>
       </c>
       <c r="N154" t="s">
-        <v>1268</v>
+        <v>1269</v>
       </c>
       <c r="O154" t="s">
-        <v>1269</v>
+        <v>1270</v>
       </c>
       <c r="P154" t="s">
         <v>755</v>
@@ -15448,12 +15466,12 @@
         <v>36</v>
       </c>
       <c r="S154" t="s">
-        <v>1270</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="155" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>1271</v>
+        <v>1272</v>
       </c>
       <c r="B155" t="s">
         <v>313</v>
@@ -15465,7 +15483,7 @@
         <v>1072</v>
       </c>
       <c r="E155" t="s">
-        <v>1272</v>
+        <v>1273</v>
       </c>
       <c r="F155" t="s">
         <v>26</v>
@@ -15477,25 +15495,25 @@
         <v>27</v>
       </c>
       <c r="I155" t="s">
-        <v>1240</v>
+        <v>1241</v>
       </c>
       <c r="J155" t="s">
         <v>899</v>
       </c>
       <c r="K155" t="s">
-        <v>1273</v>
+        <v>1274</v>
       </c>
       <c r="L155" t="s">
-        <v>1274</v>
+        <v>1275</v>
       </c>
       <c r="M155" t="s">
-        <v>1275</v>
+        <v>1276</v>
       </c>
       <c r="N155" t="s">
-        <v>1276</v>
+        <v>1277</v>
       </c>
       <c r="O155" t="s">
-        <v>1277</v>
+        <v>1278</v>
       </c>
       <c r="P155" t="s">
         <v>755</v>
@@ -15507,12 +15525,12 @@
         <v>36</v>
       </c>
       <c r="S155" t="s">
-        <v>1278</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="156" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>1279</v>
+        <v>1280</v>
       </c>
       <c r="B156" t="s">
         <v>313</v>
@@ -15524,7 +15542,7 @@
         <v>637</v>
       </c>
       <c r="E156" t="s">
-        <v>1280</v>
+        <v>1281</v>
       </c>
       <c r="F156" t="s">
         <v>459</v>
@@ -15536,25 +15554,25 @@
         <v>27</v>
       </c>
       <c r="I156" t="s">
-        <v>1240</v>
+        <v>1241</v>
       </c>
       <c r="J156" t="s">
-        <v>1240</v>
+        <v>1241</v>
       </c>
       <c r="K156" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="L156" t="s">
-        <v>1282</v>
+        <v>1283</v>
       </c>
       <c r="M156" t="s">
-        <v>1283</v>
+        <v>1284</v>
       </c>
       <c r="N156" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="O156" t="s">
-        <v>1285</v>
+        <v>1286</v>
       </c>
       <c r="P156" t="s">
         <v>755</v>
@@ -15566,12 +15584,12 @@
         <v>36</v>
       </c>
       <c r="S156" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="157" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>1287</v>
+        <v>1288</v>
       </c>
       <c r="B157" t="s">
         <v>61</v>
@@ -15583,7 +15601,7 @@
         <v>637</v>
       </c>
       <c r="E157" t="s">
-        <v>1288</v>
+        <v>1289</v>
       </c>
       <c r="F157" t="s">
         <v>86</v>
@@ -15595,25 +15613,25 @@
         <v>27</v>
       </c>
       <c r="I157" t="s">
-        <v>1240</v>
+        <v>1241</v>
       </c>
       <c r="J157" t="s">
         <v>260</v>
       </c>
       <c r="K157" t="s">
-        <v>1289</v>
+        <v>1290</v>
       </c>
       <c r="L157" t="s">
-        <v>1290</v>
+        <v>1291</v>
       </c>
       <c r="M157" t="s">
-        <v>1291</v>
+        <v>1292</v>
       </c>
       <c r="N157" t="s">
-        <v>1292</v>
+        <v>1293</v>
       </c>
       <c r="O157" t="s">
-        <v>1293</v>
+        <v>1294</v>
       </c>
       <c r="P157" t="s">
         <v>755</v>
@@ -15625,12 +15643,12 @@
         <v>36</v>
       </c>
       <c r="S157" t="s">
-        <v>1294</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="158" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>1295</v>
+        <v>1296</v>
       </c>
       <c r="B158" t="s">
         <v>313</v>
@@ -15639,10 +15657,10 @@
         <v>314</v>
       </c>
       <c r="D158" t="s">
-        <v>1296</v>
+        <v>1297</v>
       </c>
       <c r="E158" t="s">
-        <v>1297</v>
+        <v>1298</v>
       </c>
       <c r="F158" t="s">
         <v>26</v>
@@ -15654,25 +15672,25 @@
         <v>27</v>
       </c>
       <c r="I158" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="J158" t="s">
         <v>899</v>
       </c>
       <c r="K158" t="s">
-        <v>1299</v>
+        <v>1300</v>
       </c>
       <c r="L158" t="s">
-        <v>1300</v>
+        <v>1301</v>
       </c>
       <c r="M158" t="s">
-        <v>1301</v>
+        <v>1302</v>
       </c>
       <c r="N158" t="s">
-        <v>1302</v>
+        <v>1303</v>
       </c>
       <c r="O158" t="s">
-        <v>1303</v>
+        <v>1304</v>
       </c>
       <c r="P158" t="s">
         <v>755</v>
@@ -15684,12 +15702,12 @@
         <v>36</v>
       </c>
       <c r="S158" t="s">
-        <v>1304</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="159" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>1305</v>
+        <v>1306</v>
       </c>
       <c r="B159" t="s">
         <v>313</v>
@@ -15698,10 +15716,10 @@
         <v>62</v>
       </c>
       <c r="D159" t="s">
-        <v>1296</v>
+        <v>1297</v>
       </c>
       <c r="E159" t="s">
-        <v>1306</v>
+        <v>1307</v>
       </c>
       <c r="F159" t="s">
         <v>26</v>
@@ -15713,25 +15731,25 @@
         <v>27</v>
       </c>
       <c r="I159" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="J159" t="s">
         <v>899</v>
       </c>
       <c r="K159" t="s">
-        <v>1307</v>
+        <v>1308</v>
       </c>
       <c r="L159" t="s">
-        <v>1308</v>
+        <v>1309</v>
       </c>
       <c r="M159" t="s">
-        <v>1309</v>
+        <v>1310</v>
       </c>
       <c r="N159" t="s">
-        <v>1310</v>
+        <v>1311</v>
       </c>
       <c r="O159" t="s">
-        <v>1311</v>
+        <v>1312</v>
       </c>
       <c r="P159" t="s">
         <v>755</v>
@@ -15743,12 +15761,12 @@
         <v>36</v>
       </c>
       <c r="S159" t="s">
-        <v>1312</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="160" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>1313</v>
+        <v>1314</v>
       </c>
       <c r="B160" t="s">
         <v>313</v>
@@ -15760,7 +15778,7 @@
         <v>216</v>
       </c>
       <c r="E160" t="s">
-        <v>1314</v>
+        <v>1315</v>
       </c>
       <c r="F160" t="s">
         <v>26</v>
@@ -15772,25 +15790,25 @@
         <v>27</v>
       </c>
       <c r="I160" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="J160" t="s">
         <v>899</v>
       </c>
       <c r="K160" t="s">
-        <v>1315</v>
+        <v>1316</v>
       </c>
       <c r="L160" t="s">
-        <v>1316</v>
+        <v>1317</v>
       </c>
       <c r="M160" t="s">
-        <v>1317</v>
+        <v>1318</v>
       </c>
       <c r="N160" t="s">
-        <v>1318</v>
+        <v>1319</v>
       </c>
       <c r="O160" t="s">
-        <v>1319</v>
+        <v>1320</v>
       </c>
       <c r="P160" t="s">
         <v>755</v>
@@ -15802,12 +15820,12 @@
         <v>36</v>
       </c>
       <c r="S160" t="s">
-        <v>1320</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="161" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>1321</v>
+        <v>1322</v>
       </c>
       <c r="B161" t="s">
         <v>313</v>
@@ -15816,10 +15834,10 @@
         <v>62</v>
       </c>
       <c r="D161" t="s">
-        <v>1322</v>
+        <v>1323</v>
       </c>
       <c r="E161" t="s">
-        <v>1323</v>
+        <v>1324</v>
       </c>
       <c r="F161" t="s">
         <v>86</v>
@@ -15831,25 +15849,25 @@
         <v>27</v>
       </c>
       <c r="I161" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="J161" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="K161" t="s">
-        <v>1324</v>
+        <v>1325</v>
       </c>
       <c r="L161" t="s">
-        <v>1325</v>
+        <v>1326</v>
       </c>
       <c r="M161" t="s">
-        <v>1326</v>
+        <v>1327</v>
       </c>
       <c r="N161" t="s">
-        <v>1327</v>
+        <v>1328</v>
       </c>
       <c r="O161" t="s">
-        <v>1328</v>
+        <v>1329</v>
       </c>
       <c r="P161" t="s">
         <v>755</v>
@@ -15861,7 +15879,7 @@
         <v>36</v>
       </c>
       <c r="S161" t="s">
-        <v>1329</v>
+        <v>1330</v>
       </c>
     </row>
   </sheetData>
@@ -15875,48 +15893,48 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>1330</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1331</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1332</v>
+        <v>1333</v>
       </c>
       <c r="C4" t="s">
-        <v>1333</v>
+        <v>1334</v>
       </c>
       <c r="E4" t="s">
-        <v>1334</v>
+        <v>1335</v>
       </c>
       <c r="G4" t="s">
-        <v>1335</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1336</v>
+        <v>1337</v>
       </c>
       <c r="C5" t="s">
-        <v>1337</v>
+        <v>1338</v>
       </c>
       <c r="E5" t="s">
-        <v>1338</v>
+        <v>1339</v>
       </c>
       <c r="G5" t="s">
-        <v>1339</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>1340</v>
+        <v>1341</v>
       </c>
       <c r="F9" t="s">
-        <v>1341</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -15924,16 +15942,16 @@
         <v>115</v>
       </c>
       <c r="B10" t="s">
-        <v>1337</v>
+        <v>1338</v>
       </c>
       <c r="C10" t="s">
         <v>3</v>
       </c>
       <c r="D10" t="s">
-        <v>1342</v>
+        <v>1343</v>
       </c>
       <c r="F10" t="s">
-        <v>1343</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -15941,13 +15959,13 @@
         <v>109</v>
       </c>
       <c r="B11" t="s">
-        <v>1338</v>
+        <v>1339</v>
       </c>
       <c r="C11" t="s">
         <v>22</v>
       </c>
       <c r="D11" t="s">
-        <v>1344</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -15955,13 +15973,13 @@
         <v>86</v>
       </c>
       <c r="B12" t="s">
-        <v>1345</v>
+        <v>1346</v>
       </c>
       <c r="C12" t="s">
         <v>61</v>
       </c>
       <c r="D12" t="s">
-        <v>1346</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -15969,13 +15987,13 @@
         <v>459</v>
       </c>
       <c r="B13" t="s">
-        <v>1337</v>
+        <v>1338</v>
       </c>
       <c r="C13" t="s">
         <v>313</v>
       </c>
       <c r="D13" t="s">
-        <v>1347</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
@@ -15983,7 +16001,7 @@
         <v>316</v>
       </c>
       <c r="B14" t="s">
-        <v>1338</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
@@ -15991,34 +16009,34 @@
         <v>26</v>
       </c>
       <c r="B15" t="s">
-        <v>1339</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>1348</v>
+        <v>1349</v>
       </c>
       <c r="B16" t="s">
-        <v>1349</v>
+        <v>1350</v>
       </c>
       <c r="F16" t="s">
-        <v>1350</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>1351</v>
+        <v>1352</v>
       </c>
       <c r="B17" t="s">
-        <v>1349</v>
+        <v>1350</v>
       </c>
       <c r="F17" t="s">
-        <v>1352</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
@@ -16026,7 +16044,7 @@
         <v>115</v>
       </c>
       <c r="C22" t="s">
-        <v>1354</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
@@ -16034,7 +16052,7 @@
         <v>109</v>
       </c>
       <c r="C23" t="s">
-        <v>1355</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
@@ -16042,7 +16060,7 @@
         <v>316</v>
       </c>
       <c r="C24" t="s">
-        <v>1356</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
@@ -16050,7 +16068,7 @@
         <v>86</v>
       </c>
       <c r="C25" t="s">
-        <v>1357</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
@@ -16058,7 +16076,7 @@
         <v>459</v>
       </c>
       <c r="C26" t="s">
-        <v>1358</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
@@ -16066,23 +16084,23 @@
         <v>26</v>
       </c>
       <c r="C27" t="s">
-        <v>1359</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>1348</v>
+        <v>1349</v>
       </c>
       <c r="C28" t="s">
-        <v>1360</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>1351</v>
+        <v>1352</v>
       </c>
       <c r="C29" t="s">
-        <v>1361</v>
+        <v>1362</v>
       </c>
     </row>
   </sheetData>
@@ -16096,7 +16114,7 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>1362</v>
+        <v>1363</v>
       </c>
       <c r="B1"/>
       <c r="C1"/>
@@ -16105,7 +16123,7 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1363</v>
+        <v>1364</v>
       </c>
       <c r="B2"/>
       <c r="C2"/>
@@ -16114,529 +16132,529 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>1364</v>
+        <v>1365</v>
       </c>
       <c r="B3" t="s">
         <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>1365</v>
+        <v>1366</v>
       </c>
       <c r="D3" t="s">
-        <v>1366</v>
+        <v>1367</v>
       </c>
       <c r="E3" t="s">
-        <v>1367</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1368</v>
+        <v>1369</v>
       </c>
       <c r="B4" t="s">
-        <v>1369</v>
+        <v>1370</v>
       </c>
       <c r="C4" t="s">
-        <v>1370</v>
+        <v>1371</v>
       </c>
       <c r="D4" t="s">
-        <v>1371</v>
+        <v>1372</v>
       </c>
       <c r="E4" t="s">
-        <v>1372</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>1374</v>
+      </c>
+      <c r="B5" t="s">
+        <v>1375</v>
+      </c>
+      <c r="C5" t="s">
+        <v>1376</v>
+      </c>
+      <c r="D5" t="s">
+        <v>1377</v>
+      </c>
+      <c r="E5" t="s">
         <v>1373</v>
-      </c>
-      <c r="B5" t="s">
-        <v>1374</v>
-      </c>
-      <c r="C5" t="s">
-        <v>1375</v>
-      </c>
-      <c r="D5" t="s">
-        <v>1376</v>
-      </c>
-      <c r="E5" t="s">
-        <v>1372</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>1377</v>
+        <v>1378</v>
       </c>
       <c r="B6" t="s">
-        <v>1378</v>
+        <v>1379</v>
       </c>
       <c r="C6" t="s">
-        <v>1379</v>
+        <v>1380</v>
       </c>
       <c r="D6" t="s">
-        <v>1380</v>
+        <v>1381</v>
       </c>
       <c r="E6" t="s">
-        <v>1372</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>1381</v>
+        <v>1382</v>
       </c>
       <c r="B7" t="s">
-        <v>1382</v>
+        <v>1383</v>
       </c>
       <c r="C7" t="s">
-        <v>1383</v>
+        <v>1384</v>
       </c>
       <c r="D7" t="s">
-        <v>1384</v>
+        <v>1385</v>
       </c>
       <c r="E7" t="s">
-        <v>1372</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>1385</v>
+        <v>1386</v>
       </c>
       <c r="B8" t="s">
-        <v>1386</v>
+        <v>1387</v>
       </c>
       <c r="C8" t="s">
-        <v>1387</v>
+        <v>1388</v>
       </c>
       <c r="D8" t="s">
-        <v>1388</v>
+        <v>1389</v>
       </c>
       <c r="E8" t="s">
-        <v>1372</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>1389</v>
+        <v>1390</v>
       </c>
       <c r="B9" t="s">
-        <v>1390</v>
+        <v>1391</v>
       </c>
       <c r="C9" t="s">
-        <v>1391</v>
+        <v>1392</v>
       </c>
       <c r="D9" t="s">
-        <v>1392</v>
+        <v>1393</v>
       </c>
       <c r="E9" t="s">
-        <v>1372</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>1393</v>
+        <v>1394</v>
       </c>
       <c r="B10" t="s">
-        <v>1394</v>
+        <v>1395</v>
       </c>
       <c r="C10" t="s">
-        <v>1395</v>
+        <v>1396</v>
       </c>
       <c r="D10" t="s">
-        <v>1396</v>
+        <v>1397</v>
       </c>
       <c r="E10" t="s">
-        <v>1372</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>1397</v>
+        <v>1398</v>
       </c>
       <c r="B11" t="s">
-        <v>1398</v>
+        <v>1399</v>
       </c>
       <c r="C11" t="s">
-        <v>1399</v>
+        <v>1400</v>
       </c>
       <c r="D11" t="s">
-        <v>1400</v>
+        <v>1401</v>
       </c>
       <c r="E11" t="s">
-        <v>1401</v>
+        <v>1402</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>1402</v>
+        <v>1403</v>
       </c>
       <c r="B12" t="s">
-        <v>1403</v>
+        <v>1404</v>
       </c>
       <c r="C12" t="s">
-        <v>1404</v>
+        <v>1405</v>
       </c>
       <c r="D12" t="s">
-        <v>1405</v>
+        <v>1406</v>
       </c>
       <c r="E12" t="s">
-        <v>1372</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>1406</v>
+        <v>1407</v>
       </c>
       <c r="B13" t="s">
-        <v>1407</v>
+        <v>1408</v>
       </c>
       <c r="C13" t="s">
-        <v>1408</v>
+        <v>1409</v>
       </c>
       <c r="D13" t="s">
         <v>409</v>
       </c>
       <c r="E13" t="s">
-        <v>1401</v>
+        <v>1402</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>1409</v>
+        <v>1410</v>
       </c>
       <c r="B14" t="s">
-        <v>1410</v>
+        <v>1411</v>
       </c>
       <c r="C14" t="s">
-        <v>1411</v>
+        <v>1412</v>
       </c>
       <c r="D14" t="s">
-        <v>1412</v>
+        <v>1413</v>
       </c>
       <c r="E14" t="s">
-        <v>1372</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>1413</v>
+        <v>1414</v>
       </c>
       <c r="B15" t="s">
-        <v>1198</v>
+        <v>1199</v>
       </c>
       <c r="C15" t="s">
-        <v>1414</v>
+        <v>1415</v>
       </c>
       <c r="D15" t="s">
-        <v>1415</v>
+        <v>1416</v>
       </c>
       <c r="E15" t="s">
-        <v>1372</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>1416</v>
+        <v>1417</v>
       </c>
       <c r="B16" t="s">
-        <v>1417</v>
+        <v>1418</v>
       </c>
       <c r="C16" t="s">
-        <v>1418</v>
+        <v>1419</v>
       </c>
       <c r="D16" t="s">
-        <v>1419</v>
+        <v>1420</v>
       </c>
       <c r="E16" t="s">
-        <v>1372</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>1420</v>
+        <v>1421</v>
       </c>
       <c r="B17" t="s">
         <v>441</v>
       </c>
       <c r="C17" t="s">
-        <v>1421</v>
+        <v>1422</v>
       </c>
       <c r="D17" t="s">
-        <v>1422</v>
+        <v>1423</v>
       </c>
       <c r="E17" t="s">
-        <v>1401</v>
+        <v>1402</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>1423</v>
+        <v>1424</v>
       </c>
       <c r="B18" t="s">
-        <v>1322</v>
+        <v>1323</v>
       </c>
       <c r="C18" t="s">
-        <v>1424</v>
+        <v>1425</v>
       </c>
       <c r="D18" t="s">
-        <v>1425</v>
+        <v>1426</v>
       </c>
       <c r="E18" t="s">
-        <v>1401</v>
+        <v>1402</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>1426</v>
+        <v>1427</v>
       </c>
       <c r="B19" t="s">
-        <v>1427</v>
+        <v>1428</v>
       </c>
       <c r="C19" t="s">
-        <v>1428</v>
+        <v>1429</v>
       </c>
       <c r="D19" t="s">
-        <v>1429</v>
+        <v>1430</v>
       </c>
       <c r="E19" t="s">
-        <v>1401</v>
+        <v>1402</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>1430</v>
+        <v>1431</v>
       </c>
       <c r="B20" t="s">
-        <v>1296</v>
+        <v>1297</v>
       </c>
       <c r="C20" t="s">
-        <v>1431</v>
+        <v>1432</v>
       </c>
       <c r="D20" t="s">
-        <v>1432</v>
+        <v>1433</v>
       </c>
       <c r="E20" t="s">
-        <v>1372</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>1433</v>
+        <v>1434</v>
       </c>
       <c r="B21" t="s">
-        <v>1434</v>
+        <v>1435</v>
       </c>
       <c r="C21" t="s">
-        <v>1435</v>
+        <v>1436</v>
       </c>
       <c r="D21" t="s">
         <v>215</v>
       </c>
       <c r="E21" t="s">
-        <v>1401</v>
+        <v>1402</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>1436</v>
+        <v>1437</v>
       </c>
       <c r="B22" t="s">
-        <v>1437</v>
+        <v>1438</v>
       </c>
       <c r="C22" t="s">
-        <v>1438</v>
+        <v>1439</v>
       </c>
       <c r="D22" t="s">
-        <v>1439</v>
+        <v>1440</v>
       </c>
       <c r="E22" t="s">
-        <v>1372</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>1345</v>
+        <v>1346</v>
       </c>
       <c r="B23" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
       <c r="C23" t="s">
-        <v>1441</v>
+        <v>1442</v>
       </c>
       <c r="D23" t="s">
-        <v>1442</v>
+        <v>1443</v>
       </c>
       <c r="E23" t="s">
-        <v>1372</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>1443</v>
+        <v>1444</v>
       </c>
       <c r="B24" t="s">
         <v>216</v>
       </c>
       <c r="C24" t="s">
-        <v>1444</v>
+        <v>1445</v>
       </c>
       <c r="D24" t="s">
-        <v>1445</v>
+        <v>1446</v>
       </c>
       <c r="E24" t="s">
-        <v>1372</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>1446</v>
+        <v>1447</v>
       </c>
       <c r="B25" t="s">
-        <v>1447</v>
+        <v>1448</v>
       </c>
       <c r="C25" t="s">
-        <v>1448</v>
+        <v>1449</v>
       </c>
       <c r="D25" t="s">
-        <v>1449</v>
+        <v>1450</v>
       </c>
       <c r="E25" t="s">
-        <v>1401</v>
+        <v>1402</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>1450</v>
+        <v>1451</v>
       </c>
       <c r="B26" t="s">
-        <v>1451</v>
+        <v>1452</v>
       </c>
       <c r="C26" t="s">
-        <v>1452</v>
+        <v>1453</v>
       </c>
       <c r="D26" t="s">
-        <v>1453</v>
+        <v>1454</v>
       </c>
       <c r="E26" t="s">
-        <v>1401</v>
+        <v>1402</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>1454</v>
+        <v>1455</v>
       </c>
       <c r="B27" t="s">
-        <v>1455</v>
+        <v>1456</v>
       </c>
       <c r="C27" t="s">
-        <v>1456</v>
+        <v>1457</v>
       </c>
       <c r="D27" t="s">
-        <v>1457</v>
+        <v>1458</v>
       </c>
       <c r="E27" t="s">
-        <v>1372</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>1458</v>
+        <v>1459</v>
       </c>
       <c r="B28" t="s">
-        <v>1459</v>
+        <v>1460</v>
       </c>
       <c r="C28" t="s">
-        <v>1460</v>
+        <v>1461</v>
       </c>
       <c r="D28" t="s">
-        <v>1461</v>
+        <v>1462</v>
       </c>
       <c r="E28" t="s">
-        <v>1372</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
       <c r="B29" t="s">
         <v>832</v>
       </c>
       <c r="C29" t="s">
-        <v>1463</v>
+        <v>1464</v>
       </c>
       <c r="D29" t="s">
-        <v>1464</v>
+        <v>1465</v>
       </c>
       <c r="E29" t="s">
-        <v>1372</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>1465</v>
+        <v>1466</v>
       </c>
       <c r="B30" t="s">
-        <v>1466</v>
+        <v>1467</v>
       </c>
       <c r="C30" t="s">
-        <v>1467</v>
+        <v>1468</v>
       </c>
       <c r="D30" t="s">
-        <v>1468</v>
+        <v>1469</v>
       </c>
       <c r="E30" t="s">
-        <v>1401</v>
+        <v>1402</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>1469</v>
+        <v>1470</v>
       </c>
       <c r="B31" t="s">
-        <v>1470</v>
+        <v>1471</v>
       </c>
       <c r="C31" t="s">
-        <v>1471</v>
+        <v>1472</v>
       </c>
       <c r="D31" t="s">
         <v>94</v>
       </c>
       <c r="E31" t="s">
-        <v>1372</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>1472</v>
+        <v>1473</v>
       </c>
       <c r="B32" t="s">
-        <v>1473</v>
+        <v>1474</v>
       </c>
       <c r="C32" t="s">
-        <v>1474</v>
+        <v>1475</v>
       </c>
       <c r="D32" t="s">
-        <v>1475</v>
+        <v>1476</v>
       </c>
       <c r="E32" t="s">
-        <v>1372</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>1476</v>
+        <v>1477</v>
       </c>
       <c r="B33" t="s">
         <v>1047</v>
       </c>
       <c r="C33" t="s">
-        <v>1477</v>
+        <v>1478</v>
       </c>
       <c r="D33" t="s">
-        <v>1478</v>
+        <v>1479</v>
       </c>
       <c r="E33" t="s">
-        <v>1401</v>
+        <v>1402</v>
       </c>
     </row>
   </sheetData>
@@ -16650,157 +16668,157 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F33"/>
+  <dimension ref="A1:F34"/>
   <sheetFormatPr defaultRowHeight="0" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" customHeight="1"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>1479</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1480</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>1481</v>
+        <v>1482</v>
       </c>
       <c r="B3" t="s">
-        <v>1482</v>
+        <v>1483</v>
       </c>
       <c r="C3" t="s">
-        <v>1483</v>
+        <v>1484</v>
       </c>
       <c r="D3" t="s">
-        <v>1484</v>
+        <v>1485</v>
       </c>
       <c r="E3" t="s">
-        <v>1485</v>
+        <v>1486</v>
       </c>
       <c r="F3" t="s">
-        <v>1486</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1487</v>
+        <v>1488</v>
       </c>
       <c r="B4" t="s">
         <v>28</v>
       </c>
       <c r="C4" t="s">
-        <v>1488</v>
+        <v>1489</v>
       </c>
       <c r="D4" t="s">
-        <v>1489</v>
+        <v>1490</v>
       </c>
       <c r="E4" t="s">
-        <v>1490</v>
+        <v>1491</v>
       </c>
       <c r="F4" t="s">
-        <v>1491</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1492</v>
+        <v>1493</v>
       </c>
       <c r="B5" t="s">
-        <v>1493</v>
+        <v>1494</v>
       </c>
       <c r="C5" t="s">
-        <v>1494</v>
+        <v>1495</v>
       </c>
       <c r="D5" t="s">
-        <v>1495</v>
+        <v>1496</v>
       </c>
       <c r="E5" t="s">
-        <v>1496</v>
+        <v>1497</v>
       </c>
       <c r="F5" t="s">
-        <v>1497</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>1498</v>
+        <v>1499</v>
       </c>
       <c r="B6" t="s">
-        <v>1499</v>
+        <v>1500</v>
       </c>
       <c r="C6" t="s">
-        <v>1500</v>
+        <v>1501</v>
       </c>
       <c r="D6" t="s">
-        <v>1501</v>
+        <v>1502</v>
       </c>
       <c r="E6" t="s">
-        <v>1502</v>
+        <v>1503</v>
       </c>
       <c r="F6" t="s">
-        <v>1503</v>
+        <v>1504</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>1504</v>
+        <v>1505</v>
       </c>
       <c r="B7" t="s">
-        <v>1505</v>
+        <v>1506</v>
       </c>
       <c r="C7" t="s">
-        <v>1506</v>
+        <v>1507</v>
       </c>
       <c r="D7" t="s">
-        <v>1507</v>
+        <v>1508</v>
       </c>
       <c r="E7" t="s">
-        <v>1502</v>
+        <v>1503</v>
       </c>
       <c r="F7" t="s">
-        <v>1508</v>
+        <v>1509</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>1510</v>
+      </c>
+      <c r="B8" t="s">
+        <v>1511</v>
+      </c>
+      <c r="C8" t="s">
+        <v>1512</v>
+      </c>
+      <c r="D8" t="s">
+        <v>1513</v>
+      </c>
+      <c r="E8" t="s">
+        <v>1503</v>
+      </c>
+      <c r="F8" t="s">
         <v>1509</v>
-      </c>
-      <c r="B8" t="s">
-        <v>1510</v>
-      </c>
-      <c r="C8" t="s">
-        <v>1511</v>
-      </c>
-      <c r="D8" t="s">
-        <v>1512</v>
-      </c>
-      <c r="E8" t="s">
-        <v>1502</v>
-      </c>
-      <c r="F8" t="s">
-        <v>1508</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>1513</v>
+        <v>1514</v>
       </c>
       <c r="B9" t="s">
         <v>96</v>
       </c>
       <c r="C9" t="s">
-        <v>1514</v>
+        <v>1515</v>
       </c>
       <c r="D9" t="s">
-        <v>1515</v>
+        <v>1516</v>
       </c>
       <c r="E9" t="s">
-        <v>1490</v>
+        <v>1491</v>
       </c>
       <c r="F9" t="s">
-        <v>1516</v>
+        <v>1517</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -16811,93 +16829,93 @@
         <v>96</v>
       </c>
       <c r="C10" t="s">
-        <v>1517</v>
+        <v>1518</v>
       </c>
       <c r="D10" t="s">
-        <v>1518</v>
+        <v>1519</v>
       </c>
       <c r="E10" t="s">
-        <v>1519</v>
+        <v>1520</v>
       </c>
       <c r="F10" t="s">
-        <v>1520</v>
+        <v>1521</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>1521</v>
+        <v>1522</v>
       </c>
       <c r="B11" t="s">
         <v>55</v>
       </c>
       <c r="C11" t="s">
-        <v>1522</v>
+        <v>1523</v>
       </c>
       <c r="D11" t="s">
-        <v>1523</v>
+        <v>1524</v>
       </c>
       <c r="E11" t="s">
-        <v>1519</v>
+        <v>1520</v>
       </c>
       <c r="F11" t="s">
-        <v>1524</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>1525</v>
+        <v>1526</v>
       </c>
       <c r="B12" t="s">
-        <v>1526</v>
+        <v>1527</v>
       </c>
       <c r="C12" t="s">
-        <v>1527</v>
+        <v>1528</v>
       </c>
       <c r="D12" t="s">
-        <v>1528</v>
+        <v>1529</v>
       </c>
       <c r="E12" t="s">
-        <v>1529</v>
+        <v>1530</v>
       </c>
       <c r="F12" t="s">
-        <v>1530</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>1531</v>
+        <v>1532</v>
       </c>
       <c r="B13" t="s">
-        <v>1532</v>
+        <v>1533</v>
       </c>
       <c r="C13" t="s">
-        <v>1533</v>
+        <v>1534</v>
       </c>
       <c r="D13" t="s">
-        <v>1534</v>
+        <v>1535</v>
       </c>
       <c r="E13" t="s">
-        <v>1535</v>
+        <v>1536</v>
       </c>
       <c r="F13" t="s">
-        <v>1536</v>
+        <v>1537</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>1537</v>
+        <v>1538</v>
       </c>
       <c r="B14" t="s">
         <v>749</v>
       </c>
       <c r="C14" t="s">
-        <v>1538</v>
+        <v>1539</v>
       </c>
       <c r="D14" t="s">
-        <v>1539</v>
+        <v>1540</v>
       </c>
       <c r="E14" t="s">
-        <v>1540</v>
+        <v>1541</v>
       </c>
       <c r="F14" t="s">
         <v>756</v>
@@ -16905,19 +16923,19 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>1541</v>
+        <v>1542</v>
       </c>
       <c r="B15" t="s">
         <v>749</v>
       </c>
       <c r="C15" t="s">
-        <v>1542</v>
+        <v>1543</v>
       </c>
       <c r="D15" t="s">
-        <v>1543</v>
+        <v>1544</v>
       </c>
       <c r="E15" t="s">
-        <v>1544</v>
+        <v>1545</v>
       </c>
       <c r="F15" t="s">
         <v>756</v>
@@ -16925,19 +16943,19 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>1545</v>
+        <v>1546</v>
       </c>
       <c r="B16" t="s">
         <v>932</v>
       </c>
       <c r="C16" t="s">
-        <v>1546</v>
+        <v>1547</v>
       </c>
       <c r="D16" t="s">
-        <v>1547</v>
+        <v>1548</v>
       </c>
       <c r="E16" t="s">
-        <v>1544</v>
+        <v>1545</v>
       </c>
       <c r="F16" t="s">
         <v>938</v>
@@ -16945,19 +16963,19 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>1548</v>
+        <v>1549</v>
       </c>
       <c r="B17" t="s">
         <v>1015</v>
       </c>
       <c r="C17" t="s">
-        <v>1549</v>
+        <v>1550</v>
       </c>
       <c r="D17" t="s">
-        <v>1550</v>
+        <v>1551</v>
       </c>
       <c r="E17" t="s">
-        <v>1544</v>
+        <v>1545</v>
       </c>
       <c r="F17" t="s">
         <v>938</v>
@@ -16965,19 +16983,19 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>1551</v>
+        <v>1552</v>
       </c>
       <c r="B18" t="s">
         <v>1116</v>
       </c>
       <c r="C18" t="s">
-        <v>1552</v>
+        <v>1553</v>
       </c>
       <c r="D18" t="s">
-        <v>1553</v>
+        <v>1554</v>
       </c>
       <c r="E18" t="s">
-        <v>1544</v>
+        <v>1545</v>
       </c>
       <c r="F18" t="s">
         <v>938</v>
@@ -16985,19 +17003,19 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>1554</v>
+        <v>1555</v>
       </c>
       <c r="B19" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="C19" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
       <c r="D19" t="s">
-        <v>1556</v>
+        <v>1557</v>
       </c>
       <c r="E19" t="s">
-        <v>1544</v>
+        <v>1545</v>
       </c>
       <c r="F19" t="s">
         <v>938</v>
@@ -17005,19 +17023,19 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>1557</v>
+        <v>1558</v>
       </c>
       <c r="B20" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="C20" t="s">
-        <v>1558</v>
+        <v>1559</v>
       </c>
       <c r="D20" t="s">
-        <v>1559</v>
+        <v>1560</v>
       </c>
       <c r="E20" t="s">
-        <v>1544</v>
+        <v>1545</v>
       </c>
       <c r="F20" t="s">
         <v>938</v>
@@ -17025,19 +17043,19 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>1560</v>
+        <v>1561</v>
       </c>
       <c r="B21" t="s">
-        <v>1240</v>
+        <v>1241</v>
       </c>
       <c r="C21" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="D21" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
       <c r="E21" t="s">
-        <v>1544</v>
+        <v>1545</v>
       </c>
       <c r="F21" t="s">
         <v>938</v>
@@ -17045,19 +17063,19 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>1563</v>
+        <v>1564</v>
       </c>
       <c r="B22" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="C22" t="s">
-        <v>1564</v>
+        <v>1565</v>
       </c>
       <c r="D22" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="E22" t="s">
-        <v>1544</v>
+        <v>1545</v>
       </c>
       <c r="F22" t="s">
         <v>938</v>
@@ -17065,222 +17083,242 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
       <c r="B23" t="s">
         <v>627</v>
       </c>
       <c r="C23" t="s">
-        <v>1567</v>
+        <v>1568</v>
       </c>
       <c r="D23" t="s">
-        <v>1568</v>
+        <v>1569</v>
       </c>
       <c r="E23" t="s">
-        <v>1569</v>
+        <v>1570</v>
       </c>
       <c r="F23" t="s">
-        <v>1570</v>
+        <v>1571</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>1571</v>
+        <v>1572</v>
       </c>
       <c r="B24" t="s">
         <v>227</v>
       </c>
       <c r="C24" t="s">
-        <v>1572</v>
+        <v>1573</v>
       </c>
       <c r="D24" t="s">
-        <v>1573</v>
+        <v>1574</v>
       </c>
       <c r="E24" t="s">
-        <v>1569</v>
+        <v>1570</v>
       </c>
       <c r="F24" t="s">
-        <v>1570</v>
+        <v>1571</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>1574</v>
+        <v>1575</v>
       </c>
       <c r="B25" t="s">
         <v>260</v>
       </c>
       <c r="C25" t="s">
-        <v>1575</v>
+        <v>1576</v>
       </c>
       <c r="D25" t="s">
-        <v>1576</v>
+        <v>1577</v>
       </c>
       <c r="E25" t="s">
-        <v>1569</v>
+        <v>1570</v>
       </c>
       <c r="F25" t="s">
-        <v>1570</v>
+        <v>1571</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>1577</v>
+        <v>1578</v>
       </c>
       <c r="B26" t="s">
         <v>800</v>
       </c>
       <c r="C26" t="s">
-        <v>1578</v>
+        <v>1579</v>
       </c>
       <c r="D26" t="s">
-        <v>1579</v>
+        <v>1580</v>
       </c>
       <c r="E26" t="s">
-        <v>1569</v>
+        <v>1570</v>
       </c>
       <c r="F26" t="s">
-        <v>1570</v>
+        <v>1571</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>1580</v>
+        <v>1581</v>
       </c>
       <c r="B27" t="s">
         <v>899</v>
       </c>
       <c r="C27" t="s">
-        <v>1581</v>
+        <v>1582</v>
       </c>
       <c r="D27" t="s">
-        <v>1582</v>
+        <v>1583</v>
       </c>
       <c r="E27" t="s">
-        <v>1569</v>
+        <v>1570</v>
       </c>
       <c r="F27" t="s">
-        <v>1570</v>
+        <v>1571</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>1583</v>
+        <v>1584</v>
       </c>
       <c r="B28" t="s">
         <v>87</v>
       </c>
       <c r="C28" t="s">
-        <v>1584</v>
+        <v>1585</v>
       </c>
       <c r="D28" t="s">
-        <v>1585</v>
+        <v>1586</v>
       </c>
       <c r="E28" t="s">
-        <v>1569</v>
+        <v>1570</v>
       </c>
       <c r="F28" t="s">
-        <v>1570</v>
+        <v>1571</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>1586</v>
+        <v>1587</v>
       </c>
       <c r="B29" t="s">
         <v>29</v>
       </c>
       <c r="C29" t="s">
-        <v>1587</v>
+        <v>1588</v>
       </c>
       <c r="D29" t="s">
-        <v>1588</v>
+        <v>1589</v>
       </c>
       <c r="E29" t="s">
-        <v>1569</v>
+        <v>1570</v>
       </c>
       <c r="F29" t="s">
-        <v>1570</v>
+        <v>1571</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>1589</v>
+        <v>1590</v>
       </c>
       <c r="B30" t="s">
         <v>306</v>
       </c>
       <c r="C30" t="s">
-        <v>1590</v>
+        <v>1591</v>
       </c>
       <c r="D30" t="s">
-        <v>1591</v>
+        <v>1592</v>
       </c>
       <c r="E30" t="s">
-        <v>1569</v>
+        <v>1570</v>
       </c>
       <c r="F30" t="s">
-        <v>1570</v>
+        <v>1571</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>1592</v>
+        <v>1593</v>
       </c>
       <c r="B31" t="s">
         <v>1107</v>
       </c>
       <c r="C31" t="s">
-        <v>1593</v>
+        <v>1594</v>
       </c>
       <c r="D31" t="s">
-        <v>1594</v>
+        <v>1595</v>
       </c>
       <c r="E31" t="s">
-        <v>1569</v>
+        <v>1570</v>
       </c>
       <c r="F31" t="s">
-        <v>1570</v>
+        <v>1571</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>1595</v>
+        <v>1596</v>
       </c>
       <c r="B32" t="s">
         <v>208</v>
       </c>
       <c r="C32" t="s">
-        <v>1596</v>
+        <v>1597</v>
       </c>
       <c r="D32" t="s">
-        <v>1591</v>
+        <v>1592</v>
       </c>
       <c r="E32" t="s">
-        <v>1569</v>
+        <v>1570</v>
       </c>
       <c r="F32" t="s">
-        <v>1570</v>
+        <v>1571</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>1597</v>
+        <v>1598</v>
       </c>
       <c r="B33" t="s">
         <v>103</v>
       </c>
       <c r="C33" t="s">
-        <v>1598</v>
+        <v>1599</v>
       </c>
       <c r="D33" t="s">
-        <v>1599</v>
+        <v>1600</v>
       </c>
       <c r="E33" t="s">
-        <v>1569</v>
+        <v>1570</v>
       </c>
       <c r="F33" t="s">
+        <v>1571</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>1601</v>
+      </c>
+      <c r="B34" t="s">
+        <v>1149</v>
+      </c>
+      <c r="C34" t="s">
+        <v>1602</v>
+      </c>
+      <c r="D34" t="s">
+        <v>1603</v>
+      </c>
+      <c r="E34" t="s">
         <v>1570</v>
+      </c>
+      <c r="F34" t="s">
+        <v>1571</v>
       </c>
     </row>
   </sheetData>
@@ -17289,40 +17327,40 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G331"/>
+  <dimension ref="A1:G333"/>
   <sheetFormatPr defaultRowHeight="0" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" customHeight="1"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>1600</v>
+        <v>1604</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1601</v>
+        <v>1605</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>1602</v>
+        <v>1606</v>
       </c>
       <c r="B3" t="s">
-        <v>1603</v>
+        <v>1607</v>
       </c>
       <c r="C3" t="s">
-        <v>1604</v>
+        <v>1608</v>
       </c>
       <c r="D3" t="s">
-        <v>1605</v>
+        <v>1609</v>
       </c>
       <c r="E3" t="s">
-        <v>1606</v>
+        <v>1610</v>
       </c>
       <c r="F3" t="s">
-        <v>1607</v>
+        <v>1611</v>
       </c>
       <c r="G3" t="s">
-        <v>1608</v>
+        <v>1612</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -17342,10 +17380,10 @@
         <v>316</v>
       </c>
       <c r="F4" t="s">
-        <v>1609</v>
+        <v>1613</v>
       </c>
       <c r="G4" t="s">
-        <v>1610</v>
+        <v>1614</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -17365,10 +17403,10 @@
         <v>316</v>
       </c>
       <c r="F5" t="s">
-        <v>1609</v>
+        <v>1613</v>
       </c>
       <c r="G5" t="s">
-        <v>1611</v>
+        <v>1615</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -17388,10 +17426,10 @@
         <v>316</v>
       </c>
       <c r="F6" t="s">
-        <v>1609</v>
+        <v>1613</v>
       </c>
       <c r="G6" t="s">
-        <v>1612</v>
+        <v>1616</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -17411,10 +17449,10 @@
         <v>109</v>
       </c>
       <c r="F7" t="s">
-        <v>1609</v>
+        <v>1613</v>
       </c>
       <c r="G7" t="s">
-        <v>1613</v>
+        <v>1617</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -17434,10 +17472,10 @@
         <v>316</v>
       </c>
       <c r="F8" t="s">
-        <v>1609</v>
+        <v>1613</v>
       </c>
       <c r="G8" t="s">
-        <v>1614</v>
+        <v>1618</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -17457,10 +17495,10 @@
         <v>316</v>
       </c>
       <c r="F9" t="s">
-        <v>1609</v>
+        <v>1613</v>
       </c>
       <c r="G9" t="s">
-        <v>1615</v>
+        <v>1619</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -17480,10 +17518,10 @@
         <v>316</v>
       </c>
       <c r="F10" t="s">
-        <v>1609</v>
+        <v>1613</v>
       </c>
       <c r="G10" t="s">
-        <v>1616</v>
+        <v>1620</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -17503,10 +17541,10 @@
         <v>109</v>
       </c>
       <c r="F11" t="s">
-        <v>1609</v>
+        <v>1613</v>
       </c>
       <c r="G11" t="s">
-        <v>1617</v>
+        <v>1621</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -17526,10 +17564,10 @@
         <v>109</v>
       </c>
       <c r="F12" t="s">
-        <v>1609</v>
+        <v>1613</v>
       </c>
       <c r="G12" t="s">
-        <v>1618</v>
+        <v>1622</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -17549,10 +17587,10 @@
         <v>316</v>
       </c>
       <c r="F13" t="s">
-        <v>1609</v>
+        <v>1613</v>
       </c>
       <c r="G13" t="s">
-        <v>1619</v>
+        <v>1623</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -17572,10 +17610,10 @@
         <v>316</v>
       </c>
       <c r="F14" t="s">
-        <v>1620</v>
+        <v>1624</v>
       </c>
       <c r="G14" t="s">
-        <v>1621</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -17595,10 +17633,10 @@
         <v>316</v>
       </c>
       <c r="F15" t="s">
-        <v>1620</v>
+        <v>1624</v>
       </c>
       <c r="G15" t="s">
-        <v>1622</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -17618,10 +17656,10 @@
         <v>316</v>
       </c>
       <c r="F16" t="s">
-        <v>1620</v>
+        <v>1624</v>
       </c>
       <c r="G16" t="s">
-        <v>1623</v>
+        <v>1627</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -17641,10 +17679,10 @@
         <v>316</v>
       </c>
       <c r="F17" t="s">
-        <v>1620</v>
+        <v>1624</v>
       </c>
       <c r="G17" t="s">
-        <v>1624</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -17664,10 +17702,10 @@
         <v>316</v>
       </c>
       <c r="F18" t="s">
-        <v>1620</v>
+        <v>1624</v>
       </c>
       <c r="G18" t="s">
-        <v>1625</v>
+        <v>1629</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -17687,10 +17725,10 @@
         <v>316</v>
       </c>
       <c r="F19" t="s">
-        <v>1620</v>
+        <v>1624</v>
       </c>
       <c r="G19" t="s">
-        <v>1626</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -17710,10 +17748,10 @@
         <v>109</v>
       </c>
       <c r="F20" t="s">
-        <v>1620</v>
+        <v>1624</v>
       </c>
       <c r="G20" t="s">
-        <v>1627</v>
+        <v>1631</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -17733,10 +17771,10 @@
         <v>109</v>
       </c>
       <c r="F21" t="s">
-        <v>1620</v>
+        <v>1624</v>
       </c>
       <c r="G21" t="s">
-        <v>1628</v>
+        <v>1632</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
@@ -17756,10 +17794,10 @@
         <v>316</v>
       </c>
       <c r="F22" t="s">
-        <v>1620</v>
+        <v>1624</v>
       </c>
       <c r="G22" t="s">
-        <v>1629</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
@@ -17779,10 +17817,10 @@
         <v>109</v>
       </c>
       <c r="F23" t="s">
-        <v>1620</v>
+        <v>1624</v>
       </c>
       <c r="G23" t="s">
-        <v>1630</v>
+        <v>1634</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -17802,10 +17840,10 @@
         <v>109</v>
       </c>
       <c r="F24" t="s">
-        <v>1620</v>
+        <v>1624</v>
       </c>
       <c r="G24" t="s">
-        <v>1631</v>
+        <v>1635</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
@@ -17825,10 +17863,10 @@
         <v>109</v>
       </c>
       <c r="F25" t="s">
-        <v>1620</v>
+        <v>1624</v>
       </c>
       <c r="G25" t="s">
-        <v>1632</v>
+        <v>1636</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
@@ -17848,10 +17886,10 @@
         <v>109</v>
       </c>
       <c r="F26" t="s">
-        <v>1620</v>
+        <v>1624</v>
       </c>
       <c r="G26" t="s">
-        <v>1633</v>
+        <v>1637</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
@@ -17871,10 +17909,10 @@
         <v>316</v>
       </c>
       <c r="F27" t="s">
-        <v>1620</v>
+        <v>1624</v>
       </c>
       <c r="G27" t="s">
-        <v>1634</v>
+        <v>1638</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
@@ -17894,10 +17932,10 @@
         <v>109</v>
       </c>
       <c r="F28" t="s">
-        <v>1620</v>
+        <v>1624</v>
       </c>
       <c r="G28" t="s">
-        <v>1635</v>
+        <v>1639</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
@@ -17917,10 +17955,10 @@
         <v>109</v>
       </c>
       <c r="F29" t="s">
-        <v>1620</v>
+        <v>1624</v>
       </c>
       <c r="G29" t="s">
-        <v>1636</v>
+        <v>1640</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
@@ -17940,10 +17978,10 @@
         <v>316</v>
       </c>
       <c r="F30" t="s">
-        <v>1620</v>
+        <v>1624</v>
       </c>
       <c r="G30" t="s">
-        <v>1637</v>
+        <v>1641</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
@@ -17963,10 +18001,10 @@
         <v>316</v>
       </c>
       <c r="F31" t="s">
-        <v>1620</v>
+        <v>1624</v>
       </c>
       <c r="G31" t="s">
-        <v>1638</v>
+        <v>1642</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
@@ -17986,10 +18024,10 @@
         <v>109</v>
       </c>
       <c r="F32" t="s">
-        <v>1620</v>
+        <v>1624</v>
       </c>
       <c r="G32" t="s">
-        <v>1639</v>
+        <v>1643</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
@@ -18009,10 +18047,10 @@
         <v>109</v>
       </c>
       <c r="F33" t="s">
-        <v>1620</v>
+        <v>1624</v>
       </c>
       <c r="G33" t="s">
-        <v>1640</v>
+        <v>1644</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
@@ -18032,10 +18070,10 @@
         <v>109</v>
       </c>
       <c r="F34" t="s">
-        <v>1620</v>
+        <v>1624</v>
       </c>
       <c r="G34" t="s">
-        <v>1641</v>
+        <v>1645</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
@@ -18043,7 +18081,7 @@
         <v>27</v>
       </c>
       <c r="B35" t="s">
-        <v>1526</v>
+        <v>1527</v>
       </c>
       <c r="C35" t="s">
         <v>160</v>
@@ -18055,10 +18093,10 @@
         <v>316</v>
       </c>
       <c r="F35" t="s">
-        <v>1642</v>
+        <v>1646</v>
       </c>
       <c r="G35" t="s">
-        <v>1643</v>
+        <v>1647</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
@@ -18066,7 +18104,7 @@
         <v>27</v>
       </c>
       <c r="B36" t="s">
-        <v>1526</v>
+        <v>1527</v>
       </c>
       <c r="C36" t="s">
         <v>171</v>
@@ -18078,10 +18116,10 @@
         <v>316</v>
       </c>
       <c r="F36" t="s">
-        <v>1642</v>
+        <v>1646</v>
       </c>
       <c r="G36" t="s">
-        <v>1644</v>
+        <v>1648</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
@@ -18089,7 +18127,7 @@
         <v>27</v>
       </c>
       <c r="B37" t="s">
-        <v>1526</v>
+        <v>1527</v>
       </c>
       <c r="C37" t="s">
         <v>188</v>
@@ -18101,10 +18139,10 @@
         <v>316</v>
       </c>
       <c r="F37" t="s">
-        <v>1642</v>
+        <v>1646</v>
       </c>
       <c r="G37" t="s">
-        <v>1645</v>
+        <v>1649</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
@@ -18112,7 +18150,7 @@
         <v>27</v>
       </c>
       <c r="B38" t="s">
-        <v>1526</v>
+        <v>1527</v>
       </c>
       <c r="C38" t="s">
         <v>197</v>
@@ -18124,10 +18162,10 @@
         <v>316</v>
       </c>
       <c r="F38" t="s">
-        <v>1642</v>
+        <v>1646</v>
       </c>
       <c r="G38" t="s">
-        <v>1646</v>
+        <v>1650</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
@@ -18135,7 +18173,7 @@
         <v>27</v>
       </c>
       <c r="B39" t="s">
-        <v>1526</v>
+        <v>1527</v>
       </c>
       <c r="C39" t="s">
         <v>215</v>
@@ -18147,10 +18185,10 @@
         <v>316</v>
       </c>
       <c r="F39" t="s">
-        <v>1642</v>
+        <v>1646</v>
       </c>
       <c r="G39" t="s">
-        <v>1647</v>
+        <v>1651</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
@@ -18158,7 +18196,7 @@
         <v>27</v>
       </c>
       <c r="B40" t="s">
-        <v>1526</v>
+        <v>1527</v>
       </c>
       <c r="C40" t="s">
         <v>242</v>
@@ -18170,10 +18208,10 @@
         <v>316</v>
       </c>
       <c r="F40" t="s">
-        <v>1642</v>
+        <v>1646</v>
       </c>
       <c r="G40" t="s">
-        <v>1648</v>
+        <v>1652</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
@@ -18181,7 +18219,7 @@
         <v>27</v>
       </c>
       <c r="B41" t="s">
-        <v>1526</v>
+        <v>1527</v>
       </c>
       <c r="C41" t="s">
         <v>330</v>
@@ -18193,10 +18231,10 @@
         <v>316</v>
       </c>
       <c r="F41" t="s">
-        <v>1642</v>
+        <v>1646</v>
       </c>
       <c r="G41" t="s">
-        <v>1649</v>
+        <v>1653</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
@@ -18204,7 +18242,7 @@
         <v>27</v>
       </c>
       <c r="B42" t="s">
-        <v>1526</v>
+        <v>1527</v>
       </c>
       <c r="C42" t="s">
         <v>341</v>
@@ -18216,10 +18254,10 @@
         <v>316</v>
       </c>
       <c r="F42" t="s">
-        <v>1642</v>
+        <v>1646</v>
       </c>
       <c r="G42" t="s">
-        <v>1650</v>
+        <v>1654</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
@@ -18227,7 +18265,7 @@
         <v>27</v>
       </c>
       <c r="B43" t="s">
-        <v>1526</v>
+        <v>1527</v>
       </c>
       <c r="C43" t="s">
         <v>350</v>
@@ -18239,10 +18277,10 @@
         <v>316</v>
       </c>
       <c r="F43" t="s">
-        <v>1642</v>
+        <v>1646</v>
       </c>
       <c r="G43" t="s">
-        <v>1651</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
@@ -18250,7 +18288,7 @@
         <v>27</v>
       </c>
       <c r="B44" t="s">
-        <v>1526</v>
+        <v>1527</v>
       </c>
       <c r="C44" t="s">
         <v>359</v>
@@ -18262,10 +18300,10 @@
         <v>316</v>
       </c>
       <c r="F44" t="s">
-        <v>1642</v>
+        <v>1646</v>
       </c>
       <c r="G44" t="s">
-        <v>1652</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
@@ -18273,7 +18311,7 @@
         <v>27</v>
       </c>
       <c r="B45" t="s">
-        <v>1526</v>
+        <v>1527</v>
       </c>
       <c r="C45" t="s">
         <v>367</v>
@@ -18285,10 +18323,10 @@
         <v>316</v>
       </c>
       <c r="F45" t="s">
-        <v>1642</v>
+        <v>1646</v>
       </c>
       <c r="G45" t="s">
-        <v>1653</v>
+        <v>1657</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
@@ -18296,7 +18334,7 @@
         <v>27</v>
       </c>
       <c r="B46" t="s">
-        <v>1526</v>
+        <v>1527</v>
       </c>
       <c r="C46" t="s">
         <v>375</v>
@@ -18308,10 +18346,10 @@
         <v>316</v>
       </c>
       <c r="F46" t="s">
-        <v>1642</v>
+        <v>1646</v>
       </c>
       <c r="G46" t="s">
-        <v>1654</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
@@ -18319,7 +18357,7 @@
         <v>27</v>
       </c>
       <c r="B47" t="s">
-        <v>1526</v>
+        <v>1527</v>
       </c>
       <c r="C47" t="s">
         <v>384</v>
@@ -18331,10 +18369,10 @@
         <v>316</v>
       </c>
       <c r="F47" t="s">
-        <v>1642</v>
+        <v>1646</v>
       </c>
       <c r="G47" t="s">
-        <v>1655</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
@@ -18342,7 +18380,7 @@
         <v>27</v>
       </c>
       <c r="B48" t="s">
-        <v>1526</v>
+        <v>1527</v>
       </c>
       <c r="C48" t="s">
         <v>393</v>
@@ -18354,10 +18392,10 @@
         <v>316</v>
       </c>
       <c r="F48" t="s">
-        <v>1642</v>
+        <v>1646</v>
       </c>
       <c r="G48" t="s">
-        <v>1656</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
@@ -18365,7 +18403,7 @@
         <v>27</v>
       </c>
       <c r="B49" t="s">
-        <v>1526</v>
+        <v>1527</v>
       </c>
       <c r="C49" t="s">
         <v>402</v>
@@ -18377,10 +18415,10 @@
         <v>316</v>
       </c>
       <c r="F49" t="s">
-        <v>1642</v>
+        <v>1646</v>
       </c>
       <c r="G49" t="s">
-        <v>1657</v>
+        <v>1661</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
@@ -18388,7 +18426,7 @@
         <v>27</v>
       </c>
       <c r="B50" t="s">
-        <v>1526</v>
+        <v>1527</v>
       </c>
       <c r="C50" t="s">
         <v>409</v>
@@ -18400,10 +18438,10 @@
         <v>316</v>
       </c>
       <c r="F50" t="s">
-        <v>1642</v>
+        <v>1646</v>
       </c>
       <c r="G50" t="s">
-        <v>1658</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
@@ -18411,7 +18449,7 @@
         <v>27</v>
       </c>
       <c r="B51" t="s">
-        <v>1526</v>
+        <v>1527</v>
       </c>
       <c r="C51" t="s">
         <v>418</v>
@@ -18423,10 +18461,10 @@
         <v>316</v>
       </c>
       <c r="F51" t="s">
-        <v>1642</v>
+        <v>1646</v>
       </c>
       <c r="G51" t="s">
-        <v>1659</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
@@ -18434,7 +18472,7 @@
         <v>27</v>
       </c>
       <c r="B52" t="s">
-        <v>1526</v>
+        <v>1527</v>
       </c>
       <c r="C52" t="s">
         <v>426</v>
@@ -18446,10 +18484,10 @@
         <v>316</v>
       </c>
       <c r="F52" t="s">
-        <v>1642</v>
+        <v>1646</v>
       </c>
       <c r="G52" t="s">
-        <v>1660</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
@@ -18457,7 +18495,7 @@
         <v>27</v>
       </c>
       <c r="B53" t="s">
-        <v>1526</v>
+        <v>1527</v>
       </c>
       <c r="C53" t="s">
         <v>433</v>
@@ -18469,10 +18507,10 @@
         <v>316</v>
       </c>
       <c r="F53" t="s">
-        <v>1642</v>
+        <v>1646</v>
       </c>
       <c r="G53" t="s">
-        <v>1661</v>
+        <v>1665</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
@@ -18480,7 +18518,7 @@
         <v>27</v>
       </c>
       <c r="B54" t="s">
-        <v>1526</v>
+        <v>1527</v>
       </c>
       <c r="C54" t="s">
         <v>465</v>
@@ -18492,10 +18530,10 @@
         <v>316</v>
       </c>
       <c r="F54" t="s">
-        <v>1642</v>
+        <v>1646</v>
       </c>
       <c r="G54" t="s">
-        <v>1662</v>
+        <v>1666</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
@@ -18503,7 +18541,7 @@
         <v>27</v>
       </c>
       <c r="B55" t="s">
-        <v>1526</v>
+        <v>1527</v>
       </c>
       <c r="C55" t="s">
         <v>481</v>
@@ -18515,10 +18553,10 @@
         <v>316</v>
       </c>
       <c r="F55" t="s">
-        <v>1642</v>
+        <v>1646</v>
       </c>
       <c r="G55" t="s">
-        <v>1663</v>
+        <v>1667</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
@@ -18526,7 +18564,7 @@
         <v>27</v>
       </c>
       <c r="B56" t="s">
-        <v>1526</v>
+        <v>1527</v>
       </c>
       <c r="C56" t="s">
         <v>492</v>
@@ -18538,10 +18576,10 @@
         <v>316</v>
       </c>
       <c r="F56" t="s">
-        <v>1642</v>
+        <v>1646</v>
       </c>
       <c r="G56" t="s">
-        <v>1664</v>
+        <v>1668</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
@@ -18549,7 +18587,7 @@
         <v>27</v>
       </c>
       <c r="B57" t="s">
-        <v>1526</v>
+        <v>1527</v>
       </c>
       <c r="C57" t="s">
         <v>501</v>
@@ -18561,10 +18599,10 @@
         <v>316</v>
       </c>
       <c r="F57" t="s">
-        <v>1642</v>
+        <v>1646</v>
       </c>
       <c r="G57" t="s">
-        <v>1665</v>
+        <v>1669</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
@@ -18572,7 +18610,7 @@
         <v>27</v>
       </c>
       <c r="B58" t="s">
-        <v>1526</v>
+        <v>1527</v>
       </c>
       <c r="C58" t="s">
         <v>509</v>
@@ -18584,10 +18622,10 @@
         <v>316</v>
       </c>
       <c r="F58" t="s">
-        <v>1642</v>
+        <v>1646</v>
       </c>
       <c r="G58" t="s">
-        <v>1666</v>
+        <v>1670</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
@@ -18595,7 +18633,7 @@
         <v>27</v>
       </c>
       <c r="B59" t="s">
-        <v>1526</v>
+        <v>1527</v>
       </c>
       <c r="C59" t="s">
         <v>518</v>
@@ -18607,10 +18645,10 @@
         <v>316</v>
       </c>
       <c r="F59" t="s">
-        <v>1642</v>
+        <v>1646</v>
       </c>
       <c r="G59" t="s">
-        <v>1667</v>
+        <v>1671</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
@@ -18618,7 +18656,7 @@
         <v>27</v>
       </c>
       <c r="B60" t="s">
-        <v>1526</v>
+        <v>1527</v>
       </c>
       <c r="C60" t="s">
         <v>527</v>
@@ -18630,10 +18668,10 @@
         <v>316</v>
       </c>
       <c r="F60" t="s">
-        <v>1642</v>
+        <v>1646</v>
       </c>
       <c r="G60" t="s">
-        <v>1668</v>
+        <v>1672</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
@@ -18641,7 +18679,7 @@
         <v>27</v>
       </c>
       <c r="B61" t="s">
-        <v>1526</v>
+        <v>1527</v>
       </c>
       <c r="C61" t="s">
         <v>537</v>
@@ -18653,10 +18691,10 @@
         <v>316</v>
       </c>
       <c r="F61" t="s">
-        <v>1642</v>
+        <v>1646</v>
       </c>
       <c r="G61" t="s">
-        <v>1669</v>
+        <v>1673</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
@@ -18664,7 +18702,7 @@
         <v>27</v>
       </c>
       <c r="B62" t="s">
-        <v>1526</v>
+        <v>1527</v>
       </c>
       <c r="C62" t="s">
         <v>546</v>
@@ -18676,10 +18714,10 @@
         <v>316</v>
       </c>
       <c r="F62" t="s">
-        <v>1642</v>
+        <v>1646</v>
       </c>
       <c r="G62" t="s">
-        <v>1670</v>
+        <v>1674</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
@@ -18687,7 +18725,7 @@
         <v>27</v>
       </c>
       <c r="B63" t="s">
-        <v>1526</v>
+        <v>1527</v>
       </c>
       <c r="C63" t="s">
         <v>554</v>
@@ -18699,10 +18737,10 @@
         <v>316</v>
       </c>
       <c r="F63" t="s">
-        <v>1642</v>
+        <v>1646</v>
       </c>
       <c r="G63" t="s">
-        <v>1671</v>
+        <v>1675</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
@@ -18710,7 +18748,7 @@
         <v>27</v>
       </c>
       <c r="B64" t="s">
-        <v>1526</v>
+        <v>1527</v>
       </c>
       <c r="C64" t="s">
         <v>564</v>
@@ -18722,10 +18760,10 @@
         <v>316</v>
       </c>
       <c r="F64" t="s">
-        <v>1642</v>
+        <v>1646</v>
       </c>
       <c r="G64" t="s">
-        <v>1672</v>
+        <v>1676</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
@@ -18733,7 +18771,7 @@
         <v>27</v>
       </c>
       <c r="B65" t="s">
-        <v>1526</v>
+        <v>1527</v>
       </c>
       <c r="C65" t="s">
         <v>574</v>
@@ -18745,10 +18783,10 @@
         <v>316</v>
       </c>
       <c r="F65" t="s">
-        <v>1642</v>
+        <v>1646</v>
       </c>
       <c r="G65" t="s">
-        <v>1673</v>
+        <v>1677</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
@@ -18756,7 +18794,7 @@
         <v>27</v>
       </c>
       <c r="B66" t="s">
-        <v>1526</v>
+        <v>1527</v>
       </c>
       <c r="C66" t="s">
         <v>583</v>
@@ -18768,10 +18806,10 @@
         <v>316</v>
       </c>
       <c r="F66" t="s">
-        <v>1642</v>
+        <v>1646</v>
       </c>
       <c r="G66" t="s">
-        <v>1674</v>
+        <v>1678</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
@@ -18779,7 +18817,7 @@
         <v>27</v>
       </c>
       <c r="B67" t="s">
-        <v>1526</v>
+        <v>1527</v>
       </c>
       <c r="C67" t="s">
         <v>591</v>
@@ -18791,10 +18829,10 @@
         <v>316</v>
       </c>
       <c r="F67" t="s">
-        <v>1642</v>
+        <v>1646</v>
       </c>
       <c r="G67" t="s">
-        <v>1675</v>
+        <v>1679</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
@@ -18802,7 +18840,7 @@
         <v>27</v>
       </c>
       <c r="B68" t="s">
-        <v>1526</v>
+        <v>1527</v>
       </c>
       <c r="C68" t="s">
         <v>601</v>
@@ -18814,10 +18852,10 @@
         <v>316</v>
       </c>
       <c r="F68" t="s">
-        <v>1642</v>
+        <v>1646</v>
       </c>
       <c r="G68" t="s">
-        <v>1676</v>
+        <v>1680</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
@@ -18825,7 +18863,7 @@
         <v>27</v>
       </c>
       <c r="B69" t="s">
-        <v>1526</v>
+        <v>1527</v>
       </c>
       <c r="C69" t="s">
         <v>609</v>
@@ -18837,10 +18875,10 @@
         <v>316</v>
       </c>
       <c r="F69" t="s">
-        <v>1642</v>
+        <v>1646</v>
       </c>
       <c r="G69" t="s">
-        <v>1677</v>
+        <v>1681</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
@@ -18848,7 +18886,7 @@
         <v>27</v>
       </c>
       <c r="B70" t="s">
-        <v>1526</v>
+        <v>1527</v>
       </c>
       <c r="C70" t="s">
         <v>618</v>
@@ -18860,10 +18898,10 @@
         <v>316</v>
       </c>
       <c r="F70" t="s">
-        <v>1642</v>
+        <v>1646</v>
       </c>
       <c r="G70" t="s">
-        <v>1678</v>
+        <v>1682</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
@@ -18871,7 +18909,7 @@
         <v>27</v>
       </c>
       <c r="B71" t="s">
-        <v>1526</v>
+        <v>1527</v>
       </c>
       <c r="C71" t="s">
         <v>625</v>
@@ -18883,10 +18921,10 @@
         <v>316</v>
       </c>
       <c r="F71" t="s">
-        <v>1642</v>
+        <v>1646</v>
       </c>
       <c r="G71" t="s">
-        <v>1679</v>
+        <v>1683</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
@@ -18894,7 +18932,7 @@
         <v>27</v>
       </c>
       <c r="B72" t="s">
-        <v>1526</v>
+        <v>1527</v>
       </c>
       <c r="C72" t="s">
         <v>636</v>
@@ -18906,10 +18944,10 @@
         <v>316</v>
       </c>
       <c r="F72" t="s">
-        <v>1642</v>
+        <v>1646</v>
       </c>
       <c r="G72" t="s">
-        <v>1680</v>
+        <v>1684</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
@@ -18917,7 +18955,7 @@
         <v>27</v>
       </c>
       <c r="B73" t="s">
-        <v>1526</v>
+        <v>1527</v>
       </c>
       <c r="C73" t="s">
         <v>646</v>
@@ -18929,10 +18967,10 @@
         <v>316</v>
       </c>
       <c r="F73" t="s">
-        <v>1642</v>
+        <v>1646</v>
       </c>
       <c r="G73" t="s">
-        <v>1681</v>
+        <v>1685</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
@@ -18940,7 +18978,7 @@
         <v>27</v>
       </c>
       <c r="B74" t="s">
-        <v>1526</v>
+        <v>1527</v>
       </c>
       <c r="C74" t="s">
         <v>655</v>
@@ -18952,10 +18990,10 @@
         <v>316</v>
       </c>
       <c r="F74" t="s">
-        <v>1642</v>
+        <v>1646</v>
       </c>
       <c r="G74" t="s">
-        <v>1682</v>
+        <v>1686</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
@@ -18963,7 +19001,7 @@
         <v>27</v>
       </c>
       <c r="B75" t="s">
-        <v>1526</v>
+        <v>1527</v>
       </c>
       <c r="C75" t="s">
         <v>664</v>
@@ -18975,10 +19013,10 @@
         <v>316</v>
       </c>
       <c r="F75" t="s">
-        <v>1642</v>
+        <v>1646</v>
       </c>
       <c r="G75" t="s">
-        <v>1683</v>
+        <v>1687</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
@@ -18986,7 +19024,7 @@
         <v>27</v>
       </c>
       <c r="B76" t="s">
-        <v>1526</v>
+        <v>1527</v>
       </c>
       <c r="C76" t="s">
         <v>672</v>
@@ -18998,10 +19036,10 @@
         <v>316</v>
       </c>
       <c r="F76" t="s">
-        <v>1642</v>
+        <v>1646</v>
       </c>
       <c r="G76" t="s">
-        <v>1684</v>
+        <v>1688</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
@@ -19009,7 +19047,7 @@
         <v>27</v>
       </c>
       <c r="B77" t="s">
-        <v>1526</v>
+        <v>1527</v>
       </c>
       <c r="C77" t="s">
         <v>680</v>
@@ -19021,10 +19059,10 @@
         <v>316</v>
       </c>
       <c r="F77" t="s">
-        <v>1642</v>
+        <v>1646</v>
       </c>
       <c r="G77" t="s">
-        <v>1685</v>
+        <v>1689</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
@@ -19032,7 +19070,7 @@
         <v>27</v>
       </c>
       <c r="B78" t="s">
-        <v>1526</v>
+        <v>1527</v>
       </c>
       <c r="C78" t="s">
         <v>688</v>
@@ -19044,10 +19082,10 @@
         <v>316</v>
       </c>
       <c r="F78" t="s">
-        <v>1642</v>
+        <v>1646</v>
       </c>
       <c r="G78" t="s">
-        <v>1686</v>
+        <v>1690</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
@@ -19055,7 +19093,7 @@
         <v>27</v>
       </c>
       <c r="B79" t="s">
-        <v>1526</v>
+        <v>1527</v>
       </c>
       <c r="C79" t="s">
         <v>696</v>
@@ -19067,10 +19105,10 @@
         <v>316</v>
       </c>
       <c r="F79" t="s">
-        <v>1642</v>
+        <v>1646</v>
       </c>
       <c r="G79" t="s">
-        <v>1687</v>
+        <v>1691</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
@@ -19078,7 +19116,7 @@
         <v>27</v>
       </c>
       <c r="B80" t="s">
-        <v>1532</v>
+        <v>1533</v>
       </c>
       <c r="C80" t="s">
         <v>704</v>
@@ -19090,10 +19128,10 @@
         <v>316</v>
       </c>
       <c r="F80" t="s">
-        <v>1688</v>
+        <v>1692</v>
       </c>
       <c r="G80" t="s">
-        <v>1689</v>
+        <v>1693</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
@@ -19101,7 +19139,7 @@
         <v>27</v>
       </c>
       <c r="B81" t="s">
-        <v>1532</v>
+        <v>1533</v>
       </c>
       <c r="C81" t="s">
         <v>715</v>
@@ -19113,10 +19151,10 @@
         <v>316</v>
       </c>
       <c r="F81" t="s">
-        <v>1688</v>
+        <v>1692</v>
       </c>
       <c r="G81" t="s">
-        <v>1690</v>
+        <v>1694</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
@@ -19124,7 +19162,7 @@
         <v>27</v>
       </c>
       <c r="B82" t="s">
-        <v>1532</v>
+        <v>1533</v>
       </c>
       <c r="C82" t="s">
         <v>722</v>
@@ -19136,10 +19174,10 @@
         <v>316</v>
       </c>
       <c r="F82" t="s">
-        <v>1688</v>
+        <v>1692</v>
       </c>
       <c r="G82" t="s">
-        <v>1691</v>
+        <v>1695</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
@@ -19147,7 +19185,7 @@
         <v>27</v>
       </c>
       <c r="B83" t="s">
-        <v>1532</v>
+        <v>1533</v>
       </c>
       <c r="C83" t="s">
         <v>730</v>
@@ -19159,10 +19197,10 @@
         <v>316</v>
       </c>
       <c r="F83" t="s">
-        <v>1688</v>
+        <v>1692</v>
       </c>
       <c r="G83" t="s">
-        <v>1692</v>
+        <v>1696</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
@@ -19170,7 +19208,7 @@
         <v>27</v>
       </c>
       <c r="B84" t="s">
-        <v>1532</v>
+        <v>1533</v>
       </c>
       <c r="C84" t="s">
         <v>739</v>
@@ -19182,10 +19220,10 @@
         <v>316</v>
       </c>
       <c r="F84" t="s">
-        <v>1688</v>
+        <v>1692</v>
       </c>
       <c r="G84" t="s">
-        <v>1693</v>
+        <v>1697</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
@@ -19193,7 +19231,7 @@
         <v>27</v>
       </c>
       <c r="B85" t="s">
-        <v>1694</v>
+        <v>1698</v>
       </c>
       <c r="C85" t="s">
         <v>330</v>
@@ -19205,10 +19243,10 @@
         <v>109</v>
       </c>
       <c r="F85" t="s">
-        <v>1695</v>
+        <v>1699</v>
       </c>
       <c r="G85" t="s">
-        <v>1696</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
@@ -19216,7 +19254,7 @@
         <v>27</v>
       </c>
       <c r="B86" t="s">
-        <v>1694</v>
+        <v>1698</v>
       </c>
       <c r="C86" t="s">
         <v>341</v>
@@ -19228,10 +19266,10 @@
         <v>109</v>
       </c>
       <c r="F86" t="s">
-        <v>1695</v>
+        <v>1699</v>
       </c>
       <c r="G86" t="s">
-        <v>1697</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
@@ -19239,7 +19277,7 @@
         <v>27</v>
       </c>
       <c r="B87" t="s">
-        <v>1694</v>
+        <v>1698</v>
       </c>
       <c r="C87" t="s">
         <v>350</v>
@@ -19251,10 +19289,10 @@
         <v>109</v>
       </c>
       <c r="F87" t="s">
-        <v>1695</v>
+        <v>1699</v>
       </c>
       <c r="G87" t="s">
-        <v>1698</v>
+        <v>1702</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
@@ -19262,7 +19300,7 @@
         <v>27</v>
       </c>
       <c r="B88" t="s">
-        <v>1694</v>
+        <v>1698</v>
       </c>
       <c r="C88" t="s">
         <v>375</v>
@@ -19274,10 +19312,10 @@
         <v>115</v>
       </c>
       <c r="F88" t="s">
-        <v>1695</v>
+        <v>1699</v>
       </c>
       <c r="G88" t="s">
-        <v>1699</v>
+        <v>1703</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
@@ -19297,10 +19335,10 @@
         <v>316</v>
       </c>
       <c r="F89" t="s">
-        <v>1700</v>
+        <v>1704</v>
       </c>
       <c r="G89" t="s">
-        <v>1701</v>
+        <v>1705</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
@@ -19308,7 +19346,7 @@
         <v>27</v>
       </c>
       <c r="B90" t="s">
-        <v>1694</v>
+        <v>1698</v>
       </c>
       <c r="C90" t="s">
         <v>625</v>
@@ -19320,10 +19358,10 @@
         <v>115</v>
       </c>
       <c r="F90" t="s">
-        <v>1695</v>
+        <v>1699</v>
       </c>
       <c r="G90" t="s">
-        <v>1702</v>
+        <v>1706</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
@@ -19331,7 +19369,7 @@
         <v>27</v>
       </c>
       <c r="B91" t="s">
-        <v>1694</v>
+        <v>1698</v>
       </c>
       <c r="C91" t="s">
         <v>646</v>
@@ -19343,10 +19381,10 @@
         <v>109</v>
       </c>
       <c r="F91" t="s">
-        <v>1695</v>
+        <v>1699</v>
       </c>
       <c r="G91" t="s">
-        <v>1703</v>
+        <v>1707</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
@@ -19354,7 +19392,7 @@
         <v>27</v>
       </c>
       <c r="B92" t="s">
-        <v>1694</v>
+        <v>1698</v>
       </c>
       <c r="C92" t="s">
         <v>655</v>
@@ -19366,10 +19404,10 @@
         <v>115</v>
       </c>
       <c r="F92" t="s">
-        <v>1695</v>
+        <v>1699</v>
       </c>
       <c r="G92" t="s">
-        <v>1704</v>
+        <v>1708</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
@@ -19389,10 +19427,10 @@
         <v>109</v>
       </c>
       <c r="F93" t="s">
-        <v>1700</v>
+        <v>1704</v>
       </c>
       <c r="G93" t="s">
-        <v>1705</v>
+        <v>1709</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
@@ -19400,7 +19438,7 @@
         <v>27</v>
       </c>
       <c r="B94" t="s">
-        <v>1694</v>
+        <v>1698</v>
       </c>
       <c r="C94" t="s">
         <v>664</v>
@@ -19412,10 +19450,10 @@
         <v>115</v>
       </c>
       <c r="F94" t="s">
-        <v>1695</v>
+        <v>1699</v>
       </c>
       <c r="G94" t="s">
-        <v>1706</v>
+        <v>1710</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
@@ -19423,7 +19461,7 @@
         <v>27</v>
       </c>
       <c r="B95" t="s">
-        <v>1694</v>
+        <v>1698</v>
       </c>
       <c r="C95" t="s">
         <v>680</v>
@@ -19435,10 +19473,10 @@
         <v>115</v>
       </c>
       <c r="F95" t="s">
-        <v>1695</v>
+        <v>1699</v>
       </c>
       <c r="G95" t="s">
-        <v>1707</v>
+        <v>1711</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
@@ -19458,10 +19496,10 @@
         <v>316</v>
       </c>
       <c r="F96" t="s">
-        <v>1700</v>
+        <v>1704</v>
       </c>
       <c r="G96" t="s">
-        <v>1708</v>
+        <v>1712</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
@@ -19469,7 +19507,7 @@
         <v>27</v>
       </c>
       <c r="B97" t="s">
-        <v>1694</v>
+        <v>1698</v>
       </c>
       <c r="C97" t="s">
         <v>696</v>
@@ -19481,10 +19519,10 @@
         <v>115</v>
       </c>
       <c r="F97" t="s">
-        <v>1695</v>
+        <v>1699</v>
       </c>
       <c r="G97" t="s">
-        <v>1709</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
@@ -19492,7 +19530,7 @@
         <v>27</v>
       </c>
       <c r="B98" t="s">
-        <v>1694</v>
+        <v>1698</v>
       </c>
       <c r="C98" t="s">
         <v>704</v>
@@ -19504,10 +19542,10 @@
         <v>115</v>
       </c>
       <c r="F98" t="s">
-        <v>1695</v>
+        <v>1699</v>
       </c>
       <c r="G98" t="s">
-        <v>1710</v>
+        <v>1714</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
@@ -19527,10 +19565,10 @@
         <v>316</v>
       </c>
       <c r="F99" t="s">
-        <v>1700</v>
+        <v>1704</v>
       </c>
       <c r="G99" t="s">
-        <v>1711</v>
+        <v>1715</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
@@ -19538,7 +19576,7 @@
         <v>27</v>
       </c>
       <c r="B100" t="s">
-        <v>1694</v>
+        <v>1698</v>
       </c>
       <c r="C100" t="s">
         <v>715</v>
@@ -19550,10 +19588,10 @@
         <v>115</v>
       </c>
       <c r="F100" t="s">
-        <v>1695</v>
+        <v>1699</v>
       </c>
       <c r="G100" t="s">
-        <v>1712</v>
+        <v>1716</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
@@ -19573,10 +19611,10 @@
         <v>109</v>
       </c>
       <c r="F101" t="s">
-        <v>1700</v>
+        <v>1704</v>
       </c>
       <c r="G101" t="s">
-        <v>1713</v>
+        <v>1717</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
@@ -19584,7 +19622,7 @@
         <v>27</v>
       </c>
       <c r="B102" t="s">
-        <v>1694</v>
+        <v>1698</v>
       </c>
       <c r="C102" t="s">
         <v>722</v>
@@ -19596,10 +19634,10 @@
         <v>115</v>
       </c>
       <c r="F102" t="s">
-        <v>1695</v>
+        <v>1699</v>
       </c>
       <c r="G102" t="s">
-        <v>1714</v>
+        <v>1718</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
@@ -19619,10 +19657,10 @@
         <v>109</v>
       </c>
       <c r="F103" t="s">
-        <v>1700</v>
+        <v>1704</v>
       </c>
       <c r="G103" t="s">
-        <v>1715</v>
+        <v>1719</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
@@ -19630,7 +19668,7 @@
         <v>27</v>
       </c>
       <c r="B104" t="s">
-        <v>1694</v>
+        <v>1698</v>
       </c>
       <c r="C104" t="s">
         <v>730</v>
@@ -19642,10 +19680,10 @@
         <v>115</v>
       </c>
       <c r="F104" t="s">
-        <v>1695</v>
+        <v>1699</v>
       </c>
       <c r="G104" t="s">
-        <v>1716</v>
+        <v>1720</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
@@ -19665,10 +19703,10 @@
         <v>316</v>
       </c>
       <c r="F105" t="s">
-        <v>1700</v>
+        <v>1704</v>
       </c>
       <c r="G105" t="s">
-        <v>1717</v>
+        <v>1721</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
@@ -19676,7 +19714,7 @@
         <v>27</v>
       </c>
       <c r="B106" t="s">
-        <v>1694</v>
+        <v>1698</v>
       </c>
       <c r="C106" t="s">
         <v>739</v>
@@ -19688,10 +19726,10 @@
         <v>115</v>
       </c>
       <c r="F106" t="s">
-        <v>1695</v>
+        <v>1699</v>
       </c>
       <c r="G106" t="s">
-        <v>1718</v>
+        <v>1722</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
@@ -19711,10 +19749,10 @@
         <v>316</v>
       </c>
       <c r="F107" t="s">
-        <v>1700</v>
+        <v>1704</v>
       </c>
       <c r="G107" t="s">
-        <v>1719</v>
+        <v>1723</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
@@ -19728,13 +19766,13 @@
         <v>747</v>
       </c>
       <c r="D108" t="s">
-        <v>1720</v>
+        <v>1724</v>
       </c>
       <c r="E108" t="s">
         <v>115</v>
       </c>
       <c r="F108" t="s">
-        <v>1700</v>
+        <v>1704</v>
       </c>
       <c r="G108" t="s">
         <v>748</v>
@@ -19751,13 +19789,13 @@
         <v>758</v>
       </c>
       <c r="D109" t="s">
-        <v>1720</v>
+        <v>1724</v>
       </c>
       <c r="E109" t="s">
         <v>115</v>
       </c>
       <c r="F109" t="s">
-        <v>1700</v>
+        <v>1704</v>
       </c>
       <c r="G109" t="s">
         <v>759</v>
@@ -19774,13 +19812,13 @@
         <v>766</v>
       </c>
       <c r="D110" t="s">
-        <v>1720</v>
+        <v>1724</v>
       </c>
       <c r="E110" t="s">
         <v>115</v>
       </c>
       <c r="F110" t="s">
-        <v>1700</v>
+        <v>1704</v>
       </c>
       <c r="G110" t="s">
         <v>767</v>
@@ -19797,13 +19835,13 @@
         <v>774</v>
       </c>
       <c r="D111" t="s">
-        <v>1720</v>
+        <v>1724</v>
       </c>
       <c r="E111" t="s">
         <v>115</v>
       </c>
       <c r="F111" t="s">
-        <v>1700</v>
+        <v>1704</v>
       </c>
       <c r="G111" t="s">
         <v>775</v>
@@ -19820,13 +19858,13 @@
         <v>782</v>
       </c>
       <c r="D112" t="s">
-        <v>1720</v>
+        <v>1724</v>
       </c>
       <c r="E112" t="s">
         <v>115</v>
       </c>
       <c r="F112" t="s">
-        <v>1700</v>
+        <v>1704</v>
       </c>
       <c r="G112" t="s">
         <v>783</v>
@@ -19843,13 +19881,13 @@
         <v>790</v>
       </c>
       <c r="D113" t="s">
-        <v>1720</v>
+        <v>1724</v>
       </c>
       <c r="E113" t="s">
         <v>115</v>
       </c>
       <c r="F113" t="s">
-        <v>1700</v>
+        <v>1704</v>
       </c>
       <c r="G113" t="s">
         <v>791</v>
@@ -19866,13 +19904,13 @@
         <v>798</v>
       </c>
       <c r="D114" t="s">
-        <v>1720</v>
+        <v>1724</v>
       </c>
       <c r="E114" t="s">
         <v>115</v>
       </c>
       <c r="F114" t="s">
-        <v>1700</v>
+        <v>1704</v>
       </c>
       <c r="G114" t="s">
         <v>799</v>
@@ -19889,13 +19927,13 @@
         <v>807</v>
       </c>
       <c r="D115" t="s">
-        <v>1720</v>
+        <v>1724</v>
       </c>
       <c r="E115" t="s">
         <v>115</v>
       </c>
       <c r="F115" t="s">
-        <v>1700</v>
+        <v>1704</v>
       </c>
       <c r="G115" t="s">
         <v>808</v>
@@ -19912,13 +19950,13 @@
         <v>815</v>
       </c>
       <c r="D116" t="s">
-        <v>1720</v>
+        <v>1724</v>
       </c>
       <c r="E116" t="s">
         <v>115</v>
       </c>
       <c r="F116" t="s">
-        <v>1700</v>
+        <v>1704</v>
       </c>
       <c r="G116" t="s">
         <v>816</v>
@@ -19935,13 +19973,13 @@
         <v>823</v>
       </c>
       <c r="D117" t="s">
-        <v>1720</v>
+        <v>1724</v>
       </c>
       <c r="E117" t="s">
         <v>115</v>
       </c>
       <c r="F117" t="s">
-        <v>1700</v>
+        <v>1704</v>
       </c>
       <c r="G117" t="s">
         <v>824</v>
@@ -19958,13 +19996,13 @@
         <v>831</v>
       </c>
       <c r="D118" t="s">
-        <v>1720</v>
+        <v>1724</v>
       </c>
       <c r="E118" t="s">
         <v>115</v>
       </c>
       <c r="F118" t="s">
-        <v>1700</v>
+        <v>1704</v>
       </c>
       <c r="G118" t="s">
         <v>833</v>
@@ -19981,13 +20019,13 @@
         <v>840</v>
       </c>
       <c r="D119" t="s">
-        <v>1720</v>
+        <v>1724</v>
       </c>
       <c r="E119" t="s">
         <v>115</v>
       </c>
       <c r="F119" t="s">
-        <v>1700</v>
+        <v>1704</v>
       </c>
       <c r="G119" t="s">
         <v>841</v>
@@ -20004,13 +20042,13 @@
         <v>848</v>
       </c>
       <c r="D120" t="s">
-        <v>1720</v>
+        <v>1724</v>
       </c>
       <c r="E120" t="s">
         <v>115</v>
       </c>
       <c r="F120" t="s">
-        <v>1700</v>
+        <v>1704</v>
       </c>
       <c r="G120" t="s">
         <v>849</v>
@@ -20027,13 +20065,13 @@
         <v>856</v>
       </c>
       <c r="D121" t="s">
-        <v>1720</v>
+        <v>1724</v>
       </c>
       <c r="E121" t="s">
         <v>115</v>
       </c>
       <c r="F121" t="s">
-        <v>1700</v>
+        <v>1704</v>
       </c>
       <c r="G121" t="s">
         <v>857</v>
@@ -20050,13 +20088,13 @@
         <v>864</v>
       </c>
       <c r="D122" t="s">
-        <v>1720</v>
+        <v>1724</v>
       </c>
       <c r="E122" t="s">
         <v>316</v>
       </c>
       <c r="F122" t="s">
-        <v>1700</v>
+        <v>1704</v>
       </c>
       <c r="G122" t="s">
         <v>865</v>
@@ -20073,13 +20111,13 @@
         <v>872</v>
       </c>
       <c r="D123" t="s">
-        <v>1720</v>
+        <v>1724</v>
       </c>
       <c r="E123" t="s">
         <v>115</v>
       </c>
       <c r="F123" t="s">
-        <v>1700</v>
+        <v>1704</v>
       </c>
       <c r="G123" t="s">
         <v>873</v>
@@ -20096,13 +20134,13 @@
         <v>880</v>
       </c>
       <c r="D124" t="s">
-        <v>1720</v>
+        <v>1724</v>
       </c>
       <c r="E124" t="s">
         <v>115</v>
       </c>
       <c r="F124" t="s">
-        <v>1700</v>
+        <v>1704</v>
       </c>
       <c r="G124" t="s">
         <v>881</v>
@@ -20119,13 +20157,13 @@
         <v>888</v>
       </c>
       <c r="D125" t="s">
-        <v>1720</v>
+        <v>1724</v>
       </c>
       <c r="E125" t="s">
         <v>115</v>
       </c>
       <c r="F125" t="s">
-        <v>1700</v>
+        <v>1704</v>
       </c>
       <c r="G125" t="s">
         <v>890</v>
@@ -20142,13 +20180,13 @@
         <v>897</v>
       </c>
       <c r="D126" t="s">
-        <v>1720</v>
+        <v>1724</v>
       </c>
       <c r="E126" t="s">
         <v>115</v>
       </c>
       <c r="F126" t="s">
-        <v>1700</v>
+        <v>1704</v>
       </c>
       <c r="G126" t="s">
         <v>898</v>
@@ -20165,13 +20203,13 @@
         <v>906</v>
       </c>
       <c r="D127" t="s">
-        <v>1720</v>
+        <v>1724</v>
       </c>
       <c r="E127" t="s">
         <v>115</v>
       </c>
       <c r="F127" t="s">
-        <v>1700</v>
+        <v>1704</v>
       </c>
       <c r="G127" t="s">
         <v>907</v>
@@ -20188,13 +20226,13 @@
         <v>914</v>
       </c>
       <c r="D128" t="s">
-        <v>1720</v>
+        <v>1724</v>
       </c>
       <c r="E128" t="s">
         <v>459</v>
       </c>
       <c r="F128" t="s">
-        <v>1700</v>
+        <v>1704</v>
       </c>
       <c r="G128" t="s">
         <v>915</v>
@@ -20211,13 +20249,13 @@
         <v>922</v>
       </c>
       <c r="D129" t="s">
-        <v>1720</v>
+        <v>1724</v>
       </c>
       <c r="E129" t="s">
         <v>115</v>
       </c>
       <c r="F129" t="s">
-        <v>1700</v>
+        <v>1704</v>
       </c>
       <c r="G129" t="s">
         <v>923</v>
@@ -20234,13 +20272,13 @@
         <v>930</v>
       </c>
       <c r="D130" t="s">
-        <v>1720</v>
+        <v>1724</v>
       </c>
       <c r="E130" t="s">
         <v>115</v>
       </c>
       <c r="F130" t="s">
-        <v>1700</v>
+        <v>1704</v>
       </c>
       <c r="G130" t="s">
         <v>931</v>
@@ -20257,13 +20295,13 @@
         <v>940</v>
       </c>
       <c r="D131" t="s">
-        <v>1720</v>
+        <v>1724</v>
       </c>
       <c r="E131" t="s">
         <v>115</v>
       </c>
       <c r="F131" t="s">
-        <v>1700</v>
+        <v>1704</v>
       </c>
       <c r="G131" t="s">
         <v>941</v>
@@ -20280,13 +20318,13 @@
         <v>948</v>
       </c>
       <c r="D132" t="s">
-        <v>1720</v>
+        <v>1724</v>
       </c>
       <c r="E132" t="s">
         <v>115</v>
       </c>
       <c r="F132" t="s">
-        <v>1700</v>
+        <v>1704</v>
       </c>
       <c r="G132" t="s">
         <v>949</v>
@@ -20303,13 +20341,13 @@
         <v>956</v>
       </c>
       <c r="D133" t="s">
-        <v>1720</v>
+        <v>1724</v>
       </c>
       <c r="E133" t="s">
         <v>115</v>
       </c>
       <c r="F133" t="s">
-        <v>1700</v>
+        <v>1704</v>
       </c>
       <c r="G133" t="s">
         <v>957</v>
@@ -20326,13 +20364,13 @@
         <v>964</v>
       </c>
       <c r="D134" t="s">
-        <v>1720</v>
+        <v>1724</v>
       </c>
       <c r="E134" t="s">
         <v>115</v>
       </c>
       <c r="F134" t="s">
-        <v>1700</v>
+        <v>1704</v>
       </c>
       <c r="G134" t="s">
         <v>965</v>
@@ -20349,13 +20387,13 @@
         <v>972</v>
       </c>
       <c r="D135" t="s">
-        <v>1720</v>
+        <v>1724</v>
       </c>
       <c r="E135" t="s">
         <v>115</v>
       </c>
       <c r="F135" t="s">
-        <v>1700</v>
+        <v>1704</v>
       </c>
       <c r="G135" t="s">
         <v>974</v>
@@ -20372,13 +20410,13 @@
         <v>981</v>
       </c>
       <c r="D136" t="s">
-        <v>1720</v>
+        <v>1724</v>
       </c>
       <c r="E136" t="s">
         <v>115</v>
       </c>
       <c r="F136" t="s">
-        <v>1700</v>
+        <v>1704</v>
       </c>
       <c r="G136" t="s">
         <v>982</v>
@@ -20395,13 +20433,13 @@
         <v>989</v>
       </c>
       <c r="D137" t="s">
-        <v>1720</v>
+        <v>1724</v>
       </c>
       <c r="E137" t="s">
         <v>115</v>
       </c>
       <c r="F137" t="s">
-        <v>1700</v>
+        <v>1704</v>
       </c>
       <c r="G137" t="s">
         <v>990</v>
@@ -20418,13 +20456,13 @@
         <v>997</v>
       </c>
       <c r="D138" t="s">
-        <v>1720</v>
+        <v>1724</v>
       </c>
       <c r="E138" t="s">
         <v>115</v>
       </c>
       <c r="F138" t="s">
-        <v>1700</v>
+        <v>1704</v>
       </c>
       <c r="G138" t="s">
         <v>998</v>
@@ -20441,13 +20479,13 @@
         <v>1005</v>
       </c>
       <c r="D139" t="s">
-        <v>1720</v>
+        <v>1724</v>
       </c>
       <c r="E139" t="s">
         <v>115</v>
       </c>
       <c r="F139" t="s">
-        <v>1700</v>
+        <v>1704</v>
       </c>
       <c r="G139" t="s">
         <v>1006</v>
@@ -20464,13 +20502,13 @@
         <v>1013</v>
       </c>
       <c r="D140" t="s">
-        <v>1720</v>
+        <v>1724</v>
       </c>
       <c r="E140" t="s">
         <v>115</v>
       </c>
       <c r="F140" t="s">
-        <v>1700</v>
+        <v>1704</v>
       </c>
       <c r="G140" t="s">
         <v>1014</v>
@@ -20487,13 +20525,13 @@
         <v>1022</v>
       </c>
       <c r="D141" t="s">
-        <v>1720</v>
+        <v>1724</v>
       </c>
       <c r="E141" t="s">
         <v>115</v>
       </c>
       <c r="F141" t="s">
-        <v>1700</v>
+        <v>1704</v>
       </c>
       <c r="G141" t="s">
         <v>1023</v>
@@ -20510,13 +20548,13 @@
         <v>1030</v>
       </c>
       <c r="D142" t="s">
-        <v>1720</v>
+        <v>1724</v>
       </c>
       <c r="E142" t="s">
         <v>115</v>
       </c>
       <c r="F142" t="s">
-        <v>1700</v>
+        <v>1704</v>
       </c>
       <c r="G142" t="s">
         <v>1031</v>
@@ -20533,13 +20571,13 @@
         <v>1038</v>
       </c>
       <c r="D143" t="s">
-        <v>1720</v>
+        <v>1724</v>
       </c>
       <c r="E143" t="s">
         <v>459</v>
       </c>
       <c r="F143" t="s">
-        <v>1700</v>
+        <v>1704</v>
       </c>
       <c r="G143" t="s">
         <v>1039</v>
@@ -20556,13 +20594,13 @@
         <v>1046</v>
       </c>
       <c r="D144" t="s">
-        <v>1720</v>
+        <v>1724</v>
       </c>
       <c r="E144" t="s">
         <v>115</v>
       </c>
       <c r="F144" t="s">
-        <v>1700</v>
+        <v>1704</v>
       </c>
       <c r="G144" t="s">
         <v>1048</v>
@@ -20579,13 +20617,13 @@
         <v>1055</v>
       </c>
       <c r="D145" t="s">
-        <v>1720</v>
+        <v>1724</v>
       </c>
       <c r="E145" t="s">
         <v>115</v>
       </c>
       <c r="F145" t="s">
-        <v>1700</v>
+        <v>1704</v>
       </c>
       <c r="G145" t="s">
         <v>1056</v>
@@ -20602,13 +20640,13 @@
         <v>1063</v>
       </c>
       <c r="D146" t="s">
-        <v>1720</v>
+        <v>1724</v>
       </c>
       <c r="E146" t="s">
         <v>115</v>
       </c>
       <c r="F146" t="s">
-        <v>1700</v>
+        <v>1704</v>
       </c>
       <c r="G146" t="s">
         <v>1064</v>
@@ -20625,13 +20663,13 @@
         <v>1071</v>
       </c>
       <c r="D147" t="s">
-        <v>1720</v>
+        <v>1724</v>
       </c>
       <c r="E147" t="s">
         <v>115</v>
       </c>
       <c r="F147" t="s">
-        <v>1700</v>
+        <v>1704</v>
       </c>
       <c r="G147" t="s">
         <v>1073</v>
@@ -20648,13 +20686,13 @@
         <v>1080</v>
       </c>
       <c r="D148" t="s">
-        <v>1720</v>
+        <v>1724</v>
       </c>
       <c r="E148" t="s">
         <v>115</v>
       </c>
       <c r="F148" t="s">
-        <v>1700</v>
+        <v>1704</v>
       </c>
       <c r="G148" t="s">
         <v>1081</v>
@@ -20671,13 +20709,13 @@
         <v>1088</v>
       </c>
       <c r="D149" t="s">
-        <v>1720</v>
+        <v>1724</v>
       </c>
       <c r="E149" t="s">
         <v>86</v>
       </c>
       <c r="F149" t="s">
-        <v>1700</v>
+        <v>1704</v>
       </c>
       <c r="G149" t="s">
         <v>1089</v>
@@ -20694,13 +20732,13 @@
         <v>1096</v>
       </c>
       <c r="D150" t="s">
-        <v>1720</v>
+        <v>1724</v>
       </c>
       <c r="E150" t="s">
         <v>115</v>
       </c>
       <c r="F150" t="s">
-        <v>1700</v>
+        <v>1704</v>
       </c>
       <c r="G150" t="s">
         <v>1098</v>
@@ -20717,13 +20755,13 @@
         <v>1105</v>
       </c>
       <c r="D151" t="s">
-        <v>1720</v>
+        <v>1724</v>
       </c>
       <c r="E151" t="s">
         <v>86</v>
       </c>
       <c r="F151" t="s">
-        <v>1700</v>
+        <v>1704</v>
       </c>
       <c r="G151" t="s">
         <v>1106</v>
@@ -20740,13 +20778,13 @@
         <v>1114</v>
       </c>
       <c r="D152" t="s">
-        <v>1720</v>
+        <v>1724</v>
       </c>
       <c r="E152" t="s">
         <v>115</v>
       </c>
       <c r="F152" t="s">
-        <v>1700</v>
+        <v>1704</v>
       </c>
       <c r="G152" t="s">
         <v>1115</v>
@@ -20763,13 +20801,13 @@
         <v>1123</v>
       </c>
       <c r="D153" t="s">
-        <v>1720</v>
+        <v>1724</v>
       </c>
       <c r="E153" t="s">
         <v>115</v>
       </c>
       <c r="F153" t="s">
-        <v>1700</v>
+        <v>1704</v>
       </c>
       <c r="G153" t="s">
         <v>1124</v>
@@ -20786,13 +20824,13 @@
         <v>1131</v>
       </c>
       <c r="D154" t="s">
-        <v>1720</v>
+        <v>1724</v>
       </c>
       <c r="E154" t="s">
         <v>459</v>
       </c>
       <c r="F154" t="s">
-        <v>1700</v>
+        <v>1704</v>
       </c>
       <c r="G154" t="s">
         <v>1132</v>
@@ -20809,13 +20847,13 @@
         <v>1139</v>
       </c>
       <c r="D155" t="s">
-        <v>1720</v>
+        <v>1724</v>
       </c>
       <c r="E155" t="s">
         <v>115</v>
       </c>
       <c r="F155" t="s">
-        <v>1700</v>
+        <v>1704</v>
       </c>
       <c r="G155" t="s">
         <v>1140</v>
@@ -20832,13 +20870,13 @@
         <v>1147</v>
       </c>
       <c r="D156" t="s">
-        <v>1720</v>
+        <v>1724</v>
       </c>
       <c r="E156" t="s">
         <v>86</v>
       </c>
       <c r="F156" t="s">
-        <v>1700</v>
+        <v>1704</v>
       </c>
       <c r="G156" t="s">
         <v>1148</v>
@@ -20852,19 +20890,19 @@
         <v>1116</v>
       </c>
       <c r="C157" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="D157" t="s">
-        <v>1720</v>
+        <v>1724</v>
       </c>
       <c r="E157" t="s">
         <v>115</v>
       </c>
       <c r="F157" t="s">
-        <v>1700</v>
+        <v>1704</v>
       </c>
       <c r="G157" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.25">
@@ -20872,22 +20910,22 @@
         <v>27</v>
       </c>
       <c r="B158" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="C158" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="D158" t="s">
-        <v>1720</v>
+        <v>1724</v>
       </c>
       <c r="E158" t="s">
         <v>115</v>
       </c>
       <c r="F158" t="s">
-        <v>1700</v>
+        <v>1704</v>
       </c>
       <c r="G158" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.25">
@@ -20895,22 +20933,22 @@
         <v>27</v>
       </c>
       <c r="B159" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="C159" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="D159" t="s">
-        <v>1720</v>
+        <v>1724</v>
       </c>
       <c r="E159" t="s">
         <v>115</v>
       </c>
       <c r="F159" t="s">
-        <v>1700</v>
+        <v>1704</v>
       </c>
       <c r="G159" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.25">
@@ -20918,22 +20956,22 @@
         <v>27</v>
       </c>
       <c r="B160" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="C160" t="s">
-        <v>1180</v>
+        <v>1181</v>
       </c>
       <c r="D160" t="s">
-        <v>1720</v>
+        <v>1724</v>
       </c>
       <c r="E160" t="s">
         <v>115</v>
       </c>
       <c r="F160" t="s">
-        <v>1700</v>
+        <v>1704</v>
       </c>
       <c r="G160" t="s">
-        <v>1181</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.25">
@@ -20941,22 +20979,22 @@
         <v>27</v>
       </c>
       <c r="B161" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="C161" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="D161" t="s">
-        <v>1720</v>
+        <v>1724</v>
       </c>
       <c r="E161" t="s">
         <v>86</v>
       </c>
       <c r="F161" t="s">
-        <v>1700</v>
+        <v>1704</v>
       </c>
       <c r="G161" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.25">
@@ -20964,22 +21002,22 @@
         <v>27</v>
       </c>
       <c r="B162" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="C162" t="s">
-        <v>1197</v>
+        <v>1198</v>
       </c>
       <c r="D162" t="s">
-        <v>1720</v>
+        <v>1724</v>
       </c>
       <c r="E162" t="s">
         <v>115</v>
       </c>
       <c r="F162" t="s">
-        <v>1700</v>
+        <v>1704</v>
       </c>
       <c r="G162" t="s">
-        <v>1199</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.25">
@@ -20987,22 +21025,22 @@
         <v>27</v>
       </c>
       <c r="B163" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="C163" t="s">
-        <v>1206</v>
+        <v>1207</v>
       </c>
       <c r="D163" t="s">
-        <v>1720</v>
+        <v>1724</v>
       </c>
       <c r="E163" t="s">
         <v>115</v>
       </c>
       <c r="F163" t="s">
-        <v>1700</v>
+        <v>1704</v>
       </c>
       <c r="G163" t="s">
-        <v>1207</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.25">
@@ -21010,22 +21048,22 @@
         <v>27</v>
       </c>
       <c r="B164" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="C164" t="s">
-        <v>1214</v>
+        <v>1215</v>
       </c>
       <c r="D164" t="s">
-        <v>1720</v>
+        <v>1724</v>
       </c>
       <c r="E164" t="s">
         <v>115</v>
       </c>
       <c r="F164" t="s">
-        <v>1700</v>
+        <v>1704</v>
       </c>
       <c r="G164" t="s">
-        <v>1215</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.25">
@@ -21033,22 +21071,22 @@
         <v>27</v>
       </c>
       <c r="B165" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="C165" t="s">
-        <v>1222</v>
+        <v>1223</v>
       </c>
       <c r="D165" t="s">
-        <v>1720</v>
+        <v>1724</v>
       </c>
       <c r="E165" t="s">
         <v>115</v>
       </c>
       <c r="F165" t="s">
-        <v>1700</v>
+        <v>1704</v>
       </c>
       <c r="G165" t="s">
-        <v>1223</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.25">
@@ -21056,22 +21094,22 @@
         <v>27</v>
       </c>
       <c r="B166" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="C166" t="s">
-        <v>1230</v>
+        <v>1231</v>
       </c>
       <c r="D166" t="s">
-        <v>1720</v>
+        <v>1724</v>
       </c>
       <c r="E166" t="s">
         <v>86</v>
       </c>
       <c r="F166" t="s">
-        <v>1700</v>
+        <v>1704</v>
       </c>
       <c r="G166" t="s">
-        <v>1231</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.25">
@@ -21079,22 +21117,22 @@
         <v>27</v>
       </c>
       <c r="B167" t="s">
-        <v>1240</v>
+        <v>1241</v>
       </c>
       <c r="C167" t="s">
-        <v>1238</v>
+        <v>1239</v>
       </c>
       <c r="D167" t="s">
-        <v>1720</v>
+        <v>1724</v>
       </c>
       <c r="E167" t="s">
         <v>115</v>
       </c>
       <c r="F167" t="s">
-        <v>1700</v>
+        <v>1704</v>
       </c>
       <c r="G167" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.25">
@@ -21102,22 +21140,22 @@
         <v>27</v>
       </c>
       <c r="B168" t="s">
-        <v>1240</v>
+        <v>1241</v>
       </c>
       <c r="C168" t="s">
-        <v>1247</v>
+        <v>1248</v>
       </c>
       <c r="D168" t="s">
-        <v>1720</v>
+        <v>1724</v>
       </c>
       <c r="E168" t="s">
         <v>115</v>
       </c>
       <c r="F168" t="s">
-        <v>1700</v>
+        <v>1704</v>
       </c>
       <c r="G168" t="s">
-        <v>1248</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.25">
@@ -21125,22 +21163,22 @@
         <v>27</v>
       </c>
       <c r="B169" t="s">
-        <v>1240</v>
+        <v>1241</v>
       </c>
       <c r="C169" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
       <c r="D169" t="s">
-        <v>1720</v>
+        <v>1724</v>
       </c>
       <c r="E169" t="s">
         <v>115</v>
       </c>
       <c r="F169" t="s">
-        <v>1700</v>
+        <v>1704</v>
       </c>
       <c r="G169" t="s">
-        <v>1256</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.25">
@@ -21148,22 +21186,22 @@
         <v>27</v>
       </c>
       <c r="B170" t="s">
-        <v>1240</v>
+        <v>1241</v>
       </c>
       <c r="C170" t="s">
-        <v>1263</v>
+        <v>1264</v>
       </c>
       <c r="D170" t="s">
-        <v>1720</v>
+        <v>1724</v>
       </c>
       <c r="E170" t="s">
         <v>115</v>
       </c>
       <c r="F170" t="s">
-        <v>1700</v>
+        <v>1704</v>
       </c>
       <c r="G170" t="s">
-        <v>1264</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.25">
@@ -21171,22 +21209,22 @@
         <v>27</v>
       </c>
       <c r="B171" t="s">
-        <v>1240</v>
+        <v>1241</v>
       </c>
       <c r="C171" t="s">
-        <v>1271</v>
+        <v>1272</v>
       </c>
       <c r="D171" t="s">
-        <v>1720</v>
+        <v>1724</v>
       </c>
       <c r="E171" t="s">
         <v>115</v>
       </c>
       <c r="F171" t="s">
-        <v>1700</v>
+        <v>1704</v>
       </c>
       <c r="G171" t="s">
-        <v>1272</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="172" spans="1:7" x14ac:dyDescent="0.25">
@@ -21194,22 +21232,22 @@
         <v>27</v>
       </c>
       <c r="B172" t="s">
-        <v>1240</v>
+        <v>1241</v>
       </c>
       <c r="C172" t="s">
-        <v>1279</v>
+        <v>1280</v>
       </c>
       <c r="D172" t="s">
-        <v>1720</v>
+        <v>1724</v>
       </c>
       <c r="E172" t="s">
         <v>459</v>
       </c>
       <c r="F172" t="s">
-        <v>1700</v>
+        <v>1704</v>
       </c>
       <c r="G172" t="s">
-        <v>1280</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="173" spans="1:7" x14ac:dyDescent="0.25">
@@ -21217,22 +21255,22 @@
         <v>27</v>
       </c>
       <c r="B173" t="s">
-        <v>1240</v>
+        <v>1241</v>
       </c>
       <c r="C173" t="s">
-        <v>1287</v>
+        <v>1288</v>
       </c>
       <c r="D173" t="s">
-        <v>1720</v>
+        <v>1724</v>
       </c>
       <c r="E173" t="s">
         <v>115</v>
       </c>
       <c r="F173" t="s">
-        <v>1700</v>
+        <v>1704</v>
       </c>
       <c r="G173" t="s">
-        <v>1288</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="174" spans="1:7" x14ac:dyDescent="0.25">
@@ -21240,22 +21278,22 @@
         <v>27</v>
       </c>
       <c r="B174" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="C174" t="s">
-        <v>1295</v>
+        <v>1296</v>
       </c>
       <c r="D174" t="s">
-        <v>1720</v>
+        <v>1724</v>
       </c>
       <c r="E174" t="s">
         <v>115</v>
       </c>
       <c r="F174" t="s">
-        <v>1700</v>
+        <v>1704</v>
       </c>
       <c r="G174" t="s">
-        <v>1297</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="175" spans="1:7" x14ac:dyDescent="0.25">
@@ -21263,22 +21301,22 @@
         <v>27</v>
       </c>
       <c r="B175" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="C175" t="s">
-        <v>1305</v>
+        <v>1306</v>
       </c>
       <c r="D175" t="s">
-        <v>1720</v>
+        <v>1724</v>
       </c>
       <c r="E175" t="s">
         <v>115</v>
       </c>
       <c r="F175" t="s">
-        <v>1700</v>
+        <v>1704</v>
       </c>
       <c r="G175" t="s">
-        <v>1306</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="176" spans="1:7" x14ac:dyDescent="0.25">
@@ -21286,22 +21324,22 @@
         <v>27</v>
       </c>
       <c r="B176" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="C176" t="s">
-        <v>1313</v>
+        <v>1314</v>
       </c>
       <c r="D176" t="s">
-        <v>1720</v>
+        <v>1724</v>
       </c>
       <c r="E176" t="s">
         <v>115</v>
       </c>
       <c r="F176" t="s">
-        <v>1700</v>
+        <v>1704</v>
       </c>
       <c r="G176" t="s">
-        <v>1314</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.25">
@@ -21309,22 +21347,22 @@
         <v>27</v>
       </c>
       <c r="B177" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="C177" t="s">
-        <v>1321</v>
+        <v>1322</v>
       </c>
       <c r="D177" t="s">
-        <v>1720</v>
+        <v>1724</v>
       </c>
       <c r="E177" t="s">
         <v>86</v>
       </c>
       <c r="F177" t="s">
-        <v>1700</v>
+        <v>1704</v>
       </c>
       <c r="G177" t="s">
-        <v>1323</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.25">
@@ -21344,10 +21382,10 @@
         <v>26</v>
       </c>
       <c r="F178" t="s">
-        <v>1721</v>
+        <v>1725</v>
       </c>
       <c r="G178" t="s">
-        <v>1722</v>
+        <v>1726</v>
       </c>
     </row>
     <row r="179" spans="1:7" x14ac:dyDescent="0.25">
@@ -21367,10 +21405,10 @@
         <v>26</v>
       </c>
       <c r="F179" t="s">
-        <v>1721</v>
+        <v>1725</v>
       </c>
       <c r="G179" t="s">
-        <v>1723</v>
+        <v>1727</v>
       </c>
     </row>
     <row r="180" spans="1:7" x14ac:dyDescent="0.25">
@@ -21390,10 +21428,10 @@
         <v>26</v>
       </c>
       <c r="F180" t="s">
-        <v>1721</v>
+        <v>1725</v>
       </c>
       <c r="G180" t="s">
-        <v>1724</v>
+        <v>1728</v>
       </c>
     </row>
     <row r="181" spans="1:7" x14ac:dyDescent="0.25">
@@ -21413,10 +21451,10 @@
         <v>26</v>
       </c>
       <c r="F181" t="s">
-        <v>1721</v>
+        <v>1725</v>
       </c>
       <c r="G181" t="s">
-        <v>1725</v>
+        <v>1729</v>
       </c>
     </row>
     <row r="182" spans="1:7" x14ac:dyDescent="0.25">
@@ -21436,10 +21474,10 @@
         <v>26</v>
       </c>
       <c r="F182" t="s">
-        <v>1721</v>
+        <v>1725</v>
       </c>
       <c r="G182" t="s">
-        <v>1726</v>
+        <v>1730</v>
       </c>
     </row>
     <row r="183" spans="1:7" x14ac:dyDescent="0.25">
@@ -21459,10 +21497,10 @@
         <v>26</v>
       </c>
       <c r="F183" t="s">
-        <v>1721</v>
+        <v>1725</v>
       </c>
       <c r="G183" t="s">
-        <v>1727</v>
+        <v>1731</v>
       </c>
     </row>
     <row r="184" spans="1:7" x14ac:dyDescent="0.25">
@@ -21482,10 +21520,10 @@
         <v>26</v>
       </c>
       <c r="F184" t="s">
-        <v>1721</v>
+        <v>1725</v>
       </c>
       <c r="G184" t="s">
-        <v>1728</v>
+        <v>1732</v>
       </c>
     </row>
     <row r="185" spans="1:7" x14ac:dyDescent="0.25">
@@ -21505,10 +21543,10 @@
         <v>26</v>
       </c>
       <c r="F185" t="s">
-        <v>1721</v>
+        <v>1725</v>
       </c>
       <c r="G185" t="s">
-        <v>1729</v>
+        <v>1733</v>
       </c>
     </row>
     <row r="186" spans="1:7" x14ac:dyDescent="0.25">
@@ -21528,10 +21566,10 @@
         <v>26</v>
       </c>
       <c r="F186" t="s">
-        <v>1721</v>
+        <v>1725</v>
       </c>
       <c r="G186" t="s">
-        <v>1730</v>
+        <v>1734</v>
       </c>
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.25">
@@ -21551,10 +21589,10 @@
         <v>26</v>
       </c>
       <c r="F187" t="s">
-        <v>1721</v>
+        <v>1725</v>
       </c>
       <c r="G187" t="s">
-        <v>1731</v>
+        <v>1735</v>
       </c>
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.25">
@@ -21574,10 +21612,10 @@
         <v>86</v>
       </c>
       <c r="F188" t="s">
-        <v>1721</v>
+        <v>1725</v>
       </c>
       <c r="G188" t="s">
-        <v>1732</v>
+        <v>1736</v>
       </c>
     </row>
     <row r="189" spans="1:7" x14ac:dyDescent="0.25">
@@ -21597,10 +21635,10 @@
         <v>86</v>
       </c>
       <c r="F189" t="s">
-        <v>1721</v>
+        <v>1725</v>
       </c>
       <c r="G189" t="s">
-        <v>1733</v>
+        <v>1737</v>
       </c>
     </row>
     <row r="190" spans="1:7" x14ac:dyDescent="0.25">
@@ -21620,10 +21658,10 @@
         <v>86</v>
       </c>
       <c r="F190" t="s">
-        <v>1721</v>
+        <v>1725</v>
       </c>
       <c r="G190" t="s">
-        <v>1734</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="191" spans="1:7" x14ac:dyDescent="0.25">
@@ -21643,10 +21681,10 @@
         <v>86</v>
       </c>
       <c r="F191" t="s">
-        <v>1721</v>
+        <v>1725</v>
       </c>
       <c r="G191" t="s">
-        <v>1735</v>
+        <v>1739</v>
       </c>
     </row>
     <row r="192" spans="1:7" x14ac:dyDescent="0.25">
@@ -21666,10 +21704,10 @@
         <v>26</v>
       </c>
       <c r="F192" t="s">
-        <v>1721</v>
+        <v>1725</v>
       </c>
       <c r="G192" t="s">
-        <v>1736</v>
+        <v>1740</v>
       </c>
     </row>
     <row r="193" spans="1:7" x14ac:dyDescent="0.25">
@@ -21689,10 +21727,10 @@
         <v>26</v>
       </c>
       <c r="F193" t="s">
-        <v>1721</v>
+        <v>1725</v>
       </c>
       <c r="G193" t="s">
-        <v>1737</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="194" spans="1:7" x14ac:dyDescent="0.25">
@@ -21712,10 +21750,10 @@
         <v>26</v>
       </c>
       <c r="F194" t="s">
-        <v>1721</v>
+        <v>1725</v>
       </c>
       <c r="G194" t="s">
-        <v>1738</v>
+        <v>1742</v>
       </c>
     </row>
     <row r="195" spans="1:7" x14ac:dyDescent="0.25">
@@ -21735,10 +21773,10 @@
         <v>26</v>
       </c>
       <c r="F195" t="s">
-        <v>1721</v>
+        <v>1725</v>
       </c>
       <c r="G195" t="s">
-        <v>1739</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="196" spans="1:7" x14ac:dyDescent="0.25">
@@ -21758,10 +21796,10 @@
         <v>86</v>
       </c>
       <c r="F196" t="s">
-        <v>1721</v>
+        <v>1725</v>
       </c>
       <c r="G196" t="s">
-        <v>1740</v>
+        <v>1744</v>
       </c>
     </row>
     <row r="197" spans="1:7" x14ac:dyDescent="0.25">
@@ -21781,10 +21819,10 @@
         <v>26</v>
       </c>
       <c r="F197" t="s">
-        <v>1721</v>
+        <v>1725</v>
       </c>
       <c r="G197" t="s">
-        <v>1741</v>
+        <v>1745</v>
       </c>
     </row>
     <row r="198" spans="1:7" x14ac:dyDescent="0.25">
@@ -21804,10 +21842,10 @@
         <v>26</v>
       </c>
       <c r="F198" t="s">
-        <v>1721</v>
+        <v>1725</v>
       </c>
       <c r="G198" t="s">
-        <v>1742</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="199" spans="1:7" x14ac:dyDescent="0.25">
@@ -21827,10 +21865,10 @@
         <v>26</v>
       </c>
       <c r="F199" t="s">
-        <v>1721</v>
+        <v>1725</v>
       </c>
       <c r="G199" t="s">
-        <v>1743</v>
+        <v>1747</v>
       </c>
     </row>
     <row r="200" spans="1:7" x14ac:dyDescent="0.25">
@@ -21850,10 +21888,10 @@
         <v>26</v>
       </c>
       <c r="F200" t="s">
-        <v>1721</v>
+        <v>1725</v>
       </c>
       <c r="G200" t="s">
-        <v>1744</v>
+        <v>1748</v>
       </c>
     </row>
     <row r="201" spans="1:7" x14ac:dyDescent="0.25">
@@ -21873,10 +21911,10 @@
         <v>26</v>
       </c>
       <c r="F201" t="s">
-        <v>1721</v>
+        <v>1725</v>
       </c>
       <c r="G201" t="s">
-        <v>1745</v>
+        <v>1749</v>
       </c>
     </row>
     <row r="202" spans="1:7" x14ac:dyDescent="0.25">
@@ -21896,10 +21934,10 @@
         <v>26</v>
       </c>
       <c r="F202" t="s">
-        <v>1721</v>
+        <v>1725</v>
       </c>
       <c r="G202" t="s">
-        <v>1746</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="203" spans="1:7" x14ac:dyDescent="0.25">
@@ -21919,10 +21957,10 @@
         <v>86</v>
       </c>
       <c r="F203" t="s">
-        <v>1721</v>
+        <v>1725</v>
       </c>
       <c r="G203" t="s">
-        <v>1747</v>
+        <v>1751</v>
       </c>
     </row>
     <row r="204" spans="1:7" x14ac:dyDescent="0.25">
@@ -21942,10 +21980,10 @@
         <v>26</v>
       </c>
       <c r="F204" t="s">
-        <v>1721</v>
+        <v>1725</v>
       </c>
       <c r="G204" t="s">
-        <v>1748</v>
+        <v>1752</v>
       </c>
     </row>
     <row r="205" spans="1:7" x14ac:dyDescent="0.25">
@@ -21965,10 +22003,10 @@
         <v>26</v>
       </c>
       <c r="F205" t="s">
-        <v>1721</v>
+        <v>1725</v>
       </c>
       <c r="G205" t="s">
-        <v>1749</v>
+        <v>1753</v>
       </c>
     </row>
     <row r="206" spans="1:7" x14ac:dyDescent="0.25">
@@ -21988,10 +22026,10 @@
         <v>26</v>
       </c>
       <c r="F206" t="s">
-        <v>1721</v>
+        <v>1725</v>
       </c>
       <c r="G206" t="s">
-        <v>1750</v>
+        <v>1754</v>
       </c>
     </row>
     <row r="207" spans="1:7" x14ac:dyDescent="0.25">
@@ -22011,10 +22049,10 @@
         <v>26</v>
       </c>
       <c r="F207" t="s">
-        <v>1721</v>
+        <v>1725</v>
       </c>
       <c r="G207" t="s">
-        <v>1751</v>
+        <v>1755</v>
       </c>
     </row>
     <row r="208" spans="1:7" x14ac:dyDescent="0.25">
@@ -22034,10 +22072,10 @@
         <v>26</v>
       </c>
       <c r="F208" t="s">
-        <v>1721</v>
+        <v>1725</v>
       </c>
       <c r="G208" t="s">
-        <v>1752</v>
+        <v>1756</v>
       </c>
     </row>
     <row r="209" spans="1:7" x14ac:dyDescent="0.25">
@@ -22057,10 +22095,10 @@
         <v>26</v>
       </c>
       <c r="F209" t="s">
-        <v>1721</v>
+        <v>1725</v>
       </c>
       <c r="G209" t="s">
-        <v>1753</v>
+        <v>1757</v>
       </c>
     </row>
     <row r="210" spans="1:7" x14ac:dyDescent="0.25">
@@ -22080,10 +22118,10 @@
         <v>26</v>
       </c>
       <c r="F210" t="s">
-        <v>1721</v>
+        <v>1725</v>
       </c>
       <c r="G210" t="s">
-        <v>1754</v>
+        <v>1758</v>
       </c>
     </row>
     <row r="211" spans="1:7" x14ac:dyDescent="0.25">
@@ -22103,10 +22141,10 @@
         <v>26</v>
       </c>
       <c r="F211" t="s">
-        <v>1721</v>
+        <v>1725</v>
       </c>
       <c r="G211" t="s">
-        <v>1755</v>
+        <v>1759</v>
       </c>
     </row>
     <row r="212" spans="1:7" x14ac:dyDescent="0.25">
@@ -22117,7 +22155,7 @@
         <v>260</v>
       </c>
       <c r="C212" t="s">
-        <v>1247</v>
+        <v>1248</v>
       </c>
       <c r="D212" t="s">
         <v>115</v>
@@ -22126,10 +22164,10 @@
         <v>26</v>
       </c>
       <c r="F212" t="s">
-        <v>1721</v>
+        <v>1725</v>
       </c>
       <c r="G212" t="s">
-        <v>1756</v>
+        <v>1760</v>
       </c>
     </row>
     <row r="213" spans="1:7" x14ac:dyDescent="0.25">
@@ -22140,7 +22178,7 @@
         <v>260</v>
       </c>
       <c r="C213" t="s">
-        <v>1287</v>
+        <v>1288</v>
       </c>
       <c r="D213" t="s">
         <v>115</v>
@@ -22149,10 +22187,10 @@
         <v>86</v>
       </c>
       <c r="F213" t="s">
-        <v>1721</v>
+        <v>1725</v>
       </c>
       <c r="G213" t="s">
-        <v>1757</v>
+        <v>1761</v>
       </c>
     </row>
     <row r="214" spans="1:7" x14ac:dyDescent="0.25">
@@ -22163,7 +22201,7 @@
         <v>260</v>
       </c>
       <c r="C214" t="s">
-        <v>1238</v>
+        <v>1239</v>
       </c>
       <c r="D214" t="s">
         <v>115</v>
@@ -22172,10 +22210,10 @@
         <v>26</v>
       </c>
       <c r="F214" t="s">
-        <v>1721</v>
+        <v>1725</v>
       </c>
       <c r="G214" t="s">
-        <v>1758</v>
+        <v>1762</v>
       </c>
     </row>
     <row r="215" spans="1:7" x14ac:dyDescent="0.25">
@@ -22195,10 +22233,10 @@
         <v>26</v>
       </c>
       <c r="F215" t="s">
-        <v>1721</v>
+        <v>1725</v>
       </c>
       <c r="G215" t="s">
-        <v>1759</v>
+        <v>1763</v>
       </c>
     </row>
     <row r="216" spans="1:7" x14ac:dyDescent="0.25">
@@ -22218,10 +22256,10 @@
         <v>86</v>
       </c>
       <c r="F216" t="s">
-        <v>1721</v>
+        <v>1725</v>
       </c>
       <c r="G216" t="s">
-        <v>1760</v>
+        <v>1764</v>
       </c>
     </row>
     <row r="217" spans="1:7" x14ac:dyDescent="0.25">
@@ -22241,10 +22279,10 @@
         <v>26</v>
       </c>
       <c r="F217" t="s">
-        <v>1721</v>
+        <v>1725</v>
       </c>
       <c r="G217" t="s">
-        <v>1761</v>
+        <v>1765</v>
       </c>
     </row>
     <row r="218" spans="1:7" x14ac:dyDescent="0.25">
@@ -22264,10 +22302,10 @@
         <v>26</v>
       </c>
       <c r="F218" t="s">
-        <v>1721</v>
+        <v>1725</v>
       </c>
       <c r="G218" t="s">
-        <v>1762</v>
+        <v>1766</v>
       </c>
     </row>
     <row r="219" spans="1:7" x14ac:dyDescent="0.25">
@@ -22278,7 +22316,7 @@
         <v>800</v>
       </c>
       <c r="C219" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="D219" t="s">
         <v>115</v>
@@ -22287,10 +22325,10 @@
         <v>26</v>
       </c>
       <c r="F219" t="s">
-        <v>1721</v>
+        <v>1725</v>
       </c>
       <c r="G219" t="s">
-        <v>1763</v>
+        <v>1767</v>
       </c>
     </row>
     <row r="220" spans="1:7" x14ac:dyDescent="0.25">
@@ -22310,10 +22348,10 @@
         <v>26</v>
       </c>
       <c r="F220" t="s">
-        <v>1721</v>
+        <v>1725</v>
       </c>
       <c r="G220" t="s">
-        <v>1764</v>
+        <v>1768</v>
       </c>
     </row>
     <row r="221" spans="1:7" x14ac:dyDescent="0.25">
@@ -22333,10 +22371,10 @@
         <v>26</v>
       </c>
       <c r="F221" t="s">
-        <v>1721</v>
+        <v>1725</v>
       </c>
       <c r="G221" t="s">
-        <v>1765</v>
+        <v>1769</v>
       </c>
     </row>
     <row r="222" spans="1:7" x14ac:dyDescent="0.25">
@@ -22356,10 +22394,10 @@
         <v>26</v>
       </c>
       <c r="F222" t="s">
-        <v>1721</v>
+        <v>1725</v>
       </c>
       <c r="G222" t="s">
-        <v>1766</v>
+        <v>1770</v>
       </c>
     </row>
     <row r="223" spans="1:7" x14ac:dyDescent="0.25">
@@ -22379,10 +22417,10 @@
         <v>26</v>
       </c>
       <c r="F223" t="s">
-        <v>1721</v>
+        <v>1725</v>
       </c>
       <c r="G223" t="s">
-        <v>1767</v>
+        <v>1771</v>
       </c>
     </row>
     <row r="224" spans="1:7" x14ac:dyDescent="0.25">
@@ -22402,10 +22440,10 @@
         <v>26</v>
       </c>
       <c r="F224" t="s">
-        <v>1721</v>
+        <v>1725</v>
       </c>
       <c r="G224" t="s">
-        <v>1768</v>
+        <v>1772</v>
       </c>
     </row>
     <row r="225" spans="1:7" x14ac:dyDescent="0.25">
@@ -22416,7 +22454,7 @@
         <v>800</v>
       </c>
       <c r="C225" t="s">
-        <v>1197</v>
+        <v>1198</v>
       </c>
       <c r="D225" t="s">
         <v>115</v>
@@ -22425,10 +22463,10 @@
         <v>26</v>
       </c>
       <c r="F225" t="s">
-        <v>1721</v>
+        <v>1725</v>
       </c>
       <c r="G225" t="s">
-        <v>1769</v>
+        <v>1773</v>
       </c>
     </row>
     <row r="226" spans="1:7" x14ac:dyDescent="0.25">
@@ -22448,10 +22486,10 @@
         <v>26</v>
       </c>
       <c r="F226" t="s">
-        <v>1721</v>
+        <v>1725</v>
       </c>
       <c r="G226" t="s">
-        <v>1770</v>
+        <v>1774</v>
       </c>
     </row>
     <row r="227" spans="1:7" x14ac:dyDescent="0.25">
@@ -22471,10 +22509,10 @@
         <v>26</v>
       </c>
       <c r="F227" t="s">
-        <v>1721</v>
+        <v>1725</v>
       </c>
       <c r="G227" t="s">
-        <v>1771</v>
+        <v>1775</v>
       </c>
     </row>
     <row r="228" spans="1:7" x14ac:dyDescent="0.25">
@@ -22494,10 +22532,10 @@
         <v>26</v>
       </c>
       <c r="F228" t="s">
-        <v>1721</v>
+        <v>1725</v>
       </c>
       <c r="G228" t="s">
-        <v>1772</v>
+        <v>1776</v>
       </c>
     </row>
     <row r="229" spans="1:7" x14ac:dyDescent="0.25">
@@ -22517,10 +22555,10 @@
         <v>26</v>
       </c>
       <c r="F229" t="s">
-        <v>1721</v>
+        <v>1725</v>
       </c>
       <c r="G229" t="s">
-        <v>1773</v>
+        <v>1777</v>
       </c>
     </row>
     <row r="230" spans="1:7" x14ac:dyDescent="0.25">
@@ -22540,10 +22578,10 @@
         <v>26</v>
       </c>
       <c r="F230" t="s">
-        <v>1721</v>
+        <v>1725</v>
       </c>
       <c r="G230" t="s">
-        <v>1774</v>
+        <v>1778</v>
       </c>
     </row>
     <row r="231" spans="1:7" x14ac:dyDescent="0.25">
@@ -22563,10 +22601,10 @@
         <v>26</v>
       </c>
       <c r="F231" t="s">
-        <v>1721</v>
+        <v>1725</v>
       </c>
       <c r="G231" t="s">
-        <v>1775</v>
+        <v>1779</v>
       </c>
     </row>
     <row r="232" spans="1:7" x14ac:dyDescent="0.25">
@@ -22586,10 +22624,10 @@
         <v>26</v>
       </c>
       <c r="F232" t="s">
-        <v>1721</v>
+        <v>1725</v>
       </c>
       <c r="G232" t="s">
-        <v>1776</v>
+        <v>1780</v>
       </c>
     </row>
     <row r="233" spans="1:7" x14ac:dyDescent="0.25">
@@ -22609,10 +22647,10 @@
         <v>26</v>
       </c>
       <c r="F233" t="s">
-        <v>1721</v>
+        <v>1725</v>
       </c>
       <c r="G233" t="s">
-        <v>1777</v>
+        <v>1781</v>
       </c>
     </row>
     <row r="234" spans="1:7" x14ac:dyDescent="0.25">
@@ -22632,10 +22670,10 @@
         <v>26</v>
       </c>
       <c r="F234" t="s">
-        <v>1721</v>
+        <v>1725</v>
       </c>
       <c r="G234" t="s">
-        <v>1778</v>
+        <v>1782</v>
       </c>
     </row>
     <row r="235" spans="1:7" x14ac:dyDescent="0.25">
@@ -22655,10 +22693,10 @@
         <v>26</v>
       </c>
       <c r="F235" t="s">
-        <v>1721</v>
+        <v>1725</v>
       </c>
       <c r="G235" t="s">
-        <v>1779</v>
+        <v>1783</v>
       </c>
     </row>
     <row r="236" spans="1:7" x14ac:dyDescent="0.25">
@@ -22678,10 +22716,10 @@
         <v>26</v>
       </c>
       <c r="F236" t="s">
-        <v>1721</v>
+        <v>1725</v>
       </c>
       <c r="G236" t="s">
-        <v>1780</v>
+        <v>1784</v>
       </c>
     </row>
     <row r="237" spans="1:7" x14ac:dyDescent="0.25">
@@ -22701,10 +22739,10 @@
         <v>26</v>
       </c>
       <c r="F237" t="s">
-        <v>1721</v>
+        <v>1725</v>
       </c>
       <c r="G237" t="s">
-        <v>1781</v>
+        <v>1785</v>
       </c>
     </row>
     <row r="238" spans="1:7" x14ac:dyDescent="0.25">
@@ -22724,10 +22762,10 @@
         <v>26</v>
       </c>
       <c r="F238" t="s">
-        <v>1721</v>
+        <v>1725</v>
       </c>
       <c r="G238" t="s">
-        <v>1782</v>
+        <v>1786</v>
       </c>
     </row>
     <row r="239" spans="1:7" x14ac:dyDescent="0.25">
@@ -22747,10 +22785,10 @@
         <v>26</v>
       </c>
       <c r="F239" t="s">
-        <v>1721</v>
+        <v>1725</v>
       </c>
       <c r="G239" t="s">
-        <v>1783</v>
+        <v>1787</v>
       </c>
     </row>
     <row r="240" spans="1:7" x14ac:dyDescent="0.25">
@@ -22761,7 +22799,7 @@
         <v>899</v>
       </c>
       <c r="C240" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="D240" t="s">
         <v>115</v>
@@ -22770,10 +22808,10 @@
         <v>86</v>
       </c>
       <c r="F240" t="s">
-        <v>1721</v>
+        <v>1725</v>
       </c>
       <c r="G240" t="s">
-        <v>1784</v>
+        <v>1788</v>
       </c>
     </row>
     <row r="241" spans="1:7" x14ac:dyDescent="0.25">
@@ -22784,7 +22822,7 @@
         <v>899</v>
       </c>
       <c r="C241" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="D241" t="s">
         <v>115</v>
@@ -22793,10 +22831,10 @@
         <v>26</v>
       </c>
       <c r="F241" t="s">
-        <v>1721</v>
+        <v>1725</v>
       </c>
       <c r="G241" t="s">
-        <v>1785</v>
+        <v>1789</v>
       </c>
     </row>
     <row r="242" spans="1:7" x14ac:dyDescent="0.25">
@@ -22807,7 +22845,7 @@
         <v>899</v>
       </c>
       <c r="C242" t="s">
-        <v>1206</v>
+        <v>1207</v>
       </c>
       <c r="D242" t="s">
         <v>115</v>
@@ -22816,10 +22854,10 @@
         <v>26</v>
       </c>
       <c r="F242" t="s">
-        <v>1721</v>
+        <v>1725</v>
       </c>
       <c r="G242" t="s">
-        <v>1786</v>
+        <v>1790</v>
       </c>
     </row>
     <row r="243" spans="1:7" x14ac:dyDescent="0.25">
@@ -22830,7 +22868,7 @@
         <v>899</v>
       </c>
       <c r="C243" t="s">
-        <v>1214</v>
+        <v>1215</v>
       </c>
       <c r="D243" t="s">
         <v>115</v>
@@ -22839,10 +22877,10 @@
         <v>26</v>
       </c>
       <c r="F243" t="s">
-        <v>1721</v>
+        <v>1725</v>
       </c>
       <c r="G243" t="s">
-        <v>1787</v>
+        <v>1791</v>
       </c>
     </row>
     <row r="244" spans="1:7" x14ac:dyDescent="0.25">
@@ -22853,7 +22891,7 @@
         <v>899</v>
       </c>
       <c r="C244" t="s">
-        <v>1222</v>
+        <v>1223</v>
       </c>
       <c r="D244" t="s">
         <v>115</v>
@@ -22862,10 +22900,10 @@
         <v>26</v>
       </c>
       <c r="F244" t="s">
-        <v>1721</v>
+        <v>1725</v>
       </c>
       <c r="G244" t="s">
-        <v>1788</v>
+        <v>1792</v>
       </c>
     </row>
     <row r="245" spans="1:7" x14ac:dyDescent="0.25">
@@ -22876,7 +22914,7 @@
         <v>899</v>
       </c>
       <c r="C245" t="s">
-        <v>1230</v>
+        <v>1231</v>
       </c>
       <c r="D245" t="s">
         <v>86</v>
@@ -22885,10 +22923,10 @@
         <v>26</v>
       </c>
       <c r="F245" t="s">
-        <v>1721</v>
+        <v>1725</v>
       </c>
       <c r="G245" t="s">
-        <v>1789</v>
+        <v>1793</v>
       </c>
     </row>
     <row r="246" spans="1:7" x14ac:dyDescent="0.25">
@@ -22899,7 +22937,7 @@
         <v>899</v>
       </c>
       <c r="C246" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
       <c r="D246" t="s">
         <v>115</v>
@@ -22908,10 +22946,10 @@
         <v>26</v>
       </c>
       <c r="F246" t="s">
-        <v>1721</v>
+        <v>1725</v>
       </c>
       <c r="G246" t="s">
-        <v>1790</v>
+        <v>1794</v>
       </c>
     </row>
     <row r="247" spans="1:7" x14ac:dyDescent="0.25">
@@ -22922,7 +22960,7 @@
         <v>899</v>
       </c>
       <c r="C247" t="s">
-        <v>1263</v>
+        <v>1264</v>
       </c>
       <c r="D247" t="s">
         <v>115</v>
@@ -22931,10 +22969,10 @@
         <v>26</v>
       </c>
       <c r="F247" t="s">
-        <v>1721</v>
+        <v>1725</v>
       </c>
       <c r="G247" t="s">
-        <v>1791</v>
+        <v>1795</v>
       </c>
     </row>
     <row r="248" spans="1:7" x14ac:dyDescent="0.25">
@@ -22945,7 +22983,7 @@
         <v>899</v>
       </c>
       <c r="C248" t="s">
-        <v>1271</v>
+        <v>1272</v>
       </c>
       <c r="D248" t="s">
         <v>115</v>
@@ -22954,10 +22992,10 @@
         <v>26</v>
       </c>
       <c r="F248" t="s">
-        <v>1721</v>
+        <v>1725</v>
       </c>
       <c r="G248" t="s">
-        <v>1792</v>
+        <v>1796</v>
       </c>
     </row>
     <row r="249" spans="1:7" x14ac:dyDescent="0.25">
@@ -22968,7 +23006,7 @@
         <v>899</v>
       </c>
       <c r="C249" t="s">
-        <v>1295</v>
+        <v>1296</v>
       </c>
       <c r="D249" t="s">
         <v>115</v>
@@ -22977,10 +23015,10 @@
         <v>26</v>
       </c>
       <c r="F249" t="s">
-        <v>1721</v>
+        <v>1725</v>
       </c>
       <c r="G249" t="s">
-        <v>1793</v>
+        <v>1797</v>
       </c>
     </row>
     <row r="250" spans="1:7" x14ac:dyDescent="0.25">
@@ -22991,7 +23029,7 @@
         <v>899</v>
       </c>
       <c r="C250" t="s">
-        <v>1305</v>
+        <v>1306</v>
       </c>
       <c r="D250" t="s">
         <v>115</v>
@@ -23000,10 +23038,10 @@
         <v>26</v>
       </c>
       <c r="F250" t="s">
-        <v>1721</v>
+        <v>1725</v>
       </c>
       <c r="G250" t="s">
-        <v>1794</v>
+        <v>1798</v>
       </c>
     </row>
     <row r="251" spans="1:7" x14ac:dyDescent="0.25">
@@ -23014,7 +23052,7 @@
         <v>899</v>
       </c>
       <c r="C251" t="s">
-        <v>1313</v>
+        <v>1314</v>
       </c>
       <c r="D251" t="s">
         <v>115</v>
@@ -23023,10 +23061,10 @@
         <v>26</v>
       </c>
       <c r="F251" t="s">
-        <v>1721</v>
+        <v>1725</v>
       </c>
       <c r="G251" t="s">
-        <v>1795</v>
+        <v>1799</v>
       </c>
     </row>
     <row r="252" spans="1:7" x14ac:dyDescent="0.25">
@@ -23046,10 +23084,10 @@
         <v>86</v>
       </c>
       <c r="F252" t="s">
-        <v>1721</v>
+        <v>1725</v>
       </c>
       <c r="G252" t="s">
-        <v>1796</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="253" spans="1:7" x14ac:dyDescent="0.25">
@@ -23069,10 +23107,10 @@
         <v>86</v>
       </c>
       <c r="F253" t="s">
-        <v>1721</v>
+        <v>1725</v>
       </c>
       <c r="G253" t="s">
-        <v>1797</v>
+        <v>1801</v>
       </c>
     </row>
     <row r="254" spans="1:7" x14ac:dyDescent="0.25">
@@ -23092,10 +23130,10 @@
         <v>86</v>
       </c>
       <c r="F254" t="s">
-        <v>1721</v>
+        <v>1725</v>
       </c>
       <c r="G254" t="s">
-        <v>1798</v>
+        <v>1802</v>
       </c>
     </row>
     <row r="255" spans="1:7" x14ac:dyDescent="0.25">
@@ -23115,10 +23153,10 @@
         <v>316</v>
       </c>
       <c r="F255" t="s">
-        <v>1721</v>
+        <v>1725</v>
       </c>
       <c r="G255" t="s">
-        <v>1799</v>
+        <v>1803</v>
       </c>
     </row>
     <row r="256" spans="1:7" x14ac:dyDescent="0.25">
@@ -23138,10 +23176,10 @@
         <v>26</v>
       </c>
       <c r="F256" t="s">
-        <v>1721</v>
+        <v>1725</v>
       </c>
       <c r="G256" t="s">
-        <v>1800</v>
+        <v>1804</v>
       </c>
     </row>
     <row r="257" spans="1:7" x14ac:dyDescent="0.25">
@@ -23161,10 +23199,10 @@
         <v>86</v>
       </c>
       <c r="F257" t="s">
-        <v>1721</v>
+        <v>1725</v>
       </c>
       <c r="G257" t="s">
-        <v>1801</v>
+        <v>1805</v>
       </c>
     </row>
     <row r="258" spans="1:7" x14ac:dyDescent="0.25">
@@ -23184,10 +23222,10 @@
         <v>26</v>
       </c>
       <c r="F258" t="s">
-        <v>1721</v>
+        <v>1725</v>
       </c>
       <c r="G258" t="s">
-        <v>1802</v>
+        <v>1806</v>
       </c>
     </row>
     <row r="259" spans="1:7" x14ac:dyDescent="0.25">
@@ -23198,7 +23236,7 @@
         <v>87</v>
       </c>
       <c r="C259" t="s">
-        <v>1180</v>
+        <v>1181</v>
       </c>
       <c r="D259" t="s">
         <v>115</v>
@@ -23207,10 +23245,10 @@
         <v>86</v>
       </c>
       <c r="F259" t="s">
-        <v>1721</v>
+        <v>1725</v>
       </c>
       <c r="G259" t="s">
-        <v>1803</v>
+        <v>1807</v>
       </c>
     </row>
     <row r="260" spans="1:7" x14ac:dyDescent="0.25">
@@ -23230,10 +23268,10 @@
         <v>26</v>
       </c>
       <c r="F260" t="s">
-        <v>1721</v>
+        <v>1725</v>
       </c>
       <c r="G260" t="s">
-        <v>1804</v>
+        <v>1808</v>
       </c>
     </row>
     <row r="261" spans="1:7" x14ac:dyDescent="0.25">
@@ -23253,10 +23291,10 @@
         <v>26</v>
       </c>
       <c r="F261" t="s">
-        <v>1721</v>
+        <v>1725</v>
       </c>
       <c r="G261" t="s">
-        <v>1805</v>
+        <v>1809</v>
       </c>
     </row>
     <row r="262" spans="1:7" x14ac:dyDescent="0.25">
@@ -23276,10 +23314,10 @@
         <v>26</v>
       </c>
       <c r="F262" t="s">
-        <v>1721</v>
+        <v>1725</v>
       </c>
       <c r="G262" t="s">
-        <v>1806</v>
+        <v>1810</v>
       </c>
     </row>
     <row r="263" spans="1:7" x14ac:dyDescent="0.25">
@@ -23299,10 +23337,10 @@
         <v>26</v>
       </c>
       <c r="F263" t="s">
-        <v>1721</v>
+        <v>1725</v>
       </c>
       <c r="G263" t="s">
-        <v>1807</v>
+        <v>1811</v>
       </c>
     </row>
     <row r="264" spans="1:7" x14ac:dyDescent="0.25">
@@ -23322,10 +23360,10 @@
         <v>26</v>
       </c>
       <c r="F264" t="s">
-        <v>1721</v>
+        <v>1725</v>
       </c>
       <c r="G264" t="s">
-        <v>1808</v>
+        <v>1812</v>
       </c>
     </row>
     <row r="265" spans="1:7" x14ac:dyDescent="0.25">
@@ -23345,10 +23383,10 @@
         <v>26</v>
       </c>
       <c r="F265" t="s">
-        <v>1721</v>
+        <v>1725</v>
       </c>
       <c r="G265" t="s">
-        <v>1809</v>
+        <v>1813</v>
       </c>
     </row>
     <row r="266" spans="1:7" x14ac:dyDescent="0.25">
@@ -23368,10 +23406,10 @@
         <v>26</v>
       </c>
       <c r="F266" t="s">
-        <v>1721</v>
+        <v>1725</v>
       </c>
       <c r="G266" t="s">
-        <v>1810</v>
+        <v>1814</v>
       </c>
     </row>
     <row r="267" spans="1:7" x14ac:dyDescent="0.25">
@@ -23391,10 +23429,10 @@
         <v>26</v>
       </c>
       <c r="F267" t="s">
-        <v>1721</v>
+        <v>1725</v>
       </c>
       <c r="G267" t="s">
-        <v>1811</v>
+        <v>1815</v>
       </c>
     </row>
     <row r="268" spans="1:7" x14ac:dyDescent="0.25">
@@ -23414,10 +23452,10 @@
         <v>26</v>
       </c>
       <c r="F268" t="s">
-        <v>1721</v>
+        <v>1725</v>
       </c>
       <c r="G268" t="s">
-        <v>1812</v>
+        <v>1816</v>
       </c>
     </row>
     <row r="269" spans="1:7" x14ac:dyDescent="0.25">
@@ -23437,10 +23475,10 @@
         <v>26</v>
       </c>
       <c r="F269" t="s">
-        <v>1721</v>
+        <v>1725</v>
       </c>
       <c r="G269" t="s">
-        <v>1813</v>
+        <v>1817</v>
       </c>
     </row>
     <row r="270" spans="1:7" x14ac:dyDescent="0.25">
@@ -23460,10 +23498,10 @@
         <v>26</v>
       </c>
       <c r="F270" t="s">
-        <v>1721</v>
+        <v>1725</v>
       </c>
       <c r="G270" t="s">
-        <v>1814</v>
+        <v>1818</v>
       </c>
     </row>
     <row r="271" spans="1:7" x14ac:dyDescent="0.25">
@@ -23483,10 +23521,10 @@
         <v>26</v>
       </c>
       <c r="F271" t="s">
-        <v>1721</v>
+        <v>1725</v>
       </c>
       <c r="G271" t="s">
-        <v>1815</v>
+        <v>1819</v>
       </c>
     </row>
     <row r="272" spans="1:7" x14ac:dyDescent="0.25">
@@ -23506,10 +23544,10 @@
         <v>26</v>
       </c>
       <c r="F272" t="s">
-        <v>1721</v>
+        <v>1725</v>
       </c>
       <c r="G272" t="s">
-        <v>1816</v>
+        <v>1820</v>
       </c>
     </row>
     <row r="273" spans="1:7" x14ac:dyDescent="0.25">
@@ -23529,10 +23567,10 @@
         <v>26</v>
       </c>
       <c r="F273" t="s">
-        <v>1721</v>
+        <v>1725</v>
       </c>
       <c r="G273" t="s">
-        <v>1817</v>
+        <v>1821</v>
       </c>
     </row>
     <row r="274" spans="1:7" x14ac:dyDescent="0.25">
@@ -23552,10 +23590,10 @@
         <v>26</v>
       </c>
       <c r="F274" t="s">
-        <v>1721</v>
+        <v>1725</v>
       </c>
       <c r="G274" t="s">
-        <v>1818</v>
+        <v>1822</v>
       </c>
     </row>
     <row r="275" spans="1:7" x14ac:dyDescent="0.25">
@@ -23575,10 +23613,10 @@
         <v>26</v>
       </c>
       <c r="F275" t="s">
-        <v>1721</v>
+        <v>1725</v>
       </c>
       <c r="G275" t="s">
-        <v>1819</v>
+        <v>1823</v>
       </c>
     </row>
     <row r="276" spans="1:7" x14ac:dyDescent="0.25">
@@ -23598,10 +23636,10 @@
         <v>26</v>
       </c>
       <c r="F276" t="s">
-        <v>1721</v>
+        <v>1725</v>
       </c>
       <c r="G276" t="s">
-        <v>1820</v>
+        <v>1824</v>
       </c>
     </row>
     <row r="277" spans="1:7" x14ac:dyDescent="0.25">
@@ -23621,10 +23659,10 @@
         <v>26</v>
       </c>
       <c r="F277" t="s">
-        <v>1721</v>
+        <v>1725</v>
       </c>
       <c r="G277" t="s">
-        <v>1821</v>
+        <v>1825</v>
       </c>
     </row>
     <row r="278" spans="1:7" x14ac:dyDescent="0.25">
@@ -23644,10 +23682,10 @@
         <v>26</v>
       </c>
       <c r="F278" t="s">
-        <v>1721</v>
+        <v>1725</v>
       </c>
       <c r="G278" t="s">
-        <v>1822</v>
+        <v>1826</v>
       </c>
     </row>
     <row r="279" spans="1:7" x14ac:dyDescent="0.25">
@@ -23667,10 +23705,10 @@
         <v>26</v>
       </c>
       <c r="F279" t="s">
-        <v>1721</v>
+        <v>1725</v>
       </c>
       <c r="G279" t="s">
-        <v>1823</v>
+        <v>1827</v>
       </c>
     </row>
     <row r="280" spans="1:7" x14ac:dyDescent="0.25">
@@ -23690,10 +23728,10 @@
         <v>26</v>
       </c>
       <c r="F280" t="s">
-        <v>1721</v>
+        <v>1725</v>
       </c>
       <c r="G280" t="s">
-        <v>1824</v>
+        <v>1828</v>
       </c>
     </row>
     <row r="281" spans="1:7" x14ac:dyDescent="0.25">
@@ -23713,10 +23751,10 @@
         <v>26</v>
       </c>
       <c r="F281" t="s">
-        <v>1721</v>
+        <v>1725</v>
       </c>
       <c r="G281" t="s">
-        <v>1825</v>
+        <v>1829</v>
       </c>
     </row>
     <row r="282" spans="1:7" x14ac:dyDescent="0.25">
@@ -23736,10 +23774,10 @@
         <v>26</v>
       </c>
       <c r="F282" t="s">
-        <v>1721</v>
+        <v>1725</v>
       </c>
       <c r="G282" t="s">
-        <v>1826</v>
+        <v>1830</v>
       </c>
     </row>
     <row r="283" spans="1:7" x14ac:dyDescent="0.25">
@@ -23759,10 +23797,10 @@
         <v>26</v>
       </c>
       <c r="F283" t="s">
-        <v>1721</v>
+        <v>1725</v>
       </c>
       <c r="G283" t="s">
-        <v>1827</v>
+        <v>1831</v>
       </c>
     </row>
     <row r="284" spans="1:7" x14ac:dyDescent="0.25">
@@ -23782,10 +23820,10 @@
         <v>26</v>
       </c>
       <c r="F284" t="s">
-        <v>1721</v>
+        <v>1725</v>
       </c>
       <c r="G284" t="s">
-        <v>1828</v>
+        <v>1832</v>
       </c>
     </row>
     <row r="285" spans="1:7" x14ac:dyDescent="0.25">
@@ -23805,10 +23843,10 @@
         <v>26</v>
       </c>
       <c r="F285" t="s">
-        <v>1721</v>
+        <v>1725</v>
       </c>
       <c r="G285" t="s">
-        <v>1829</v>
+        <v>1833</v>
       </c>
     </row>
     <row r="286" spans="1:7" x14ac:dyDescent="0.25">
@@ -23828,10 +23866,10 @@
         <v>26</v>
       </c>
       <c r="F286" t="s">
-        <v>1721</v>
+        <v>1725</v>
       </c>
       <c r="G286" t="s">
-        <v>1830</v>
+        <v>1834</v>
       </c>
     </row>
     <row r="287" spans="1:7" x14ac:dyDescent="0.25">
@@ -23851,10 +23889,10 @@
         <v>26</v>
       </c>
       <c r="F287" t="s">
-        <v>1721</v>
+        <v>1725</v>
       </c>
       <c r="G287" t="s">
-        <v>1831</v>
+        <v>1835</v>
       </c>
     </row>
     <row r="288" spans="1:7" x14ac:dyDescent="0.25">
@@ -23874,10 +23912,10 @@
         <v>26</v>
       </c>
       <c r="F288" t="s">
-        <v>1721</v>
+        <v>1725</v>
       </c>
       <c r="G288" t="s">
-        <v>1832</v>
+        <v>1836</v>
       </c>
     </row>
     <row r="289" spans="1:7" x14ac:dyDescent="0.25">
@@ -23897,10 +23935,10 @@
         <v>26</v>
       </c>
       <c r="F289" t="s">
-        <v>1721</v>
+        <v>1725</v>
       </c>
       <c r="G289" t="s">
-        <v>1833</v>
+        <v>1837</v>
       </c>
     </row>
     <row r="290" spans="1:7" x14ac:dyDescent="0.25">
@@ -23920,10 +23958,10 @@
         <v>26</v>
       </c>
       <c r="F290" t="s">
-        <v>1721</v>
+        <v>1725</v>
       </c>
       <c r="G290" t="s">
-        <v>1834</v>
+        <v>1838</v>
       </c>
     </row>
     <row r="291" spans="1:7" x14ac:dyDescent="0.25">
@@ -23943,10 +23981,10 @@
         <v>26</v>
       </c>
       <c r="F291" t="s">
-        <v>1721</v>
+        <v>1725</v>
       </c>
       <c r="G291" t="s">
-        <v>1835</v>
+        <v>1839</v>
       </c>
     </row>
     <row r="292" spans="1:7" x14ac:dyDescent="0.25">
@@ -23966,10 +24004,10 @@
         <v>26</v>
       </c>
       <c r="F292" t="s">
-        <v>1721</v>
+        <v>1725</v>
       </c>
       <c r="G292" t="s">
-        <v>1836</v>
+        <v>1840</v>
       </c>
     </row>
     <row r="293" spans="1:7" x14ac:dyDescent="0.25">
@@ -23989,10 +24027,10 @@
         <v>26</v>
       </c>
       <c r="F293" t="s">
-        <v>1721</v>
+        <v>1725</v>
       </c>
       <c r="G293" t="s">
-        <v>1837</v>
+        <v>1841</v>
       </c>
     </row>
     <row r="294" spans="1:7" x14ac:dyDescent="0.25">
@@ -24012,10 +24050,10 @@
         <v>26</v>
       </c>
       <c r="F294" t="s">
-        <v>1721</v>
+        <v>1725</v>
       </c>
       <c r="G294" t="s">
-        <v>1838</v>
+        <v>1842</v>
       </c>
     </row>
     <row r="295" spans="1:7" x14ac:dyDescent="0.25">
@@ -24035,10 +24073,10 @@
         <v>26</v>
       </c>
       <c r="F295" t="s">
-        <v>1721</v>
+        <v>1725</v>
       </c>
       <c r="G295" t="s">
-        <v>1839</v>
+        <v>1843</v>
       </c>
     </row>
     <row r="296" spans="1:7" x14ac:dyDescent="0.25">
@@ -24058,10 +24096,10 @@
         <v>26</v>
       </c>
       <c r="F296" t="s">
-        <v>1721</v>
+        <v>1725</v>
       </c>
       <c r="G296" t="s">
-        <v>1840</v>
+        <v>1844</v>
       </c>
     </row>
     <row r="297" spans="1:7" x14ac:dyDescent="0.25">
@@ -24081,10 +24119,10 @@
         <v>26</v>
       </c>
       <c r="F297" t="s">
-        <v>1721</v>
+        <v>1725</v>
       </c>
       <c r="G297" t="s">
-        <v>1841</v>
+        <v>1845</v>
       </c>
     </row>
     <row r="298" spans="1:7" x14ac:dyDescent="0.25">
@@ -24104,10 +24142,10 @@
         <v>26</v>
       </c>
       <c r="F298" t="s">
-        <v>1721</v>
+        <v>1725</v>
       </c>
       <c r="G298" t="s">
-        <v>1842</v>
+        <v>1846</v>
       </c>
     </row>
     <row r="299" spans="1:7" x14ac:dyDescent="0.25">
@@ -24127,10 +24165,10 @@
         <v>26</v>
       </c>
       <c r="F299" t="s">
-        <v>1721</v>
+        <v>1725</v>
       </c>
       <c r="G299" t="s">
-        <v>1843</v>
+        <v>1847</v>
       </c>
     </row>
     <row r="300" spans="1:7" x14ac:dyDescent="0.25">
@@ -24150,10 +24188,10 @@
         <v>26</v>
       </c>
       <c r="F300" t="s">
-        <v>1721</v>
+        <v>1725</v>
       </c>
       <c r="G300" t="s">
-        <v>1844</v>
+        <v>1848</v>
       </c>
     </row>
     <row r="301" spans="1:7" x14ac:dyDescent="0.25">
@@ -24173,10 +24211,10 @@
         <v>26</v>
       </c>
       <c r="F301" t="s">
-        <v>1721</v>
+        <v>1725</v>
       </c>
       <c r="G301" t="s">
-        <v>1845</v>
+        <v>1849</v>
       </c>
     </row>
     <row r="302" spans="1:7" x14ac:dyDescent="0.25">
@@ -24196,10 +24234,10 @@
         <v>26</v>
       </c>
       <c r="F302" t="s">
-        <v>1721</v>
+        <v>1725</v>
       </c>
       <c r="G302" t="s">
-        <v>1846</v>
+        <v>1850</v>
       </c>
     </row>
     <row r="303" spans="1:7" x14ac:dyDescent="0.25">
@@ -24219,10 +24257,10 @@
         <v>26</v>
       </c>
       <c r="F303" t="s">
-        <v>1721</v>
+        <v>1725</v>
       </c>
       <c r="G303" t="s">
-        <v>1847</v>
+        <v>1851</v>
       </c>
     </row>
     <row r="304" spans="1:7" x14ac:dyDescent="0.25">
@@ -24242,10 +24280,10 @@
         <v>26</v>
       </c>
       <c r="F304" t="s">
-        <v>1721</v>
+        <v>1725</v>
       </c>
       <c r="G304" t="s">
-        <v>1848</v>
+        <v>1852</v>
       </c>
     </row>
     <row r="305" spans="1:7" x14ac:dyDescent="0.25">
@@ -24265,10 +24303,10 @@
         <v>26</v>
       </c>
       <c r="F305" t="s">
-        <v>1721</v>
+        <v>1725</v>
       </c>
       <c r="G305" t="s">
-        <v>1849</v>
+        <v>1853</v>
       </c>
     </row>
     <row r="306" spans="1:7" x14ac:dyDescent="0.25">
@@ -24288,10 +24326,10 @@
         <v>26</v>
       </c>
       <c r="F306" t="s">
-        <v>1721</v>
+        <v>1725</v>
       </c>
       <c r="G306" t="s">
-        <v>1850</v>
+        <v>1854</v>
       </c>
     </row>
     <row r="307" spans="1:7" x14ac:dyDescent="0.25">
@@ -24311,10 +24349,10 @@
         <v>26</v>
       </c>
       <c r="F307" t="s">
-        <v>1721</v>
+        <v>1725</v>
       </c>
       <c r="G307" t="s">
-        <v>1851</v>
+        <v>1855</v>
       </c>
     </row>
     <row r="308" spans="1:7" x14ac:dyDescent="0.25">
@@ -24334,10 +24372,10 @@
         <v>26</v>
       </c>
       <c r="F308" t="s">
-        <v>1721</v>
+        <v>1725</v>
       </c>
       <c r="G308" t="s">
-        <v>1852</v>
+        <v>1856</v>
       </c>
     </row>
     <row r="309" spans="1:7" x14ac:dyDescent="0.25">
@@ -24357,10 +24395,10 @@
         <v>26</v>
       </c>
       <c r="F309" t="s">
-        <v>1721</v>
+        <v>1725</v>
       </c>
       <c r="G309" t="s">
-        <v>1853</v>
+        <v>1857</v>
       </c>
     </row>
     <row r="310" spans="1:7" x14ac:dyDescent="0.25">
@@ -24380,10 +24418,10 @@
         <v>26</v>
       </c>
       <c r="F310" t="s">
-        <v>1721</v>
+        <v>1725</v>
       </c>
       <c r="G310" t="s">
-        <v>1854</v>
+        <v>1858</v>
       </c>
     </row>
     <row r="311" spans="1:7" x14ac:dyDescent="0.25">
@@ -24403,10 +24441,10 @@
         <v>26</v>
       </c>
       <c r="F311" t="s">
-        <v>1721</v>
+        <v>1725</v>
       </c>
       <c r="G311" t="s">
-        <v>1855</v>
+        <v>1859</v>
       </c>
     </row>
     <row r="312" spans="1:7" x14ac:dyDescent="0.25">
@@ -24426,10 +24464,10 @@
         <v>26</v>
       </c>
       <c r="F312" t="s">
-        <v>1721</v>
+        <v>1725</v>
       </c>
       <c r="G312" t="s">
-        <v>1856</v>
+        <v>1860</v>
       </c>
     </row>
     <row r="313" spans="1:7" x14ac:dyDescent="0.25">
@@ -24449,10 +24487,10 @@
         <v>26</v>
       </c>
       <c r="F313" t="s">
-        <v>1721</v>
+        <v>1725</v>
       </c>
       <c r="G313" t="s">
-        <v>1857</v>
+        <v>1861</v>
       </c>
     </row>
     <row r="314" spans="1:7" x14ac:dyDescent="0.25">
@@ -24472,10 +24510,10 @@
         <v>26</v>
       </c>
       <c r="F314" t="s">
-        <v>1721</v>
+        <v>1725</v>
       </c>
       <c r="G314" t="s">
-        <v>1858</v>
+        <v>1862</v>
       </c>
     </row>
     <row r="315" spans="1:7" x14ac:dyDescent="0.25">
@@ -24495,10 +24533,10 @@
         <v>86</v>
       </c>
       <c r="F315" t="s">
-        <v>1721</v>
+        <v>1725</v>
       </c>
       <c r="G315" t="s">
-        <v>1859</v>
+        <v>1863</v>
       </c>
     </row>
     <row r="316" spans="1:7" x14ac:dyDescent="0.25">
@@ -24518,10 +24556,10 @@
         <v>86</v>
       </c>
       <c r="F316" t="s">
-        <v>1721</v>
+        <v>1725</v>
       </c>
       <c r="G316" t="s">
-        <v>1860</v>
+        <v>1864</v>
       </c>
     </row>
     <row r="317" spans="1:7" x14ac:dyDescent="0.25">
@@ -24541,10 +24579,10 @@
         <v>86</v>
       </c>
       <c r="F317" t="s">
-        <v>1721</v>
+        <v>1725</v>
       </c>
       <c r="G317" t="s">
-        <v>1861</v>
+        <v>1865</v>
       </c>
     </row>
     <row r="318" spans="1:7" x14ac:dyDescent="0.25">
@@ -24564,10 +24602,10 @@
         <v>26</v>
       </c>
       <c r="F318" t="s">
-        <v>1721</v>
+        <v>1725</v>
       </c>
       <c r="G318" t="s">
-        <v>1862</v>
+        <v>1866</v>
       </c>
     </row>
     <row r="319" spans="1:7" x14ac:dyDescent="0.25">
@@ -24587,10 +24625,10 @@
         <v>26</v>
       </c>
       <c r="F319" t="s">
-        <v>1721</v>
+        <v>1725</v>
       </c>
       <c r="G319" t="s">
-        <v>1863</v>
+        <v>1867</v>
       </c>
     </row>
     <row r="320" spans="1:7" x14ac:dyDescent="0.25">
@@ -24610,10 +24648,10 @@
         <v>26</v>
       </c>
       <c r="F320" t="s">
-        <v>1721</v>
+        <v>1725</v>
       </c>
       <c r="G320" t="s">
-        <v>1864</v>
+        <v>1868</v>
       </c>
     </row>
     <row r="321" spans="1:7" x14ac:dyDescent="0.25">
@@ -24633,10 +24671,10 @@
         <v>86</v>
       </c>
       <c r="F321" t="s">
-        <v>1721</v>
+        <v>1725</v>
       </c>
       <c r="G321" t="s">
-        <v>1865</v>
+        <v>1869</v>
       </c>
     </row>
     <row r="322" spans="1:7" x14ac:dyDescent="0.25">
@@ -24656,10 +24694,10 @@
         <v>26</v>
       </c>
       <c r="F322" t="s">
-        <v>1721</v>
+        <v>1725</v>
       </c>
       <c r="G322" t="s">
-        <v>1866</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="323" spans="1:7" x14ac:dyDescent="0.25">
@@ -24679,10 +24717,10 @@
         <v>26</v>
       </c>
       <c r="F323" t="s">
-        <v>1721</v>
+        <v>1725</v>
       </c>
       <c r="G323" t="s">
-        <v>1867</v>
+        <v>1871</v>
       </c>
     </row>
     <row r="324" spans="1:7" x14ac:dyDescent="0.25">
@@ -24702,10 +24740,10 @@
         <v>26</v>
       </c>
       <c r="F324" t="s">
-        <v>1721</v>
+        <v>1725</v>
       </c>
       <c r="G324" t="s">
-        <v>1868</v>
+        <v>1872</v>
       </c>
     </row>
     <row r="325" spans="1:7" x14ac:dyDescent="0.25">
@@ -24716,7 +24754,7 @@
         <v>1107</v>
       </c>
       <c r="C325" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="D325" t="s">
         <v>86</v>
@@ -24725,10 +24763,10 @@
         <v>26</v>
       </c>
       <c r="F325" t="s">
-        <v>1721</v>
+        <v>1725</v>
       </c>
       <c r="G325" t="s">
-        <v>1869</v>
+        <v>1873</v>
       </c>
     </row>
     <row r="326" spans="1:7" x14ac:dyDescent="0.25">
@@ -24748,10 +24786,10 @@
         <v>26</v>
       </c>
       <c r="F326" t="s">
-        <v>1721</v>
+        <v>1725</v>
       </c>
       <c r="G326" t="s">
-        <v>1870</v>
+        <v>1874</v>
       </c>
     </row>
     <row r="327" spans="1:7" x14ac:dyDescent="0.25">
@@ -24771,10 +24809,10 @@
         <v>26</v>
       </c>
       <c r="F327" t="s">
-        <v>1721</v>
+        <v>1725</v>
       </c>
       <c r="G327" t="s">
-        <v>1871</v>
+        <v>1875</v>
       </c>
     </row>
     <row r="328" spans="1:7" x14ac:dyDescent="0.25">
@@ -24794,10 +24832,10 @@
         <v>26</v>
       </c>
       <c r="F328" t="s">
-        <v>1721</v>
+        <v>1725</v>
       </c>
       <c r="G328" t="s">
-        <v>1872</v>
+        <v>1876</v>
       </c>
     </row>
     <row r="329" spans="1:7" x14ac:dyDescent="0.25">
@@ -24817,10 +24855,10 @@
         <v>26</v>
       </c>
       <c r="F329" t="s">
-        <v>1721</v>
+        <v>1725</v>
       </c>
       <c r="G329" t="s">
-        <v>1873</v>
+        <v>1877</v>
       </c>
     </row>
     <row r="330" spans="1:7" x14ac:dyDescent="0.25">
@@ -24840,10 +24878,10 @@
         <v>86</v>
       </c>
       <c r="F330" t="s">
-        <v>1721</v>
+        <v>1725</v>
       </c>
       <c r="G330" t="s">
-        <v>1874</v>
+        <v>1878</v>
       </c>
     </row>
     <row r="331" spans="1:7" x14ac:dyDescent="0.25">
@@ -24863,10 +24901,56 @@
         <v>26</v>
       </c>
       <c r="F331" t="s">
-        <v>1721</v>
+        <v>1725</v>
       </c>
       <c r="G331" t="s">
-        <v>1875</v>
+        <v>1879</v>
+      </c>
+    </row>
+    <row r="332" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A332" t="s">
+        <v>27</v>
+      </c>
+      <c r="B332" t="s">
+        <v>1149</v>
+      </c>
+      <c r="C332" t="s">
+        <v>1147</v>
+      </c>
+      <c r="D332" t="s">
+        <v>26</v>
+      </c>
+      <c r="E332" t="s">
+        <v>26</v>
+      </c>
+      <c r="F332" t="s">
+        <v>1725</v>
+      </c>
+      <c r="G332" t="s">
+        <v>1880</v>
+      </c>
+    </row>
+    <row r="333" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A333" t="s">
+        <v>27</v>
+      </c>
+      <c r="B333" t="s">
+        <v>1149</v>
+      </c>
+      <c r="C333" t="s">
+        <v>1190</v>
+      </c>
+      <c r="D333" t="s">
+        <v>26</v>
+      </c>
+      <c r="E333" t="s">
+        <v>26</v>
+      </c>
+      <c r="F333" t="s">
+        <v>1725</v>
+      </c>
+      <c r="G333" t="s">
+        <v>1881</v>
       </c>
     </row>
   </sheetData>
@@ -24880,7 +24964,7 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>1876</v>
+        <v>1882</v>
       </c>
       <c r="B1"/>
       <c r="C1"/>
@@ -24888,7 +24972,7 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1877</v>
+        <v>1883</v>
       </c>
       <c r="B2"/>
       <c r="C2"/>
@@ -24899,181 +24983,181 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>1878</v>
+        <v>1884</v>
       </c>
       <c r="C3" t="s">
-        <v>1879</v>
+        <v>1885</v>
       </c>
       <c r="D3" t="s">
-        <v>1880</v>
+        <v>1886</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1881</v>
+        <v>1887</v>
       </c>
       <c r="B4" t="s">
-        <v>1882</v>
+        <v>1888</v>
       </c>
       <c r="C4" t="s">
-        <v>1883</v>
+        <v>1889</v>
       </c>
       <c r="D4" t="s">
-        <v>1884</v>
+        <v>1890</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1885</v>
+        <v>1891</v>
       </c>
       <c r="B5" t="s">
-        <v>1882</v>
+        <v>1888</v>
       </c>
       <c r="C5" t="s">
-        <v>1886</v>
+        <v>1892</v>
       </c>
       <c r="D5" t="s">
-        <v>1887</v>
+        <v>1893</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>1894</v>
+      </c>
+      <c r="B6" t="s">
         <v>1888</v>
       </c>
-      <c r="B6" t="s">
-        <v>1882</v>
-      </c>
       <c r="C6" t="s">
-        <v>1889</v>
+        <v>1895</v>
       </c>
       <c r="D6" t="s">
-        <v>1890</v>
+        <v>1896</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>1891</v>
+        <v>1897</v>
       </c>
       <c r="B7" t="s">
-        <v>1882</v>
+        <v>1888</v>
       </c>
       <c r="C7" t="s">
-        <v>1892</v>
+        <v>1898</v>
       </c>
       <c r="D7" t="s">
-        <v>1893</v>
+        <v>1899</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>1894</v>
+        <v>1900</v>
       </c>
       <c r="B8" t="s">
-        <v>1882</v>
+        <v>1888</v>
       </c>
       <c r="C8" t="s">
-        <v>1895</v>
+        <v>1901</v>
       </c>
       <c r="D8" t="s">
-        <v>1896</v>
+        <v>1902</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>1897</v>
+        <v>1903</v>
       </c>
       <c r="B9" t="s">
-        <v>1898</v>
+        <v>1904</v>
       </c>
       <c r="C9" t="s">
-        <v>1899</v>
+        <v>1905</v>
       </c>
       <c r="D9" t="s">
-        <v>1900</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>1901</v>
+        <v>1907</v>
       </c>
       <c r="B10" t="s">
-        <v>1898</v>
+        <v>1904</v>
       </c>
       <c r="C10" t="s">
-        <v>1902</v>
+        <v>1908</v>
       </c>
       <c r="D10" t="s">
-        <v>1903</v>
+        <v>1909</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>1910</v>
+      </c>
+      <c r="B11" t="s">
         <v>1904</v>
       </c>
-      <c r="B11" t="s">
-        <v>1898</v>
-      </c>
       <c r="C11" t="s">
-        <v>1905</v>
+        <v>1911</v>
       </c>
       <c r="D11" t="s">
-        <v>1906</v>
+        <v>1912</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>1907</v>
+        <v>1913</v>
       </c>
       <c r="B12" t="s">
-        <v>1908</v>
+        <v>1914</v>
       </c>
       <c r="C12" t="s">
-        <v>1909</v>
+        <v>1915</v>
       </c>
       <c r="D12" t="s">
-        <v>1910</v>
+        <v>1916</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>1911</v>
+        <v>1917</v>
       </c>
       <c r="B13" t="s">
-        <v>1908</v>
+        <v>1914</v>
       </c>
       <c r="C13" t="s">
-        <v>1912</v>
+        <v>1918</v>
       </c>
       <c r="D13" t="s">
-        <v>1913</v>
+        <v>1919</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>1914</v>
+        <v>1920</v>
       </c>
       <c r="B14" t="s">
         <v>889</v>
       </c>
       <c r="C14" t="s">
-        <v>1915</v>
+        <v>1921</v>
       </c>
       <c r="D14" t="s">
-        <v>1916</v>
+        <v>1922</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>1917</v>
+        <v>1923</v>
       </c>
       <c r="B15" t="s">
         <v>889</v>
       </c>
       <c r="C15" t="s">
-        <v>1918</v>
+        <v>1924</v>
       </c>
       <c r="D15" t="s">
-        <v>1919</v>
+        <v>1925</v>
       </c>
     </row>
   </sheetData>
@@ -25092,7 +25176,7 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>1920</v>
+        <v>1926</v>
       </c>
       <c r="B1"/>
       <c r="C1"/>
@@ -25100,133 +25184,133 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>1921</v>
+        <v>1927</v>
       </c>
       <c r="B3" t="s">
-        <v>1922</v>
+        <v>1928</v>
       </c>
       <c r="C3" t="s">
-        <v>1923</v>
+        <v>1929</v>
       </c>
       <c r="D3" t="s">
-        <v>1924</v>
+        <v>1930</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1368</v>
+        <v>1369</v>
       </c>
       <c r="B4" t="s">
-        <v>1925</v>
+        <v>1931</v>
       </c>
       <c r="C4" t="s">
-        <v>1926</v>
+        <v>1932</v>
       </c>
       <c r="D4" t="s">
-        <v>1927</v>
+        <v>1933</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1373</v>
+        <v>1374</v>
       </c>
       <c r="B5" t="s">
-        <v>1928</v>
+        <v>1934</v>
       </c>
       <c r="C5" t="s">
-        <v>1929</v>
+        <v>1935</v>
       </c>
       <c r="D5" t="s">
-        <v>1930</v>
+        <v>1936</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>1377</v>
+        <v>1378</v>
       </c>
       <c r="B6" t="s">
-        <v>1931</v>
+        <v>1937</v>
       </c>
       <c r="C6" t="s">
-        <v>1932</v>
+        <v>1938</v>
       </c>
       <c r="D6" t="s">
-        <v>1933</v>
+        <v>1939</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>1381</v>
+        <v>1382</v>
       </c>
       <c r="B7" t="s">
-        <v>1934</v>
+        <v>1940</v>
       </c>
       <c r="C7" t="s">
-        <v>1935</v>
+        <v>1941</v>
       </c>
       <c r="D7" t="s">
-        <v>1936</v>
+        <v>1942</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>1385</v>
+        <v>1386</v>
       </c>
       <c r="B8" t="s">
-        <v>1937</v>
+        <v>1943</v>
       </c>
       <c r="C8" t="s">
-        <v>1938</v>
+        <v>1944</v>
       </c>
       <c r="D8" t="s">
-        <v>1939</v>
+        <v>1945</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>1389</v>
+        <v>1390</v>
       </c>
       <c r="B9" t="s">
-        <v>1940</v>
+        <v>1946</v>
       </c>
       <c r="C9" t="s">
-        <v>1941</v>
+        <v>1947</v>
       </c>
       <c r="D9" t="s">
-        <v>1942</v>
+        <v>1948</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>1393</v>
+        <v>1394</v>
       </c>
       <c r="B10" t="s">
-        <v>1943</v>
+        <v>1949</v>
       </c>
       <c r="C10" t="s">
-        <v>1944</v>
+        <v>1950</v>
       </c>
       <c r="D10" t="s">
-        <v>1945</v>
+        <v>1951</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>1397</v>
+        <v>1398</v>
       </c>
       <c r="B11" t="s">
-        <v>1946</v>
+        <v>1952</v>
       </c>
       <c r="C11" t="s">
-        <v>1947</v>
+        <v>1953</v>
       </c>
       <c r="D11" t="s">
-        <v>1948</v>
+        <v>1954</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>1949</v>
+        <v>1955</v>
       </c>
       <c r="B13"/>
       <c r="C13"/>
@@ -25234,72 +25318,72 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>1950</v>
+        <v>1956</v>
       </c>
       <c r="B14" t="s">
         <v>28</v>
       </c>
       <c r="C14" t="s">
-        <v>1951</v>
+        <v>1957</v>
       </c>
       <c r="D14" t="s">
-        <v>1952</v>
+        <v>1958</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>1953</v>
+        <v>1959</v>
       </c>
       <c r="B15" t="s">
         <v>96</v>
       </c>
       <c r="C15" t="s">
-        <v>1954</v>
+        <v>1960</v>
       </c>
       <c r="D15" t="s">
-        <v>1955</v>
+        <v>1961</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>1956</v>
+        <v>1962</v>
       </c>
       <c r="B16" t="s">
         <v>96</v>
       </c>
       <c r="C16" t="s">
-        <v>1957</v>
+        <v>1963</v>
       </c>
       <c r="D16" t="s">
-        <v>1958</v>
+        <v>1964</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>1959</v>
+        <v>1965</v>
       </c>
       <c r="B17" t="s">
         <v>96</v>
       </c>
       <c r="C17" t="s">
-        <v>1960</v>
+        <v>1966</v>
       </c>
       <c r="D17" t="s">
-        <v>1961</v>
+        <v>1967</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>1962</v>
+        <v>1968</v>
       </c>
       <c r="B18" t="s">
-        <v>1963</v>
+        <v>1969</v>
       </c>
       <c r="C18" t="s">
-        <v>1964</v>
+        <v>1970</v>
       </c>
       <c r="D18" t="s">
-        <v>1965</v>
+        <v>1971</v>
       </c>
     </row>
   </sheetData>
@@ -25318,7 +25402,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>1966</v>
+        <v>1972</v>
       </c>
       <c r="B1"/>
       <c r="C1"/>
@@ -25328,7 +25412,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1967</v>
+        <v>1973</v>
       </c>
       <c r="B2"/>
       <c r="C2"/>
@@ -25338,99 +25422,99 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1968</v>
+        <v>1974</v>
       </c>
       <c r="B4" t="s">
-        <v>1969</v>
+        <v>1975</v>
       </c>
       <c r="C4" t="s">
-        <v>1970</v>
+        <v>1976</v>
       </c>
       <c r="D4" t="s">
-        <v>1971</v>
+        <v>1977</v>
       </c>
       <c r="E4" t="s">
-        <v>1972</v>
+        <v>1978</v>
       </c>
       <c r="F4" t="s">
-        <v>1973</v>
+        <v>1979</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1974</v>
+        <v>1980</v>
       </c>
       <c r="B5" t="s">
-        <v>1975</v>
+        <v>1981</v>
       </c>
       <c r="C5" t="s">
-        <v>1976</v>
+        <v>1982</v>
       </c>
       <c r="D5" t="s">
-        <v>1977</v>
+        <v>1983</v>
       </c>
       <c r="E5" t="s">
-        <v>1978</v>
+        <v>1984</v>
       </c>
       <c r="F5" t="s">
-        <v>1979</v>
+        <v>1985</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>1980</v>
+        <v>1986</v>
       </c>
       <c r="B6" t="s">
-        <v>1981</v>
+        <v>1987</v>
       </c>
       <c r="C6" t="s">
-        <v>1982</v>
+        <v>1988</v>
       </c>
       <c r="D6" t="s">
-        <v>1983</v>
+        <v>1989</v>
       </c>
       <c r="E6" t="s">
-        <v>1984</v>
+        <v>1990</v>
       </c>
       <c r="F6" t="s">
-        <v>1985</v>
+        <v>1991</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>1986</v>
+        <v>1992</v>
       </c>
       <c r="B7" t="s">
-        <v>1981</v>
+        <v>1987</v>
       </c>
       <c r="C7" t="s">
-        <v>1987</v>
+        <v>1993</v>
       </c>
       <c r="D7" t="s">
-        <v>1988</v>
+        <v>1994</v>
       </c>
       <c r="E7" t="s">
-        <v>1989</v>
+        <v>1995</v>
       </c>
       <c r="F7" t="s">
-        <v>1990</v>
+        <v>1996</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>1991</v>
+        <v>1997</v>
       </c>
       <c r="B8" t="s">
-        <v>1992</v>
+        <v>1998</v>
       </c>
       <c r="C8" t="s">
-        <v>1993</v>
+        <v>1999</v>
       </c>
       <c r="D8" t="s">
-        <v>1994</v>
+        <v>2000</v>
       </c>
       <c r="E8" t="s">
-        <v>1995</v>
+        <v>2001</v>
       </c>
       <c r="F8" t="s">
         <v>636</v>
@@ -25438,19 +25522,19 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>1996</v>
+        <v>2002</v>
       </c>
       <c r="B9" t="s">
-        <v>1997</v>
+        <v>2003</v>
       </c>
       <c r="C9" t="s">
-        <v>1998</v>
+        <v>2004</v>
       </c>
       <c r="D9" t="s">
-        <v>1999</v>
+        <v>2005</v>
       </c>
       <c r="E9" t="s">
-        <v>2000</v>
+        <v>2006</v>
       </c>
       <c r="F9" t="s">
         <v>375</v>
@@ -25458,39 +25542,39 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>2001</v>
+        <v>2007</v>
       </c>
       <c r="B10" t="s">
-        <v>2002</v>
+        <v>2008</v>
       </c>
       <c r="C10" t="s">
-        <v>2003</v>
+        <v>2009</v>
       </c>
       <c r="D10" t="s">
-        <v>2004</v>
+        <v>2010</v>
       </c>
       <c r="E10" t="s">
-        <v>2005</v>
+        <v>2011</v>
       </c>
       <c r="F10" t="s">
-        <v>2006</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>2007</v>
+        <v>2013</v>
       </c>
       <c r="B11" t="s">
-        <v>2008</v>
+        <v>2014</v>
       </c>
       <c r="C11" t="s">
-        <v>2009</v>
+        <v>2015</v>
       </c>
       <c r="D11" t="s">
-        <v>2010</v>
+        <v>2016</v>
       </c>
       <c r="E11" t="s">
-        <v>2011</v>
+        <v>2017</v>
       </c>
       <c r="F11" t="s">
         <v>47</v>
@@ -25498,99 +25582,99 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>2012</v>
+        <v>2018</v>
       </c>
       <c r="B12" t="s">
-        <v>2013</v>
+        <v>2019</v>
       </c>
       <c r="C12" t="s">
-        <v>2014</v>
+        <v>2020</v>
       </c>
       <c r="D12" t="s">
-        <v>2015</v>
+        <v>2021</v>
       </c>
       <c r="E12" t="s">
-        <v>2016</v>
+        <v>2022</v>
       </c>
       <c r="F12" t="s">
-        <v>2017</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>2018</v>
+        <v>2024</v>
       </c>
       <c r="B13" t="s">
-        <v>2019</v>
+        <v>2025</v>
       </c>
       <c r="C13" t="s">
-        <v>2020</v>
+        <v>2026</v>
       </c>
       <c r="D13" t="s">
-        <v>2021</v>
+        <v>2027</v>
       </c>
       <c r="E13" t="s">
-        <v>2022</v>
+        <v>2028</v>
       </c>
       <c r="F13" t="s">
-        <v>2023</v>
+        <v>2029</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>2024</v>
+        <v>2030</v>
       </c>
       <c r="B14" t="s">
-        <v>2025</v>
+        <v>2031</v>
       </c>
       <c r="C14" t="s">
-        <v>2026</v>
+        <v>2032</v>
       </c>
       <c r="D14" t="s">
-        <v>2027</v>
+        <v>2033</v>
       </c>
       <c r="E14" t="s">
-        <v>2028</v>
+        <v>2034</v>
       </c>
       <c r="F14" t="s">
-        <v>2029</v>
+        <v>2035</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>2030</v>
+        <v>2036</v>
       </c>
       <c r="B15" t="s">
-        <v>2031</v>
+        <v>2037</v>
       </c>
       <c r="C15" t="s">
-        <v>2032</v>
+        <v>2038</v>
       </c>
       <c r="D15" t="s">
-        <v>2033</v>
+        <v>2039</v>
       </c>
       <c r="E15" t="s">
-        <v>2034</v>
+        <v>2040</v>
       </c>
       <c r="F15" t="s">
-        <v>2035</v>
+        <v>2041</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>2036</v>
+        <v>2042</v>
       </c>
       <c r="B16" t="s">
-        <v>2037</v>
+        <v>2043</v>
       </c>
       <c r="C16" t="s">
-        <v>2038</v>
+        <v>2044</v>
       </c>
       <c r="D16" t="s">
-        <v>2039</v>
+        <v>2045</v>
       </c>
       <c r="E16" t="s">
-        <v>2040</v>
+        <v>2046</v>
       </c>
       <c r="F16" t="s">
         <v>209</v>
@@ -25598,19 +25682,19 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>2041</v>
+        <v>2047</v>
       </c>
       <c r="B17" t="s">
-        <v>2042</v>
+        <v>2048</v>
       </c>
       <c r="C17" t="s">
-        <v>2043</v>
+        <v>2049</v>
       </c>
       <c r="D17" t="s">
-        <v>2044</v>
+        <v>2050</v>
       </c>
       <c r="E17" t="s">
-        <v>2045</v>
+        <v>2051</v>
       </c>
       <c r="F17" t="s">
         <v>384</v>
@@ -25632,7 +25716,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>2046</v>
+        <v>2052</v>
       </c>
       <c r="B1"/>
       <c r="C1"/>
@@ -25642,7 +25726,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>2047</v>
+        <v>2053</v>
       </c>
       <c r="B2"/>
       <c r="C2"/>
@@ -25652,162 +25736,162 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>2048</v>
+        <v>2054</v>
       </c>
       <c r="B4" t="s">
-        <v>1946</v>
+        <v>1952</v>
       </c>
       <c r="C4" t="s">
-        <v>2049</v>
+        <v>2055</v>
       </c>
       <c r="D4" t="s">
-        <v>2050</v>
+        <v>2056</v>
       </c>
       <c r="E4" t="s">
-        <v>1365</v>
+        <v>1366</v>
       </c>
       <c r="F4" t="s">
-        <v>2051</v>
+        <v>2057</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1368</v>
+        <v>1369</v>
       </c>
       <c r="B5" t="s">
-        <v>2052</v>
+        <v>2058</v>
       </c>
       <c r="C5" t="s">
-        <v>2053</v>
+        <v>2059</v>
       </c>
       <c r="D5" t="s">
-        <v>2054</v>
+        <v>2060</v>
       </c>
       <c r="E5" t="s">
-        <v>2055</v>
+        <v>2061</v>
       </c>
       <c r="F5" t="s">
-        <v>2056</v>
+        <v>2062</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>1373</v>
+        <v>1374</v>
       </c>
       <c r="B6" t="s">
-        <v>2057</v>
+        <v>2063</v>
       </c>
       <c r="C6" t="s">
-        <v>2058</v>
+        <v>2064</v>
       </c>
       <c r="D6" t="s">
-        <v>2059</v>
+        <v>2065</v>
       </c>
       <c r="E6" t="s">
-        <v>2060</v>
+        <v>2066</v>
       </c>
       <c r="F6" t="s">
-        <v>2056</v>
+        <v>2062</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>1377</v>
+        <v>1378</v>
       </c>
       <c r="B7" t="s">
-        <v>2061</v>
+        <v>2067</v>
       </c>
       <c r="C7" t="s">
+        <v>2068</v>
+      </c>
+      <c r="D7" t="s">
+        <v>2069</v>
+      </c>
+      <c r="E7" t="s">
+        <v>2070</v>
+      </c>
+      <c r="F7" t="s">
         <v>2062</v>
-      </c>
-      <c r="D7" t="s">
-        <v>2063</v>
-      </c>
-      <c r="E7" t="s">
-        <v>2064</v>
-      </c>
-      <c r="F7" t="s">
-        <v>2056</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>1381</v>
+        <v>1382</v>
       </c>
       <c r="B8" t="s">
-        <v>2065</v>
+        <v>2071</v>
       </c>
       <c r="C8" t="s">
-        <v>2066</v>
+        <v>2072</v>
       </c>
       <c r="D8" t="s">
-        <v>2067</v>
+        <v>2073</v>
       </c>
       <c r="E8" t="s">
-        <v>2068</v>
+        <v>2074</v>
       </c>
       <c r="F8" t="s">
-        <v>2056</v>
+        <v>2062</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>1385</v>
+        <v>1386</v>
       </c>
       <c r="B9" t="s">
-        <v>2069</v>
+        <v>2075</v>
       </c>
       <c r="C9" t="s">
-        <v>2070</v>
+        <v>2076</v>
       </c>
       <c r="D9" t="s">
-        <v>2071</v>
+        <v>2077</v>
       </c>
       <c r="E9" t="s">
         <v>889</v>
       </c>
       <c r="F9" t="s">
-        <v>2072</v>
+        <v>2078</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>1389</v>
+        <v>1390</v>
       </c>
       <c r="B10" t="s">
-        <v>2073</v>
+        <v>2079</v>
       </c>
       <c r="C10" t="s">
-        <v>2074</v>
+        <v>2080</v>
       </c>
       <c r="D10" t="s">
-        <v>2075</v>
+        <v>2081</v>
       </c>
       <c r="E10" t="s">
-        <v>2076</v>
+        <v>2082</v>
       </c>
       <c r="F10" t="s">
-        <v>2072</v>
+        <v>2078</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>1393</v>
+        <v>1394</v>
       </c>
       <c r="B11" t="s">
-        <v>2077</v>
+        <v>2083</v>
       </c>
       <c r="C11" t="s">
-        <v>2078</v>
+        <v>2084</v>
       </c>
       <c r="D11" t="s">
-        <v>2079</v>
+        <v>2085</v>
       </c>
       <c r="E11" t="s">
-        <v>2080</v>
+        <v>2086</v>
       </c>
       <c r="F11" t="s">
-        <v>2081</v>
+        <v>2087</v>
       </c>
     </row>
   </sheetData>
